--- a/data/BPSO.MI.xlsx
+++ b/data/BPSO.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1956" uniqueCount="1956">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1957" uniqueCount="1957">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,25 +44,25 @@
     <t xml:space="preserve">BPSO.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80963706970215</t>
+    <t xml:space="preserve">2.80963730812073</t>
   </si>
   <si>
     <t xml:space="preserve">2.74855828285217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71246576309204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63611674308777</t>
+    <t xml:space="preserve">2.71246600151062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63611698150635</t>
   </si>
   <si>
     <t xml:space="preserve">2.60835409164429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69303226470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69858455657959</t>
+    <t xml:space="preserve">2.69303178787231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69858431816101</t>
   </si>
   <si>
     <t xml:space="preserve">2.61112999916077</t>
@@ -71,76 +71,76 @@
     <t xml:space="preserve">2.51257061958313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4556565284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2668662071228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38069534301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40568208694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36542582511902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51951122283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44455122947693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35570883750916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43899869918823</t>
+    <t xml:space="preserve">2.45565629005432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26686644554138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38069558143616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40568232536316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3654260635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51951146125793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44455075263977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35570859909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43899893760681</t>
   </si>
   <si>
     <t xml:space="preserve">2.40429425239563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32100510597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22105717658997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23216247558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20995187759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04059600830078</t>
+    <t xml:space="preserve">2.32100486755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22105693817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23216223716736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20995211601257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04059624671936</t>
   </si>
   <si>
     <t xml:space="preserve">2.06280660629272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14332032203674</t>
+    <t xml:space="preserve">2.14332008361816</t>
   </si>
   <si>
     <t xml:space="preserve">2.07668805122375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1821882724762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22522163391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27797198295593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19329380989075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16553044319153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24604439735413</t>
+    <t xml:space="preserve">2.18218803405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22522211074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27797150611877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19329357147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16553020477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24604415893555</t>
   </si>
   <si>
     <t xml:space="preserve">2.18635272979736</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">2.17663598060608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21550488471985</t>
+    <t xml:space="preserve">2.21550464630127</t>
   </si>
   <si>
     <t xml:space="preserve">2.25992560386658</t>
@@ -164,7 +164,7 @@
     <t xml:space="preserve">2.38208365440369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37514305114746</t>
+    <t xml:space="preserve">2.3751425743103</t>
   </si>
   <si>
     <t xml:space="preserve">2.24187970161438</t>
@@ -176,73 +176,73 @@
     <t xml:space="preserve">2.25020813941956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31961631774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43344497680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35848498344421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30156993865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34599184989929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3598735332489</t>
+    <t xml:space="preserve">2.31961679458618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43344521522522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35848546028137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30157017707825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34599161148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35987329483032</t>
   </si>
   <si>
     <t xml:space="preserve">2.39318871498108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29324126243591</t>
+    <t xml:space="preserve">2.29324102401733</t>
   </si>
   <si>
     <t xml:space="preserve">2.23771524429321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18774080276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.139155626297</t>
+    <t xml:space="preserve">2.18774056434631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13915586471558</t>
   </si>
   <si>
     <t xml:space="preserve">2.14748454093933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12110948562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06974697113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01283264160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01838564872742</t>
+    <t xml:space="preserve">2.1211097240448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06974720954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01283288002014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01838541030884</t>
   </si>
   <si>
     <t xml:space="preserve">2.07113528251648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11694550514221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12527370452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22799825668335</t>
+    <t xml:space="preserve">2.11694502830505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12527394294739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22799801826477</t>
   </si>
   <si>
     <t xml:space="preserve">2.30295825004578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23910331726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29046511650085</t>
+    <t xml:space="preserve">2.23910307884216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29046487808228</t>
   </si>
   <si>
     <t xml:space="preserve">2.3321099281311</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">2.2793595790863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32378125190735</t>
+    <t xml:space="preserve">2.32378149032593</t>
   </si>
   <si>
     <t xml:space="preserve">2.30851101875305</t>
@@ -263,25 +263,25 @@
     <t xml:space="preserve">2.26131391525269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.234938621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15720152854919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11139225959778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08224034309387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09889936447144</t>
+    <t xml:space="preserve">2.23493909835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15720129013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11139249801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08224058151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09889912605286</t>
   </si>
   <si>
     <t xml:space="preserve">2.08918213844299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10583972930908</t>
+    <t xml:space="preserve">2.10583996772766</t>
   </si>
   <si>
     <t xml:space="preserve">2.04892492294312</t>
@@ -290,10 +290,10 @@
     <t xml:space="preserve">2.03781962394714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06558275222778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03226733207703</t>
+    <t xml:space="preserve">2.06558299064636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03226685523987</t>
   </si>
   <si>
     <t xml:space="preserve">2.07252383232117</t>
@@ -302,88 +302,88 @@
     <t xml:space="preserve">2.05725383758545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05156707763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12691903114319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19942736625671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15393209457397</t>
+    <t xml:space="preserve">2.05156683921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12691855430603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19942760467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1539318561554</t>
   </si>
   <si>
     <t xml:space="preserve">2.17525815963745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15535378456116</t>
+    <t xml:space="preserve">2.15535402297974</t>
   </si>
   <si>
     <t xml:space="preserve">2.09279704093933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07147145271301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99896228313446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95773208141327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87669312953949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98901009559631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93640625476837</t>
+    <t xml:space="preserve">2.07147121429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99896252155304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95773220062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87669289112091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9890102148056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93640649318695</t>
   </si>
   <si>
     <t xml:space="preserve">1.94351482391357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84114968776703</t>
+    <t xml:space="preserve">1.84114980697632</t>
   </si>
   <si>
     <t xml:space="preserve">1.78143692016602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75158023834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72598898410797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64210605621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69613265991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77006244659424</t>
+    <t xml:space="preserve">1.75157999992371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72598886489868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64210617542267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69613230228424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77006256580353</t>
   </si>
   <si>
     <t xml:space="preserve">1.81129336357117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78001415729523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89375352859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63499784469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5653327703476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66911971569061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65632355213165</t>
+    <t xml:space="preserve">1.78001439571381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89375364780426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63499748706818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56533288955688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6691198348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65632367134094</t>
   </si>
   <si>
     <t xml:space="preserve">1.63926267623901</t>
@@ -392,43 +392,43 @@
     <t xml:space="preserve">1.63641929626465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5767068862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51130640506744</t>
+    <t xml:space="preserve">1.57670676708221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51130652427673</t>
   </si>
   <si>
     <t xml:space="preserve">1.52552378177643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53121066093445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63784122467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67196321487427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69471096992493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67054128646851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74304962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70892810821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72172391414642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77574956417084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76721918582916</t>
+    <t xml:space="preserve">1.53121078014374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63784098625183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67196345329285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69471108913422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67054164409637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74304974079132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70892798900604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72172367572784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77574944496155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76721906661987</t>
   </si>
   <si>
     <t xml:space="preserve">1.72741055488586</t>
@@ -437,19 +437,19 @@
     <t xml:space="preserve">1.69755423069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72456705570221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71888017654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66343283653259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55395889282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57528507709503</t>
+    <t xml:space="preserve">1.72456741333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7188800573349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66343247890472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55395913124084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57528495788574</t>
   </si>
   <si>
     <t xml:space="preserve">1.5212584733963</t>
@@ -467,49 +467,49 @@
     <t xml:space="preserve">1.68760204315186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71461534500122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70608448982239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70039761066437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74447131156921</t>
+    <t xml:space="preserve">1.71461522579193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70608460903168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70039784908295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74447166919708</t>
   </si>
   <si>
     <t xml:space="preserve">1.70750629901886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72030198574066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73167586326599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7828586101532</t>
+    <t xml:space="preserve">1.72030186653137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73167562484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78285896778107</t>
   </si>
   <si>
     <t xml:space="preserve">1.77859282493591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77148425579071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76437544822693</t>
+    <t xml:space="preserve">1.77148413658142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76437532901764</t>
   </si>
   <si>
     <t xml:space="preserve">1.75584530830383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76295399665833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74162793159485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76864075660706</t>
+    <t xml:space="preserve">1.76295387744904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74162757396698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76864087581635</t>
   </si>
   <si>
     <t xml:space="preserve">1.74873661994934</t>
@@ -518,40 +518,40 @@
     <t xml:space="preserve">1.73451924324036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78428030014038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85252368450165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8496800661087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81271529197693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83546268939972</t>
+    <t xml:space="preserve">1.78428053855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85252356529236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84967994689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81271481513977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83546257019043</t>
   </si>
   <si>
     <t xml:space="preserve">1.84825813770294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85963213443756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94778001308441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97621476650238</t>
+    <t xml:space="preserve">1.85963201522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9477801322937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97621464729309</t>
   </si>
   <si>
     <t xml:space="preserve">2.09848403930664</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10843658447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07573652267456</t>
+    <t xml:space="preserve">2.10843634605408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07573628425598</t>
   </si>
   <si>
     <t xml:space="preserve">2.08568835258484</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">2.09706234931946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16104054450989</t>
+    <t xml:space="preserve">2.16104102134705</t>
   </si>
   <si>
     <t xml:space="preserve">2.18236660957336</t>
@@ -575,19 +575,19 @@
     <t xml:space="preserve">2.00038385391235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03877139091492</t>
+    <t xml:space="preserve">2.0387716293335</t>
   </si>
   <si>
     <t xml:space="preserve">2.00891423225403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05298900604248</t>
+    <t xml:space="preserve">2.05298852920532</t>
   </si>
   <si>
     <t xml:space="preserve">2.06294083595276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11554479598999</t>
+    <t xml:space="preserve">2.11554503440857</t>
   </si>
   <si>
     <t xml:space="preserve">2.12549662590027</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">2.16246247291565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15961909294128</t>
+    <t xml:space="preserve">2.15961885452271</t>
   </si>
   <si>
     <t xml:space="preserve">2.13260555267334</t>
@@ -605,43 +605,43 @@
     <t xml:space="preserve">2.08142304420471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03592753410339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07715797424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09990549087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08995366096497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01033616065979</t>
+    <t xml:space="preserve">2.03592777252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07715845108032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09990572929382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08995389938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01033592224121</t>
   </si>
   <si>
     <t xml:space="preserve">2.12407517433167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10417103767395</t>
+    <t xml:space="preserve">2.10417079925537</t>
   </si>
   <si>
     <t xml:space="preserve">2.07289290428162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16814970970154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27478003501892</t>
+    <t xml:space="preserve">2.16814947128296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27477955818176</t>
   </si>
   <si>
     <t xml:space="preserve">2.37430143356323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26340579986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23354887962341</t>
+    <t xml:space="preserve">2.2634060382843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23354911804199</t>
   </si>
   <si>
     <t xml:space="preserve">2.27193641662598</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">2.23212718963623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17810201644897</t>
+    <t xml:space="preserve">2.1781017780304</t>
   </si>
   <si>
     <t xml:space="preserve">2.16957116127014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23639249801636</t>
+    <t xml:space="preserve">2.23639273643494</t>
   </si>
   <si>
     <t xml:space="preserve">2.22217512130737</t>
@@ -668,28 +668,28 @@
     <t xml:space="preserve">2.2051146030426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22359681129456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26482796669006</t>
+    <t xml:space="preserve">2.22359728813171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26482772827148</t>
   </si>
   <si>
     <t xml:space="preserve">2.31032299995422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31743144989014</t>
+    <t xml:space="preserve">2.31743168830872</t>
   </si>
   <si>
     <t xml:space="preserve">2.34302282333374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34160137176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30463624000549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29752707481384</t>
+    <t xml:space="preserve">2.34160113334656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30463576316833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29752731323242</t>
   </si>
   <si>
     <t xml:space="preserve">2.29610586166382</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">2.34017944335938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40273594856262</t>
+    <t xml:space="preserve">2.4027361869812</t>
   </si>
   <si>
     <t xml:space="preserve">2.41695356369019</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">2.45249652862549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4112663269043</t>
+    <t xml:space="preserve">2.41126656532288</t>
   </si>
   <si>
     <t xml:space="preserve">2.41553211212158</t>
@@ -722,28 +722,28 @@
     <t xml:space="preserve">2.42406225204468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44396662712097</t>
+    <t xml:space="preserve">2.44396638870239</t>
   </si>
   <si>
     <t xml:space="preserve">2.35439658164978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33733558654785</t>
+    <t xml:space="preserve">2.33733582496643</t>
   </si>
   <si>
     <t xml:space="preserve">2.33022737503052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36434864997864</t>
+    <t xml:space="preserve">2.36434888839722</t>
   </si>
   <si>
     <t xml:space="preserve">2.32738375663757</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28188824653625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30037093162537</t>
+    <t xml:space="preserve">2.28188848495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30037117004395</t>
   </si>
   <si>
     <t xml:space="preserve">2.32311868667603</t>
@@ -752,40 +752,40 @@
     <t xml:space="preserve">2.33449244499207</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30890107154846</t>
+    <t xml:space="preserve">2.30890130996704</t>
   </si>
   <si>
     <t xml:space="preserve">2.29894924163818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25629758834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12834024429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13402724266052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28473162651062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22928380966187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27335810661316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27904486656189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31316685676575</t>
+    <t xml:space="preserve">2.25629782676697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12834072113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13402700424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2847318649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22928404808044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27335786819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27904534339905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31316637992859</t>
   </si>
   <si>
     <t xml:space="preserve">2.33875775337219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37856698036194</t>
+    <t xml:space="preserve">2.37856674194336</t>
   </si>
   <si>
     <t xml:space="preserve">2.32880568504333</t>
@@ -794,16 +794,16 @@
     <t xml:space="preserve">2.36719250679016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34870982170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29468417167664</t>
+    <t xml:space="preserve">2.34870958328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29468393325806</t>
   </si>
   <si>
     <t xml:space="preserve">2.30321431159973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28757572174072</t>
+    <t xml:space="preserve">2.28757524490356</t>
   </si>
   <si>
     <t xml:space="preserve">2.32027506828308</t>
@@ -815,46 +815,46 @@
     <t xml:space="preserve">2.29041886329651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29326248168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30605792999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35581803321838</t>
+    <t xml:space="preserve">2.29326224327087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30605816841125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35581827163696</t>
   </si>
   <si>
     <t xml:space="preserve">2.31174468994141</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3316490650177</t>
+    <t xml:space="preserve">2.33164882659912</t>
   </si>
   <si>
     <t xml:space="preserve">2.46671390533447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43117094039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42974901199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49799275398254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46387028694153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48661851882935</t>
+    <t xml:space="preserve">2.43117070198059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42974925041199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49799299240112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46387052536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48661804199219</t>
   </si>
   <si>
     <t xml:space="preserve">2.51647520065308</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51789689064026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56907939910889</t>
+    <t xml:space="preserve">2.51789712905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56907916069031</t>
   </si>
   <si>
     <t xml:space="preserve">2.53353595733643</t>
@@ -863,13 +863,13 @@
     <t xml:space="preserve">2.48804020881653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50510144233704</t>
+    <t xml:space="preserve">2.50510120391846</t>
   </si>
   <si>
     <t xml:space="preserve">2.50794506072998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50936627388</t>
+    <t xml:space="preserve">2.50936651229858</t>
   </si>
   <si>
     <t xml:space="preserve">2.50652313232422</t>
@@ -881,34 +881,34 @@
     <t xml:space="preserve">2.57221221923828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63293886184692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65607333183289</t>
+    <t xml:space="preserve">2.63293862342834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65607309341431</t>
   </si>
   <si>
     <t xml:space="preserve">2.70667862892151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56642866134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52594375610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52883577346802</t>
+    <t xml:space="preserve">2.56642913818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52594399452209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52883553504944</t>
   </si>
   <si>
     <t xml:space="preserve">2.47389245033264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5216064453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5143768787384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47100067138672</t>
+    <t xml:space="preserve">2.52160620689392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51437664031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4710009098053</t>
   </si>
   <si>
     <t xml:space="preserve">2.48979711532593</t>
@@ -926,7 +926,7 @@
     <t xml:space="preserve">2.47967600822449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46087980270386</t>
+    <t xml:space="preserve">2.46087956428528</t>
   </si>
   <si>
     <t xml:space="preserve">2.48112177848816</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.45798802375793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48256802558899</t>
+    <t xml:space="preserve">2.48256754875183</t>
   </si>
   <si>
     <t xml:space="preserve">2.48835110664368</t>
@@ -944,52 +944,52 @@
     <t xml:space="preserve">2.48690533638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50859332084656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53751134872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6025755405426</t>
+    <t xml:space="preserve">2.50859355926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53751158714294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60257530212402</t>
   </si>
   <si>
     <t xml:space="preserve">2.55919933319092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49558043479919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59245443344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66330242156982</t>
+    <t xml:space="preserve">2.49558091163635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.592453956604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6633026599884</t>
   </si>
   <si>
     <t xml:space="preserve">2.61414241790771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63149285316467</t>
+    <t xml:space="preserve">2.63149261474609</t>
   </si>
   <si>
     <t xml:space="preserve">2.62281727790833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61703419685364</t>
+    <t xml:space="preserve">2.61703395843506</t>
   </si>
   <si>
     <t xml:space="preserve">2.72692060470581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73704171180725</t>
+    <t xml:space="preserve">2.73704195022583</t>
   </si>
   <si>
     <t xml:space="preserve">2.72258305549622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71246194839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71390771865845</t>
+    <t xml:space="preserve">2.71246218681335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71390795707703</t>
   </si>
   <si>
     <t xml:space="preserve">2.70812439918518</t>
@@ -998,25 +998,25 @@
     <t xml:space="preserve">2.68932819366455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68643641471863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6878821849823</t>
+    <t xml:space="preserve">2.68643617630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68788194656372</t>
   </si>
   <si>
     <t xml:space="preserve">2.7110161781311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65028929710388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67920708656311</t>
+    <t xml:space="preserve">2.6502890586853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67920732498169</t>
   </si>
   <si>
     <t xml:space="preserve">2.67197775840759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67053198814392</t>
+    <t xml:space="preserve">2.67053174972534</t>
   </si>
   <si>
     <t xml:space="preserve">2.65318083763123</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">2.65173506736755</t>
   </si>
   <si>
-    <t xml:space="preserve">2.667640209198</t>
+    <t xml:space="preserve">2.66764044761658</t>
   </si>
   <si>
     <t xml:space="preserve">2.65896511077881</t>
@@ -1037,25 +1037,25 @@
     <t xml:space="preserve">2.59823775291443</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62426352500916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6040210723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5447404384613</t>
+    <t xml:space="preserve">2.624263048172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60402131080627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54474091529846</t>
   </si>
   <si>
     <t xml:space="preserve">2.57654976844788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52449822425842</t>
+    <t xml:space="preserve">2.52449798583984</t>
   </si>
   <si>
     <t xml:space="preserve">2.48545956611633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50280976295471</t>
+    <t xml:space="preserve">2.50281000137329</t>
   </si>
   <si>
     <t xml:space="preserve">2.52016019821167</t>
@@ -1064,37 +1064,37 @@
     <t xml:space="preserve">2.51148533821106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51871418952942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53317284584045</t>
+    <t xml:space="preserve">2.518714427948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53317308425903</t>
   </si>
   <si>
     <t xml:space="preserve">2.5519700050354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50714755058289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55052447319031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54618644714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53606581687927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57944130897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64161372184753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63004684448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58956265449524</t>
+    <t xml:space="preserve">2.50714731216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55052423477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54618620872498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53606534004211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5794415473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64161396026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.630047082901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58956289291382</t>
   </si>
   <si>
     <t xml:space="preserve">2.52305197715759</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">2.51582264900208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49268865585327</t>
+    <t xml:space="preserve">2.49268889427185</t>
   </si>
   <si>
     <t xml:space="preserve">2.53461885452271</t>
@@ -1112,34 +1112,34 @@
     <t xml:space="preserve">2.49124312400818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47244668006897</t>
+    <t xml:space="preserve">2.47244644165039</t>
   </si>
   <si>
     <t xml:space="preserve">2.50425577163696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48401379585266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49413442611694</t>
+    <t xml:space="preserve">2.48401355743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49413466453552</t>
   </si>
   <si>
     <t xml:space="preserve">2.49847221374512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47822999954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51293110847473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44931316375732</t>
+    <t xml:space="preserve">2.47823023796082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51293063163757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44931268692017</t>
   </si>
   <si>
     <t xml:space="preserve">2.40738201141357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45509624481201</t>
+    <t xml:space="preserve">2.45509648323059</t>
   </si>
   <si>
     <t xml:space="preserve">2.41027355194092</t>
@@ -1151,25 +1151,25 @@
     <t xml:space="preserve">2.24688982963562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28159070014954</t>
+    <t xml:space="preserve">2.28159117698669</t>
   </si>
   <si>
     <t xml:space="preserve">2.18471765518188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19773054122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22086429595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26279473304749</t>
+    <t xml:space="preserve">2.19773077964783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22086453437805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26279449462891</t>
   </si>
   <si>
     <t xml:space="preserve">2.28448247909546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28592848777771</t>
+    <t xml:space="preserve">2.28592824935913</t>
   </si>
   <si>
     <t xml:space="preserve">2.32496738433838</t>
@@ -1178,13 +1178,13 @@
     <t xml:space="preserve">2.34810137748718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37846493721008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41461181640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34231805801392</t>
+    <t xml:space="preserve">2.3784646987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41461229324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34231781959534</t>
   </si>
   <si>
     <t xml:space="preserve">2.35677647590637</t>
@@ -1202,61 +1202,61 @@
     <t xml:space="preserve">2.39292335510254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40015268325806</t>
+    <t xml:space="preserve">2.40015292167664</t>
   </si>
   <si>
     <t xml:space="preserve">2.4059362411499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33653426170349</t>
+    <t xml:space="preserve">2.33653450012207</t>
   </si>
   <si>
     <t xml:space="preserve">2.29315781593323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20496034622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2396605014801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23821473121643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23387718200684</t>
+    <t xml:space="preserve">2.20495986938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23966073989868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23821496963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23387694358826</t>
   </si>
   <si>
     <t xml:space="preserve">2.18327188491821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21797251701355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24544405937195</t>
+    <t xml:space="preserve">2.21797275543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24544382095337</t>
   </si>
   <si>
     <t xml:space="preserve">2.20062208175659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2266480922699</t>
+    <t xml:space="preserve">2.22664785385132</t>
   </si>
   <si>
     <t xml:space="preserve">2.28303694725037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31340074539185</t>
+    <t xml:space="preserve">2.31340050697327</t>
   </si>
   <si>
     <t xml:space="preserve">2.31050896644592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38858556747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38714003562927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34665536880493</t>
+    <t xml:space="preserve">2.38858532905579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38713955879211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34665560722351</t>
   </si>
   <si>
     <t xml:space="preserve">2.34520983695984</t>
@@ -1265,28 +1265,28 @@
     <t xml:space="preserve">2.36545181274414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39436936378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40304446220398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40449047088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3278591632843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34954738616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33364295959473</t>
+    <t xml:space="preserve">2.39436912536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4030442237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40449023246765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32785940170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34954714775085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33364272117615</t>
   </si>
   <si>
     <t xml:space="preserve">2.31195473670959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22953987121582</t>
+    <t xml:space="preserve">2.22953963279724</t>
   </si>
   <si>
     <t xml:space="preserve">2.31484651565552</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">2.30327963829041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32062959671021</t>
+    <t xml:space="preserve">2.32062983512878</t>
   </si>
   <si>
     <t xml:space="preserve">2.3076171875</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">2.42907047271729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36400604248047</t>
+    <t xml:space="preserve">2.36400580406189</t>
   </si>
   <si>
     <t xml:space="preserve">2.31629252433777</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">2.35388493537903</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27725291252136</t>
+    <t xml:space="preserve">2.27725315093994</t>
   </si>
   <si>
     <t xml:space="preserve">2.32930517196655</t>
@@ -1325,73 +1325,73 @@
     <t xml:space="preserve">2.30617141723633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30038785934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37412714958191</t>
+    <t xml:space="preserve">2.30038809776306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37412691116333</t>
   </si>
   <si>
     <t xml:space="preserve">2.33075094223022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32641363143921</t>
+    <t xml:space="preserve">2.32641339302063</t>
   </si>
   <si>
     <t xml:space="preserve">2.39726066589355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39870667457581</t>
+    <t xml:space="preserve">2.39870691299438</t>
   </si>
   <si>
     <t xml:space="preserve">2.38569402694702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60112953186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71969127655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70957040786743</t>
+    <t xml:space="preserve">2.60112929344177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71969103813171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70956993103027</t>
   </si>
   <si>
     <t xml:space="preserve">2.75439214706421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77752685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84837436676025</t>
+    <t xml:space="preserve">2.77752709388733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84837412834167</t>
   </si>
   <si>
     <t xml:space="preserve">2.84114503860474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83391571044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86861634254456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90042591094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82957816123962</t>
+    <t xml:space="preserve">2.83391547203064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86861610412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90042614936829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82957768440247</t>
   </si>
   <si>
     <t xml:space="preserve">2.73125839233398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78620171546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75583791732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82524013519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80644416809082</t>
+    <t xml:space="preserve">2.78620195388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7558376789093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82524061203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80644392967224</t>
   </si>
   <si>
     <t xml:space="preserve">2.83680748939514</t>
@@ -1406,19 +1406,19 @@
     <t xml:space="preserve">2.6343846321106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66092014312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65060067176819</t>
+    <t xml:space="preserve">2.66091966629028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65060043334961</t>
   </si>
   <si>
     <t xml:space="preserve">2.71251678466797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70367121696472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63143587112427</t>
+    <t xml:space="preserve">2.70367097854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63143610954285</t>
   </si>
   <si>
     <t xml:space="preserve">2.52824234962463</t>
@@ -1430,16 +1430,16 @@
     <t xml:space="preserve">2.52234554290771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56509733200073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61079788208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57689070701599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51939749717712</t>
+    <t xml:space="preserve">2.56509709358215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6107976436615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57689046859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51939725875854</t>
   </si>
   <si>
     <t xml:space="preserve">2.59163331985474</t>
@@ -1451,16 +1451,16 @@
     <t xml:space="preserve">2.59015941619873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54888081550598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56067442893982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55625200271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54593276977539</t>
+    <t xml:space="preserve">2.54888105392456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5606746673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55625176429749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54593253135681</t>
   </si>
   <si>
     <t xml:space="preserve">2.57099390029907</t>
@@ -1469,25 +1469,25 @@
     <t xml:space="preserve">2.51350045204163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51055240631104</t>
+    <t xml:space="preserve">2.51055216789246</t>
   </si>
   <si>
     <t xml:space="preserve">2.53708744049072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54151010513306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65354895591736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6594455242157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70514559745789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69040369987488</t>
+    <t xml:space="preserve">2.54150986671448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65354871749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65944576263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70514535903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6904034614563</t>
   </si>
   <si>
     <t xml:space="preserve">2.65797162055969</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">2.63291025161743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6491265296936</t>
+    <t xml:space="preserve">2.64912605285645</t>
   </si>
   <si>
     <t xml:space="preserve">2.64322948455811</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">2.66386818885803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71399140357971</t>
+    <t xml:space="preserve">2.71399116516113</t>
   </si>
   <si>
     <t xml:space="preserve">2.73168182373047</t>
@@ -1529,19 +1529,19 @@
     <t xml:space="preserve">2.73315572738647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78180384635925</t>
+    <t xml:space="preserve">2.78180336952209</t>
   </si>
   <si>
     <t xml:space="preserve">2.70661950111389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69187784194946</t>
+    <t xml:space="preserve">2.69187760353088</t>
   </si>
   <si>
     <t xml:space="preserve">2.68892931938171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67713570594788</t>
+    <t xml:space="preserve">2.6771354675293</t>
   </si>
   <si>
     <t xml:space="preserve">2.64617800712585</t>
@@ -1562,10 +1562,10 @@
     <t xml:space="preserve">2.58868479728699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58131313323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53561329841614</t>
+    <t xml:space="preserve">2.58131289482117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53561305999756</t>
   </si>
   <si>
     <t xml:space="preserve">2.48843932151794</t>
@@ -1589,28 +1589,28 @@
     <t xml:space="preserve">2.65502285957336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68450689315796</t>
+    <t xml:space="preserve">2.68450665473938</t>
   </si>
   <si>
     <t xml:space="preserve">2.66239380836487</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62406516075134</t>
+    <t xml:space="preserve">2.62406539916992</t>
   </si>
   <si>
     <t xml:space="preserve">2.62996196746826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63733291625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62111687660217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42210054397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41915225982666</t>
+    <t xml:space="preserve">2.63733315467834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62111663818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42210030555725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41915202140808</t>
   </si>
   <si>
     <t xml:space="preserve">2.36608147621155</t>
@@ -1622,16 +1622,16 @@
     <t xml:space="preserve">2.41325545310974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33659648895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24667191505432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23045539855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22898125648499</t>
+    <t xml:space="preserve">2.33659672737122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24667167663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23045563697815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22898149490356</t>
   </si>
   <si>
     <t xml:space="preserve">2.16706514358521</t>
@@ -1640,7 +1640,7 @@
     <t xml:space="preserve">2.18033266067505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15674567222595</t>
+    <t xml:space="preserve">2.15674543380737</t>
   </si>
   <si>
     <t xml:space="preserve">2.20244526863098</t>
@@ -1655,16 +1655,16 @@
     <t xml:space="preserve">2.11399412155151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08745813369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0417582988739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00932621955872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05207753181458</t>
+    <t xml:space="preserve">2.08745837211609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04175853729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00932645797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05207777023315</t>
   </si>
   <si>
     <t xml:space="preserve">2.105149269104</t>
@@ -1676,7 +1676,7 @@
     <t xml:space="preserve">2.0550262928009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09335541725159</t>
+    <t xml:space="preserve">2.09335589408875</t>
   </si>
   <si>
     <t xml:space="preserve">2.13610696792603</t>
@@ -1685,13 +1685,13 @@
     <t xml:space="preserve">2.11694240570068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09925222396851</t>
+    <t xml:space="preserve">2.09925270080566</t>
   </si>
   <si>
     <t xml:space="preserve">2.10220050811768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10072660446167</t>
+    <t xml:space="preserve">2.10072684288025</t>
   </si>
   <si>
     <t xml:space="preserve">2.09040641784668</t>
@@ -1700,40 +1700,40 @@
     <t xml:space="preserve">2.04912948608398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06829357147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05060362815857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04765510559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02701640129089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01964569091797</t>
+    <t xml:space="preserve">2.06829380989075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05060338973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0476553440094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02701663970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01964592933655</t>
   </si>
   <si>
     <t xml:space="preserve">1.97394597530365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9798424243927</t>
+    <t xml:space="preserve">1.97984278202057</t>
   </si>
   <si>
     <t xml:space="preserve">1.96215176582336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98426508903503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08008718490601</t>
+    <t xml:space="preserve">1.98426520824432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08008742332458</t>
   </si>
   <si>
     <t xml:space="preserve">2.06387114524841</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07861304283142</t>
+    <t xml:space="preserve">2.07861280441284</t>
   </si>
   <si>
     <t xml:space="preserve">2.04618120193481</t>
@@ -1742,25 +1742,25 @@
     <t xml:space="preserve">2.0859842300415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05649995803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95625507831573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98279082775116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94446158409119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9370903968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96657431125641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96804857254028</t>
+    <t xml:space="preserve">2.05650019645691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95625495910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98279058933258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9444614648819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93709051609039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9665744304657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9680483341217</t>
   </si>
   <si>
     <t xml:space="preserve">1.89286506175995</t>
@@ -1769,31 +1769,31 @@
     <t xml:space="preserve">1.98131668567657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91497778892517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8751745223999</t>
+    <t xml:space="preserve">1.91497790813446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87517476081848</t>
   </si>
   <si>
     <t xml:space="preserve">1.8737006187439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94003903865814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92677128314972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99311017990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0034294128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99458456039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99163591861725</t>
+    <t xml:space="preserve">1.94003880023956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92677104473114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99311029911041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00342965126038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.994584441185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99163615703583</t>
   </si>
   <si>
     <t xml:space="preserve">1.94888412952423</t>
@@ -1802,49 +1802,49 @@
     <t xml:space="preserve">1.88844239711761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87222635746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91940057277679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89433944225311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86485528945923</t>
+    <t xml:space="preserve">1.87222623825073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91940033435822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89433920383453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86485517024994</t>
   </si>
   <si>
     <t xml:space="preserve">1.85306215286255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83831930160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88549411296844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8515876531601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82505166530609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78230035305023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71596121788025</t>
+    <t xml:space="preserve">1.83831918239594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88549399375916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85158753395081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8250515460968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78230011463165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71596133708954</t>
   </si>
   <si>
     <t xml:space="preserve">1.69532251358032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71006453037262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73217821121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78377425670624</t>
+    <t xml:space="preserve">1.71006441116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73217809200287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78377437591553</t>
   </si>
   <si>
     <t xml:space="preserve">1.76313591003418</t>
@@ -1853,19 +1853,19 @@
     <t xml:space="preserve">1.76166176795959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78672313690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80588722229004</t>
+    <t xml:space="preserve">1.78672289848328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80588710308075</t>
   </si>
   <si>
     <t xml:space="preserve">1.83389687538147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87664878368378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86927807331085</t>
+    <t xml:space="preserve">1.87664890289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86927795410156</t>
   </si>
   <si>
     <t xml:space="preserve">1.84569013118744</t>
@@ -1877,16 +1877,16 @@
     <t xml:space="preserve">1.83242249488831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84274172782898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83684515953064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89728736877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88991641998291</t>
+    <t xml:space="preserve">1.84274184703827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83684504032135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89728724956512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88991630077362</t>
   </si>
   <si>
     <t xml:space="preserve">1.88254570960999</t>
@@ -1895,40 +1895,40 @@
     <t xml:space="preserve">1.91055500507355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87075221538544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80293881893158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80441308021545</t>
+    <t xml:space="preserve">1.87075209617615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80293893814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80441296100616</t>
   </si>
   <si>
     <t xml:space="preserve">1.79114532470703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75576508045197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81325840950012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81178402900696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83537101745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79556798934937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77492940425873</t>
+    <t xml:space="preserve">1.75576496124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81325829029083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81178414821625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83537089824677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79556810855865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77492928504944</t>
   </si>
   <si>
     <t xml:space="preserve">1.80883574485779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79851639270782</t>
+    <t xml:space="preserve">1.79851615428925</t>
   </si>
   <si>
     <t xml:space="preserve">1.79704225063324</t>
@@ -1940,13 +1940,13 @@
     <t xml:space="preserve">1.78082621097565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7542906999588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71301293373108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70711624622345</t>
+    <t xml:space="preserve">1.75429058074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71301281452179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70711636543274</t>
   </si>
   <si>
     <t xml:space="preserve">1.74544548988342</t>
@@ -1955,16 +1955,16 @@
     <t xml:space="preserve">1.76460993289948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77198100090027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77787792682648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78819692134857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74839401245117</t>
+    <t xml:space="preserve">1.77198112010956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77787780761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78819715976715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74839389324188</t>
   </si>
   <si>
     <t xml:space="preserve">1.6658388376236</t>
@@ -1973,22 +1973,22 @@
     <t xml:space="preserve">1.67910647392273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61129415035248</t>
+    <t xml:space="preserve">1.61129426956177</t>
   </si>
   <si>
     <t xml:space="preserve">1.57886123657227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5361100435257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55822265148163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54200649261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53445506095886</t>
+    <t xml:space="preserve">1.53610992431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55822253227234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54200673103333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53445518016815</t>
   </si>
   <si>
     <t xml:space="preserve">1.53596556186676</t>
@@ -1997,37 +1997,37 @@
     <t xml:space="preserve">1.56466102600098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54351699352264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55559921264648</t>
+    <t xml:space="preserve">1.54351711273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55559909343719</t>
   </si>
   <si>
     <t xml:space="preserve">1.53898620605469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54502713680267</t>
+    <t xml:space="preserve">1.54502737522125</t>
   </si>
   <si>
     <t xml:space="preserve">1.60543859004974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58429455757141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56768131256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56919157505035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58882534503937</t>
+    <t xml:space="preserve">1.58429443836212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56768155097961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56919169425964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58882522583008</t>
   </si>
   <si>
     <t xml:space="preserve">1.51028990745544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51935231685638</t>
+    <t xml:space="preserve">1.51935243606567</t>
   </si>
   <si>
     <t xml:space="preserve">1.52690374851227</t>
@@ -2036,25 +2036,25 @@
     <t xml:space="preserve">1.4717777967453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47026753425598</t>
+    <t xml:space="preserve">1.47026741504669</t>
   </si>
   <si>
     <t xml:space="preserve">1.471022605896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45138895511627</t>
+    <t xml:space="preserve">1.45138907432556</t>
   </si>
   <si>
     <t xml:space="preserve">1.46875727176666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49367678165436</t>
+    <t xml:space="preserve">1.49367666244507</t>
   </si>
   <si>
     <t xml:space="preserve">1.48386001586914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50047314167023</t>
+    <t xml:space="preserve">1.50047326087952</t>
   </si>
   <si>
     <t xml:space="preserve">1.45894038677216</t>
@@ -2078,7 +2078,7 @@
     <t xml:space="preserve">1.57523286342621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56315064430237</t>
+    <t xml:space="preserve">1.56315052509308</t>
   </si>
   <si>
     <t xml:space="preserve">1.52539360523224</t>
@@ -2087,73 +2087,73 @@
     <t xml:space="preserve">1.50424885749817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47328817844391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4725329875946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44912362098694</t>
+    <t xml:space="preserve">1.47328805923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47253286838531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44912350177765</t>
   </si>
   <si>
     <t xml:space="preserve">1.4536544084549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46649169921875</t>
+    <t xml:space="preserve">1.46649181842804</t>
   </si>
   <si>
     <t xml:space="preserve">1.44987881183624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4461030960083</t>
+    <t xml:space="preserve">1.44610297679901</t>
   </si>
   <si>
     <t xml:space="preserve">1.43779647350311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42269361019135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42042827606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42722463607788</t>
+    <t xml:space="preserve">1.42269372940063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42042815685272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42722451686859</t>
   </si>
   <si>
     <t xml:space="preserve">1.41665256023407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40683567523956</t>
+    <t xml:space="preserve">1.40683555603027</t>
   </si>
   <si>
     <t xml:space="preserve">1.400794506073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39097774028778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38644623756409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28374683856964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25354075431824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25127506256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20068073272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23617231845856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25278544425964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22182464599609</t>
+    <t xml:space="preserve">1.39097762107849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3864461183548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28374695777893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25354063510895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25127518177032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20068061351776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23617243766785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25278532505035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22182476520538</t>
   </si>
   <si>
     <t xml:space="preserve">1.23088645935059</t>
@@ -2162,22 +2162,22 @@
     <t xml:space="preserve">1.27695071697235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26637887954712</t>
+    <t xml:space="preserve">1.26637876033783</t>
   </si>
   <si>
     <t xml:space="preserve">1.27619552612305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31395256519318</t>
+    <t xml:space="preserve">1.31395268440247</t>
   </si>
   <si>
     <t xml:space="preserve">1.27090954780579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28223669528961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28752267360687</t>
+    <t xml:space="preserve">1.28223657608032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28752255439758</t>
   </si>
   <si>
     <t xml:space="preserve">1.35775077342987</t>
@@ -2186,19 +2186,19 @@
     <t xml:space="preserve">1.38342559337616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37436389923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35246467590332</t>
+    <t xml:space="preserve">1.37436366081238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35246479511261</t>
   </si>
   <si>
     <t xml:space="preserve">1.4098562002182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39852917194366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36681246757507</t>
+    <t xml:space="preserve">1.39852905273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36681234836578</t>
   </si>
   <si>
     <t xml:space="preserve">1.350954413414</t>
@@ -2207,10 +2207,10 @@
     <t xml:space="preserve">1.35926103591919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36454701423645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33736181259155</t>
+    <t xml:space="preserve">1.36454713344574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33736193180084</t>
   </si>
   <si>
     <t xml:space="preserve">1.30262541770935</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">1.2897881269455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26109254360199</t>
+    <t xml:space="preserve">1.26109266281128</t>
   </si>
   <si>
     <t xml:space="preserve">1.26864409446716</t>
@@ -2231,7 +2231,7 @@
     <t xml:space="preserve">1.27468526363373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27997124195099</t>
+    <t xml:space="preserve">1.27997136116028</t>
   </si>
   <si>
     <t xml:space="preserve">1.25958156585693</t>
@@ -2240,46 +2240,46 @@
     <t xml:space="preserve">1.25429570674896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26939928531647</t>
+    <t xml:space="preserve">1.26939940452576</t>
   </si>
   <si>
     <t xml:space="preserve">1.2814816236496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30413591861725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33660674095154</t>
+    <t xml:space="preserve">1.30413568019867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33660686016083</t>
   </si>
   <si>
     <t xml:space="preserve">1.36077129840851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38871228694916</t>
+    <t xml:space="preserve">1.38871240615845</t>
   </si>
   <si>
     <t xml:space="preserve">1.38267040252686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3517097234726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35699570178986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36152637004852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36228168010712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34113764762878</t>
+    <t xml:space="preserve">1.35170960426331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35699558258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36152648925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36228156089783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34113788604736</t>
   </si>
   <si>
     <t xml:space="preserve">1.36756765842438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42495894432068</t>
+    <t xml:space="preserve">1.42495906352997</t>
   </si>
   <si>
     <t xml:space="preserve">1.41740763187408</t>
@@ -2294,10 +2294,10 @@
     <t xml:space="preserve">1.43477594852448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62960290908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58278429508209</t>
+    <t xml:space="preserve">1.62960302829742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5827841758728</t>
   </si>
   <si>
     <t xml:space="preserve">1.57825350761414</t>
@@ -2306,79 +2306,79 @@
     <t xml:space="preserve">1.58127391338348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54653739929199</t>
+    <t xml:space="preserve">1.54653751850128</t>
   </si>
   <si>
     <t xml:space="preserve">1.53747594356537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52237284183502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55257868766785</t>
+    <t xml:space="preserve">1.52237296104431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55257856845856</t>
   </si>
   <si>
     <t xml:space="preserve">1.60241782665253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63111329078674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6009076833725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62054121494293</t>
+    <t xml:space="preserve">1.63111317157745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60090756416321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62054145336151</t>
   </si>
   <si>
     <t xml:space="preserve">1.54955792427063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57221233844757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61147940158844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64168608188629</t>
+    <t xml:space="preserve">1.57221245765686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61147952079773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.641685962677</t>
   </si>
   <si>
     <t xml:space="preserve">1.61298990249634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61752080917358</t>
+    <t xml:space="preserve">1.61752068996429</t>
   </si>
   <si>
     <t xml:space="preserve">1.59184598922729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58731520175934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61903119087219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57976365089417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56013011932373</t>
+    <t xml:space="preserve">1.58731496334076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6190310716629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57976377010345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56013000011444</t>
   </si>
   <si>
     <t xml:space="preserve">1.55861973762512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59788703918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60392820835114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58580493927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59939730167389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59637677669525</t>
+    <t xml:space="preserve">1.59788691997528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60392796993256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58580482006073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59939742088318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59637665748596</t>
   </si>
   <si>
     <t xml:space="preserve">1.59033560752869</t>
@@ -2387,64 +2387,64 @@
     <t xml:space="preserve">1.52992451190948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5133113861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50953471660614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52388322353363</t>
+    <t xml:space="preserve">1.51331114768982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50953495502472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52388334274292</t>
   </si>
   <si>
     <t xml:space="preserve">1.54049634933472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63866472244263</t>
+    <t xml:space="preserve">1.63866460323334</t>
   </si>
   <si>
     <t xml:space="preserve">1.75948810577393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.806307554245</t>
+    <t xml:space="preserve">1.80630743503571</t>
   </si>
   <si>
     <t xml:space="preserve">1.78365325927734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8395334482193</t>
+    <t xml:space="preserve">1.83953368663788</t>
   </si>
   <si>
     <t xml:space="preserve">2.02983069419861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06909823417664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94827461242676</t>
+    <t xml:space="preserve">2.06909799575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94827473163605</t>
   </si>
   <si>
     <t xml:space="preserve">1.89088308811188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77912247180939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77308106422424</t>
+    <t xml:space="preserve">1.7791223526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77308130264282</t>
   </si>
   <si>
     <t xml:space="preserve">1.81687939167023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70813858509064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48008441925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37511885166168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32452464103699</t>
+    <t xml:space="preserve">1.70813834667206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4800843000412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37511909008026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3245245218277</t>
   </si>
   <si>
     <t xml:space="preserve">1.2407032251358</t>
@@ -2453,16 +2453,16 @@
     <t xml:space="preserve">1.19917047023773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18406760692596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959789335727692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995280921459198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91901171207428</t>
+    <t xml:space="preserve">1.18406784534454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959789216518402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995280981063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919011652469635</t>
   </si>
   <si>
     <t xml:space="preserve">0.945441544055939</t>
@@ -2477,25 +2477,25 @@
     <t xml:space="preserve">1.04361057281494</t>
   </si>
   <si>
-    <t xml:space="preserve">0.990750133991241</t>
+    <t xml:space="preserve">0.990750193595886</t>
   </si>
   <si>
     <t xml:space="preserve">1.07155072689056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07910227775574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06777501106262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01944625377655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99981164932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04134523868561</t>
+    <t xml:space="preserve">1.07910239696503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06777513027191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01944613456726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999811828136444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0413453578949</t>
   </si>
   <si>
     <t xml:space="preserve">1.02699756622314</t>
@@ -2516,10 +2516,10 @@
     <t xml:space="preserve">1.20219099521637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16745460033417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16594421863556</t>
+    <t xml:space="preserve">1.16745448112488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16594409942627</t>
   </si>
   <si>
     <t xml:space="preserve">1.08740878105164</t>
@@ -2528,85 +2528,85 @@
     <t xml:space="preserve">1.06701993942261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09420502185822</t>
+    <t xml:space="preserve">1.0942051410675</t>
   </si>
   <si>
     <t xml:space="preserve">1.06324434280396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09496033191681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07834696769714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08212280273438</t>
+    <t xml:space="preserve">1.09496021270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07834708690643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08212292194366</t>
   </si>
   <si>
     <t xml:space="preserve">1.07457137107849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08665359020233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09269487857819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03756964206696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07306122779846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0496518611908</t>
+    <t xml:space="preserve">1.08665370941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0926947593689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03756952285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07306110858917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04965174198151</t>
   </si>
   <si>
     <t xml:space="preserve">1.03530418872833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04436576366425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04285550117493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01189482212067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985464096069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970361351966858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989239811897278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94317626953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926563143730164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921276986598969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913725733757019</t>
+    <t xml:space="preserve">1.04436588287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04285562038422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01189470291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985464155673981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970361232757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989239871501923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943176209926605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926563084125519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921277046203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913725674152374</t>
   </si>
   <si>
     <t xml:space="preserve">0.986219227313995</t>
   </si>
   <si>
-    <t xml:space="preserve">0.997546374797821</t>
+    <t xml:space="preserve">0.997546255588531</t>
   </si>
   <si>
     <t xml:space="preserve">1.058713555336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09722554683685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10251152515411</t>
+    <t xml:space="preserve">1.09722566604614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1025116443634</t>
   </si>
   <si>
     <t xml:space="preserve">1.13422763347626</t>
@@ -2615,31 +2615,31 @@
     <t xml:space="preserve">1.18180215358734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21502840518951</t>
+    <t xml:space="preserve">1.21502828598022</t>
   </si>
   <si>
     <t xml:space="preserve">1.23919296264648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19992566108704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18935358524323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14782094955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16820955276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1870881319046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16216850280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19312930107117</t>
+    <t xml:space="preserve">1.19992554187775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18935346603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14782083034515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16820979118347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18708825111389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16216862201691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19312942028046</t>
   </si>
   <si>
     <t xml:space="preserve">1.17047512531281</t>
@@ -2648,7 +2648,7 @@
     <t xml:space="preserve">1.24598908424377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29280877113342</t>
+    <t xml:space="preserve">1.29280865192413</t>
   </si>
   <si>
     <t xml:space="preserve">1.36303675174713</t>
@@ -2663,37 +2663,37 @@
     <t xml:space="preserve">1.39399826526642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39928424358368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4015496969223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40306007862091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41589748859406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49292182922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44836831092834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48763573169708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47630870342255</t>
+    <t xml:space="preserve">1.39928436279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40154957771301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40305995941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41589725017548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49292171001434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44836854934692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48763561248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47630858421326</t>
   </si>
   <si>
     <t xml:space="preserve">1.46498155593872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39626371860504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37662923336029</t>
+    <t xml:space="preserve">1.39626383781433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37662935256958</t>
   </si>
   <si>
     <t xml:space="preserve">1.34264802932739</t>
@@ -2705,13 +2705,13 @@
     <t xml:space="preserve">1.43175530433655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44534778594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47479832172394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48461532592773</t>
+    <t xml:space="preserve">1.445347905159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47479844093323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48461520671844</t>
   </si>
   <si>
     <t xml:space="preserve">1.55106842517853</t>
@@ -2723,10 +2723,10 @@
     <t xml:space="preserve">1.37889468669891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37813949584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34415817260742</t>
+    <t xml:space="preserve">1.3781396150589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34415829181671</t>
   </si>
   <si>
     <t xml:space="preserve">1.37209856510162</t>
@@ -2735,19 +2735,19 @@
     <t xml:space="preserve">1.39475345611572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37964987754822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38795709609985</t>
+    <t xml:space="preserve">1.37964999675751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38795721530914</t>
   </si>
   <si>
     <t xml:space="preserve">1.3924880027771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32150399684906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31848335266113</t>
+    <t xml:space="preserve">1.32150411605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31848347187042</t>
   </si>
   <si>
     <t xml:space="preserve">1.34340310096741</t>
@@ -2759,52 +2759,52 @@
     <t xml:space="preserve">1.32376945018768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33434152603149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39777386188507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.369833111763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38191521167755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34038245677948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35473024845123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31772828102112</t>
+    <t xml:space="preserve">1.3343414068222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39777410030365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36983299255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38191533088684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34038257598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35473012924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31772840023041</t>
   </si>
   <si>
     <t xml:space="preserve">1.33207607269287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33585178852081</t>
+    <t xml:space="preserve">1.33585166931152</t>
   </si>
   <si>
     <t xml:space="preserve">1.27393019199371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26486837863922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22484517097473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24145841598511</t>
+    <t xml:space="preserve">1.26486849784851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22484529018402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24145829677582</t>
   </si>
   <si>
     <t xml:space="preserve">1.11761450767517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10779774188995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13800394535065</t>
+    <t xml:space="preserve">1.10779762268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13800406455994</t>
   </si>
   <si>
     <t xml:space="preserve">1.22711062431335</t>
@@ -2813,7 +2813,7 @@
     <t xml:space="preserve">1.24221348762512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23843777179718</t>
+    <t xml:space="preserve">1.23843765258789</t>
   </si>
   <si>
     <t xml:space="preserve">1.22862088680267</t>
@@ -2822,76 +2822,76 @@
     <t xml:space="preserve">1.44232726097107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43251037597656</t>
+    <t xml:space="preserve">1.43251049518585</t>
   </si>
   <si>
     <t xml:space="preserve">1.50273847579956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55408895015717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81234848499298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78214311599731</t>
+    <t xml:space="preserve">1.55408883094788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81234860420227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78214299678802</t>
   </si>
   <si>
     <t xml:space="preserve">1.77459156513214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75797772407532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69303560256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72173094749451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68548405170441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70209729671478</t>
+    <t xml:space="preserve">1.75797760486603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69303572177887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7217310667038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6854841709137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70209717750549</t>
   </si>
   <si>
     <t xml:space="preserve">1.70360743999481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.730792760849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72777235507965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69907665252686</t>
+    <t xml:space="preserve">1.73079264163971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72777223587036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69907653331757</t>
   </si>
   <si>
     <t xml:space="preserve">1.66887104511261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66282975673676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67944312095642</t>
+    <t xml:space="preserve">1.66282987594604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67944288253784</t>
   </si>
   <si>
     <t xml:space="preserve">1.66131961345673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67642259597778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64470660686493</t>
+    <t xml:space="preserve">1.6764223575592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64470648765564</t>
   </si>
   <si>
     <t xml:space="preserve">1.61601042747498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63564395904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65829908847809</t>
+    <t xml:space="preserve">1.63564419746399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65829920768738</t>
   </si>
   <si>
     <t xml:space="preserve">1.66585063934326</t>
@@ -2900,25 +2900,25 @@
     <t xml:space="preserve">1.66434013843536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74438524246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77761197090149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75646734237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7202205657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7368335723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69454574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65225791931152</t>
+    <t xml:space="preserve">1.74438536167145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77761220932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.756467461586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72022044658661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73683369159698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69454598426819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65225827693939</t>
   </si>
   <si>
     <t xml:space="preserve">1.67491221427917</t>
@@ -2927,91 +2927,91 @@
     <t xml:space="preserve">1.65376830101013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63715422153473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57070183753967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59486651420593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62205147743225</t>
+    <t xml:space="preserve">1.63715434074402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57070207595825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59486639499664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62205159664154</t>
   </si>
   <si>
     <t xml:space="preserve">1.7474057674408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8863525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85765707492828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88031113147736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86822879314423</t>
+    <t xml:space="preserve">1.88635241985321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85765719413757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88031125068665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86822891235352</t>
   </si>
   <si>
     <t xml:space="preserve">1.85463654994965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88937294483185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8501056432724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80932819843292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83047223091125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82141017913818</t>
+    <t xml:space="preserve">1.88937306404114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85010552406311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80932807922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83047199249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82141005992889</t>
   </si>
   <si>
     <t xml:space="preserve">1.81838965415955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82594108581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80781769752502</t>
+    <t xml:space="preserve">1.82594120502472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80781781673431</t>
   </si>
   <si>
     <t xml:space="preserve">1.80177652835846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84557461738586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83500277996063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82745146751404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87124967575073</t>
+    <t xml:space="preserve">1.84557473659515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83500266075134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82745134830475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87124955654144</t>
   </si>
   <si>
     <t xml:space="preserve">1.86369800567627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92713093757629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97999048233032</t>
+    <t xml:space="preserve">1.927130818367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9799907207489</t>
   </si>
   <si>
     <t xml:space="preserve">2.05399513244629</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13706088066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18085956573486</t>
+    <t xml:space="preserve">2.13706064224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18085932731628</t>
   </si>
   <si>
     <t xml:space="preserve">2.15216398239136</t>
@@ -3023,40 +3023,40 @@
     <t xml:space="preserve">2.10685515403748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15518498420715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13555002212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13857126235962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22465777397156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15669512748718</t>
+    <t xml:space="preserve">2.15518450737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13555026054382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13857102394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22465753555298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15669536590576</t>
   </si>
   <si>
     <t xml:space="preserve">2.18992114067078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18690085411072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16877722740173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17028784751892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2352294921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24731230735779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26996684074402</t>
+    <t xml:space="preserve">2.18690061569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16877746582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17028737068176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23522973060608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24731206893921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2699670791626</t>
   </si>
   <si>
     <t xml:space="preserve">2.30168294906616</t>
@@ -3065,31 +3065,31 @@
     <t xml:space="preserve">2.23673987388611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2458016872406</t>
+    <t xml:space="preserve">2.24580192565918</t>
   </si>
   <si>
     <t xml:space="preserve">2.24882221221924</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36964559555054</t>
+    <t xml:space="preserve">2.36964535713196</t>
   </si>
   <si>
     <t xml:space="preserve">2.39985179901123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48140716552734</t>
+    <t xml:space="preserve">2.48140692710876</t>
   </si>
   <si>
     <t xml:space="preserve">2.54937052726746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64300799369812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61733341217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60223054885864</t>
+    <t xml:space="preserve">2.6430082321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61733317375183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60223031044006</t>
   </si>
   <si>
     <t xml:space="preserve">2.70190978050232</t>
@@ -3104,22 +3104,22 @@
     <t xml:space="preserve">2.88616490364075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86502075195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86200022697449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94204592704773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94506621360779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93147420883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97980308532715</t>
+    <t xml:space="preserve">2.8650209903717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86200070381165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94204616546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94506669044495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93147397041321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97980332374573</t>
   </si>
   <si>
     <t xml:space="preserve">2.96621036529541</t>
@@ -3128,25 +3128,25 @@
     <t xml:space="preserve">2.95714902877808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97829294204712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08411288261414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07337737083435</t>
+    <t xml:space="preserve">2.97829270362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08411312103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07337713241577</t>
   </si>
   <si>
     <t xml:space="preserve">3.05804061889648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15312552452087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09178066253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11478519439697</t>
+    <t xml:space="preserve">3.15312528610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0917809009552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11478495597839</t>
   </si>
   <si>
     <t xml:space="preserve">3.19299960136414</t>
@@ -3155,28 +3155,28 @@
     <t xml:space="preserve">3.21600413322449</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18839859962463</t>
+    <t xml:space="preserve">3.18839812278748</t>
   </si>
   <si>
     <t xml:space="preserve">3.17459583282471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12858772277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06264162063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98749446868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96602416038513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95988965034485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94455289840698</t>
+    <t xml:space="preserve">3.12858748435974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06264138221741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98749470710754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96602392196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95988941192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9445526599884</t>
   </si>
   <si>
     <t xml:space="preserve">2.91388034820557</t>
@@ -3188,28 +3188,28 @@
     <t xml:space="preserve">2.83106517791748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80192565917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80039215087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73598027229309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79425811767578</t>
+    <t xml:space="preserve">2.80192589759827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80039238929749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73598051071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79425764083862</t>
   </si>
   <si>
     <t xml:space="preserve">2.79272437095642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83719968795776</t>
+    <t xml:space="preserve">2.83719944953918</t>
   </si>
   <si>
     <t xml:space="preserve">2.76665258407593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80499267578125</t>
+    <t xml:space="preserve">2.80499315261841</t>
   </si>
   <si>
     <t xml:space="preserve">2.79119038581848</t>
@@ -3221,43 +3221,43 @@
     <t xml:space="preserve">2.78198909759521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75131678581238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72371172904968</t>
+    <t xml:space="preserve">2.7513165473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7237114906311</t>
   </si>
   <si>
     <t xml:space="preserve">2.84333419799805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79579162597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77892184257507</t>
+    <t xml:space="preserve">2.79579138755798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77892160415649</t>
   </si>
   <si>
     <t xml:space="preserve">2.72524523735046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6731014251709</t>
+    <t xml:space="preserve">2.67310166358948</t>
   </si>
   <si>
     <t xml:space="preserve">2.58108496665955</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66543340682983</t>
+    <t xml:space="preserve">2.66543364524841</t>
   </si>
   <si>
     <t xml:space="preserve">2.73291325569153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75745105743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78352236747742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92614936828613</t>
+    <t xml:space="preserve">2.75745129585266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.783522605896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92614912986755</t>
   </si>
   <si>
     <t xml:space="preserve">2.88934254646301</t>
@@ -3272,28 +3272,28 @@
     <t xml:space="preserve">2.85100221633911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86020398139954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85867023468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83873319625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84486794471741</t>
+    <t xml:space="preserve">2.86020374298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85867047309875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83873343467712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84486770629883</t>
   </si>
   <si>
     <t xml:space="preserve">2.91848111152649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95222139358521</t>
+    <t xml:space="preserve">2.95222163200378</t>
   </si>
   <si>
     <t xml:space="preserve">2.90467858314514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96755743026733</t>
+    <t xml:space="preserve">2.96755766868591</t>
   </si>
   <si>
     <t xml:space="preserve">2.92768287658691</t>
@@ -3302,13 +3302,13 @@
     <t xml:space="preserve">2.92461562156677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83566617965698</t>
+    <t xml:space="preserve">2.83566641807556</t>
   </si>
   <si>
     <t xml:space="preserve">2.8617377281189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84640169143677</t>
+    <t xml:space="preserve">2.84640121459961</t>
   </si>
   <si>
     <t xml:space="preserve">2.87860727310181</t>
@@ -3317,13 +3317,13 @@
     <t xml:space="preserve">2.89854431152344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99976372718811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0074315071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98289370536804</t>
+    <t xml:space="preserve">2.99976348876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00743126869202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98289346694946</t>
   </si>
   <si>
     <t xml:space="preserve">2.98596096038818</t>
@@ -3332,22 +3332,22 @@
     <t xml:space="preserve">2.95375490188599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99056148529053</t>
+    <t xml:space="preserve">2.99056172370911</t>
   </si>
   <si>
     <t xml:space="preserve">2.93688440322876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95682215690613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90007781982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84180068969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8740062713623</t>
+    <t xml:space="preserve">2.95682191848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9000780582428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84180045127869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87400650978088</t>
   </si>
   <si>
     <t xml:space="preserve">2.81726264953613</t>
@@ -3374,25 +3374,25 @@
     <t xml:space="preserve">2.80652666091919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81419491767883</t>
+    <t xml:space="preserve">2.81419467926025</t>
   </si>
   <si>
     <t xml:space="preserve">2.78045535087585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82646441459656</t>
+    <t xml:space="preserve">2.82646465301514</t>
   </si>
   <si>
     <t xml:space="preserve">2.84793496131897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82339715957642</t>
+    <t xml:space="preserve">2.823397397995</t>
   </si>
   <si>
     <t xml:space="preserve">2.93075013160706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90314483642578</t>
+    <t xml:space="preserve">2.90314531326294</t>
   </si>
   <si>
     <t xml:space="preserve">2.88320803642273</t>
@@ -3404,13 +3404,13 @@
     <t xml:space="preserve">2.87554001808167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90621209144592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95528841018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9752254486084</t>
+    <t xml:space="preserve">2.90621256828308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95528864860535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97522568702698</t>
   </si>
   <si>
     <t xml:space="preserve">2.98902797698975</t>
@@ -3422,19 +3422,19 @@
     <t xml:space="preserve">2.99669623374939</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02890205383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03656983375549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92001461982727</t>
+    <t xml:space="preserve">3.02890229225159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03657007217407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92001485824585</t>
   </si>
   <si>
     <t xml:space="preserve">2.93535089492798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88014101982117</t>
+    <t xml:space="preserve">2.88014078140259</t>
   </si>
   <si>
     <t xml:space="preserve">2.91234683990479</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">2.94915413856506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85560297966003</t>
+    <t xml:space="preserve">2.85560321807861</t>
   </si>
   <si>
     <t xml:space="preserve">2.80806040763855</t>
@@ -3464,13 +3464,13 @@
     <t xml:space="preserve">2.69917392730713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70684170722961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66083288192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7605185508728</t>
+    <t xml:space="preserve">2.70684194564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66083264350891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76051831245422</t>
   </si>
   <si>
     <t xml:space="preserve">2.71144270896912</t>
@@ -3485,16 +3485,16 @@
     <t xml:space="preserve">2.62249255180359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65009760856628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67770266532898</t>
+    <t xml:space="preserve">2.65009737014771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6777024269104</t>
   </si>
   <si>
     <t xml:space="preserve">2.67463541030884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74671602249146</t>
+    <t xml:space="preserve">2.74671578407288</t>
   </si>
   <si>
     <t xml:space="preserve">2.72064423561096</t>
@@ -3503,28 +3503,28 @@
     <t xml:space="preserve">2.71911072731018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69610667228699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66850066184998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75438380241394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82493090629578</t>
+    <t xml:space="preserve">2.69610643386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66850090026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75438404083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8249306678772</t>
   </si>
   <si>
     <t xml:space="preserve">2.85406947135925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89701080322266</t>
+    <t xml:space="preserve">2.89701056480408</t>
   </si>
   <si>
     <t xml:space="preserve">2.9782931804657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86327147483826</t>
+    <t xml:space="preserve">2.86327123641968</t>
   </si>
   <si>
     <t xml:space="preserve">2.94148540496826</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">3.03503656387329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02736854553223</t>
+    <t xml:space="preserve">3.02736830711365</t>
   </si>
   <si>
     <t xml:space="preserve">2.89087605476379</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">2.74058127403259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7850558757782</t>
+    <t xml:space="preserve">2.78505611419678</t>
   </si>
   <si>
     <t xml:space="preserve">2.86480474472046</t>
@@ -3563,13 +3563,13 @@
     <t xml:space="preserve">3.05187320709229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07029509544373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15472817420959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08871674537659</t>
+    <t xml:space="preserve">3.07029485702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15472841262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08871698379517</t>
   </si>
   <si>
     <t xml:space="preserve">3.19771218299866</t>
@@ -3581,22 +3581,22 @@
     <t xml:space="preserve">3.18850111961365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2529776096344</t>
+    <t xml:space="preserve">3.25297737121582</t>
   </si>
   <si>
     <t xml:space="preserve">3.16547417640686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09485745429993</t>
+    <t xml:space="preserve">3.09485769271851</t>
   </si>
   <si>
     <t xml:space="preserve">2.94748306274414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80010890960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84769892692566</t>
+    <t xml:space="preserve">2.80010914802551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8476984500885</t>
   </si>
   <si>
     <t xml:space="preserve">2.72028136253357</t>
@@ -3620,25 +3620,25 @@
     <t xml:space="preserve">2.33342409133911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5345287322998</t>
+    <t xml:space="preserve">2.53452849388123</t>
   </si>
   <si>
     <t xml:space="preserve">2.40557622909546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42860317230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5299232006073</t>
+    <t xml:space="preserve">2.42860341072083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52992296218872</t>
   </si>
   <si>
     <t xml:space="preserve">2.56983685493469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75098419189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7248866558075</t>
+    <t xml:space="preserve">2.75098443031311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72488689422607</t>
   </si>
   <si>
     <t xml:space="preserve">2.76326560974121</t>
@@ -3656,7 +3656,7 @@
     <t xml:space="preserve">2.79243326187134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73870301246643</t>
+    <t xml:space="preserve">2.73870325088501</t>
   </si>
   <si>
     <t xml:space="preserve">2.79703879356384</t>
@@ -3668,25 +3668,25 @@
     <t xml:space="preserve">2.92906141281128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85383892059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89221787452698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91831541061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89835834503174</t>
+    <t xml:space="preserve">2.85383915901184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8922176361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91831564903259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89835858345032</t>
   </si>
   <si>
     <t xml:space="preserve">2.80931997299194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7985737323761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93366694450378</t>
+    <t xml:space="preserve">2.79857397079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93366670608521</t>
   </si>
   <si>
     <t xml:space="preserve">2.94594788551331</t>
@@ -3704,22 +3704,22 @@
     <t xml:space="preserve">2.96590495109558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95208859443665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90603423118591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92752599716187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9167799949646</t>
+    <t xml:space="preserve">2.95208835601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90603399276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92752623558044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91678047180176</t>
   </si>
   <si>
     <t xml:space="preserve">2.90296387672424</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90756940841675</t>
+    <t xml:space="preserve">2.90756916999817</t>
   </si>
   <si>
     <t xml:space="preserve">2.7908980846405</t>
@@ -3731,10 +3731,10 @@
     <t xml:space="preserve">2.75712490081787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68343782424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78168725967407</t>
+    <t xml:space="preserve">2.68343806266785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78168749809265</t>
   </si>
   <si>
     <t xml:space="preserve">2.80624961853027</t>
@@ -3749,7 +3749,7 @@
     <t xml:space="preserve">2.88147187232971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86151480674744</t>
+    <t xml:space="preserve">2.86151504516602</t>
   </si>
   <si>
     <t xml:space="preserve">2.85230422019958</t>
@@ -3758,10 +3758,10 @@
     <t xml:space="preserve">2.81239008903503</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05271005630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07706642150879</t>
+    <t xml:space="preserve">3.05270981788635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07706665992737</t>
   </si>
   <si>
     <t xml:space="preserve">3.13065147399902</t>
@@ -3773,7 +3773,7 @@
     <t xml:space="preserve">3.1176609992981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07544302940369</t>
+    <t xml:space="preserve">3.07544279098511</t>
   </si>
   <si>
     <t xml:space="preserve">3.04946255683899</t>
@@ -3794,7 +3794,7 @@
     <t xml:space="preserve">3.0088677406311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96664929389954</t>
+    <t xml:space="preserve">2.96664953231812</t>
   </si>
   <si>
     <t xml:space="preserve">2.76205277442932</t>
@@ -3809,7 +3809,7 @@
     <t xml:space="preserve">2.74256753921509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66137838363647</t>
+    <t xml:space="preserve">2.66137862205505</t>
   </si>
   <si>
     <t xml:space="preserve">2.70197296142578</t>
@@ -3818,22 +3818,22 @@
     <t xml:space="preserve">2.76367664337158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78478574752808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77666711807251</t>
+    <t xml:space="preserve">2.78478598594666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77666735649109</t>
   </si>
   <si>
     <t xml:space="preserve">2.6954779624939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73282504081726</t>
+    <t xml:space="preserve">2.73282480239868</t>
   </si>
   <si>
     <t xml:space="preserve">2.69385433197021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7003493309021</t>
+    <t xml:space="preserve">2.70034909248352</t>
   </si>
   <si>
     <t xml:space="preserve">2.75880527496338</t>
@@ -3857,19 +3857,19 @@
     <t xml:space="preserve">2.67274522781372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76042938232422</t>
+    <t xml:space="preserve">2.76042914390564</t>
   </si>
   <si>
     <t xml:space="preserve">2.71821093559265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70359659194946</t>
+    <t xml:space="preserve">2.70359683036804</t>
   </si>
   <si>
     <t xml:space="preserve">2.64026927947998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51361441612244</t>
+    <t xml:space="preserve">2.51361417770386</t>
   </si>
   <si>
     <t xml:space="preserve">2.52822875976562</t>
@@ -3878,28 +3878,28 @@
     <t xml:space="preserve">2.57207036018372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69060659408569</t>
+    <t xml:space="preserve">2.69060635566711</t>
   </si>
   <si>
     <t xml:space="preserve">2.61428880691528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57856583595276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5460901260376</t>
+    <t xml:space="preserve">2.57856559753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54608988761902</t>
   </si>
   <si>
     <t xml:space="preserve">2.58343696594238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5168616771698</t>
+    <t xml:space="preserve">2.51686191558838</t>
   </si>
   <si>
     <t xml:space="preserve">2.55908012390137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62727928161621</t>
+    <t xml:space="preserve">2.62727904319763</t>
   </si>
   <si>
     <t xml:space="preserve">2.65975475311279</t>
@@ -3908,7 +3908,7 @@
     <t xml:space="preserve">2.72957730293274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66949772834778</t>
+    <t xml:space="preserve">2.6694974899292</t>
   </si>
   <si>
     <t xml:space="preserve">2.78153848648071</t>
@@ -3923,7 +3923,7 @@
     <t xml:space="preserve">2.71171569824219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70684432983398</t>
+    <t xml:space="preserve">2.70684456825256</t>
   </si>
   <si>
     <t xml:space="preserve">2.61753630638123</t>
@@ -3932,10 +3932,10 @@
     <t xml:space="preserve">2.66624975204468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60941767692566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56395173072815</t>
+    <t xml:space="preserve">2.60941743850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56395149230957</t>
   </si>
   <si>
     <t xml:space="preserve">2.56232762336731</t>
@@ -3953,7 +3953,7 @@
     <t xml:space="preserve">2.59642720222473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59805083274841</t>
+    <t xml:space="preserve">2.59805107116699</t>
   </si>
   <si>
     <t xml:space="preserve">2.58830833435059</t>
@@ -3977,10 +3977,10 @@
     <t xml:space="preserve">2.90819334983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88870811462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83999443054199</t>
+    <t xml:space="preserve">2.88870787620544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83999466896057</t>
   </si>
   <si>
     <t xml:space="preserve">2.78965735435486</t>
@@ -4001,13 +4001,13 @@
     <t xml:space="preserve">2.75393414497375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76692414283752</t>
+    <t xml:space="preserve">2.7669243812561</t>
   </si>
   <si>
     <t xml:space="preserve">2.8546085357666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79290509223938</t>
+    <t xml:space="preserve">2.7929048538208</t>
   </si>
   <si>
     <t xml:space="preserve">2.68086385726929</t>
@@ -4049,7 +4049,7 @@
     <t xml:space="preserve">2.95528316497803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94716429710388</t>
+    <t xml:space="preserve">2.9471640586853</t>
   </si>
   <si>
     <t xml:space="preserve">2.95690679550171</t>
@@ -4058,13 +4058,13 @@
     <t xml:space="preserve">3.02997708320618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04459095001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10467076301575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87409400939941</t>
+    <t xml:space="preserve">3.04459118843079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10467100143433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87409377098083</t>
   </si>
   <si>
     <t xml:space="preserve">2.8497371673584</t>
@@ -4073,7 +4073,7 @@
     <t xml:space="preserve">2.89520311355591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88708424568176</t>
+    <t xml:space="preserve">2.88708400726318</t>
   </si>
   <si>
     <t xml:space="preserve">2.91793608665466</t>
@@ -4100,13 +4100,13 @@
     <t xml:space="preserve">3.12740397453308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16637492179871</t>
+    <t xml:space="preserve">3.16637468338013</t>
   </si>
   <si>
     <t xml:space="preserve">3.14201784133911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1209089756012</t>
+    <t xml:space="preserve">3.12090873718262</t>
   </si>
   <si>
     <t xml:space="preserve">3.08031415939331</t>
@@ -4139,13 +4139,13 @@
     <t xml:space="preserve">3.18261241912842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17611742019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14039397239685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12415647506714</t>
+    <t xml:space="preserve">3.17611718177795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14039421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12415623664856</t>
   </si>
   <si>
     <t xml:space="preserve">3.17774105072021</t>
@@ -4160,10 +4160,10 @@
     <t xml:space="preserve">3.28003931045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2767915725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27029657363892</t>
+    <t xml:space="preserve">3.27679181098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2702968120575</t>
   </si>
   <si>
     <t xml:space="preserve">3.31251502037048</t>
@@ -4172,7 +4172,7 @@
     <t xml:space="preserve">3.3417432308197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29465341567993</t>
+    <t xml:space="preserve">3.29465365409851</t>
   </si>
   <si>
     <t xml:space="preserve">3.32388138771057</t>
@@ -4196,25 +4196,25 @@
     <t xml:space="preserve">3.51386404037476</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53822040557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52035880088806</t>
+    <t xml:space="preserve">3.53822064399719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52035903930664</t>
   </si>
   <si>
     <t xml:space="preserve">3.65838050842285</t>
   </si>
   <si>
-    <t xml:space="preserve">3.733074426651</t>
+    <t xml:space="preserve">3.73307466506958</t>
   </si>
   <si>
     <t xml:space="preserve">3.65675687789917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66487550735474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7022225856781</t>
+    <t xml:space="preserve">3.66487574577332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70222282409668</t>
   </si>
   <si>
     <t xml:space="preserve">3.68436098098755</t>
@@ -4241,7 +4241,7 @@
     <t xml:space="preserve">3.59830093383789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64376616477966</t>
+    <t xml:space="preserve">3.64376640319824</t>
   </si>
   <si>
     <t xml:space="preserve">3.61616206169128</t>
@@ -4250,46 +4250,46 @@
     <t xml:space="preserve">3.68598461151123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69572758674622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81101560592651</t>
+    <t xml:space="preserve">3.69572734832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81101536750793</t>
   </si>
   <si>
     <t xml:space="preserve">3.90032410621643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87921500205994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89869999885559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89382886886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9717710018158</t>
+    <t xml:space="preserve">3.87921476364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89870047569275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89382863044739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97177076339722</t>
   </si>
   <si>
     <t xml:space="preserve">3.89220499992371</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91980934143066</t>
+    <t xml:space="preserve">3.91980957984924</t>
   </si>
   <si>
     <t xml:space="preserve">3.82400631904602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41806077957153</t>
+    <t xml:space="preserve">3.41806101799011</t>
   </si>
   <si>
     <t xml:space="preserve">3.41643738746643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19885039329529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21021676063538</t>
+    <t xml:space="preserve">3.19885015487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21021699905396</t>
   </si>
   <si>
     <t xml:space="preserve">3.09492826461792</t>
@@ -4322,7 +4322,7 @@
     <t xml:space="preserve">3.1517608165741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27192068099976</t>
+    <t xml:space="preserve">3.27192091941833</t>
   </si>
   <si>
     <t xml:space="preserve">3.28815841674805</t>
@@ -4337,7 +4337,7 @@
     <t xml:space="preserve">3.34823822975159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44891285896301</t>
+    <t xml:space="preserve">3.44891262054443</t>
   </si>
   <si>
     <t xml:space="preserve">3.4342987537384</t>
@@ -4355,16 +4355,16 @@
     <t xml:space="preserve">3.34661459922791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32712888717651</t>
+    <t xml:space="preserve">3.32712912559509</t>
   </si>
   <si>
     <t xml:space="preserve">3.26704931259155</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38720870018005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43105101585388</t>
+    <t xml:space="preserve">3.38720893859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4310507774353</t>
   </si>
   <si>
     <t xml:space="preserve">3.50736904144287</t>
@@ -4373,13 +4373,13 @@
     <t xml:space="preserve">3.36934733390808</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38558530807495</t>
+    <t xml:space="preserve">3.38558506965637</t>
   </si>
   <si>
     <t xml:space="preserve">3.38233757019043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38396167755127</t>
+    <t xml:space="preserve">3.38396143913269</t>
   </si>
   <si>
     <t xml:space="preserve">3.33499121665955</t>
@@ -5880,6 +5880,9 @@
   </si>
   <si>
     <t xml:space="preserve">12.9449996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2049999237061</t>
   </si>
 </sst>
 </file>
@@ -70932,7 +70935,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.6498611111</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>484397</v>
@@ -70953,6 +70956,32 @@
         <v>1955</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.649525463</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>746823</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>13.2799997329712</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>12.8900003433228</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>13.2049999237061</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>1956</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BPSO.MI.xlsx
+++ b/data/BPSO.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1957" uniqueCount="1957">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1958" uniqueCount="1958">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,37 +47,37 @@
     <t xml:space="preserve">2.80963730812073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74855828285217</t>
+    <t xml:space="preserve">2.74855804443359</t>
   </si>
   <si>
     <t xml:space="preserve">2.71246600151062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63611698150635</t>
+    <t xml:space="preserve">2.63611745834351</t>
   </si>
   <si>
     <t xml:space="preserve">2.60835409164429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69303178787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69858431816101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61112999916077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51257061958313</t>
+    <t xml:space="preserve">2.69303202629089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69858455657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61113023757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51257085800171</t>
   </si>
   <si>
     <t xml:space="preserve">2.45565629005432</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26686644554138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38069558143616</t>
+    <t xml:space="preserve">2.2668662071228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38069534301758</t>
   </si>
   <si>
     <t xml:space="preserve">2.40568232536316</t>
@@ -86,34 +86,34 @@
     <t xml:space="preserve">2.3654260635376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51951146125793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44455075263977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35570859909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43899893760681</t>
+    <t xml:space="preserve">2.51951169967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44455099105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.355708360672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43899869918823</t>
   </si>
   <si>
     <t xml:space="preserve">2.40429425239563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32100486755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22105693817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23216223716736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20995211601257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04059624671936</t>
+    <t xml:space="preserve">2.32100534439087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22105765342712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23216271400452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20995187759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04059600830078</t>
   </si>
   <si>
     <t xml:space="preserve">2.06280660629272</t>
@@ -128,16 +128,16 @@
     <t xml:space="preserve">2.18218803405762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22522211074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27797150611877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19329357147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16553020477295</t>
+    <t xml:space="preserve">2.22522187232971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27797174453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19329333305359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16553044319153</t>
   </si>
   <si>
     <t xml:space="preserve">2.24604415893555</t>
@@ -146,16 +146,16 @@
     <t xml:space="preserve">2.18635272979736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17663598060608</t>
+    <t xml:space="preserve">2.1766357421875</t>
   </si>
   <si>
     <t xml:space="preserve">2.21550464630127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25992560386658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31822848320007</t>
+    <t xml:space="preserve">2.259925365448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31822896003723</t>
   </si>
   <si>
     <t xml:space="preserve">2.38763618469238</t>
@@ -164,52 +164,52 @@
     <t xml:space="preserve">2.38208365440369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3751425743103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24187970161438</t>
+    <t xml:space="preserve">2.37514281272888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2418794631958</t>
   </si>
   <si>
     <t xml:space="preserve">2.26270174980164</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25020813941956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31961679458618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43344521522522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35848546028137</t>
+    <t xml:space="preserve">2.25020837783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31961703300476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4334454536438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35848522186279</t>
   </si>
   <si>
     <t xml:space="preserve">2.30157017707825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34599161148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35987329483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39318871498108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29324102401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23771524429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18774056434631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13915586471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14748454093933</t>
+    <t xml:space="preserve">2.34599184989929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35987305641174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39318919181824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29324126243591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23771500587463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18774104118347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.139155626297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14748477935791</t>
   </si>
   <si>
     <t xml:space="preserve">2.1211097240448</t>
@@ -221,28 +221,28 @@
     <t xml:space="preserve">2.01283288002014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01838541030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07113528251648</t>
+    <t xml:space="preserve">2.01838564872742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07113552093506</t>
   </si>
   <si>
     <t xml:space="preserve">2.11694502830505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12527394294739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22799801826477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30295825004578</t>
+    <t xml:space="preserve">2.12527418136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22799777984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3029580116272</t>
   </si>
   <si>
     <t xml:space="preserve">2.23910307884216</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29046487808228</t>
+    <t xml:space="preserve">2.29046511650085</t>
   </si>
   <si>
     <t xml:space="preserve">2.3321099281311</t>
@@ -254,31 +254,31 @@
     <t xml:space="preserve">2.2793595790863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32378149032593</t>
+    <t xml:space="preserve">2.32378125190735</t>
   </si>
   <si>
     <t xml:space="preserve">2.30851101875305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26131391525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23493909835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15720129013062</t>
+    <t xml:space="preserve">2.26131415367126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23493885993958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15720152854919</t>
   </si>
   <si>
     <t xml:space="preserve">2.11139249801636</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08224058151245</t>
+    <t xml:space="preserve">2.08224081993103</t>
   </si>
   <si>
     <t xml:space="preserve">2.09889912605286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08918213844299</t>
+    <t xml:space="preserve">2.08918237686157</t>
   </si>
   <si>
     <t xml:space="preserve">2.10583996772766</t>
@@ -290,19 +290,19 @@
     <t xml:space="preserve">2.03781962394714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06558299064636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03226685523987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07252383232117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05725383758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05156683921814</t>
+    <t xml:space="preserve">2.0655825138092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03226733207703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07252359390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05725336074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05156707763672</t>
   </si>
   <si>
     <t xml:space="preserve">2.12691855430603</t>
@@ -311,49 +311,49 @@
     <t xml:space="preserve">2.19942760467529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1539318561554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17525815963745</t>
+    <t xml:space="preserve">2.15393233299255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17525792121887</t>
   </si>
   <si>
     <t xml:space="preserve">2.15535402297974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09279704093933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07147121429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99896252155304</t>
+    <t xml:space="preserve">2.09279680252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07147145271301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99896216392517</t>
   </si>
   <si>
     <t xml:space="preserve">1.95773220062256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87669289112091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9890102148056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93640649318695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94351482391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84114980697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78143692016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75157999992371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72598886489868</t>
+    <t xml:space="preserve">1.87669312953949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98901045322418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93640625476837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94351506233215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84114956855774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78143715858459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75158023834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7259886264801</t>
   </si>
   <si>
     <t xml:space="preserve">1.64210617542267</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">1.69613230228424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77006256580353</t>
+    <t xml:space="preserve">1.77006232738495</t>
   </si>
   <si>
     <t xml:space="preserve">1.81129336357117</t>
@@ -377,22 +377,22 @@
     <t xml:space="preserve">1.63499748706818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56533288955688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6691198348999</t>
+    <t xml:space="preserve">1.56533265113831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66911971569061</t>
   </si>
   <si>
     <t xml:space="preserve">1.65632367134094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63926267623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63641929626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57670676708221</t>
+    <t xml:space="preserve">1.6392627954483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63641917705536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57670652866364</t>
   </si>
   <si>
     <t xml:space="preserve">1.51130652427673</t>
@@ -404,55 +404,55 @@
     <t xml:space="preserve">1.53121078014374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63784098625183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67196345329285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69471108913422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67054164409637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74304974079132</t>
+    <t xml:space="preserve">1.63784086704254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67196333408356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69471096992493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67054176330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74304962158203</t>
   </si>
   <si>
     <t xml:space="preserve">1.70892798900604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72172367572784</t>
+    <t xml:space="preserve">1.72172355651855</t>
   </si>
   <si>
     <t xml:space="preserve">1.77574944496155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76721906661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72741055488586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69755423069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72456741333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7188800573349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66343247890472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55395913124084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57528495788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5212584733963</t>
+    <t xml:space="preserve">1.76721882820129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72741079330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69755434989929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72456729412079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71888041496277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66343283653259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55395901203156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57528507709503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52125871181488</t>
   </si>
   <si>
     <t xml:space="preserve">1.63357591629028</t>
@@ -461,88 +461,88 @@
     <t xml:space="preserve">1.65916705131531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64779305458069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68760204315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71461522579193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70608460903168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70039784908295</t>
+    <t xml:space="preserve">1.6477929353714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68760240077972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71461510658264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70608472824097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70039796829224</t>
   </si>
   <si>
     <t xml:space="preserve">1.74447166919708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70750629901886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72030186653137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73167562484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78285896778107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77859282493591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77148413658142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76437532901764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75584530830383</t>
+    <t xml:space="preserve">1.70750641822815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72030210494995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73167598247528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78285872936249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7785929441452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.771484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7643758058548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75584506988525</t>
   </si>
   <si>
     <t xml:space="preserve">1.76295387744904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74162757396698</t>
+    <t xml:space="preserve">1.74162805080414</t>
   </si>
   <si>
     <t xml:space="preserve">1.76864087581635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74873661994934</t>
+    <t xml:space="preserve">1.74873685836792</t>
   </si>
   <si>
     <t xml:space="preserve">1.73451924324036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78428053855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85252356529236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84967994689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81271481513977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83546257019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84825813770294</t>
+    <t xml:space="preserve">1.78428030014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85252344608307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84968018531799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81271541118622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83546280860901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84825837612152</t>
   </si>
   <si>
     <t xml:space="preserve">1.85963201522827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9477801322937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97621464729309</t>
+    <t xml:space="preserve">1.94778025150299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9762145280838</t>
   </si>
   <si>
     <t xml:space="preserve">2.09848403930664</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">2.07573628425598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08568835258484</t>
+    <t xml:space="preserve">2.08568859100342</t>
   </si>
   <si>
     <t xml:space="preserve">2.08853197097778</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">2.09706234931946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16104102134705</t>
+    <t xml:space="preserve">2.16104054450989</t>
   </si>
   <si>
     <t xml:space="preserve">2.18236660957336</t>
@@ -572,13 +572,13 @@
     <t xml:space="preserve">2.11412310600281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00038385391235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0387716293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00891423225403</t>
+    <t xml:space="preserve">2.00038409233093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03877139091492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00891447067261</t>
   </si>
   <si>
     <t xml:space="preserve">2.05298852920532</t>
@@ -587,91 +587,91 @@
     <t xml:space="preserve">2.06294083595276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11554503440857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12549662590027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16246247291565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15961885452271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13260555267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08142304420471</t>
+    <t xml:space="preserve">2.11554479598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12549686431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16246271133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15961909294128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13260579109192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08142328262329</t>
   </si>
   <si>
     <t xml:space="preserve">2.03592777252197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07715845108032</t>
+    <t xml:space="preserve">2.07715797424316</t>
   </si>
   <si>
     <t xml:space="preserve">2.09990572929382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08995389938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01033592224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12407517433167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10417079925537</t>
+    <t xml:space="preserve">2.08995342254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01033639907837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12407493591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10417103767395</t>
   </si>
   <si>
     <t xml:space="preserve">2.07289290428162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16814947128296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27477955818176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37430143356323</t>
+    <t xml:space="preserve">2.16814923286438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27478003501892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37430167198181</t>
   </si>
   <si>
     <t xml:space="preserve">2.2634060382843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23354911804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27193641662598</t>
+    <t xml:space="preserve">2.23354887962341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2719361782074</t>
   </si>
   <si>
     <t xml:space="preserve">2.23212718963623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1781017780304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16957116127014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23639273643494</t>
+    <t xml:space="preserve">2.17810153961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16957139968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23639249801636</t>
   </si>
   <si>
     <t xml:space="preserve">2.22217512130737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21790981292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2051146030426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22359728813171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26482772827148</t>
+    <t xml:space="preserve">2.2179102897644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20511436462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22359704971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26482796669006</t>
   </si>
   <si>
     <t xml:space="preserve">2.31032299995422</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">2.34302282333374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34160113334656</t>
+    <t xml:space="preserve">2.34160089492798</t>
   </si>
   <si>
     <t xml:space="preserve">2.30463576316833</t>
@@ -695,34 +695,34 @@
     <t xml:space="preserve">2.29610586166382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36008358001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3529748916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34017944335938</t>
+    <t xml:space="preserve">2.36008381843567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35297513008118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3401792049408</t>
   </si>
   <si>
     <t xml:space="preserve">2.4027361869812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41695356369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45249652862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41126656532288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41553211212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42406225204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44396638870239</t>
+    <t xml:space="preserve">2.41695332527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45249676704407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4112663269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.415531873703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42406249046326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44396615028381</t>
   </si>
   <si>
     <t xml:space="preserve">2.35439658164978</t>
@@ -740,10 +740,10 @@
     <t xml:space="preserve">2.32738375663757</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28188848495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30037117004395</t>
+    <t xml:space="preserve">2.28188824653625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30037093162537</t>
   </si>
   <si>
     <t xml:space="preserve">2.32311868667603</t>
@@ -752,22 +752,22 @@
     <t xml:space="preserve">2.33449244499207</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30890130996704</t>
+    <t xml:space="preserve">2.30890154838562</t>
   </si>
   <si>
     <t xml:space="preserve">2.29894924163818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25629782676697</t>
+    <t xml:space="preserve">2.25629734992981</t>
   </si>
   <si>
     <t xml:space="preserve">2.12834072113037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13402700424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2847318649292</t>
+    <t xml:space="preserve">2.13402724266052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28473210334778</t>
   </si>
   <si>
     <t xml:space="preserve">2.22928404808044</t>
@@ -776,13 +776,13 @@
     <t xml:space="preserve">2.27335786819458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27904534339905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31316637992859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33875775337219</t>
+    <t xml:space="preserve">2.27904486656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31316661834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33875751495361</t>
   </si>
   <si>
     <t xml:space="preserve">2.37856674194336</t>
@@ -791,121 +791,121 @@
     <t xml:space="preserve">2.32880568504333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36719250679016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34870958328247</t>
+    <t xml:space="preserve">2.367192029953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34870982170105</t>
   </si>
   <si>
     <t xml:space="preserve">2.29468393325806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30321431159973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28757524490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32027506828308</t>
+    <t xml:space="preserve">2.30321455001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28757548332214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32027530670166</t>
   </si>
   <si>
     <t xml:space="preserve">2.2833104133606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29041886329651</t>
+    <t xml:space="preserve">2.29041862487793</t>
   </si>
   <si>
     <t xml:space="preserve">2.29326224327087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30605816841125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35581827163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31174468994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33164882659912</t>
+    <t xml:space="preserve">2.30605792999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35581851005554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31174492835999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3316490650177</t>
   </si>
   <si>
     <t xml:space="preserve">2.46671390533447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43117070198059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42974925041199</t>
+    <t xml:space="preserve">2.43117094039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42974877357483</t>
   </si>
   <si>
     <t xml:space="preserve">2.49799299240112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46387052536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48661804199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51647520065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51789712905884</t>
+    <t xml:space="preserve">2.46387076377869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48661828041077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51647543907166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51789689064026</t>
   </si>
   <si>
     <t xml:space="preserve">2.56907916069031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53353595733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48804020881653</t>
+    <t xml:space="preserve">2.53353571891785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48803997039795</t>
   </si>
   <si>
     <t xml:space="preserve">2.50510120391846</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50794506072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50936651229858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50652313232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5548620223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57221221923828</t>
+    <t xml:space="preserve">2.5079448223114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50936675071716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50652289390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55486178398132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5722119808197</t>
   </si>
   <si>
     <t xml:space="preserve">2.63293862342834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65607309341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70667862892151</t>
+    <t xml:space="preserve">2.65607333183289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70667886734009</t>
   </si>
   <si>
     <t xml:space="preserve">2.56642913818359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52594399452209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52883553504944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47389245033264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52160620689392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51437664031982</t>
+    <t xml:space="preserve">2.52594351768494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52883577346802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47389268875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5216064453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5143768787384</t>
   </si>
   <si>
     <t xml:space="preserve">2.4710009098053</t>
@@ -926,22 +926,22 @@
     <t xml:space="preserve">2.47967600822449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46087956428528</t>
+    <t xml:space="preserve">2.46087980270386</t>
   </si>
   <si>
     <t xml:space="preserve">2.48112177848816</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45798802375793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48256754875183</t>
+    <t xml:space="preserve">2.45798778533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48256802558899</t>
   </si>
   <si>
     <t xml:space="preserve">2.48835110664368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48690533638</t>
+    <t xml:space="preserve">2.48690509796143</t>
   </si>
   <si>
     <t xml:space="preserve">2.50859355926514</t>
@@ -953,25 +953,25 @@
     <t xml:space="preserve">2.60257530212402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55919933319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49558091163635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.592453956604</t>
+    <t xml:space="preserve">2.5591995716095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49558067321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59245419502258</t>
   </si>
   <si>
     <t xml:space="preserve">2.6633026599884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61414241790771</t>
+    <t xml:space="preserve">2.61414265632629</t>
   </si>
   <si>
     <t xml:space="preserve">2.63149261474609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62281727790833</t>
+    <t xml:space="preserve">2.6228175163269</t>
   </si>
   <si>
     <t xml:space="preserve">2.61703395843506</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">2.72692060470581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73704195022583</t>
+    <t xml:space="preserve">2.73704171180725</t>
   </si>
   <si>
     <t xml:space="preserve">2.72258305549622</t>
@@ -1001,13 +1001,13 @@
     <t xml:space="preserve">2.68643617630005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68788194656372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7110161781311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6502890586853</t>
+    <t xml:space="preserve">2.6878821849823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71101641654968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65028882026672</t>
   </si>
   <si>
     <t xml:space="preserve">2.67920732498169</t>
@@ -1016,34 +1016,34 @@
     <t xml:space="preserve">2.67197775840759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67053174972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65318083763123</t>
+    <t xml:space="preserve">2.67053198814392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65318059921265</t>
   </si>
   <si>
     <t xml:space="preserve">2.65173506736755</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66764044761658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65896511077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64595127105713</t>
+    <t xml:space="preserve">2.66763997077942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65896534919739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64595150947571</t>
   </si>
   <si>
     <t xml:space="preserve">2.59823775291443</t>
   </si>
   <si>
-    <t xml:space="preserve">2.624263048172</t>
+    <t xml:space="preserve">2.62426352500916</t>
   </si>
   <si>
     <t xml:space="preserve">2.60402131080627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54474091529846</t>
+    <t xml:space="preserve">2.54474067687988</t>
   </si>
   <si>
     <t xml:space="preserve">2.57654976844788</t>
@@ -1055,16 +1055,16 @@
     <t xml:space="preserve">2.48545956611633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50281000137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52016019821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51148533821106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.518714427948</t>
+    <t xml:space="preserve">2.50280976295471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52016043663025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51148509979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51871418952942</t>
   </si>
   <si>
     <t xml:space="preserve">2.53317308425903</t>
@@ -1073,13 +1073,13 @@
     <t xml:space="preserve">2.5519700050354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50714731216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55052423477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54618620872498</t>
+    <t xml:space="preserve">2.50714755058289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55052375793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54618644714355</t>
   </si>
   <si>
     <t xml:space="preserve">2.53606534004211</t>
@@ -1088,13 +1088,13 @@
     <t xml:space="preserve">2.5794415473938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64161396026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.630047082901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58956289291382</t>
+    <t xml:space="preserve">2.64161348342896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63004684448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58956265449524</t>
   </si>
   <si>
     <t xml:space="preserve">2.52305197715759</t>
@@ -1103,16 +1103,16 @@
     <t xml:space="preserve">2.51582264900208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49268889427185</t>
+    <t xml:space="preserve">2.49268913269043</t>
   </si>
   <si>
     <t xml:space="preserve">2.53461885452271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49124312400818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47244644165039</t>
+    <t xml:space="preserve">2.4912428855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47244668006897</t>
   </si>
   <si>
     <t xml:space="preserve">2.50425577163696</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">2.49413466453552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49847221374512</t>
+    <t xml:space="preserve">2.4984724521637</t>
   </si>
   <si>
     <t xml:space="preserve">2.47823023796082</t>
@@ -1136,61 +1136,61 @@
     <t xml:space="preserve">2.44931268692017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40738201141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45509648323059</t>
+    <t xml:space="preserve">2.407381772995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45509600639343</t>
   </si>
   <si>
     <t xml:space="preserve">2.41027355194092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29605031013489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24688982963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28159117698669</t>
+    <t xml:space="preserve">2.29605054855347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2468900680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28159093856812</t>
   </si>
   <si>
     <t xml:space="preserve">2.18471765518188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19773077964783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22086453437805</t>
+    <t xml:space="preserve">2.19773054122925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22086405754089</t>
   </si>
   <si>
     <t xml:space="preserve">2.26279449462891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28448247909546</t>
+    <t xml:space="preserve">2.28448224067688</t>
   </si>
   <si>
     <t xml:space="preserve">2.28592824935913</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32496738433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34810137748718</t>
+    <t xml:space="preserve">2.32496762275696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34810161590576</t>
   </si>
   <si>
     <t xml:space="preserve">2.3784646987915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41461229324341</t>
+    <t xml:space="preserve">2.41461253166199</t>
   </si>
   <si>
     <t xml:space="preserve">2.34231781959534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35677647590637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35966825485229</t>
+    <t xml:space="preserve">2.35677671432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35966849327087</t>
   </si>
   <si>
     <t xml:space="preserve">2.34087204933167</t>
@@ -1199,19 +1199,19 @@
     <t xml:space="preserve">2.37701869010925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39292335510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40015292167664</t>
+    <t xml:space="preserve">2.39292359352112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40015244483948</t>
   </si>
   <si>
     <t xml:space="preserve">2.4059362411499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33653450012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29315781593323</t>
+    <t xml:space="preserve">2.33653426170349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29315757751465</t>
   </si>
   <si>
     <t xml:space="preserve">2.20495986938477</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">2.23966073989868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23821496963501</t>
+    <t xml:space="preserve">2.23821473121643</t>
   </si>
   <si>
     <t xml:space="preserve">2.23387694358826</t>
@@ -1229,19 +1229,19 @@
     <t xml:space="preserve">2.18327188491821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21797275543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24544382095337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20062208175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22664785385132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28303694725037</t>
+    <t xml:space="preserve">2.21797251701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24544405937195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20062232017517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22664761543274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28303670883179</t>
   </si>
   <si>
     <t xml:space="preserve">2.31340050697327</t>
@@ -1250,13 +1250,13 @@
     <t xml:space="preserve">2.31050896644592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38858532905579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38713955879211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34665560722351</t>
+    <t xml:space="preserve">2.38858580589294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38713979721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34665584564209</t>
   </si>
   <si>
     <t xml:space="preserve">2.34520983695984</t>
@@ -1271,28 +1271,28 @@
     <t xml:space="preserve">2.4030442237854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40449023246765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32785940170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34954714775085</t>
+    <t xml:space="preserve">2.40449047088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32785964012146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34954690933228</t>
   </si>
   <si>
     <t xml:space="preserve">2.33364272117615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31195473670959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22953963279724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31484651565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30327963829041</t>
+    <t xml:space="preserve">2.31195449829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22953987121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3148467540741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30327939987183</t>
   </si>
   <si>
     <t xml:space="preserve">2.32062983512878</t>
@@ -1304,31 +1304,31 @@
     <t xml:space="preserve">2.37268114089966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42907047271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36400580406189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31629252433777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35388493537903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27725315093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32930517196655</t>
+    <t xml:space="preserve">2.42907071113586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36400604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31629228591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35388469696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27725338935852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32930541038513</t>
   </si>
   <si>
     <t xml:space="preserve">2.30617141723633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30038809776306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37412691116333</t>
+    <t xml:space="preserve">2.30038785934448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37412714958191</t>
   </si>
   <si>
     <t xml:space="preserve">2.33075094223022</t>
@@ -1346,25 +1346,25 @@
     <t xml:space="preserve">2.38569402694702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60112929344177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71969103813171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70956993103027</t>
+    <t xml:space="preserve">2.60112977027893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71969151496887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70957016944885</t>
   </si>
   <si>
     <t xml:space="preserve">2.75439214706421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77752709388733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84837412834167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84114503860474</t>
+    <t xml:space="preserve">2.77752685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84837436676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84114480018616</t>
   </si>
   <si>
     <t xml:space="preserve">2.83391547203064</t>
@@ -1373,10 +1373,10 @@
     <t xml:space="preserve">2.86861610412598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90042614936829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82957768440247</t>
+    <t xml:space="preserve">2.90042591094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82957816123962</t>
   </si>
   <si>
     <t xml:space="preserve">2.73125839233398</t>
@@ -1385,16 +1385,16 @@
     <t xml:space="preserve">2.78620195388794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7558376789093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82524061203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80644392967224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83680748939514</t>
+    <t xml:space="preserve">2.75583791732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82524037361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80644416809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83680725097656</t>
   </si>
   <si>
     <t xml:space="preserve">2.74716305732727</t>
@@ -1403,19 +1403,19 @@
     <t xml:space="preserve">2.7384877204895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6343846321106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66091966629028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65060043334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71251678466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70367097854614</t>
+    <t xml:space="preserve">2.63438439369202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66091990470886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65060067176819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71251702308655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70367121696472</t>
   </si>
   <si>
     <t xml:space="preserve">2.63143610954285</t>
@@ -1427,10 +1427,10 @@
     <t xml:space="preserve">2.48254251480103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52234554290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56509709358215</t>
+    <t xml:space="preserve">2.52234578132629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56509685516357</t>
   </si>
   <si>
     <t xml:space="preserve">2.6107976436615</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">2.618168592453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59015941619873</t>
+    <t xml:space="preserve">2.59015893936157</t>
   </si>
   <si>
     <t xml:space="preserve">2.54888105392456</t>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">2.55625176429749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54593253135681</t>
+    <t xml:space="preserve">2.54593276977539</t>
   </si>
   <si>
     <t xml:space="preserve">2.57099390029907</t>
@@ -1475,13 +1475,13 @@
     <t xml:space="preserve">2.53708744049072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54150986671448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65354871749878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65944576263428</t>
+    <t xml:space="preserve">2.54151010513306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65354895591736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6594455242157</t>
   </si>
   <si>
     <t xml:space="preserve">2.70514535903931</t>
@@ -1490,16 +1490,16 @@
     <t xml:space="preserve">2.6904034614563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65797162055969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61964273452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63291025161743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64912605285645</t>
+    <t xml:space="preserve">2.65797185897827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61964249610901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63291049003601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64912629127502</t>
   </si>
   <si>
     <t xml:space="preserve">2.64322948455811</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">2.6653425693512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64470386505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63880705833435</t>
+    <t xml:space="preserve">2.64470410346985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63880729675293</t>
   </si>
   <si>
     <t xml:space="preserve">2.66386818885803</t>
@@ -1520,7 +1520,7 @@
     <t xml:space="preserve">2.71399116516113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73168182373047</t>
+    <t xml:space="preserve">2.73168158531189</t>
   </si>
   <si>
     <t xml:space="preserve">2.71693968772888</t>
@@ -1529,25 +1529,25 @@
     <t xml:space="preserve">2.73315572738647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78180336952209</t>
+    <t xml:space="preserve">2.78180360794067</t>
   </si>
   <si>
     <t xml:space="preserve">2.70661950111389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69187760353088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68892931938171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6771354675293</t>
+    <t xml:space="preserve">2.69187784194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68892955780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67713570594788</t>
   </si>
   <si>
     <t xml:space="preserve">2.64617800712585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64175534248352</t>
+    <t xml:space="preserve">2.6417555809021</t>
   </si>
   <si>
     <t xml:space="preserve">2.57541632652283</t>
@@ -1556,25 +1556,25 @@
     <t xml:space="preserve">2.61374592781067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60932326316833</t>
+    <t xml:space="preserve">2.60932350158691</t>
   </si>
   <si>
     <t xml:space="preserve">2.58868479728699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58131289482117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53561305999756</t>
+    <t xml:space="preserve">2.58131313323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53561353683472</t>
   </si>
   <si>
     <t xml:space="preserve">2.48843932151794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47222352027893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50170707702637</t>
+    <t xml:space="preserve">2.47222375869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50170683860779</t>
   </si>
   <si>
     <t xml:space="preserve">2.56362271308899</t>
@@ -1583,13 +1583,13 @@
     <t xml:space="preserve">2.67123913764954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67418766021729</t>
+    <t xml:space="preserve">2.67418742179871</t>
   </si>
   <si>
     <t xml:space="preserve">2.65502285957336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68450665473938</t>
+    <t xml:space="preserve">2.68450689315796</t>
   </si>
   <si>
     <t xml:space="preserve">2.66239380836487</t>
@@ -1619,10 +1619,10 @@
     <t xml:space="preserve">2.38966822624207</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41325545310974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33659672737122</t>
+    <t xml:space="preserve">2.41325497627258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33659648895264</t>
   </si>
   <si>
     <t xml:space="preserve">2.24667167663574</t>
@@ -1631,25 +1631,25 @@
     <t xml:space="preserve">2.23045563697815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22898149490356</t>
+    <t xml:space="preserve">2.22898125648499</t>
   </si>
   <si>
     <t xml:space="preserve">2.16706514358521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18033266067505</t>
+    <t xml:space="preserve">2.18033242225647</t>
   </si>
   <si>
     <t xml:space="preserve">2.15674543380737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20244526863098</t>
+    <t xml:space="preserve">2.20244550704956</t>
   </si>
   <si>
     <t xml:space="preserve">2.19360017776489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13905549049377</t>
+    <t xml:space="preserve">2.13905572891235</t>
   </si>
   <si>
     <t xml:space="preserve">2.11399412155151</t>
@@ -1658,46 +1658,46 @@
     <t xml:space="preserve">2.08745837211609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04175853729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00932645797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05207777023315</t>
+    <t xml:space="preserve">2.0417582988739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00932621955872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05207753181458</t>
   </si>
   <si>
     <t xml:space="preserve">2.105149269104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05797433853149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0550262928009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09335589408875</t>
+    <t xml:space="preserve">2.05797410011292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05502605438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09335565567017</t>
   </si>
   <si>
     <t xml:space="preserve">2.13610696792603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11694240570068</t>
+    <t xml:space="preserve">2.11694264411926</t>
   </si>
   <si>
     <t xml:space="preserve">2.09925270080566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10220050811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10072684288025</t>
+    <t xml:space="preserve">2.10220074653625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10072636604309</t>
   </si>
   <si>
     <t xml:space="preserve">2.09040641784668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04912948608398</t>
+    <t xml:space="preserve">2.04912924766541</t>
   </si>
   <si>
     <t xml:space="preserve">2.06829380989075</t>
@@ -1712,61 +1712,61 @@
     <t xml:space="preserve">2.02701663970947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01964592933655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97394597530365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97984278202057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96215176582336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98426520824432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08008742332458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06387114524841</t>
+    <t xml:space="preserve">2.01964569091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97394585609436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97984254360199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96215164661407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98426532745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08008718490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06387090682983</t>
   </si>
   <si>
     <t xml:space="preserve">2.07861280441284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04618120193481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0859842300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05650019645691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95625495910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98279058933258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9444614648819</t>
+    <t xml:space="preserve">2.04618096351624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08598351478577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05650043487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95625483989716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98279082775116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94446122646332</t>
   </si>
   <si>
     <t xml:space="preserve">1.93709051609039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9665744304657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9680483341217</t>
+    <t xml:space="preserve">1.96657431125641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96804821491241</t>
   </si>
   <si>
     <t xml:space="preserve">1.89286506175995</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98131668567657</t>
+    <t xml:space="preserve">1.98131680488586</t>
   </si>
   <si>
     <t xml:space="preserve">1.91497790813446</t>
@@ -1775,19 +1775,19 @@
     <t xml:space="preserve">1.87517476081848</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8737006187439</t>
+    <t xml:space="preserve">1.87370038032532</t>
   </si>
   <si>
     <t xml:space="preserve">1.94003880023956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92677104473114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99311029911041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00342965126038</t>
+    <t xml:space="preserve">1.92677128314972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9931104183197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0034294128418</t>
   </si>
   <si>
     <t xml:space="preserve">1.994584441185</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">1.94888412952423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88844239711761</t>
+    <t xml:space="preserve">1.8884425163269</t>
   </si>
   <si>
     <t xml:space="preserve">1.87222623825073</t>
@@ -1808,10 +1808,10 @@
     <t xml:space="preserve">1.91940033435822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89433920383453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86485517024994</t>
+    <t xml:space="preserve">1.89433896541595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86485540866852</t>
   </si>
   <si>
     <t xml:space="preserve">1.85306215286255</t>
@@ -1832,16 +1832,16 @@
     <t xml:space="preserve">1.78230011463165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71596133708954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69532251358032</t>
+    <t xml:space="preserve">1.71596121788025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69532263278961</t>
   </si>
   <si>
     <t xml:space="preserve">1.71006441116333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73217809200287</t>
+    <t xml:space="preserve">1.73217797279358</t>
   </si>
   <si>
     <t xml:space="preserve">1.78377437591553</t>
@@ -1856,7 +1856,7 @@
     <t xml:space="preserve">1.78672289848328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80588710308075</t>
+    <t xml:space="preserve">1.80588722229004</t>
   </si>
   <si>
     <t xml:space="preserve">1.83389687538147</t>
@@ -1868,10 +1868,10 @@
     <t xml:space="preserve">1.86927795410156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84569013118744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83979368209839</t>
+    <t xml:space="preserve">1.84569036960602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83979344367981</t>
   </si>
   <si>
     <t xml:space="preserve">1.83242249488831</t>
@@ -1880,109 +1880,109 @@
     <t xml:space="preserve">1.84274184703827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83684504032135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89728724956512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88991630077362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88254570960999</t>
+    <t xml:space="preserve">1.83684527873993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8972874879837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88991641998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88254547119141</t>
   </si>
   <si>
     <t xml:space="preserve">1.91055500507355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87075209617615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80293893814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80441296100616</t>
+    <t xml:space="preserve">1.87075197696686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80293881893158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80441308021545</t>
   </si>
   <si>
     <t xml:space="preserve">1.79114532470703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75576496124268</t>
+    <t xml:space="preserve">1.75576484203339</t>
   </si>
   <si>
     <t xml:space="preserve">1.81325829029083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81178414821625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83537089824677</t>
+    <t xml:space="preserve">1.81178390979767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83537101745605</t>
   </si>
   <si>
     <t xml:space="preserve">1.79556810855865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77492928504944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80883574485779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79851615428925</t>
+    <t xml:space="preserve">1.77492940425873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80883586406708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79851627349854</t>
   </si>
   <si>
     <t xml:space="preserve">1.79704225063324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80736148357391</t>
+    <t xml:space="preserve">1.8073616027832</t>
   </si>
   <si>
     <t xml:space="preserve">1.78082621097565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75429058074951</t>
+    <t xml:space="preserve">1.7542906999588</t>
   </si>
   <si>
     <t xml:space="preserve">1.71301281452179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70711636543274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74544548988342</t>
+    <t xml:space="preserve">1.70711624622345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.745445728302</t>
   </si>
   <si>
     <t xml:space="preserve">1.76460993289948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77198112010956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77787780761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78819715976715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74839389324188</t>
+    <t xml:space="preserve">1.77198076248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77787756919861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78819692134857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74839413166046</t>
   </si>
   <si>
     <t xml:space="preserve">1.6658388376236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67910647392273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61129426956177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57886123657227</t>
+    <t xml:space="preserve">1.67910659313202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6112939119339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57886111736298</t>
   </si>
   <si>
     <t xml:space="preserve">1.53610992431641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55822253227234</t>
+    <t xml:space="preserve">1.55822277069092</t>
   </si>
   <si>
     <t xml:space="preserve">1.54200673103333</t>
@@ -1994,34 +1994,34 @@
     <t xml:space="preserve">1.53596556186676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56466102600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54351711273193</t>
+    <t xml:space="preserve">1.56466090679169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54351699352264</t>
   </si>
   <si>
     <t xml:space="preserve">1.55559909343719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53898620605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54502737522125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60543859004974</t>
+    <t xml:space="preserve">1.5389860868454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54502725601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60543847084045</t>
   </si>
   <si>
     <t xml:space="preserve">1.58429443836212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56768155097961</t>
+    <t xml:space="preserve">1.56768143177032</t>
   </si>
   <si>
     <t xml:space="preserve">1.56919169425964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58882522583008</t>
+    <t xml:space="preserve">1.58882546424866</t>
   </si>
   <si>
     <t xml:space="preserve">1.51028990745544</t>
@@ -2048,31 +2048,31 @@
     <t xml:space="preserve">1.46875727176666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49367666244507</t>
+    <t xml:space="preserve">1.49367690086365</t>
   </si>
   <si>
     <t xml:space="preserve">1.48386001586914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50047326087952</t>
+    <t xml:space="preserve">1.50047314167023</t>
   </si>
   <si>
     <t xml:space="preserve">1.45894038677216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46800196170807</t>
+    <t xml:space="preserve">1.46800220012665</t>
   </si>
   <si>
     <t xml:space="preserve">1.48990118503571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48234975337982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48083961009979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53294503688812</t>
+    <t xml:space="preserve">1.4823499917984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4808394908905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53294491767883</t>
   </si>
   <si>
     <t xml:space="preserve">1.57523286342621</t>
@@ -2090,7 +2090,7 @@
     <t xml:space="preserve">1.47328805923462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47253286838531</t>
+    <t xml:space="preserve">1.4725329875946</t>
   </si>
   <si>
     <t xml:space="preserve">1.44912350177765</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">1.46649181842804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44987881183624</t>
+    <t xml:space="preserve">1.44987869262695</t>
   </si>
   <si>
     <t xml:space="preserve">1.44610297679901</t>
@@ -2111,19 +2111,19 @@
     <t xml:space="preserve">1.43779647350311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42269372940063</t>
+    <t xml:space="preserve">1.42269361019135</t>
   </si>
   <si>
     <t xml:space="preserve">1.42042815685272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42722451686859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41665256023407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40683555603027</t>
+    <t xml:space="preserve">1.4272243976593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41665244102478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40683567523956</t>
   </si>
   <si>
     <t xml:space="preserve">1.400794506073</t>
@@ -2138,55 +2138,55 @@
     <t xml:space="preserve">1.28374695777893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25354063510895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25127518177032</t>
+    <t xml:space="preserve">1.25354051589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25127530097961</t>
   </si>
   <si>
     <t xml:space="preserve">1.20068061351776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23617243766785</t>
+    <t xml:space="preserve">1.23617231845856</t>
   </si>
   <si>
     <t xml:space="preserve">1.25278532505035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22182476520538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23088645935059</t>
+    <t xml:space="preserve">1.2218245267868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2308863401413</t>
   </si>
   <si>
     <t xml:space="preserve">1.27695071697235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26637876033783</t>
+    <t xml:space="preserve">1.26637887954712</t>
   </si>
   <si>
     <t xml:space="preserve">1.27619552612305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31395268440247</t>
+    <t xml:space="preserve">1.31395256519318</t>
   </si>
   <si>
     <t xml:space="preserve">1.27090954780579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28223657608032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28752255439758</t>
+    <t xml:space="preserve">1.28223669528961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28752267360687</t>
   </si>
   <si>
     <t xml:space="preserve">1.35775077342987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38342559337616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37436366081238</t>
+    <t xml:space="preserve">1.38342571258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37436378002167</t>
   </si>
   <si>
     <t xml:space="preserve">1.35246479511261</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">1.4098562002182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39852905273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36681234836578</t>
+    <t xml:space="preserve">1.39852917194366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36681246757507</t>
   </si>
   <si>
     <t xml:space="preserve">1.350954413414</t>
@@ -2207,25 +2207,25 @@
     <t xml:space="preserve">1.35926103591919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36454713344574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33736193180084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30262541770935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2897881269455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26109266281128</t>
+    <t xml:space="preserve">1.36454701423645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33736181259155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30262529850006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28978824615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26109290122986</t>
   </si>
   <si>
     <t xml:space="preserve">1.26864409446716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25505077838898</t>
+    <t xml:space="preserve">1.25505089759827</t>
   </si>
   <si>
     <t xml:space="preserve">1.27468526363373</t>
@@ -2237,43 +2237,43 @@
     <t xml:space="preserve">1.25958156585693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25429570674896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26939940452576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2814816236496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30413568019867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33660686016083</t>
+    <t xml:space="preserve">1.25429558753967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26939928531647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28148138523102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30413579940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33660697937012</t>
   </si>
   <si>
     <t xml:space="preserve">1.36077129840851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38871240615845</t>
+    <t xml:space="preserve">1.38871252536774</t>
   </si>
   <si>
     <t xml:space="preserve">1.38267040252686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35170960426331</t>
+    <t xml:space="preserve">1.3517097234726</t>
   </si>
   <si>
     <t xml:space="preserve">1.35699558258057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36152648925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36228156089783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34113788604736</t>
+    <t xml:space="preserve">1.3615266084671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36228168010712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34113776683807</t>
   </si>
   <si>
     <t xml:space="preserve">1.36756765842438</t>
@@ -2291,16 +2291,16 @@
     <t xml:space="preserve">1.40532541275024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43477594852448</t>
+    <t xml:space="preserve">1.43477582931519</t>
   </si>
   <si>
     <t xml:space="preserve">1.62960302829742</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5827841758728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57825350761414</t>
+    <t xml:space="preserve">1.58278429508209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57825362682343</t>
   </si>
   <si>
     <t xml:space="preserve">1.58127391338348</t>
@@ -2309,13 +2309,13 @@
     <t xml:space="preserve">1.54653751850128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53747594356537</t>
+    <t xml:space="preserve">1.53747582435608</t>
   </si>
   <si>
     <t xml:space="preserve">1.52237296104431</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55257856845856</t>
+    <t xml:space="preserve">1.55257868766785</t>
   </si>
   <si>
     <t xml:space="preserve">1.60241782665253</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">1.60090756416321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62054145336151</t>
+    <t xml:space="preserve">1.62054133415222</t>
   </si>
   <si>
     <t xml:space="preserve">1.54955792427063</t>
@@ -2339,25 +2339,25 @@
     <t xml:space="preserve">1.61147952079773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.641685962677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61298990249634</t>
+    <t xml:space="preserve">1.64168608188629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61298978328705</t>
   </si>
   <si>
     <t xml:space="preserve">1.61752068996429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59184598922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58731496334076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6190310716629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57976377010345</t>
+    <t xml:space="preserve">1.59184587001801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58731508255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61903119087219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57976365089417</t>
   </si>
   <si>
     <t xml:space="preserve">1.56013000011444</t>
@@ -2366,10 +2366,10 @@
     <t xml:space="preserve">1.55861973762512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59788691997528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60392796993256</t>
+    <t xml:space="preserve">1.59788703918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60392820835114</t>
   </si>
   <si>
     <t xml:space="preserve">1.58580482006073</t>
@@ -2378,7 +2378,7 @@
     <t xml:space="preserve">1.59939742088318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59637665748596</t>
+    <t xml:space="preserve">1.59637677669525</t>
   </si>
   <si>
     <t xml:space="preserve">1.59033560752869</t>
@@ -2390,7 +2390,7 @@
     <t xml:space="preserve">1.51331114768982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50953495502472</t>
+    <t xml:space="preserve">1.50953483581543</t>
   </si>
   <si>
     <t xml:space="preserve">1.52388334274292</t>
@@ -2402,10 +2402,10 @@
     <t xml:space="preserve">1.63866460323334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75948810577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80630743503571</t>
+    <t xml:space="preserve">1.75948798656464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.806307554245</t>
   </si>
   <si>
     <t xml:space="preserve">1.78365325927734</t>
@@ -2417,31 +2417,31 @@
     <t xml:space="preserve">2.02983069419861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06909799575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94827473163605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89088308811188</t>
+    <t xml:space="preserve">2.06909823417664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94827461242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89088332653046</t>
   </si>
   <si>
     <t xml:space="preserve">1.7791223526001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77308130264282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81687939167023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70813834667206</t>
+    <t xml:space="preserve">1.77308106422424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81687951087952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70813858509064</t>
   </si>
   <si>
     <t xml:space="preserve">1.4800843000412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37511909008026</t>
+    <t xml:space="preserve">1.37511885166168</t>
   </si>
   <si>
     <t xml:space="preserve">1.3245245218277</t>
@@ -2453,10 +2453,10 @@
     <t xml:space="preserve">1.19917047023773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18406784534454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959789216518402</t>
+    <t xml:space="preserve">1.18406772613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959789276123047</t>
   </si>
   <si>
     <t xml:space="preserve">0.995280981063843</t>
@@ -2465,10 +2465,10 @@
     <t xml:space="preserve">0.919011652469635</t>
   </si>
   <si>
-    <t xml:space="preserve">0.945441544055939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96280974149704</t>
+    <t xml:space="preserve">0.945441663265228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962809920310974</t>
   </si>
   <si>
     <t xml:space="preserve">1.01869106292725</t>
@@ -2477,22 +2477,22 @@
     <t xml:space="preserve">1.04361057281494</t>
   </si>
   <si>
-    <t xml:space="preserve">0.990750193595886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07155072689056</t>
+    <t xml:space="preserve">0.990750133991241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07155084609985</t>
   </si>
   <si>
     <t xml:space="preserve">1.07910239696503</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06777513027191</t>
+    <t xml:space="preserve">1.0677752494812</t>
   </si>
   <si>
     <t xml:space="preserve">1.01944613456726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999811828136444</t>
+    <t xml:space="preserve">0.999811768531799</t>
   </si>
   <si>
     <t xml:space="preserve">1.0413453578949</t>
@@ -2504,7 +2504,7 @@
     <t xml:space="preserve">1.10628736019135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05720329284668</t>
+    <t xml:space="preserve">1.05720317363739</t>
   </si>
   <si>
     <t xml:space="preserve">1.11459398269653</t>
@@ -2519,16 +2519,16 @@
     <t xml:space="preserve">1.16745448112488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16594409942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08740878105164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06701993942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0942051410675</t>
+    <t xml:space="preserve">1.16594421863556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08740890026093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0670200586319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09420502185822</t>
   </si>
   <si>
     <t xml:space="preserve">1.06324434280396</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">1.07834708690643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08212292194366</t>
+    <t xml:space="preserve">1.08212280273438</t>
   </si>
   <si>
     <t xml:space="preserve">1.07457137107849</t>
@@ -2549,13 +2549,13 @@
     <t xml:space="preserve">1.08665370941162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0926947593689</t>
+    <t xml:space="preserve">1.09269499778748</t>
   </si>
   <si>
     <t xml:space="preserve">1.03756952285767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07306110858917</t>
+    <t xml:space="preserve">1.07306122779846</t>
   </si>
   <si>
     <t xml:space="preserve">1.04965174198151</t>
@@ -2567,28 +2567,28 @@
     <t xml:space="preserve">1.04436588287354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04285562038422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01189470291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985464155673981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970361232757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989239871501923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943176209926605</t>
+    <t xml:space="preserve">1.04285550117493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01189482212067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985464036464691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970361411571503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989239811897278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94317615032196</t>
   </si>
   <si>
     <t xml:space="preserve">0.926563084125519</t>
   </si>
   <si>
-    <t xml:space="preserve">0.921277046203613</t>
+    <t xml:space="preserve">0.921277105808258</t>
   </si>
   <si>
     <t xml:space="preserve">0.913725674152374</t>
@@ -2612,25 +2612,25 @@
     <t xml:space="preserve">1.13422763347626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18180215358734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21502828598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23919296264648</t>
+    <t xml:space="preserve">1.18180227279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21502840518951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23919284343719</t>
   </si>
   <si>
     <t xml:space="preserve">1.19992554187775</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18935346603394</t>
+    <t xml:space="preserve">1.18935358524323</t>
   </si>
   <si>
     <t xml:space="preserve">1.14782083034515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16820979118347</t>
+    <t xml:space="preserve">1.16820967197418</t>
   </si>
   <si>
     <t xml:space="preserve">1.18708825111389</t>
@@ -2639,22 +2639,22 @@
     <t xml:space="preserve">1.16216862201691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19312942028046</t>
+    <t xml:space="preserve">1.19312930107117</t>
   </si>
   <si>
     <t xml:space="preserve">1.17047512531281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24598908424377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29280865192413</t>
+    <t xml:space="preserve">1.24598920345306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29280877113342</t>
   </si>
   <si>
     <t xml:space="preserve">1.36303675174713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40381503105164</t>
+    <t xml:space="preserve">1.40381515026093</t>
   </si>
   <si>
     <t xml:space="preserve">1.41136646270752</t>
@@ -2672,25 +2672,25 @@
     <t xml:space="preserve">1.40305995941162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41589725017548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49292171001434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44836854934692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48763561248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47630858421326</t>
+    <t xml:space="preserve">1.41589736938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49292182922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44836831092834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48763573169708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47630870342255</t>
   </si>
   <si>
     <t xml:space="preserve">1.46498155593872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39626383781433</t>
+    <t xml:space="preserve">1.39626371860504</t>
   </si>
   <si>
     <t xml:space="preserve">1.37662935256958</t>
@@ -2702,16 +2702,16 @@
     <t xml:space="preserve">1.3690779209137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43175530433655</t>
+    <t xml:space="preserve">1.43175542354584</t>
   </si>
   <si>
     <t xml:space="preserve">1.445347905159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47479844093323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48461520671844</t>
+    <t xml:space="preserve">1.47479832172394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48461508750916</t>
   </si>
   <si>
     <t xml:space="preserve">1.55106842517853</t>
@@ -2726,7 +2726,7 @@
     <t xml:space="preserve">1.3781396150589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34415829181671</t>
+    <t xml:space="preserve">1.34415817260742</t>
   </si>
   <si>
     <t xml:space="preserve">1.37209856510162</t>
@@ -2741,28 +2741,28 @@
     <t xml:space="preserve">1.38795721530914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3924880027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32150411605835</t>
+    <t xml:space="preserve">1.39248812198639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32150399684906</t>
   </si>
   <si>
     <t xml:space="preserve">1.31848347187042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34340310096741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30036020278931</t>
+    <t xml:space="preserve">1.34340298175812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30036008358002</t>
   </si>
   <si>
     <t xml:space="preserve">1.32376945018768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3343414068222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39777410030365</t>
+    <t xml:space="preserve">1.33434152603149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39777398109436</t>
   </si>
   <si>
     <t xml:space="preserve">1.36983299255371</t>
@@ -2774,13 +2774,13 @@
     <t xml:space="preserve">1.34038257598877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35473012924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31772840023041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33207607269287</t>
+    <t xml:space="preserve">1.35473024845123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31772828102112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33207595348358</t>
   </si>
   <si>
     <t xml:space="preserve">1.33585166931152</t>
@@ -2804,7 +2804,7 @@
     <t xml:space="preserve">1.10779762268066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13800406455994</t>
+    <t xml:space="preserve">1.13800394535065</t>
   </si>
   <si>
     <t xml:space="preserve">1.22711062431335</t>
@@ -2813,10 +2813,10 @@
     <t xml:space="preserve">1.24221348762512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23843765258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22862088680267</t>
+    <t xml:space="preserve">1.23843777179718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22862076759338</t>
   </si>
   <si>
     <t xml:space="preserve">1.44232726097107</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">1.43251049518585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50273847579956</t>
+    <t xml:space="preserve">1.50273859500885</t>
   </si>
   <si>
     <t xml:space="preserve">1.55408883094788</t>
@@ -2837,13 +2837,13 @@
     <t xml:space="preserve">1.78214299678802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77459156513214</t>
+    <t xml:space="preserve">1.77459168434143</t>
   </si>
   <si>
     <t xml:space="preserve">1.75797760486603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69303572177887</t>
+    <t xml:space="preserve">1.69303560256958</t>
   </si>
   <si>
     <t xml:space="preserve">1.7217310667038</t>
@@ -2852,19 +2852,19 @@
     <t xml:space="preserve">1.6854841709137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70209717750549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70360743999481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73079264163971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72777223587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69907653331757</t>
+    <t xml:space="preserve">1.70209729671478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7036075592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73079252243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72777211666107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69907665252686</t>
   </si>
   <si>
     <t xml:space="preserve">1.66887104511261</t>
@@ -2879,28 +2879,28 @@
     <t xml:space="preserve">1.66131961345673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6764223575592</t>
+    <t xml:space="preserve">1.67642223834991</t>
   </si>
   <si>
     <t xml:space="preserve">1.64470648765564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61601042747498</t>
+    <t xml:space="preserve">1.61601054668427</t>
   </si>
   <si>
     <t xml:space="preserve">1.63564419746399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65829920768738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66585063934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66434013843536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74438536167145</t>
+    <t xml:space="preserve">1.65829908847809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66585052013397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66434001922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74438524246216</t>
   </si>
   <si>
     <t xml:space="preserve">1.77761220932007</t>
@@ -2909,7 +2909,7 @@
     <t xml:space="preserve">1.756467461586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72022044658661</t>
+    <t xml:space="preserve">1.72022068500519</t>
   </si>
   <si>
     <t xml:space="preserve">1.73683369159698</t>
@@ -2918,19 +2918,19 @@
     <t xml:space="preserve">1.69454598426819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65225827693939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67491221427917</t>
+    <t xml:space="preserve">1.6522581577301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67491209506989</t>
   </si>
   <si>
     <t xml:space="preserve">1.65376830101013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63715434074402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57070207595825</t>
+    <t xml:space="preserve">1.63715445995331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57070195674896</t>
   </si>
   <si>
     <t xml:space="preserve">1.59486639499664</t>
@@ -2942,46 +2942,46 @@
     <t xml:space="preserve">1.7474057674408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88635241985321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85765719413757</t>
+    <t xml:space="preserve">1.88635230064392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85765707492828</t>
   </si>
   <si>
     <t xml:space="preserve">1.88031125068665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86822891235352</t>
+    <t xml:space="preserve">1.86822915077209</t>
   </si>
   <si>
     <t xml:space="preserve">1.85463654994965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88937306404114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85010552406311</t>
+    <t xml:space="preserve">1.88937282562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8501056432724</t>
   </si>
   <si>
     <t xml:space="preserve">1.80932807922363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83047199249268</t>
+    <t xml:space="preserve">1.83047211170197</t>
   </si>
   <si>
     <t xml:space="preserve">1.82141005992889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81838965415955</t>
+    <t xml:space="preserve">1.81838989257812</t>
   </si>
   <si>
     <t xml:space="preserve">1.82594120502472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80781781673431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80177652835846</t>
+    <t xml:space="preserve">1.80781745910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80177640914917</t>
   </si>
   <si>
     <t xml:space="preserve">1.84557473659515</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">1.82745134830475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87124955654144</t>
+    <t xml:space="preserve">1.87124967575073</t>
   </si>
   <si>
     <t xml:space="preserve">1.86369800567627</t>
@@ -3008,25 +3008,25 @@
     <t xml:space="preserve">2.05399513244629</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13706064224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18085932731628</t>
+    <t xml:space="preserve">2.13706040382385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18085956573486</t>
   </si>
   <si>
     <t xml:space="preserve">2.15216398239136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12950921058655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10685515403748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15518450737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13555026054382</t>
+    <t xml:space="preserve">2.12950897216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1068549156189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15518474578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1355504989624</t>
   </si>
   <si>
     <t xml:space="preserve">2.13857102394104</t>
@@ -3044,28 +3044,28 @@
     <t xml:space="preserve">2.18690061569214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16877746582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17028737068176</t>
+    <t xml:space="preserve">2.16877722740173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17028760910034</t>
   </si>
   <si>
     <t xml:space="preserve">2.23522973060608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24731206893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2699670791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30168294906616</t>
+    <t xml:space="preserve">2.24731183052063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26996684074402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30168318748474</t>
   </si>
   <si>
     <t xml:space="preserve">2.23673987388611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24580192565918</t>
+    <t xml:space="preserve">2.24580144882202</t>
   </si>
   <si>
     <t xml:space="preserve">2.24882221221924</t>
@@ -3083,7 +3083,7 @@
     <t xml:space="preserve">2.54937052726746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6430082321167</t>
+    <t xml:space="preserve">2.64300799369812</t>
   </si>
   <si>
     <t xml:space="preserve">2.61733317375183</t>
@@ -3101,16 +3101,16 @@
     <t xml:space="preserve">2.78648638725281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88616490364075</t>
+    <t xml:space="preserve">2.88616514205933</t>
   </si>
   <si>
     <t xml:space="preserve">2.8650209903717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86200070381165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94204616546631</t>
+    <t xml:space="preserve">2.86200046539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94204592704773</t>
   </si>
   <si>
     <t xml:space="preserve">2.94506669044495</t>
@@ -3119,28 +3119,28 @@
     <t xml:space="preserve">2.93147397041321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97980332374573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96621036529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95714902877808</t>
+    <t xml:space="preserve">2.97980308532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96621060371399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9571487903595</t>
   </si>
   <si>
     <t xml:space="preserve">2.97829270362854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08411312103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07337713241577</t>
+    <t xml:space="preserve">3.08411288261414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07337737083435</t>
   </si>
   <si>
     <t xml:space="preserve">3.05804061889648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15312528610229</t>
+    <t xml:space="preserve">3.15312552452087</t>
   </si>
   <si>
     <t xml:space="preserve">3.0917809009552</t>
@@ -3167,19 +3167,19 @@
     <t xml:space="preserve">3.06264138221741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98749470710754</t>
+    <t xml:space="preserve">2.98749446868896</t>
   </si>
   <si>
     <t xml:space="preserve">2.96602392196655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95988941192627</t>
+    <t xml:space="preserve">2.95988917350769</t>
   </si>
   <si>
     <t xml:space="preserve">2.9445526599884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91388034820557</t>
+    <t xml:space="preserve">2.91388010978699</t>
   </si>
   <si>
     <t xml:space="preserve">2.901611328125</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">2.80192589759827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80039238929749</t>
+    <t xml:space="preserve">2.80039215087891</t>
   </si>
   <si>
     <t xml:space="preserve">2.73598051071167</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">2.83719944953918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76665258407593</t>
+    <t xml:space="preserve">2.76665282249451</t>
   </si>
   <si>
     <t xml:space="preserve">2.80499315261841</t>
@@ -3215,7 +3215,7 @@
     <t xml:space="preserve">2.79119038581848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85713648796082</t>
+    <t xml:space="preserve">2.85713672637939</t>
   </si>
   <si>
     <t xml:space="preserve">2.78198909759521</t>
@@ -3230,7 +3230,7 @@
     <t xml:space="preserve">2.84333419799805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79579138755798</t>
+    <t xml:space="preserve">2.79579162597656</t>
   </si>
   <si>
     <t xml:space="preserve">2.77892160415649</t>
@@ -3245,7 +3245,7 @@
     <t xml:space="preserve">2.58108496665955</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66543364524841</t>
+    <t xml:space="preserve">2.66543340682983</t>
   </si>
   <si>
     <t xml:space="preserve">2.73291325569153</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">2.94301891326904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90774583816528</t>
+    <t xml:space="preserve">2.90774607658386</t>
   </si>
   <si>
     <t xml:space="preserve">2.85100221633911</t>
@@ -3278,22 +3278,22 @@
     <t xml:space="preserve">2.85867047309875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83873343467712</t>
+    <t xml:space="preserve">2.83873319625854</t>
   </si>
   <si>
     <t xml:space="preserve">2.84486770629883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91848111152649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95222163200378</t>
+    <t xml:space="preserve">2.91848134994507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95222139358521</t>
   </si>
   <si>
     <t xml:space="preserve">2.90467858314514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96755766868591</t>
+    <t xml:space="preserve">2.96755743026733</t>
   </si>
   <si>
     <t xml:space="preserve">2.92768287658691</t>
@@ -3302,10 +3302,10 @@
     <t xml:space="preserve">2.92461562156677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83566641807556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8617377281189</t>
+    <t xml:space="preserve">2.83566617965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86173748970032</t>
   </si>
   <si>
     <t xml:space="preserve">2.84640121459961</t>
@@ -3314,22 +3314,22 @@
     <t xml:space="preserve">2.87860727310181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89854431152344</t>
+    <t xml:space="preserve">2.89854407310486</t>
   </si>
   <si>
     <t xml:space="preserve">2.99976348876953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00743126869202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98289346694946</t>
+    <t xml:space="preserve">3.0074315071106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98289370536804</t>
   </si>
   <si>
     <t xml:space="preserve">2.98596096038818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95375490188599</t>
+    <t xml:space="preserve">2.95375514030457</t>
   </si>
   <si>
     <t xml:space="preserve">2.99056172370911</t>
@@ -3338,22 +3338,22 @@
     <t xml:space="preserve">2.93688440322876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95682191848755</t>
+    <t xml:space="preserve">2.95682215690613</t>
   </si>
   <si>
     <t xml:space="preserve">2.9000780582428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84180045127869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87400650978088</t>
+    <t xml:space="preserve">2.84180068969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8740062713623</t>
   </si>
   <si>
     <t xml:space="preserve">2.81726264953613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76511931419373</t>
+    <t xml:space="preserve">2.76511907577515</t>
   </si>
   <si>
     <t xml:space="preserve">2.8295316696167</t>
@@ -3380,22 +3380,22 @@
     <t xml:space="preserve">2.78045535087585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82646465301514</t>
+    <t xml:space="preserve">2.82646441459656</t>
   </si>
   <si>
     <t xml:space="preserve">2.84793496131897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.823397397995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93075013160706</t>
+    <t xml:space="preserve">2.82339715957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93075037002563</t>
   </si>
   <si>
     <t xml:space="preserve">2.90314531326294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88320803642273</t>
+    <t xml:space="preserve">2.88320827484131</t>
   </si>
   <si>
     <t xml:space="preserve">2.86633825302124</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">2.87554001808167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90621256828308</t>
+    <t xml:space="preserve">2.9062123298645</t>
   </si>
   <si>
     <t xml:space="preserve">2.95528864860535</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">2.95068788528442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99669623374939</t>
+    <t xml:space="preserve">2.99669599533081</t>
   </si>
   <si>
     <t xml:space="preserve">3.02890229225159</t>
@@ -3434,10 +3434,10 @@
     <t xml:space="preserve">2.93535089492798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88014078140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91234683990479</t>
+    <t xml:space="preserve">2.88014101982117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91234660148621</t>
   </si>
   <si>
     <t xml:space="preserve">2.98136019706726</t>
@@ -3455,13 +3455,13 @@
     <t xml:space="preserve">2.80806040763855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76205205917358</t>
+    <t xml:space="preserve">2.762051820755</t>
   </si>
   <si>
     <t xml:space="preserve">2.77432084083557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69917392730713</t>
+    <t xml:space="preserve">2.69917368888855</t>
   </si>
   <si>
     <t xml:space="preserve">2.70684194564819</t>
@@ -3470,22 +3470,22 @@
     <t xml:space="preserve">2.66083264350891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76051831245422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71144270896912</t>
+    <t xml:space="preserve">2.7605185508728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71144247055054</t>
   </si>
   <si>
     <t xml:space="preserve">2.58875298500061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73137950897217</t>
+    <t xml:space="preserve">2.73137974739075</t>
   </si>
   <si>
     <t xml:space="preserve">2.62249255180359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65009737014771</t>
+    <t xml:space="preserve">2.65009760856628</t>
   </si>
   <si>
     <t xml:space="preserve">2.6777024269104</t>
@@ -3503,10 +3503,10 @@
     <t xml:space="preserve">2.71911072731018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69610643386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66850090026855</t>
+    <t xml:space="preserve">2.69610667228699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66850066184998</t>
   </si>
   <si>
     <t xml:space="preserve">2.75438404083252</t>
@@ -3524,16 +3524,16 @@
     <t xml:space="preserve">2.9782931804657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86327123641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94148540496826</t>
+    <t xml:space="preserve">2.8632709980011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94148516654968</t>
   </si>
   <si>
     <t xml:space="preserve">3.03503656387329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02736830711365</t>
+    <t xml:space="preserve">3.02736854553223</t>
   </si>
   <si>
     <t xml:space="preserve">2.89087605476379</t>
@@ -3566,7 +3566,7 @@
     <t xml:space="preserve">3.07029485702515</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15472841262817</t>
+    <t xml:space="preserve">3.15472817420959</t>
   </si>
   <si>
     <t xml:space="preserve">3.08871698379517</t>
@@ -3575,7 +3575,7 @@
     <t xml:space="preserve">3.19771218299866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21459913253784</t>
+    <t xml:space="preserve">3.21459889411926</t>
   </si>
   <si>
     <t xml:space="preserve">3.18850111961365</t>
@@ -3587,7 +3587,7 @@
     <t xml:space="preserve">3.16547417640686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09485769271851</t>
+    <t xml:space="preserve">3.09485745429993</t>
   </si>
   <si>
     <t xml:space="preserve">2.94748306274414</t>
@@ -3599,7 +3599,7 @@
     <t xml:space="preserve">2.8476984500885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72028136253357</t>
+    <t xml:space="preserve">2.72028112411499</t>
   </si>
   <si>
     <t xml:space="preserve">2.55602049827576</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">2.58979392051697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54066896438599</t>
+    <t xml:space="preserve">2.54066920280457</t>
   </si>
   <si>
     <t xml:space="preserve">2.25359654426575</t>
@@ -3626,7 +3626,7 @@
     <t xml:space="preserve">2.40557622909546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42860341072083</t>
+    <t xml:space="preserve">2.42860317230225</t>
   </si>
   <si>
     <t xml:space="preserve">2.52992296218872</t>
@@ -3638,13 +3638,13 @@
     <t xml:space="preserve">2.75098443031311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72488689422607</t>
+    <t xml:space="preserve">2.7248866558075</t>
   </si>
   <si>
     <t xml:space="preserve">2.76326560974121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78015208244324</t>
+    <t xml:space="preserve">2.78015184402466</t>
   </si>
   <si>
     <t xml:space="preserve">2.82927680015564</t>
@@ -3656,10 +3656,10 @@
     <t xml:space="preserve">2.79243326187134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73870325088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79703879356384</t>
+    <t xml:space="preserve">2.73870348930359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79703903198242</t>
   </si>
   <si>
     <t xml:space="preserve">2.92292094230652</t>
@@ -3671,34 +3671,34 @@
     <t xml:space="preserve">2.85383915901184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8922176361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91831564903259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89835858345032</t>
+    <t xml:space="preserve">2.89221787452698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91831541061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89835834503174</t>
   </si>
   <si>
     <t xml:space="preserve">2.80931997299194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79857397079468</t>
+    <t xml:space="preserve">2.7985737323761</t>
   </si>
   <si>
     <t xml:space="preserve">2.93366670608521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94594788551331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87226104736328</t>
+    <t xml:space="preserve">2.94594812393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87226128578186</t>
   </si>
   <si>
     <t xml:space="preserve">2.93980741500854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88607716560364</t>
+    <t xml:space="preserve">2.88607740402222</t>
   </si>
   <si>
     <t xml:space="preserve">2.96590495109558</t>
@@ -3707,7 +3707,7 @@
     <t xml:space="preserve">2.95208835601807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90603399276733</t>
+    <t xml:space="preserve">2.90603423118591</t>
   </si>
   <si>
     <t xml:space="preserve">2.92752623558044</t>
@@ -3731,10 +3731,10 @@
     <t xml:space="preserve">2.75712490081787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68343806266785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78168749809265</t>
+    <t xml:space="preserve">2.68343782424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78168725967407</t>
   </si>
   <si>
     <t xml:space="preserve">2.80624961853027</t>
@@ -3743,7 +3743,7 @@
     <t xml:space="preserve">2.82467126846313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81853079795837</t>
+    <t xml:space="preserve">2.81853055953979</t>
   </si>
   <si>
     <t xml:space="preserve">2.88147187232971</t>
@@ -3755,10 +3755,10 @@
     <t xml:space="preserve">2.85230422019958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81239008903503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05270981788635</t>
+    <t xml:space="preserve">2.81239032745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05271005630493</t>
   </si>
   <si>
     <t xml:space="preserve">3.07706665992737</t>
@@ -3776,16 +3776,16 @@
     <t xml:space="preserve">3.07544279098511</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04946255683899</t>
+    <t xml:space="preserve">3.04946231842041</t>
   </si>
   <si>
     <t xml:space="preserve">3.01211524009705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99587750434875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03809595108032</t>
+    <t xml:space="preserve">2.99587774276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0380961894989</t>
   </si>
   <si>
     <t xml:space="preserve">3.03322458267212</t>
@@ -3809,7 +3809,7 @@
     <t xml:space="preserve">2.74256753921509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66137862205505</t>
+    <t xml:space="preserve">2.66137886047363</t>
   </si>
   <si>
     <t xml:space="preserve">2.70197296142578</t>
@@ -3824,13 +3824,13 @@
     <t xml:space="preserve">2.77666735649109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6954779624939</t>
+    <t xml:space="preserve">2.69547772407532</t>
   </si>
   <si>
     <t xml:space="preserve">2.73282480239868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69385433197021</t>
+    <t xml:space="preserve">2.69385409355164</t>
   </si>
   <si>
     <t xml:space="preserve">2.70034909248352</t>
@@ -3854,10 +3854,10 @@
     <t xml:space="preserve">2.60129857063293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67274522781372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76042914390564</t>
+    <t xml:space="preserve">2.67274498939514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76042938232422</t>
   </si>
   <si>
     <t xml:space="preserve">2.71821093559265</t>
@@ -3872,7 +3872,7 @@
     <t xml:space="preserve">2.51361417770386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52822875976562</t>
+    <t xml:space="preserve">2.52822852134705</t>
   </si>
   <si>
     <t xml:space="preserve">2.57207036018372</t>
@@ -3881,7 +3881,7 @@
     <t xml:space="preserve">2.69060635566711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61428880691528</t>
+    <t xml:space="preserve">2.61428904533386</t>
   </si>
   <si>
     <t xml:space="preserve">2.57856559753418</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">2.54608988761902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58343696594238</t>
+    <t xml:space="preserve">2.58343720436096</t>
   </si>
   <si>
     <t xml:space="preserve">2.51686191558838</t>
@@ -3905,19 +3905,19 @@
     <t xml:space="preserve">2.65975475311279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72957730293274</t>
+    <t xml:space="preserve">2.72957754135132</t>
   </si>
   <si>
     <t xml:space="preserve">2.6694974899292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78153848648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7360725402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71496367454529</t>
+    <t xml:space="preserve">2.78153872489929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73607230186462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71496343612671</t>
   </si>
   <si>
     <t xml:space="preserve">2.71171569824219</t>
@@ -3929,19 +3929,19 @@
     <t xml:space="preserve">2.61753630638123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66624975204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60941743850708</t>
+    <t xml:space="preserve">2.66624999046326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60941767692566</t>
   </si>
   <si>
     <t xml:space="preserve">2.56395149230957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56232762336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59155607223511</t>
+    <t xml:space="preserve">2.56232786178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59155583381653</t>
   </si>
   <si>
     <t xml:space="preserve">2.59967470169067</t>
@@ -3956,22 +3956,22 @@
     <t xml:space="preserve">2.59805107116699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58830833435059</t>
+    <t xml:space="preserve">2.58830857276917</t>
   </si>
   <si>
     <t xml:space="preserve">2.7263298034668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82050919532776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81726169586182</t>
+    <t xml:space="preserve">2.82050895690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81726145744324</t>
   </si>
   <si>
     <t xml:space="preserve">2.84811329841614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92767858505249</t>
+    <t xml:space="preserve">2.92767882347107</t>
   </si>
   <si>
     <t xml:space="preserve">2.90819334983826</t>
@@ -3980,7 +3980,7 @@
     <t xml:space="preserve">2.88870787620544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83999466896057</t>
+    <t xml:space="preserve">2.83999443054199</t>
   </si>
   <si>
     <t xml:space="preserve">2.78965735435486</t>
@@ -3998,13 +3998,13 @@
     <t xml:space="preserve">2.64514064788818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75393414497375</t>
+    <t xml:space="preserve">2.75393390655518</t>
   </si>
   <si>
     <t xml:space="preserve">2.7669243812561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8546085357666</t>
+    <t xml:space="preserve">2.85460877418518</t>
   </si>
   <si>
     <t xml:space="preserve">2.7929048538208</t>
@@ -4031,16 +4031,16 @@
     <t xml:space="preserve">2.86435127258301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87734150886536</t>
+    <t xml:space="preserve">2.87734127044678</t>
   </si>
   <si>
     <t xml:space="preserve">2.9163122177124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95853066444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92443132400513</t>
+    <t xml:space="preserve">2.95853090286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92443108558655</t>
   </si>
   <si>
     <t xml:space="preserve">2.93904519081116</t>
@@ -4058,7 +4058,7 @@
     <t xml:space="preserve">3.02997708320618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04459118843079</t>
+    <t xml:space="preserve">3.04459095001221</t>
   </si>
   <si>
     <t xml:space="preserve">3.10467100143433</t>
@@ -4067,7 +4067,7 @@
     <t xml:space="preserve">2.87409377098083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8497371673584</t>
+    <t xml:space="preserve">2.84973740577698</t>
   </si>
   <si>
     <t xml:space="preserve">2.89520311355591</t>
@@ -4079,7 +4079,7 @@
     <t xml:space="preserve">2.91793608665466</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04621505737305</t>
+    <t xml:space="preserve">3.04621481895447</t>
   </si>
   <si>
     <t xml:space="preserve">3.05108594894409</t>
@@ -4088,7 +4088,7 @@
     <t xml:space="preserve">3.1014232635498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10629487037659</t>
+    <t xml:space="preserve">3.10629463195801</t>
   </si>
   <si>
     <t xml:space="preserve">3.11441349983215</t>
@@ -4097,16 +4097,16 @@
     <t xml:space="preserve">3.15987944602966</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12740397453308</t>
+    <t xml:space="preserve">3.1274037361145</t>
   </si>
   <si>
     <t xml:space="preserve">3.16637468338013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14201784133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12090873718262</t>
+    <t xml:space="preserve">3.14201807975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1209089756012</t>
   </si>
   <si>
     <t xml:space="preserve">3.08031415939331</t>
@@ -4136,7 +4136,7 @@
     <t xml:space="preserve">3.17449355125427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18261241912842</t>
+    <t xml:space="preserve">3.182612657547</t>
   </si>
   <si>
     <t xml:space="preserve">3.17611718177795</t>
@@ -4148,7 +4148,7 @@
     <t xml:space="preserve">3.12415623664856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17774105072021</t>
+    <t xml:space="preserve">3.17774128913879</t>
   </si>
   <si>
     <t xml:space="preserve">3.21508836746216</t>
@@ -4163,16 +4163,16 @@
     <t xml:space="preserve">3.27679181098938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2702968120575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31251502037048</t>
+    <t xml:space="preserve">3.27029657363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3125147819519</t>
   </si>
   <si>
     <t xml:space="preserve">3.3417432308197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29465365409851</t>
+    <t xml:space="preserve">3.29465341567993</t>
   </si>
   <si>
     <t xml:space="preserve">3.32388138771057</t>
@@ -4187,7 +4187,7 @@
     <t xml:space="preserve">3.43917012214661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46190309524536</t>
+    <t xml:space="preserve">3.46190285682678</t>
   </si>
   <si>
     <t xml:space="preserve">3.48301196098328</t>
@@ -4196,25 +4196,25 @@
     <t xml:space="preserve">3.51386404037476</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53822064399719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52035903930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65838050842285</t>
+    <t xml:space="preserve">3.53822040557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52035927772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65838074684143</t>
   </si>
   <si>
     <t xml:space="preserve">3.73307466506958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65675687789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66487574577332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70222282409668</t>
+    <t xml:space="preserve">3.65675711631775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66487598419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7022225856781</t>
   </si>
   <si>
     <t xml:space="preserve">3.68436098098755</t>
@@ -4226,34 +4226,34 @@
     <t xml:space="preserve">3.62428140640259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66325211524963</t>
+    <t xml:space="preserve">3.66325187683105</t>
   </si>
   <si>
     <t xml:space="preserve">3.59505319595337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60804295539856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64539003372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59830093383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64376640319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61616206169128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68598461151123</t>
+    <t xml:space="preserve">3.60804319381714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6453902721405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59830069541931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6437668800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61616230010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68598484992981</t>
   </si>
   <si>
     <t xml:space="preserve">3.69572734832764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81101536750793</t>
+    <t xml:space="preserve">3.81101584434509</t>
   </si>
   <si>
     <t xml:space="preserve">3.90032410621643</t>
@@ -4271,7 +4271,7 @@
     <t xml:space="preserve">3.97177076339722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89220499992371</t>
+    <t xml:space="preserve">3.89220547676086</t>
   </si>
   <si>
     <t xml:space="preserve">3.91980957984924</t>
@@ -4283,16 +4283,16 @@
     <t xml:space="preserve">3.41806101799011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41643738746643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19885015487671</t>
+    <t xml:space="preserve">3.41643714904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19885039329529</t>
   </si>
   <si>
     <t xml:space="preserve">3.21021699905396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09492826461792</t>
+    <t xml:space="preserve">3.0949285030365</t>
   </si>
   <si>
     <t xml:space="preserve">3.37259483337402</t>
@@ -4301,7 +4301,7 @@
     <t xml:space="preserve">3.28491067886353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21995949745178</t>
+    <t xml:space="preserve">3.21995973587036</t>
   </si>
   <si>
     <t xml:space="preserve">3.08843326568604</t>
@@ -4310,13 +4310,13 @@
     <t xml:space="preserve">3.09330439567566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09979963302612</t>
+    <t xml:space="preserve">3.0997998714447</t>
   </si>
   <si>
     <t xml:space="preserve">3.19560265541077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21184086799622</t>
+    <t xml:space="preserve">3.21184062957764</t>
   </si>
   <si>
     <t xml:space="preserve">3.1517608165741</t>
@@ -4325,10 +4325,10 @@
     <t xml:space="preserve">3.27192091941833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28815841674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31738638877869</t>
+    <t xml:space="preserve">3.28815865516663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31738615036011</t>
   </si>
   <si>
     <t xml:space="preserve">3.36122846603394</t>
@@ -4337,7 +4337,7 @@
     <t xml:space="preserve">3.34823822975159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44891262054443</t>
+    <t xml:space="preserve">3.44891285896301</t>
   </si>
   <si>
     <t xml:space="preserve">3.4342987537384</t>
@@ -4346,10 +4346,10 @@
     <t xml:space="preserve">3.47326922416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47002196311951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44241738319397</t>
+    <t xml:space="preserve">3.47002220153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44241714477539</t>
   </si>
   <si>
     <t xml:space="preserve">3.34661459922791</t>
@@ -4367,7 +4367,7 @@
     <t xml:space="preserve">3.4310507774353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50736904144287</t>
+    <t xml:space="preserve">3.50736880302429</t>
   </si>
   <si>
     <t xml:space="preserve">3.36934733390808</t>
@@ -4391,19 +4391,19 @@
     <t xml:space="preserve">3.18703985214233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19400238990784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20096492767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18355870246887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13134098052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04605150222778</t>
+    <t xml:space="preserve">3.19400262832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20096468925476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18355894088745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13134074211121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0460512638092</t>
   </si>
   <si>
     <t xml:space="preserve">3.13308143615723</t>
@@ -4412,22 +4412,22 @@
     <t xml:space="preserve">3.22533321380615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19748377799988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21140837669373</t>
+    <t xml:space="preserve">3.1974835395813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2114086151123</t>
   </si>
   <si>
     <t xml:space="preserve">3.23055481910706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24273943901062</t>
+    <t xml:space="preserve">3.24273920059204</t>
   </si>
   <si>
     <t xml:space="preserve">3.23229551315308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22011160850525</t>
+    <t xml:space="preserve">3.22011137008667</t>
   </si>
   <si>
     <t xml:space="preserve">3.29321646690369</t>
@@ -4436,25 +4436,25 @@
     <t xml:space="preserve">3.25840449333191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28625440597534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30017900466919</t>
+    <t xml:space="preserve">3.28625416755676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30017924308777</t>
   </si>
   <si>
     <t xml:space="preserve">3.34891581535339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38546848297119</t>
+    <t xml:space="preserve">3.38546872138977</t>
   </si>
   <si>
     <t xml:space="preserve">3.41505861282349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37676572799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38024687767029</t>
+    <t xml:space="preserve">3.37676548957825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38024663925171</t>
   </si>
   <si>
     <t xml:space="preserve">3.32106614112854</t>
@@ -4475,28 +4475,28 @@
     <t xml:space="preserve">3.33673167228699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30888223648071</t>
+    <t xml:space="preserve">3.30888199806213</t>
   </si>
   <si>
     <t xml:space="preserve">3.34369397163391</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40809607505798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42028069496155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4342052936554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50905132293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53167915344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55430698394775</t>
+    <t xml:space="preserve">3.40809631347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42028045654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43420553207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50905108451843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5316789150238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55430674552917</t>
   </si>
   <si>
     <t xml:space="preserve">3.63785552978516</t>
@@ -4511,7 +4511,7 @@
     <t xml:space="preserve">3.70922040939331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78406596183777</t>
+    <t xml:space="preserve">3.78406620025635</t>
   </si>
   <si>
     <t xml:space="preserve">3.82409977912903</t>
@@ -4523,31 +4523,31 @@
     <t xml:space="preserve">3.75099468231201</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72140431404114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7318480014801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73881030082703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52471661567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65352082252502</t>
+    <t xml:space="preserve">3.72140455245972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73184823989868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73881053924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52471685409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6535210609436</t>
   </si>
   <si>
     <t xml:space="preserve">3.68833303451538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74229168891907</t>
+    <t xml:space="preserve">3.74229192733765</t>
   </si>
   <si>
     <t xml:space="preserve">3.73358845710754</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6848521232605</t>
+    <t xml:space="preserve">3.68485188484192</t>
   </si>
   <si>
     <t xml:space="preserve">3.64655876159668</t>
@@ -4556,37 +4556,37 @@
     <t xml:space="preserve">3.68137073516846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69007349014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71270132064819</t>
+    <t xml:space="preserve">3.69007325172424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71270108222961</t>
   </si>
   <si>
     <t xml:space="preserve">3.72314476966858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80321264266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83802461624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8171374797821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76666021347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7684006690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86065268516541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90416789054871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90590786933899</t>
+    <t xml:space="preserve">3.8032124042511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83802437782288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81713771820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76665997505188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76840043067932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86065220832825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90416741371155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90590834617615</t>
   </si>
   <si>
     <t xml:space="preserve">4.00338172912598</t>
@@ -4601,7 +4601,7 @@
     <t xml:space="preserve">4.07648706436157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17744159698486</t>
+    <t xml:space="preserve">4.17744207382202</t>
   </si>
   <si>
     <t xml:space="preserve">4.34976148605347</t>
@@ -4631,7 +4631,7 @@
     <t xml:space="preserve">4.31668996810913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22095632553101</t>
+    <t xml:space="preserve">4.22095680236816</t>
   </si>
   <si>
     <t xml:space="preserve">4.19310712814331</t>
@@ -4640,7 +4640,7 @@
     <t xml:space="preserve">4.28884029388428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3732590675354</t>
+    <t xml:space="preserve">4.37325954437256</t>
   </si>
   <si>
     <t xml:space="preserve">4.3393177986145</t>
@@ -4712,10 +4712,10 @@
     <t xml:space="preserve">5.0607967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21309900283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1956934928894</t>
+    <t xml:space="preserve">5.21309947967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19569301605225</t>
   </si>
   <si>
     <t xml:space="preserve">5.13042068481445</t>
@@ -4724,7 +4724,7 @@
     <t xml:space="preserve">5.14347505569458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08690595626831</t>
+    <t xml:space="preserve">5.08690547943115</t>
   </si>
   <si>
     <t xml:space="preserve">5.04774236679077</t>
@@ -4829,13 +4829,13 @@
     <t xml:space="preserve">5.33494138717651</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55251693725586</t>
+    <t xml:space="preserve">5.5525164604187</t>
   </si>
   <si>
     <t xml:space="preserve">5.65695238113403</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7048192024231</t>
+    <t xml:space="preserve">5.70481872558594</t>
   </si>
   <si>
     <t xml:space="preserve">5.7091703414917</t>
@@ -4853,7 +4853,7 @@
     <t xml:space="preserve">6.13561773300171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80055236816406</t>
+    <t xml:space="preserve">5.8005518913269</t>
   </si>
   <si>
     <t xml:space="preserve">5.78749752044678</t>
@@ -4862,7 +4862,7 @@
     <t xml:space="preserve">5.87017583847046</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83971548080444</t>
+    <t xml:space="preserve">5.8397159576416</t>
   </si>
   <si>
     <t xml:space="preserve">5.71352195739746</t>
@@ -4871,10 +4871,10 @@
     <t xml:space="preserve">5.72222471237183</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84406757354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93109750747681</t>
+    <t xml:space="preserve">5.84406709671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93109703063965</t>
   </si>
   <si>
     <t xml:space="preserve">5.97896337509155</t>
@@ -4883,7 +4883,7 @@
     <t xml:space="preserve">5.94415140151978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89628505706787</t>
+    <t xml:space="preserve">5.89628553390503</t>
   </si>
   <si>
     <t xml:space="preserve">5.98766660690308</t>
@@ -4901,7 +4901,7 @@
     <t xml:space="preserve">6.24005365371704</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17913293838501</t>
+    <t xml:space="preserve">6.17913246154785</t>
   </si>
   <si>
     <t xml:space="preserve">6.01812744140625</t>
@@ -4910,10 +4910,10 @@
     <t xml:space="preserve">6.16172647476196</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23570251464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23135042190552</t>
+    <t xml:space="preserve">6.23570203781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23135089874268</t>
   </si>
   <si>
     <t xml:space="preserve">6.07904815673828</t>
@@ -4922,7 +4922,7 @@
     <t xml:space="preserve">6.00507259368896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86582469940186</t>
+    <t xml:space="preserve">5.8658242225647</t>
   </si>
   <si>
     <t xml:space="preserve">5.69176435470581</t>
@@ -4934,34 +4934,34 @@
     <t xml:space="preserve">5.91369104385376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93979978561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18783569335938</t>
+    <t xml:space="preserve">5.93980026245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18783617019653</t>
   </si>
   <si>
     <t xml:space="preserve">6.065993309021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0398850440979</t>
+    <t xml:space="preserve">6.03988456726074</t>
   </si>
   <si>
     <t xml:space="preserve">6.09645414352417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22264814376831</t>
+    <t xml:space="preserve">6.22264766693115</t>
   </si>
   <si>
     <t xml:space="preserve">5.93544864654541</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06164264678955</t>
+    <t xml:space="preserve">6.06164216995239</t>
   </si>
   <si>
     <t xml:space="preserve">5.82666110992432</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85276985168457</t>
+    <t xml:space="preserve">5.85277032852173</t>
   </si>
   <si>
     <t xml:space="preserve">5.92674541473389</t>
@@ -4970,28 +4970,28 @@
     <t xml:space="preserve">6.11821174621582</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37930154800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53595638275146</t>
+    <t xml:space="preserve">6.37930202484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53595590591431</t>
   </si>
   <si>
     <t xml:space="preserve">6.53160429000854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47068357467651</t>
+    <t xml:space="preserve">6.47068309783936</t>
   </si>
   <si>
     <t xml:space="preserve">6.66650104522705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82315492630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8405613899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90148162841797</t>
+    <t xml:space="preserve">6.82315540313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84056091308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90148210525513</t>
   </si>
   <si>
     <t xml:space="preserve">6.80574893951416</t>
@@ -5000,7 +5000,7 @@
     <t xml:space="preserve">6.95369958877563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07119035720825</t>
+    <t xml:space="preserve">7.07119083404541</t>
   </si>
   <si>
     <t xml:space="preserve">6.96240282058716</t>
@@ -5012,10 +5012,10 @@
     <t xml:space="preserve">6.99286365509033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12775945663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12340927124023</t>
+    <t xml:space="preserve">7.12775993347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12340879440308</t>
   </si>
   <si>
     <t xml:space="preserve">7.20173501968384</t>
@@ -5883,6 +5883,9 @@
   </si>
   <si>
     <t xml:space="preserve">13.2049999237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9650001525879</t>
   </si>
 </sst>
 </file>
@@ -70961,7 +70964,7 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.649525463</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>746823</v>
@@ -70982,6 +70985,32 @@
         <v>1956</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.6495486111</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>599034</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>13.1750001907349</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>12.7399997711182</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>12.835000038147</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>12.9650001525879</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>1957</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BPSO.MI.xlsx
+++ b/data/BPSO.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1958" uniqueCount="1958">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1959" uniqueCount="1959">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,73 +47,73 @@
     <t xml:space="preserve">2.80963730812073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74855804443359</t>
+    <t xml:space="preserve">2.74855828285217</t>
   </si>
   <si>
     <t xml:space="preserve">2.71246600151062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63611745834351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60835409164429</t>
+    <t xml:space="preserve">2.63611698150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60835361480713</t>
   </si>
   <si>
     <t xml:space="preserve">2.69303202629089</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69858455657959</t>
+    <t xml:space="preserve">2.69858431816101</t>
   </si>
   <si>
     <t xml:space="preserve">2.61113023757935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51257085800171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45565629005432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2668662071228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38069534301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40568232536316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3654260635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51951169967651</t>
+    <t xml:space="preserve">2.51257061958313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4556565284729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26686668395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38069558143616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40568208694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36542582511902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51951146125793</t>
   </si>
   <si>
     <t xml:space="preserve">2.44455099105835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.355708360672</t>
+    <t xml:space="preserve">2.35570859909058</t>
   </si>
   <si>
     <t xml:space="preserve">2.43899869918823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40429425239563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32100534439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22105765342712</t>
+    <t xml:space="preserve">2.40429401397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32100486755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22105717658997</t>
   </si>
   <si>
     <t xml:space="preserve">2.23216271400452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20995187759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04059600830078</t>
+    <t xml:space="preserve">2.20995211601257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0405957698822</t>
   </si>
   <si>
     <t xml:space="preserve">2.06280660629272</t>
@@ -125,28 +125,28 @@
     <t xml:space="preserve">2.07668805122375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18218803405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22522187232971</t>
+    <t xml:space="preserve">2.1821882724762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22522163391113</t>
   </si>
   <si>
     <t xml:space="preserve">2.27797174453735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19329333305359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16553044319153</t>
+    <t xml:space="preserve">2.19329380989075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16553068161011</t>
   </si>
   <si>
     <t xml:space="preserve">2.24604415893555</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18635272979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1766357421875</t>
+    <t xml:space="preserve">2.18635249137878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17663598060608</t>
   </si>
   <si>
     <t xml:space="preserve">2.21550464630127</t>
@@ -155,19 +155,19 @@
     <t xml:space="preserve">2.259925365448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31822896003723</t>
+    <t xml:space="preserve">2.31822848320007</t>
   </si>
   <si>
     <t xml:space="preserve">2.38763618469238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38208365440369</t>
+    <t xml:space="preserve">2.38208341598511</t>
   </si>
   <si>
     <t xml:space="preserve">2.37514281272888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2418794631958</t>
+    <t xml:space="preserve">2.24187970161438</t>
   </si>
   <si>
     <t xml:space="preserve">2.26270174980164</t>
@@ -176,13 +176,13 @@
     <t xml:space="preserve">2.25020837783813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31961703300476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4334454536438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35848522186279</t>
+    <t xml:space="preserve">2.31961679458618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43344497680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35848498344421</t>
   </si>
   <si>
     <t xml:space="preserve">2.30157017707825</t>
@@ -191,13 +191,13 @@
     <t xml:space="preserve">2.34599184989929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35987305641174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39318919181824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29324126243591</t>
+    <t xml:space="preserve">2.3598735332489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39318895339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29324102401733</t>
   </si>
   <si>
     <t xml:space="preserve">2.23771500587463</t>
@@ -206,16 +206,16 @@
     <t xml:space="preserve">2.18774104118347</t>
   </si>
   <si>
-    <t xml:space="preserve">2.139155626297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14748477935791</t>
+    <t xml:space="preserve">2.13915586471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14748430252075</t>
   </si>
   <si>
     <t xml:space="preserve">2.1211097240448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06974720954895</t>
+    <t xml:space="preserve">2.06974697113037</t>
   </si>
   <si>
     <t xml:space="preserve">2.01283288002014</t>
@@ -224,22 +224,22 @@
     <t xml:space="preserve">2.01838564872742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07113552093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11694502830505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12527418136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22799777984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3029580116272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23910307884216</t>
+    <t xml:space="preserve">2.07113575935364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11694526672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12527370452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22799801826477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30295825004578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23910331726074</t>
   </si>
   <si>
     <t xml:space="preserve">2.29046511650085</t>
@@ -248,61 +248,61 @@
     <t xml:space="preserve">2.3321099281311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32655763626099</t>
+    <t xml:space="preserve">2.32655739784241</t>
   </si>
   <si>
     <t xml:space="preserve">2.2793595790863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32378125190735</t>
+    <t xml:space="preserve">2.32378101348877</t>
   </si>
   <si>
     <t xml:space="preserve">2.30851101875305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26131415367126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23493885993958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15720152854919</t>
+    <t xml:space="preserve">2.26131391525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23493909835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15720129013062</t>
   </si>
   <si>
     <t xml:space="preserve">2.11139249801636</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08224081993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09889912605286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08918237686157</t>
+    <t xml:space="preserve">2.08224034309387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09889888763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08918213844299</t>
   </si>
   <si>
     <t xml:space="preserve">2.10583996772766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04892492294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03781962394714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0655825138092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03226733207703</t>
+    <t xml:space="preserve">2.04892516136169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03781986236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06558299064636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03226685523987</t>
   </si>
   <si>
     <t xml:space="preserve">2.07252359390259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05725336074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05156707763672</t>
+    <t xml:space="preserve">2.05725383758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05156683921814</t>
   </si>
   <si>
     <t xml:space="preserve">2.12691855430603</t>
@@ -311,22 +311,22 @@
     <t xml:space="preserve">2.19942760467529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15393233299255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17525792121887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15535402297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09279680252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07147145271301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99896216392517</t>
+    <t xml:space="preserve">2.15393209457397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17525815963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15535378456116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09279704093933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07147097587585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99896228313446</t>
   </si>
   <si>
     <t xml:space="preserve">1.95773220062256</t>
@@ -335,49 +335,49 @@
     <t xml:space="preserve">1.87669312953949</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98901045322418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93640625476837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94351506233215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84114956855774</t>
+    <t xml:space="preserve">1.98900997638702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93640637397766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94351530075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84114944934845</t>
   </si>
   <si>
     <t xml:space="preserve">1.78143715858459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75158023834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7259886264801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64210617542267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69613230228424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77006232738495</t>
+    <t xml:space="preserve">1.75157999992371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72598898410797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64210629463196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69613242149353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77006220817566</t>
   </si>
   <si>
     <t xml:space="preserve">1.81129336357117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78001439571381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89375364780426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63499748706818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56533265113831</t>
+    <t xml:space="preserve">1.78001415729523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89375376701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63499760627747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56533300876617</t>
   </si>
   <si>
     <t xml:space="preserve">1.66911971569061</t>
@@ -386,13 +386,13 @@
     <t xml:space="preserve">1.65632367134094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6392627954483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63641917705536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57670652866364</t>
+    <t xml:space="preserve">1.63926267623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63641941547394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5767068862915</t>
   </si>
   <si>
     <t xml:space="preserve">1.51130652427673</t>
@@ -401,148 +401,148 @@
     <t xml:space="preserve">1.52552378177643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53121078014374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63784086704254</t>
+    <t xml:space="preserve">1.53121066093445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63784098625183</t>
   </si>
   <si>
     <t xml:space="preserve">1.67196333408356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69471096992493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67054176330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74304962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70892798900604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72172355651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77574944496155</t>
+    <t xml:space="preserve">1.69471073150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67054164409637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74304950237274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70892810821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72172379493713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77574920654297</t>
   </si>
   <si>
     <t xml:space="preserve">1.76721882820129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72741079330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69755434989929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72456729412079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71888041496277</t>
+    <t xml:space="preserve">1.72741067409515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69755423069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7245671749115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71888017654419</t>
   </si>
   <si>
     <t xml:space="preserve">1.66343283653259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55395901203156</t>
+    <t xml:space="preserve">1.55395877361298</t>
   </si>
   <si>
     <t xml:space="preserve">1.57528507709503</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52125871181488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63357591629028</t>
+    <t xml:space="preserve">1.5212584733963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63357603549957</t>
   </si>
   <si>
     <t xml:space="preserve">1.65916705131531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6477929353714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68760240077972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71461510658264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70608472824097</t>
+    <t xml:space="preserve">1.64779329299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68760228157043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71461534500122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70608460903168</t>
   </si>
   <si>
     <t xml:space="preserve">1.70039796829224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74447166919708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70750641822815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72030210494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73167598247528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78285872936249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7785929441452</t>
+    <t xml:space="preserve">1.74447154998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70750629901886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72030222415924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7316757440567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78285884857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77859306335449</t>
   </si>
   <si>
     <t xml:space="preserve">1.771484375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7643758058548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75584506988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76295387744904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74162805080414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76864087581635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74873685836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73451924324036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78428030014038</t>
+    <t xml:space="preserve">1.76437556743622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75584530830383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76295399665833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74162769317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76864099502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74873650074005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73451936244965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78428041934967</t>
   </si>
   <si>
     <t xml:space="preserve">1.85252344608307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84968018531799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81271541118622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83546280860901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84825837612152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85963201522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94778025150299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9762145280838</t>
+    <t xml:space="preserve">1.8496800661087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81271529197693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83546245098114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84825825691223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85963189601898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9477801322937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97621464729309</t>
   </si>
   <si>
     <t xml:space="preserve">2.09848403930664</t>
@@ -560,13 +560,13 @@
     <t xml:space="preserve">2.08853197097778</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09706234931946</t>
+    <t xml:space="preserve">2.09706258773804</t>
   </si>
   <si>
     <t xml:space="preserve">2.16104054450989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18236660957336</t>
+    <t xml:space="preserve">2.18236684799194</t>
   </si>
   <si>
     <t xml:space="preserve">2.11412310600281</t>
@@ -575,64 +575,64 @@
     <t xml:space="preserve">2.00038409233093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03877139091492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00891447067261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05298852920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06294083595276</t>
+    <t xml:space="preserve">2.03877115249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00891423225403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0529887676239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06294059753418</t>
   </si>
   <si>
     <t xml:space="preserve">2.11554479598999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12549686431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16246271133423</t>
+    <t xml:space="preserve">2.12549662590027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16246247291565</t>
   </si>
   <si>
     <t xml:space="preserve">2.15961909294128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13260579109192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08142328262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03592777252197</t>
+    <t xml:space="preserve">2.13260531425476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08142304420471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03592801094055</t>
   </si>
   <si>
     <t xml:space="preserve">2.07715797424316</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09990572929382</t>
+    <t xml:space="preserve">2.09990549087524</t>
   </si>
   <si>
     <t xml:space="preserve">2.08995342254639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01033639907837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12407493591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10417103767395</t>
+    <t xml:space="preserve">2.01033592224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12407541275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10417127609253</t>
   </si>
   <si>
     <t xml:space="preserve">2.07289290428162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16814923286438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27478003501892</t>
+    <t xml:space="preserve">2.16814970970154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27477979660034</t>
   </si>
   <si>
     <t xml:space="preserve">2.37430167198181</t>
@@ -647,52 +647,52 @@
     <t xml:space="preserve">2.2719361782074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23212718963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17810153961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16957139968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23639249801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22217512130737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2179102897644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20511436462402</t>
+    <t xml:space="preserve">2.23212742805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17810201644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16957116127014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2363920211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22217535972595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21791005134583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2051146030426</t>
   </si>
   <si>
     <t xml:space="preserve">2.22359704971313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26482796669006</t>
+    <t xml:space="preserve">2.26482772827148</t>
   </si>
   <si>
     <t xml:space="preserve">2.31032299995422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31743168830872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34302282333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34160089492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30463576316833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29752731323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29610586166382</t>
+    <t xml:space="preserve">2.31743144989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34302306175232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34160113334656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30463600158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29752707481384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29610562324524</t>
   </si>
   <si>
     <t xml:space="preserve">2.36008381843567</t>
@@ -701,43 +701,43 @@
     <t xml:space="preserve">2.35297513008118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3401792049408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4027361869812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41695332527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45249676704407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4112663269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.415531873703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42406249046326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44396615028381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35439658164978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33733582496643</t>
+    <t xml:space="preserve">2.34017968177795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40273642539978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41695356369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45249652862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41126680374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41553163528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42406225204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44396638870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35439682006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33733606338501</t>
   </si>
   <si>
     <t xml:space="preserve">2.33022737503052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36434888839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32738375663757</t>
+    <t xml:space="preserve">2.3643491268158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32738399505615</t>
   </si>
   <si>
     <t xml:space="preserve">2.28188824653625</t>
@@ -746,16 +746,16 @@
     <t xml:space="preserve">2.30037093162537</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32311868667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33449244499207</t>
+    <t xml:space="preserve">2.32311844825745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33449268341064</t>
   </si>
   <si>
     <t xml:space="preserve">2.30890154838562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29894924163818</t>
+    <t xml:space="preserve">2.2989490032196</t>
   </si>
   <si>
     <t xml:space="preserve">2.25629734992981</t>
@@ -764,13 +764,13 @@
     <t xml:space="preserve">2.12834072113037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13402724266052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28473210334778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22928404808044</t>
+    <t xml:space="preserve">2.1340274810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28473162651062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22928380966187</t>
   </si>
   <si>
     <t xml:space="preserve">2.27335786819458</t>
@@ -779,10 +779,10 @@
     <t xml:space="preserve">2.27904486656189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31316661834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33875751495361</t>
+    <t xml:space="preserve">2.31316637992859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33875799179077</t>
   </si>
   <si>
     <t xml:space="preserve">2.37856674194336</t>
@@ -791,67 +791,67 @@
     <t xml:space="preserve">2.32880568504333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.367192029953</t>
+    <t xml:space="preserve">2.36719226837158</t>
   </si>
   <si>
     <t xml:space="preserve">2.34870982170105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29468393325806</t>
+    <t xml:space="preserve">2.29468417167664</t>
   </si>
   <si>
     <t xml:space="preserve">2.30321455001831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28757548332214</t>
+    <t xml:space="preserve">2.28757524490356</t>
   </si>
   <si>
     <t xml:space="preserve">2.32027530670166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2833104133606</t>
+    <t xml:space="preserve">2.28331065177917</t>
   </si>
   <si>
     <t xml:space="preserve">2.29041862487793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29326224327087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30605792999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35581851005554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31174492835999</t>
+    <t xml:space="preserve">2.29326248168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3060576915741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35581827163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31174445152283</t>
   </si>
   <si>
     <t xml:space="preserve">2.3316490650177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46671390533447</t>
+    <t xml:space="preserve">2.46671366691589</t>
   </si>
   <si>
     <t xml:space="preserve">2.43117094039917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42974877357483</t>
+    <t xml:space="preserve">2.42974901199341</t>
   </si>
   <si>
     <t xml:space="preserve">2.49799299240112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46387076377869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48661828041077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51647543907166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51789689064026</t>
+    <t xml:space="preserve">2.46387052536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48661851882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51647520065308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51789712905884</t>
   </si>
   <si>
     <t xml:space="preserve">2.56907916069031</t>
@@ -863,16 +863,16 @@
     <t xml:space="preserve">2.48803997039795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50510120391846</t>
+    <t xml:space="preserve">2.50510144233704</t>
   </si>
   <si>
     <t xml:space="preserve">2.5079448223114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50936675071716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50652289390564</t>
+    <t xml:space="preserve">2.50936627388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5065233707428</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486178398132</t>
@@ -884,43 +884,43 @@
     <t xml:space="preserve">2.63293862342834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65607333183289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70667886734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56642913818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52594351768494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52883577346802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47389268875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5216064453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5143768787384</t>
+    <t xml:space="preserve">2.65607357025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70667862892151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56642889976501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52594399452209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52883553504944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47389245033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52160620689392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51437664031982</t>
   </si>
   <si>
     <t xml:space="preserve">2.4710009098053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48979711532593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47533845901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51726865768433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45654225349426</t>
+    <t xml:space="preserve">2.48979735374451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47533822059631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51726889610291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45654201507568</t>
   </si>
   <si>
     <t xml:space="preserve">2.47967600822449</t>
@@ -932,10 +932,10 @@
     <t xml:space="preserve">2.48112177848816</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45798778533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48256802558899</t>
+    <t xml:space="preserve">2.45798826217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48256778717041</t>
   </si>
   <si>
     <t xml:space="preserve">2.48835110664368</t>
@@ -944,7 +944,7 @@
     <t xml:space="preserve">2.48690509796143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50859355926514</t>
+    <t xml:space="preserve">2.50859308242798</t>
   </si>
   <si>
     <t xml:space="preserve">2.53751158714294</t>
@@ -953,28 +953,28 @@
     <t xml:space="preserve">2.60257530212402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5591995716095</t>
+    <t xml:space="preserve">2.55919933319092</t>
   </si>
   <si>
     <t xml:space="preserve">2.49558067321777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59245419502258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6633026599884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61414265632629</t>
+    <t xml:space="preserve">2.59245443344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66330218315125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61414241790771</t>
   </si>
   <si>
     <t xml:space="preserve">2.63149261474609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6228175163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61703395843506</t>
+    <t xml:space="preserve">2.62281775474548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61703419685364</t>
   </si>
   <si>
     <t xml:space="preserve">2.72692060470581</t>
@@ -989,16 +989,16 @@
     <t xml:space="preserve">2.71246218681335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71390795707703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70812439918518</t>
+    <t xml:space="preserve">2.71390771865845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7081241607666</t>
   </si>
   <si>
     <t xml:space="preserve">2.68932819366455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68643617630005</t>
+    <t xml:space="preserve">2.68643641471863</t>
   </si>
   <si>
     <t xml:space="preserve">2.6878821849823</t>
@@ -1007,10 +1007,10 @@
     <t xml:space="preserve">2.71101641654968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65028882026672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67920732498169</t>
+    <t xml:space="preserve">2.6502890586853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67920708656311</t>
   </si>
   <si>
     <t xml:space="preserve">2.67197775840759</t>
@@ -1022,31 +1022,31 @@
     <t xml:space="preserve">2.65318059921265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65173506736755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66763997077942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65896534919739</t>
+    <t xml:space="preserve">2.6517345905304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.667640209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65896487236023</t>
   </si>
   <si>
     <t xml:space="preserve">2.64595150947571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59823775291443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62426352500916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60402131080627</t>
+    <t xml:space="preserve">2.59823799133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62426328659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6040210723877</t>
   </si>
   <si>
     <t xml:space="preserve">2.54474067687988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57654976844788</t>
+    <t xml:space="preserve">2.5765495300293</t>
   </si>
   <si>
     <t xml:space="preserve">2.52449798583984</t>
@@ -1064,7 +1064,7 @@
     <t xml:space="preserve">2.51148509979248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51871418952942</t>
+    <t xml:space="preserve">2.518714427948</t>
   </si>
   <si>
     <t xml:space="preserve">2.53317308425903</t>
@@ -1073,22 +1073,22 @@
     <t xml:space="preserve">2.5519700050354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50714755058289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55052375793457</t>
+    <t xml:space="preserve">2.50714731216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55052423477173</t>
   </si>
   <si>
     <t xml:space="preserve">2.54618644714355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53606534004211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5794415473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64161348342896</t>
+    <t xml:space="preserve">2.53606557846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57944130897522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64161372184753</t>
   </si>
   <si>
     <t xml:space="preserve">2.63004684448242</t>
@@ -1097,16 +1097,16 @@
     <t xml:space="preserve">2.58956265449524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52305197715759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51582264900208</t>
+    <t xml:space="preserve">2.52305245399475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51582288742065</t>
   </si>
   <si>
     <t xml:space="preserve">2.49268913269043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53461885452271</t>
+    <t xml:space="preserve">2.53461909294128</t>
   </si>
   <si>
     <t xml:space="preserve">2.4912428855896</t>
@@ -1121,73 +1121,73 @@
     <t xml:space="preserve">2.48401355743408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49413466453552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4984724521637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47823023796082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51293063163757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44931268692017</t>
+    <t xml:space="preserve">2.49413442611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49847221374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47823047637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51293087005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44931292533875</t>
   </si>
   <si>
     <t xml:space="preserve">2.407381772995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45509600639343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41027355194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29605054855347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2468900680542</t>
+    <t xml:space="preserve">2.45509648323059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4102737903595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29605031013489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24688982963562</t>
   </si>
   <si>
     <t xml:space="preserve">2.28159093856812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18471765518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19773054122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22086405754089</t>
+    <t xml:space="preserve">2.18471789360046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19773030281067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22086453437805</t>
   </si>
   <si>
     <t xml:space="preserve">2.26279449462891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28448224067688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28592824935913</t>
+    <t xml:space="preserve">2.28448247909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28592848777771</t>
   </si>
   <si>
     <t xml:space="preserve">2.32496762275696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34810161590576</t>
+    <t xml:space="preserve">2.34810137748718</t>
   </si>
   <si>
     <t xml:space="preserve">2.3784646987915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41461253166199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34231781959534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35677671432495</t>
+    <t xml:space="preserve">2.41461205482483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34231805801392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35677623748779</t>
   </si>
   <si>
     <t xml:space="preserve">2.35966849327087</t>
@@ -1199,34 +1199,34 @@
     <t xml:space="preserve">2.37701869010925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39292359352112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40015244483948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4059362411499</t>
+    <t xml:space="preserve">2.39292335510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40015268325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40593600273132</t>
   </si>
   <si>
     <t xml:space="preserve">2.33653426170349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29315757751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20495986938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23966073989868</t>
+    <t xml:space="preserve">2.29315781593323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20496010780334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2396605014801</t>
   </si>
   <si>
     <t xml:space="preserve">2.23821473121643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23387694358826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18327188491821</t>
+    <t xml:space="preserve">2.23387718200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18327164649963</t>
   </si>
   <si>
     <t xml:space="preserve">2.21797251701355</t>
@@ -1235,13 +1235,13 @@
     <t xml:space="preserve">2.24544405937195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20062232017517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22664761543274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28303670883179</t>
+    <t xml:space="preserve">2.20062208175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22664785385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28303694725037</t>
   </si>
   <si>
     <t xml:space="preserve">2.31340050697327</t>
@@ -1256,43 +1256,43 @@
     <t xml:space="preserve">2.38713979721069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34665584564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34520983695984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36545181274414</t>
+    <t xml:space="preserve">2.34665560722351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34520959854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36545205116272</t>
   </si>
   <si>
     <t xml:space="preserve">2.39436912536621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4030442237854</t>
+    <t xml:space="preserve">2.40304446220398</t>
   </si>
   <si>
     <t xml:space="preserve">2.40449047088623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32785964012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34954690933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33364272117615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31195449829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22953987121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3148467540741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30327939987183</t>
+    <t xml:space="preserve">2.32785940170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34954714775085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33364295959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31195473670959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22953963279724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31484651565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30327963829041</t>
   </si>
   <si>
     <t xml:space="preserve">2.32062983512878</t>
@@ -1301,25 +1301,25 @@
     <t xml:space="preserve">2.3076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37268114089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42907071113586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36400604248047</t>
+    <t xml:space="preserve">2.37268161773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42907047271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36400580406189</t>
   </si>
   <si>
     <t xml:space="preserve">2.31629228591919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35388469696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27725338935852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32930541038513</t>
+    <t xml:space="preserve">2.35388493537903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27725315093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32930493354797</t>
   </si>
   <si>
     <t xml:space="preserve">2.30617141723633</t>
@@ -1331,10 +1331,10 @@
     <t xml:space="preserve">2.37412714958191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33075094223022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32641339302063</t>
+    <t xml:space="preserve">2.33075070381165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32641363143921</t>
   </si>
   <si>
     <t xml:space="preserve">2.39726066589355</t>
@@ -1343,7 +1343,7 @@
     <t xml:space="preserve">2.39870691299438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38569402694702</t>
+    <t xml:space="preserve">2.3856942653656</t>
   </si>
   <si>
     <t xml:space="preserve">2.60112977027893</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">2.71969151496887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70957016944885</t>
+    <t xml:space="preserve">2.70956993103027</t>
   </si>
   <si>
     <t xml:space="preserve">2.75439214706421</t>
@@ -1364,13 +1364,13 @@
     <t xml:space="preserve">2.84837436676025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84114480018616</t>
+    <t xml:space="preserve">2.84114527702332</t>
   </si>
   <si>
     <t xml:space="preserve">2.83391547203064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86861610412598</t>
+    <t xml:space="preserve">2.86861658096313</t>
   </si>
   <si>
     <t xml:space="preserve">2.90042591094971</t>
@@ -1391,13 +1391,13 @@
     <t xml:space="preserve">2.82524037361145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80644416809082</t>
+    <t xml:space="preserve">2.80644392967224</t>
   </si>
   <si>
     <t xml:space="preserve">2.83680725097656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74716305732727</t>
+    <t xml:space="preserve">2.74716281890869</t>
   </si>
   <si>
     <t xml:space="preserve">2.7384877204895</t>
@@ -1409,58 +1409,58 @@
     <t xml:space="preserve">2.66091990470886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65060067176819</t>
+    <t xml:space="preserve">2.65060091018677</t>
   </si>
   <si>
     <t xml:space="preserve">2.71251702308655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70367121696472</t>
+    <t xml:space="preserve">2.7036714553833</t>
   </si>
   <si>
     <t xml:space="preserve">2.63143610954285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52824234962463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48254251480103</t>
+    <t xml:space="preserve">2.52824258804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4825427532196</t>
   </si>
   <si>
     <t xml:space="preserve">2.52234578132629</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56509685516357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6107976436615</t>
+    <t xml:space="preserve">2.56509733200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61079740524292</t>
   </si>
   <si>
     <t xml:space="preserve">2.57689046859741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51939725875854</t>
+    <t xml:space="preserve">2.51939749717712</t>
   </si>
   <si>
     <t xml:space="preserve">2.59163331985474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.618168592453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59015893936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54888105392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5606746673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55625176429749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54593276977539</t>
+    <t xml:space="preserve">2.61816835403442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59015917778015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54888081550598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56067442893982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55625200271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54593300819397</t>
   </si>
   <si>
     <t xml:space="preserve">2.57099390029907</t>
@@ -1469,7 +1469,7 @@
     <t xml:space="preserve">2.51350045204163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51055216789246</t>
+    <t xml:space="preserve">2.51055240631104</t>
   </si>
   <si>
     <t xml:space="preserve">2.53708744049072</t>
@@ -1481,22 +1481,22 @@
     <t xml:space="preserve">2.65354895591736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6594455242157</t>
+    <t xml:space="preserve">2.65944576263428</t>
   </si>
   <si>
     <t xml:space="preserve">2.70514535903931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6904034614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65797185897827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61964249610901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63291049003601</t>
+    <t xml:space="preserve">2.69040369987488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65797138214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61964273452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63291025161743</t>
   </si>
   <si>
     <t xml:space="preserve">2.64912629127502</t>
@@ -1508,28 +1508,28 @@
     <t xml:space="preserve">2.6653425693512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64470410346985</t>
+    <t xml:space="preserve">2.64470362663269</t>
   </si>
   <si>
     <t xml:space="preserve">2.63880729675293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66386818885803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71399116516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73168158531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71693968772888</t>
+    <t xml:space="preserve">2.66386866569519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71399140357971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73168134689331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71693992614746</t>
   </si>
   <si>
     <t xml:space="preserve">2.73315572738647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78180360794067</t>
+    <t xml:space="preserve">2.78180384635925</t>
   </si>
   <si>
     <t xml:space="preserve">2.70661950111389</t>
@@ -1538,10 +1538,10 @@
     <t xml:space="preserve">2.69187784194946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68892955780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67713570594788</t>
+    <t xml:space="preserve">2.68892931938171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67713618278503</t>
   </si>
   <si>
     <t xml:space="preserve">2.64617800712585</t>
@@ -1556,13 +1556,13 @@
     <t xml:space="preserve">2.61374592781067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60932350158691</t>
+    <t xml:space="preserve">2.60932326316833</t>
   </si>
   <si>
     <t xml:space="preserve">2.58868479728699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58131313323975</t>
+    <t xml:space="preserve">2.58131289482117</t>
   </si>
   <si>
     <t xml:space="preserve">2.53561353683472</t>
@@ -1571,109 +1571,109 @@
     <t xml:space="preserve">2.48843932151794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47222375869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50170683860779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56362271308899</t>
+    <t xml:space="preserve">2.47222352027893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50170731544495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56362295150757</t>
   </si>
   <si>
     <t xml:space="preserve">2.67123913764954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67418742179871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65502285957336</t>
+    <t xml:space="preserve">2.67418766021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65502309799194</t>
   </si>
   <si>
     <t xml:space="preserve">2.68450689315796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66239380836487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62406539916992</t>
+    <t xml:space="preserve">2.66239404678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62406516075134</t>
   </si>
   <si>
     <t xml:space="preserve">2.62996196746826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63733315467834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62111663818359</t>
+    <t xml:space="preserve">2.63733291625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62111687660217</t>
   </si>
   <si>
     <t xml:space="preserve">2.42210030555725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41915202140808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36608147621155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38966822624207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41325497627258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33659648895264</t>
+    <t xml:space="preserve">2.41915225982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36608171463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38966846466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41325521469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33659696578979</t>
   </si>
   <si>
     <t xml:space="preserve">2.24667167663574</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23045563697815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22898125648499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16706514358521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18033242225647</t>
+    <t xml:space="preserve">2.23045539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22898149490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16706490516663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18033266067505</t>
   </si>
   <si>
     <t xml:space="preserve">2.15674543380737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20244550704956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19360017776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13905572891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11399412155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08745837211609</t>
+    <t xml:space="preserve">2.20244526863098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19360041618347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13905549049377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11399388313293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08745813369751</t>
   </si>
   <si>
     <t xml:space="preserve">2.0417582988739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00932621955872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05207753181458</t>
+    <t xml:space="preserve">2.00932645797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05207777023315</t>
   </si>
   <si>
     <t xml:space="preserve">2.105149269104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05797410011292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05502605438232</t>
+    <t xml:space="preserve">2.05797457695007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05502581596375</t>
   </si>
   <si>
     <t xml:space="preserve">2.09335565567017</t>
@@ -1682,13 +1682,13 @@
     <t xml:space="preserve">2.13610696792603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11694264411926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09925270080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10220074653625</t>
+    <t xml:space="preserve">2.11694240570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09925246238708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10220098495483</t>
   </si>
   <si>
     <t xml:space="preserve">2.10072636604309</t>
@@ -1697,49 +1697,49 @@
     <t xml:space="preserve">2.09040641784668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04912924766541</t>
+    <t xml:space="preserve">2.04912948608398</t>
   </si>
   <si>
     <t xml:space="preserve">2.06829380989075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05060338973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0476553440094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02701663970947</t>
+    <t xml:space="preserve">2.05060315132141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04765510559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02701640129089</t>
   </si>
   <si>
     <t xml:space="preserve">2.01964569091797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97394585609436</t>
+    <t xml:space="preserve">1.97394597530365</t>
   </si>
   <si>
     <t xml:space="preserve">1.97984254360199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96215164661407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98426532745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08008718490601</t>
+    <t xml:space="preserve">1.96215176582336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98426496982574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08008742332458</t>
   </si>
   <si>
     <t xml:space="preserve">2.06387090682983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07861280441284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04618096351624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08598351478577</t>
+    <t xml:space="preserve">2.07861304283142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04618120193481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08598375320435</t>
   </si>
   <si>
     <t xml:space="preserve">2.05650043487549</t>
@@ -1748,73 +1748,73 @@
     <t xml:space="preserve">1.95625483989716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98279082775116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94446122646332</t>
+    <t xml:space="preserve">1.98279118537903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94446110725403</t>
   </si>
   <si>
     <t xml:space="preserve">1.93709051609039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96657431125641</t>
+    <t xml:space="preserve">1.9665744304657</t>
   </si>
   <si>
     <t xml:space="preserve">1.96804821491241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89286506175995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98131680488586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91497790813446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87517476081848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87370038032532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94003880023956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92677128314972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9931104183197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0034294128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.994584441185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99163615703583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94888412952423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8884425163269</t>
+    <t xml:space="preserve">1.89286530017853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98131656646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91497766971588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87517464160919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87370049953461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94003915786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92677140235901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99311053752899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00342965126038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99458432197571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99163603782654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94888401031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88844239711761</t>
   </si>
   <si>
     <t xml:space="preserve">1.87222623825073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91940033435822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89433896541595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86485540866852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85306215286255</t>
+    <t xml:space="preserve">1.91940057277679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89433884620667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86485517024994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85306191444397</t>
   </si>
   <si>
     <t xml:space="preserve">1.83831918239594</t>
@@ -1823,58 +1823,58 @@
     <t xml:space="preserve">1.88549399375916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85158753395081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8250515460968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78230011463165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71596121788025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69532263278961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71006441116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73217797279358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78377437591553</t>
+    <t xml:space="preserve">1.8515876531601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82505142688751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78230023384094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71596133708954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69532251358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71006453037262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73217809200287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78377461433411</t>
   </si>
   <si>
     <t xml:space="preserve">1.76313591003418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76166176795959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78672289848328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80588722229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83389687538147</t>
+    <t xml:space="preserve">1.76166188716888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78672301769257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80588710308075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83389711380005</t>
   </si>
   <si>
     <t xml:space="preserve">1.87664890289307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86927795410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84569036960602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83979344367981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83242249488831</t>
+    <t xml:space="preserve">1.86927819252014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84569025039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8397935628891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83242237567902</t>
   </si>
   <si>
     <t xml:space="preserve">1.84274184703827</t>
@@ -1886,10 +1886,10 @@
     <t xml:space="preserve">1.8972874879837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88991641998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88254547119141</t>
+    <t xml:space="preserve">1.88991665840149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88254570960999</t>
   </si>
   <si>
     <t xml:space="preserve">1.91055500507355</t>
@@ -1898,16 +1898,16 @@
     <t xml:space="preserve">1.87075197696686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80293881893158</t>
+    <t xml:space="preserve">1.80293893814087</t>
   </si>
   <si>
     <t xml:space="preserve">1.80441308021545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79114532470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75576484203339</t>
+    <t xml:space="preserve">1.79114508628845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75576496124268</t>
   </si>
   <si>
     <t xml:space="preserve">1.81325829029083</t>
@@ -1919,19 +1919,19 @@
     <t xml:space="preserve">1.83537101745605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79556810855865</t>
+    <t xml:space="preserve">1.79556798934937</t>
   </si>
   <si>
     <t xml:space="preserve">1.77492940425873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80883586406708</t>
+    <t xml:space="preserve">1.80883550643921</t>
   </si>
   <si>
     <t xml:space="preserve">1.79851627349854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79704225063324</t>
+    <t xml:space="preserve">1.79704236984253</t>
   </si>
   <si>
     <t xml:space="preserve">1.8073616027832</t>
@@ -1940,22 +1940,22 @@
     <t xml:space="preserve">1.78082621097565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7542906999588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71301281452179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70711624622345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.745445728302</t>
+    <t xml:space="preserve">1.75429081916809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7130126953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70711612701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74544548988342</t>
   </si>
   <si>
     <t xml:space="preserve">1.76460993289948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77198076248169</t>
+    <t xml:space="preserve">1.77198100090027</t>
   </si>
   <si>
     <t xml:space="preserve">1.77787756919861</t>
@@ -1964,49 +1964,49 @@
     <t xml:space="preserve">1.78819692134857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74839413166046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6658388376236</t>
+    <t xml:space="preserve">1.74839389324188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66583895683289</t>
   </si>
   <si>
     <t xml:space="preserve">1.67910659313202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6112939119339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57886111736298</t>
+    <t xml:space="preserve">1.61129379272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57886123657227</t>
   </si>
   <si>
     <t xml:space="preserve">1.53610992431641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55822277069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54200673103333</t>
+    <t xml:space="preserve">1.55822265148163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54200661182404</t>
   </si>
   <si>
     <t xml:space="preserve">1.53445518016815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53596556186676</t>
+    <t xml:space="preserve">1.53596544265747</t>
   </si>
   <si>
     <t xml:space="preserve">1.56466090679169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54351699352264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55559909343719</t>
+    <t xml:space="preserve">1.54351687431335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55559897422791</t>
   </si>
   <si>
     <t xml:space="preserve">1.5389860868454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54502725601196</t>
+    <t xml:space="preserve">1.54502713680267</t>
   </si>
   <si>
     <t xml:space="preserve">1.60543847084045</t>
@@ -2021,7 +2021,7 @@
     <t xml:space="preserve">1.56919169425964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58882546424866</t>
+    <t xml:space="preserve">1.58882534503937</t>
   </si>
   <si>
     <t xml:space="preserve">1.51028990745544</t>
@@ -2030,16 +2030,16 @@
     <t xml:space="preserve">1.51935243606567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52690374851227</t>
+    <t xml:space="preserve">1.52690386772156</t>
   </si>
   <si>
     <t xml:space="preserve">1.4717777967453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47026741504669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.471022605896</t>
+    <t xml:space="preserve">1.47026753425598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47102272510529</t>
   </si>
   <si>
     <t xml:space="preserve">1.45138907432556</t>
@@ -2051,22 +2051,22 @@
     <t xml:space="preserve">1.49367690086365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48386001586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50047314167023</t>
+    <t xml:space="preserve">1.48385989665985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50047302246094</t>
   </si>
   <si>
     <t xml:space="preserve">1.45894038677216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46800220012665</t>
+    <t xml:space="preserve">1.46800208091736</t>
   </si>
   <si>
     <t xml:space="preserve">1.48990118503571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4823499917984</t>
+    <t xml:space="preserve">1.48234987258911</t>
   </si>
   <si>
     <t xml:space="preserve">1.4808394908905</t>
@@ -2075,55 +2075,55 @@
     <t xml:space="preserve">1.53294491767883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57523286342621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56315052509308</t>
+    <t xml:space="preserve">1.57523274421692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56315040588379</t>
   </si>
   <si>
     <t xml:space="preserve">1.52539360523224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50424885749817</t>
+    <t xml:space="preserve">1.50424873828888</t>
   </si>
   <si>
     <t xml:space="preserve">1.47328805923462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4725329875946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44912350177765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4536544084549</t>
+    <t xml:space="preserve">1.47253286838531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44912362098694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45365452766418</t>
   </si>
   <si>
     <t xml:space="preserve">1.46649181842804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44987869262695</t>
+    <t xml:space="preserve">1.44987881183624</t>
   </si>
   <si>
     <t xml:space="preserve">1.44610297679901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43779647350311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42269361019135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42042815685272</t>
+    <t xml:space="preserve">1.4377965927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42269372940063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42042827606201</t>
   </si>
   <si>
     <t xml:space="preserve">1.4272243976593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41665244102478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40683567523956</t>
+    <t xml:space="preserve">1.41665256023407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40683579444885</t>
   </si>
   <si>
     <t xml:space="preserve">1.400794506073</t>
@@ -2135,16 +2135,16 @@
     <t xml:space="preserve">1.3864461183548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28374695777893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25354051589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25127530097961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20068061351776</t>
+    <t xml:space="preserve">1.28374683856964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25354063510895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25127518177032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20068073272705</t>
   </si>
   <si>
     <t xml:space="preserve">1.23617231845856</t>
@@ -2153,37 +2153,37 @@
     <t xml:space="preserve">1.25278532505035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2218245267868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2308863401413</t>
+    <t xml:space="preserve">1.22182464599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23088622093201</t>
   </si>
   <si>
     <t xml:space="preserve">1.27695071697235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26637887954712</t>
+    <t xml:space="preserve">1.26637876033783</t>
   </si>
   <si>
     <t xml:space="preserve">1.27619552612305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31395256519318</t>
+    <t xml:space="preserve">1.31395268440247</t>
   </si>
   <si>
     <t xml:space="preserve">1.27090954780579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28223669528961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28752267360687</t>
+    <t xml:space="preserve">1.28223657608032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28752255439758</t>
   </si>
   <si>
     <t xml:space="preserve">1.35775077342987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38342571258545</t>
+    <t xml:space="preserve">1.38342559337616</t>
   </si>
   <si>
     <t xml:space="preserve">1.37436378002167</t>
@@ -2201,61 +2201,61 @@
     <t xml:space="preserve">1.36681246757507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.350954413414</t>
+    <t xml:space="preserve">1.35095453262329</t>
   </si>
   <si>
     <t xml:space="preserve">1.35926103591919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36454701423645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33736181259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30262529850006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28978824615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26109290122986</t>
+    <t xml:space="preserve">1.36454689502716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33736193180084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30262553691864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2897881269455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26109278202057</t>
   </si>
   <si>
     <t xml:space="preserve">1.26864409446716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25505089759827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27468526363373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27997136116028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25958156585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25429558753967</t>
+    <t xml:space="preserve">1.25505077838898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27468514442444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27997124195099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25958168506622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25429570674896</t>
   </si>
   <si>
     <t xml:space="preserve">1.26939928531647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28148138523102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30413579940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33660697937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36077129840851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38871252536774</t>
+    <t xml:space="preserve">1.2814816236496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30413591861725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33660686016083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36077117919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38871228694916</t>
   </si>
   <si>
     <t xml:space="preserve">1.38267040252686</t>
@@ -2288,25 +2288,25 @@
     <t xml:space="preserve">1.43326556682587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40532541275024</t>
+    <t xml:space="preserve">1.40532553195953</t>
   </si>
   <si>
     <t xml:space="preserve">1.43477582931519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62960302829742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58278429508209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57825362682343</t>
+    <t xml:space="preserve">1.62960290908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58278405666351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57825338840485</t>
   </si>
   <si>
     <t xml:space="preserve">1.58127391338348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54653751850128</t>
+    <t xml:space="preserve">1.54653763771057</t>
   </si>
   <si>
     <t xml:space="preserve">1.53747582435608</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">1.63111317157745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60090756416321</t>
+    <t xml:space="preserve">1.6009076833725</t>
   </si>
   <si>
     <t xml:space="preserve">1.62054133415222</t>
@@ -2339,43 +2339,43 @@
     <t xml:space="preserve">1.61147952079773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64168608188629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61298978328705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61752068996429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59184587001801</t>
+    <t xml:space="preserve">1.641685962677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61298990249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.617520570755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59184598922729</t>
   </si>
   <si>
     <t xml:space="preserve">1.58731508255005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61903119087219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57976365089417</t>
+    <t xml:space="preserve">1.6190310716629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57976377010345</t>
   </si>
   <si>
     <t xml:space="preserve">1.56013000011444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55861973762512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59788703918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60392820835114</t>
+    <t xml:space="preserve">1.55861985683441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59788691997528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60392808914185</t>
   </si>
   <si>
     <t xml:space="preserve">1.58580482006073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59939742088318</t>
+    <t xml:space="preserve">1.59939730167389</t>
   </si>
   <si>
     <t xml:space="preserve">1.59637677669525</t>
@@ -2384,58 +2384,58 @@
     <t xml:space="preserve">1.59033560752869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52992451190948</t>
+    <t xml:space="preserve">1.52992463111877</t>
   </si>
   <si>
     <t xml:space="preserve">1.51331114768982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50953483581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52388334274292</t>
+    <t xml:space="preserve">1.50953495502472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52388322353363</t>
   </si>
   <si>
     <t xml:space="preserve">1.54049634933472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63866460323334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75948798656464</t>
+    <t xml:space="preserve">1.63866472244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75948822498322</t>
   </si>
   <si>
     <t xml:space="preserve">1.806307554245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78365325927734</t>
+    <t xml:space="preserve">1.78365314006805</t>
   </si>
   <si>
     <t xml:space="preserve">1.83953368663788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02983069419861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06909823417664</t>
+    <t xml:space="preserve">2.02983045578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06909799575806</t>
   </si>
   <si>
     <t xml:space="preserve">1.94827461242676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89088332653046</t>
+    <t xml:space="preserve">1.89088344573975</t>
   </si>
   <si>
     <t xml:space="preserve">1.7791223526001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77308106422424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81687951087952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70813858509064</t>
+    <t xml:space="preserve">1.77308118343353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81687963008881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70813846588135</t>
   </si>
   <si>
     <t xml:space="preserve">1.4800843000412</t>
@@ -2447,10 +2447,10 @@
     <t xml:space="preserve">1.3245245218277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2407032251358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19917047023773</t>
+    <t xml:space="preserve">1.24070310592651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19917058944702</t>
   </si>
   <si>
     <t xml:space="preserve">1.18406772613525</t>
@@ -2459,25 +2459,25 @@
     <t xml:space="preserve">0.959789276123047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995280981063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919011652469635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945441663265228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962809920310974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01869106292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04361057281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990750133991241</t>
+    <t xml:space="preserve">0.995281040668488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.91901171207428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945441722869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962809860706329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01869094371796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04361069202423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990750074386597</t>
   </si>
   <si>
     <t xml:space="preserve">1.07155084609985</t>
@@ -2492,10 +2492,10 @@
     <t xml:space="preserve">1.01944613456726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999811768531799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0413453578949</t>
+    <t xml:space="preserve">0.999811708927155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04134523868561</t>
   </si>
   <si>
     <t xml:space="preserve">1.02699756622314</t>
@@ -2504,25 +2504,25 @@
     <t xml:space="preserve">1.10628736019135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05720317363739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11459398269653</t>
+    <t xml:space="preserve">1.0572030544281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11459386348724</t>
   </si>
   <si>
     <t xml:space="preserve">1.13875913619995</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20219099521637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16745448112488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16594421863556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08740890026093</t>
+    <t xml:space="preserve">1.20219111442566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16745460033417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16594409942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08740878105164</t>
   </si>
   <si>
     <t xml:space="preserve">1.0670200586319</t>
@@ -2531,10 +2531,10 @@
     <t xml:space="preserve">1.09420502185822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06324434280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09496021270752</t>
+    <t xml:space="preserve">1.06324422359467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09496009349823</t>
   </si>
   <si>
     <t xml:space="preserve">1.07834708690643</t>
@@ -2546,7 +2546,7 @@
     <t xml:space="preserve">1.07457137107849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08665370941162</t>
+    <t xml:space="preserve">1.08665382862091</t>
   </si>
   <si>
     <t xml:space="preserve">1.09269499778748</t>
@@ -2555,49 +2555,49 @@
     <t xml:space="preserve">1.03756952285767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07306122779846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04965174198151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03530418872833</t>
+    <t xml:space="preserve">1.07306110858917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0496518611908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03530406951904</t>
   </si>
   <si>
     <t xml:space="preserve">1.04436588287354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04285550117493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01189482212067</t>
+    <t xml:space="preserve">1.04285562038422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01189494132996</t>
   </si>
   <si>
     <t xml:space="preserve">0.985464036464691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.970361411571503</t>
+    <t xml:space="preserve">0.970361292362213</t>
   </si>
   <si>
     <t xml:space="preserve">0.989239811897278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.94317615032196</t>
+    <t xml:space="preserve">0.943176209926605</t>
   </si>
   <si>
     <t xml:space="preserve">0.926563084125519</t>
   </si>
   <si>
-    <t xml:space="preserve">0.921277105808258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913725674152374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986219227313995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997546255588531</t>
+    <t xml:space="preserve">0.921277046203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913725733757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986219048500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997546315193176</t>
   </si>
   <si>
     <t xml:space="preserve">1.058713555336</t>
@@ -2612,34 +2612,34 @@
     <t xml:space="preserve">1.13422763347626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18180227279663</t>
+    <t xml:space="preserve">1.18180215358734</t>
   </si>
   <si>
     <t xml:space="preserve">1.21502840518951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23919284343719</t>
+    <t xml:space="preserve">1.23919296264648</t>
   </si>
   <si>
     <t xml:space="preserve">1.19992554187775</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18935358524323</t>
+    <t xml:space="preserve">1.18935370445251</t>
   </si>
   <si>
     <t xml:space="preserve">1.14782083034515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16820967197418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18708825111389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16216862201691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19312930107117</t>
+    <t xml:space="preserve">1.16820979118347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1870881319046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16216850280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19312918186188</t>
   </si>
   <si>
     <t xml:space="preserve">1.17047512531281</t>
@@ -2654,31 +2654,31 @@
     <t xml:space="preserve">1.36303675174713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40381515026093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41136646270752</t>
+    <t xml:space="preserve">1.40381503105164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41136658191681</t>
   </si>
   <si>
     <t xml:space="preserve">1.39399826526642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39928436279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40154957771301</t>
+    <t xml:space="preserve">1.39928424358368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40154981613159</t>
   </si>
   <si>
     <t xml:space="preserve">1.40305995941162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41589736938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49292182922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44836831092834</t>
+    <t xml:space="preserve">1.41589725017548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49292171001434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44836843013763</t>
   </si>
   <si>
     <t xml:space="preserve">1.48763573169708</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">1.46498155593872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39626371860504</t>
+    <t xml:space="preserve">1.39626359939575</t>
   </si>
   <si>
     <t xml:space="preserve">1.37662935256958</t>
@@ -2702,22 +2702,22 @@
     <t xml:space="preserve">1.3690779209137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43175542354584</t>
+    <t xml:space="preserve">1.43175530433655</t>
   </si>
   <si>
     <t xml:space="preserve">1.445347905159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47479832172394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48461508750916</t>
+    <t xml:space="preserve">1.47479844093323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48461520671844</t>
   </si>
   <si>
     <t xml:space="preserve">1.55106842517853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52086269855499</t>
+    <t xml:space="preserve">1.5208625793457</t>
   </si>
   <si>
     <t xml:space="preserve">1.37889468669891</t>
@@ -2726,10 +2726,10 @@
     <t xml:space="preserve">1.3781396150589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34415817260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37209856510162</t>
+    <t xml:space="preserve">1.34415805339813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37209844589233</t>
   </si>
   <si>
     <t xml:space="preserve">1.39475345611572</t>
@@ -2741,13 +2741,13 @@
     <t xml:space="preserve">1.38795721530914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39248812198639</t>
+    <t xml:space="preserve">1.39248788356781</t>
   </si>
   <si>
     <t xml:space="preserve">1.32150399684906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31848347187042</t>
+    <t xml:space="preserve">1.31848335266113</t>
   </si>
   <si>
     <t xml:space="preserve">1.34340298175812</t>
@@ -2756,19 +2756,19 @@
     <t xml:space="preserve">1.30036008358002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32376945018768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33434152603149</t>
+    <t xml:space="preserve">1.32376956939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3343414068222</t>
   </si>
   <si>
     <t xml:space="preserve">1.39777398109436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36983299255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38191533088684</t>
+    <t xml:space="preserve">1.369833111763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38191509246826</t>
   </si>
   <si>
     <t xml:space="preserve">1.34038257598877</t>
@@ -2786,7 +2786,7 @@
     <t xml:space="preserve">1.33585166931152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27393019199371</t>
+    <t xml:space="preserve">1.27393007278442</t>
   </si>
   <si>
     <t xml:space="preserve">1.26486849784851</t>
@@ -2801,37 +2801,37 @@
     <t xml:space="preserve">1.11761450767517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10779762268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13800394535065</t>
+    <t xml:space="preserve">1.10779774188995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13800406455994</t>
   </si>
   <si>
     <t xml:space="preserve">1.22711062431335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24221348762512</t>
+    <t xml:space="preserve">1.24221336841583</t>
   </si>
   <si>
     <t xml:space="preserve">1.23843777179718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22862076759338</t>
+    <t xml:space="preserve">1.22862100601196</t>
   </si>
   <si>
     <t xml:space="preserve">1.44232726097107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43251049518585</t>
+    <t xml:space="preserve">1.43251061439514</t>
   </si>
   <si>
     <t xml:space="preserve">1.50273859500885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55408883094788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81234860420227</t>
+    <t xml:space="preserve">1.55408895015717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81234848499298</t>
   </si>
   <si>
     <t xml:space="preserve">1.78214299678802</t>
@@ -2840,46 +2840,46 @@
     <t xml:space="preserve">1.77459168434143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75797760486603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69303560256958</t>
+    <t xml:space="preserve">1.75797772407532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.693035364151</t>
   </si>
   <si>
     <t xml:space="preserve">1.7217310667038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6854841709137</t>
+    <t xml:space="preserve">1.68548429012299</t>
   </si>
   <si>
     <t xml:space="preserve">1.70209729671478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7036075592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73079252243042</t>
+    <t xml:space="preserve">1.70360743999481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73079264163971</t>
   </si>
   <si>
     <t xml:space="preserve">1.72777211666107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69907665252686</t>
+    <t xml:space="preserve">1.69907653331757</t>
   </si>
   <si>
     <t xml:space="preserve">1.66887104511261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66282987594604</t>
+    <t xml:space="preserve">1.66282999515533</t>
   </si>
   <si>
     <t xml:space="preserve">1.67944288253784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66131961345673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67642223834991</t>
+    <t xml:space="preserve">1.66131949424744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67642247676849</t>
   </si>
   <si>
     <t xml:space="preserve">1.64470648765564</t>
@@ -2897,13 +2897,13 @@
     <t xml:space="preserve">1.66585052013397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66434001922607</t>
+    <t xml:space="preserve">1.66434013843536</t>
   </si>
   <si>
     <t xml:space="preserve">1.74438524246216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77761220932007</t>
+    <t xml:space="preserve">1.77761209011078</t>
   </si>
   <si>
     <t xml:space="preserve">1.756467461586</t>
@@ -2915,34 +2915,34 @@
     <t xml:space="preserve">1.73683369159698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69454598426819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6522581577301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67491209506989</t>
+    <t xml:space="preserve">1.6945458650589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65225803852081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67491221427917</t>
   </si>
   <si>
     <t xml:space="preserve">1.65376830101013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63715445995331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57070195674896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59486639499664</t>
+    <t xml:space="preserve">1.63715434074402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57070183753967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59486651420593</t>
   </si>
   <si>
     <t xml:space="preserve">1.62205159664154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7474057674408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88635230064392</t>
+    <t xml:space="preserve">1.74740564823151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88635241985321</t>
   </si>
   <si>
     <t xml:space="preserve">1.85765707492828</t>
@@ -2954,13 +2954,13 @@
     <t xml:space="preserve">1.86822915077209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85463654994965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88937282562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8501056432724</t>
+    <t xml:space="preserve">1.85463643074036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88937318325043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85010552406311</t>
   </si>
   <si>
     <t xml:space="preserve">1.80932807922363</t>
@@ -2969,28 +2969,28 @@
     <t xml:space="preserve">1.83047211170197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82141005992889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81838989257812</t>
+    <t xml:space="preserve">1.82141017913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81838977336884</t>
   </si>
   <si>
     <t xml:space="preserve">1.82594120502472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80781745910645</t>
+    <t xml:space="preserve">1.80781757831573</t>
   </si>
   <si>
     <t xml:space="preserve">1.80177640914917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84557473659515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83500266075134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82745134830475</t>
+    <t xml:space="preserve">1.84557461738586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83500254154205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82745146751404</t>
   </si>
   <si>
     <t xml:space="preserve">1.87124967575073</t>
@@ -3002,7 +3002,7 @@
     <t xml:space="preserve">1.927130818367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9799907207489</t>
+    <t xml:space="preserve">1.97999060153961</t>
   </si>
   <si>
     <t xml:space="preserve">2.05399513244629</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">2.18085956573486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15216398239136</t>
+    <t xml:space="preserve">2.15216422080994</t>
   </si>
   <si>
     <t xml:space="preserve">2.12950897216797</t>
@@ -3029,7 +3029,7 @@
     <t xml:space="preserve">2.1355504989624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13857102394104</t>
+    <t xml:space="preserve">2.13857126235962</t>
   </si>
   <si>
     <t xml:space="preserve">2.22465753555298</t>
@@ -3041,7 +3041,7 @@
     <t xml:space="preserve">2.18992114067078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18690061569214</t>
+    <t xml:space="preserve">2.18690085411072</t>
   </si>
   <si>
     <t xml:space="preserve">2.16877722740173</t>
@@ -3050,7 +3050,7 @@
     <t xml:space="preserve">2.17028760910034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23522973060608</t>
+    <t xml:space="preserve">2.2352294921875</t>
   </si>
   <si>
     <t xml:space="preserve">2.24731183052063</t>
@@ -3059,28 +3059,28 @@
     <t xml:space="preserve">2.26996684074402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30168318748474</t>
+    <t xml:space="preserve">2.30168294906616</t>
   </si>
   <si>
     <t xml:space="preserve">2.23673987388611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24580144882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24882221221924</t>
+    <t xml:space="preserve">2.2458016872406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24882245063782</t>
   </si>
   <si>
     <t xml:space="preserve">2.36964535713196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39985179901123</t>
+    <t xml:space="preserve">2.39985203742981</t>
   </si>
   <si>
     <t xml:space="preserve">2.48140692710876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54937052726746</t>
+    <t xml:space="preserve">2.54937028884888</t>
   </si>
   <si>
     <t xml:space="preserve">2.64300799369812</t>
@@ -3098,16 +3098,16 @@
     <t xml:space="preserve">2.73815655708313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78648638725281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88616514205933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8650209903717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86200046539307</t>
+    <t xml:space="preserve">2.78648614883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88616490364075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86502122879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86200022697449</t>
   </si>
   <si>
     <t xml:space="preserve">2.94204592704773</t>
@@ -3125,7 +3125,7 @@
     <t xml:space="preserve">2.96621060371399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9571487903595</t>
+    <t xml:space="preserve">2.95714855194092</t>
   </si>
   <si>
     <t xml:space="preserve">2.97829270362854</t>
@@ -3134,19 +3134,19 @@
     <t xml:space="preserve">3.08411288261414</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07337737083435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05804061889648</t>
+    <t xml:space="preserve">3.07337760925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05804085731506</t>
   </si>
   <si>
     <t xml:space="preserve">3.15312552452087</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0917809009552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11478495597839</t>
+    <t xml:space="preserve">3.09178066253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11478519439697</t>
   </si>
   <si>
     <t xml:space="preserve">3.19299960136414</t>
@@ -3155,16 +3155,16 @@
     <t xml:space="preserve">3.21600413322449</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18839812278748</t>
+    <t xml:space="preserve">3.18839836120605</t>
   </si>
   <si>
     <t xml:space="preserve">3.17459583282471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12858748435974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06264138221741</t>
+    <t xml:space="preserve">3.12858772277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06264162063599</t>
   </si>
   <si>
     <t xml:space="preserve">2.98749446868896</t>
@@ -3173,19 +3173,19 @@
     <t xml:space="preserve">2.96602392196655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95988917350769</t>
+    <t xml:space="preserve">2.95988941192627</t>
   </si>
   <si>
     <t xml:space="preserve">2.9445526599884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91388010978699</t>
+    <t xml:space="preserve">2.91388034820557</t>
   </si>
   <si>
     <t xml:space="preserve">2.901611328125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83106517791748</t>
+    <t xml:space="preserve">2.83106541633606</t>
   </si>
   <si>
     <t xml:space="preserve">2.80192589759827</t>
@@ -3197,10 +3197,10 @@
     <t xml:space="preserve">2.73598051071167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79425764083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79272437095642</t>
+    <t xml:space="preserve">2.7942578792572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79272413253784</t>
   </si>
   <si>
     <t xml:space="preserve">2.83719944953918</t>
@@ -3209,34 +3209,34 @@
     <t xml:space="preserve">2.76665282249451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80499315261841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79119038581848</t>
+    <t xml:space="preserve">2.80499291419983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79119062423706</t>
   </si>
   <si>
     <t xml:space="preserve">2.85713672637939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78198909759521</t>
+    <t xml:space="preserve">2.78198885917664</t>
   </si>
   <si>
     <t xml:space="preserve">2.7513165473938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7237114906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84333419799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79579162597656</t>
+    <t xml:space="preserve">2.72371172904968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84333443641663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79579138755798</t>
   </si>
   <si>
     <t xml:space="preserve">2.77892160415649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72524523735046</t>
+    <t xml:space="preserve">2.72524499893188</t>
   </si>
   <si>
     <t xml:space="preserve">2.67310166358948</t>
@@ -3245,19 +3245,19 @@
     <t xml:space="preserve">2.58108496665955</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66543340682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73291325569153</t>
+    <t xml:space="preserve">2.66543364524841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73291349411011</t>
   </si>
   <si>
     <t xml:space="preserve">2.75745129585266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.783522605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92614912986755</t>
+    <t xml:space="preserve">2.78352236747742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92614936828613</t>
   </si>
   <si>
     <t xml:space="preserve">2.88934254646301</t>
@@ -3266,16 +3266,16 @@
     <t xml:space="preserve">2.94301891326904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90774607658386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85100221633911</t>
+    <t xml:space="preserve">2.90774583816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85100197792053</t>
   </si>
   <si>
     <t xml:space="preserve">2.86020374298096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85867047309875</t>
+    <t xml:space="preserve">2.85867023468018</t>
   </si>
   <si>
     <t xml:space="preserve">2.83873319625854</t>
@@ -3293,22 +3293,22 @@
     <t xml:space="preserve">2.90467858314514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96755743026733</t>
+    <t xml:space="preserve">2.96755766868591</t>
   </si>
   <si>
     <t xml:space="preserve">2.92768287658691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92461562156677</t>
+    <t xml:space="preserve">2.92461538314819</t>
   </si>
   <si>
     <t xml:space="preserve">2.83566617965698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86173748970032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84640121459961</t>
+    <t xml:space="preserve">2.86173725128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84640145301819</t>
   </si>
   <si>
     <t xml:space="preserve">2.87860727310181</t>
@@ -3320,10 +3320,10 @@
     <t xml:space="preserve">2.99976348876953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0074315071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98289370536804</t>
+    <t xml:space="preserve">3.00743174552917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98289394378662</t>
   </si>
   <si>
     <t xml:space="preserve">2.98596096038818</t>
@@ -3332,7 +3332,7 @@
     <t xml:space="preserve">2.95375514030457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99056172370911</t>
+    <t xml:space="preserve">2.99056148529053</t>
   </si>
   <si>
     <t xml:space="preserve">2.93688440322876</t>
@@ -3341,7 +3341,7 @@
     <t xml:space="preserve">2.95682215690613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9000780582428</t>
+    <t xml:space="preserve">2.90007758140564</t>
   </si>
   <si>
     <t xml:space="preserve">2.84180068969727</t>
@@ -3353,7 +3353,7 @@
     <t xml:space="preserve">2.81726264953613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76511907577515</t>
+    <t xml:space="preserve">2.76511931419373</t>
   </si>
   <si>
     <t xml:space="preserve">2.8295316696167</t>
@@ -3392,10 +3392,10 @@
     <t xml:space="preserve">2.93075037002563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90314531326294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88320827484131</t>
+    <t xml:space="preserve">2.90314507484436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88320803642273</t>
   </si>
   <si>
     <t xml:space="preserve">2.86633825302124</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">2.87554001808167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9062123298645</t>
+    <t xml:space="preserve">2.90621256828308</t>
   </si>
   <si>
     <t xml:space="preserve">2.95528864860535</t>
@@ -3416,13 +3416,13 @@
     <t xml:space="preserve">2.98902797698975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95068788528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99669599533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02890229225159</t>
+    <t xml:space="preserve">2.950688123703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99669623374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02890205383301</t>
   </si>
   <si>
     <t xml:space="preserve">3.03657007217407</t>
@@ -3434,19 +3434,19 @@
     <t xml:space="preserve">2.93535089492798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88014101982117</t>
+    <t xml:space="preserve">2.88014078140259</t>
   </si>
   <si>
     <t xml:space="preserve">2.91234660148621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98136019706726</t>
+    <t xml:space="preserve">2.98135995864868</t>
   </si>
   <si>
     <t xml:space="preserve">3.03350281715393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94915413856506</t>
+    <t xml:space="preserve">2.94915390014648</t>
   </si>
   <si>
     <t xml:space="preserve">2.85560321807861</t>
@@ -3467,13 +3467,13 @@
     <t xml:space="preserve">2.70684194564819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66083264350891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7605185508728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71144247055054</t>
+    <t xml:space="preserve">2.66083288192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76051831245422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71144270896912</t>
   </si>
   <si>
     <t xml:space="preserve">2.58875298500061</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">2.73137974739075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62249255180359</t>
+    <t xml:space="preserve">2.62249231338501</t>
   </si>
   <si>
     <t xml:space="preserve">2.65009760856628</t>
@@ -3497,7 +3497,7 @@
     <t xml:space="preserve">2.74671578407288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72064423561096</t>
+    <t xml:space="preserve">2.72064447402954</t>
   </si>
   <si>
     <t xml:space="preserve">2.71911072731018</t>
@@ -3506,10 +3506,10 @@
     <t xml:space="preserve">2.69610667228699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66850066184998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75438404083252</t>
+    <t xml:space="preserve">2.66850090026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75438380241394</t>
   </si>
   <si>
     <t xml:space="preserve">2.8249306678772</t>
@@ -3518,16 +3518,16 @@
     <t xml:space="preserve">2.85406947135925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89701056480408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9782931804657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8632709980011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94148516654968</t>
+    <t xml:space="preserve">2.89701080322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97829294204712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86327123641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94148540496826</t>
   </si>
   <si>
     <t xml:space="preserve">3.03503656387329</t>
@@ -3548,7 +3548,7 @@
     <t xml:space="preserve">2.86480474472046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82799816131592</t>
+    <t xml:space="preserve">2.82799792289734</t>
   </si>
   <si>
     <t xml:space="preserve">2.97062468528748</t>
@@ -3557,25 +3557,25 @@
     <t xml:space="preserve">2.92445588111877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90142869949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05187320709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07029485702515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15472817420959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08871698379517</t>
+    <t xml:space="preserve">2.90142893791199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05187344551086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07029509544373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15472841262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08871674537659</t>
   </si>
   <si>
     <t xml:space="preserve">3.19771218299866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21459889411926</t>
+    <t xml:space="preserve">3.21459913253784</t>
   </si>
   <si>
     <t xml:space="preserve">3.18850111961365</t>
@@ -3593,25 +3593,25 @@
     <t xml:space="preserve">2.94748306274414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80010914802551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8476984500885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72028112411499</t>
+    <t xml:space="preserve">2.80010890960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84769868850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72028136253357</t>
   </si>
   <si>
     <t xml:space="preserve">2.55602049827576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58979392051697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54066920280457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25359654426575</t>
+    <t xml:space="preserve">2.58979368209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54066896438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25359630584717</t>
   </si>
   <si>
     <t xml:space="preserve">2.24592089653015</t>
@@ -3626,7 +3626,7 @@
     <t xml:space="preserve">2.40557622909546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42860317230225</t>
+    <t xml:space="preserve">2.42860341072083</t>
   </si>
   <si>
     <t xml:space="preserve">2.52992296218872</t>
@@ -3638,28 +3638,28 @@
     <t xml:space="preserve">2.75098443031311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7248866558075</t>
+    <t xml:space="preserve">2.72488689422607</t>
   </si>
   <si>
     <t xml:space="preserve">2.76326560974121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78015184402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82927680015564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79550361633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79243326187134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73870348930359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79703903198242</t>
+    <t xml:space="preserve">2.78015208244324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82927703857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79550337791443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79243350028992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73870325088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79703879356384</t>
   </si>
   <si>
     <t xml:space="preserve">2.92292094230652</t>
@@ -3683,7 +3683,7 @@
     <t xml:space="preserve">2.80931997299194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7985737323761</t>
+    <t xml:space="preserve">2.79857397079468</t>
   </si>
   <si>
     <t xml:space="preserve">2.93366670608521</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">2.94594812393188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87226128578186</t>
+    <t xml:space="preserve">2.87226104736328</t>
   </si>
   <si>
     <t xml:space="preserve">2.93980741500854</t>
@@ -3701,25 +3701,25 @@
     <t xml:space="preserve">2.88607740402222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96590495109558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95208835601807</t>
+    <t xml:space="preserve">2.96590518951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95208859443665</t>
   </si>
   <si>
     <t xml:space="preserve">2.90603423118591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92752623558044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91678047180176</t>
+    <t xml:space="preserve">2.92752599716187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91678023338318</t>
   </si>
   <si>
     <t xml:space="preserve">2.90296387672424</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90756916999817</t>
+    <t xml:space="preserve">2.90756964683533</t>
   </si>
   <si>
     <t xml:space="preserve">2.7908980846405</t>
@@ -3734,10 +3734,10 @@
     <t xml:space="preserve">2.68343782424927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78168725967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80624961853027</t>
+    <t xml:space="preserve">2.78168702125549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80624938011169</t>
   </si>
   <si>
     <t xml:space="preserve">2.82467126846313</t>
@@ -3749,7 +3749,7 @@
     <t xml:space="preserve">2.88147187232971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86151504516602</t>
+    <t xml:space="preserve">2.86151480674744</t>
   </si>
   <si>
     <t xml:space="preserve">2.85230422019958</t>
@@ -3773,7 +3773,7 @@
     <t xml:space="preserve">3.1176609992981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07544279098511</t>
+    <t xml:space="preserve">3.07544302940369</t>
   </si>
   <si>
     <t xml:space="preserve">3.04946231842041</t>
@@ -3782,10 +3782,10 @@
     <t xml:space="preserve">3.01211524009705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99587774276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0380961894989</t>
+    <t xml:space="preserve">2.99587750434875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03809595108032</t>
   </si>
   <si>
     <t xml:space="preserve">3.03322458267212</t>
@@ -3794,13 +3794,13 @@
     <t xml:space="preserve">3.0088677406311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96664953231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76205277442932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63377404212952</t>
+    <t xml:space="preserve">2.96664929389954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7620530128479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6337742805481</t>
   </si>
   <si>
     <t xml:space="preserve">2.62565517425537</t>
@@ -3821,16 +3821,16 @@
     <t xml:space="preserve">2.78478598594666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77666735649109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69547772407532</t>
+    <t xml:space="preserve">2.77666711807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6954779624939</t>
   </si>
   <si>
     <t xml:space="preserve">2.73282480239868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69385409355164</t>
+    <t xml:space="preserve">2.69385433197021</t>
   </si>
   <si>
     <t xml:space="preserve">2.70034909248352</t>
@@ -3860,7 +3860,7 @@
     <t xml:space="preserve">2.76042938232422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71821093559265</t>
+    <t xml:space="preserve">2.71821069717407</t>
   </si>
   <si>
     <t xml:space="preserve">2.70359683036804</t>
@@ -3878,19 +3878,19 @@
     <t xml:space="preserve">2.57207036018372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69060635566711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61428904533386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57856559753418</t>
+    <t xml:space="preserve">2.69060659408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61428880691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57856583595276</t>
   </si>
   <si>
     <t xml:space="preserve">2.54608988761902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58343720436096</t>
+    <t xml:space="preserve">2.58343696594238</t>
   </si>
   <si>
     <t xml:space="preserve">2.51686191558838</t>
@@ -3902,16 +3902,16 @@
     <t xml:space="preserve">2.62727904319763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65975475311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72957754135132</t>
+    <t xml:space="preserve">2.65975451469421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72957730293274</t>
   </si>
   <si>
     <t xml:space="preserve">2.6694974899292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78153872489929</t>
+    <t xml:space="preserve">2.78153848648071</t>
   </si>
   <si>
     <t xml:space="preserve">2.73607230186462</t>
@@ -3932,7 +3932,7 @@
     <t xml:space="preserve">2.66624999046326</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60941767692566</t>
+    <t xml:space="preserve">2.60941743850708</t>
   </si>
   <si>
     <t xml:space="preserve">2.56395149230957</t>
@@ -3944,7 +3944,7 @@
     <t xml:space="preserve">2.59155583381653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59967470169067</t>
+    <t xml:space="preserve">2.59967494010925</t>
   </si>
   <si>
     <t xml:space="preserve">2.56070399284363</t>
@@ -3953,16 +3953,16 @@
     <t xml:space="preserve">2.59642720222473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59805107116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58830857276917</t>
+    <t xml:space="preserve">2.59805083274841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58830833435059</t>
   </si>
   <si>
     <t xml:space="preserve">2.7263298034668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82050895690918</t>
+    <t xml:space="preserve">2.82050919532776</t>
   </si>
   <si>
     <t xml:space="preserve">2.81726145744324</t>
@@ -3998,13 +3998,13 @@
     <t xml:space="preserve">2.64514064788818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75393390655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7669243812561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85460877418518</t>
+    <t xml:space="preserve">2.75393414497375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76692414283752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8546085357666</t>
   </si>
   <si>
     <t xml:space="preserve">2.7929048538208</t>
@@ -4031,16 +4031,16 @@
     <t xml:space="preserve">2.86435127258301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87734127044678</t>
+    <t xml:space="preserve">2.87734150886536</t>
   </si>
   <si>
     <t xml:space="preserve">2.9163122177124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95853090286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92443108558655</t>
+    <t xml:space="preserve">2.95853066444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92443132400513</t>
   </si>
   <si>
     <t xml:space="preserve">2.93904519081116</t>
@@ -4058,7 +4058,7 @@
     <t xml:space="preserve">3.02997708320618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04459095001221</t>
+    <t xml:space="preserve">3.04459118843079</t>
   </si>
   <si>
     <t xml:space="preserve">3.10467100143433</t>
@@ -4073,7 +4073,7 @@
     <t xml:space="preserve">2.89520311355591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88708400726318</t>
+    <t xml:space="preserve">2.88708424568176</t>
   </si>
   <si>
     <t xml:space="preserve">2.91793608665466</t>
@@ -4088,7 +4088,7 @@
     <t xml:space="preserve">3.1014232635498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10629463195801</t>
+    <t xml:space="preserve">3.10629487037659</t>
   </si>
   <si>
     <t xml:space="preserve">3.11441349983215</t>
@@ -4097,13 +4097,13 @@
     <t xml:space="preserve">3.15987944602966</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1274037361145</t>
+    <t xml:space="preserve">3.12740397453308</t>
   </si>
   <si>
     <t xml:space="preserve">3.16637468338013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14201807975769</t>
+    <t xml:space="preserve">3.14201784133911</t>
   </si>
   <si>
     <t xml:space="preserve">3.1209089756012</t>
@@ -4127,7 +4127,7 @@
     <t xml:space="preserve">3.06894779205322</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04134345054626</t>
+    <t xml:space="preserve">3.04134321212769</t>
   </si>
   <si>
     <t xml:space="preserve">3.11278986930847</t>
@@ -4145,7 +4145,7 @@
     <t xml:space="preserve">3.14039421081543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12415623664856</t>
+    <t xml:space="preserve">3.12415647506714</t>
   </si>
   <si>
     <t xml:space="preserve">3.17774128913879</t>
@@ -4163,7 +4163,7 @@
     <t xml:space="preserve">3.27679181098938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27029657363892</t>
+    <t xml:space="preserve">3.27029633522034</t>
   </si>
   <si>
     <t xml:space="preserve">3.3125147819519</t>
@@ -4205,13 +4205,13 @@
     <t xml:space="preserve">3.65838074684143</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73307466506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65675711631775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66487598419189</t>
+    <t xml:space="preserve">3.733074426651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65675687789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66487574577332</t>
   </si>
   <si>
     <t xml:space="preserve">3.7022225856781</t>
@@ -4229,10 +4229,10 @@
     <t xml:space="preserve">3.66325187683105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59505319595337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60804319381714</t>
+    <t xml:space="preserve">3.59505295753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60804295539856</t>
   </si>
   <si>
     <t xml:space="preserve">3.6453902721405</t>
@@ -4241,7 +4241,7 @@
     <t xml:space="preserve">3.59830069541931</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6437668800354</t>
+    <t xml:space="preserve">3.64376664161682</t>
   </si>
   <si>
     <t xml:space="preserve">3.61616230010986</t>
@@ -4253,10 +4253,10 @@
     <t xml:space="preserve">3.69572734832764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81101584434509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90032410621643</t>
+    <t xml:space="preserve">3.81101608276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90032386779785</t>
   </si>
   <si>
     <t xml:space="preserve">3.87921476364136</t>
@@ -4268,10 +4268,10 @@
     <t xml:space="preserve">3.89382863044739</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97177076339722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89220547676086</t>
+    <t xml:space="preserve">3.97177052497864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89220499992371</t>
   </si>
   <si>
     <t xml:space="preserve">3.91980957984924</t>
@@ -4286,10 +4286,10 @@
     <t xml:space="preserve">3.41643714904785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19885039329529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21021699905396</t>
+    <t xml:space="preserve">3.19885063171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21021676063538</t>
   </si>
   <si>
     <t xml:space="preserve">3.0949285030365</t>
@@ -4301,31 +4301,31 @@
     <t xml:space="preserve">3.28491067886353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21995973587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08843326568604</t>
+    <t xml:space="preserve">3.21995949745178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08843302726746</t>
   </si>
   <si>
     <t xml:space="preserve">3.09330439567566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0997998714447</t>
+    <t xml:space="preserve">3.09979963302612</t>
   </si>
   <si>
     <t xml:space="preserve">3.19560265541077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21184062957764</t>
+    <t xml:space="preserve">3.21184039115906</t>
   </si>
   <si>
     <t xml:space="preserve">3.1517608165741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27192091941833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28815865516663</t>
+    <t xml:space="preserve">3.27192068099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28815841674805</t>
   </si>
   <si>
     <t xml:space="preserve">3.31738615036011</t>
@@ -4343,13 +4343,13 @@
     <t xml:space="preserve">3.4342987537384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47326922416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47002220153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44241714477539</t>
+    <t xml:space="preserve">3.47326946258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47002196311951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44241738319397</t>
   </si>
   <si>
     <t xml:space="preserve">3.34661459922791</t>
@@ -4364,22 +4364,22 @@
     <t xml:space="preserve">3.38720893859863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4310507774353</t>
+    <t xml:space="preserve">3.43105101585388</t>
   </si>
   <si>
     <t xml:space="preserve">3.50736880302429</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36934733390808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38558506965637</t>
+    <t xml:space="preserve">3.36934757232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38558530807495</t>
   </si>
   <si>
     <t xml:space="preserve">3.38233757019043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38396143913269</t>
+    <t xml:space="preserve">3.38396167755127</t>
   </si>
   <si>
     <t xml:space="preserve">3.33499121665955</t>
@@ -5886,6 +5886,9 @@
   </si>
   <si>
     <t xml:space="preserve">12.9650001525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4650001525879</t>
   </si>
 </sst>
 </file>
@@ -70990,7 +70993,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6495486111</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>599034</v>
@@ -71011,6 +71014,32 @@
         <v>1957</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6494328704</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>841065</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>13.5600004196167</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>13.1599998474121</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>13.164999961853</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>13.4650001525879</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>1958</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BPSO.MI.xlsx
+++ b/data/BPSO.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1962" uniqueCount="1962">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1963" uniqueCount="1963">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82907128334045</t>
+    <t xml:space="preserve">2.82907176017761</t>
   </si>
   <si>
     <t xml:space="preserve">BPSO.MI</t>
@@ -50,10 +50,10 @@
     <t xml:space="preserve">2.74855804443359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7124662399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63611698150635</t>
+    <t xml:space="preserve">2.71246576309204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63611674308777</t>
   </si>
   <si>
     <t xml:space="preserve">2.60835385322571</t>
@@ -65,10 +65,10 @@
     <t xml:space="preserve">2.69858455657959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61113047599792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51257061958313</t>
+    <t xml:space="preserve">2.61113023757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51257085800171</t>
   </si>
   <si>
     <t xml:space="preserve">2.4556565284729</t>
@@ -77,40 +77,40 @@
     <t xml:space="preserve">2.26686644554138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38069534301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40568232536316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3654260635376</t>
+    <t xml:space="preserve">2.38069558143616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40568208694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36542558670044</t>
   </si>
   <si>
     <t xml:space="preserve">2.51951146125793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44455099105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35570883750916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43899869918823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40429401397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32100486755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22105765342712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23216223716736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20995235443115</t>
+    <t xml:space="preserve">2.44455122947693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.355708360672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43899893760681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40429425239563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32100510597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22105741500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23216247558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20995211601257</t>
   </si>
   <si>
     <t xml:space="preserve">2.04059600830078</t>
@@ -119,52 +119,52 @@
     <t xml:space="preserve">2.06280660629272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14331984519958</t>
+    <t xml:space="preserve">2.14332008361816</t>
   </si>
   <si>
     <t xml:space="preserve">2.07668805122375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18218803405762</t>
+    <t xml:space="preserve">2.1821882724762</t>
   </si>
   <si>
     <t xml:space="preserve">2.22522163391113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27797150611877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19329357147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16553020477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24604415893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18635249137878</t>
+    <t xml:space="preserve">2.2779712677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19329380989075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16553044319153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24604368209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18635272979736</t>
   </si>
   <si>
     <t xml:space="preserve">2.1766357421875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21550464630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.259925365448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31822896003723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3876359462738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38208341598511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3751425743103</t>
+    <t xml:space="preserve">2.21550488471985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25992560386658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31822872161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38763618469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38208365440369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37514281272888</t>
   </si>
   <si>
     <t xml:space="preserve">2.2418794631958</t>
@@ -176,25 +176,25 @@
     <t xml:space="preserve">2.25020837783813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31961679458618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43344473838806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35848546028137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30157017707825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34599208831787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35987329483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39318895339966</t>
+    <t xml:space="preserve">2.31961703300476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43344497680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35848498344421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30156993865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34599184989929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3598735332489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39318871498108</t>
   </si>
   <si>
     <t xml:space="preserve">2.29324126243591</t>
@@ -203,28 +203,28 @@
     <t xml:space="preserve">2.23771500587463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18774104118347</t>
+    <t xml:space="preserve">2.18774056434631</t>
   </si>
   <si>
     <t xml:space="preserve">2.139155626297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14748454093933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1211097240448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06974697113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01283311843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01838517189026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07113575935364</t>
+    <t xml:space="preserve">2.14748477935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12110996246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06974720954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01283288002014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01838564872742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07113552093506</t>
   </si>
   <si>
     <t xml:space="preserve">2.11694502830505</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">2.12527418136597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22799801826477</t>
+    <t xml:space="preserve">2.22799825668335</t>
   </si>
   <si>
     <t xml:space="preserve">2.30295848846436</t>
@@ -242,13 +242,13 @@
     <t xml:space="preserve">2.23910331726074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2904646396637</t>
+    <t xml:space="preserve">2.29046487808228</t>
   </si>
   <si>
     <t xml:space="preserve">2.3321099281311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32655787467957</t>
+    <t xml:space="preserve">2.32655763626099</t>
   </si>
   <si>
     <t xml:space="preserve">2.27935981750488</t>
@@ -263,40 +263,40 @@
     <t xml:space="preserve">2.26131367683411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.234938621521</t>
+    <t xml:space="preserve">2.23493885993958</t>
   </si>
   <si>
     <t xml:space="preserve">2.15720152854919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11139249801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08224058151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09889912605286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08918213844299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10583972930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04892468452454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03781962394714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06558275222778</t>
+    <t xml:space="preserve">2.11139225959778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08224081993103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09889936447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08918190002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10583996772766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04892492294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03781986236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06558299064636</t>
   </si>
   <si>
     <t xml:space="preserve">2.03226709365845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07252383232117</t>
+    <t xml:space="preserve">2.07252335548401</t>
   </si>
   <si>
     <t xml:space="preserve">2.05725407600403</t>
@@ -311,19 +311,19 @@
     <t xml:space="preserve">2.19942760467529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15393233299255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17525815963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15535402297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09279727935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07147097587585</t>
+    <t xml:space="preserve">2.15393209457397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17525839805603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15535378456116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09279680252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07147121429443</t>
   </si>
   <si>
     <t xml:space="preserve">1.99896240234375</t>
@@ -332,52 +332,52 @@
     <t xml:space="preserve">1.95773220062256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87669289112091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9890102148056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93640601634979</t>
+    <t xml:space="preserve">1.87669265270233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98901009559631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93640613555908</t>
   </si>
   <si>
     <t xml:space="preserve">1.94351482391357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84114956855774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78143715858459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.751580119133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72598910331726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64210617542267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69613254070282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77006232738495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81129324436188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78001439571381</t>
+    <t xml:space="preserve">1.84114968776703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78143727779388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75158023834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72598898410797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64210629463196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6961327791214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77006244659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81129312515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78001427650452</t>
   </si>
   <si>
     <t xml:space="preserve">1.89375364780426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63499772548676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5653327703476</t>
+    <t xml:space="preserve">1.63499760627747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56533288955688</t>
   </si>
   <si>
     <t xml:space="preserve">1.6691198348999</t>
@@ -386,46 +386,46 @@
     <t xml:space="preserve">1.65632367134094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6392627954483</t>
+    <t xml:space="preserve">1.63926255702972</t>
   </si>
   <si>
     <t xml:space="preserve">1.63641941547394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57670676708221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51130640506744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52552378177643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53121054172516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63784110546112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67196321487427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69471073150635</t>
+    <t xml:space="preserve">1.5767068862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51130664348602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52552390098572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53121078014374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63784074783325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67196333408356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69471085071564</t>
   </si>
   <si>
     <t xml:space="preserve">1.67054164409637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74304962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70892798900604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72172379493713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77574944496155</t>
+    <t xml:space="preserve">1.74304986000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70892822742462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72172367572784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77574968338013</t>
   </si>
   <si>
     <t xml:space="preserve">1.76721894741058</t>
@@ -434,52 +434,52 @@
     <t xml:space="preserve">1.72741055488586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69755423069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7245671749115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71888041496277</t>
+    <t xml:space="preserve">1.69755446910858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72456705570221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71888053417206</t>
   </si>
   <si>
     <t xml:space="preserve">1.6634327173233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55395889282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57528507709503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52125871181488</t>
+    <t xml:space="preserve">1.55395877361298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57528483867645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52125859260559</t>
   </si>
   <si>
     <t xml:space="preserve">1.63357591629028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6591671705246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64779305458069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68760216236115</t>
+    <t xml:space="preserve">1.65916693210602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64779317378998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68760228157043</t>
   </si>
   <si>
     <t xml:space="preserve">1.71461510658264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70608460903168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70039784908295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74447131156921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70750617980957</t>
+    <t xml:space="preserve">1.70608472824097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70039761066437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7444714307785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70750653743744</t>
   </si>
   <si>
     <t xml:space="preserve">1.72030210494995</t>
@@ -488,31 +488,31 @@
     <t xml:space="preserve">1.7316757440567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78285872936249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77859282493591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.771484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76437568664551</t>
+    <t xml:space="preserve">1.78285896778107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7785929441452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77148413658142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76437556743622</t>
   </si>
   <si>
     <t xml:space="preserve">1.75584518909454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76295387744904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74162793159485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76864099502563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74873685836792</t>
+    <t xml:space="preserve">1.76295363903046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74162781238556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76864075660706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74873650074005</t>
   </si>
   <si>
     <t xml:space="preserve">1.73451936244965</t>
@@ -521,85 +521,85 @@
     <t xml:space="preserve">1.78428041934967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85252356529236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84967982769012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81271529197693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8354629278183</t>
+    <t xml:space="preserve">1.85252332687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84967970848083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81271505355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83546268939972</t>
   </si>
   <si>
     <t xml:space="preserve">1.84825849533081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85963201522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94778025150299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9762145280838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09848403930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10843634605408</t>
+    <t xml:space="preserve">1.85963213443756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9477801322937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97621488571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09848380088806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1084361076355</t>
   </si>
   <si>
     <t xml:space="preserve">2.07573628425598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08568835258484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08853197097778</t>
+    <t xml:space="preserve">2.08568859100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0885317325592</t>
   </si>
   <si>
     <t xml:space="preserve">2.09706234931946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16104078292847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18236660957336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11412334442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00038409233093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03877139091492</t>
+    <t xml:space="preserve">2.16104102134705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18236684799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11412286758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00038433074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0387716293335</t>
   </si>
   <si>
     <t xml:space="preserve">2.00891423225403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05298852920532</t>
+    <t xml:space="preserve">2.0529887676239</t>
   </si>
   <si>
     <t xml:space="preserve">2.06294083595276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11554479598999</t>
+    <t xml:space="preserve">2.11554455757141</t>
   </si>
   <si>
     <t xml:space="preserve">2.12549686431885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16246271133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15961885452271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13260555267334</t>
+    <t xml:space="preserve">2.16246247291565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15961909294128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13260579109192</t>
   </si>
   <si>
     <t xml:space="preserve">2.08142328262329</t>
@@ -608,16 +608,16 @@
     <t xml:space="preserve">2.03592801094055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07715821266174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09990572929382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08995366096497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01033616065979</t>
+    <t xml:space="preserve">2.07715797424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09990549087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08995342254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01033568382263</t>
   </si>
   <si>
     <t xml:space="preserve">2.12407493591309</t>
@@ -629,34 +629,34 @@
     <t xml:space="preserve">2.07289290428162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16814947128296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27478003501892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37430167198181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26340627670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23354864120483</t>
+    <t xml:space="preserve">2.16814970970154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27477979660034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37430143356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2634060382843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23354887962341</t>
   </si>
   <si>
     <t xml:space="preserve">2.2719361782074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23212695121765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1781017780304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1695716381073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23639249801636</t>
+    <t xml:space="preserve">2.23212742805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17810130119324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16957139968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23639273643494</t>
   </si>
   <si>
     <t xml:space="preserve">2.22217512130737</t>
@@ -665,28 +665,28 @@
     <t xml:space="preserve">2.21791005134583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20511436462402</t>
+    <t xml:space="preserve">2.2051146030426</t>
   </si>
   <si>
     <t xml:space="preserve">2.22359681129456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26482796669006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31032299995422</t>
+    <t xml:space="preserve">2.26482748985291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31032276153564</t>
   </si>
   <si>
     <t xml:space="preserve">2.31743144989014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34302282333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34160113334656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30463576316833</t>
+    <t xml:space="preserve">2.34302306175232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34160089492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30463624000549</t>
   </si>
   <si>
     <t xml:space="preserve">2.29752731323242</t>
@@ -698,37 +698,37 @@
     <t xml:space="preserve">2.36008358001709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35297513008118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34017944335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40273642539978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41695380210876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45249652862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4112663269043</t>
+    <t xml:space="preserve">2.3529748916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34017968177795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4027361869812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41695332527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45249700546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41126680374146</t>
   </si>
   <si>
     <t xml:space="preserve">2.415531873703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42406225204468</t>
+    <t xml:space="preserve">2.4240620136261</t>
   </si>
   <si>
     <t xml:space="preserve">2.44396638870239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35439682006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33733606338501</t>
+    <t xml:space="preserve">2.3543963432312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33733582496643</t>
   </si>
   <si>
     <t xml:space="preserve">2.33022713661194</t>
@@ -737,64 +737,64 @@
     <t xml:space="preserve">2.36434864997864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32738375663757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28188848495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30037093162537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3231189250946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33449268341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30890154838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29894924163818</t>
+    <t xml:space="preserve">2.32738399505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28188824653625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30037117004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32311844825745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33449244499207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30890130996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2989490032196</t>
   </si>
   <si>
     <t xml:space="preserve">2.25629734992981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12834048271179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1340274810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2847318649292</t>
+    <t xml:space="preserve">2.12834024429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13402724266052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28473162651062</t>
   </si>
   <si>
     <t xml:space="preserve">2.22928404808044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27335810661316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27904462814331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31316661834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33875775337219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37856650352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32880568504333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36719226837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34870982170105</t>
+    <t xml:space="preserve">2.27335786819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27904510498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31316637992859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33875727653503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37856674194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32880544662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.367192029953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34870958328247</t>
   </si>
   <si>
     <t xml:space="preserve">2.29468417167664</t>
@@ -803,34 +803,34 @@
     <t xml:space="preserve">2.30321431159973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28757548332214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32027554512024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2833104133606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29041886329651</t>
+    <t xml:space="preserve">2.28757524490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32027530670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28331017494202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29041862487793</t>
   </si>
   <si>
     <t xml:space="preserve">2.29326248168945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30605816841125</t>
+    <t xml:space="preserve">2.30605792999268</t>
   </si>
   <si>
     <t xml:space="preserve">2.35581827163696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31174445152283</t>
+    <t xml:space="preserve">2.31174468994141</t>
   </si>
   <si>
     <t xml:space="preserve">2.33164882659912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46671390533447</t>
+    <t xml:space="preserve">2.46671414375305</t>
   </si>
   <si>
     <t xml:space="preserve">2.43117070198059</t>
@@ -839,13 +839,13 @@
     <t xml:space="preserve">2.42974925041199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49799299240112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46387052536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48661804199219</t>
+    <t xml:space="preserve">2.49799275398254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46387028694153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48661828041077</t>
   </si>
   <si>
     <t xml:space="preserve">2.51647520065308</t>
@@ -854,16 +854,16 @@
     <t xml:space="preserve">2.51789665222168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56907939910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53353571891785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48804020881653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50510144233704</t>
+    <t xml:space="preserve">2.56907916069031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53353595733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48803973197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50510120391846</t>
   </si>
   <si>
     <t xml:space="preserve">2.5079448223114</t>
@@ -872,13 +872,13 @@
     <t xml:space="preserve">2.50936651229858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50652313232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55486178398132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5722119808197</t>
+    <t xml:space="preserve">2.50652289390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5548620223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57221221923828</t>
   </si>
   <si>
     <t xml:space="preserve">2.63293862342834</t>
@@ -890,43 +890,43 @@
     <t xml:space="preserve">2.70667886734009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56642866134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52594351768494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52883529663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47389268875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52160620689392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5143768787384</t>
+    <t xml:space="preserve">2.56642889976501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52594375610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52883553504944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47389245033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5216064453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51437664031982</t>
   </si>
   <si>
     <t xml:space="preserve">2.47100067138672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48979687690735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47533845901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51726889610291</t>
+    <t xml:space="preserve">2.48979711532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47533798217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51726865768433</t>
   </si>
   <si>
     <t xml:space="preserve">2.45654249191284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47967624664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46087980270386</t>
+    <t xml:space="preserve">2.47967576980591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46088004112244</t>
   </si>
   <si>
     <t xml:space="preserve">2.48112177848816</t>
@@ -935,22 +935,22 @@
     <t xml:space="preserve">2.45798802375793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48256778717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48835110664368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48690509796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50859332084656</t>
+    <t xml:space="preserve">2.48256802558899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48835134506226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48690533638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50859355926514</t>
   </si>
   <si>
     <t xml:space="preserve">2.53751134872437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6025755405426</t>
+    <t xml:space="preserve">2.60257530212402</t>
   </si>
   <si>
     <t xml:space="preserve">2.55919933319092</t>
@@ -965,13 +965,13 @@
     <t xml:space="preserve">2.66330242156982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61414217948914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63149261474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62281775474548</t>
+    <t xml:space="preserve">2.61414241790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63149309158325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6228175163269</t>
   </si>
   <si>
     <t xml:space="preserve">2.61703419685364</t>
@@ -980,31 +980,31 @@
     <t xml:space="preserve">2.72692084312439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73704147338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72258281707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71246218681335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71390771865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70812439918518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68932819366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68643665313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68788266181946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71101641654968</t>
+    <t xml:space="preserve">2.73704195022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72258305549622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71246194839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71390795707703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7081241607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68932795524597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68643641471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6878821849823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7110161781311</t>
   </si>
   <si>
     <t xml:space="preserve">2.65028882026672</t>
@@ -1013,55 +1013,55 @@
     <t xml:space="preserve">2.67920732498169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67197799682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67053198814392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65318083763123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6517345905304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66763997077942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65896487236023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64595150947571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59823799133301</t>
+    <t xml:space="preserve">2.67197775840759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67053174972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65318059921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65173482894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.667640209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65896511077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64595127105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59823775291443</t>
   </si>
   <si>
     <t xml:space="preserve">2.62426352500916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60402154922485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5447404384613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5765495300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52449798583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48545932769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50280976295471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52016043663025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51148509979248</t>
+    <t xml:space="preserve">2.60402131080627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54474067687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57655000686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52449774742126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48545956611633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50281000137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52016019821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5114848613739</t>
   </si>
   <si>
     <t xml:space="preserve">2.518714427948</t>
@@ -1070,37 +1070,37 @@
     <t xml:space="preserve">2.53317332267761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55196976661682</t>
+    <t xml:space="preserve">2.55197024345398</t>
   </si>
   <si>
     <t xml:space="preserve">2.50714731216431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55052399635315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54618644714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53606534004211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5794415473938</t>
+    <t xml:space="preserve">2.55052423477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54618668556213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53606557846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57944178581238</t>
   </si>
   <si>
     <t xml:space="preserve">2.64161372184753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63004660606384</t>
+    <t xml:space="preserve">2.63004684448242</t>
   </si>
   <si>
     <t xml:space="preserve">2.58956241607666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52305221557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51582312583923</t>
+    <t xml:space="preserve">2.52305197715759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51582264900208</t>
   </si>
   <si>
     <t xml:space="preserve">2.49268889427185</t>
@@ -1112,46 +1112,46 @@
     <t xml:space="preserve">2.4912428855896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47244691848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50425553321838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48401355743408</t>
+    <t xml:space="preserve">2.47244668006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50425577163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4840133190155</t>
   </si>
   <si>
     <t xml:space="preserve">2.49413466453552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4984724521637</t>
+    <t xml:space="preserve">2.49847221374512</t>
   </si>
   <si>
     <t xml:space="preserve">2.47823023796082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51293087005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44931268692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40738201141357</t>
+    <t xml:space="preserve">2.51293110847473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44931292533875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.407381772995</t>
   </si>
   <si>
     <t xml:space="preserve">2.45509624481201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41027355194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29605031013489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2468900680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28159070014954</t>
+    <t xml:space="preserve">2.41027331352234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29605007171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24688982963562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28159117698669</t>
   </si>
   <si>
     <t xml:space="preserve">2.18471765518188</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">2.19773054122925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22086453437805</t>
+    <t xml:space="preserve">2.22086405754089</t>
   </si>
   <si>
     <t xml:space="preserve">2.26279449462891</t>
@@ -1169,40 +1169,40 @@
     <t xml:space="preserve">2.28448271751404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28592848777771</t>
+    <t xml:space="preserve">2.28592824935913</t>
   </si>
   <si>
     <t xml:space="preserve">2.32496738433838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34810137748718</t>
+    <t xml:space="preserve">2.34810161590576</t>
   </si>
   <si>
     <t xml:space="preserve">2.3784646987915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41461229324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34231781959534</t>
+    <t xml:space="preserve">2.41461181640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34231805801392</t>
   </si>
   <si>
     <t xml:space="preserve">2.35677647590637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35966849327087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34087181091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37701845169067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39292359352112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40015244483948</t>
+    <t xml:space="preserve">2.35966825485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34087204933167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37701869010925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39292335510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40015268325806</t>
   </si>
   <si>
     <t xml:space="preserve">2.4059362411499</t>
@@ -1211,31 +1211,31 @@
     <t xml:space="preserve">2.33653426170349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29315757751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20496010780334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2396605014801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23821473121643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23387694358826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18327236175537</t>
+    <t xml:space="preserve">2.29315733909607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20495986938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23966073989868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23821496963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23387742042542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18327188491821</t>
   </si>
   <si>
     <t xml:space="preserve">2.21797251701355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24544429779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20062232017517</t>
+    <t xml:space="preserve">2.24544405937195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20062208175659</t>
   </si>
   <si>
     <t xml:space="preserve">2.22664785385132</t>
@@ -1244,13 +1244,13 @@
     <t xml:space="preserve">2.28303694725037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31340050697327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31050896644592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38858580589294</t>
+    <t xml:space="preserve">2.31340074539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31050872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38858556747437</t>
   </si>
   <si>
     <t xml:space="preserve">2.38714003562927</t>
@@ -1262,25 +1262,25 @@
     <t xml:space="preserve">2.34520959854126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36545181274414</t>
+    <t xml:space="preserve">2.36545205116272</t>
   </si>
   <si>
     <t xml:space="preserve">2.39436912536621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40304398536682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40448999404907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32785964012146</t>
+    <t xml:space="preserve">2.40304446220398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40449023246765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32785940170288</t>
   </si>
   <si>
     <t xml:space="preserve">2.34954714775085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33364272117615</t>
+    <t xml:space="preserve">2.33364295959473</t>
   </si>
   <si>
     <t xml:space="preserve">2.31195449829102</t>
@@ -1289,10 +1289,10 @@
     <t xml:space="preserve">2.22953963279724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3148467540741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30327939987183</t>
+    <t xml:space="preserve">2.31484651565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30327963829041</t>
   </si>
   <si>
     <t xml:space="preserve">2.32062983512878</t>
@@ -1301,10 +1301,10 @@
     <t xml:space="preserve">2.30761742591858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37268137931824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42907047271729</t>
+    <t xml:space="preserve">2.37268114089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42907071113586</t>
   </si>
   <si>
     <t xml:space="preserve">2.36400604248047</t>
@@ -1319,28 +1319,28 @@
     <t xml:space="preserve">2.27725315093994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32930541038513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30617165565491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30038809776306</t>
+    <t xml:space="preserve">2.32930493354797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30617141723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3003876209259</t>
   </si>
   <si>
     <t xml:space="preserve">2.37412714958191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3307511806488</t>
+    <t xml:space="preserve">2.33075094223022</t>
   </si>
   <si>
     <t xml:space="preserve">2.32641339302063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39726066589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39870667457581</t>
+    <t xml:space="preserve">2.39726090431213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39870715141296</t>
   </si>
   <si>
     <t xml:space="preserve">2.38569402694702</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">2.60112977027893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71969151496887</t>
+    <t xml:space="preserve">2.71969127655029</t>
   </si>
   <si>
     <t xml:space="preserve">2.70957016944885</t>
@@ -1358,31 +1358,31 @@
     <t xml:space="preserve">2.75439214706421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77752661705017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84837436676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84114480018616</t>
+    <t xml:space="preserve">2.77752685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84837412834167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84114503860474</t>
   </si>
   <si>
     <t xml:space="preserve">2.83391571044922</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86861610412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90042591094971</t>
+    <t xml:space="preserve">2.86861634254456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90042614936829</t>
   </si>
   <si>
     <t xml:space="preserve">2.82957816123962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73125815391541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78620171546936</t>
+    <t xml:space="preserve">2.73125863075256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78620195388794</t>
   </si>
   <si>
     <t xml:space="preserve">2.75583791732788</t>
@@ -1391,16 +1391,16 @@
     <t xml:space="preserve">2.82524037361145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80644416809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83680748939514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74716305732727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73848748207092</t>
+    <t xml:space="preserve">2.80644392967224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83680725097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74716281890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7384877204895</t>
   </si>
   <si>
     <t xml:space="preserve">2.63438439369202</t>
@@ -1409,40 +1409,40 @@
     <t xml:space="preserve">2.66091990470886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65060067176819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71251702308655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7036714553833</t>
+    <t xml:space="preserve">2.65060091018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71251726150513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70367121696472</t>
   </si>
   <si>
     <t xml:space="preserve">2.63143610954285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52824211120605</t>
+    <t xml:space="preserve">2.52824258804321</t>
   </si>
   <si>
     <t xml:space="preserve">2.48254251480103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52234578132629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56509709358215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61079740524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57689046859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51939749717712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59163331985474</t>
+    <t xml:space="preserve">2.52234554290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56509733200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6107976436615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57689070701599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51939725875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59163308143616</t>
   </si>
   <si>
     <t xml:space="preserve">2.618168592453</t>
@@ -1457,7 +1457,7 @@
     <t xml:space="preserve">2.56067442893982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55625176429749</t>
+    <t xml:space="preserve">2.55625200271606</t>
   </si>
   <si>
     <t xml:space="preserve">2.54593253135681</t>
@@ -1466,7 +1466,7 @@
     <t xml:space="preserve">2.57099390029907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51350069046021</t>
+    <t xml:space="preserve">2.51350045204163</t>
   </si>
   <si>
     <t xml:space="preserve">2.51055216789246</t>
@@ -1478,22 +1478,22 @@
     <t xml:space="preserve">2.54151010513306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65354895591736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6594455242157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70514559745789</t>
+    <t xml:space="preserve">2.65354871749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65944576263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70514512062073</t>
   </si>
   <si>
     <t xml:space="preserve">2.6904034614563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65797185897827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61964249610901</t>
+    <t xml:space="preserve">2.65797162055969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61964273452759</t>
   </si>
   <si>
     <t xml:space="preserve">2.63291049003601</t>
@@ -1502,34 +1502,34 @@
     <t xml:space="preserve">2.64912629127502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64322972297668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66534233093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64470386505127</t>
+    <t xml:space="preserve">2.64322948455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6653425693512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64470338821411</t>
   </si>
   <si>
     <t xml:space="preserve">2.63880705833435</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66386842727661</t>
+    <t xml:space="preserve">2.66386818885803</t>
   </si>
   <si>
     <t xml:space="preserve">2.71399140357971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73168158531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71693968772888</t>
+    <t xml:space="preserve">2.73168134689331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71693992614746</t>
   </si>
   <si>
     <t xml:space="preserve">2.73315572738647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78180384635925</t>
+    <t xml:space="preserve">2.78180408477783</t>
   </si>
   <si>
     <t xml:space="preserve">2.70661973953247</t>
@@ -1550,13 +1550,13 @@
     <t xml:space="preserve">2.64175534248352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57541656494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61374568939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60932350158691</t>
+    <t xml:space="preserve">2.57541632652283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61374592781067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60932326316833</t>
   </si>
   <si>
     <t xml:space="preserve">2.58868479728699</t>
@@ -1571,10 +1571,10 @@
     <t xml:space="preserve">2.48843955993652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47222352027893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50170683860779</t>
+    <t xml:space="preserve">2.47222328186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50170707702637</t>
   </si>
   <si>
     <t xml:space="preserve">2.56362271308899</t>
@@ -1583,19 +1583,19 @@
     <t xml:space="preserve">2.67123913764954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67418742179871</t>
+    <t xml:space="preserve">2.67418766021729</t>
   </si>
   <si>
     <t xml:space="preserve">2.65502309799194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68450689315796</t>
+    <t xml:space="preserve">2.68450713157654</t>
   </si>
   <si>
     <t xml:space="preserve">2.66239380836487</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62406516075134</t>
+    <t xml:space="preserve">2.6240656375885</t>
   </si>
   <si>
     <t xml:space="preserve">2.62996196746826</t>
@@ -1604,16 +1604,16 @@
     <t xml:space="preserve">2.63733291625977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62111663818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42210030555725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4191517829895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36608147621155</t>
+    <t xml:space="preserve">2.62111711502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42210006713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41915202140808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36608123779297</t>
   </si>
   <si>
     <t xml:space="preserve">2.38966822624207</t>
@@ -1622,31 +1622,31 @@
     <t xml:space="preserve">2.41325521469116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33659672737122</t>
+    <t xml:space="preserve">2.33659696578979</t>
   </si>
   <si>
     <t xml:space="preserve">2.24667167663574</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23045563697815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22898125648499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16706490516663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18033218383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15674591064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20244526863098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19360041618347</t>
+    <t xml:space="preserve">2.23045539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22898149490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16706466674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18033266067505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15674567222595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2024450302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19360017776489</t>
   </si>
   <si>
     <t xml:space="preserve">2.13905549049377</t>
@@ -1655,10 +1655,10 @@
     <t xml:space="preserve">2.11399412155151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08745837211609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04175853729248</t>
+    <t xml:space="preserve">2.08745813369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04175806045532</t>
   </si>
   <si>
     <t xml:space="preserve">2.00932621955872</t>
@@ -1679,19 +1679,19 @@
     <t xml:space="preserve">2.09335565567017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1361072063446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11694240570068</t>
+    <t xml:space="preserve">2.13610696792603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11694288253784</t>
   </si>
   <si>
     <t xml:space="preserve">2.09925246238708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10220074653625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10072636604309</t>
+    <t xml:space="preserve">2.10220050811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10072660446167</t>
   </si>
   <si>
     <t xml:space="preserve">2.09040665626526</t>
@@ -1700,22 +1700,22 @@
     <t xml:space="preserve">2.04912924766541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06829380989075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05060338973999</t>
+    <t xml:space="preserve">2.06829357147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05060291290283</t>
   </si>
   <si>
     <t xml:space="preserve">2.04765510559082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02701663970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01964545249939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97394585609436</t>
+    <t xml:space="preserve">2.02701687812805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01964569091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97394597530365</t>
   </si>
   <si>
     <t xml:space="preserve">1.97984254360199</t>
@@ -1724,7 +1724,7 @@
     <t xml:space="preserve">1.96215164661407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98426532745361</t>
+    <t xml:space="preserve">1.98426508903503</t>
   </si>
   <si>
     <t xml:space="preserve">2.08008742332458</t>
@@ -1736,16 +1736,16 @@
     <t xml:space="preserve">2.07861280441284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04618072509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08598399162292</t>
+    <t xml:space="preserve">2.04618096351624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0859842300415</t>
   </si>
   <si>
     <t xml:space="preserve">2.05650043487549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95625483989716</t>
+    <t xml:space="preserve">1.95625495910645</t>
   </si>
   <si>
     <t xml:space="preserve">1.98279082775116</t>
@@ -1754,64 +1754,64 @@
     <t xml:space="preserve">1.94446122646332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93709027767181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96657431125641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96804869174957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89286506175995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98131704330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91497766971588</t>
+    <t xml:space="preserve">1.93709051609039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96657419204712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96804857254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89286482334137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98131692409515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91497755050659</t>
   </si>
   <si>
     <t xml:space="preserve">1.8751745223999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87370038032532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94003903865814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92677104473114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9931104183197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0034294128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99458420276642</t>
+    <t xml:space="preserve">1.87370073795319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94003891944885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92677128314972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99311053752899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00342965126038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99458456039429</t>
   </si>
   <si>
     <t xml:space="preserve">1.99163615703583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94888365268707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8884425163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87222623825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91940033435822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89433944225311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86485540866852</t>
+    <t xml:space="preserve">1.94888377189636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88844227790833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8722265958786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91940009593964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89433908462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86485517024994</t>
   </si>
   <si>
     <t xml:space="preserve">1.85306179523468</t>
@@ -1829,10 +1829,10 @@
     <t xml:space="preserve">1.8250515460968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78230023384094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71596133708954</t>
+    <t xml:space="preserve">1.78230047225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71596121788025</t>
   </si>
   <si>
     <t xml:space="preserve">1.69532251358032</t>
@@ -1850,64 +1850,64 @@
     <t xml:space="preserve">1.76313579082489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76166164875031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78672289848328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80588734149933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83389663696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87664890289307</t>
+    <t xml:space="preserve">1.76166188716888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78672301769257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80588710308075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83389675617218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87664914131165</t>
   </si>
   <si>
     <t xml:space="preserve">1.86927819252014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84569001197815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83979344367981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83242237567902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84274172782898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83684492111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8972874879837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88991665840149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88254570960999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91055524349213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87075209617615</t>
+    <t xml:space="preserve">1.84569013118744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83979368209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8324226140976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84274184703827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83684527873993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89728736877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8899165391922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8825455904007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91055500507355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87075185775757</t>
   </si>
   <si>
     <t xml:space="preserve">1.80293905735016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80441319942474</t>
+    <t xml:space="preserve">1.80441308021545</t>
   </si>
   <si>
     <t xml:space="preserve">1.79114532470703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75576508045197</t>
+    <t xml:space="preserve">1.75576496124268</t>
   </si>
   <si>
     <t xml:space="preserve">1.81325840950012</t>
@@ -1916,82 +1916,82 @@
     <t xml:space="preserve">1.81178390979767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83537077903748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79556810855865</t>
+    <t xml:space="preserve">1.83537113666534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79556798934937</t>
   </si>
   <si>
     <t xml:space="preserve">1.77492940425873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80883574485779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79851639270782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79704201221466</t>
+    <t xml:space="preserve">1.8088356256485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79851627349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79704177379608</t>
   </si>
   <si>
     <t xml:space="preserve">1.8073616027832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78082621097565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7542906999588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71301281452179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70711624622345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74544560909271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76460993289948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7719806432724</t>
+    <t xml:space="preserve">1.78082633018494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75429081916809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7130126953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70711600780487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.745445728302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76461005210876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77198100090027</t>
   </si>
   <si>
     <t xml:space="preserve">1.7778776884079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78819704055786</t>
+    <t xml:space="preserve">1.78819692134857</t>
   </si>
   <si>
     <t xml:space="preserve">1.74839389324188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6658388376236</t>
+    <t xml:space="preserve">1.66583895683289</t>
   </si>
   <si>
     <t xml:space="preserve">1.67910647392273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61129403114319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57886135578156</t>
+    <t xml:space="preserve">1.61129415035248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57886123657227</t>
   </si>
   <si>
     <t xml:space="preserve">1.53610992431641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55822253227234</t>
+    <t xml:space="preserve">1.55822241306305</t>
   </si>
   <si>
     <t xml:space="preserve">1.54200661182404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53445518016815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53596544265747</t>
+    <t xml:space="preserve">1.53445529937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53596556186676</t>
   </si>
   <si>
     <t xml:space="preserve">1.56466102600098</t>
@@ -2000,7 +2000,7 @@
     <t xml:space="preserve">1.54351711273193</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55559921264648</t>
+    <t xml:space="preserve">1.55559909343719</t>
   </si>
   <si>
     <t xml:space="preserve">1.5389860868454</t>
@@ -2012,34 +2012,34 @@
     <t xml:space="preserve">1.60543859004974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58429443836212</t>
+    <t xml:space="preserve">1.58429455757141</t>
   </si>
   <si>
     <t xml:space="preserve">1.56768143177032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56919169425964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58882534503937</t>
+    <t xml:space="preserve">1.56919157505035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58882522583008</t>
   </si>
   <si>
     <t xml:space="preserve">1.51028990745544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51935231685638</t>
+    <t xml:space="preserve">1.51935243606567</t>
   </si>
   <si>
     <t xml:space="preserve">1.52690374851227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47177791595459</t>
+    <t xml:space="preserve">1.4717777967453</t>
   </si>
   <si>
     <t xml:space="preserve">1.47026753425598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.471022605896</t>
+    <t xml:space="preserve">1.47102272510529</t>
   </si>
   <si>
     <t xml:space="preserve">1.45138907432556</t>
@@ -2051,31 +2051,31 @@
     <t xml:space="preserve">1.49367678165436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48386001586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50047302246094</t>
+    <t xml:space="preserve">1.48385989665985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50047326087952</t>
   </si>
   <si>
     <t xml:space="preserve">1.45894038677216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46800208091736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48990106582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48234987258911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4808394908905</t>
+    <t xml:space="preserve">1.46800196170807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48990118503571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48234963417053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48083961009979</t>
   </si>
   <si>
     <t xml:space="preserve">1.53294491767883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57523286342621</t>
+    <t xml:space="preserve">1.57523274421692</t>
   </si>
   <si>
     <t xml:space="preserve">1.56315052509308</t>
@@ -2084,10 +2084,10 @@
     <t xml:space="preserve">1.52539348602295</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50424873828888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47328805923462</t>
+    <t xml:space="preserve">1.50424885749817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47328817844391</t>
   </si>
   <si>
     <t xml:space="preserve">1.4725329875946</t>
@@ -2096,16 +2096,16 @@
     <t xml:space="preserve">1.44912350177765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4536544084549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46649181842804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44987869262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44610285758972</t>
+    <t xml:space="preserve">1.45365452766418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46649169921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44987881183624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44610297679901</t>
   </si>
   <si>
     <t xml:space="preserve">1.43779647350311</t>
@@ -2123,19 +2123,19 @@
     <t xml:space="preserve">1.41665244102478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40683555603027</t>
+    <t xml:space="preserve">1.40683567523956</t>
   </si>
   <si>
     <t xml:space="preserve">1.400794506073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39097762107849</t>
+    <t xml:space="preserve">1.39097774028778</t>
   </si>
   <si>
     <t xml:space="preserve">1.3864461183548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28374707698822</t>
+    <t xml:space="preserve">1.28374695777893</t>
   </si>
   <si>
     <t xml:space="preserve">1.25354063510895</t>
@@ -2144,25 +2144,25 @@
     <t xml:space="preserve">1.25127518177032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20068061351776</t>
+    <t xml:space="preserve">1.20068073272705</t>
   </si>
   <si>
     <t xml:space="preserve">1.23617243766785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25278532505035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2218245267868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2308863401413</t>
+    <t xml:space="preserve">1.25278544425964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22182464599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23088645935059</t>
   </si>
   <si>
     <t xml:space="preserve">1.27695071697235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26637876033783</t>
+    <t xml:space="preserve">1.26637864112854</t>
   </si>
   <si>
     <t xml:space="preserve">1.27619564533234</t>
@@ -2174,10 +2174,10 @@
     <t xml:space="preserve">1.27090954780579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2822368144989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28752279281616</t>
+    <t xml:space="preserve">1.28223669528961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28752267360687</t>
   </si>
   <si>
     <t xml:space="preserve">1.35775077342987</t>
@@ -2189,31 +2189,31 @@
     <t xml:space="preserve">1.37436378002167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35246479511261</t>
+    <t xml:space="preserve">1.35246467590332</t>
   </si>
   <si>
     <t xml:space="preserve">1.40985631942749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39852929115295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36681234836578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.350954413414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35926103591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36454701423645</t>
+    <t xml:space="preserve">1.39852917194366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36681246757507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35095453262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35926115512848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36454713344574</t>
   </si>
   <si>
     <t xml:space="preserve">1.33736193180084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30262541770935</t>
+    <t xml:space="preserve">1.30262553691864</t>
   </si>
   <si>
     <t xml:space="preserve">1.2897881269455</t>
@@ -2225,7 +2225,7 @@
     <t xml:space="preserve">1.26864409446716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25505089759827</t>
+    <t xml:space="preserve">1.25505077838898</t>
   </si>
   <si>
     <t xml:space="preserve">1.27468526363373</t>
@@ -2255,10 +2255,10 @@
     <t xml:space="preserve">1.36077129840851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38871240615845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38267040252686</t>
+    <t xml:space="preserve">1.38871228694916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38267028331757</t>
   </si>
   <si>
     <t xml:space="preserve">1.3517097234726</t>
@@ -2267,7 +2267,7 @@
     <t xml:space="preserve">1.35699558258057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36152637004852</t>
+    <t xml:space="preserve">1.36152648925781</t>
   </si>
   <si>
     <t xml:space="preserve">1.36228168010712</t>
@@ -2288,22 +2288,22 @@
     <t xml:space="preserve">1.43326556682587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40532541275024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43477582931519</t>
+    <t xml:space="preserve">1.40532553195953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43477594852448</t>
   </si>
   <si>
     <t xml:space="preserve">1.62960302829742</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58278429508209</t>
+    <t xml:space="preserve">1.5827841758728</t>
   </si>
   <si>
     <t xml:space="preserve">1.57825350761414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58127391338348</t>
+    <t xml:space="preserve">1.58127403259277</t>
   </si>
   <si>
     <t xml:space="preserve">1.54653751850128</t>
@@ -2318,28 +2318,28 @@
     <t xml:space="preserve">1.55257856845856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60241794586182</t>
+    <t xml:space="preserve">1.60241782665253</t>
   </si>
   <si>
     <t xml:space="preserve">1.63111317157745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60090756416321</t>
+    <t xml:space="preserve">1.6009076833725</t>
   </si>
   <si>
     <t xml:space="preserve">1.62054145336151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54955792427063</t>
+    <t xml:space="preserve">1.54955804347992</t>
   </si>
   <si>
     <t xml:space="preserve">1.57221233844757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61147952079773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.641685962677</t>
+    <t xml:space="preserve">1.61147964000702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64168584346771</t>
   </si>
   <si>
     <t xml:space="preserve">1.61298990249634</t>
@@ -2354,10 +2354,10 @@
     <t xml:space="preserve">1.58731508255005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61903119087219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57976365089417</t>
+    <t xml:space="preserve">1.6190310716629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57976377010345</t>
   </si>
   <si>
     <t xml:space="preserve">1.56013000011444</t>
@@ -2369,10 +2369,10 @@
     <t xml:space="preserve">1.59788703918457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60392820835114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58580470085144</t>
+    <t xml:space="preserve">1.60392808914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58580482006073</t>
   </si>
   <si>
     <t xml:space="preserve">1.59939742088318</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">1.59637665748596</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5903354883194</t>
+    <t xml:space="preserve">1.59033560752869</t>
   </si>
   <si>
     <t xml:space="preserve">1.52992451190948</t>
@@ -2393,7 +2393,7 @@
     <t xml:space="preserve">1.50953495502472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52388322353363</t>
+    <t xml:space="preserve">1.52388334274292</t>
   </si>
   <si>
     <t xml:space="preserve">1.54049634933472</t>
@@ -2402,7 +2402,7 @@
     <t xml:space="preserve">1.63866460323334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75948798656464</t>
+    <t xml:space="preserve">1.75948810577393</t>
   </si>
   <si>
     <t xml:space="preserve">1.80630731582642</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">1.78365325927734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83953368663788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02983093261719</t>
+    <t xml:space="preserve">1.83953380584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02983069419861</t>
   </si>
   <si>
     <t xml:space="preserve">2.06909799575806</t>
@@ -2432,22 +2432,22 @@
     <t xml:space="preserve">1.77308118343353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81687963008881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70813846588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48008441925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37511897087097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32452464103699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2407032251358</t>
+    <t xml:space="preserve">1.81687951087952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70813834667206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4800843000412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37511909008026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3245245218277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24070310592651</t>
   </si>
   <si>
     <t xml:space="preserve">1.19917047023773</t>
@@ -2456,13 +2456,13 @@
     <t xml:space="preserve">1.18406772613525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.959789276123047</t>
+    <t xml:space="preserve">0.959789395332336</t>
   </si>
   <si>
     <t xml:space="preserve">0.995280861854553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.91901171207428</t>
+    <t xml:space="preserve">0.919011652469635</t>
   </si>
   <si>
     <t xml:space="preserve">0.945441544055939</t>
@@ -2471,34 +2471,34 @@
     <t xml:space="preserve">0.962809801101685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01869118213654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04361057281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990750253200531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07155096530914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07910239696503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0677752494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01944613456726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999811768531799</t>
+    <t xml:space="preserve">1.01869094371796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04361069202423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990750193595886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07155084609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07910227775574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06777513027191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01944601535797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999811708927155</t>
   </si>
   <si>
     <t xml:space="preserve">1.0413453578949</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02699744701385</t>
+    <t xml:space="preserve">1.02699756622314</t>
   </si>
   <si>
     <t xml:space="preserve">1.10628747940063</t>
@@ -2507,7 +2507,7 @@
     <t xml:space="preserve">1.05720329284668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11459398269653</t>
+    <t xml:space="preserve">1.11459386348724</t>
   </si>
   <si>
     <t xml:space="preserve">1.13875913619995</t>
@@ -2525,16 +2525,16 @@
     <t xml:space="preserve">1.08740890026093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0670200586319</t>
+    <t xml:space="preserve">1.06701993942261</t>
   </si>
   <si>
     <t xml:space="preserve">1.09420502185822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06324434280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09496033191681</t>
+    <t xml:space="preserve">1.06324422359467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09496021270752</t>
   </si>
   <si>
     <t xml:space="preserve">1.07834708690643</t>
@@ -2546,49 +2546,49 @@
     <t xml:space="preserve">1.07457149028778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08665359020233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09269487857819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03756952285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07306122779846</t>
+    <t xml:space="preserve">1.08665382862091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0926947593689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03756964206696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07306134700775</t>
   </si>
   <si>
     <t xml:space="preserve">1.04965174198151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03530418872833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04436576366425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04285550117493</t>
+    <t xml:space="preserve">1.03530406951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04436588287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04285562038422</t>
   </si>
   <si>
     <t xml:space="preserve">1.01189470291138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.985464155673981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970361292362213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989239811897278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94317615032196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926563084125519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921277105808258</t>
+    <t xml:space="preserve">0.985464096069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970361232757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989239871501923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94317626953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926563143730164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921277046203613</t>
   </si>
   <si>
     <t xml:space="preserve">0.913725674152374</t>
@@ -2603,13 +2603,13 @@
     <t xml:space="preserve">1.058713555336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09722566604614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1025116443634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13422763347626</t>
+    <t xml:space="preserve">1.09722554683685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10251152515411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13422775268555</t>
   </si>
   <si>
     <t xml:space="preserve">1.18180227279663</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">1.21502840518951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23919284343719</t>
+    <t xml:space="preserve">1.23919296264648</t>
   </si>
   <si>
     <t xml:space="preserve">1.19992554187775</t>
@@ -2627,10 +2627,10 @@
     <t xml:space="preserve">1.18935358524323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14782094955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16820967197418</t>
+    <t xml:space="preserve">1.14782071113586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16820979118347</t>
   </si>
   <si>
     <t xml:space="preserve">1.18708825111389</t>
@@ -2639,10 +2639,10 @@
     <t xml:space="preserve">1.16216850280762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19312942028046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17047512531281</t>
+    <t xml:space="preserve">1.19312930107117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17047524452209</t>
   </si>
   <si>
     <t xml:space="preserve">1.24598920345306</t>
@@ -2666,31 +2666,31 @@
     <t xml:space="preserve">1.39928424358368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40154957771301</t>
+    <t xml:space="preserve">1.4015496969223</t>
   </si>
   <si>
     <t xml:space="preserve">1.40305995941162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41589748859406</t>
+    <t xml:space="preserve">1.41589736938477</t>
   </si>
   <si>
     <t xml:space="preserve">1.49292171001434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44836843013763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48763585090637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47630870342255</t>
+    <t xml:space="preserve">1.44836854934692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48763573169708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47630858421326</t>
   </si>
   <si>
     <t xml:space="preserve">1.46498155593872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39626371860504</t>
+    <t xml:space="preserve">1.39626383781433</t>
   </si>
   <si>
     <t xml:space="preserve">1.37662935256958</t>
@@ -2699,10 +2699,10 @@
     <t xml:space="preserve">1.34264802932739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3690779209137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43175542354584</t>
+    <t xml:space="preserve">1.36907780170441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43175530433655</t>
   </si>
   <si>
     <t xml:space="preserve">1.445347905159</t>
@@ -2711,13 +2711,13 @@
     <t xml:space="preserve">1.47479832172394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48461520671844</t>
+    <t xml:space="preserve">1.48461532592773</t>
   </si>
   <si>
     <t xml:space="preserve">1.55106842517853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5208625793457</t>
+    <t xml:space="preserve">1.52086281776428</t>
   </si>
   <si>
     <t xml:space="preserve">1.37889468669891</t>
@@ -2732,7 +2732,7 @@
     <t xml:space="preserve">1.37209856510162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39475345611572</t>
+    <t xml:space="preserve">1.39475333690643</t>
   </si>
   <si>
     <t xml:space="preserve">1.37964999675751</t>
@@ -2741,19 +2741,19 @@
     <t xml:space="preserve">1.38795721530914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39248812198639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32150411605835</t>
+    <t xml:space="preserve">1.3924880027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32150399684906</t>
   </si>
   <si>
     <t xml:space="preserve">1.31848347187042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34340298175812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30035996437073</t>
+    <t xml:space="preserve">1.34340310096741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30036008358002</t>
   </si>
   <si>
     <t xml:space="preserve">1.32376933097839</t>
@@ -2762,7 +2762,7 @@
     <t xml:space="preserve">1.33434152603149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39777410030365</t>
+    <t xml:space="preserve">1.39777398109436</t>
   </si>
   <si>
     <t xml:space="preserve">1.36983299255371</t>
@@ -2777,49 +2777,49 @@
     <t xml:space="preserve">1.35473012924194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31772828102112</t>
+    <t xml:space="preserve">1.31772840023041</t>
   </si>
   <si>
     <t xml:space="preserve">1.33207595348358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33585178852081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27393007278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26486849784851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22484529018402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24145829677582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11761450767517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10779774188995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13800394535065</t>
+    <t xml:space="preserve">1.33585166931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27393019199371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26486837863922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22484505176544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24145817756653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11761462688446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10779762268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13800406455994</t>
   </si>
   <si>
     <t xml:space="preserve">1.22711050510406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24221348762512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23843765258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22862088680267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44232726097107</t>
+    <t xml:space="preserve">1.24221336841583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2384375333786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22862100601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44232738018036</t>
   </si>
   <si>
     <t xml:space="preserve">1.43251049518585</t>
@@ -2834,7 +2834,7 @@
     <t xml:space="preserve">1.81234848499298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78214299678802</t>
+    <t xml:space="preserve">1.78214287757874</t>
   </si>
   <si>
     <t xml:space="preserve">1.77459144592285</t>
@@ -2843,7 +2843,7 @@
     <t xml:space="preserve">1.75797760486603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69303572177887</t>
+    <t xml:space="preserve">1.69303560256958</t>
   </si>
   <si>
     <t xml:space="preserve">1.7217310667038</t>
@@ -2864,28 +2864,28 @@
     <t xml:space="preserve">1.72777223587036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69907665252686</t>
+    <t xml:space="preserve">1.69907653331757</t>
   </si>
   <si>
     <t xml:space="preserve">1.66887104511261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66282987594604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67944288253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66131961345673</t>
+    <t xml:space="preserve">1.66282999515533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67944300174713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66131949424744</t>
   </si>
   <si>
     <t xml:space="preserve">1.6764223575592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64470648765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61601054668427</t>
+    <t xml:space="preserve">1.64470636844635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61601042747498</t>
   </si>
   <si>
     <t xml:space="preserve">1.63564419746399</t>
@@ -2897,16 +2897,16 @@
     <t xml:space="preserve">1.66585063934326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66434001922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74438512325287</t>
+    <t xml:space="preserve">1.66434013843536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74438524246216</t>
   </si>
   <si>
     <t xml:space="preserve">1.77761209011078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75646758079529</t>
+    <t xml:space="preserve">1.756467461586</t>
   </si>
   <si>
     <t xml:space="preserve">1.7202205657959</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">1.67491221427917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65376818180084</t>
+    <t xml:space="preserve">1.65376830101013</t>
   </si>
   <si>
     <t xml:space="preserve">1.63715434074402</t>
@@ -2933,7 +2933,7 @@
     <t xml:space="preserve">1.57070195674896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59486639499664</t>
+    <t xml:space="preserve">1.59486651420593</t>
   </si>
   <si>
     <t xml:space="preserve">1.62205147743225</t>
@@ -2942,49 +2942,49 @@
     <t xml:space="preserve">1.7474057674408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88635230064392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85765731334686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88031125068665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86822915077209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85463654994965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88937294483185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8501056432724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80932807922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83047211170197</t>
+    <t xml:space="preserve">1.8863525390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85765719413757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88031136989594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86822879314423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85463666915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88937318325043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85010552406311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80932796001434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83047199249268</t>
   </si>
   <si>
     <t xml:space="preserve">1.82141017913818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81838965415955</t>
+    <t xml:space="preserve">1.81838977336884</t>
   </si>
   <si>
     <t xml:space="preserve">1.82594120502472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80781757831573</t>
+    <t xml:space="preserve">1.80781769752502</t>
   </si>
   <si>
     <t xml:space="preserve">1.80177640914917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84557497501373</t>
+    <t xml:space="preserve">1.84557473659515</t>
   </si>
   <si>
     <t xml:space="preserve">1.83500266075134</t>
@@ -2993,28 +2993,28 @@
     <t xml:space="preserve">1.82745134830475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87124967575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86369824409485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.927130818367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9799907207489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05399489402771</t>
+    <t xml:space="preserve">1.87124943733215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86369800567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92713069915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97999060153961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05399513244629</t>
   </si>
   <si>
     <t xml:space="preserve">2.13706088066101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18085956573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15216398239136</t>
+    <t xml:space="preserve">2.18085932731628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15216422080994</t>
   </si>
   <si>
     <t xml:space="preserve">2.12950897216797</t>
@@ -3026,31 +3026,31 @@
     <t xml:space="preserve">2.15518450737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1355504989624</t>
+    <t xml:space="preserve">2.13555026054382</t>
   </si>
   <si>
     <t xml:space="preserve">2.13857102394104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22465777397156</t>
+    <t xml:space="preserve">2.22465753555298</t>
   </si>
   <si>
     <t xml:space="preserve">2.15669512748718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18992114067078</t>
+    <t xml:space="preserve">2.1899209022522</t>
   </si>
   <si>
     <t xml:space="preserve">2.18690061569214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16877722740173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17028760910034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2352294921875</t>
+    <t xml:space="preserve">2.16877746582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17028784751892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23522996902466</t>
   </si>
   <si>
     <t xml:space="preserve">2.24731206893921</t>
@@ -3059,13 +3059,13 @@
     <t xml:space="preserve">2.2699670791626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30168318748474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23673987388611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24580144882202</t>
+    <t xml:space="preserve">2.30168294906616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23674011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2458016872406</t>
   </si>
   <si>
     <t xml:space="preserve">2.24882221221924</t>
@@ -3074,22 +3074,22 @@
     <t xml:space="preserve">2.36964559555054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39985179901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48140716552734</t>
+    <t xml:space="preserve">2.39985203742981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48140692710876</t>
   </si>
   <si>
     <t xml:space="preserve">2.54937052726746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6430082321167</t>
+    <t xml:space="preserve">2.64300799369812</t>
   </si>
   <si>
     <t xml:space="preserve">2.61733317375183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60223031044006</t>
+    <t xml:space="preserve">2.60223054885864</t>
   </si>
   <si>
     <t xml:space="preserve">2.70190978050232</t>
@@ -3107,22 +3107,22 @@
     <t xml:space="preserve">2.8650209903717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86200070381165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94204616546631</t>
+    <t xml:space="preserve">2.86200046539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94204640388489</t>
   </si>
   <si>
     <t xml:space="preserve">2.94506669044495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93147397041321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97980308532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96621036529541</t>
+    <t xml:space="preserve">2.93147373199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97980332374573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96621012687683</t>
   </si>
   <si>
     <t xml:space="preserve">2.9571487903595</t>
@@ -3137,25 +3137,25 @@
     <t xml:space="preserve">3.07337737083435</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05804061889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15312528610229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09178066253662</t>
+    <t xml:space="preserve">3.05804085731506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15312552452087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0917809009552</t>
   </si>
   <si>
     <t xml:space="preserve">3.11478495597839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19299936294556</t>
+    <t xml:space="preserve">3.19299960136414</t>
   </si>
   <si>
     <t xml:space="preserve">3.21600413322449</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18839836120605</t>
+    <t xml:space="preserve">3.18839812278748</t>
   </si>
   <si>
     <t xml:space="preserve">3.17459583282471</t>
@@ -3170,16 +3170,16 @@
     <t xml:space="preserve">2.98749470710754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96602416038513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95988941192627</t>
+    <t xml:space="preserve">2.96602392196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95988965034485</t>
   </si>
   <si>
     <t xml:space="preserve">2.9445526599884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91388010978699</t>
+    <t xml:space="preserve">2.91388034820557</t>
   </si>
   <si>
     <t xml:space="preserve">2.901611328125</t>
@@ -3188,10 +3188,10 @@
     <t xml:space="preserve">2.83106517791748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80192589759827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80039238929749</t>
+    <t xml:space="preserve">2.80192565917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80039262771606</t>
   </si>
   <si>
     <t xml:space="preserve">2.73598051071167</t>
@@ -3200,16 +3200,16 @@
     <t xml:space="preserve">2.7942578792572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79272437095642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83719944953918</t>
+    <t xml:space="preserve">2.79272413253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83719968795776</t>
   </si>
   <si>
     <t xml:space="preserve">2.76665258407593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80499315261841</t>
+    <t xml:space="preserve">2.80499291419983</t>
   </si>
   <si>
     <t xml:space="preserve">2.79119038581848</t>
@@ -3224,7 +3224,7 @@
     <t xml:space="preserve">2.7513165473938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7237114906311</t>
+    <t xml:space="preserve">2.72371172904968</t>
   </si>
   <si>
     <t xml:space="preserve">2.84333419799805</t>
@@ -3239,25 +3239,25 @@
     <t xml:space="preserve">2.72524523735046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6731014251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58108496665955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66543340682983</t>
+    <t xml:space="preserve">2.67310166358948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58108472824097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66543364524841</t>
   </si>
   <si>
     <t xml:space="preserve">2.73291325569153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75745105743408</t>
+    <t xml:space="preserve">2.75745129585266</t>
   </si>
   <si>
     <t xml:space="preserve">2.783522605896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92614912986755</t>
+    <t xml:space="preserve">2.92614936828613</t>
   </si>
   <si>
     <t xml:space="preserve">2.88934254646301</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">2.94301891326904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90774607658386</t>
+    <t xml:space="preserve">2.90774583816528</t>
   </si>
   <si>
     <t xml:space="preserve">2.85100221633911</t>
@@ -3281,28 +3281,28 @@
     <t xml:space="preserve">2.83873343467712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84486770629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91848111152649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95222139358521</t>
+    <t xml:space="preserve">2.84486746788025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91848087310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95222163200378</t>
   </si>
   <si>
     <t xml:space="preserve">2.90467858314514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96755766868591</t>
+    <t xml:space="preserve">2.96755790710449</t>
   </si>
   <si>
     <t xml:space="preserve">2.92768287658691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92461538314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83566617965698</t>
+    <t xml:space="preserve">2.92461562156677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83566641807556</t>
   </si>
   <si>
     <t xml:space="preserve">2.8617377281189</t>
@@ -3320,13 +3320,13 @@
     <t xml:space="preserve">2.99976348876953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00743126869202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98289346694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98596119880676</t>
+    <t xml:space="preserve">3.0074315071106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98289370536804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98596096038818</t>
   </si>
   <si>
     <t xml:space="preserve">2.95375514030457</t>
@@ -3335,16 +3335,16 @@
     <t xml:space="preserve">2.99056172370911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93688416481018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95682215690613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9000780582428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84180045127869</t>
+    <t xml:space="preserve">2.93688440322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95682191848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90007781982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84180068969727</t>
   </si>
   <si>
     <t xml:space="preserve">2.87400650978088</t>
@@ -3365,7 +3365,7 @@
     <t xml:space="preserve">2.70224118232727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70530843734741</t>
+    <t xml:space="preserve">2.70530819892883</t>
   </si>
   <si>
     <t xml:space="preserve">2.79732513427734</t>
@@ -3380,31 +3380,31 @@
     <t xml:space="preserve">2.78045535087585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82646441459656</t>
+    <t xml:space="preserve">2.82646465301514</t>
   </si>
   <si>
     <t xml:space="preserve">2.84793496131897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82339715957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93075013160706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90314531326294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88320827484131</t>
+    <t xml:space="preserve">2.823397397995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93074989318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90314507484436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88320803642273</t>
   </si>
   <si>
     <t xml:space="preserve">2.86633825302124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87554025650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90621256828308</t>
+    <t xml:space="preserve">2.87554001808167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9062123298645</t>
   </si>
   <si>
     <t xml:space="preserve">2.95528864860535</t>
@@ -3413,7 +3413,7 @@
     <t xml:space="preserve">2.97522568702698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98902821540833</t>
+    <t xml:space="preserve">2.98902797698975</t>
   </si>
   <si>
     <t xml:space="preserve">2.95068788528442</t>
@@ -3437,7 +3437,7 @@
     <t xml:space="preserve">2.88014078140259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91234660148621</t>
+    <t xml:space="preserve">2.91234683990479</t>
   </si>
   <si>
     <t xml:space="preserve">2.98136019706726</t>
@@ -3464,7 +3464,7 @@
     <t xml:space="preserve">2.69917392730713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70684194564819</t>
+    <t xml:space="preserve">2.70684170722961</t>
   </si>
   <si>
     <t xml:space="preserve">2.66083264350891</t>
@@ -3473,10 +3473,10 @@
     <t xml:space="preserve">2.76051831245422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71144270896912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58875298500061</t>
+    <t xml:space="preserve">2.7114429473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58875274658203</t>
   </si>
   <si>
     <t xml:space="preserve">2.73137950897217</t>
@@ -3506,28 +3506,28 @@
     <t xml:space="preserve">2.69610667228699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66850090026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75438380241394</t>
+    <t xml:space="preserve">2.66850113868713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75438404083252</t>
   </si>
   <si>
     <t xml:space="preserve">2.8249306678772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85406947135925</t>
+    <t xml:space="preserve">2.85406970977783</t>
   </si>
   <si>
     <t xml:space="preserve">2.89701080322266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9782931804657</t>
+    <t xml:space="preserve">2.97829294204712</t>
   </si>
   <si>
     <t xml:space="preserve">2.86327123641968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94148540496826</t>
+    <t xml:space="preserve">2.94148564338684</t>
   </si>
   <si>
     <t xml:space="preserve">3.03503656387329</t>
@@ -3536,7 +3536,7 @@
     <t xml:space="preserve">3.02736830711365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89087629318237</t>
+    <t xml:space="preserve">2.89087605476379</t>
   </si>
   <si>
     <t xml:space="preserve">2.74058127403259</t>
@@ -3557,31 +3557,31 @@
     <t xml:space="preserve">2.92445588111877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90142869949341</t>
+    <t xml:space="preserve">2.90142893791199</t>
   </si>
   <si>
     <t xml:space="preserve">3.05187320709229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07029509544373</t>
+    <t xml:space="preserve">3.07029485702515</t>
   </si>
   <si>
     <t xml:space="preserve">3.15472817420959</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08871698379517</t>
+    <t xml:space="preserve">3.08871674537659</t>
   </si>
   <si>
     <t xml:space="preserve">3.19771218299866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21459889411926</t>
+    <t xml:space="preserve">3.21459913253784</t>
   </si>
   <si>
     <t xml:space="preserve">3.18850111961365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25297737121582</t>
+    <t xml:space="preserve">3.2529776096344</t>
   </si>
   <si>
     <t xml:space="preserve">3.16547417640686</t>
@@ -3605,10 +3605,10 @@
     <t xml:space="preserve">2.55602025985718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58979392051697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54066920280457</t>
+    <t xml:space="preserve">2.58979368209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54066896438599</t>
   </si>
   <si>
     <t xml:space="preserve">2.25359654426575</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">2.24592089653015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33342409133911</t>
+    <t xml:space="preserve">2.33342432975769</t>
   </si>
   <si>
     <t xml:space="preserve">2.53452849388123</t>
@@ -3635,7 +3635,7 @@
     <t xml:space="preserve">2.56983685493469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75098443031311</t>
+    <t xml:space="preserve">2.75098419189453</t>
   </si>
   <si>
     <t xml:space="preserve">2.72488689422607</t>
@@ -3644,7 +3644,7 @@
     <t xml:space="preserve">2.76326560974121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78015208244324</t>
+    <t xml:space="preserve">2.78015232086182</t>
   </si>
   <si>
     <t xml:space="preserve">2.82927680015564</t>
@@ -3653,10 +3653,10 @@
     <t xml:space="preserve">2.79550361633301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79243302345276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73870325088501</t>
+    <t xml:space="preserve">2.79243326187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73870301246643</t>
   </si>
   <si>
     <t xml:space="preserve">2.79703879356384</t>
@@ -3668,7 +3668,7 @@
     <t xml:space="preserve">2.92906141281128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85383915901184</t>
+    <t xml:space="preserve">2.85383892059326</t>
   </si>
   <si>
     <t xml:space="preserve">2.8922176361084</t>
@@ -3680,25 +3680,25 @@
     <t xml:space="preserve">2.89835858345032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80931973457336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7985737323761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93366694450378</t>
+    <t xml:space="preserve">2.80931997299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79857397079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93366670608521</t>
   </si>
   <si>
     <t xml:space="preserve">2.94594788551331</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87226104736328</t>
+    <t xml:space="preserve">2.8722608089447</t>
   </si>
   <si>
     <t xml:space="preserve">2.93980741500854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88607740402222</t>
+    <t xml:space="preserve">2.88607716560364</t>
   </si>
   <si>
     <t xml:space="preserve">2.96590495109558</t>
@@ -3707,49 +3707,49 @@
     <t xml:space="preserve">2.95208835601807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90603423118591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92752623558044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91678023338318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90296411514282</t>
+    <t xml:space="preserve">2.90603399276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92752599716187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91678047180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90296387672424</t>
   </si>
   <si>
     <t xml:space="preserve">2.90756940841675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7908980846405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78936290740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75712490081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68343806266785</t>
+    <t xml:space="preserve">2.79089784622192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78936314582825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75712466239929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68343782424927</t>
   </si>
   <si>
     <t xml:space="preserve">2.78168749809265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80624961853027</t>
+    <t xml:space="preserve">2.80624938011169</t>
   </si>
   <si>
     <t xml:space="preserve">2.82467126846313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81853055953979</t>
+    <t xml:space="preserve">2.81853079795837</t>
   </si>
   <si>
     <t xml:space="preserve">2.88147187232971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86151480674744</t>
+    <t xml:space="preserve">2.86151504516602</t>
   </si>
   <si>
     <t xml:space="preserve">2.85230398178101</t>
@@ -3758,10 +3758,10 @@
     <t xml:space="preserve">2.81239008903503</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05271005630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07706642150879</t>
+    <t xml:space="preserve">3.05270981788635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07706665992737</t>
   </si>
   <si>
     <t xml:space="preserve">3.13065147399902</t>
@@ -3773,7 +3773,7 @@
     <t xml:space="preserve">3.1176609992981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07544302940369</t>
+    <t xml:space="preserve">3.07544279098511</t>
   </si>
   <si>
     <t xml:space="preserve">3.04946255683899</t>
@@ -3794,7 +3794,7 @@
     <t xml:space="preserve">3.0088677406311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96664929389954</t>
+    <t xml:space="preserve">2.96664953231812</t>
   </si>
   <si>
     <t xml:space="preserve">2.76205277442932</t>
@@ -3809,7 +3809,7 @@
     <t xml:space="preserve">2.74256753921509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66137838363647</t>
+    <t xml:space="preserve">2.66137862205505</t>
   </si>
   <si>
     <t xml:space="preserve">2.70197296142578</t>
@@ -3818,22 +3818,22 @@
     <t xml:space="preserve">2.76367664337158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78478574752808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77666711807251</t>
+    <t xml:space="preserve">2.78478598594666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77666735649109</t>
   </si>
   <si>
     <t xml:space="preserve">2.6954779624939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73282504081726</t>
+    <t xml:space="preserve">2.73282480239868</t>
   </si>
   <si>
     <t xml:space="preserve">2.69385433197021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7003493309021</t>
+    <t xml:space="preserve">2.70034909248352</t>
   </si>
   <si>
     <t xml:space="preserve">2.75880527496338</t>
@@ -3857,19 +3857,19 @@
     <t xml:space="preserve">2.67274522781372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76042938232422</t>
+    <t xml:space="preserve">2.76042914390564</t>
   </si>
   <si>
     <t xml:space="preserve">2.71821093559265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70359659194946</t>
+    <t xml:space="preserve">2.70359683036804</t>
   </si>
   <si>
     <t xml:space="preserve">2.64026927947998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51361441612244</t>
+    <t xml:space="preserve">2.51361417770386</t>
   </si>
   <si>
     <t xml:space="preserve">2.52822875976562</t>
@@ -3878,28 +3878,28 @@
     <t xml:space="preserve">2.57207036018372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69060659408569</t>
+    <t xml:space="preserve">2.69060635566711</t>
   </si>
   <si>
     <t xml:space="preserve">2.61428880691528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57856583595276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5460901260376</t>
+    <t xml:space="preserve">2.57856559753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54608988761902</t>
   </si>
   <si>
     <t xml:space="preserve">2.58343696594238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5168616771698</t>
+    <t xml:space="preserve">2.51686191558838</t>
   </si>
   <si>
     <t xml:space="preserve">2.55908012390137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62727928161621</t>
+    <t xml:space="preserve">2.62727904319763</t>
   </si>
   <si>
     <t xml:space="preserve">2.65975475311279</t>
@@ -3908,7 +3908,7 @@
     <t xml:space="preserve">2.72957730293274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66949772834778</t>
+    <t xml:space="preserve">2.6694974899292</t>
   </si>
   <si>
     <t xml:space="preserve">2.78153848648071</t>
@@ -3923,7 +3923,7 @@
     <t xml:space="preserve">2.71171569824219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70684432983398</t>
+    <t xml:space="preserve">2.70684456825256</t>
   </si>
   <si>
     <t xml:space="preserve">2.61753630638123</t>
@@ -3932,10 +3932,10 @@
     <t xml:space="preserve">2.66624975204468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60941767692566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56395173072815</t>
+    <t xml:space="preserve">2.60941743850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56395149230957</t>
   </si>
   <si>
     <t xml:space="preserve">2.56232762336731</t>
@@ -3953,7 +3953,7 @@
     <t xml:space="preserve">2.59642720222473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59805083274841</t>
+    <t xml:space="preserve">2.59805107116699</t>
   </si>
   <si>
     <t xml:space="preserve">2.58830833435059</t>
@@ -3977,10 +3977,10 @@
     <t xml:space="preserve">2.90819334983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88870811462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83999443054199</t>
+    <t xml:space="preserve">2.88870787620544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83999466896057</t>
   </si>
   <si>
     <t xml:space="preserve">2.78965735435486</t>
@@ -4001,13 +4001,13 @@
     <t xml:space="preserve">2.75393414497375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76692414283752</t>
+    <t xml:space="preserve">2.7669243812561</t>
   </si>
   <si>
     <t xml:space="preserve">2.8546085357666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79290509223938</t>
+    <t xml:space="preserve">2.7929048538208</t>
   </si>
   <si>
     <t xml:space="preserve">2.68086385726929</t>
@@ -4049,7 +4049,7 @@
     <t xml:space="preserve">2.95528316497803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94716429710388</t>
+    <t xml:space="preserve">2.9471640586853</t>
   </si>
   <si>
     <t xml:space="preserve">2.95690679550171</t>
@@ -4058,13 +4058,13 @@
     <t xml:space="preserve">3.02997708320618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04459095001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10467076301575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87409400939941</t>
+    <t xml:space="preserve">3.04459118843079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10467100143433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87409377098083</t>
   </si>
   <si>
     <t xml:space="preserve">2.8497371673584</t>
@@ -4073,7 +4073,7 @@
     <t xml:space="preserve">2.89520311355591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88708424568176</t>
+    <t xml:space="preserve">2.88708400726318</t>
   </si>
   <si>
     <t xml:space="preserve">2.91793608665466</t>
@@ -4100,13 +4100,13 @@
     <t xml:space="preserve">3.12740397453308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16637492179871</t>
+    <t xml:space="preserve">3.16637468338013</t>
   </si>
   <si>
     <t xml:space="preserve">3.14201784133911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1209089756012</t>
+    <t xml:space="preserve">3.12090873718262</t>
   </si>
   <si>
     <t xml:space="preserve">3.08031415939331</t>
@@ -4139,13 +4139,13 @@
     <t xml:space="preserve">3.18261241912842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17611742019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14039397239685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12415647506714</t>
+    <t xml:space="preserve">3.17611718177795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14039421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12415623664856</t>
   </si>
   <si>
     <t xml:space="preserve">3.17774105072021</t>
@@ -4160,10 +4160,10 @@
     <t xml:space="preserve">3.28003931045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2767915725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27029657363892</t>
+    <t xml:space="preserve">3.27679181098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2702968120575</t>
   </si>
   <si>
     <t xml:space="preserve">3.31251502037048</t>
@@ -4172,7 +4172,7 @@
     <t xml:space="preserve">3.3417432308197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29465341567993</t>
+    <t xml:space="preserve">3.29465365409851</t>
   </si>
   <si>
     <t xml:space="preserve">3.32388138771057</t>
@@ -4196,25 +4196,25 @@
     <t xml:space="preserve">3.51386404037476</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53822040557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52035880088806</t>
+    <t xml:space="preserve">3.53822064399719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52035903930664</t>
   </si>
   <si>
     <t xml:space="preserve">3.65838050842285</t>
   </si>
   <si>
-    <t xml:space="preserve">3.733074426651</t>
+    <t xml:space="preserve">3.73307466506958</t>
   </si>
   <si>
     <t xml:space="preserve">3.65675687789917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66487550735474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7022225856781</t>
+    <t xml:space="preserve">3.66487574577332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70222282409668</t>
   </si>
   <si>
     <t xml:space="preserve">3.68436098098755</t>
@@ -4241,7 +4241,7 @@
     <t xml:space="preserve">3.59830093383789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64376616477966</t>
+    <t xml:space="preserve">3.64376640319824</t>
   </si>
   <si>
     <t xml:space="preserve">3.61616206169128</t>
@@ -4250,46 +4250,46 @@
     <t xml:space="preserve">3.68598461151123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69572758674622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81101560592651</t>
+    <t xml:space="preserve">3.69572734832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81101536750793</t>
   </si>
   <si>
     <t xml:space="preserve">3.90032410621643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87921500205994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89869999885559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89382886886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9717710018158</t>
+    <t xml:space="preserve">3.87921476364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89870047569275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89382863044739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97177076339722</t>
   </si>
   <si>
     <t xml:space="preserve">3.89220499992371</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91980934143066</t>
+    <t xml:space="preserve">3.91980957984924</t>
   </si>
   <si>
     <t xml:space="preserve">3.82400631904602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41806077957153</t>
+    <t xml:space="preserve">3.41806101799011</t>
   </si>
   <si>
     <t xml:space="preserve">3.41643738746643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19885039329529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21021676063538</t>
+    <t xml:space="preserve">3.19885015487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21021699905396</t>
   </si>
   <si>
     <t xml:space="preserve">3.09492826461792</t>
@@ -4322,7 +4322,7 @@
     <t xml:space="preserve">3.1517608165741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27192068099976</t>
+    <t xml:space="preserve">3.27192091941833</t>
   </si>
   <si>
     <t xml:space="preserve">3.28815841674805</t>
@@ -4337,7 +4337,7 @@
     <t xml:space="preserve">3.34823822975159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44891285896301</t>
+    <t xml:space="preserve">3.44891262054443</t>
   </si>
   <si>
     <t xml:space="preserve">3.4342987537384</t>
@@ -4355,16 +4355,16 @@
     <t xml:space="preserve">3.34661459922791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32712888717651</t>
+    <t xml:space="preserve">3.32712912559509</t>
   </si>
   <si>
     <t xml:space="preserve">3.26704931259155</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38720870018005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43105101585388</t>
+    <t xml:space="preserve">3.38720893859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4310507774353</t>
   </si>
   <si>
     <t xml:space="preserve">3.50736904144287</t>
@@ -4373,13 +4373,13 @@
     <t xml:space="preserve">3.36934733390808</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38558530807495</t>
+    <t xml:space="preserve">3.38558506965637</t>
   </si>
   <si>
     <t xml:space="preserve">3.38233757019043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38396167755127</t>
+    <t xml:space="preserve">3.38396143913269</t>
   </si>
   <si>
     <t xml:space="preserve">3.33499121665955</t>
@@ -5898,6 +5898,9 @@
   </si>
   <si>
     <t xml:space="preserve">13.3299999237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9700002670288</t>
   </si>
 </sst>
 </file>
@@ -71132,7 +71135,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.6496064815</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>618611</v>
@@ -71153,6 +71156,32 @@
         <v>1948</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6912847222</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>739308</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>13.9700002670288</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>13.6750001907349</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>13.7150001525879</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>13.9700002670288</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>1962</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BPSO.MI.xlsx
+++ b/data/BPSO.MI.xlsx
@@ -38,52 +38,52 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82907176017761</t>
+    <t xml:space="preserve">2.82907152175903</t>
   </si>
   <si>
     <t xml:space="preserve">BPSO.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80963754653931</t>
+    <t xml:space="preserve">2.80963730812073</t>
   </si>
   <si>
     <t xml:space="preserve">2.74855804443359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71246576309204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63611674308777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60835385322571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69303178787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69858455657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61113023757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51257085800171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4556565284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26686644554138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38069558143616</t>
+    <t xml:space="preserve">2.71246600151062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63611698150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60835433006287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69303202629089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69858431816101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61113047599792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51257038116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45565605163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26686596870422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38069534301758</t>
   </si>
   <si>
     <t xml:space="preserve">2.40568208694458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36542558670044</t>
+    <t xml:space="preserve">2.3654260635376</t>
   </si>
   <si>
     <t xml:space="preserve">2.51951146125793</t>
@@ -92,16 +92,16 @@
     <t xml:space="preserve">2.44455122947693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.355708360672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43899893760681</t>
+    <t xml:space="preserve">2.35570883750916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43899869918823</t>
   </si>
   <si>
     <t xml:space="preserve">2.40429425239563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32100510597229</t>
+    <t xml:space="preserve">2.32100486755371</t>
   </si>
   <si>
     <t xml:space="preserve">2.22105741500854</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">2.23216247558594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20995211601257</t>
+    <t xml:space="preserve">2.20995187759399</t>
   </si>
   <si>
     <t xml:space="preserve">2.04059600830078</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">2.14332008361816</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07668805122375</t>
+    <t xml:space="preserve">2.07668781280518</t>
   </si>
   <si>
     <t xml:space="preserve">2.1821882724762</t>
@@ -131,58 +131,58 @@
     <t xml:space="preserve">2.22522163391113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2779712677002</t>
+    <t xml:space="preserve">2.27797150611877</t>
   </si>
   <si>
     <t xml:space="preserve">2.19329380989075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16553044319153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24604368209839</t>
+    <t xml:space="preserve">2.16553068161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24604415893555</t>
   </si>
   <si>
     <t xml:space="preserve">2.18635272979736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1766357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21550488471985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25992560386658</t>
+    <t xml:space="preserve">2.17663598060608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21550464630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25992512702942</t>
   </si>
   <si>
     <t xml:space="preserve">2.31822872161865</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38763618469238</t>
+    <t xml:space="preserve">2.38763642311096</t>
   </si>
   <si>
     <t xml:space="preserve">2.38208365440369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37514281272888</t>
+    <t xml:space="preserve">2.37514305114746</t>
   </si>
   <si>
     <t xml:space="preserve">2.2418794631958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26270151138306</t>
+    <t xml:space="preserve">2.26270174980164</t>
   </si>
   <si>
     <t xml:space="preserve">2.25020837783813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31961703300476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43344497680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35848498344421</t>
+    <t xml:space="preserve">2.3196165561676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43344521522522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35848522186279</t>
   </si>
   <si>
     <t xml:space="preserve">2.30156993865967</t>
@@ -191,22 +191,22 @@
     <t xml:space="preserve">2.34599184989929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3598735332489</t>
+    <t xml:space="preserve">2.35987329483032</t>
   </si>
   <si>
     <t xml:space="preserve">2.39318871498108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29324126243591</t>
+    <t xml:space="preserve">2.29324102401733</t>
   </si>
   <si>
     <t xml:space="preserve">2.23771500587463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18774056434631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.139155626297</t>
+    <t xml:space="preserve">2.18774104118347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13915586471558</t>
   </si>
   <si>
     <t xml:space="preserve">2.14748477935791</t>
@@ -218,76 +218,76 @@
     <t xml:space="preserve">2.06974720954895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01283288002014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01838564872742</t>
+    <t xml:space="preserve">2.01283264160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01838541030884</t>
   </si>
   <si>
     <t xml:space="preserve">2.07113552093506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11694502830505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12527418136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22799825668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30295848846436</t>
+    <t xml:space="preserve">2.11694526672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12527394294739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22799801826477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30295825004578</t>
   </si>
   <si>
     <t xml:space="preserve">2.23910331726074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29046487808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3321099281311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32655763626099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27935981750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32378101348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30851078033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26131367683411</t>
+    <t xml:space="preserve">2.29046535491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33211016654968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32655739784241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2793595790863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32378125190735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30851101875305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26131391525269</t>
   </si>
   <si>
     <t xml:space="preserve">2.23493885993958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15720152854919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11139225959778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08224081993103</t>
+    <t xml:space="preserve">2.15720129013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11139273643494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08224058151245</t>
   </si>
   <si>
     <t xml:space="preserve">2.09889936447144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08918190002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10583996772766</t>
+    <t xml:space="preserve">2.08918213844299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10583972930908</t>
   </si>
   <si>
     <t xml:space="preserve">2.04892492294312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03781986236572</t>
+    <t xml:space="preserve">2.03781938552856</t>
   </si>
   <si>
     <t xml:space="preserve">2.06558299064636</t>
@@ -296,10 +296,10 @@
     <t xml:space="preserve">2.03226709365845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07252335548401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05725407600403</t>
+    <t xml:space="preserve">2.07252359390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05725359916687</t>
   </si>
   <si>
     <t xml:space="preserve">2.05156683921814</t>
@@ -314,19 +314,19 @@
     <t xml:space="preserve">2.15393209457397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17525839805603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15535378456116</t>
+    <t xml:space="preserve">2.17525815963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15535402297974</t>
   </si>
   <si>
     <t xml:space="preserve">2.09279680252075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07147121429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99896240234375</t>
+    <t xml:space="preserve">2.07147097587585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99896228313446</t>
   </si>
   <si>
     <t xml:space="preserve">1.95773220062256</t>
@@ -335,67 +335,67 @@
     <t xml:space="preserve">1.87669265270233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98901009559631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93640613555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94351482391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84114968776703</t>
+    <t xml:space="preserve">1.98900997638702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93640625476837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94351506233215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84114980697632</t>
   </si>
   <si>
     <t xml:space="preserve">1.78143727779388</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75158023834229</t>
+    <t xml:space="preserve">1.75157999992371</t>
   </si>
   <si>
     <t xml:space="preserve">1.72598898410797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64210629463196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6961327791214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77006244659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81129312515259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78001427650452</t>
+    <t xml:space="preserve">1.64210617542267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69613254070282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77006256580353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81129324436188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78001439571381</t>
   </si>
   <si>
     <t xml:space="preserve">1.89375364780426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63499760627747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56533288955688</t>
+    <t xml:space="preserve">1.6349972486496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5653327703476</t>
   </si>
   <si>
     <t xml:space="preserve">1.6691198348999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65632367134094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63926255702972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63641941547394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5767068862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51130664348602</t>
+    <t xml:space="preserve">1.65632343292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63926267623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63641917705536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57670664787292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51130652427673</t>
   </si>
   <si>
     <t xml:space="preserve">1.52552390098572</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">1.53121078014374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63784074783325</t>
+    <t xml:space="preserve">1.63784086704254</t>
   </si>
   <si>
     <t xml:space="preserve">1.67196333408356</t>
@@ -413,49 +413,49 @@
     <t xml:space="preserve">1.69471085071564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67054164409637</t>
+    <t xml:space="preserve">1.6705414056778</t>
   </si>
   <si>
     <t xml:space="preserve">1.74304986000061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70892822742462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72172367572784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77574968338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76721894741058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72741055488586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69755446910858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72456705570221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71888053417206</t>
+    <t xml:space="preserve">1.70892798900604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72172331809998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77574956417084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76721882820129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72741067409515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69755423069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72456741333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71888029575348</t>
   </si>
   <si>
     <t xml:space="preserve">1.6634327173233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55395877361298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57528483867645</t>
+    <t xml:space="preserve">1.55395901203156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57528495788574</t>
   </si>
   <si>
     <t xml:space="preserve">1.52125859260559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63357591629028</t>
+    <t xml:space="preserve">1.6335756778717</t>
   </si>
   <si>
     <t xml:space="preserve">1.65916693210602</t>
@@ -464,13 +464,13 @@
     <t xml:space="preserve">1.64779317378998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68760228157043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71461510658264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70608472824097</t>
+    <t xml:space="preserve">1.68760216236115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71461486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70608460903168</t>
   </si>
   <si>
     <t xml:space="preserve">1.70039761066437</t>
@@ -479,16 +479,16 @@
     <t xml:space="preserve">1.7444714307785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70750653743744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72030210494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7316757440567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78285896778107</t>
+    <t xml:space="preserve">1.70750641822815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72030198574066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73167598247528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78285884857178</t>
   </si>
   <si>
     <t xml:space="preserve">1.7785929441452</t>
@@ -503,43 +503,43 @@
     <t xml:space="preserve">1.75584518909454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76295363903046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74162781238556</t>
+    <t xml:space="preserve">1.76295375823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74162793159485</t>
   </si>
   <si>
     <t xml:space="preserve">1.76864075660706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74873650074005</t>
+    <t xml:space="preserve">1.74873673915863</t>
   </si>
   <si>
     <t xml:space="preserve">1.73451936244965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78428041934967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85252332687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84967970848083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81271505355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83546268939972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84825849533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85963213443756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9477801322937</t>
+    <t xml:space="preserve">1.78428053855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85252320766449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84967982769012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81271517276764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83546280860901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84825837612152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85963201522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94777989387512</t>
   </si>
   <si>
     <t xml:space="preserve">1.97621488571167</t>
@@ -557,19 +557,19 @@
     <t xml:space="preserve">2.08568859100342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0885317325592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09706234931946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16104102134705</t>
+    <t xml:space="preserve">2.08853197097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09706211090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16104078292847</t>
   </si>
   <si>
     <t xml:space="preserve">2.18236684799194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11412286758423</t>
+    <t xml:space="preserve">2.11412310600281</t>
   </si>
   <si>
     <t xml:space="preserve">2.00038433074951</t>
@@ -578,49 +578,49 @@
     <t xml:space="preserve">2.0387716293335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00891423225403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0529887676239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06294083595276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11554455757141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12549686431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16246247291565</t>
+    <t xml:space="preserve">2.00891447067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05298852920532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0629403591156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11554503440857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12549662590027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16246271133423</t>
   </si>
   <si>
     <t xml:space="preserve">2.15961909294128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13260579109192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08142328262329</t>
+    <t xml:space="preserve">2.13260555267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08142304420471</t>
   </si>
   <si>
     <t xml:space="preserve">2.03592801094055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07715797424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09990549087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08995342254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01033568382263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12407493591309</t>
+    <t xml:space="preserve">2.07715821266174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09990572929382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08995389938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01033592224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12407517433167</t>
   </si>
   <si>
     <t xml:space="preserve">2.10417103767395</t>
@@ -629,28 +629,28 @@
     <t xml:space="preserve">2.07289290428162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16814970970154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27477979660034</t>
+    <t xml:space="preserve">2.16814947128296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27478003501892</t>
   </si>
   <si>
     <t xml:space="preserve">2.37430143356323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2634060382843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23354887962341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2719361782074</t>
+    <t xml:space="preserve">2.26340579986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23354935646057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27193641662598</t>
   </si>
   <si>
     <t xml:space="preserve">2.23212742805481</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17810130119324</t>
+    <t xml:space="preserve">2.17810153961182</t>
   </si>
   <si>
     <t xml:space="preserve">2.16957139968872</t>
@@ -662,106 +662,106 @@
     <t xml:space="preserve">2.22217512130737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21791005134583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2051146030426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22359681129456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26482748985291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31032276153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31743144989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34302306175232</t>
+    <t xml:space="preserve">2.2179102897644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20511436462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22359704971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26482772827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3103232383728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31743168830872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34302282333374</t>
   </si>
   <si>
     <t xml:space="preserve">2.34160089492798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30463624000549</t>
+    <t xml:space="preserve">2.30463600158691</t>
   </si>
   <si>
     <t xml:space="preserve">2.29752731323242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29610562324524</t>
+    <t xml:space="preserve">2.29610586166382</t>
   </si>
   <si>
     <t xml:space="preserve">2.36008358001709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3529748916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34017968177795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4027361869812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41695332527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45249700546265</t>
+    <t xml:space="preserve">2.35297465324402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34017944335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40273594856262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41695356369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45249652862549</t>
   </si>
   <si>
     <t xml:space="preserve">2.41126680374146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.415531873703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4240620136261</t>
+    <t xml:space="preserve">2.41553211212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42406225204468</t>
   </si>
   <si>
     <t xml:space="preserve">2.44396638870239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3543963432312</t>
+    <t xml:space="preserve">2.35439682006836</t>
   </si>
   <si>
     <t xml:space="preserve">2.33733582496643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33022713661194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36434864997864</t>
+    <t xml:space="preserve">2.33022737503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36434888839722</t>
   </si>
   <si>
     <t xml:space="preserve">2.32738399505615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28188824653625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30037117004395</t>
+    <t xml:space="preserve">2.28188848495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30037093162537</t>
   </si>
   <si>
     <t xml:space="preserve">2.32311844825745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33449244499207</t>
+    <t xml:space="preserve">2.33449268341064</t>
   </si>
   <si>
     <t xml:space="preserve">2.30890130996704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2989490032196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25629734992981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12834024429321</t>
+    <t xml:space="preserve">2.29894924163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25629758834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12834048271179</t>
   </si>
   <si>
     <t xml:space="preserve">2.13402724266052</t>
@@ -770,19 +770,19 @@
     <t xml:space="preserve">2.28473162651062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22928404808044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27335786819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27904510498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31316637992859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33875727653503</t>
+    <t xml:space="preserve">2.22928428649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.273357629776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27904486656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31316661834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33875751495361</t>
   </si>
   <si>
     <t xml:space="preserve">2.37856674194336</t>
@@ -791,37 +791,37 @@
     <t xml:space="preserve">2.32880544662476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.367192029953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34870958328247</t>
+    <t xml:space="preserve">2.36719250679016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34870982170105</t>
   </si>
   <si>
     <t xml:space="preserve">2.29468417167664</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30321431159973</t>
+    <t xml:space="preserve">2.30321407318115</t>
   </si>
   <si>
     <t xml:space="preserve">2.28757524490356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32027530670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28331017494202</t>
+    <t xml:space="preserve">2.32027506828308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2833104133606</t>
   </si>
   <si>
     <t xml:space="preserve">2.29041862487793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29326248168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30605792999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35581827163696</t>
+    <t xml:space="preserve">2.29326200485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3060576915741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35581803321838</t>
   </si>
   <si>
     <t xml:space="preserve">2.31174468994141</t>
@@ -833,25 +833,25 @@
     <t xml:space="preserve">2.46671414375305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43117070198059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42974925041199</t>
+    <t xml:space="preserve">2.43117094039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42974901199341</t>
   </si>
   <si>
     <t xml:space="preserve">2.49799275398254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46387028694153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48661828041077</t>
+    <t xml:space="preserve">2.46387076377869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48661804199219</t>
   </si>
   <si>
     <t xml:space="preserve">2.51647520065308</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51789665222168</t>
+    <t xml:space="preserve">2.51789689064026</t>
   </si>
   <si>
     <t xml:space="preserve">2.56907916069031</t>
@@ -860,19 +860,19 @@
     <t xml:space="preserve">2.53353595733643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48803973197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50510120391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5079448223114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50936651229858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50652289390564</t>
+    <t xml:space="preserve">2.48803997039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50510144233704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50794506072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50936627388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5065233707428</t>
   </si>
   <si>
     <t xml:space="preserve">2.5548620223999</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">2.57221221923828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63293862342834</t>
+    <t xml:space="preserve">2.63293838500977</t>
   </si>
   <si>
     <t xml:space="preserve">2.65607333183289</t>
@@ -890,7 +890,7 @@
     <t xml:space="preserve">2.70667886734009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56642889976501</t>
+    <t xml:space="preserve">2.56642866134644</t>
   </si>
   <si>
     <t xml:space="preserve">2.52594375610352</t>
@@ -899,10 +899,10 @@
     <t xml:space="preserve">2.52883553504944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47389245033264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5216064453125</t>
+    <t xml:space="preserve">2.47389268875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52160620689392</t>
   </si>
   <si>
     <t xml:space="preserve">2.51437664031982</t>
@@ -914,13 +914,13 @@
     <t xml:space="preserve">2.48979711532593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47533798217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51726865768433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45654249191284</t>
+    <t xml:space="preserve">2.47533845901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51726889610291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45654225349426</t>
   </si>
   <si>
     <t xml:space="preserve">2.47967576980591</t>
@@ -932,13 +932,13 @@
     <t xml:space="preserve">2.48112177848816</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45798802375793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48256802558899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48835134506226</t>
+    <t xml:space="preserve">2.45798826217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48256778717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48835110664368</t>
   </si>
   <si>
     <t xml:space="preserve">2.48690533638</t>
@@ -950,16 +950,16 @@
     <t xml:space="preserve">2.53751134872437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60257530212402</t>
+    <t xml:space="preserve">2.6025755405426</t>
   </si>
   <si>
     <t xml:space="preserve">2.55919933319092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49558067321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59245443344116</t>
+    <t xml:space="preserve">2.49558091163635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59245419502258</t>
   </si>
   <si>
     <t xml:space="preserve">2.66330242156982</t>
@@ -968,88 +968,88 @@
     <t xml:space="preserve">2.61414241790771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63149309158325</t>
+    <t xml:space="preserve">2.63149285316467</t>
   </si>
   <si>
     <t xml:space="preserve">2.6228175163269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61703419685364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72692084312439</t>
+    <t xml:space="preserve">2.61703395843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72692060470581</t>
   </si>
   <si>
     <t xml:space="preserve">2.73704195022583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72258305549622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71246194839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71390795707703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7081241607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68932795524597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68643641471863</t>
+    <t xml:space="preserve">2.72258329391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71246218681335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71390771865845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70812439918518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68932819366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68643665313721</t>
   </si>
   <si>
     <t xml:space="preserve">2.6878821849823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7110161781311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65028882026672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67920732498169</t>
+    <t xml:space="preserve">2.71101641654968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6502890586853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67920708656311</t>
   </si>
   <si>
     <t xml:space="preserve">2.67197775840759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67053174972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65318059921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65173482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.667640209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65896511077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64595127105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59823775291443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62426352500916</t>
+    <t xml:space="preserve">2.67053198814392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65318083763123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65173506736755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66764044761658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65896534919739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64595150947571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59823799133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62426328659058</t>
   </si>
   <si>
     <t xml:space="preserve">2.60402131080627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54474067687988</t>
+    <t xml:space="preserve">2.54474091529846</t>
   </si>
   <si>
     <t xml:space="preserve">2.57655000686646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52449774742126</t>
+    <t xml:space="preserve">2.52449822425842</t>
   </si>
   <si>
     <t xml:space="preserve">2.48545956611633</t>
@@ -1061,19 +1061,19 @@
     <t xml:space="preserve">2.52016019821167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5114848613739</t>
+    <t xml:space="preserve">2.51148509979248</t>
   </si>
   <si>
     <t xml:space="preserve">2.518714427948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53317332267761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55197024345398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50714731216431</t>
+    <t xml:space="preserve">2.53317308425903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55196976661682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50714755058289</t>
   </si>
   <si>
     <t xml:space="preserve">2.55052423477173</t>
@@ -1085,40 +1085,40 @@
     <t xml:space="preserve">2.53606557846069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57944178581238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64161372184753</t>
+    <t xml:space="preserve">2.5794415473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64161396026611</t>
   </si>
   <si>
     <t xml:space="preserve">2.63004684448242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58956241607666</t>
+    <t xml:space="preserve">2.58956265449524</t>
   </si>
   <si>
     <t xml:space="preserve">2.52305197715759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51582264900208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49268889427185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53461885452271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4912428855896</t>
+    <t xml:space="preserve">2.51582288742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49268865585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53461861610413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49124312400818</t>
   </si>
   <si>
     <t xml:space="preserve">2.47244668006897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50425577163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4840133190155</t>
+    <t xml:space="preserve">2.50425601005554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48401355743408</t>
   </si>
   <si>
     <t xml:space="preserve">2.49413466453552</t>
@@ -1127,31 +1127,31 @@
     <t xml:space="preserve">2.49847221374512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47823023796082</t>
+    <t xml:space="preserve">2.47822999954224</t>
   </si>
   <si>
     <t xml:space="preserve">2.51293110847473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44931292533875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.407381772995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45509624481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41027331352234</t>
+    <t xml:space="preserve">2.44931316375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40738201141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45509648323059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4102737903595</t>
   </si>
   <si>
     <t xml:space="preserve">2.29605007171631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24688982963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28159117698669</t>
+    <t xml:space="preserve">2.2468900680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28159093856812</t>
   </si>
   <si>
     <t xml:space="preserve">2.18471765518188</t>
@@ -1160,13 +1160,13 @@
     <t xml:space="preserve">2.19773054122925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22086405754089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26279449462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28448271751404</t>
+    <t xml:space="preserve">2.22086429595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26279473304749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28448247909546</t>
   </si>
   <si>
     <t xml:space="preserve">2.28592824935913</t>
@@ -1175,16 +1175,16 @@
     <t xml:space="preserve">2.32496738433838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34810161590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3784646987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41461181640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34231805801392</t>
+    <t xml:space="preserve">2.34810137748718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37846446037292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41461205482483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34231781959534</t>
   </si>
   <si>
     <t xml:space="preserve">2.35677647590637</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">2.37701869010925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39292335510254</t>
+    <t xml:space="preserve">2.39292311668396</t>
   </si>
   <si>
     <t xml:space="preserve">2.40015268325806</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">2.33653426170349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29315733909607</t>
+    <t xml:space="preserve">2.29315781593323</t>
   </si>
   <si>
     <t xml:space="preserve">2.20495986938477</t>
@@ -1220,10 +1220,10 @@
     <t xml:space="preserve">2.23966073989868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23821496963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23387742042542</t>
+    <t xml:space="preserve">2.23821473121643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23387694358826</t>
   </si>
   <si>
     <t xml:space="preserve">2.18327188491821</t>
@@ -1247,25 +1247,25 @@
     <t xml:space="preserve">2.31340074539185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31050872802734</t>
+    <t xml:space="preserve">2.31050896644592</t>
   </si>
   <si>
     <t xml:space="preserve">2.38858556747437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38714003562927</t>
+    <t xml:space="preserve">2.38713932037354</t>
   </si>
   <si>
     <t xml:space="preserve">2.34665584564209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34520959854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36545205116272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39436912536621</t>
+    <t xml:space="preserve">2.34520936012268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36545157432556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39436936378479</t>
   </si>
   <si>
     <t xml:space="preserve">2.40304446220398</t>
@@ -1274,13 +1274,13 @@
     <t xml:space="preserve">2.40449023246765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32785940170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34954714775085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33364295959473</t>
+    <t xml:space="preserve">2.3278591632843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34954738616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33364272117615</t>
   </si>
   <si>
     <t xml:space="preserve">2.31195449829102</t>
@@ -1289,22 +1289,22 @@
     <t xml:space="preserve">2.22953963279724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31484651565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30327963829041</t>
+    <t xml:space="preserve">2.31484627723694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30327939987183</t>
   </si>
   <si>
     <t xml:space="preserve">2.32062983512878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30761742591858</t>
+    <t xml:space="preserve">2.3076171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.37268114089966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42907071113586</t>
+    <t xml:space="preserve">2.42907047271729</t>
   </si>
   <si>
     <t xml:space="preserve">2.36400604248047</t>
@@ -1322,16 +1322,16 @@
     <t xml:space="preserve">2.32930493354797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30617141723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3003876209259</t>
+    <t xml:space="preserve">2.30617117881775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30038785934448</t>
   </si>
   <si>
     <t xml:space="preserve">2.37412714958191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33075094223022</t>
+    <t xml:space="preserve">2.3307511806488</t>
   </si>
   <si>
     <t xml:space="preserve">2.32641339302063</t>
@@ -1340,28 +1340,28 @@
     <t xml:space="preserve">2.39726090431213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39870715141296</t>
+    <t xml:space="preserve">2.39870691299438</t>
   </si>
   <si>
     <t xml:space="preserve">2.38569402694702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60112977027893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71969127655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70957016944885</t>
+    <t xml:space="preserve">2.60112953186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71969151496887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70957040786743</t>
   </si>
   <si>
     <t xml:space="preserve">2.75439214706421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77752685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84837412834167</t>
+    <t xml:space="preserve">2.77752661705017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84837436676025</t>
   </si>
   <si>
     <t xml:space="preserve">2.84114503860474</t>
@@ -1373,16 +1373,16 @@
     <t xml:space="preserve">2.86861634254456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90042614936829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82957816123962</t>
+    <t xml:space="preserve">2.90042591094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82957792282104</t>
   </si>
   <si>
     <t xml:space="preserve">2.73125863075256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78620195388794</t>
+    <t xml:space="preserve">2.78620171546936</t>
   </si>
   <si>
     <t xml:space="preserve">2.75583791732788</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">2.74716281890869</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7384877204895</t>
+    <t xml:space="preserve">2.73848748207092</t>
   </si>
   <si>
     <t xml:space="preserve">2.63438439369202</t>
@@ -1409,10 +1409,10 @@
     <t xml:space="preserve">2.66091990470886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65060091018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71251726150513</t>
+    <t xml:space="preserve">2.65060043334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71251702308655</t>
   </si>
   <si>
     <t xml:space="preserve">2.70367121696472</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">2.63143610954285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52824258804321</t>
+    <t xml:space="preserve">2.52824234962463</t>
   </si>
   <si>
     <t xml:space="preserve">2.48254251480103</t>
@@ -1430,16 +1430,16 @@
     <t xml:space="preserve">2.52234554290771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56509733200073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6107976436615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57689070701599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51939725875854</t>
+    <t xml:space="preserve">2.56509709358215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61079740524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57689046859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51939749717712</t>
   </si>
   <si>
     <t xml:space="preserve">2.59163308143616</t>
@@ -1448,10 +1448,10 @@
     <t xml:space="preserve">2.618168592453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59015917778015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54888105392456</t>
+    <t xml:space="preserve">2.59015893936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54888081550598</t>
   </si>
   <si>
     <t xml:space="preserve">2.56067442893982</t>
@@ -1463,13 +1463,13 @@
     <t xml:space="preserve">2.54593253135681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57099390029907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51350045204163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51055216789246</t>
+    <t xml:space="preserve">2.57099413871765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51350069046021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51055240631104</t>
   </si>
   <si>
     <t xml:space="preserve">2.53708744049072</t>
@@ -1481,22 +1481,22 @@
     <t xml:space="preserve">2.65354871749878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65944576263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70514512062073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6904034614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65797162055969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61964273452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63291049003601</t>
+    <t xml:space="preserve">2.6594455242157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70514535903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69040322303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65797138214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61964249610901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63291025161743</t>
   </si>
   <si>
     <t xml:space="preserve">2.64912629127502</t>
@@ -1505,19 +1505,19 @@
     <t xml:space="preserve">2.64322948455811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6653425693512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64470338821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63880705833435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66386818885803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71399140357971</t>
+    <t xml:space="preserve">2.66534233093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64470362663269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63880681991577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66386842727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71399116516113</t>
   </si>
   <si>
     <t xml:space="preserve">2.73168134689331</t>
@@ -1529,16 +1529,16 @@
     <t xml:space="preserve">2.73315572738647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78180408477783</t>
+    <t xml:space="preserve">2.78180384635925</t>
   </si>
   <si>
     <t xml:space="preserve">2.70661973953247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69187808036804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68892955780029</t>
+    <t xml:space="preserve">2.69187784194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68892931938171</t>
   </si>
   <si>
     <t xml:space="preserve">2.67713570594788</t>
@@ -1547,19 +1547,19 @@
     <t xml:space="preserve">2.64617800712585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64175534248352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57541632652283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61374592781067</t>
+    <t xml:space="preserve">2.64175510406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57541656494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61374568939209</t>
   </si>
   <si>
     <t xml:space="preserve">2.60932326316833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58868479728699</t>
+    <t xml:space="preserve">2.58868455886841</t>
   </si>
   <si>
     <t xml:space="preserve">2.58131289482117</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">2.47222328186035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50170707702637</t>
+    <t xml:space="preserve">2.50170731544495</t>
   </si>
   <si>
     <t xml:space="preserve">2.56362271308899</t>
@@ -1583,19 +1583,19 @@
     <t xml:space="preserve">2.67123913764954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67418766021729</t>
+    <t xml:space="preserve">2.67418742179871</t>
   </si>
   <si>
     <t xml:space="preserve">2.65502309799194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68450713157654</t>
+    <t xml:space="preserve">2.68450665473938</t>
   </si>
   <si>
     <t xml:space="preserve">2.66239380836487</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6240656375885</t>
+    <t xml:space="preserve">2.62406539916992</t>
   </si>
   <si>
     <t xml:space="preserve">2.62996196746826</t>
@@ -1604,7 +1604,7 @@
     <t xml:space="preserve">2.63733291625977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62111711502075</t>
+    <t xml:space="preserve">2.62111687660217</t>
   </si>
   <si>
     <t xml:space="preserve">2.42210006713867</t>
@@ -1634,13 +1634,13 @@
     <t xml:space="preserve">2.22898149490356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16706466674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18033266067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15674567222595</t>
+    <t xml:space="preserve">2.16706490516663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18033242225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15674543380737</t>
   </si>
   <si>
     <t xml:space="preserve">2.2024450302124</t>
@@ -1649,22 +1649,22 @@
     <t xml:space="preserve">2.19360017776489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13905549049377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11399412155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08745813369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04175806045532</t>
+    <t xml:space="preserve">2.1390552520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11399435997009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08745837211609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0417582988739</t>
   </si>
   <si>
     <t xml:space="preserve">2.00932621955872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05207777023315</t>
+    <t xml:space="preserve">2.05207800865173</t>
   </si>
   <si>
     <t xml:space="preserve">2.105149269104</t>
@@ -1682,13 +1682,13 @@
     <t xml:space="preserve">2.13610696792603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11694288253784</t>
+    <t xml:space="preserve">2.11694264411926</t>
   </si>
   <si>
     <t xml:space="preserve">2.09925246238708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10220050811768</t>
+    <t xml:space="preserve">2.10220074653625</t>
   </si>
   <si>
     <t xml:space="preserve">2.10072660446167</t>
@@ -1700,16 +1700,16 @@
     <t xml:space="preserve">2.04912924766541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06829357147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05060291290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04765510559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02701687812805</t>
+    <t xml:space="preserve">2.06829380989075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05060338973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0476553440094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02701663970947</t>
   </si>
   <si>
     <t xml:space="preserve">2.01964569091797</t>
@@ -1721,19 +1721,19 @@
     <t xml:space="preserve">1.97984254360199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96215164661407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98426508903503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08008742332458</t>
+    <t xml:space="preserve">1.96215176582336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98426496982574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08008718490601</t>
   </si>
   <si>
     <t xml:space="preserve">2.06387114524841</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07861280441284</t>
+    <t xml:space="preserve">2.07861304283142</t>
   </si>
   <si>
     <t xml:space="preserve">2.04618096351624</t>
@@ -1751,13 +1751,13 @@
     <t xml:space="preserve">1.98279082775116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94446122646332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93709051609039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96657419204712</t>
+    <t xml:space="preserve">1.94446134567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9370903968811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96657395362854</t>
   </si>
   <si>
     <t xml:space="preserve">1.96804857254028</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">1.98131692409515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91497755050659</t>
+    <t xml:space="preserve">1.9149774312973</t>
   </si>
   <si>
     <t xml:space="preserve">1.8751745223999</t>
@@ -1778,40 +1778,40 @@
     <t xml:space="preserve">1.87370073795319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94003891944885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92677128314972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99311053752899</t>
+    <t xml:space="preserve">1.94003903865814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92677104473114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99311029911041</t>
   </si>
   <si>
     <t xml:space="preserve">2.00342965126038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99458456039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99163615703583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94888377189636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88844227790833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8722265958786</t>
+    <t xml:space="preserve">1.994584441185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99163591861725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94888401031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88844239711761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87222647666931</t>
   </si>
   <si>
     <t xml:space="preserve">1.91940009593964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89433908462524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86485517024994</t>
+    <t xml:space="preserve">1.89433944225311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86485540866852</t>
   </si>
   <si>
     <t xml:space="preserve">1.85306179523468</t>
@@ -1829,16 +1829,16 @@
     <t xml:space="preserve">1.8250515460968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78230047225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71596121788025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69532251358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71006453037262</t>
+    <t xml:space="preserve">1.78230035305023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71596109867096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69532239437103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71006441116333</t>
   </si>
   <si>
     <t xml:space="preserve">1.73217797279358</t>
@@ -1847,13 +1847,13 @@
     <t xml:space="preserve">1.78377437591553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76313579082489</t>
+    <t xml:space="preserve">1.7631356716156</t>
   </si>
   <si>
     <t xml:space="preserve">1.76166188716888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78672301769257</t>
+    <t xml:space="preserve">1.78672289848328</t>
   </si>
   <si>
     <t xml:space="preserve">1.80588710308075</t>
@@ -1862,7 +1862,7 @@
     <t xml:space="preserve">1.83389675617218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87664914131165</t>
+    <t xml:space="preserve">1.87664902210236</t>
   </si>
   <si>
     <t xml:space="preserve">1.86927819252014</t>
@@ -1871,40 +1871,40 @@
     <t xml:space="preserve">1.84569013118744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83979368209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8324226140976</t>
+    <t xml:space="preserve">1.8397935628891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83242249488831</t>
   </si>
   <si>
     <t xml:space="preserve">1.84274184703827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83684527873993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89728736877441</t>
+    <t xml:space="preserve">1.83684504032135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8972874879837</t>
   </si>
   <si>
     <t xml:space="preserve">1.8899165391922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8825455904007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91055500507355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87075185775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80293905735016</t>
+    <t xml:space="preserve">1.88254582881927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91055488586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87075197696686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80293881893158</t>
   </si>
   <si>
     <t xml:space="preserve">1.80441308021545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79114532470703</t>
+    <t xml:space="preserve">1.79114520549774</t>
   </si>
   <si>
     <t xml:space="preserve">1.75576496124268</t>
@@ -1916,7 +1916,7 @@
     <t xml:space="preserve">1.81178390979767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83537113666534</t>
+    <t xml:space="preserve">1.83537101745605</t>
   </si>
   <si>
     <t xml:space="preserve">1.79556798934937</t>
@@ -1931,31 +1931,31 @@
     <t xml:space="preserve">1.79851627349854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79704177379608</t>
+    <t xml:space="preserve">1.79704201221466</t>
   </si>
   <si>
     <t xml:space="preserve">1.8073616027832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78082633018494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75429081916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7130126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70711600780487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.745445728302</t>
+    <t xml:space="preserve">1.78082609176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75429058074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71301257610321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70711612701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74544548988342</t>
   </si>
   <si>
     <t xml:space="preserve">1.76461005210876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77198100090027</t>
+    <t xml:space="preserve">1.77198088169098</t>
   </si>
   <si>
     <t xml:space="preserve">1.7778776884079</t>
@@ -1970,7 +1970,7 @@
     <t xml:space="preserve">1.66583895683289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67910647392273</t>
+    <t xml:space="preserve">1.67910659313202</t>
   </si>
   <si>
     <t xml:space="preserve">1.61129415035248</t>
@@ -1982,13 +1982,13 @@
     <t xml:space="preserve">1.53610992431641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55822241306305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54200661182404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53445529937744</t>
+    <t xml:space="preserve">1.55822253227234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54200673103333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53445518016815</t>
   </si>
   <si>
     <t xml:space="preserve">1.53596556186676</t>
@@ -2003,16 +2003,16 @@
     <t xml:space="preserve">1.55559909343719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5389860868454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54502725601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60543859004974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58429455757141</t>
+    <t xml:space="preserve">1.53898620605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54502737522125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60543870925903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58429443836212</t>
   </si>
   <si>
     <t xml:space="preserve">1.56768143177032</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">1.58882522583008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51028990745544</t>
+    <t xml:space="preserve">1.51029002666473</t>
   </si>
   <si>
     <t xml:space="preserve">1.51935243606567</t>
@@ -2033,13 +2033,13 @@
     <t xml:space="preserve">1.52690374851227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4717777967453</t>
+    <t xml:space="preserve">1.47177791595459</t>
   </si>
   <si>
     <t xml:space="preserve">1.47026753425598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47102272510529</t>
+    <t xml:space="preserve">1.471022605896</t>
   </si>
   <si>
     <t xml:space="preserve">1.45138907432556</t>
@@ -2051,16 +2051,16 @@
     <t xml:space="preserve">1.49367678165436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48385989665985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50047326087952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45894038677216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46800196170807</t>
+    <t xml:space="preserve">1.48386001586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50047314167023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45894026756287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46800208091736</t>
   </si>
   <si>
     <t xml:space="preserve">1.48990118503571</t>
@@ -2069,10 +2069,10 @@
     <t xml:space="preserve">1.48234963417053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48083961009979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53294491767883</t>
+    <t xml:space="preserve">1.4808394908905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53294503688812</t>
   </si>
   <si>
     <t xml:space="preserve">1.57523274421692</t>
@@ -2081,13 +2081,13 @@
     <t xml:space="preserve">1.56315052509308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52539348602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50424885749817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47328817844391</t>
+    <t xml:space="preserve">1.52539360523224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50424873828888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47328805923462</t>
   </si>
   <si>
     <t xml:space="preserve">1.4725329875946</t>
@@ -2096,7 +2096,7 @@
     <t xml:space="preserve">1.44912350177765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45365452766418</t>
+    <t xml:space="preserve">1.4536544084549</t>
   </si>
   <si>
     <t xml:space="preserve">1.46649169921875</t>
@@ -2105,13 +2105,13 @@
     <t xml:space="preserve">1.44987881183624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44610297679901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43779647350311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42269361019135</t>
+    <t xml:space="preserve">1.44610285758972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43779635429382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42269372940063</t>
   </si>
   <si>
     <t xml:space="preserve">1.42042827606201</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">1.42722451686859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41665244102478</t>
+    <t xml:space="preserve">1.41665256023407</t>
   </si>
   <si>
     <t xml:space="preserve">1.40683567523956</t>
@@ -2135,7 +2135,7 @@
     <t xml:space="preserve">1.3864461183548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28374695777893</t>
+    <t xml:space="preserve">1.28374707698822</t>
   </si>
   <si>
     <t xml:space="preserve">1.25354063510895</t>
@@ -2144,13 +2144,13 @@
     <t xml:space="preserve">1.25127518177032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20068073272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23617243766785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25278544425964</t>
+    <t xml:space="preserve">1.20068061351776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23617231845856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25278532505035</t>
   </si>
   <si>
     <t xml:space="preserve">1.22182464599609</t>
@@ -2171,7 +2171,7 @@
     <t xml:space="preserve">1.31395268440247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27090954780579</t>
+    <t xml:space="preserve">1.2709094285965</t>
   </si>
   <si>
     <t xml:space="preserve">1.28223669528961</t>
@@ -2189,7 +2189,7 @@
     <t xml:space="preserve">1.37436378002167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35246467590332</t>
+    <t xml:space="preserve">1.35246479511261</t>
   </si>
   <si>
     <t xml:space="preserve">1.40985631942749</t>
@@ -2198,16 +2198,16 @@
     <t xml:space="preserve">1.39852917194366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36681246757507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35095453262329</t>
+    <t xml:space="preserve">1.36681234836578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.350954413414</t>
   </si>
   <si>
     <t xml:space="preserve">1.35926115512848</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36454713344574</t>
+    <t xml:space="preserve">1.36454701423645</t>
   </si>
   <si>
     <t xml:space="preserve">1.33736193180084</t>
@@ -2228,10 +2228,10 @@
     <t xml:space="preserve">1.25505077838898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27468526363373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27997124195099</t>
+    <t xml:space="preserve">1.27468538284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27997136116028</t>
   </si>
   <si>
     <t xml:space="preserve">1.25958168506622</t>
@@ -2243,25 +2243,25 @@
     <t xml:space="preserve">1.26939928531647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28148150444031</t>
+    <t xml:space="preserve">1.2814816236496</t>
   </si>
   <si>
     <t xml:space="preserve">1.30413579940796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33660686016083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36077129840851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38871228694916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38267028331757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3517097234726</t>
+    <t xml:space="preserve">1.33660674095154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3607714176178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38871240615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38267040252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35170960426331</t>
   </si>
   <si>
     <t xml:space="preserve">1.35699558258057</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">1.36152648925781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36228168010712</t>
+    <t xml:space="preserve">1.36228156089783</t>
   </si>
   <si>
     <t xml:space="preserve">1.34113776683807</t>
@@ -2297,13 +2297,13 @@
     <t xml:space="preserve">1.62960302829742</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5827841758728</t>
+    <t xml:space="preserve">1.58278429508209</t>
   </si>
   <si>
     <t xml:space="preserve">1.57825350761414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58127403259277</t>
+    <t xml:space="preserve">1.58127391338348</t>
   </si>
   <si>
     <t xml:space="preserve">1.54653751850128</t>
@@ -2312,13 +2312,13 @@
     <t xml:space="preserve">1.53747594356537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52237284183502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55257856845856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60241782665253</t>
+    <t xml:space="preserve">1.52237296104431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55257844924927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60241794586182</t>
   </si>
   <si>
     <t xml:space="preserve">1.63111317157745</t>
@@ -2330,16 +2330,16 @@
     <t xml:space="preserve">1.62054145336151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54955804347992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57221233844757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61147964000702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64168584346771</t>
+    <t xml:space="preserve">1.54955780506134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57221221923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61147952079773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.641685962677</t>
   </si>
   <si>
     <t xml:space="preserve">1.61298990249634</t>
@@ -2351,7 +2351,7 @@
     <t xml:space="preserve">1.59184598922729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58731508255005</t>
+    <t xml:space="preserve">1.58731496334076</t>
   </si>
   <si>
     <t xml:space="preserve">1.6190310716629</t>
@@ -2366,7 +2366,7 @@
     <t xml:space="preserve">1.55861973762512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59788703918457</t>
+    <t xml:space="preserve">1.59788691997528</t>
   </si>
   <si>
     <t xml:space="preserve">1.60392808914185</t>
@@ -2378,16 +2378,16 @@
     <t xml:space="preserve">1.59939742088318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59637665748596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59033560752869</t>
+    <t xml:space="preserve">1.59637677669525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5903354883194</t>
   </si>
   <si>
     <t xml:space="preserve">1.52992451190948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51331114768982</t>
+    <t xml:space="preserve">1.51331126689911</t>
   </si>
   <si>
     <t xml:space="preserve">1.50953495502472</t>
@@ -2396,22 +2396,22 @@
     <t xml:space="preserve">1.52388334274292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54049634933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63866460323334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75948810577393</t>
+    <t xml:space="preserve">1.54049646854401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63866472244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75948786735535</t>
   </si>
   <si>
     <t xml:space="preserve">1.80630731582642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78365325927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83953380584717</t>
+    <t xml:space="preserve">1.78365314006805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83953368663788</t>
   </si>
   <si>
     <t xml:space="preserve">2.02983069419861</t>
@@ -2420,13 +2420,13 @@
     <t xml:space="preserve">2.06909799575806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94827485084534</t>
+    <t xml:space="preserve">1.94827473163605</t>
   </si>
   <si>
     <t xml:space="preserve">1.89088308811188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7791223526001</t>
+    <t xml:space="preserve">1.77912223339081</t>
   </si>
   <si>
     <t xml:space="preserve">1.77308118343353</t>
@@ -2435,7 +2435,7 @@
     <t xml:space="preserve">1.81687951087952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70813834667206</t>
+    <t xml:space="preserve">1.70813846588135</t>
   </si>
   <si>
     <t xml:space="preserve">1.4800843000412</t>
@@ -2453,10 +2453,10 @@
     <t xml:space="preserve">1.19917047023773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18406772613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959789395332336</t>
+    <t xml:space="preserve">1.18406784534454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959789335727692</t>
   </si>
   <si>
     <t xml:space="preserve">0.995280861854553</t>
@@ -2468,40 +2468,40 @@
     <t xml:space="preserve">0.945441544055939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.962809801101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01869094371796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04361069202423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990750193595886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07155084609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07910227775574</t>
+    <t xml:space="preserve">0.962809860706329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01869106292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04361057281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990750014781952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07155096530914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07910239696503</t>
   </si>
   <si>
     <t xml:space="preserve">1.06777513027191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01944601535797</t>
+    <t xml:space="preserve">1.01944625377655</t>
   </si>
   <si>
     <t xml:space="preserve">0.999811708927155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0413453578949</t>
+    <t xml:space="preserve">1.04134523868561</t>
   </si>
   <si>
     <t xml:space="preserve">1.02699756622314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10628747940063</t>
+    <t xml:space="preserve">1.10628736019135</t>
   </si>
   <si>
     <t xml:space="preserve">1.05720329284668</t>
@@ -2513,22 +2513,22 @@
     <t xml:space="preserve">1.13875913619995</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20219099521637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16745448112488</t>
+    <t xml:space="preserve">1.20219111442566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16745460033417</t>
   </si>
   <si>
     <t xml:space="preserve">1.16594421863556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08740890026093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06701993942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09420502185822</t>
+    <t xml:space="preserve">1.08740878105164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0670200586319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0942051410675</t>
   </si>
   <si>
     <t xml:space="preserve">1.06324422359467</t>
@@ -2540,61 +2540,61 @@
     <t xml:space="preserve">1.07834708690643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08212280273438</t>
+    <t xml:space="preserve">1.08212292194366</t>
   </si>
   <si>
     <t xml:space="preserve">1.07457149028778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08665382862091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0926947593689</t>
+    <t xml:space="preserve">1.08665370941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09269487857819</t>
   </si>
   <si>
     <t xml:space="preserve">1.03756964206696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07306134700775</t>
+    <t xml:space="preserve">1.07306122779846</t>
   </si>
   <si>
     <t xml:space="preserve">1.04965174198151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03530406951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04436588287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04285562038422</t>
+    <t xml:space="preserve">1.03530418872833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04436576366425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04285550117493</t>
   </si>
   <si>
     <t xml:space="preserve">1.01189470291138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.985464096069336</t>
+    <t xml:space="preserve">0.985464155673981</t>
   </si>
   <si>
     <t xml:space="preserve">0.970361232757568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989239871501923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94317626953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926563143730164</t>
+    <t xml:space="preserve">0.989239752292633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943176209926605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926563084125519</t>
   </si>
   <si>
     <t xml:space="preserve">0.921277046203613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.913725674152374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986219227313995</t>
+    <t xml:space="preserve">0.913725733757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986219108104706</t>
   </si>
   <si>
     <t xml:space="preserve">0.997546255588531</t>
@@ -2603,31 +2603,31 @@
     <t xml:space="preserve">1.058713555336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09722554683685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10251152515411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13422775268555</t>
+    <t xml:space="preserve">1.09722566604614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1025116443634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13422763347626</t>
   </si>
   <si>
     <t xml:space="preserve">1.18180227279663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21502840518951</t>
+    <t xml:space="preserve">1.21502816677094</t>
   </si>
   <si>
     <t xml:space="preserve">1.23919296264648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19992554187775</t>
+    <t xml:space="preserve">1.19992566108704</t>
   </si>
   <si>
     <t xml:space="preserve">1.18935358524323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14782071113586</t>
+    <t xml:space="preserve">1.14782094955444</t>
   </si>
   <si>
     <t xml:space="preserve">1.16820979118347</t>
@@ -2639,13 +2639,13 @@
     <t xml:space="preserve">1.16216850280762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19312930107117</t>
+    <t xml:space="preserve">1.19312942028046</t>
   </si>
   <si>
     <t xml:space="preserve">1.17047524452209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24598920345306</t>
+    <t xml:space="preserve">1.24598908424377</t>
   </si>
   <si>
     <t xml:space="preserve">1.29280865192413</t>
@@ -2654,22 +2654,22 @@
     <t xml:space="preserve">1.36303675174713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40381515026093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41136646270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39399826526642</t>
+    <t xml:space="preserve">1.40381503105164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41136658191681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39399838447571</t>
   </si>
   <si>
     <t xml:space="preserve">1.39928424358368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4015496969223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40305995941162</t>
+    <t xml:space="preserve">1.40154957771301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40306007862091</t>
   </si>
   <si>
     <t xml:space="preserve">1.41589736938477</t>
@@ -2678,7 +2678,7 @@
     <t xml:space="preserve">1.49292171001434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44836854934692</t>
+    <t xml:space="preserve">1.44836843013763</t>
   </si>
   <si>
     <t xml:space="preserve">1.48763573169708</t>
@@ -2687,37 +2687,37 @@
     <t xml:space="preserve">1.47630858421326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46498155593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39626383781433</t>
+    <t xml:space="preserve">1.46498143672943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39626371860504</t>
   </si>
   <si>
     <t xml:space="preserve">1.37662935256958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34264802932739</t>
+    <t xml:space="preserve">1.3426479101181</t>
   </si>
   <si>
     <t xml:space="preserve">1.36907780170441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43175530433655</t>
+    <t xml:space="preserve">1.43175542354584</t>
   </si>
   <si>
     <t xml:space="preserve">1.445347905159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47479832172394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48461532592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55106842517853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52086281776428</t>
+    <t xml:space="preserve">1.47479844093323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48461520671844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55106830596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5208625793457</t>
   </si>
   <si>
     <t xml:space="preserve">1.37889468669891</t>
@@ -2726,13 +2726,13 @@
     <t xml:space="preserve">1.3781396150589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34415817260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37209856510162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39475333690643</t>
+    <t xml:space="preserve">1.34415829181671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37209844589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39475345611572</t>
   </si>
   <si>
     <t xml:space="preserve">1.37964999675751</t>
@@ -2744,22 +2744,22 @@
     <t xml:space="preserve">1.3924880027771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32150399684906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31848347187042</t>
+    <t xml:space="preserve">1.32150411605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31848359107971</t>
   </si>
   <si>
     <t xml:space="preserve">1.34340310096741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30036008358002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32376933097839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33434152603149</t>
+    <t xml:space="preserve">1.30036020278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32376945018768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3343414068222</t>
   </si>
   <si>
     <t xml:space="preserve">1.39777398109436</t>
@@ -2786,46 +2786,46 @@
     <t xml:space="preserve">1.33585166931152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27393019199371</t>
+    <t xml:space="preserve">1.27393007278442</t>
   </si>
   <si>
     <t xml:space="preserve">1.26486837863922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22484505176544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24145817756653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11761462688446</t>
+    <t xml:space="preserve">1.22484517097473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24145829677582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11761450767517</t>
   </si>
   <si>
     <t xml:space="preserve">1.10779762268066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13800406455994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22711050510406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24221336841583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2384375333786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22862100601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44232738018036</t>
+    <t xml:space="preserve">1.13800394535065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22711062431335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24221348762512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23843765258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22862088680267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44232726097107</t>
   </si>
   <si>
     <t xml:space="preserve">1.43251049518585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50273859500885</t>
+    <t xml:space="preserve">1.50273847579956</t>
   </si>
   <si>
     <t xml:space="preserve">1.55408883094788</t>
@@ -2834,7 +2834,7 @@
     <t xml:space="preserve">1.81234848499298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78214287757874</t>
+    <t xml:space="preserve">1.78214311599731</t>
   </si>
   <si>
     <t xml:space="preserve">1.77459144592285</t>
@@ -2843,16 +2843,16 @@
     <t xml:space="preserve">1.75797760486603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69303560256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7217310667038</t>
+    <t xml:space="preserve">1.69303572177887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72173094749451</t>
   </si>
   <si>
     <t xml:space="preserve">1.68548405170441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70209717750549</t>
+    <t xml:space="preserve">1.70209729671478</t>
   </si>
   <si>
     <t xml:space="preserve">1.7036075592041</t>
@@ -2861,28 +2861,28 @@
     <t xml:space="preserve">1.73079264163971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72777223587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69907653331757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66887104511261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66282999515533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67944300174713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66131949424744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6764223575592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64470636844635</t>
+    <t xml:space="preserve">1.72777211666107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69907665252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6688711643219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66282987594604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67944288253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66131961345673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67642247676849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64470648765564</t>
   </si>
   <si>
     <t xml:space="preserve">1.61601042747498</t>
@@ -2900,28 +2900,28 @@
     <t xml:space="preserve">1.66434013843536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74438524246216</t>
+    <t xml:space="preserve">1.74438512325287</t>
   </si>
   <si>
     <t xml:space="preserve">1.77761209011078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.756467461586</t>
+    <t xml:space="preserve">1.75646758079529</t>
   </si>
   <si>
     <t xml:space="preserve">1.7202205657959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73683369159698</t>
+    <t xml:space="preserve">1.7368335723877</t>
   </si>
   <si>
     <t xml:space="preserve">1.69454598426819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6522581577301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67491221427917</t>
+    <t xml:space="preserve">1.65225827693939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67491233348846</t>
   </si>
   <si>
     <t xml:space="preserve">1.65376830101013</t>
@@ -2930,19 +2930,19 @@
     <t xml:space="preserve">1.63715434074402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57070195674896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59486651420593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62205147743225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7474057674408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8863525390625</t>
+    <t xml:space="preserve">1.57070183753967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59486639499664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62205159664154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74740564823151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88635241985321</t>
   </si>
   <si>
     <t xml:space="preserve">1.85765719413757</t>
@@ -2951,19 +2951,19 @@
     <t xml:space="preserve">1.88031136989594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86822879314423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85463666915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88937318325043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85010552406311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80932796001434</t>
+    <t xml:space="preserve">1.86822915077209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85463654994965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88937306404114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8501056432724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80932807922363</t>
   </si>
   <si>
     <t xml:space="preserve">1.83047199249268</t>
@@ -2984,25 +2984,25 @@
     <t xml:space="preserve">1.80177640914917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84557473659515</t>
+    <t xml:space="preserve">1.84557497501373</t>
   </si>
   <si>
     <t xml:space="preserve">1.83500266075134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82745134830475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87124943733215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86369800567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92713069915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97999060153961</t>
+    <t xml:space="preserve">1.82745146751404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87124967575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86369836330414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.927130818367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97999048233032</t>
   </si>
   <si>
     <t xml:space="preserve">2.05399513244629</t>
@@ -3017,13 +3017,13 @@
     <t xml:space="preserve">2.15216422080994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12950897216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1068549156189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15518450737</t>
+    <t xml:space="preserve">2.12950921058655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10685515403748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15518474578857</t>
   </si>
   <si>
     <t xml:space="preserve">2.13555026054382</t>
@@ -3038,19 +3038,19 @@
     <t xml:space="preserve">2.15669512748718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1899209022522</t>
+    <t xml:space="preserve">2.18992114067078</t>
   </si>
   <si>
     <t xml:space="preserve">2.18690061569214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16877746582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17028784751892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23522996902466</t>
+    <t xml:space="preserve">2.16877722740173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17028760910034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23522973060608</t>
   </si>
   <si>
     <t xml:space="preserve">2.24731206893921</t>
@@ -3062,7 +3062,7 @@
     <t xml:space="preserve">2.30168294906616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23674011230469</t>
+    <t xml:space="preserve">2.23673987388611</t>
   </si>
   <si>
     <t xml:space="preserve">2.2458016872406</t>
@@ -3080,16 +3080,16 @@
     <t xml:space="preserve">2.48140692710876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54937052726746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64300799369812</t>
+    <t xml:space="preserve">2.54937076568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6430082321167</t>
   </si>
   <si>
     <t xml:space="preserve">2.61733317375183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60223054885864</t>
+    <t xml:space="preserve">2.60223078727722</t>
   </si>
   <si>
     <t xml:space="preserve">2.70190978050232</t>
@@ -3107,40 +3107,40 @@
     <t xml:space="preserve">2.8650209903717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86200046539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94204640388489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94506669044495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93147373199463</t>
+    <t xml:space="preserve">2.86200070381165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94204592704773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94506645202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93147397041321</t>
   </si>
   <si>
     <t xml:space="preserve">2.97980332374573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96621012687683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9571487903595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97829270362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08411288261414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07337737083435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05804085731506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15312552452087</t>
+    <t xml:space="preserve">2.96621036529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95714902877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97829294204712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08411312103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07337713241577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05804061889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15312528610229</t>
   </si>
   <si>
     <t xml:space="preserve">3.0917809009552</t>
@@ -3173,7 +3173,7 @@
     <t xml:space="preserve">2.96602392196655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95988965034485</t>
+    <t xml:space="preserve">2.95988941192627</t>
   </si>
   <si>
     <t xml:space="preserve">2.9445526599884</t>
@@ -3188,28 +3188,28 @@
     <t xml:space="preserve">2.83106517791748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80192565917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80039262771606</t>
+    <t xml:space="preserve">2.80192589759827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80039238929749</t>
   </si>
   <si>
     <t xml:space="preserve">2.73598051071167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7942578792572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79272413253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83719968795776</t>
+    <t xml:space="preserve">2.79425764083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79272437095642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83719944953918</t>
   </si>
   <si>
     <t xml:space="preserve">2.76665258407593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80499291419983</t>
+    <t xml:space="preserve">2.80499315261841</t>
   </si>
   <si>
     <t xml:space="preserve">2.79119038581848</t>
@@ -3224,7 +3224,7 @@
     <t xml:space="preserve">2.7513165473938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72371172904968</t>
+    <t xml:space="preserve">2.7237114906311</t>
   </si>
   <si>
     <t xml:space="preserve">2.84333419799805</t>
@@ -3242,7 +3242,7 @@
     <t xml:space="preserve">2.67310166358948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58108472824097</t>
+    <t xml:space="preserve">2.58108496665955</t>
   </si>
   <si>
     <t xml:space="preserve">2.66543364524841</t>
@@ -3257,7 +3257,7 @@
     <t xml:space="preserve">2.783522605896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92614936828613</t>
+    <t xml:space="preserve">2.92614912986755</t>
   </si>
   <si>
     <t xml:space="preserve">2.88934254646301</t>
@@ -3275,16 +3275,16 @@
     <t xml:space="preserve">2.86020374298096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85867023468018</t>
+    <t xml:space="preserve">2.85867047309875</t>
   </si>
   <si>
     <t xml:space="preserve">2.83873343467712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84486746788025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91848087310791</t>
+    <t xml:space="preserve">2.84486770629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91848111152649</t>
   </si>
   <si>
     <t xml:space="preserve">2.95222163200378</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">2.90467858314514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96755790710449</t>
+    <t xml:space="preserve">2.96755766868591</t>
   </si>
   <si>
     <t xml:space="preserve">2.92768287658691</t>
@@ -3320,16 +3320,16 @@
     <t xml:space="preserve">2.99976348876953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0074315071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98289370536804</t>
+    <t xml:space="preserve">3.00743126869202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98289346694946</t>
   </si>
   <si>
     <t xml:space="preserve">2.98596096038818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95375514030457</t>
+    <t xml:space="preserve">2.95375490188599</t>
   </si>
   <si>
     <t xml:space="preserve">2.99056172370911</t>
@@ -3341,10 +3341,10 @@
     <t xml:space="preserve">2.95682191848755</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90007781982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84180068969727</t>
+    <t xml:space="preserve">2.9000780582428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84180045127869</t>
   </si>
   <si>
     <t xml:space="preserve">2.87400650978088</t>
@@ -3371,10 +3371,10 @@
     <t xml:space="preserve">2.79732513427734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80652689933777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81419491767883</t>
+    <t xml:space="preserve">2.80652666091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81419467926025</t>
   </si>
   <si>
     <t xml:space="preserve">2.78045535087585</t>
@@ -3389,10 +3389,10 @@
     <t xml:space="preserve">2.823397397995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93074989318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90314507484436</t>
+    <t xml:space="preserve">2.93075013160706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90314531326294</t>
   </si>
   <si>
     <t xml:space="preserve">2.88320803642273</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">2.87554001808167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9062123298645</t>
+    <t xml:space="preserve">2.90621256828308</t>
   </si>
   <si>
     <t xml:space="preserve">2.95528864860535</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">2.99669623374939</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02890205383301</t>
+    <t xml:space="preserve">3.02890229225159</t>
   </si>
   <si>
     <t xml:space="preserve">3.03657007217407</t>
@@ -3464,7 +3464,7 @@
     <t xml:space="preserve">2.69917392730713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70684170722961</t>
+    <t xml:space="preserve">2.70684194564819</t>
   </si>
   <si>
     <t xml:space="preserve">2.66083264350891</t>
@@ -3473,10 +3473,10 @@
     <t xml:space="preserve">2.76051831245422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7114429473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58875274658203</t>
+    <t xml:space="preserve">2.71144270896912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58875298500061</t>
   </si>
   <si>
     <t xml:space="preserve">2.73137950897217</t>
@@ -3503,10 +3503,10 @@
     <t xml:space="preserve">2.71911072731018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69610667228699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66850113868713</t>
+    <t xml:space="preserve">2.69610643386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66850090026855</t>
   </si>
   <si>
     <t xml:space="preserve">2.75438404083252</t>
@@ -3515,19 +3515,19 @@
     <t xml:space="preserve">2.8249306678772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85406970977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89701080322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97829294204712</t>
+    <t xml:space="preserve">2.85406947135925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89701056480408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9782931804657</t>
   </si>
   <si>
     <t xml:space="preserve">2.86327123641968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94148564338684</t>
+    <t xml:space="preserve">2.94148540496826</t>
   </si>
   <si>
     <t xml:space="preserve">3.03503656387329</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">2.92445588111877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90142893791199</t>
+    <t xml:space="preserve">2.90142869949341</t>
   </si>
   <si>
     <t xml:space="preserve">3.05187320709229</t>
@@ -3566,10 +3566,10 @@
     <t xml:space="preserve">3.07029485702515</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15472817420959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08871674537659</t>
+    <t xml:space="preserve">3.15472841262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08871698379517</t>
   </si>
   <si>
     <t xml:space="preserve">3.19771218299866</t>
@@ -3581,13 +3581,13 @@
     <t xml:space="preserve">3.18850111961365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2529776096344</t>
+    <t xml:space="preserve">3.25297737121582</t>
   </si>
   <si>
     <t xml:space="preserve">3.16547417640686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09485745429993</t>
+    <t xml:space="preserve">3.09485769271851</t>
   </si>
   <si>
     <t xml:space="preserve">2.94748306274414</t>
@@ -3602,10 +3602,10 @@
     <t xml:space="preserve">2.72028136253357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55602025985718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58979368209839</t>
+    <t xml:space="preserve">2.55602049827576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58979392051697</t>
   </si>
   <si>
     <t xml:space="preserve">2.54066896438599</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">2.24592089653015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33342432975769</t>
+    <t xml:space="preserve">2.33342409133911</t>
   </si>
   <si>
     <t xml:space="preserve">2.53452849388123</t>
@@ -3635,7 +3635,7 @@
     <t xml:space="preserve">2.56983685493469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75098419189453</t>
+    <t xml:space="preserve">2.75098443031311</t>
   </si>
   <si>
     <t xml:space="preserve">2.72488689422607</t>
@@ -3644,7 +3644,7 @@
     <t xml:space="preserve">2.76326560974121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78015232086182</t>
+    <t xml:space="preserve">2.78015208244324</t>
   </si>
   <si>
     <t xml:space="preserve">2.82927680015564</t>
@@ -3656,7 +3656,7 @@
     <t xml:space="preserve">2.79243326187134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73870301246643</t>
+    <t xml:space="preserve">2.73870325088501</t>
   </si>
   <si>
     <t xml:space="preserve">2.79703879356384</t>
@@ -3668,13 +3668,13 @@
     <t xml:space="preserve">2.92906141281128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85383892059326</t>
+    <t xml:space="preserve">2.85383915901184</t>
   </si>
   <si>
     <t xml:space="preserve">2.8922176361084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91831541061401</t>
+    <t xml:space="preserve">2.91831564903259</t>
   </si>
   <si>
     <t xml:space="preserve">2.89835858345032</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">2.94594788551331</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8722608089447</t>
+    <t xml:space="preserve">2.87226104736328</t>
   </si>
   <si>
     <t xml:space="preserve">2.93980741500854</t>
@@ -3710,7 +3710,7 @@
     <t xml:space="preserve">2.90603399276733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92752599716187</t>
+    <t xml:space="preserve">2.92752623558044</t>
   </si>
   <si>
     <t xml:space="preserve">2.91678047180176</t>
@@ -3719,25 +3719,25 @@
     <t xml:space="preserve">2.90296387672424</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90756940841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79089784622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78936314582825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75712466239929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68343782424927</t>
+    <t xml:space="preserve">2.90756916999817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7908980846405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78936290740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75712490081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68343806266785</t>
   </si>
   <si>
     <t xml:space="preserve">2.78168749809265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80624938011169</t>
+    <t xml:space="preserve">2.80624961853027</t>
   </si>
   <si>
     <t xml:space="preserve">2.82467126846313</t>
@@ -3752,7 +3752,7 @@
     <t xml:space="preserve">2.86151504516602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85230398178101</t>
+    <t xml:space="preserve">2.85230422019958</t>
   </si>
   <si>
     <t xml:space="preserve">2.81239008903503</t>
@@ -71161,7 +71161,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6912847222</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>739308</v>
@@ -71182,6 +71182,32 @@
         <v>1962</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.6913078704</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>435442</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>14.0649995803833</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>13.8900003433228</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>13.9200000762939</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>13.9700002670288</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>1962</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BPSO.MI.xlsx
+++ b/data/BPSO.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1966" uniqueCount="1966">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1967" uniqueCount="1967">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">2.71246600151062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63611674308777</t>
+    <t xml:space="preserve">2.63611698150635</t>
   </si>
   <si>
     <t xml:space="preserve">2.60835409164429</t>
@@ -68,64 +68,64 @@
     <t xml:space="preserve">2.61113023757935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51257061958313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4556565284729</t>
+    <t xml:space="preserve">2.51257038116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45565629005432</t>
   </si>
   <si>
     <t xml:space="preserve">2.2668662071228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38069534301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40568280220032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36542582511902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51951146125793</t>
+    <t xml:space="preserve">2.38069558143616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40568208694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36542558670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51951122283936</t>
   </si>
   <si>
     <t xml:space="preserve">2.44455122947693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35570859909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43899869918823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40429425239563</t>
+    <t xml:space="preserve">2.35570907592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43899846076965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40429449081421</t>
   </si>
   <si>
     <t xml:space="preserve">2.32100486755371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22105717658997</t>
+    <t xml:space="preserve">2.22105741500854</t>
   </si>
   <si>
     <t xml:space="preserve">2.23216247558594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20995187759399</t>
+    <t xml:space="preserve">2.20995211601257</t>
   </si>
   <si>
     <t xml:space="preserve">2.04059600830078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06280636787415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14331984519958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07668805122375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18218803405762</t>
+    <t xml:space="preserve">2.06280660629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14332008361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07668828964233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18218851089478</t>
   </si>
   <si>
     <t xml:space="preserve">2.22522163391113</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">2.18635296821594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17663598060608</t>
+    <t xml:space="preserve">2.17663550376892</t>
   </si>
   <si>
     <t xml:space="preserve">2.21550464630127</t>
@@ -167,34 +167,34 @@
     <t xml:space="preserve">2.37514281272888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2418794631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26270151138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25020861625671</t>
+    <t xml:space="preserve">2.24187970161438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26270174980164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25020837783813</t>
   </si>
   <si>
     <t xml:space="preserve">2.31961679458618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4334454536438</t>
+    <t xml:space="preserve">2.43344521522522</t>
   </si>
   <si>
     <t xml:space="preserve">2.35848498344421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30156970024109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34599161148071</t>
+    <t xml:space="preserve">2.30156993865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34599208831787</t>
   </si>
   <si>
     <t xml:space="preserve">2.35987329483032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39318871498108</t>
+    <t xml:space="preserve">2.39318895339966</t>
   </si>
   <si>
     <t xml:space="preserve">2.29324126243591</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">2.23771500587463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18774080276489</t>
+    <t xml:space="preserve">2.18774127960205</t>
   </si>
   <si>
     <t xml:space="preserve">2.13915586471558</t>
@@ -212,67 +212,67 @@
     <t xml:space="preserve">2.14748454093933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1211097240448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06974720954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01283311843872</t>
+    <t xml:space="preserve">2.12110948562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06974697113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01283288002014</t>
   </si>
   <si>
     <t xml:space="preserve">2.01838541030884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07113575935364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11694526672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12527394294739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22799777984619</t>
+    <t xml:space="preserve">2.07113552093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11694502830505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12527418136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22799801826477</t>
   </si>
   <si>
     <t xml:space="preserve">2.30295825004578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23910307884216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2904646396637</t>
+    <t xml:space="preserve">2.23910355567932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29046511650085</t>
   </si>
   <si>
     <t xml:space="preserve">2.33211016654968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32655763626099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27935934066772</t>
+    <t xml:space="preserve">2.32655787467957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2793595790863</t>
   </si>
   <si>
     <t xml:space="preserve">2.32378125190735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30851125717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26131391525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.234938621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15720152854919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11139273643494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08224034309387</t>
+    <t xml:space="preserve">2.30851101875305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26131343841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23493885993958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15720129013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11139249801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08224081993103</t>
   </si>
   <si>
     <t xml:space="preserve">2.09889912605286</t>
@@ -281,10 +281,10 @@
     <t xml:space="preserve">2.08918213844299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10583996772766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04892468452454</t>
+    <t xml:space="preserve">2.10583972930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04892492294312</t>
   </si>
   <si>
     <t xml:space="preserve">2.03781962394714</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">2.06558275222778</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03226733207703</t>
+    <t xml:space="preserve">2.03226685523987</t>
   </si>
   <si>
     <t xml:space="preserve">2.07252359390259</t>
@@ -305,88 +305,88 @@
     <t xml:space="preserve">2.05156707763672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12691879272461</t>
+    <t xml:space="preserve">2.12691855430603</t>
   </si>
   <si>
     <t xml:space="preserve">2.19942760467529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15393233299255</t>
+    <t xml:space="preserve">2.15393209457397</t>
   </si>
   <si>
     <t xml:space="preserve">2.17525792121887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15535402297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09279704093933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07147145271301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99896204471588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95773220062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87669312953949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98901009559631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93640637397766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94351470470428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84114968776703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78143703937531</t>
+    <t xml:space="preserve">2.15535378456116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09279680252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07147121429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99896228313446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95773231983185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8766930103302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98901057243347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93640601634979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94351482391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84114956855774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78143692016602</t>
   </si>
   <si>
     <t xml:space="preserve">1.751580119133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72598886489868</t>
+    <t xml:space="preserve">1.72598898410797</t>
   </si>
   <si>
     <t xml:space="preserve">1.64210617542267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69613254070282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77006232738495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81129324436188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78001439571381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89375352859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63499736785889</t>
+    <t xml:space="preserve">1.69613265991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77006220817566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8112930059433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78001463413239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89375364780426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63499760627747</t>
   </si>
   <si>
     <t xml:space="preserve">1.5653327703476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66911971569061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65632355213165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6392627954483</t>
+    <t xml:space="preserve">1.66911959648132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65632343292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63926267623901</t>
   </si>
   <si>
     <t xml:space="preserve">1.63641929626465</t>
@@ -401,142 +401,142 @@
     <t xml:space="preserve">1.52552378177643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53121066093445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63784086704254</t>
+    <t xml:space="preserve">1.53121078014374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63784110546112</t>
   </si>
   <si>
     <t xml:space="preserve">1.67196321487427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69471085071564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67054152488708</t>
+    <t xml:space="preserve">1.69471096992493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6705414056778</t>
   </si>
   <si>
     <t xml:space="preserve">1.74304974079132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70892810821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72172367572784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77574944496155</t>
+    <t xml:space="preserve">1.70892822742462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72172379493713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77574920654297</t>
   </si>
   <si>
     <t xml:space="preserve">1.76721906661987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72741079330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69755458831787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72456729412079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71888041496277</t>
+    <t xml:space="preserve">1.72741055488586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69755446910858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72456741333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71888053417206</t>
   </si>
   <si>
     <t xml:space="preserve">1.66343283653259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55395901203156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57528495788574</t>
+    <t xml:space="preserve">1.55395889282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57528483867645</t>
   </si>
   <si>
     <t xml:space="preserve">1.5212584733963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63357591629028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6591671705246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64779317378998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68760204315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71461498737335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70608472824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70039796829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74447154998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70750665664673</t>
+    <t xml:space="preserve">1.6335756778717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65916681289673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64779329299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68760228157043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71461486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70608460903168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70039772987366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7444714307785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70750653743744</t>
   </si>
   <si>
     <t xml:space="preserve">1.72030186653137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7316757440567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78285884857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77859282493591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.771484375</t>
+    <t xml:space="preserve">1.73167586326599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78285872936249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7785929441452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77148425579071</t>
   </si>
   <si>
     <t xml:space="preserve">1.76437544822693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75584554672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76295387744904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74162781238556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76864075660706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74873661994934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73451912403107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78428053855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85252356529236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84967982769012</t>
+    <t xml:space="preserve">1.75584518909454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76295399665833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74162793159485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76864087581635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74873673915863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73451936244965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78428030014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85252368450165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8496800661087</t>
   </si>
   <si>
     <t xml:space="preserve">1.81271529197693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8354629278183</t>
+    <t xml:space="preserve">1.83546268939972</t>
   </si>
   <si>
     <t xml:space="preserve">1.84825837612152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85963225364685</t>
+    <t xml:space="preserve">1.85963237285614</t>
   </si>
   <si>
     <t xml:space="preserve">1.94778025150299</t>
@@ -545,25 +545,25 @@
     <t xml:space="preserve">1.9762145280838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09848380088806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10843634605408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07573628425598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08568859100342</t>
+    <t xml:space="preserve">2.09848427772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1084361076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07573652267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08568835258484</t>
   </si>
   <si>
     <t xml:space="preserve">2.08853197097778</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09706258773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16104102134705</t>
+    <t xml:space="preserve">2.09706234931946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16104078292847</t>
   </si>
   <si>
     <t xml:space="preserve">2.18236660957336</t>
@@ -575,70 +575,70 @@
     <t xml:space="preserve">2.00038409233093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0387716293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00891447067261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05298852920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06294107437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11554479598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12549662590027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16246271133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15961909294128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13260531425476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08142328262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03592777252197</t>
+    <t xml:space="preserve">2.03877139091492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00891399383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0529887676239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06294083595276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11554503440857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12549686431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16246247291565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15961933135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13260579109192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08142280578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03592801094055</t>
   </si>
   <si>
     <t xml:space="preserve">2.07715821266174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09990549087524</t>
+    <t xml:space="preserve">2.09990572929382</t>
   </si>
   <si>
     <t xml:space="preserve">2.08995366096497</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01033568382263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12407517433167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10417056083679</t>
+    <t xml:space="preserve">2.01033616065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12407493591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10417127609253</t>
   </si>
   <si>
     <t xml:space="preserve">2.07289290428162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16814947128296</t>
+    <t xml:space="preserve">2.16814970970154</t>
   </si>
   <si>
     <t xml:space="preserve">2.27478003501892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37430167198181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2634060382843</t>
+    <t xml:space="preserve">2.37430119514465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26340627670288</t>
   </si>
   <si>
     <t xml:space="preserve">2.23354887962341</t>
@@ -647,28 +647,28 @@
     <t xml:space="preserve">2.27193641662598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23212695121765</t>
+    <t xml:space="preserve">2.23212766647339</t>
   </si>
   <si>
     <t xml:space="preserve">2.1781017780304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16957092285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23639273643494</t>
+    <t xml:space="preserve">2.1695716381073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23639249801636</t>
   </si>
   <si>
     <t xml:space="preserve">2.22217512130737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21791005134583</t>
+    <t xml:space="preserve">2.21790981292725</t>
   </si>
   <si>
     <t xml:space="preserve">2.2051146030426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22359681129456</t>
+    <t xml:space="preserve">2.22359704971313</t>
   </si>
   <si>
     <t xml:space="preserve">2.26482748985291</t>
@@ -677,19 +677,19 @@
     <t xml:space="preserve">2.31032299995422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31743168830872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34302282333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34160113334656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30463624000549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.297527551651</t>
+    <t xml:space="preserve">2.31743144989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34302306175232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34160137176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30463600158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29752731323242</t>
   </si>
   <si>
     <t xml:space="preserve">2.29610586166382</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">2.34017968177795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40273594856262</t>
+    <t xml:space="preserve">2.4027361869812</t>
   </si>
   <si>
     <t xml:space="preserve">2.41695356369019</t>
@@ -713,34 +713,34 @@
     <t xml:space="preserve">2.45249676704407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4112663269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41553163528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4240620136261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44396638870239</t>
+    <t xml:space="preserve">2.41126680374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.415531873703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42406249046326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44396615028381</t>
   </si>
   <si>
     <t xml:space="preserve">2.35439658164978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33733606338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3302276134491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3643491268158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32738399505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28188824653625</t>
+    <t xml:space="preserve">2.33733582496643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33022737503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36434888839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32738375663757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28188872337341</t>
   </si>
   <si>
     <t xml:space="preserve">2.30037093162537</t>
@@ -749,19 +749,19 @@
     <t xml:space="preserve">2.32311868667603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33449220657349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30890130996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29894924163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25629734992981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12834048271179</t>
+    <t xml:space="preserve">2.33449244499207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30890154838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29894948005676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25629711151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12834024429321</t>
   </si>
   <si>
     <t xml:space="preserve">2.13402724266052</t>
@@ -770,19 +770,19 @@
     <t xml:space="preserve">2.28473234176636</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22928404808044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27335810661316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27904486656189</t>
+    <t xml:space="preserve">2.22928380966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27335786819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27904510498047</t>
   </si>
   <si>
     <t xml:space="preserve">2.31316661834717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33875775337219</t>
+    <t xml:space="preserve">2.33875751495361</t>
   </si>
   <si>
     <t xml:space="preserve">2.37856698036194</t>
@@ -791,10 +791,10 @@
     <t xml:space="preserve">2.32880544662476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.367192029953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34870958328247</t>
+    <t xml:space="preserve">2.36719226837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34870982170105</t>
   </si>
   <si>
     <t xml:space="preserve">2.29468417167664</t>
@@ -806,13 +806,13 @@
     <t xml:space="preserve">2.28757548332214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32027530670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2833104133606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29041862487793</t>
+    <t xml:space="preserve">2.32027506828308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28331017494202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29041886329651</t>
   </si>
   <si>
     <t xml:space="preserve">2.29326224327087</t>
@@ -824,7 +824,7 @@
     <t xml:space="preserve">2.35581827163696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31174445152283</t>
+    <t xml:space="preserve">2.31174468994141</t>
   </si>
   <si>
     <t xml:space="preserve">2.3316490650177</t>
@@ -836,46 +836,46 @@
     <t xml:space="preserve">2.43117070198059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42974901199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49799299240112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46387100219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48661851882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51647520065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51789712905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56907916069031</t>
+    <t xml:space="preserve">2.42974877357483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49799275398254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46387028694153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48661828041077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51647543907166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51789689064026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56907963752747</t>
   </si>
   <si>
     <t xml:space="preserve">2.53353595733643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48803997039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50510168075562</t>
+    <t xml:space="preserve">2.48803973197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50510144233704</t>
   </si>
   <si>
     <t xml:space="preserve">2.5079448223114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50936627388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50652289390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55486154556274</t>
+    <t xml:space="preserve">2.50936651229858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5065233707428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55486178398132</t>
   </si>
   <si>
     <t xml:space="preserve">2.57221221923828</t>
@@ -884,13 +884,13 @@
     <t xml:space="preserve">2.63293862342834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65607333183289</t>
+    <t xml:space="preserve">2.65607309341431</t>
   </si>
   <si>
     <t xml:space="preserve">2.70667862892151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56642913818359</t>
+    <t xml:space="preserve">2.56642889976501</t>
   </si>
   <si>
     <t xml:space="preserve">2.52594375610352</t>
@@ -902,58 +902,58 @@
     <t xml:space="preserve">2.47389245033264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52160620689392</t>
+    <t xml:space="preserve">2.5216064453125</t>
   </si>
   <si>
     <t xml:space="preserve">2.5143768787384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4710009098053</t>
+    <t xml:space="preserve">2.47100067138672</t>
   </si>
   <si>
     <t xml:space="preserve">2.48979735374451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47533869743347</t>
+    <t xml:space="preserve">2.47533822059631</t>
   </si>
   <si>
     <t xml:space="preserve">2.51726841926575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45654201507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47967576980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46087980270386</t>
+    <t xml:space="preserve">2.45654225349426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47967600822449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46087956428528</t>
   </si>
   <si>
     <t xml:space="preserve">2.48112177848816</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45798778533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48256778717041</t>
+    <t xml:space="preserve">2.45798802375793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48256802558899</t>
   </si>
   <si>
     <t xml:space="preserve">2.48835110664368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48690533638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50859355926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53751134872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6025755405426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55919933319092</t>
+    <t xml:space="preserve">2.48690509796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50859308242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53751158714294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60257530212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5591995716095</t>
   </si>
   <si>
     <t xml:space="preserve">2.49558043479919</t>
@@ -971,31 +971,31 @@
     <t xml:space="preserve">2.63149285316467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6228175163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61703443527222</t>
+    <t xml:space="preserve">2.62281775474548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61703372001648</t>
   </si>
   <si>
     <t xml:space="preserve">2.72692060470581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73704147338867</t>
+    <t xml:space="preserve">2.73704171180725</t>
   </si>
   <si>
     <t xml:space="preserve">2.72258305549622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71246218681335</t>
+    <t xml:space="preserve">2.71246194839478</t>
   </si>
   <si>
     <t xml:space="preserve">2.71390795707703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70812439918518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68932843208313</t>
+    <t xml:space="preserve">2.70812463760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68932771682739</t>
   </si>
   <si>
     <t xml:space="preserve">2.68643641471863</t>
@@ -1004,28 +1004,28 @@
     <t xml:space="preserve">2.6878821849823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71101641654968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65028882026672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67920684814453</t>
+    <t xml:space="preserve">2.7110161781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65028929710388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67920708656311</t>
   </si>
   <si>
     <t xml:space="preserve">2.67197775840759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67053198814392</t>
+    <t xml:space="preserve">2.67053174972534</t>
   </si>
   <si>
     <t xml:space="preserve">2.65318083763123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65173482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66764044761658</t>
+    <t xml:space="preserve">2.6517345905304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.667640209198</t>
   </si>
   <si>
     <t xml:space="preserve">2.65896487236023</t>
@@ -1034,25 +1034,25 @@
     <t xml:space="preserve">2.64595150947571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59823751449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62426352500916</t>
+    <t xml:space="preserve">2.59823775291443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62426328659058</t>
   </si>
   <si>
     <t xml:space="preserve">2.60402131080627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54474115371704</t>
+    <t xml:space="preserve">2.54474067687988</t>
   </si>
   <si>
     <t xml:space="preserve">2.57654976844788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52449774742126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48545956611633</t>
+    <t xml:space="preserve">2.52449798583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48545932769775</t>
   </si>
   <si>
     <t xml:space="preserve">2.50280976295471</t>
@@ -1064,25 +1064,25 @@
     <t xml:space="preserve">2.51148533821106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51871466636658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53317308425903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55197024345398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50714731216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55052447319031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54618644714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53606557846069</t>
+    <t xml:space="preserve">2.518714427948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53317284584045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5519700050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50714755058289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55052423477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54618620872498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53606581687927</t>
   </si>
   <si>
     <t xml:space="preserve">2.5794415473938</t>
@@ -1091,7 +1091,7 @@
     <t xml:space="preserve">2.64161372184753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63004684448242</t>
+    <t xml:space="preserve">2.63004636764526</t>
   </si>
   <si>
     <t xml:space="preserve">2.58956265449524</t>
@@ -1112,13 +1112,13 @@
     <t xml:space="preserve">2.4912428855896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47244668006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50425577163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48401355743408</t>
+    <t xml:space="preserve">2.47244644165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50425601005554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48401379585266</t>
   </si>
   <si>
     <t xml:space="preserve">2.49413466453552</t>
@@ -1130,10 +1130,10 @@
     <t xml:space="preserve">2.47822999954224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51293087005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44931292533875</t>
+    <t xml:space="preserve">2.51293110847473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44931268692017</t>
   </si>
   <si>
     <t xml:space="preserve">2.40738201141357</t>
@@ -1142,22 +1142,22 @@
     <t xml:space="preserve">2.45509624481201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4102737903595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29605007171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2468900680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28159093856812</t>
+    <t xml:space="preserve">2.41027355194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29605054855347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24688959121704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28159117698669</t>
   </si>
   <si>
     <t xml:space="preserve">2.18471765518188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19773077964783</t>
+    <t xml:space="preserve">2.19773054122925</t>
   </si>
   <si>
     <t xml:space="preserve">2.22086429595947</t>
@@ -1169,31 +1169,31 @@
     <t xml:space="preserve">2.28448271751404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28592824935913</t>
+    <t xml:space="preserve">2.28592848777771</t>
   </si>
   <si>
     <t xml:space="preserve">2.32496738433838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34810137748718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37846493721008</t>
+    <t xml:space="preserve">2.34810161590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3784646987915</t>
   </si>
   <si>
     <t xml:space="preserve">2.41461181640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34231805801392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35677671432495</t>
+    <t xml:space="preserve">2.34231781959534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35677647590637</t>
   </si>
   <si>
     <t xml:space="preserve">2.35966825485229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34087181091309</t>
+    <t xml:space="preserve">2.34087204933167</t>
   </si>
   <si>
     <t xml:space="preserve">2.37701869010925</t>
@@ -1202,31 +1202,31 @@
     <t xml:space="preserve">2.39292359352112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40015292167664</t>
+    <t xml:space="preserve">2.40015268325806</t>
   </si>
   <si>
     <t xml:space="preserve">2.40593600273132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33653450012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29315781593323</t>
+    <t xml:space="preserve">2.33653426170349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29315757751465</t>
   </si>
   <si>
     <t xml:space="preserve">2.20496010780334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2396605014801</t>
+    <t xml:space="preserve">2.23966073989868</t>
   </si>
   <si>
     <t xml:space="preserve">2.23821473121643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23387742042542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18327212333679</t>
+    <t xml:space="preserve">2.23387694358826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18327188491821</t>
   </si>
   <si>
     <t xml:space="preserve">2.21797251701355</t>
@@ -1235,28 +1235,28 @@
     <t xml:space="preserve">2.24544405937195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20062232017517</t>
+    <t xml:space="preserve">2.20062184333801</t>
   </si>
   <si>
     <t xml:space="preserve">2.2266480922699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28303647041321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31340098381042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31050872802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38858580589294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38713955879211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34665536880493</t>
+    <t xml:space="preserve">2.28303670883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31340074539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31050896644592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38858556747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38713979721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34665560722351</t>
   </si>
   <si>
     <t xml:space="preserve">2.34520983695984</t>
@@ -1268,16 +1268,16 @@
     <t xml:space="preserve">2.39436912536621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40304446220398</t>
+    <t xml:space="preserve">2.4030442237854</t>
   </si>
   <si>
     <t xml:space="preserve">2.40449023246765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32785940170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34954762458801</t>
+    <t xml:space="preserve">2.3278591632843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34954738616943</t>
   </si>
   <si>
     <t xml:space="preserve">2.33364295959473</t>
@@ -1298,40 +1298,40 @@
     <t xml:space="preserve">2.32063007354736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30761694908142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37268137931824</t>
+    <t xml:space="preserve">2.3076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37268114089966</t>
   </si>
   <si>
     <t xml:space="preserve">2.42907071113586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36400604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31629204750061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35388469696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27725315093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32930493354797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30617165565491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30038785934448</t>
+    <t xml:space="preserve">2.36400580406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31629228591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35388493537903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27725291252136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32930517196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30617117881775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3003876209259</t>
   </si>
   <si>
     <t xml:space="preserve">2.37412691116333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33075094223022</t>
+    <t xml:space="preserve">2.33075070381165</t>
   </si>
   <si>
     <t xml:space="preserve">2.32641363143921</t>
@@ -1340,22 +1340,22 @@
     <t xml:space="preserve">2.39726090431213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39870667457581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3856942653656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60112953186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71969151496887</t>
+    <t xml:space="preserve">2.39870691299438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38569402694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60112977027893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71969127655029</t>
   </si>
   <si>
     <t xml:space="preserve">2.70957016944885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75439238548279</t>
+    <t xml:space="preserve">2.75439214706421</t>
   </si>
   <si>
     <t xml:space="preserve">2.77752685546875</t>
@@ -1364,7 +1364,7 @@
     <t xml:space="preserve">2.84837436676025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84114480018616</t>
+    <t xml:space="preserve">2.84114503860474</t>
   </si>
   <si>
     <t xml:space="preserve">2.83391547203064</t>
@@ -1376,13 +1376,13 @@
     <t xml:space="preserve">2.90042591094971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82957816123962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73125815391541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78620195388794</t>
+    <t xml:space="preserve">2.82957792282104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73125839233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78620171546936</t>
   </si>
   <si>
     <t xml:space="preserve">2.75583791732788</t>
@@ -1397,124 +1397,124 @@
     <t xml:space="preserve">2.83680748939514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74716305732727</t>
+    <t xml:space="preserve">2.74716258049011</t>
   </si>
   <si>
     <t xml:space="preserve">2.7384877204895</t>
   </si>
   <si>
+    <t xml:space="preserve">2.63438487052917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66092014312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65060043334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71251702308655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70367121696472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63143610954285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52824234962463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48254251480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52234578132629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56509733200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6107976436615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57689070701599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51939749717712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59163308143616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.618168592453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59015893936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54888081550598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56067442893982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55625200271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54593300819397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57099390029907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51350069046021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51055240631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53708744049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54151010513306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65354895591736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6594455242157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70514559745789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69040369987488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65797162055969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61964273452759</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.6343846321106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66092014312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65060067176819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71251702308655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70367121696472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63143634796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52824211120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48254251480103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52234554290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56509709358215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6107976436615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57689046859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51939749717712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59163308143616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.618168592453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59015893936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54888081550598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5606746673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55625176429749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54593300819397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57099390029907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51350069046021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51055240631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53708744049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54151010513306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65354895591736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6594455242157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70514559745789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69040369987488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65797162055969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61964273452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63438439369202</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.63291025161743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64912605285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64322948455811</t>
+    <t xml:space="preserve">2.6491265296936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64322972297668</t>
   </si>
   <si>
     <t xml:space="preserve">2.66534233093262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64470410346985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63880729675293</t>
+    <t xml:space="preserve">2.64470386505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63880705833435</t>
   </si>
   <si>
     <t xml:space="preserve">2.66386842727661</t>
@@ -1523,19 +1523,19 @@
     <t xml:space="preserve">2.71399116516113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73168134689331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71693968772888</t>
+    <t xml:space="preserve">2.73168158531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71693992614746</t>
   </si>
   <si>
     <t xml:space="preserve">2.7331554889679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78180360794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70661950111389</t>
+    <t xml:space="preserve">2.78180384635925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70661973953247</t>
   </si>
   <si>
     <t xml:space="preserve">2.69187784194946</t>
@@ -1544,16 +1544,16 @@
     <t xml:space="preserve">2.68892955780029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67713570594788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64617824554443</t>
+    <t xml:space="preserve">2.67713594436646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64617800712585</t>
   </si>
   <si>
     <t xml:space="preserve">2.6417555809021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57541632652283</t>
+    <t xml:space="preserve">2.57541608810425</t>
   </si>
   <si>
     <t xml:space="preserve">2.61374592781067</t>
@@ -1562,10 +1562,10 @@
     <t xml:space="preserve">2.60932326316833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58868455886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58131289482117</t>
+    <t xml:space="preserve">2.58868479728699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58131313323975</t>
   </si>
   <si>
     <t xml:space="preserve">2.53561329841614</t>
@@ -1574,10 +1574,10 @@
     <t xml:space="preserve">2.48843932151794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47222375869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50170731544495</t>
+    <t xml:space="preserve">2.47222328186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50170755386353</t>
   </si>
   <si>
     <t xml:space="preserve">2.56362295150757</t>
@@ -1586,7 +1586,7 @@
     <t xml:space="preserve">2.67123913764954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67418742179871</t>
+    <t xml:space="preserve">2.67418766021729</t>
   </si>
   <si>
     <t xml:space="preserve">2.65502309799194</t>
@@ -1595,10 +1595,10 @@
     <t xml:space="preserve">2.68450689315796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66239404678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6240656375885</t>
+    <t xml:space="preserve">2.66239380836487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62406539916992</t>
   </si>
   <si>
     <t xml:space="preserve">2.62996196746826</t>
@@ -1610,10 +1610,10 @@
     <t xml:space="preserve">2.62111687660217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42210030555725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41915225982666</t>
+    <t xml:space="preserve">2.42210054397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41915202140808</t>
   </si>
   <si>
     <t xml:space="preserve">2.36608147621155</t>
@@ -1622,31 +1622,31 @@
     <t xml:space="preserve">2.38966822624207</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41325545310974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33659672737122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24667167663574</t>
+    <t xml:space="preserve">2.41325521469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33659648895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24667143821716</t>
   </si>
   <si>
     <t xml:space="preserve">2.23045539855957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22898125648499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16706490516663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18033242225647</t>
+    <t xml:space="preserve">2.22898149490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16706466674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18033266067505</t>
   </si>
   <si>
     <t xml:space="preserve">2.15674567222595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2024450302124</t>
+    <t xml:space="preserve">2.20244526863098</t>
   </si>
   <si>
     <t xml:space="preserve">2.19360041618347</t>
@@ -1658,10 +1658,10 @@
     <t xml:space="preserve">2.11399412155151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08745837211609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04175853729248</t>
+    <t xml:space="preserve">2.08745813369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0417582988739</t>
   </si>
   <si>
     <t xml:space="preserve">2.00932645797729</t>
@@ -1673,13 +1673,13 @@
     <t xml:space="preserve">2.10514903068542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05797410011292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05502581596375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09335565567017</t>
+    <t xml:space="preserve">2.05797433853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0550262928009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09335541725159</t>
   </si>
   <si>
     <t xml:space="preserve">2.13610696792603</t>
@@ -1697,106 +1697,106 @@
     <t xml:space="preserve">2.10072636604309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09040665626526</t>
+    <t xml:space="preserve">2.0904061794281</t>
   </si>
   <si>
     <t xml:space="preserve">2.04912948608398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06829380989075</t>
+    <t xml:space="preserve">2.06829357147217</t>
   </si>
   <si>
     <t xml:space="preserve">2.05060338973999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04765510559082</t>
+    <t xml:space="preserve">2.0476553440094</t>
   </si>
   <si>
     <t xml:space="preserve">2.02701663970947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01964592933655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97394561767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97984254360199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96215164661407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98426520824432</t>
+    <t xml:space="preserve">2.01964545249939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97394573688507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97984266281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96215128898621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98426508903503</t>
   </si>
   <si>
     <t xml:space="preserve">2.08008718490601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06387138366699</t>
+    <t xml:space="preserve">2.06387114524841</t>
   </si>
   <si>
     <t xml:space="preserve">2.07861304283142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04618120193481</t>
+    <t xml:space="preserve">2.04618096351624</t>
   </si>
   <si>
     <t xml:space="preserve">2.0859842300415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05650043487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95625495910645</t>
+    <t xml:space="preserve">2.05650019645691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95625483989716</t>
   </si>
   <si>
     <t xml:space="preserve">1.98279082775116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94446122646332</t>
+    <t xml:space="preserve">1.94446134567261</t>
   </si>
   <si>
     <t xml:space="preserve">1.9370903968811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96657419204712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96804857254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89286494255066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98131680488586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91497766971588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87517464160919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87370049953461</t>
+    <t xml:space="preserve">1.96657431125641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9680483341217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89286506175995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98131692409515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91497755050659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8751745223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87370085716248</t>
   </si>
   <si>
     <t xml:space="preserve">1.94003880023956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92677128314972</t>
+    <t xml:space="preserve">1.9267715215683</t>
   </si>
   <si>
     <t xml:space="preserve">1.99311017990112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0034294128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99458420276642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99163615703583</t>
+    <t xml:space="preserve">2.00342965126038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99458432197571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99163591861725</t>
   </si>
   <si>
     <t xml:space="preserve">1.94888412952423</t>
@@ -1817,28 +1817,28 @@
     <t xml:space="preserve">1.86485540866852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85306203365326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83831918239594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88549399375916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85158753395081</t>
+    <t xml:space="preserve">1.85306179523468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83831894397736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88549435138702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8515876531601</t>
   </si>
   <si>
     <t xml:space="preserve">1.82505166530609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78230023384094</t>
+    <t xml:space="preserve">1.78230059146881</t>
   </si>
   <si>
     <t xml:space="preserve">1.71596121788025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69532251358032</t>
+    <t xml:space="preserve">1.6953227519989</t>
   </si>
   <si>
     <t xml:space="preserve">1.71006441116333</t>
@@ -1847,7 +1847,7 @@
     <t xml:space="preserve">1.73217797279358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78377461433411</t>
+    <t xml:space="preserve">1.78377437591553</t>
   </si>
   <si>
     <t xml:space="preserve">1.76313602924347</t>
@@ -1856,19 +1856,19 @@
     <t xml:space="preserve">1.76166176795959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78672313690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80588734149933</t>
+    <t xml:space="preserve">1.78672289848328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80588722229004</t>
   </si>
   <si>
     <t xml:space="preserve">1.83389687538147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87664866447449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86927795410156</t>
+    <t xml:space="preserve">1.87664890289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86927807331085</t>
   </si>
   <si>
     <t xml:space="preserve">1.84569013118744</t>
@@ -1886,64 +1886,64 @@
     <t xml:space="preserve">1.83684515953064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8972874879837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88991677761078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8825455904007</t>
+    <t xml:space="preserve">1.89728736877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88991665840149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88254570960999</t>
   </si>
   <si>
     <t xml:space="preserve">1.91055524349213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87075185775757</t>
+    <t xml:space="preserve">1.87075197696686</t>
   </si>
   <si>
     <t xml:space="preserve">1.80293893814087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80441296100616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79114544391632</t>
+    <t xml:space="preserve">1.80441308021545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79114532470703</t>
   </si>
   <si>
     <t xml:space="preserve">1.75576508045197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81325829029083</t>
+    <t xml:space="preserve">1.81325817108154</t>
   </si>
   <si>
     <t xml:space="preserve">1.81178379058838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83537089824677</t>
+    <t xml:space="preserve">1.83537077903748</t>
   </si>
   <si>
     <t xml:space="preserve">1.79556775093079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77492928504944</t>
+    <t xml:space="preserve">1.77492940425873</t>
   </si>
   <si>
     <t xml:space="preserve">1.80883574485779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79851615428925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79704213142395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8073616027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78082633018494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7542906999588</t>
+    <t xml:space="preserve">1.79851627349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79704225063324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80736148357391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78082597255707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75429081916809</t>
   </si>
   <si>
     <t xml:space="preserve">1.7130126953125</t>
@@ -1958,997 +1958,997 @@
     <t xml:space="preserve">1.76461005210876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77198088169098</t>
+    <t xml:space="preserve">1.77198076248169</t>
   </si>
   <si>
     <t xml:space="preserve">1.7778776884079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78819704055786</t>
+    <t xml:space="preserve">1.78819727897644</t>
   </si>
   <si>
     <t xml:space="preserve">1.74839389324188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6658388376236</t>
+    <t xml:space="preserve">1.66583859920502</t>
   </si>
   <si>
     <t xml:space="preserve">1.67910647392273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61129403114319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57886135578156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53610992431641</t>
+    <t xml:space="preserve">1.6112939119339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57886123657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53610980510712</t>
   </si>
   <si>
     <t xml:space="preserve">1.55822265148163</t>
   </si>
   <si>
+    <t xml:space="preserve">1.54200649261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53445506095886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53596556186676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56466090679169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54351699352264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55559921264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53898620605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54502725601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60543859004974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58429455757141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56768131256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56919169425964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58882546424866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51028990745544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51935231685638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52690374851227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4717777967453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47026753425598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.471022605896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45138895511627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46875727176666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49367690086365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48386001586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50047314167023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45894038677216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46800196170807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48990118503571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48234975337982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48083961009979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53294503688812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57523286342621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56315064430237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52539360523224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50424885749817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47328817844391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4725329875946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44912350177765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4536544084549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46649169921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44987881183624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44610297679901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43779647350311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42269361019135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42042815685272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42722451686859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41665256023407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40683579444885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40079462528229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39097774028778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3864461183548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28374683856964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25354075431824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25127506256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20068073272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23617231845856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25278544425964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22182464599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2308863401413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27695071697235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26637876033783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27619552612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31395268440247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27090954780579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28223669528961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28752267360687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35775065422058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38342559337616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37436389923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35246479511261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4098562002182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39852917194366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36681258678436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35095453262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35926103591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36454701423645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33736181259155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30262541770935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2897881269455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26109254360199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26864409446716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25505077838898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27468526363373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27997124195099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25958168506622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25429570674896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26939928531647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28148174285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30413591861725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33660686016083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36077129840851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38871228694916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38267040252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35170960426331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35699570178986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36152637004852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36228168010712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34113764762878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36756753921509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42495906352997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41740763187408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43326556682587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40532553195953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43477594852448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62960290908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5827841758728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57825350761414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58127391338348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54653739929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53747582435608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52237296104431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55257868766785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60241782665253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63111317157745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6009076833725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62054121494293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54955780506134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57221233844757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61147940158844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64168584346771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61298990249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61752068996429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59184610843658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58731520175934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61903119087219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57976353168488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56013011932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55861973762512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59788715839386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60392820835114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58580482006073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59939730167389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59637677669525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59033560752869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52992451190948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51331126689911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50953471660614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52388334274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54049634933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63866448402405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75948786735535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.806307554245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78365349769592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8395334482193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02983069419861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06909799575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94827461242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89088308811188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7791223526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77308106422424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81687939167023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70813858509064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48008441925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37511885166168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32452464103699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2407032251358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19917047023773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18406760692596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959789454936981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995280921459198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.91901171207428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945441544055939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962809801101685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01869094371796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04361057281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990750133991241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07155072689056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07910227775574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06777501106262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01944625377655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999811768531799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04134523868561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02699756622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10628736019135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05720329284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11459398269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13875913619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20219099521637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16745460033417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16594421863556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08740878105164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06701993942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0942051410675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06324434280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09496021270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07834708690643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08212280273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07457137107849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08665359020233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09269499778748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03756952285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07306122779846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04965198040009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03530418872833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04436576366425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04285550117493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01189482212067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985464096069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970361351966858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989239811897278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94317615032196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926563143730164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921277105808258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913725674152374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986219227313995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997546374797821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.058713555336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09722566604614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10251152515411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13422763347626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18180215358734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21502840518951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23919296264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19992566108704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18935358524323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14782083034515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16820955276489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18708825111389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16216850280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19312930107117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17047500610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24598908424377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29280865192413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36303675174713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40381515026093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41136646270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39399826526642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39928424358368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40154957771301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40305995941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41589748859406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49292182922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44836843013763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48763573169708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47630870342255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46498155593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39626371860504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37662923336029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34264802932739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3690779209137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43175530433655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.445347905159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47479832172394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48461520671844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55106842517853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52086281776428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37889468669891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3781396150589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34415817260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37209844589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39475345611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37964987754822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38795721530914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3924880027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32150399684906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31848335266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34340310096741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30036020278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32376945018768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33434152603149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39777386188507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.369833111763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38191521167755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34038245677948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35473012924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31772828102112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33207607269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33585178852081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27393019199371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26486825942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22484517097473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24145841598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11761450767517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10779774188995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13800394535065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22711062431335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24221348762512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23843777179718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22862088680267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44232738018036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43251037597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50273847579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55408895015717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81234848499298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78214299678802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77459156513214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75797772407532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69303560256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72173118591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68548405170441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70209729671478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70360743999481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.730792760849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72777235507965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69907665252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66887104511261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66282999515533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67944288253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66131961345673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6764223575592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64470636844635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61601042747498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63564395904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65829908847809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66585063934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66434013843536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74438524246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77761197090149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75646734237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7202205657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73683381080627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69454574584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6522581577301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67491221427917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65376818180084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63715445995331</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.54200661182404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53445506095886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53596556186676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56466102600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54351699352264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55559921264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53898620605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54502713680267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60543859004974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58429455757141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56768131256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56919157505035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58882534503937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51028990745544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51935231685638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52690374851227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4717777967453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47026753425598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.471022605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45138895511627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46875727176666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49367678165436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48386001586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50047314167023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45894038677216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46800196170807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48990118503571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48234975337982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48083961009979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53294503688812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57523286342621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56315064430237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52539360523224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50424885749817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47328817844391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4725329875946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44912362098694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4536544084549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46649169921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44987881183624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4461030960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43779647350311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42269361019135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42042827606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42722463607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41665256023407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40683567523956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.400794506073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39097774028778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38644623756409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28374683856964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25354075431824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25127506256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20068073272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23617231845856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25278544425964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22182464599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23088645935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27695071697235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26637887954712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27619552612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31395256519318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27090954780579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28223669528961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28752267360687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35775077342987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38342559337616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37436389923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35246467590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4098562002182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39852917194366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36681246757507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.350954413414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35926103591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36454701423645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33736181259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30262541770935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2897881269455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26109254360199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26864409446716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25505077838898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27468526363373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27997124195099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25958156585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25429570674896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26939928531647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2814816236496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30413591861725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33660674095154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36077129840851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38871228694916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38267040252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3517097234726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35699570178986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36152637004852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36228168010712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34113764762878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36756765842438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42495894432068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41740763187408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43326556682587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40532541275024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43477594852448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62960290908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58278429508209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57825350761414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58127391338348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54653739929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53747594356537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52237284183502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55257868766785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60241782665253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63111329078674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6009076833725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62054121494293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54955792427063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57221233844757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61147940158844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64168608188629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61298990249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61752080917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59184598922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58731520175934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61903119087219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57976365089417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56013011932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55861973762512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59788703918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60392820835114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58580493927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59939730167389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59637677669525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59033560752869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52992451190948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5133113861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50953471660614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52388322353363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54049634933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63866472244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75948810577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.806307554245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78365325927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8395334482193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02983069419861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06909823417664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94827461242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89088308811188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77912247180939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77308106422424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81687939167023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70813858509064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48008441925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37511885166168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32452464103699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2407032251358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19917047023773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18406760692596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959789335727692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995280921459198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91901171207428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945441544055939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96280974149704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01869106292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04361057281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990750133991241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07155072689056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07910227775574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06777501106262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01944625377655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99981164932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04134523868561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02699756622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10628736019135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05720329284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11459398269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13875913619995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20219099521637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16745460033417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16594421863556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08740878105164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06701993942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09420502185822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06324434280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09496033191681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07834696769714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08212280273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07457137107849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08665359020233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09269487857819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03756964206696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07306122779846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0496518611908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03530418872833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04436576366425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04285550117493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01189482212067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985464096069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970361351966858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989239811897278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94317626953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926563143730164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921276986598969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913725733757019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986219227313995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997546374797821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.058713555336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09722554683685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10251152515411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13422763347626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18180215358734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21502840518951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23919296264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19992566108704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18935358524323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14782094955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16820955276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1870881319046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16216850280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19312930107117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17047512531281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24598908424377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29280877113342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36303675174713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40381503105164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41136646270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39399826526642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39928424358368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4015496969223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40306007862091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41589748859406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49292182922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44836831092834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48763573169708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47630870342255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46498155593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39626371860504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37662923336029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34264802932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3690779209137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43175530433655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44534778594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47479832172394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48461532592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55106842517853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52086269855499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37889468669891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37813949584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34415817260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37209856510162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39475345611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37964987754822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38795709609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3924880027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32150399684906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31848335266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34340310096741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30036020278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32376945018768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33434152603149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39777386188507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.369833111763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38191521167755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34038245677948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35473024845123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31772828102112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33207607269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33585178852081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27393019199371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26486837863922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22484517097473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24145841598511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11761450767517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10779774188995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13800394535065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22711062431335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24221348762512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23843777179718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22862088680267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44232726097107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43251037597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50273847579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55408895015717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81234848499298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78214311599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77459156513214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75797772407532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69303560256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72173094749451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68548405170441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70209729671478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70360743999481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.730792760849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72777235507965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69907665252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66887104511261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66282975673676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67944312095642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66131961345673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67642259597778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64470660686493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61601042747498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63564395904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65829908847809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66585063934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66434013843536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74438524246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77761197090149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75646734237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7202205657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7368335723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69454574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65225791931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67491221427917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65376830101013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63715422153473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54200649261475</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.57070183753967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59486651420593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62205147743225</t>
+    <t xml:space="preserve">1.59486663341522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62205159664154</t>
   </si>
   <si>
     <t xml:space="preserve">1.7474057674408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8863525390625</t>
+    <t xml:space="preserve">1.88635230064392</t>
   </si>
   <si>
     <t xml:space="preserve">1.85765707492828</t>
@@ -2972,7 +2972,7 @@
     <t xml:space="preserve">1.80932819843292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83047223091125</t>
+    <t xml:space="preserve">1.83047199249268</t>
   </si>
   <si>
     <t xml:space="preserve">1.82141017913818</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">1.81838965415955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82594108581543</t>
+    <t xml:space="preserve">1.82594132423401</t>
   </si>
   <si>
     <t xml:space="preserve">1.80781769752502</t>
@@ -2990,22 +2990,22 @@
     <t xml:space="preserve">1.80177652835846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84557461738586</t>
+    <t xml:space="preserve">1.84557485580444</t>
   </si>
   <si>
     <t xml:space="preserve">1.83500277996063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82745146751404</t>
+    <t xml:space="preserve">1.82745134830475</t>
   </si>
   <si>
     <t xml:space="preserve">1.87124967575073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86369800567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92713093757629</t>
+    <t xml:space="preserve">1.86369812488556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92713069915771</t>
   </si>
   <si>
     <t xml:space="preserve">1.97999048233032</t>
@@ -3029,13 +3029,13 @@
     <t xml:space="preserve">2.10685515403748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15518498420715</t>
+    <t xml:space="preserve">2.15518474578857</t>
   </si>
   <si>
     <t xml:space="preserve">2.13555002212524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13857126235962</t>
+    <t xml:space="preserve">2.13857102394104</t>
   </si>
   <si>
     <t xml:space="preserve">2.22465777397156</t>
@@ -3044,7 +3044,7 @@
     <t xml:space="preserve">2.15669512748718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18992114067078</t>
+    <t xml:space="preserve">2.1899209022522</t>
   </si>
   <si>
     <t xml:space="preserve">2.18690085411072</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">2.17028784751892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2352294921875</t>
+    <t xml:space="preserve">2.23522973060608</t>
   </si>
   <si>
     <t xml:space="preserve">2.24731230735779</t>
@@ -3065,7 +3065,7 @@
     <t xml:space="preserve">2.26996684074402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30168294906616</t>
+    <t xml:space="preserve">2.30168271064758</t>
   </si>
   <si>
     <t xml:space="preserve">2.23673987388611</t>
@@ -3092,7 +3092,7 @@
     <t xml:space="preserve">2.64300799369812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61733341217041</t>
+    <t xml:space="preserve">2.61733317375183</t>
   </si>
   <si>
     <t xml:space="preserve">2.60223054885864</t>
@@ -3113,7 +3113,7 @@
     <t xml:space="preserve">2.86502075195312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86200022697449</t>
+    <t xml:space="preserve">2.86200046539307</t>
   </si>
   <si>
     <t xml:space="preserve">2.94204592704773</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">2.96621036529541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95714902877808</t>
+    <t xml:space="preserve">2.9571487903595</t>
   </si>
   <si>
     <t xml:space="preserve">2.97829294204712</t>
@@ -5910,6 +5910,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.3549995422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4300003051758</t>
   </si>
 </sst>
 </file>
@@ -71222,7 +71225,7 @@
     </row>
     <row r="2500">
       <c r="A2500" s="1" t="n">
-        <v>45959.6911226852</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2500" t="n">
         <v>922602</v>
@@ -71243,6 +71246,32 @@
         <v>1965</v>
       </c>
       <c r="H2500" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>45960.6912847222</v>
+      </c>
+      <c r="B2501" t="n">
+        <v>955456</v>
+      </c>
+      <c r="C2501" t="n">
+        <v>14.5649995803833</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>14.2550001144409</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>14.4700002670288</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>14.4300003051758</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>1966</v>
+      </c>
+      <c r="H2501" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BPSO.MI.xlsx
+++ b/data/BPSO.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1975" uniqueCount="1975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1976" uniqueCount="1976">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,73 +38,73 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82907152175903</t>
+    <t xml:space="preserve">2.82907199859619</t>
   </si>
   <si>
     <t xml:space="preserve">BPSO.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80963754653931</t>
+    <t xml:space="preserve">2.80963706970215</t>
   </si>
   <si>
     <t xml:space="preserve">2.74855804443359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71246600151062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63611698150635</t>
+    <t xml:space="preserve">2.7124662399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63611721992493</t>
   </si>
   <si>
     <t xml:space="preserve">2.60835409164429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69303178787231</t>
+    <t xml:space="preserve">2.69303202629089</t>
   </si>
   <si>
     <t xml:space="preserve">2.69858431816101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61112999916077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51257085800171</t>
+    <t xml:space="preserve">2.61113023757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51257038116455</t>
   </si>
   <si>
     <t xml:space="preserve">2.4556565284729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26686644554138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38069558143616</t>
+    <t xml:space="preserve">2.2668662071228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38069534301758</t>
   </si>
   <si>
     <t xml:space="preserve">2.40568256378174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36542558670044</t>
+    <t xml:space="preserve">2.3654260635376</t>
   </si>
   <si>
     <t xml:space="preserve">2.51951146125793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44455122947693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35570859909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43899869918823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40429449081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32100486755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22105693817139</t>
+    <t xml:space="preserve">2.44455099105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35570883750916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43899846076965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40429401397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32100510597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22105741500854</t>
   </si>
   <si>
     <t xml:space="preserve">2.23216247558594</t>
@@ -113,16 +113,16 @@
     <t xml:space="preserve">2.20995211601257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04059648513794</t>
+    <t xml:space="preserve">2.0405957698822</t>
   </si>
   <si>
     <t xml:space="preserve">2.06280660629272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14332008361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07668781280518</t>
+    <t xml:space="preserve">2.14331984519958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07668828964233</t>
   </si>
   <si>
     <t xml:space="preserve">2.18218851089478</t>
@@ -134,25 +134,25 @@
     <t xml:space="preserve">2.27797150611877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19329333305359</t>
+    <t xml:space="preserve">2.19329357147217</t>
   </si>
   <si>
     <t xml:space="preserve">2.16553044319153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24604368209839</t>
+    <t xml:space="preserve">2.24604392051697</t>
   </si>
   <si>
     <t xml:space="preserve">2.18635272979736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1766357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21550488471985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25992560386658</t>
+    <t xml:space="preserve">2.17663598060608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21550440788269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.259925365448</t>
   </si>
   <si>
     <t xml:space="preserve">2.31822848320007</t>
@@ -161,16 +161,16 @@
     <t xml:space="preserve">2.38763618469238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38208389282227</t>
+    <t xml:space="preserve">2.38208365440369</t>
   </si>
   <si>
     <t xml:space="preserve">2.37514281272888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24187970161438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26270174980164</t>
+    <t xml:space="preserve">2.2418794631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26270198822021</t>
   </si>
   <si>
     <t xml:space="preserve">2.25020813941956</t>
@@ -182,109 +182,109 @@
     <t xml:space="preserve">2.4334454536438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35848546028137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30157017707825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34599184989929</t>
+    <t xml:space="preserve">2.35848498344421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30156993865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34599161148071</t>
   </si>
   <si>
     <t xml:space="preserve">2.35987305641174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39318919181824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29324126243591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23771524429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18774104118347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.139155626297</t>
+    <t xml:space="preserve">2.39318895339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29324102401733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23771500587463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18774080276489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13915586471558</t>
   </si>
   <si>
     <t xml:space="preserve">2.14748477935791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12110948562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06974720954895</t>
+    <t xml:space="preserve">2.1211097240448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06974697113037</t>
   </si>
   <si>
     <t xml:space="preserve">2.01283288002014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01838564872742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07113528251648</t>
+    <t xml:space="preserve">2.01838612556458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07113552093506</t>
   </si>
   <si>
     <t xml:space="preserve">2.11694502830505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12527418136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22799825668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3029580116272</t>
+    <t xml:space="preserve">2.12527394294739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22799801826477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30295825004578</t>
   </si>
   <si>
     <t xml:space="preserve">2.23910355567932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2904646396637</t>
+    <t xml:space="preserve">2.29046487808228</t>
   </si>
   <si>
     <t xml:space="preserve">2.3321099281311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32655763626099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2793595790863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32378172874451</t>
+    <t xml:space="preserve">2.32655715942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27935981750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32378149032593</t>
   </si>
   <si>
     <t xml:space="preserve">2.30851101875305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26131343841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.234938621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15720152854919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1113920211792</t>
+    <t xml:space="preserve">2.26131367683411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23493885993958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15720129013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11139273643494</t>
   </si>
   <si>
     <t xml:space="preserve">2.08224034309387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09889888763428</t>
+    <t xml:space="preserve">2.09889912605286</t>
   </si>
   <si>
     <t xml:space="preserve">2.08918190002441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10583996772766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04892492294312</t>
+    <t xml:space="preserve">2.10583972930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04892468452454</t>
   </si>
   <si>
     <t xml:space="preserve">2.03781962394714</t>
@@ -299,25 +299,25 @@
     <t xml:space="preserve">2.07252359390259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05725407600403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05156707763672</t>
+    <t xml:space="preserve">2.05725383758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05156683921814</t>
   </si>
   <si>
     <t xml:space="preserve">2.12691879272461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19942760467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15393209457397</t>
+    <t xml:space="preserve">2.19942736625671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15393233299255</t>
   </si>
   <si>
     <t xml:space="preserve">2.17525792121887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15535378456116</t>
+    <t xml:space="preserve">2.15535402297974</t>
   </si>
   <si>
     <t xml:space="preserve">2.09279704093933</t>
@@ -326,100 +326,100 @@
     <t xml:space="preserve">2.07147121429443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99896240234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95773220062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87669312953949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98901033401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9364058971405</t>
+    <t xml:space="preserve">1.99896228313446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95773196220398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8766930103302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9890102148056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93640625476837</t>
   </si>
   <si>
     <t xml:space="preserve">1.94351482391357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84114956855774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78143727779388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75157999992371</t>
+    <t xml:space="preserve">1.84114980697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78143703937531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75157988071442</t>
   </si>
   <si>
     <t xml:space="preserve">1.72598886489868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64210629463196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69613242149353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77006256580353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81129348278046</t>
+    <t xml:space="preserve">1.64210605621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69613265991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77006244659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81129336357117</t>
   </si>
   <si>
     <t xml:space="preserve">1.78001439571381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89375364780426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63499772548676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56533265113831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66911971569061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65632343292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63926255702972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63641929626465</t>
+    <t xml:space="preserve">1.89375340938568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63499760627747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5653327703476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6691198348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65632355213165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63926267623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63641941547394</t>
   </si>
   <si>
     <t xml:space="preserve">1.57670664787292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51130640506744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52552402019501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53121066093445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63784098625183</t>
+    <t xml:space="preserve">1.51130676269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52552378177643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53121078014374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63784086704254</t>
   </si>
   <si>
     <t xml:space="preserve">1.67196333408356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69471096992493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67054188251495</t>
+    <t xml:space="preserve">1.69471073150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6705414056778</t>
   </si>
   <si>
     <t xml:space="preserve">1.74304974079132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70892822742462</t>
+    <t xml:space="preserve">1.70892810821533</t>
   </si>
   <si>
     <t xml:space="preserve">1.72172379493713</t>
@@ -428,94 +428,94 @@
     <t xml:space="preserve">1.77574956417084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76721906661987</t>
+    <t xml:space="preserve">1.76721894741058</t>
   </si>
   <si>
     <t xml:space="preserve">1.72741055488586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69755423069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72456729412079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71888029575348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66343283653259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55395913124084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57528495788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52125835418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63357591629028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65916681289673</t>
+    <t xml:space="preserve">1.69755411148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7245671749115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71888017654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6634327173233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55395901203156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57528483867645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52125871181488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63357603549957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65916705131531</t>
   </si>
   <si>
     <t xml:space="preserve">1.64779317378998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68760228157043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71461522579193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70608484745026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70039772987366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74447166919708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70750629901886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72030198574066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73167586326599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78285896778107</t>
+    <t xml:space="preserve">1.68760216236115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71461498737335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70608472824097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70039761066437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74447131156921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70750617980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72030210494995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7316757440567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78285872936249</t>
   </si>
   <si>
     <t xml:space="preserve">1.77859282493591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77148425579071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76437556743622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75584530830383</t>
+    <t xml:space="preserve">1.77148413658142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76437568664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75584506988525</t>
   </si>
   <si>
     <t xml:space="preserve">1.76295399665833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74162793159485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76864063739777</t>
+    <t xml:space="preserve">1.74162781238556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76864075660706</t>
   </si>
   <si>
     <t xml:space="preserve">1.74873673915863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73451936244965</t>
+    <t xml:space="preserve">1.73451912403107</t>
   </si>
   <si>
     <t xml:space="preserve">1.78428030014038</t>
@@ -524,19 +524,19 @@
     <t xml:space="preserve">1.85252344608307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84967994689941</t>
+    <t xml:space="preserve">1.84968018531799</t>
   </si>
   <si>
     <t xml:space="preserve">1.81271517276764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83546304702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84825825691223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85963213443756</t>
+    <t xml:space="preserve">1.83546268939972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84825849533081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85963225364685</t>
   </si>
   <si>
     <t xml:space="preserve">1.94778037071228</t>
@@ -545,34 +545,34 @@
     <t xml:space="preserve">1.97621464729309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09848403930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1084361076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07573628425598</t>
+    <t xml:space="preserve">2.09848427772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10843634605408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07573652267456</t>
   </si>
   <si>
     <t xml:space="preserve">2.08568835258484</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08853197097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09706211090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16104078292847</t>
+    <t xml:space="preserve">2.0885317325592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09706234931946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16104054450989</t>
   </si>
   <si>
     <t xml:space="preserve">2.18236660957336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11412310600281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00038409233093</t>
+    <t xml:space="preserve">2.11412334442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00038385391235</t>
   </si>
   <si>
     <t xml:space="preserve">2.03877139091492</t>
@@ -587,7 +587,7 @@
     <t xml:space="preserve">2.06294083595276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11554503440857</t>
+    <t xml:space="preserve">2.11554479598999</t>
   </si>
   <si>
     <t xml:space="preserve">2.12549662590027</t>
@@ -596,25 +596,25 @@
     <t xml:space="preserve">2.16246247291565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15961933135986</t>
+    <t xml:space="preserve">2.15961909294128</t>
   </si>
   <si>
     <t xml:space="preserve">2.13260531425476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08142304420471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03592824935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07715821266174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09990549087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08995366096497</t>
+    <t xml:space="preserve">2.08142328262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03592801094055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07715797424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09990572929382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08995389938354</t>
   </si>
   <si>
     <t xml:space="preserve">2.01033592224121</t>
@@ -626,55 +626,55 @@
     <t xml:space="preserve">2.10417103767395</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07289290428162</t>
+    <t xml:space="preserve">2.0728931427002</t>
   </si>
   <si>
     <t xml:space="preserve">2.16814923286438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27477979660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37430167198181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2634060382843</t>
+    <t xml:space="preserve">2.2747802734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37430143356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26340579986572</t>
   </si>
   <si>
     <t xml:space="preserve">2.23354911804199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27193641662598</t>
+    <t xml:space="preserve">2.2719361782074</t>
   </si>
   <si>
     <t xml:space="preserve">2.23212718963623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17810130119324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16957092285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23639273643494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22217535972595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21791005134583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20511436462402</t>
+    <t xml:space="preserve">2.17810153961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16957139968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23639249801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22217488288879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2179102897644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2051146030426</t>
   </si>
   <si>
     <t xml:space="preserve">2.22359681129456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26482748985291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3103232383728</t>
+    <t xml:space="preserve">2.26482796669006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31032299995422</t>
   </si>
   <si>
     <t xml:space="preserve">2.31743168830872</t>
@@ -689,28 +689,28 @@
     <t xml:space="preserve">2.30463624000549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.297527551651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29610562324524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36008358001709</t>
+    <t xml:space="preserve">2.29752731323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29610586166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36008334159851</t>
   </si>
   <si>
     <t xml:space="preserve">2.35297513008118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34017944335938</t>
+    <t xml:space="preserve">2.34017968177795</t>
   </si>
   <si>
     <t xml:space="preserve">2.4027361869812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41695332527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45249652862549</t>
+    <t xml:space="preserve">2.41695356369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45249676704407</t>
   </si>
   <si>
     <t xml:space="preserve">2.41126656532288</t>
@@ -719,22 +719,22 @@
     <t xml:space="preserve">2.415531873703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42406225204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44396638870239</t>
+    <t xml:space="preserve">2.4240620136261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44396615028381</t>
   </si>
   <si>
     <t xml:space="preserve">2.35439682006836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33733606338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33022713661194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36434864997864</t>
+    <t xml:space="preserve">2.33733534812927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3302276134491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3643491268158</t>
   </si>
   <si>
     <t xml:space="preserve">2.32738375663757</t>
@@ -743,61 +743,61 @@
     <t xml:space="preserve">2.28188848495483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30037069320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32311844825745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33449220657349</t>
+    <t xml:space="preserve">2.30037093162537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32311868667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33449244499207</t>
   </si>
   <si>
     <t xml:space="preserve">2.30890130996704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2989490032196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25629711151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12834024429321</t>
+    <t xml:space="preserve">2.29894924163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25629758834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12834048271179</t>
   </si>
   <si>
     <t xml:space="preserve">2.13402724266052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28473138809204</t>
+    <t xml:space="preserve">2.28473210334778</t>
   </si>
   <si>
     <t xml:space="preserve">2.22928404808044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27335810661316</t>
+    <t xml:space="preserve">2.273357629776</t>
   </si>
   <si>
     <t xml:space="preserve">2.27904486656189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31316661834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33875751495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37856674194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32880520820618</t>
+    <t xml:space="preserve">2.31316637992859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33875799179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37856650352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32880544662476</t>
   </si>
   <si>
     <t xml:space="preserve">2.36719226837158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34870958328247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29468417167664</t>
+    <t xml:space="preserve">2.34871006011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29468441009521</t>
   </si>
   <si>
     <t xml:space="preserve">2.30321431159973</t>
@@ -806,34 +806,34 @@
     <t xml:space="preserve">2.28757548332214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3202748298645</t>
+    <t xml:space="preserve">2.32027554512024</t>
   </si>
   <si>
     <t xml:space="preserve">2.28331017494202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29041886329651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29326224327087</t>
+    <t xml:space="preserve">2.29041910171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29326248168945</t>
   </si>
   <si>
     <t xml:space="preserve">2.30605792999268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35581851005554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31174468994141</t>
+    <t xml:space="preserve">2.35581827163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31174445152283</t>
   </si>
   <si>
     <t xml:space="preserve">2.3316490650177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46671414375305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43117094039917</t>
+    <t xml:space="preserve">2.46671390533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43117070198059</t>
   </si>
   <si>
     <t xml:space="preserve">2.42974901199341</t>
@@ -842,13 +842,13 @@
     <t xml:space="preserve">2.49799275398254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46387076377869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48661828041077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5164749622345</t>
+    <t xml:space="preserve">2.46387052536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48661851882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51647543907166</t>
   </si>
   <si>
     <t xml:space="preserve">2.51789689064026</t>
@@ -863,13 +863,13 @@
     <t xml:space="preserve">2.48803973197937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50510168075562</t>
+    <t xml:space="preserve">2.50510144233704</t>
   </si>
   <si>
     <t xml:space="preserve">2.50794506072998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50936651229858</t>
+    <t xml:space="preserve">2.50936675071716</t>
   </si>
   <si>
     <t xml:space="preserve">2.50652313232422</t>
@@ -881,13 +881,13 @@
     <t xml:space="preserve">2.5722119808197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63293862342834</t>
+    <t xml:space="preserve">2.63293838500977</t>
   </si>
   <si>
     <t xml:space="preserve">2.65607309341431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70667862892151</t>
+    <t xml:space="preserve">2.70667839050293</t>
   </si>
   <si>
     <t xml:space="preserve">2.56642889976501</t>
@@ -905,52 +905,52 @@
     <t xml:space="preserve">2.52160596847534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5143768787384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47100114822388</t>
+    <t xml:space="preserve">2.51437664031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47100067138672</t>
   </si>
   <si>
     <t xml:space="preserve">2.48979711532593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47533845901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51726841926575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45654249191284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47967624664307</t>
+    <t xml:space="preserve">2.47533822059631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51726865768433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45654225349426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47967576980591</t>
   </si>
   <si>
     <t xml:space="preserve">2.46087956428528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48112177848816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45798826217651</t>
+    <t xml:space="preserve">2.48112201690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45798802375793</t>
   </si>
   <si>
     <t xml:space="preserve">2.48256778717041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48835134506226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48690509796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50859332084656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53751134872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60257530212402</t>
+    <t xml:space="preserve">2.48835110664368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48690557479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50859355926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53751158714294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60257506370544</t>
   </si>
   <si>
     <t xml:space="preserve">2.55919933319092</t>
@@ -959,16 +959,16 @@
     <t xml:space="preserve">2.49558067321777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59245443344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66330242156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61414241790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63149261474609</t>
+    <t xml:space="preserve">2.59245419502258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6633026599884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61414217948914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63149285316467</t>
   </si>
   <si>
     <t xml:space="preserve">2.6228175163269</t>
@@ -983,16 +983,16 @@
     <t xml:space="preserve">2.73704171180725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72258305549622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7124617099762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71390795707703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70812439918518</t>
+    <t xml:space="preserve">2.72258281707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71246194839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71390771865845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70812463760376</t>
   </si>
   <si>
     <t xml:space="preserve">2.68932819366455</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">2.68643641471863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6878821849823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7110161781311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65028882026672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67920732498169</t>
+    <t xml:space="preserve">2.68788266181946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71101641654968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6502890586853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67920708656311</t>
   </si>
   <si>
     <t xml:space="preserve">2.67197775840759</t>
@@ -1019,10 +1019,10 @@
     <t xml:space="preserve">2.67053174972534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65318083763123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65173482894897</t>
+    <t xml:space="preserve">2.65318059921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65173506736755</t>
   </si>
   <si>
     <t xml:space="preserve">2.66763997077942</t>
@@ -1034,19 +1034,19 @@
     <t xml:space="preserve">2.64595150947571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59823751449585</t>
+    <t xml:space="preserve">2.59823775291443</t>
   </si>
   <si>
     <t xml:space="preserve">2.62426352500916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6040210723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54474091529846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57654976844788</t>
+    <t xml:space="preserve">2.60402131080627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54474067687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57655000686646</t>
   </si>
   <si>
     <t xml:space="preserve">2.52449798583984</t>
@@ -1067,25 +1067,25 @@
     <t xml:space="preserve">2.518714427948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53317308425903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5519700050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50714731216431</t>
+    <t xml:space="preserve">2.53317284584045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55196976661682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50714755058289</t>
   </si>
   <si>
     <t xml:space="preserve">2.55052447319031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54618644714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53606557846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57944178581238</t>
+    <t xml:space="preserve">2.54618668556213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53606534004211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5794415473938</t>
   </si>
   <si>
     <t xml:space="preserve">2.64161396026611</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">2.63004684448242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58956265449524</t>
+    <t xml:space="preserve">2.58956289291382</t>
   </si>
   <si>
     <t xml:space="preserve">2.52305197715759</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">2.51582264900208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49268889427185</t>
+    <t xml:space="preserve">2.49268865585327</t>
   </si>
   <si>
     <t xml:space="preserve">2.53461909294128</t>
@@ -1115,7 +1115,7 @@
     <t xml:space="preserve">2.47244668006897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50425553321838</t>
+    <t xml:space="preserve">2.50425601005554</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401379585266</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">2.49413466453552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4984724521637</t>
+    <t xml:space="preserve">2.49847221374512</t>
   </si>
   <si>
     <t xml:space="preserve">2.47823023796082</t>
@@ -1133,25 +1133,25 @@
     <t xml:space="preserve">2.51293087005615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44931292533875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40738201141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45509624481201</t>
+    <t xml:space="preserve">2.44931268692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40738153457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45509648323059</t>
   </si>
   <si>
     <t xml:space="preserve">2.41027355194092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29605007171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24689030647278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28159070014954</t>
+    <t xml:space="preserve">2.29604983329773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2468900680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28159093856812</t>
   </si>
   <si>
     <t xml:space="preserve">2.18471765518188</t>
@@ -1160,28 +1160,28 @@
     <t xml:space="preserve">2.19773077964783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22086405754089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26279473304749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28448247909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28592824935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32496738433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34810137748718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37846446037292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41461181640625</t>
+    <t xml:space="preserve">2.22086453437805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26279449462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28448224067688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28592848777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32496762275696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34810185432434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37846493721008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41461229324341</t>
   </si>
   <si>
     <t xml:space="preserve">2.34231781959534</t>
@@ -1193,22 +1193,22 @@
     <t xml:space="preserve">2.35966825485229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34087228775024</t>
+    <t xml:space="preserve">2.34087204933167</t>
   </si>
   <si>
     <t xml:space="preserve">2.37701869010925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39292335510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40015244483948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40593600273132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33653450012207</t>
+    <t xml:space="preserve">2.39292311668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40015268325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4059362411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33653426170349</t>
   </si>
   <si>
     <t xml:space="preserve">2.29315757751465</t>
@@ -1217,13 +1217,13 @@
     <t xml:space="preserve">2.20495986938477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2396605014801</t>
+    <t xml:space="preserve">2.23966073989868</t>
   </si>
   <si>
     <t xml:space="preserve">2.23821496963501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23387718200684</t>
+    <t xml:space="preserve">2.23387694358826</t>
   </si>
   <si>
     <t xml:space="preserve">2.18327212333679</t>
@@ -1238,25 +1238,25 @@
     <t xml:space="preserve">2.20062208175659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22664785385132</t>
+    <t xml:space="preserve">2.22664761543274</t>
   </si>
   <si>
     <t xml:space="preserve">2.28303694725037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31340074539185</t>
+    <t xml:space="preserve">2.31340050697327</t>
   </si>
   <si>
     <t xml:space="preserve">2.31050872802734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38858580589294</t>
+    <t xml:space="preserve">2.38858556747437</t>
   </si>
   <si>
     <t xml:space="preserve">2.38713979721069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34665536880493</t>
+    <t xml:space="preserve">2.34665560722351</t>
   </si>
   <si>
     <t xml:space="preserve">2.34520983695984</t>
@@ -1265,16 +1265,16 @@
     <t xml:space="preserve">2.36545157432556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39436912536621</t>
+    <t xml:space="preserve">2.39436936378479</t>
   </si>
   <si>
     <t xml:space="preserve">2.40304446220398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40448999404907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32785987854004</t>
+    <t xml:space="preserve">2.40449023246765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32785940170288</t>
   </si>
   <si>
     <t xml:space="preserve">2.34954714775085</t>
@@ -1289,22 +1289,22 @@
     <t xml:space="preserve">2.22953963279724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31484651565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30327963829041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32062983512878</t>
+    <t xml:space="preserve">2.31484627723694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30327939987183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32063007354736</t>
   </si>
   <si>
     <t xml:space="preserve">2.3076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37268161773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42907071113586</t>
+    <t xml:space="preserve">2.37268114089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42907047271729</t>
   </si>
   <si>
     <t xml:space="preserve">2.36400604248047</t>
@@ -1313,34 +1313,34 @@
     <t xml:space="preserve">2.31629228591919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35388517379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27725338935852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32930493354797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30617117881775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30038785934448</t>
+    <t xml:space="preserve">2.35388493537903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27725315093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32930517196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30617141723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30038809776306</t>
   </si>
   <si>
     <t xml:space="preserve">2.37412714958191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33075094223022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32641339302063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39726090431213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39870691299438</t>
+    <t xml:space="preserve">2.3307511806488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32641315460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39726066589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39870667457581</t>
   </si>
   <si>
     <t xml:space="preserve">2.38569402694702</t>
@@ -1349,22 +1349,22 @@
     <t xml:space="preserve">2.60112953186035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71969127655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70957040786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75439190864563</t>
+    <t xml:space="preserve">2.71969151496887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70957016944885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75439238548279</t>
   </si>
   <si>
     <t xml:space="preserve">2.77752685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84837436676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84114503860474</t>
+    <t xml:space="preserve">2.8483738899231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84114527702332</t>
   </si>
   <si>
     <t xml:space="preserve">2.83391547203064</t>
@@ -1373,7 +1373,7 @@
     <t xml:space="preserve">2.86861634254456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90042614936829</t>
+    <t xml:space="preserve">2.90042591094971</t>
   </si>
   <si>
     <t xml:space="preserve">2.82957792282104</t>
@@ -1385,13 +1385,13 @@
     <t xml:space="preserve">2.78620195388794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75583791732788</t>
+    <t xml:space="preserve">2.7558376789093</t>
   </si>
   <si>
     <t xml:space="preserve">2.82524037361145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80644416809082</t>
+    <t xml:space="preserve">2.80644392967224</t>
   </si>
   <si>
     <t xml:space="preserve">2.83680725097656</t>
@@ -1400,105 +1400,105 @@
     <t xml:space="preserve">2.74716281890869</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7384877204895</t>
+    <t xml:space="preserve">2.73848748207092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6343846321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66091990470886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65060043334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71251702308655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70367097854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63143634796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52824211120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4825427532196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52234554290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56509733200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6107976436615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57689070701599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51939725875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59163308143616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61816883087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59015893936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54888081550598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56067442893982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55625200271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54593276977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57099390029907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51350069046021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51055216789246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53708720207214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54150986671448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65354871749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65944576263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70514535903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69040369987488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65797162055969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61964249610901</t>
   </si>
   <si>
     <t xml:space="preserve">2.63438439369202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66092014312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65060067176819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71251702308655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70367121696472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63143634796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52824258804321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48254251480103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52234554290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56509709358215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6107976436615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57689046859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51939749717712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59163308143616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.618168592453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59015917778015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54888105392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5606746673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55625176429749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54593253135681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57099366188049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51350069046021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51055216789246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53708744049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54151010513306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65354871749878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6594455242157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70514559745789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69040369987488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65797162055969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61964273452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6343846321106</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.63291025161743</t>
   </si>
   <si>
@@ -1508,7 +1508,7 @@
     <t xml:space="preserve">2.64322948455811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6653425693512</t>
+    <t xml:space="preserve">2.66534233093262</t>
   </si>
   <si>
     <t xml:space="preserve">2.64470386505127</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">2.66386818885803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71399140357971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73168182373047</t>
+    <t xml:space="preserve">2.71399116516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73168158531189</t>
   </si>
   <si>
     <t xml:space="preserve">2.7169394493103</t>
@@ -1532,19 +1532,19 @@
     <t xml:space="preserve">2.73315572738647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78180384635925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70661973953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69187808036804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68892908096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67713594436646</t>
+    <t xml:space="preserve">2.78180360794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70661950111389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69187760353088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68892931938171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67713570594788</t>
   </si>
   <si>
     <t xml:space="preserve">2.64617800712585</t>
@@ -1553,7 +1553,7 @@
     <t xml:space="preserve">2.64175534248352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57541656494141</t>
+    <t xml:space="preserve">2.57541632652283</t>
   </si>
   <si>
     <t xml:space="preserve">2.61374592781067</t>
@@ -1562,31 +1562,31 @@
     <t xml:space="preserve">2.60932326316833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58868455886841</t>
+    <t xml:space="preserve">2.58868479728699</t>
   </si>
   <si>
     <t xml:space="preserve">2.58131289482117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53561305999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48843955993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47222352027893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50170707702637</t>
+    <t xml:space="preserve">2.53561353683472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48843932151794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47222375869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50170731544495</t>
   </si>
   <si>
     <t xml:space="preserve">2.56362295150757</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67123937606812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67418766021729</t>
+    <t xml:space="preserve">2.67123913764954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67418742179871</t>
   </si>
   <si>
     <t xml:space="preserve">2.65502309799194</t>
@@ -1601,7 +1601,7 @@
     <t xml:space="preserve">2.62406516075134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62996220588684</t>
+    <t xml:space="preserve">2.62996172904968</t>
   </si>
   <si>
     <t xml:space="preserve">2.63733291625977</t>
@@ -1613,22 +1613,22 @@
     <t xml:space="preserve">2.42210030555725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41915225982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36608123779297</t>
+    <t xml:space="preserve">2.41915202140808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36608147621155</t>
   </si>
   <si>
     <t xml:space="preserve">2.38966822624207</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41325545310974</t>
+    <t xml:space="preserve">2.41325521469116</t>
   </si>
   <si>
     <t xml:space="preserve">2.33659696578979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24667191505432</t>
+    <t xml:space="preserve">2.24667143821716</t>
   </si>
   <si>
     <t xml:space="preserve">2.23045563697815</t>
@@ -1637,7 +1637,7 @@
     <t xml:space="preserve">2.22898125648499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16706490516663</t>
+    <t xml:space="preserve">2.16706514358521</t>
   </si>
   <si>
     <t xml:space="preserve">2.18033266067505</t>
@@ -1655,25 +1655,25 @@
     <t xml:space="preserve">2.13905549049377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11399412155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08745789527893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0417582988739</t>
+    <t xml:space="preserve">2.11399435997009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08745837211609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04175877571106</t>
   </si>
   <si>
     <t xml:space="preserve">2.00932645797729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05207753181458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10514903068542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05797410011292</t>
+    <t xml:space="preserve">2.05207777023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.105149269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05797433853149</t>
   </si>
   <si>
     <t xml:space="preserve">2.0550262928009</t>
@@ -1685,7 +1685,7 @@
     <t xml:space="preserve">2.13610696792603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11694264411926</t>
+    <t xml:space="preserve">2.11694240570068</t>
   </si>
   <si>
     <t xml:space="preserve">2.09925246238708</t>
@@ -1697,10 +1697,10 @@
     <t xml:space="preserve">2.10072660446167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09040689468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04912924766541</t>
+    <t xml:space="preserve">2.09040641784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04912900924683</t>
   </si>
   <si>
     <t xml:space="preserve">2.06829357147217</t>
@@ -1712,25 +1712,25 @@
     <t xml:space="preserve">2.04765510559082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02701640129089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01964592933655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97394597530365</t>
+    <t xml:space="preserve">2.02701663970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01964545249939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97394573688507</t>
   </si>
   <si>
     <t xml:space="preserve">1.97984278202057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96215188503265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98426508903503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08008718490601</t>
+    <t xml:space="preserve">1.96215176582336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98426485061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08008694648743</t>
   </si>
   <si>
     <t xml:space="preserve">2.06387114524841</t>
@@ -1745,19 +1745,19 @@
     <t xml:space="preserve">2.0859842300415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05650019645691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95625472068787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98279082775116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9444614648819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93709027767181</t>
+    <t xml:space="preserve">2.05650043487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95625495910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98279106616974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94446134567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9370903968811</t>
   </si>
   <si>
     <t xml:space="preserve">1.96657419204712</t>
@@ -1772,88 +1772,88 @@
     <t xml:space="preserve">1.98131668567657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91497755050659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87517464160919</t>
+    <t xml:space="preserve">1.91497766971588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87517488002777</t>
   </si>
   <si>
     <t xml:space="preserve">1.87370049953461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94003891944885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92677128314972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99311017990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00342965126038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99458456039429</t>
+    <t xml:space="preserve">1.94003903865814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92677104473114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99311029911041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00342988967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99458420276642</t>
   </si>
   <si>
     <t xml:space="preserve">1.99163615703583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94888424873352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8884425163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8722265958786</t>
+    <t xml:space="preserve">1.94888401031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88844227790833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87222635746002</t>
   </si>
   <si>
     <t xml:space="preserve">1.91940057277679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89433908462524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86485505104065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85306191444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83831930160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88549399375916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8515876531601</t>
+    <t xml:space="preserve">1.89433896541595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86485517024994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85306179523468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83831942081451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88549387454987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85158741474152</t>
   </si>
   <si>
     <t xml:space="preserve">1.82505166530609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78230035305023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71596145629883</t>
+    <t xml:space="preserve">1.78230011463165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71596121788025</t>
   </si>
   <si>
     <t xml:space="preserve">1.6953227519989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71006429195404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73217809200287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78377425670624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76313579082489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76166164875031</t>
+    <t xml:space="preserve">1.71006441116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73217821121216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78377437591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76313602924347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76166188716888</t>
   </si>
   <si>
     <t xml:space="preserve">1.78672289848328</t>
@@ -1862,10 +1862,10 @@
     <t xml:space="preserve">1.80588710308075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83389675617218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87664890289307</t>
+    <t xml:space="preserve">1.83389699459076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87664878368378</t>
   </si>
   <si>
     <t xml:space="preserve">1.86927795410156</t>
@@ -1874,28 +1874,28 @@
     <t xml:space="preserve">1.84569013118744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83979380130768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83242249488831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84274196624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83684492111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89728736877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8899165391922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8825455904007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91055488586426</t>
+    <t xml:space="preserve">1.83979344367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83242225646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84274172782898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83684515953064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89728724956512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88991665840149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88254535198212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91055524349213</t>
   </si>
   <si>
     <t xml:space="preserve">1.87075209617615</t>
@@ -1904,40 +1904,40 @@
     <t xml:space="preserve">1.80293881893158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80441308021545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79114532470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75576508045197</t>
+    <t xml:space="preserve">1.80441319942474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79114520549774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75576496124268</t>
   </si>
   <si>
     <t xml:space="preserve">1.81325817108154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81178390979767</t>
+    <t xml:space="preserve">1.81178367137909</t>
   </si>
   <si>
     <t xml:space="preserve">1.83537101745605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79556810855865</t>
+    <t xml:space="preserve">1.79556798934937</t>
   </si>
   <si>
     <t xml:space="preserve">1.77492928504944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80883598327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79851627349854</t>
+    <t xml:space="preserve">1.8088356256485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79851615428925</t>
   </si>
   <si>
     <t xml:space="preserve">1.79704201221466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80736136436462</t>
+    <t xml:space="preserve">1.8073616027832</t>
   </si>
   <si>
     <t xml:space="preserve">1.78082609176636</t>
@@ -1946,13 +1946,13 @@
     <t xml:space="preserve">1.7542906999588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7130126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70711624622345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74544560909271</t>
+    <t xml:space="preserve">1.71301293373108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70711612701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.745445728302</t>
   </si>
   <si>
     <t xml:space="preserve">1.76461005210876</t>
@@ -1961,982 +1961,985 @@
     <t xml:space="preserve">1.77198088169098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77787792682648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78819727897644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74839401245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66583907604218</t>
+    <t xml:space="preserve">1.7778776884079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78819704055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74839413166046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66583871841431</t>
   </si>
   <si>
     <t xml:space="preserve">1.67910647392273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61129415035248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57886135578156</t>
+    <t xml:space="preserve">1.61129403114319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57886111736298</t>
   </si>
   <si>
     <t xml:space="preserve">1.53610992431641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55822265148163</t>
+    <t xml:space="preserve">1.55822253227234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54200673103333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53445518016815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53596544265747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56466102600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54351699352264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55559909343719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53898620605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54502725601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60543859004974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58429431915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56768143177032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56919169425964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58882522583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51028990745544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51935243606567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52690386772156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47177791595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47026753425598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.471022605896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45138895511627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46875727176666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49367678165436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48386001586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50047314167023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45894038677216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46800196170807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48990106582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48234975337982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48083961009979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53294503688812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57523286342621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56315052509308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52539360523224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50424873828888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47328794002533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47253274917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44912362098694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4536544084549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46649181842804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44987881183624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44610285758972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43779647350311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42269372940063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42042827606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42722451686859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41665256023407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40683555603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.400794506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39097774028778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3864461183548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28374707698822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25354051589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25127530097961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20068061351776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23617243766785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25278532505035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22182476520538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2308863401413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27695071697235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26637887954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27619564533234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31395268440247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27090954780579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28223669528961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28752267360687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35775077342987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38342547416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37436378002167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35246479511261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4098562002182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39852917194366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36681234836578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.350954413414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35926103591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36454713344574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33736181259155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30262541770935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2897881269455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26109278202057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26864409446716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25505077838898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27468526363373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27997136116028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25958156585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25429570674896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26939940452576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2814816236496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30413579940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33660686016083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36077129840851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38871240615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38267040252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35170960426331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35699570178986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36152637004852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36228156089783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34113788604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36756753921509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42495906352997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41740763187408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43326568603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40532553195953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43477594852448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62960302829742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5827841758728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57825350761414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58127391338348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54653751850128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53747594356537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52237284183502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55257856845856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60241794586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63111317157745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60090756416321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62054133415222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54955804347992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57221233844757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61147952079773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.641685962677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61298990249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.617520570755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59184598922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58731496334076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61903095245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57976377010345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56013011932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55861973762512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59788691997528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60392808914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58580482006073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59939742088318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59637665748596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59033560752869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52992451190948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51331126689911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50953483581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52388322353363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54049634933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63866448402405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75948786735535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80630767345428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78365325927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83953368663788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02983045578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06909775733948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94827497005463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89088308811188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7791223526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77308118343353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81687951087952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70813834667206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4800843000412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37511909008026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32452464103699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2407032251358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19917047023773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18406772613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959789216518402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995280981063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919011831283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945441544055939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962809860706329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01869118213654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04361057281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990750193595886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07155072689056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07910239696503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0677752494812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01944625377655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999811828136444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0413453578949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02699756622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10628747940063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05720317363739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11459398269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13875913619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20219111442566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16745460033417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16594409942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08740878105164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06701982021332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09420502185822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06324446201324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09496033191681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07834720611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08212280273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07457137107849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08665359020233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09269487857819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03756952285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07306110858917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04965162277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03530418872833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04436576366425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04285550117493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01189470291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985464155673981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970361232757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989239752292633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.943176209926605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926563084125519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921276986598969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913725674152374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986219227313995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997546374797821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05871343612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09722566604614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1025116443634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13422763347626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18180215358734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21502828598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23919296264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19992554187775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18935346603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14782094955444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16820967197418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1870881319046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16216862201691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19312930107117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17047512531281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24598908424377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29280865192413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36303675174713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40381515026093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41136646270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39399826526642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39928436279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40154957771301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40305995941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41589736938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49292182922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44836854934692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48763561248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47630858421326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46498155593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39626371860504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37662935256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34264802932739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3690779209137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43175542354584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.445347905159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47479844093323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48461508750916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55106842517853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5208625793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37889468669891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3781396150589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34415817260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37209844589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39475345611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37964999675751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38795733451843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3924880027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32150399684906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31848347187042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34340310096741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30036008358002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32376933097839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3343414068222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39777410030365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.369833111763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38191521167755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34038257598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35473012924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31772828102112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33207607269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33585178852081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27393007278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26486837863922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22484529018402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24145829677582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11761450767517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10779762268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13800406455994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22711074352264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24221348762512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23843765258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22862100601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44232738018036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43251037597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50273847579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55408895015717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81234860420227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78214275836945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77459180355072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75797760486603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69303560256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7217310667038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68548405170441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70209729671478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70360743999481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73079252243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72777211666107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69907653331757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66887104511261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66282999515533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67944288253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66131973266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67642259597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64470648765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61601030826569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63564419746399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6582989692688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66585063934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66434001922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74438524246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77761232852936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75646734237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72022044658661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73683393001556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69454598426819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6522581577301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67491221427917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65376818180084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63715434074402</t>
   </si>
   <si>
     <t xml:space="preserve">1.54200661182404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53445518016815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53596544265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56466102600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54351699352264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55559909343719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53898620605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54502725601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60543847084045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58429455757141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56768131256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56919157505035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58882546424866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51029002666473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51935243606567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52690386772156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4717777967453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47026753425598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.471022605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45138895511627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46875727176666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49367690086365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48386001586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50047314167023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45894050598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46800208091736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48990118503571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48234975337982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48083961009979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53294503688812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57523274421692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56315064430237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52539360523224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50424885749817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47328817844391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4725329875946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44912350177765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4536544084549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46649169921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44987881183624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44610297679901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43779647350311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42269361019135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42042815685272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4272243976593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41665256023407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40683579444885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.400794506073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39097774028778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38644623756409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28374683856964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25354075431824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25127518177032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20068085193634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23617231845856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25278544425964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22182464599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2308863401413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27695071697235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26637876033783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27619564533234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31395268440247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27090954780579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28223669528961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28752279281616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35775065422058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38342559337616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37436389923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35246479511261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40985631942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39852917194366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36681246757507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35095453262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35926103591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36454701423645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33736193180084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30262541770935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2897881269455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26109266281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26864421367645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25505077838898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27468526363373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27997136116028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25958168506622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25429570674896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26939928531647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2814816236496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30413579940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33660686016083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36077117919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38871216773987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38267040252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35170960426331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35699570178986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36152648925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36228168010712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34113764762878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36756765842438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42495906352997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41740763187408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43326556682587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40532553195953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43477594852448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62960290908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5827841758728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57825338840485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58127391338348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54653739929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53747582435608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52237296104431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55257868766785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60241782665253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63111317157745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6009076833725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62054133415222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54955780506134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57221233844757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61147940158844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64168584346771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61298990249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61752068996429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59184610843658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58731520175934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6190310716629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57976353168488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56013011932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55861973762512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59788715839386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60392820835114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58580482006073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59939730167389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59637677669525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59033560752869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52992451190948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51331126689911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50953483581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52388334274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54049634933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63866460323334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75948786735535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.806307554245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78365337848663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8395334482193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02983069419861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06909799575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94827461242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89088308811188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7791223526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77308118343353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81687939167023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70813846588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4800843000412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37511897087097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32452464103699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2407032251358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19917047023773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18406772613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959789395332336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995280981063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91901171207428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945441544055939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962809801101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01869094371796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04361057281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990750074386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07155084609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07910239696503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06777513027191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01944613456726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999811828136444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0413453578949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02699756622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10628747940063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05720317363739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11459398269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13875913619995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20219099521637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16745448112488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16594421863556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08740878105164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06701993942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0942051410675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06324434280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09496021270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07834720611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08212280273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07457137107849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08665370941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09269499778748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03756952285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07306122779846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0496518611908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03530418872833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04436576366425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04285550117493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01189470291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985464096069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970361292362213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989239752292633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94317615032196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926563143730164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921277105808258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913725614547729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986219227313995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997546255588531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.058713555336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09722566604614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10251152515411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13422763347626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18180227279663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21502840518951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23919308185577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19992554187775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18935358524323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14782071113586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16820967197418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18708825111389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16216862201691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19312930107117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17047512531281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24598908424377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29280865192413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36303675174713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40381515026093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41136646270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39399826526642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39928424358368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40154957771301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40305995941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41589748859406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49292182922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44836854934692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48763561248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47630858421326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46498143672943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39626383781433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37662923336029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34264802932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3690779209137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43175530433655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.445347905159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47479832172394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48461520671844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55106854438782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52086281776428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37889468669891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3781396150589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34415817260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37209832668304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39475333690643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37964987754822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38795721530914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3924880027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32150399684906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31848347187042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34340310096741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30036008358002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32376945018768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33434152603149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39777386188507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.369833111763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38191521167755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34038245677948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35473012924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31772840023041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33207607269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33585166931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27393019199371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26486837863922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22484505176544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24145829677582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11761462688446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10779762268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13800406455994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22711062431335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24221348762512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23843777179718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22862088680267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44232738018036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43251037597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50273859500885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55408906936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81234848499298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78214299678802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77459156513214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75797760486603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69303560256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72173118591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68548393249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70209729671478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70360743999481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73079264163971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72777223587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69907677173615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6688711643219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66282999515533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67944288253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66131973266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67642247676849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64470636844635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61601042747498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63564395904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65829908847809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66585063934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66434013843536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74438524246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77761197090149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.756467461586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7202205657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73683381080627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69454574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6522581577301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67491221427917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65376818180084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63715445995331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57070183753967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59486663341522</t>
+    <t xml:space="preserve">1.57070207595825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59486639499664</t>
   </si>
   <si>
     <t xml:space="preserve">1.62205159664154</t>
@@ -2945,22 +2948,22 @@
     <t xml:space="preserve">1.7474057674408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88635230064392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85765695571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88031101226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86822879314423</t>
+    <t xml:space="preserve">1.88635241985321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85765707492828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88031125068665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86822915077209</t>
   </si>
   <si>
     <t xml:space="preserve">1.85463654994965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88937294483185</t>
+    <t xml:space="preserve">1.88937306404114</t>
   </si>
   <si>
     <t xml:space="preserve">1.85010552406311</t>
@@ -2972,13 +2975,13 @@
     <t xml:space="preserve">1.83047199249268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82141005992889</t>
+    <t xml:space="preserve">1.82141017913818</t>
   </si>
   <si>
     <t xml:space="preserve">1.81838965415955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82594132423401</t>
+    <t xml:space="preserve">1.82594096660614</t>
   </si>
   <si>
     <t xml:space="preserve">1.80781769752502</t>
@@ -2987,31 +2990,31 @@
     <t xml:space="preserve">1.80177652835846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84557485580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83500277996063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82745122909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87124967575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86369812488556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92713069915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97999060153961</t>
+    <t xml:space="preserve">1.84557461738586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83500266075134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82745134830475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87124955654144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86369800567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.927130818367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97999083995819</t>
   </si>
   <si>
     <t xml:space="preserve">2.05399513244629</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13706064224243</t>
+    <t xml:space="preserve">2.13706088066101</t>
   </si>
   <si>
     <t xml:space="preserve">2.18085956573486</t>
@@ -3023,40 +3026,40 @@
     <t xml:space="preserve">2.12950921058655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1068549156189</t>
+    <t xml:space="preserve">2.10685515403748</t>
   </si>
   <si>
     <t xml:space="preserve">2.15518450737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13555026054382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13857078552246</t>
+    <t xml:space="preserve">2.1355504989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13857102394104</t>
   </si>
   <si>
     <t xml:space="preserve">2.22465777397156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1566948890686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1899209022522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18690085411072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16877722740173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17028784751892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23522996902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24731230735779</t>
+    <t xml:space="preserve">2.15669512748718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18992114067078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18690061569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16877698898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17028737068176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2352294921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24731206893921</t>
   </si>
   <si>
     <t xml:space="preserve">2.26996684074402</t>
@@ -3065,7 +3068,7 @@
     <t xml:space="preserve">2.30168271064758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23673987388611</t>
+    <t xml:space="preserve">2.23674011230469</t>
   </si>
   <si>
     <t xml:space="preserve">2.2458016872406</t>
@@ -3077,10 +3080,10 @@
     <t xml:space="preserve">2.36964559555054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39985156059265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48140740394592</t>
+    <t xml:space="preserve">2.39985179901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48140716552734</t>
   </si>
   <si>
     <t xml:space="preserve">2.54937052726746</t>
@@ -3089,10 +3092,10 @@
     <t xml:space="preserve">2.64300799369812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61733293533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60223054885864</t>
+    <t xml:space="preserve">2.61733317375183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60223031044006</t>
   </si>
   <si>
     <t xml:space="preserve">2.70190978050232</t>
@@ -3110,16 +3113,16 @@
     <t xml:space="preserve">2.86502075195312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86200022697449</t>
+    <t xml:space="preserve">2.86200046539307</t>
   </si>
   <si>
     <t xml:space="preserve">2.94204592704773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94506621360779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93147420883179</t>
+    <t xml:space="preserve">2.94506645202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93147397041321</t>
   </si>
   <si>
     <t xml:space="preserve">2.97980308532715</t>
@@ -3131,19 +3134,19 @@
     <t xml:space="preserve">2.9571487903595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97829270362854</t>
+    <t xml:space="preserve">2.97829294204712</t>
   </si>
   <si>
     <t xml:space="preserve">3.08411288261414</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07337760925293</t>
+    <t xml:space="preserve">3.07337737083435</t>
   </si>
   <si>
     <t xml:space="preserve">3.05804061889648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15312552452087</t>
+    <t xml:space="preserve">3.15312528610229</t>
   </si>
   <si>
     <t xml:space="preserve">3.09178066253662</t>
@@ -3152,7 +3155,7 @@
     <t xml:space="preserve">3.11478519439697</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19299960136414</t>
+    <t xml:space="preserve">3.19299936294556</t>
   </si>
   <si>
     <t xml:space="preserve">3.21600413322449</t>
@@ -3167,16 +3170,16 @@
     <t xml:space="preserve">3.12858748435974</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06264162063599</t>
+    <t xml:space="preserve">3.06264138221741</t>
   </si>
   <si>
     <t xml:space="preserve">2.98749446868896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96602392196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95988965034485</t>
+    <t xml:space="preserve">2.96602416038513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95988941192627</t>
   </si>
   <si>
     <t xml:space="preserve">2.9445526599884</t>
@@ -3185,34 +3188,34 @@
     <t xml:space="preserve">2.91388034820557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.901611328125</t>
+    <t xml:space="preserve">2.90161108970642</t>
   </si>
   <si>
     <t xml:space="preserve">2.83106517791748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80192565917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80039238929749</t>
+    <t xml:space="preserve">2.80192589759827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80039215087891</t>
   </si>
   <si>
     <t xml:space="preserve">2.73598051071167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79425811767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79272413253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83719968795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76665258407593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80499267578125</t>
+    <t xml:space="preserve">2.7942578792572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79272437095642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83719944953918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76665282249451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80499315261841</t>
   </si>
   <si>
     <t xml:space="preserve">2.79119038581848</t>
@@ -3227,7 +3230,7 @@
     <t xml:space="preserve">2.75131678581238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72371196746826</t>
+    <t xml:space="preserve">2.72371172904968</t>
   </si>
   <si>
     <t xml:space="preserve">2.84333419799805</t>
@@ -3236,7 +3239,7 @@
     <t xml:space="preserve">2.79579138755798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77892184257507</t>
+    <t xml:space="preserve">2.77892160415649</t>
   </si>
   <si>
     <t xml:space="preserve">2.72524523735046</t>
@@ -3245,7 +3248,7 @@
     <t xml:space="preserve">2.6731014251709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58108472824097</t>
+    <t xml:space="preserve">2.58108496665955</t>
   </si>
   <si>
     <t xml:space="preserve">2.66543340682983</t>
@@ -3254,52 +3257,52 @@
     <t xml:space="preserve">2.73291325569153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75745129585266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78352236747742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92614936828613</t>
+    <t xml:space="preserve">2.75745105743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.783522605896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92614912986755</t>
   </si>
   <si>
     <t xml:space="preserve">2.88934254646301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94301891326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90774583816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85100197792053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86020398139954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85867023468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83873319625854</t>
+    <t xml:space="preserve">2.94301915168762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90774607658386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85100245475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86020374298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8586699962616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83873343467712</t>
   </si>
   <si>
     <t xml:space="preserve">2.84486770629883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91848111152649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95222115516663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90467858314514</t>
+    <t xml:space="preserve">2.91848134994507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95222139358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90467834472656</t>
   </si>
   <si>
     <t xml:space="preserve">2.96755766868591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92768287658691</t>
+    <t xml:space="preserve">2.92768311500549</t>
   </si>
   <si>
     <t xml:space="preserve">2.92461562156677</t>
@@ -3311,25 +3314,25 @@
     <t xml:space="preserve">2.8617377281189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84640145301819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87860703468323</t>
+    <t xml:space="preserve">2.84640121459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87860727310181</t>
   </si>
   <si>
     <t xml:space="preserve">2.89854431152344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99976372718811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0074315071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98289370536804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98596096038818</t>
+    <t xml:space="preserve">2.99976348876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00743126869202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98289346694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98596119880676</t>
   </si>
   <si>
     <t xml:space="preserve">2.95375514030457</t>
@@ -3338,25 +3341,25 @@
     <t xml:space="preserve">2.99056148529053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93688440322876</t>
+    <t xml:space="preserve">2.93688416481018</t>
   </si>
   <si>
     <t xml:space="preserve">2.95682215690613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90007781982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84180068969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87400650978088</t>
+    <t xml:space="preserve">2.9000780582428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84180045127869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8740062713623</t>
   </si>
   <si>
     <t xml:space="preserve">2.81726264953613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76511907577515</t>
+    <t xml:space="preserve">2.76511931419373</t>
   </si>
   <si>
     <t xml:space="preserve">2.8295316696167</t>
@@ -3374,16 +3377,16 @@
     <t xml:space="preserve">2.79732513427734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80652689933777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81419491767883</t>
+    <t xml:space="preserve">2.80652666091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81419467926025</t>
   </si>
   <si>
     <t xml:space="preserve">2.78045535087585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82646441459656</t>
+    <t xml:space="preserve">2.82646417617798</t>
   </si>
   <si>
     <t xml:space="preserve">2.84793496131897</t>
@@ -3398,25 +3401,25 @@
     <t xml:space="preserve">2.90314507484436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88320803642273</t>
+    <t xml:space="preserve">2.88320827484131</t>
   </si>
   <si>
     <t xml:space="preserve">2.86633825302124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87554001808167</t>
+    <t xml:space="preserve">2.87554025650024</t>
   </si>
   <si>
     <t xml:space="preserve">2.9062123298645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95528841018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97522568702698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98902821540833</t>
+    <t xml:space="preserve">2.95528864860535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9752254486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98902797698975</t>
   </si>
   <si>
     <t xml:space="preserve">2.95068788528442</t>
@@ -3428,7 +3431,7 @@
     <t xml:space="preserve">3.02890205383301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03656983375549</t>
+    <t xml:space="preserve">3.03657007217407</t>
   </si>
   <si>
     <t xml:space="preserve">2.92001485824585</t>
@@ -3437,10 +3440,10 @@
     <t xml:space="preserve">2.93535089492798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88014101982117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91234683990479</t>
+    <t xml:space="preserve">2.88014078140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91234660148621</t>
   </si>
   <si>
     <t xml:space="preserve">2.98136019706726</t>
@@ -3449,10 +3452,10 @@
     <t xml:space="preserve">3.03350281715393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94915390014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85560321807861</t>
+    <t xml:space="preserve">2.94915413856506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85560297966003</t>
   </si>
   <si>
     <t xml:space="preserve">2.80806040763855</t>
@@ -3467,7 +3470,7 @@
     <t xml:space="preserve">2.69917392730713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70684170722961</t>
+    <t xml:space="preserve">2.70684194564819</t>
   </si>
   <si>
     <t xml:space="preserve">2.66083288192749</t>
@@ -3476,10 +3479,10 @@
     <t xml:space="preserve">2.76051831245422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7114429473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58875274658203</t>
+    <t xml:space="preserve">2.71144247055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58875298500061</t>
   </si>
   <si>
     <t xml:space="preserve">2.73137950897217</t>
@@ -3491,22 +3494,22 @@
     <t xml:space="preserve">2.65009760856628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67770266532898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67463564872742</t>
+    <t xml:space="preserve">2.6777024269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67463541030884</t>
   </si>
   <si>
     <t xml:space="preserve">2.74671578407288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72064423561096</t>
+    <t xml:space="preserve">2.72064447402954</t>
   </si>
   <si>
     <t xml:space="preserve">2.71911072731018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69610667228699</t>
+    <t xml:space="preserve">2.69610643386841</t>
   </si>
   <si>
     <t xml:space="preserve">2.66850090026855</t>
@@ -3518,22 +3521,19 @@
     <t xml:space="preserve">2.82493090629578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85406947135925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89701056480408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97829294204712</t>
+    <t xml:space="preserve">2.85406970977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89701080322266</t>
   </si>
   <si>
     <t xml:space="preserve">2.86327123641968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94148516654968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03503680229187</t>
+    <t xml:space="preserve">2.94148540496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03503656387329</t>
   </si>
   <si>
     <t xml:space="preserve">3.02736854553223</t>
@@ -3545,25 +3545,25 @@
     <t xml:space="preserve">2.74058127403259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7850558757782</t>
+    <t xml:space="preserve">2.78505611419678</t>
   </si>
   <si>
     <t xml:space="preserve">2.86480474472046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8279983997345</t>
+    <t xml:space="preserve">2.82799816131592</t>
   </si>
   <si>
     <t xml:space="preserve">2.97062468528748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92445611953735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90142869949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05187344551086</t>
+    <t xml:space="preserve">2.92445588111877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90142846107483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05187320709229</t>
   </si>
   <si>
     <t xml:space="preserve">3.07029509544373</t>
@@ -3572,7 +3572,7 @@
     <t xml:space="preserve">3.15472817420959</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08871674537659</t>
+    <t xml:space="preserve">3.08871698379517</t>
   </si>
   <si>
     <t xml:space="preserve">3.19771218299866</t>
@@ -3584,7 +3584,7 @@
     <t xml:space="preserve">3.18850111961365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2529776096344</t>
+    <t xml:space="preserve">3.25297737121582</t>
   </si>
   <si>
     <t xml:space="preserve">3.16547417640686</t>
@@ -3593,13 +3593,13 @@
     <t xml:space="preserve">3.09485745429993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94748306274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80010890960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84769868850708</t>
+    <t xml:space="preserve">2.94748330116272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80010914802551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8476984500885</t>
   </si>
   <si>
     <t xml:space="preserve">2.72028136253357</t>
@@ -3617,13 +3617,13 @@
     <t xml:space="preserve">2.25359654426575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24592113494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33342432975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5345287322998</t>
+    <t xml:space="preserve">2.24592089653015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33342409133911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53452849388123</t>
   </si>
   <si>
     <t xml:space="preserve">2.40557622909546</t>
@@ -3638,19 +3638,19 @@
     <t xml:space="preserve">2.56983685493469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75098419189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7248866558075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76326560974121</t>
+    <t xml:space="preserve">2.75098443031311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72488689422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76326537132263</t>
   </si>
   <si>
     <t xml:space="preserve">2.78015208244324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82927680015564</t>
+    <t xml:space="preserve">2.82927703857422</t>
   </si>
   <si>
     <t xml:space="preserve">2.79550361633301</t>
@@ -3659,13 +3659,13 @@
     <t xml:space="preserve">2.79243326187134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73870301246643</t>
+    <t xml:space="preserve">2.73870325088501</t>
   </si>
   <si>
     <t xml:space="preserve">2.79703879356384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9229211807251</t>
+    <t xml:space="preserve">2.92292094230652</t>
   </si>
   <si>
     <t xml:space="preserve">2.92906141281128</t>
@@ -3674,22 +3674,22 @@
     <t xml:space="preserve">2.85383915901184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89221787452698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91831517219543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89835834503174</t>
+    <t xml:space="preserve">2.8922176361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91831541061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89835858345032</t>
   </si>
   <si>
     <t xml:space="preserve">2.80931997299194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79857349395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93366694450378</t>
+    <t xml:space="preserve">2.7985737323761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93366670608521</t>
   </si>
   <si>
     <t xml:space="preserve">2.94594788551331</t>
@@ -3701,7 +3701,7 @@
     <t xml:space="preserve">2.93980741500854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88607716560364</t>
+    <t xml:space="preserve">2.88607740402222</t>
   </si>
   <si>
     <t xml:space="preserve">2.96590495109558</t>
@@ -3722,37 +3722,37 @@
     <t xml:space="preserve">2.90296411514282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90756964683533</t>
+    <t xml:space="preserve">2.90756940841675</t>
   </si>
   <si>
     <t xml:space="preserve">2.7908980846405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78936290740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75712466239929</t>
+    <t xml:space="preserve">2.78936314582825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75712490081787</t>
   </si>
   <si>
     <t xml:space="preserve">2.68343782424927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78168725967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80624938011169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82467126846313</t>
+    <t xml:space="preserve">2.78168749809265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80624961853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82467150688171</t>
   </si>
   <si>
     <t xml:space="preserve">2.81853055953979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88147187232971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86151504516602</t>
+    <t xml:space="preserve">2.88147163391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86151480674744</t>
   </si>
   <si>
     <t xml:space="preserve">2.85230398178101</t>
@@ -3761,25 +3761,25 @@
     <t xml:space="preserve">2.81239008903503</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05270981788635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07706665992737</t>
+    <t xml:space="preserve">3.05271005630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07706642150879</t>
   </si>
   <si>
     <t xml:space="preserve">3.13065147399902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13877034187317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1176609992981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07544279098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04946255683899</t>
+    <t xml:space="preserve">3.13877058029175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11766123771667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07544302940369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04946231842041</t>
   </si>
   <si>
     <t xml:space="preserve">3.01211524009705</t>
@@ -3809,7 +3809,7 @@
     <t xml:space="preserve">2.62565517425537</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74256753921509</t>
+    <t xml:space="preserve">2.74256777763367</t>
   </si>
   <si>
     <t xml:space="preserve">2.66137862205505</t>
@@ -3818,13 +3818,13 @@
     <t xml:space="preserve">2.70197296142578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76367664337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78478598594666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77666735649109</t>
+    <t xml:space="preserve">2.76367688179016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78478574752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77666711807251</t>
   </si>
   <si>
     <t xml:space="preserve">2.6954779624939</t>
@@ -3833,10 +3833,10 @@
     <t xml:space="preserve">2.73282480239868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69385433197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70034909248352</t>
+    <t xml:space="preserve">2.69385409355164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7003493309021</t>
   </si>
   <si>
     <t xml:space="preserve">2.75880527496338</t>
@@ -3854,13 +3854,13 @@
     <t xml:space="preserve">2.59480357170105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60129857063293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67274522781372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76042914390564</t>
+    <t xml:space="preserve">2.60129880905151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67274498939514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76042938232422</t>
   </si>
   <si>
     <t xml:space="preserve">2.71821093559265</t>
@@ -3869,25 +3869,25 @@
     <t xml:space="preserve">2.70359683036804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64026927947998</t>
+    <t xml:space="preserve">2.64026951789856</t>
   </si>
   <si>
     <t xml:space="preserve">2.51361417770386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52822875976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57207036018372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69060635566711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61428880691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57856559753418</t>
+    <t xml:space="preserve">2.52822852134705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57207059860229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69060659408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61428904533386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57856583595276</t>
   </si>
   <si>
     <t xml:space="preserve">2.54608988761902</t>
@@ -3896,13 +3896,13 @@
     <t xml:space="preserve">2.58343696594238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51686191558838</t>
+    <t xml:space="preserve">2.5168616771698</t>
   </si>
   <si>
     <t xml:space="preserve">2.55908012390137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62727904319763</t>
+    <t xml:space="preserve">2.62727928161621</t>
   </si>
   <si>
     <t xml:space="preserve">2.65975475311279</t>
@@ -3911,31 +3911,31 @@
     <t xml:space="preserve">2.72957730293274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6694974899292</t>
+    <t xml:space="preserve">2.66949772834778</t>
   </si>
   <si>
     <t xml:space="preserve">2.78153848648071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7360725402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71496367454529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71171569824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70684456825256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61753630638123</t>
+    <t xml:space="preserve">2.73607230186462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71496343612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71171545982361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70684432983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6175365447998</t>
   </si>
   <si>
     <t xml:space="preserve">2.66624975204468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60941743850708</t>
+    <t xml:space="preserve">2.60941767692566</t>
   </si>
   <si>
     <t xml:space="preserve">2.56395149230957</t>
@@ -3953,7 +3953,7 @@
     <t xml:space="preserve">2.56070399284363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59642720222473</t>
+    <t xml:space="preserve">2.59642744064331</t>
   </si>
   <si>
     <t xml:space="preserve">2.59805107116699</t>
@@ -3968,28 +3968,28 @@
     <t xml:space="preserve">2.82050919532776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81726169586182</t>
+    <t xml:space="preserve">2.81726145744324</t>
   </si>
   <si>
     <t xml:space="preserve">2.84811329841614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92767858505249</t>
+    <t xml:space="preserve">2.92767882347107</t>
   </si>
   <si>
     <t xml:space="preserve">2.90819334983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88870787620544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83999466896057</t>
+    <t xml:space="preserve">2.88870811462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83999443054199</t>
   </si>
   <si>
     <t xml:space="preserve">2.78965735435486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85136103630066</t>
+    <t xml:space="preserve">2.85136127471924</t>
   </si>
   <si>
     <t xml:space="preserve">2.7880334854126</t>
@@ -4001,13 +4001,13 @@
     <t xml:space="preserve">2.64514064788818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75393414497375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7669243812561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8546085357666</t>
+    <t xml:space="preserve">2.75393390655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76692414283752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85460877418518</t>
   </si>
   <si>
     <t xml:space="preserve">2.7929048538208</t>
@@ -4028,10 +4028,10 @@
     <t xml:space="preserve">2.75555801391602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83512330055237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86435127258301</t>
+    <t xml:space="preserve">2.83512306213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86435151100159</t>
   </si>
   <si>
     <t xml:space="preserve">2.87734150886536</t>
@@ -4052,7 +4052,7 @@
     <t xml:space="preserve">2.95528316497803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9471640586853</t>
+    <t xml:space="preserve">2.94716429710388</t>
   </si>
   <si>
     <t xml:space="preserve">2.95690679550171</t>
@@ -4061,13 +4061,13 @@
     <t xml:space="preserve">3.02997708320618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04459118843079</t>
+    <t xml:space="preserve">3.04459095001221</t>
   </si>
   <si>
     <t xml:space="preserve">3.10467100143433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87409377098083</t>
+    <t xml:space="preserve">2.87409400939941</t>
   </si>
   <si>
     <t xml:space="preserve">2.8497371673584</t>
@@ -4076,13 +4076,13 @@
     <t xml:space="preserve">2.89520311355591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88708400726318</t>
+    <t xml:space="preserve">2.88708424568176</t>
   </si>
   <si>
     <t xml:space="preserve">2.91793608665466</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04621505737305</t>
+    <t xml:space="preserve">3.04621481895447</t>
   </si>
   <si>
     <t xml:space="preserve">3.05108594894409</t>
@@ -4091,10 +4091,10 @@
     <t xml:space="preserve">3.1014232635498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10629487037659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11441349983215</t>
+    <t xml:space="preserve">3.10629463195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11441373825073</t>
   </si>
   <si>
     <t xml:space="preserve">3.15987944602966</t>
@@ -4103,13 +4103,13 @@
     <t xml:space="preserve">3.12740397453308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16637468338013</t>
+    <t xml:space="preserve">3.16637492179871</t>
   </si>
   <si>
     <t xml:space="preserve">3.14201784133911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12090873718262</t>
+    <t xml:space="preserve">3.1209089756012</t>
   </si>
   <si>
     <t xml:space="preserve">3.08031415939331</t>
@@ -4118,7 +4118,7 @@
     <t xml:space="preserve">3.07219505310059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08193802833557</t>
+    <t xml:space="preserve">3.08193778991699</t>
   </si>
   <si>
     <t xml:space="preserve">3.09168076515198</t>
@@ -4127,7 +4127,7 @@
     <t xml:space="preserve">3.09817576408386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06894779205322</t>
+    <t xml:space="preserve">3.06894755363464</t>
   </si>
   <si>
     <t xml:space="preserve">3.04134345054626</t>
@@ -4136,25 +4136,25 @@
     <t xml:space="preserve">3.11278986930847</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17449355125427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18261241912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17611718177795</t>
+    <t xml:space="preserve">3.17449378967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.182612657547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17611742019653</t>
   </si>
   <si>
     <t xml:space="preserve">3.14039421081543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12415623664856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17774105072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21508836746216</t>
+    <t xml:space="preserve">3.12415647506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17774128913879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21508812904358</t>
   </si>
   <si>
     <t xml:space="preserve">3.26542520523071</t>
@@ -4163,10 +4163,10 @@
     <t xml:space="preserve">3.28003931045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27679181098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2702968120575</t>
+    <t xml:space="preserve">3.2767915725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27029657363892</t>
   </si>
   <si>
     <t xml:space="preserve">3.31251502037048</t>
@@ -4175,7 +4175,7 @@
     <t xml:space="preserve">3.3417432308197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29465365409851</t>
+    <t xml:space="preserve">3.29465341567993</t>
   </si>
   <si>
     <t xml:space="preserve">3.32388138771057</t>
@@ -4196,34 +4196,34 @@
     <t xml:space="preserve">3.48301196098328</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51386404037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53822064399719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52035903930664</t>
+    <t xml:space="preserve">3.51386380195618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53822040557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52035927772522</t>
   </si>
   <si>
     <t xml:space="preserve">3.65838050842285</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73307466506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65675687789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66487574577332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70222282409668</t>
+    <t xml:space="preserve">3.733074426651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65675711631775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66487550735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7022225856781</t>
   </si>
   <si>
     <t xml:space="preserve">3.68436098098755</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65026140213013</t>
+    <t xml:space="preserve">3.65026164054871</t>
   </si>
   <si>
     <t xml:space="preserve">3.62428140640259</t>
@@ -4235,7 +4235,7 @@
     <t xml:space="preserve">3.59505319595337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60804295539856</t>
+    <t xml:space="preserve">3.60804343223572</t>
   </si>
   <si>
     <t xml:space="preserve">3.64539003372192</t>
@@ -4244,58 +4244,58 @@
     <t xml:space="preserve">3.59830093383789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64376640319824</t>
+    <t xml:space="preserve">3.64376664161682</t>
   </si>
   <si>
     <t xml:space="preserve">3.61616206169128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68598461151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69572734832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81101536750793</t>
+    <t xml:space="preserve">3.68598508834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69572782516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81101608276367</t>
   </si>
   <si>
     <t xml:space="preserve">3.90032410621643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87921476364136</t>
+    <t xml:space="preserve">3.87921500205994</t>
   </si>
   <si>
     <t xml:space="preserve">3.89870047569275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89382863044739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97177076339722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89220499992371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91980957984924</t>
+    <t xml:space="preserve">3.89382886886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97177052497864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89220523834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91980934143066</t>
   </si>
   <si>
     <t xml:space="preserve">3.82400631904602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41806101799011</t>
+    <t xml:space="preserve">3.41806077957153</t>
   </si>
   <si>
     <t xml:space="preserve">3.41643738746643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19885015487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21021699905396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09492826461792</t>
+    <t xml:space="preserve">3.19885039329529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21021676063538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09492802619934</t>
   </si>
   <si>
     <t xml:space="preserve">3.37259483337402</t>
@@ -4307,7 +4307,7 @@
     <t xml:space="preserve">3.21995949745178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08843326568604</t>
+    <t xml:space="preserve">3.08843302726746</t>
   </si>
   <si>
     <t xml:space="preserve">3.09330439567566</t>
@@ -4316,16 +4316,16 @@
     <t xml:space="preserve">3.09979963302612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19560265541077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21184086799622</t>
+    <t xml:space="preserve">3.19560289382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21184062957764</t>
   </si>
   <si>
     <t xml:space="preserve">3.1517608165741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27192091941833</t>
+    <t xml:space="preserve">3.27192044258118</t>
   </si>
   <si>
     <t xml:space="preserve">3.28815841674805</t>
@@ -4334,13 +4334,13 @@
     <t xml:space="preserve">3.31738638877869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36122846603394</t>
+    <t xml:space="preserve">3.36122822761536</t>
   </si>
   <si>
     <t xml:space="preserve">3.34823822975159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44891262054443</t>
+    <t xml:space="preserve">3.44891309738159</t>
   </si>
   <si>
     <t xml:space="preserve">3.4342987537384</t>
@@ -4358,7 +4358,7 @@
     <t xml:space="preserve">3.34661459922791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32712912559509</t>
+    <t xml:space="preserve">3.32712888717651</t>
   </si>
   <si>
     <t xml:space="preserve">3.26704931259155</t>
@@ -4367,16 +4367,16 @@
     <t xml:space="preserve">3.38720893859863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4310507774353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50736904144287</t>
+    <t xml:space="preserve">3.43105101585388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50736880302429</t>
   </si>
   <si>
     <t xml:space="preserve">3.36934733390808</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38558506965637</t>
+    <t xml:space="preserve">3.38558530807495</t>
   </si>
   <si>
     <t xml:space="preserve">3.38233757019043</t>
@@ -5937,6 +5937,9 @@
   </si>
   <si>
     <t xml:space="preserve">15.4049997329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3450002670288</t>
   </si>
 </sst>
 </file>
@@ -39755,7 +39758,7 @@
         <v>2.03996992111206</v>
       </c>
       <c r="G1288" t="s">
-        <v>658</v>
+        <v>973</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -39781,7 +39784,7 @@
         <v>2.07793188095093</v>
       </c>
       <c r="G1289" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -39859,7 +39862,7 @@
         <v>2.10989999771118</v>
       </c>
       <c r="G1292" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -39885,7 +39888,7 @@
         <v>2.14586400985718</v>
       </c>
       <c r="G1293" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -39937,7 +39940,7 @@
         <v>2.31169891357422</v>
       </c>
       <c r="G1295" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -39963,7 +39966,7 @@
         <v>2.49551606178284</v>
       </c>
       <c r="G1296" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -39989,7 +39992,7 @@
         <v>2.45755410194397</v>
       </c>
       <c r="G1297" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -40015,7 +40018,7 @@
         <v>2.48752403259277</v>
       </c>
       <c r="G1298" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -40041,7 +40044,7 @@
         <v>2.47153997421265</v>
       </c>
       <c r="G1299" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -40067,7 +40070,7 @@
         <v>2.48752403259277</v>
       </c>
       <c r="G1300" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -40093,7 +40096,7 @@
         <v>2.45355796813965</v>
       </c>
       <c r="G1301" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -40119,7 +40122,7 @@
         <v>2.49951195716858</v>
       </c>
       <c r="G1302" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -40145,7 +40148,7 @@
         <v>2.44756388664246</v>
       </c>
       <c r="G1303" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -40171,7 +40174,7 @@
         <v>2.39361810684204</v>
       </c>
       <c r="G1304" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -40197,7 +40200,7 @@
         <v>2.42159008979797</v>
       </c>
       <c r="G1305" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -40223,7 +40226,7 @@
         <v>2.40960192680359</v>
       </c>
       <c r="G1306" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -40249,7 +40252,7 @@
         <v>2.40560603141785</v>
       </c>
       <c r="G1307" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -40275,7 +40278,7 @@
         <v>2.41559600830078</v>
       </c>
       <c r="G1308" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -40301,7 +40304,7 @@
         <v>2.39161992073059</v>
       </c>
       <c r="G1309" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -40327,7 +40330,7 @@
         <v>2.38362789154053</v>
       </c>
       <c r="G1310" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -40353,7 +40356,7 @@
         <v>2.44157004356384</v>
       </c>
       <c r="G1311" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -40379,7 +40382,7 @@
         <v>2.42758393287659</v>
       </c>
       <c r="G1312" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -40405,7 +40408,7 @@
         <v>2.44157004356384</v>
       </c>
       <c r="G1313" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -40431,7 +40434,7 @@
         <v>2.41759395599365</v>
       </c>
       <c r="G1314" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -40457,7 +40460,7 @@
         <v>2.44756388664246</v>
       </c>
       <c r="G1315" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -40483,7 +40486,7 @@
         <v>2.47553610801697</v>
       </c>
       <c r="G1316" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -40509,7 +40512,7 @@
         <v>2.47153997421265</v>
       </c>
       <c r="G1317" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -40535,7 +40538,7 @@
         <v>2.46554589271545</v>
       </c>
       <c r="G1318" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -40561,7 +40564,7 @@
         <v>2.54946303367615</v>
       </c>
       <c r="G1319" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -40587,7 +40590,7 @@
         <v>2.61939311027527</v>
       </c>
       <c r="G1320" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -40613,7 +40616,7 @@
         <v>2.71729588508606</v>
       </c>
       <c r="G1321" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -40639,7 +40642,7 @@
         <v>2.8271861076355</v>
       </c>
       <c r="G1322" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -40665,7 +40668,7 @@
         <v>2.88512897491455</v>
       </c>
       <c r="G1323" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -40691,7 +40694,7 @@
         <v>2.84716701507568</v>
       </c>
       <c r="G1324" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -40717,7 +40720,7 @@
         <v>2.84716701507568</v>
       </c>
       <c r="G1325" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -40743,7 +40746,7 @@
         <v>2.81719589233398</v>
       </c>
       <c r="G1326" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -40769,7 +40772,7 @@
         <v>2.78722596168518</v>
       </c>
       <c r="G1327" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -40795,7 +40798,7 @@
         <v>2.85116291046143</v>
       </c>
       <c r="G1328" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -40821,7 +40824,7 @@
         <v>2.82518792152405</v>
       </c>
       <c r="G1329" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -40847,7 +40850,7 @@
         <v>2.84716701507568</v>
       </c>
       <c r="G1330" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -40873,7 +40876,7 @@
         <v>2.82918405532837</v>
       </c>
       <c r="G1331" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -40899,7 +40902,7 @@
         <v>2.94307088851929</v>
       </c>
       <c r="G1332" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -40925,7 +40928,7 @@
         <v>2.85316109657288</v>
       </c>
       <c r="G1333" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -40951,7 +40954,7 @@
         <v>2.89711689949036</v>
       </c>
       <c r="G1334" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -40977,7 +40980,7 @@
         <v>2.89711689949036</v>
       </c>
       <c r="G1335" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -41003,7 +41006,7 @@
         <v>2.89312100410461</v>
       </c>
       <c r="G1336" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -41029,7 +41032,7 @@
         <v>2.84716701507568</v>
       </c>
       <c r="G1337" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -41055,7 +41058,7 @@
         <v>2.82518792152405</v>
       </c>
       <c r="G1338" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -41081,7 +41084,7 @@
         <v>2.86914491653442</v>
       </c>
       <c r="G1339" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -41107,7 +41110,7 @@
         <v>2.87114310264587</v>
       </c>
       <c r="G1340" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -41133,7 +41136,7 @@
         <v>2.95705699920654</v>
       </c>
       <c r="G1341" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -41159,7 +41162,7 @@
         <v>2.97304105758667</v>
       </c>
       <c r="G1342" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -41185,7 +41188,7 @@
         <v>3.00301194190979</v>
       </c>
       <c r="G1343" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -41211,7 +41214,7 @@
         <v>3.04497003555298</v>
       </c>
       <c r="G1344" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -41237,7 +41240,7 @@
         <v>2.95905494689941</v>
       </c>
       <c r="G1345" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -41263,7 +41266,7 @@
         <v>2.9710431098938</v>
       </c>
       <c r="G1346" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -41289,7 +41292,7 @@
         <v>2.97503900527954</v>
       </c>
       <c r="G1347" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -41315,7 +41318,7 @@
         <v>3.04497003555298</v>
       </c>
       <c r="G1348" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -41341,7 +41344,7 @@
         <v>3.13488006591797</v>
       </c>
       <c r="G1349" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -41367,7 +41370,7 @@
         <v>3.17484092712402</v>
       </c>
       <c r="G1350" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -41393,7 +41396,7 @@
         <v>3.28273296356201</v>
       </c>
       <c r="G1351" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -41419,7 +41422,7 @@
         <v>3.37264394760132</v>
       </c>
       <c r="G1352" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -41445,7 +41448,7 @@
         <v>3.49652004241943</v>
       </c>
       <c r="G1353" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -41471,7 +41474,7 @@
         <v>3.46255397796631</v>
       </c>
       <c r="G1354" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -41497,7 +41500,7 @@
         <v>3.44257402420044</v>
       </c>
       <c r="G1355" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -41523,7 +41526,7 @@
         <v>3.57444310188293</v>
       </c>
       <c r="G1356" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -41549,7 +41552,7 @@
         <v>3.62239503860474</v>
       </c>
       <c r="G1357" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -41575,7 +41578,7 @@
         <v>3.68633198738098</v>
       </c>
       <c r="G1358" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -41601,7 +41604,7 @@
         <v>3.81820011138916</v>
       </c>
       <c r="G1359" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -41627,7 +41630,7 @@
         <v>3.79022789001465</v>
       </c>
       <c r="G1360" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -41653,7 +41656,7 @@
         <v>3.78623199462891</v>
       </c>
       <c r="G1361" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -41679,7 +41682,7 @@
         <v>3.89212703704834</v>
       </c>
       <c r="G1362" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -41705,7 +41708,7 @@
         <v>3.89612293243408</v>
       </c>
       <c r="G1363" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -41731,7 +41734,7 @@
         <v>3.87814092636108</v>
       </c>
       <c r="G1364" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -41757,7 +41760,7 @@
         <v>3.94207692146301</v>
       </c>
       <c r="G1365" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -41783,7 +41786,7 @@
         <v>3.92409491539001</v>
       </c>
       <c r="G1366" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -41809,7 +41812,7 @@
         <v>3.91210699081421</v>
       </c>
       <c r="G1367" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -41835,7 +41838,7 @@
         <v>3.94007897377014</v>
       </c>
       <c r="G1368" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -41861,7 +41864,7 @@
         <v>4.01800203323364</v>
       </c>
       <c r="G1369" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -41887,7 +41890,7 @@
         <v>4.00401592254639</v>
       </c>
       <c r="G1370" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -41913,7 +41916,7 @@
         <v>3.9840350151062</v>
       </c>
       <c r="G1371" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -41939,7 +41942,7 @@
         <v>4.10791206359863</v>
       </c>
       <c r="G1372" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -41965,7 +41968,7 @@
         <v>4.027991771698</v>
       </c>
       <c r="G1373" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -41991,7 +41994,7 @@
         <v>4.05796194076538</v>
       </c>
       <c r="G1374" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -42017,7 +42020,7 @@
         <v>4.15986013412476</v>
       </c>
       <c r="G1375" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -42043,7 +42046,7 @@
         <v>4.1898307800293</v>
       </c>
       <c r="G1376" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -42069,7 +42072,7 @@
         <v>4.15386581420898</v>
       </c>
       <c r="G1377" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -42095,7 +42098,7 @@
         <v>4.13588380813599</v>
       </c>
       <c r="G1378" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -42121,7 +42124,7 @@
         <v>4.07594394683838</v>
       </c>
       <c r="G1379" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -42147,7 +42150,7 @@
         <v>3.99002909660339</v>
       </c>
       <c r="G1380" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -42173,7 +42176,7 @@
         <v>3.89212703704834</v>
       </c>
       <c r="G1381" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -42199,7 +42202,7 @@
         <v>3.86415505409241</v>
       </c>
       <c r="G1382" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -42225,7 +42228,7 @@
         <v>3.85616302490234</v>
       </c>
       <c r="G1383" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -42251,7 +42254,7 @@
         <v>3.83618211746216</v>
       </c>
       <c r="G1384" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -42277,7 +42280,7 @@
         <v>3.79622197151184</v>
       </c>
       <c r="G1385" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -42303,7 +42306,7 @@
         <v>3.78023791313171</v>
       </c>
       <c r="G1386" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -42329,7 +42332,7 @@
         <v>3.68832993507385</v>
       </c>
       <c r="G1387" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -42355,7 +42358,7 @@
         <v>3.65036702156067</v>
       </c>
       <c r="G1388" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -42381,7 +42384,7 @@
         <v>3.6483690738678</v>
       </c>
       <c r="G1389" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -42407,7 +42410,7 @@
         <v>3.56445288658142</v>
       </c>
       <c r="G1390" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -42433,7 +42436,7 @@
         <v>3.64037704467773</v>
       </c>
       <c r="G1391" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -42459,7 +42462,7 @@
         <v>3.63837909698486</v>
       </c>
       <c r="G1392" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -42485,7 +42488,7 @@
         <v>3.69632196426392</v>
       </c>
       <c r="G1393" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -42511,7 +42514,7 @@
         <v>3.60441303253174</v>
       </c>
       <c r="G1394" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -42537,7 +42540,7 @@
         <v>3.69632196426392</v>
       </c>
       <c r="G1395" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -42563,7 +42566,7 @@
         <v>3.65436291694641</v>
       </c>
       <c r="G1396" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -42589,7 +42592,7 @@
         <v>3.68832993507385</v>
       </c>
       <c r="G1397" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -42615,7 +42618,7 @@
         <v>3.63638091087341</v>
       </c>
       <c r="G1398" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -42641,7 +42644,7 @@
         <v>3.72229599952698</v>
       </c>
       <c r="G1399" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -42667,7 +42670,7 @@
         <v>3.62439298629761</v>
       </c>
       <c r="G1400" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -42693,7 +42696,7 @@
         <v>3.58443307876587</v>
       </c>
       <c r="G1401" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -42719,7 +42722,7 @@
         <v>3.54846906661987</v>
       </c>
       <c r="G1402" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -42745,7 +42748,7 @@
         <v>3.70431399345398</v>
       </c>
       <c r="G1403" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -42771,7 +42774,7 @@
         <v>3.64237499237061</v>
       </c>
       <c r="G1404" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -42797,7 +42800,7 @@
         <v>3.62039709091187</v>
       </c>
       <c r="G1405" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -42823,7 +42826,7 @@
         <v>3.63638091087341</v>
       </c>
       <c r="G1406" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -42849,7 +42852,7 @@
         <v>3.55046701431274</v>
       </c>
       <c r="G1407" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -42875,7 +42878,7 @@
         <v>3.48253393173218</v>
       </c>
       <c r="G1408" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -42901,7 +42904,7 @@
         <v>3.36265397071838</v>
       </c>
       <c r="G1409" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -42927,7 +42930,7 @@
         <v>3.47254395484924</v>
       </c>
       <c r="G1410" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -42953,7 +42956,7 @@
         <v>3.56045699119568</v>
       </c>
       <c r="G1411" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -42979,7 +42982,7 @@
         <v>3.59242510795593</v>
       </c>
       <c r="G1412" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -43005,7 +43008,7 @@
         <v>3.62639093399048</v>
       </c>
       <c r="G1413" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -43031,7 +43034,7 @@
         <v>3.81220602989197</v>
       </c>
       <c r="G1414" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -43057,7 +43060,7 @@
         <v>3.76425409317017</v>
       </c>
       <c r="G1415" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -43083,7 +43086,7 @@
         <v>3.83418393135071</v>
       </c>
       <c r="G1416" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -43109,7 +43112,7 @@
         <v>3.78822994232178</v>
       </c>
       <c r="G1417" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -43135,7 +43138,7 @@
         <v>3.71430397033691</v>
       </c>
       <c r="G1418" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -43161,7 +43164,7 @@
         <v>3.72629189491272</v>
       </c>
       <c r="G1419" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -43187,7 +43190,7 @@
         <v>3.72429394721985</v>
       </c>
       <c r="G1420" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -43213,7 +43216,7 @@
         <v>3.69831991195679</v>
       </c>
       <c r="G1421" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -43239,7 +43242,7 @@
         <v>3.70631194114685</v>
       </c>
       <c r="G1422" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -43265,7 +43268,7 @@
         <v>3.80221605300903</v>
       </c>
       <c r="G1423" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -43291,7 +43294,7 @@
         <v>3.84617304801941</v>
       </c>
       <c r="G1424" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -43317,7 +43320,7 @@
         <v>3.78423404693604</v>
       </c>
       <c r="G1425" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -43343,7 +43346,7 @@
         <v>3.86615300178528</v>
       </c>
       <c r="G1426" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -43369,7 +43372,7 @@
         <v>3.81420397758484</v>
       </c>
       <c r="G1427" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -43395,7 +43398,7 @@
         <v>3.8102080821991</v>
       </c>
       <c r="G1428" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -43421,7 +43424,7 @@
         <v>3.79622197151184</v>
       </c>
       <c r="G1429" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -43447,7 +43450,7 @@
         <v>3.69432401657104</v>
       </c>
       <c r="G1430" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -43473,7 +43476,7 @@
         <v>3.72829008102417</v>
       </c>
       <c r="G1431" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -43499,7 +43502,7 @@
         <v>3.70830988883972</v>
       </c>
       <c r="G1432" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -43525,7 +43528,7 @@
         <v>3.69432401657104</v>
       </c>
       <c r="G1433" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -43551,7 +43554,7 @@
         <v>3.75026798248291</v>
       </c>
       <c r="G1434" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -43577,7 +43580,7 @@
         <v>3.77624201774597</v>
       </c>
       <c r="G1435" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -43603,7 +43606,7 @@
         <v>3.90811109542847</v>
       </c>
       <c r="G1436" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -43629,7 +43632,7 @@
         <v>3.9181010723114</v>
       </c>
       <c r="G1437" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -43655,7 +43658,7 @@
         <v>3.88613295555115</v>
       </c>
       <c r="G1438" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -43681,7 +43684,7 @@
         <v>3.89012908935547</v>
       </c>
       <c r="G1439" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -43707,7 +43710,7 @@
         <v>3.84817099571228</v>
       </c>
       <c r="G1440" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -43733,7 +43736,7 @@
         <v>3.89212703704834</v>
       </c>
       <c r="G1441" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -43759,7 +43762,7 @@
         <v>3.89612293243408</v>
       </c>
       <c r="G1442" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -43785,7 +43788,7 @@
         <v>3.82619190216064</v>
       </c>
       <c r="G1443" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -43811,7 +43814,7 @@
         <v>3.85216689109802</v>
       </c>
       <c r="G1444" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -43837,7 +43840,7 @@
         <v>3.77823996543884</v>
       </c>
       <c r="G1445" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -43863,7 +43866,7 @@
         <v>3.70231604576111</v>
       </c>
       <c r="G1446" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -43889,7 +43892,7 @@
         <v>3.74427390098572</v>
       </c>
       <c r="G1447" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -43915,7 +43918,7 @@
         <v>3.68832993507385</v>
       </c>
       <c r="G1448" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -43941,7 +43944,7 @@
         <v>3.70830988883972</v>
       </c>
       <c r="G1449" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -43967,7 +43970,7 @@
         <v>3.67034792900085</v>
       </c>
       <c r="G1450" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -43993,7 +43996,7 @@
         <v>3.60241508483887</v>
       </c>
       <c r="G1451" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -44019,7 +44022,7 @@
         <v>3.68633198738098</v>
       </c>
       <c r="G1452" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -44045,7 +44048,7 @@
         <v>3.60840892791748</v>
       </c>
       <c r="G1453" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -44071,7 +44074,7 @@
         <v>3.52049708366394</v>
       </c>
       <c r="G1454" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -44097,7 +44100,7 @@
         <v>3.52449297904968</v>
       </c>
       <c r="G1455" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -44123,7 +44126,7 @@
         <v>3.64437294006348</v>
       </c>
       <c r="G1456" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -44149,7 +44152,7 @@
         <v>3.65636110305786</v>
       </c>
       <c r="G1457" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -44175,7 +44178,7 @@
         <v>3.6663510799408</v>
       </c>
       <c r="G1458" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -44201,7 +44204,7 @@
         <v>3.69632196426392</v>
       </c>
       <c r="G1459" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -44227,7 +44230,7 @@
         <v>3.63638091087341</v>
       </c>
       <c r="G1460" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -44253,7 +44256,7 @@
         <v>3.62239503860474</v>
       </c>
       <c r="G1461" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -44279,7 +44282,7 @@
         <v>3.68233609199524</v>
       </c>
       <c r="G1462" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -44305,7 +44308,7 @@
         <v>3.71030807495117</v>
       </c>
       <c r="G1463" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -44331,7 +44334,7 @@
         <v>3.67833995819092</v>
       </c>
       <c r="G1464" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -44357,7 +44360,7 @@
         <v>3.81820011138916</v>
       </c>
       <c r="G1465" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -44383,7 +44386,7 @@
         <v>3.78223609924316</v>
       </c>
       <c r="G1466" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -44409,7 +44412,7 @@
         <v>3.7562620639801</v>
       </c>
       <c r="G1467" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -44435,7 +44438,7 @@
         <v>3.73428392410278</v>
       </c>
       <c r="G1468" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -44461,7 +44464,7 @@
         <v>3.74627208709717</v>
       </c>
       <c r="G1469" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -44487,7 +44490,7 @@
         <v>3.78623199462891</v>
       </c>
       <c r="G1470" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -44513,7 +44516,7 @@
         <v>3.73428392410278</v>
       </c>
       <c r="G1471" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -44539,7 +44542,7 @@
         <v>3.77624201774597</v>
       </c>
       <c r="G1472" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -44565,7 +44568,7 @@
         <v>3.85016894340515</v>
       </c>
       <c r="G1473" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -44591,7 +44594,7 @@
         <v>3.87614297866821</v>
       </c>
       <c r="G1474" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -44617,7 +44620,7 @@
         <v>3.88613295555115</v>
       </c>
       <c r="G1475" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -44643,7 +44646,7 @@
         <v>3.89412498474121</v>
       </c>
       <c r="G1476" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -44669,7 +44672,7 @@
         <v>3.84417510032654</v>
       </c>
       <c r="G1477" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -44695,7 +44698,7 @@
         <v>3.90411496162415</v>
       </c>
       <c r="G1478" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -44721,7 +44724,7 @@
         <v>3.94607305526733</v>
       </c>
       <c r="G1479" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -44747,7 +44750,7 @@
         <v>3.95606303215027</v>
       </c>
       <c r="G1480" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -44773,7 +44776,7 @@
         <v>3.8042140007019</v>
       </c>
       <c r="G1481" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -44799,7 +44802,7 @@
         <v>3.82419395446777</v>
       </c>
       <c r="G1482" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -44825,7 +44828,7 @@
         <v>3.75226593017578</v>
       </c>
       <c r="G1483" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -44851,7 +44854,7 @@
         <v>3.79422402381897</v>
       </c>
       <c r="G1484" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -44877,7 +44880,7 @@
         <v>3.85016894340515</v>
       </c>
       <c r="G1485" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -44903,7 +44906,7 @@
         <v>3.85616302490234</v>
       </c>
       <c r="G1486" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -44929,7 +44932,7 @@
         <v>3.88413500785828</v>
       </c>
       <c r="G1487" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -44955,7 +44958,7 @@
         <v>3.95206689834595</v>
       </c>
       <c r="G1488" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -44981,7 +44984,7 @@
         <v>3.99002909660339</v>
       </c>
       <c r="G1489" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -45007,7 +45010,7 @@
         <v>3.84217691421509</v>
       </c>
       <c r="G1490" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -45033,7 +45036,7 @@
         <v>3.8102080821991</v>
       </c>
       <c r="G1491" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -45059,7 +45062,7 @@
         <v>3.7562620639801</v>
       </c>
       <c r="G1492" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -45085,7 +45088,7 @@
         <v>3.72029805183411</v>
       </c>
       <c r="G1493" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -45111,7 +45114,7 @@
         <v>3.68633198738098</v>
       </c>
       <c r="G1494" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -45137,7 +45140,7 @@
         <v>3.65835905075073</v>
       </c>
       <c r="G1495" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -45163,7 +45166,7 @@
         <v>3.59841895103455</v>
       </c>
       <c r="G1496" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -45189,7 +45192,7 @@
         <v>3.61440300941467</v>
       </c>
       <c r="G1497" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -45215,7 +45218,7 @@
         <v>3.51650094985962</v>
       </c>
       <c r="G1498" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -45241,7 +45244,7 @@
         <v>3.52649092674255</v>
       </c>
       <c r="G1499" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -45267,7 +45270,7 @@
         <v>3.46655011177063</v>
       </c>
       <c r="G1500" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -45293,7 +45296,7 @@
         <v>3.59642100334167</v>
       </c>
       <c r="G1501" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -45319,7 +45322,7 @@
         <v>3.53248500823975</v>
       </c>
       <c r="G1502" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -45345,7 +45348,7 @@
         <v>3.37264394760132</v>
       </c>
       <c r="G1503" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -45371,7 +45374,7 @@
         <v>3.55845904350281</v>
       </c>
       <c r="G1504" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -45397,7 +45400,7 @@
         <v>3.41659998893738</v>
       </c>
       <c r="G1505" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -45423,7 +45426,7 @@
         <v>3.45256400108337</v>
       </c>
       <c r="G1506" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -45449,7 +45452,7 @@
         <v>3.48852801322937</v>
       </c>
       <c r="G1507" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -45475,7 +45478,7 @@
         <v>3.48453211784363</v>
       </c>
       <c r="G1508" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -45501,7 +45504,7 @@
         <v>3.57843899726868</v>
       </c>
       <c r="G1509" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -45527,7 +45530,7 @@
         <v>3.59242510795593</v>
       </c>
       <c r="G1510" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -45553,7 +45556,7 @@
         <v>3.54447293281555</v>
       </c>
       <c r="G1511" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -45579,7 +45582,7 @@
         <v>3.54247498512268</v>
       </c>
       <c r="G1512" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -45605,7 +45608,7 @@
         <v>3.51250505447388</v>
       </c>
       <c r="G1513" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -45631,7 +45634,7 @@
         <v>3.47654008865356</v>
       </c>
       <c r="G1514" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -45657,7 +45660,7 @@
         <v>3.56445288658142</v>
       </c>
       <c r="G1515" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -45683,7 +45686,7 @@
         <v>3.70431399345398</v>
       </c>
       <c r="G1516" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -45709,7 +45712,7 @@
         <v>3.65436291694641</v>
       </c>
       <c r="G1517" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -45735,7 +45738,7 @@
         <v>3.59841895103455</v>
       </c>
       <c r="G1518" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -45761,7 +45764,7 @@
         <v>3.58842897415161</v>
       </c>
       <c r="G1519" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -45787,7 +45790,7 @@
         <v>3.62039709091187</v>
       </c>
       <c r="G1520" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -45813,7 +45816,7 @@
         <v>3.68033790588379</v>
       </c>
       <c r="G1521" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -45839,7 +45842,7 @@
         <v>3.70631194114685</v>
       </c>
       <c r="G1522" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -45865,7 +45868,7 @@
         <v>3.70431399345398</v>
       </c>
       <c r="G1523" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -45891,7 +45894,7 @@
         <v>3.71830010414124</v>
       </c>
       <c r="G1524" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -45917,7 +45920,7 @@
         <v>3.7742440700531</v>
       </c>
       <c r="G1525" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -45943,7 +45946,7 @@
         <v>3.69432401657104</v>
       </c>
       <c r="G1526" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -45969,7 +45972,7 @@
         <v>3.78423404693604</v>
       </c>
       <c r="G1527" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -45995,7 +45998,7 @@
         <v>3.84217691421509</v>
       </c>
       <c r="G1528" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -46021,7 +46024,7 @@
         <v>3.88013911247253</v>
       </c>
       <c r="G1529" t="s">
-        <v>1170</v>
+        <v>1040</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -46047,7 +46050,7 @@
         <v>3.83618211746216</v>
       </c>
       <c r="G1530" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -46073,7 +46076,7 @@
         <v>3.78623199462891</v>
       </c>
       <c r="G1531" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -46151,7 +46154,7 @@
         <v>3.94607305526733</v>
       </c>
       <c r="G1534" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -46203,7 +46206,7 @@
         <v>3.95206689834595</v>
       </c>
       <c r="G1536" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -46255,7 +46258,7 @@
         <v>3.82419395446777</v>
       </c>
       <c r="G1538" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -46281,7 +46284,7 @@
         <v>3.76425409317017</v>
       </c>
       <c r="G1539" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -46411,7 +46414,7 @@
         <v>3.69831991195679</v>
       </c>
       <c r="G1544" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -46489,7 +46492,7 @@
         <v>3.70830988883972</v>
       </c>
       <c r="G1547" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -46515,7 +46518,7 @@
         <v>3.82619190216064</v>
       </c>
       <c r="G1548" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -46567,7 +46570,7 @@
         <v>3.89212703704834</v>
       </c>
       <c r="G1550" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -71509,7 +71512,7 @@
     </row>
     <row r="2510">
       <c r="A2510" s="1" t="n">
-        <v>45973.6912384259</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B2510" t="n">
         <v>1526968</v>
@@ -71530,6 +71533,32 @@
         <v>1974</v>
       </c>
       <c r="H2510" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" s="1" t="n">
+        <v>45974.6912615741</v>
+      </c>
+      <c r="B2511" t="n">
+        <v>940314</v>
+      </c>
+      <c r="C2511" t="n">
+        <v>15.6400003433228</v>
+      </c>
+      <c r="D2511" t="n">
+        <v>15.3299999237061</v>
+      </c>
+      <c r="E2511" t="n">
+        <v>15.4200000762939</v>
+      </c>
+      <c r="F2511" t="n">
+        <v>15.3450002670288</v>
+      </c>
+      <c r="G2511" t="s">
+        <v>1975</v>
+      </c>
+      <c r="H2511" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BPSO.MI.xlsx
+++ b/data/BPSO.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1983" uniqueCount="1983">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1984" uniqueCount="1984">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82907152175903</t>
+    <t xml:space="preserve">2.82907128334045</t>
   </si>
   <si>
     <t xml:space="preserve">BPSO.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80963730812073</t>
+    <t xml:space="preserve">2.80963754653931</t>
   </si>
   <si>
     <t xml:space="preserve">2.74855804443359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71246600151062</t>
+    <t xml:space="preserve">2.7124662399292</t>
   </si>
   <si>
     <t xml:space="preserve">2.63611721992493</t>
@@ -59,22 +59,22 @@
     <t xml:space="preserve">2.60835385322571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69303226470947</t>
+    <t xml:space="preserve">2.69303202629089</t>
   </si>
   <si>
     <t xml:space="preserve">2.69858455657959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61113047599792</t>
+    <t xml:space="preserve">2.61113023757935</t>
   </si>
   <si>
     <t xml:space="preserve">2.51257061958313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4556565284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26686644554138</t>
+    <t xml:space="preserve">2.45565629005432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2668662071228</t>
   </si>
   <si>
     <t xml:space="preserve">2.38069558143616</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">2.51951146125793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44455122947693</t>
+    <t xml:space="preserve">2.44455099105835</t>
   </si>
   <si>
     <t xml:space="preserve">2.35570859909058</t>
@@ -110,13 +110,13 @@
     <t xml:space="preserve">2.23216247558594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20995163917542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04059600830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06280660629272</t>
+    <t xml:space="preserve">2.20995211601257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04059624671936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06280636787415</t>
   </si>
   <si>
     <t xml:space="preserve">2.14331984519958</t>
@@ -125,40 +125,40 @@
     <t xml:space="preserve">2.07668828964233</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18218851089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22522163391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27797174453735</t>
+    <t xml:space="preserve">2.18218803405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22522187232971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27797150611877</t>
   </si>
   <si>
     <t xml:space="preserve">2.19329380989075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16553020477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24604415893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18635249137878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1766357421875</t>
+    <t xml:space="preserve">2.16553044319153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24604439735413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18635272979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17663598060608</t>
   </si>
   <si>
     <t xml:space="preserve">2.21550440788269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.259925365448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31822896003723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3876359462738</t>
+    <t xml:space="preserve">2.25992560386658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31822872161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38763618469238</t>
   </si>
   <si>
     <t xml:space="preserve">2.38208341598511</t>
@@ -167,22 +167,22 @@
     <t xml:space="preserve">2.37514281272888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2418794631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26270198822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25020837783813</t>
+    <t xml:space="preserve">2.24187922477722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26270174980164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25020861625671</t>
   </si>
   <si>
     <t xml:space="preserve">2.31961703300476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43344497680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35848474502563</t>
+    <t xml:space="preserve">2.43344521522522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35848498344421</t>
   </si>
   <si>
     <t xml:space="preserve">2.30156993865967</t>
@@ -191,22 +191,22 @@
     <t xml:space="preserve">2.34599161148071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35987329483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39318919181824</t>
+    <t xml:space="preserve">2.35987305641174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39318895339966</t>
   </si>
   <si>
     <t xml:space="preserve">2.29324126243591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23771476745605</t>
+    <t xml:space="preserve">2.23771500587463</t>
   </si>
   <si>
     <t xml:space="preserve">2.18774056434631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13915538787842</t>
+    <t xml:space="preserve">2.139155626297</t>
   </si>
   <si>
     <t xml:space="preserve">2.14748454093933</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">2.12110996246338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06974697113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01283264160156</t>
+    <t xml:space="preserve">2.06974720954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01283311843872</t>
   </si>
   <si>
     <t xml:space="preserve">2.01838541030884</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">2.12527418136597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22799801826477</t>
+    <t xml:space="preserve">2.22799777984619</t>
   </si>
   <si>
     <t xml:space="preserve">2.30295825004578</t>
@@ -245,34 +245,34 @@
     <t xml:space="preserve">2.29046487808228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33211016654968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32655739784241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27935981750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32378149032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30851101875305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26131367683411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23493885993958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15720129013062</t>
+    <t xml:space="preserve">2.3321099281311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32655763626099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27935934066772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32378101348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30851125717163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26131391525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.234938621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15720152854919</t>
   </si>
   <si>
     <t xml:space="preserve">2.11139249801636</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08224058151245</t>
+    <t xml:space="preserve">2.08224081993103</t>
   </si>
   <si>
     <t xml:space="preserve">2.09889912605286</t>
@@ -281,34 +281,34 @@
     <t xml:space="preserve">2.08918213844299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10583996772766</t>
+    <t xml:space="preserve">2.10584020614624</t>
   </si>
   <si>
     <t xml:space="preserve">2.04892492294312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03781962394714</t>
+    <t xml:space="preserve">2.03781986236572</t>
   </si>
   <si>
     <t xml:space="preserve">2.06558275222778</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03226733207703</t>
+    <t xml:space="preserve">2.03226709365845</t>
   </si>
   <si>
     <t xml:space="preserve">2.07252359390259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05725407600403</t>
+    <t xml:space="preserve">2.05725383758545</t>
   </si>
   <si>
     <t xml:space="preserve">2.05156683921814</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12691879272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19942760467529</t>
+    <t xml:space="preserve">2.12691855430603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19942736625671</t>
   </si>
   <si>
     <t xml:space="preserve">2.15393209457397</t>
@@ -317,49 +317,49 @@
     <t xml:space="preserve">2.17525792121887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15535378456116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09279680252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07147121429443</t>
+    <t xml:space="preserve">2.15535402297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09279704093933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07147145271301</t>
   </si>
   <si>
     <t xml:space="preserve">1.99896240234375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95773220062256</t>
+    <t xml:space="preserve">1.95773243904114</t>
   </si>
   <si>
     <t xml:space="preserve">1.87669312953949</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9890102148056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93640613555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94351482391357</t>
+    <t xml:space="preserve">1.98900997638702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93640649318695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94351518154144</t>
   </si>
   <si>
     <t xml:space="preserve">1.84114956855774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78143680095673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75157999992371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72598886489868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64210593700409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69613254070282</t>
+    <t xml:space="preserve">1.78143703937531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.751580119133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72598874568939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64210605621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69613242149353</t>
   </si>
   <si>
     <t xml:space="preserve">1.77006256580353</t>
@@ -368,19 +368,19 @@
     <t xml:space="preserve">1.81129324436188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7800145149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89375352859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63499760627747</t>
+    <t xml:space="preserve">1.78001427650452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89375340938568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63499772548676</t>
   </si>
   <si>
     <t xml:space="preserve">1.56533265113831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6691198348999</t>
+    <t xml:space="preserve">1.66911971569061</t>
   </si>
   <si>
     <t xml:space="preserve">1.65632355213165</t>
@@ -389,28 +389,28 @@
     <t xml:space="preserve">1.6392627954483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63641905784607</t>
+    <t xml:space="preserve">1.63641929626465</t>
   </si>
   <si>
     <t xml:space="preserve">1.57670652866364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51130652427673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52552378177643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53121066093445</t>
+    <t xml:space="preserve">1.51130640506744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52552390098572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53121078014374</t>
   </si>
   <si>
     <t xml:space="preserve">1.63784086704254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67196345329285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69471073150635</t>
+    <t xml:space="preserve">1.67196321487427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69471085071564</t>
   </si>
   <si>
     <t xml:space="preserve">1.67054164409637</t>
@@ -419,73 +419,73 @@
     <t xml:space="preserve">1.74304962158203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70892798900604</t>
+    <t xml:space="preserve">1.70892822742462</t>
   </si>
   <si>
     <t xml:space="preserve">1.72172379493713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77574956417084</t>
+    <t xml:space="preserve">1.77574944496155</t>
   </si>
   <si>
     <t xml:space="preserve">1.76721906661987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72741055488586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69755434989929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72456753253937</t>
+    <t xml:space="preserve">1.72741067409515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69755446910858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72456741333008</t>
   </si>
   <si>
     <t xml:space="preserve">1.71888029575348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66343283653259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55395913124084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57528495788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52125871181488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63357591629028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65916728973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64779305458069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68760204315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71461510658264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70608472824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70039808750153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7444714307785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70750617980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72030174732208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7316757440567</t>
+    <t xml:space="preserve">1.66343295574188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55395901203156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57528507709503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52125859260559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63357579708099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6591671705246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64779317378998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68760216236115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71461486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70608484745026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70039796829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74447131156921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70750641822815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72030162811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73167562484741</t>
   </si>
   <si>
     <t xml:space="preserve">1.78285884857178</t>
@@ -500,13 +500,13 @@
     <t xml:space="preserve">1.76437544822693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75584506988525</t>
+    <t xml:space="preserve">1.75584530830383</t>
   </si>
   <si>
     <t xml:space="preserve">1.76295387744904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74162793159485</t>
+    <t xml:space="preserve">1.74162769317627</t>
   </si>
   <si>
     <t xml:space="preserve">1.76864075660706</t>
@@ -515,37 +515,37 @@
     <t xml:space="preserve">1.74873661994934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73451912403107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78428053855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85252368450165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84967994689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81271505355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83546304702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84825837612152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85963213443756</t>
+    <t xml:space="preserve">1.73451924324036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78428041934967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85252356529236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84967982769012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81271493434906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8354629278183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84825825691223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85963201522827</t>
   </si>
   <si>
     <t xml:space="preserve">1.9477801322937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97621440887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09848427772522</t>
+    <t xml:space="preserve">1.9762145280838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09848403930664</t>
   </si>
   <si>
     <t xml:space="preserve">2.10843634605408</t>
@@ -554,22 +554,22 @@
     <t xml:space="preserve">2.07573628425598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08568859100342</t>
+    <t xml:space="preserve">2.08568835258484</t>
   </si>
   <si>
     <t xml:space="preserve">2.0885317325592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09706258773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16104054450989</t>
+    <t xml:space="preserve">2.09706234931946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16104102134705</t>
   </si>
   <si>
     <t xml:space="preserve">2.18236660957336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11412310600281</t>
+    <t xml:space="preserve">2.11412334442139</t>
   </si>
   <si>
     <t xml:space="preserve">2.00038385391235</t>
@@ -581,13 +581,13 @@
     <t xml:space="preserve">2.00891423225403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0529887676239</t>
+    <t xml:space="preserve">2.05298852920532</t>
   </si>
   <si>
     <t xml:space="preserve">2.06294059753418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11554455757141</t>
+    <t xml:space="preserve">2.11554479598999</t>
   </si>
   <si>
     <t xml:space="preserve">2.12549686431885</t>
@@ -605,31 +605,31 @@
     <t xml:space="preserve">2.08142328262329</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03592777252197</t>
+    <t xml:space="preserve">2.03592801094055</t>
   </si>
   <si>
     <t xml:space="preserve">2.07715797424316</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09990549087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08995389938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01033639907837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12407493591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10417103767395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07289266586304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16814947128296</t>
+    <t xml:space="preserve">2.09990525245667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08995366096497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01033592224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12407517433167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10417079925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0728931427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16814970970154</t>
   </si>
   <si>
     <t xml:space="preserve">2.27478003501892</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">2.26340627670288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23354911804199</t>
+    <t xml:space="preserve">2.23354887962341</t>
   </si>
   <si>
     <t xml:space="preserve">2.27193665504456</t>
@@ -653,13 +653,13 @@
     <t xml:space="preserve">2.1781017780304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16957116127014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23639225959778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22217512130737</t>
+    <t xml:space="preserve">2.16957092285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23639249801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22217488288879</t>
   </si>
   <si>
     <t xml:space="preserve">2.21791005134583</t>
@@ -668,28 +668,28 @@
     <t xml:space="preserve">2.2051146030426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22359681129456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26482796669006</t>
+    <t xml:space="preserve">2.22359704971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26482772827148</t>
   </si>
   <si>
     <t xml:space="preserve">2.31032299995422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31743168830872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34302258491516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34160089492798</t>
+    <t xml:space="preserve">2.31743144989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34302306175232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34160113334656</t>
   </si>
   <si>
     <t xml:space="preserve">2.30463624000549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29752731323242</t>
+    <t xml:space="preserve">2.297527551651</t>
   </si>
   <si>
     <t xml:space="preserve">2.29610562324524</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">2.36008381843567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3529748916626</t>
+    <t xml:space="preserve">2.35297536849976</t>
   </si>
   <si>
     <t xml:space="preserve">2.34017944335938</t>
@@ -707,22 +707,22 @@
     <t xml:space="preserve">2.40273594856262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41695332527161</t>
+    <t xml:space="preserve">2.41695356369019</t>
   </si>
   <si>
     <t xml:space="preserve">2.45249676704407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4112663269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41553163528442</t>
+    <t xml:space="preserve">2.41126656532288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.415531873703</t>
   </si>
   <si>
     <t xml:space="preserve">2.4240620136261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44396638870239</t>
+    <t xml:space="preserve">2.44396662712097</t>
   </si>
   <si>
     <t xml:space="preserve">2.35439658164978</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">2.33022737503052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36434888839722</t>
+    <t xml:space="preserve">2.3643491268158</t>
   </si>
   <si>
     <t xml:space="preserve">2.32738375663757</t>
@@ -743,19 +743,19 @@
     <t xml:space="preserve">2.28188824653625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30037093162537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32311868667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33449268341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30890130996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2989490032196</t>
+    <t xml:space="preserve">2.30037140846252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32311844825745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33449220657349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30890154838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29894924163818</t>
   </si>
   <si>
     <t xml:space="preserve">2.25629734992981</t>
@@ -764,19 +764,19 @@
     <t xml:space="preserve">2.12834048271179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1340274810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28473210334778</t>
+    <t xml:space="preserve">2.13402724266052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28473234176636</t>
   </si>
   <si>
     <t xml:space="preserve">2.22928404808044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27335786819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27904486656189</t>
+    <t xml:space="preserve">2.27335810661316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27904510498047</t>
   </si>
   <si>
     <t xml:space="preserve">2.31316661834717</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">2.37856698036194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32880544662476</t>
+    <t xml:space="preserve">2.32880520820618</t>
   </si>
   <si>
     <t xml:space="preserve">2.36719226837158</t>
@@ -797,43 +797,43 @@
     <t xml:space="preserve">2.34870982170105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29468393325806</t>
+    <t xml:space="preserve">2.29468441009521</t>
   </si>
   <si>
     <t xml:space="preserve">2.30321431159973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28757572174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32027530670166</t>
+    <t xml:space="preserve">2.28757548332214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32027554512024</t>
   </si>
   <si>
     <t xml:space="preserve">2.2833104133606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29041886329651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29326224327087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3060576915741</t>
+    <t xml:space="preserve">2.29041838645935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29326248168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30605792999268</t>
   </si>
   <si>
     <t xml:space="preserve">2.35581827163696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31174492835999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3316490650177</t>
+    <t xml:space="preserve">2.31174445152283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33164930343628</t>
   </si>
   <si>
     <t xml:space="preserve">2.46671414375305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43117094039917</t>
+    <t xml:space="preserve">2.43117117881775</t>
   </si>
   <si>
     <t xml:space="preserve">2.42974901199341</t>
@@ -842,13 +842,13 @@
     <t xml:space="preserve">2.49799275398254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46387052536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48661804199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51647543907166</t>
+    <t xml:space="preserve">2.46387076377869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48661828041077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51647520065308</t>
   </si>
   <si>
     <t xml:space="preserve">2.51789689064026</t>
@@ -857,28 +857,28 @@
     <t xml:space="preserve">2.56907916069031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53353548049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48803973197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50510144233704</t>
+    <t xml:space="preserve">2.533536195755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48803997039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50510120391846</t>
   </si>
   <si>
     <t xml:space="preserve">2.5079448223114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50936651229858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50652289390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55486154556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57221221923828</t>
+    <t xml:space="preserve">2.50936627388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50652313232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55486178398132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5722119808197</t>
   </si>
   <si>
     <t xml:space="preserve">2.63293862342834</t>
@@ -890,13 +890,13 @@
     <t xml:space="preserve">2.70667886734009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56642866134644</t>
+    <t xml:space="preserve">2.56642889976501</t>
   </si>
   <si>
     <t xml:space="preserve">2.52594375610352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52883577346802</t>
+    <t xml:space="preserve">2.5288360118866</t>
   </si>
   <si>
     <t xml:space="preserve">2.47389245033264</t>
@@ -905,31 +905,31 @@
     <t xml:space="preserve">2.52160620689392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51437664031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47100067138672</t>
+    <t xml:space="preserve">2.5143768787384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4710009098053</t>
   </si>
   <si>
     <t xml:space="preserve">2.48979711532593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47533845901489</t>
+    <t xml:space="preserve">2.47533869743347</t>
   </si>
   <si>
     <t xml:space="preserve">2.51726841926575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45654249191284</t>
+    <t xml:space="preserve">2.45654225349426</t>
   </si>
   <si>
     <t xml:space="preserve">2.47967576980591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46087980270386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48112177848816</t>
+    <t xml:space="preserve">2.46088004112244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48112201690674</t>
   </si>
   <si>
     <t xml:space="preserve">2.45798802375793</t>
@@ -941,10 +941,10 @@
     <t xml:space="preserve">2.48835134506226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48690509796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50859332084656</t>
+    <t xml:space="preserve">2.48690533638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50859355926514</t>
   </si>
   <si>
     <t xml:space="preserve">2.53751134872437</t>
@@ -956,10 +956,10 @@
     <t xml:space="preserve">2.55919909477234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49558067321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59245443344116</t>
+    <t xml:space="preserve">2.49558091163635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59245419502258</t>
   </si>
   <si>
     <t xml:space="preserve">2.66330242156982</t>
@@ -971,16 +971,16 @@
     <t xml:space="preserve">2.63149261474609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62281775474548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61703419685364</t>
+    <t xml:space="preserve">2.6228175163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61703443527222</t>
   </si>
   <si>
     <t xml:space="preserve">2.72692060470581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73704171180725</t>
+    <t xml:space="preserve">2.73704195022583</t>
   </si>
   <si>
     <t xml:space="preserve">2.72258281707764</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">2.71246218681335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71390795707703</t>
+    <t xml:space="preserve">2.71390771865845</t>
   </si>
   <si>
     <t xml:space="preserve">2.7081241607666</t>
@@ -1007,7 +1007,7 @@
     <t xml:space="preserve">2.7110161781311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6502890586853</t>
+    <t xml:space="preserve">2.65028882026672</t>
   </si>
   <si>
     <t xml:space="preserve">2.67920732498169</t>
@@ -1022,10 +1022,10 @@
     <t xml:space="preserve">2.65318083763123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65173482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.667640209198</t>
+    <t xml:space="preserve">2.65173506736755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66763997077942</t>
   </si>
   <si>
     <t xml:space="preserve">2.65896511077881</t>
@@ -1055,37 +1055,37 @@
     <t xml:space="preserve">2.48545932769775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50280976295471</t>
+    <t xml:space="preserve">2.50281000137329</t>
   </si>
   <si>
     <t xml:space="preserve">2.52016019821167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51148509979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51871418952942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53317308425903</t>
+    <t xml:space="preserve">2.51148533821106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.518714427948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53317284584045</t>
   </si>
   <si>
     <t xml:space="preserve">2.55196976661682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50714731216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55052423477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54618620872498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53606534004211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5794415473938</t>
+    <t xml:space="preserve">2.50714755058289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55052447319031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54618644714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53606557846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57944130897522</t>
   </si>
   <si>
     <t xml:space="preserve">2.64161348342896</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">2.58956265449524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52305173873901</t>
+    <t xml:space="preserve">2.52305197715759</t>
   </si>
   <si>
     <t xml:space="preserve">2.51582264900208</t>
@@ -1109,10 +1109,10 @@
     <t xml:space="preserve">2.53461909294128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4912428855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47244691848755</t>
+    <t xml:space="preserve">2.49124312400818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47244668006897</t>
   </si>
   <si>
     <t xml:space="preserve">2.50425577163696</t>
@@ -1121,13 +1121,13 @@
     <t xml:space="preserve">2.48401379585266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49413466453552</t>
+    <t xml:space="preserve">2.49413442611694</t>
   </si>
   <si>
     <t xml:space="preserve">2.4984724521637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47823047637939</t>
+    <t xml:space="preserve">2.47823023796082</t>
   </si>
   <si>
     <t xml:space="preserve">2.51293063163757</t>
@@ -1160,10 +1160,10 @@
     <t xml:space="preserve">2.19773054122925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22086453437805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26279449462891</t>
+    <t xml:space="preserve">2.22086429595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26279425621033</t>
   </si>
   <si>
     <t xml:space="preserve">2.28448271751404</t>
@@ -1178,19 +1178,19 @@
     <t xml:space="preserve">2.34810137748718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37846493721008</t>
+    <t xml:space="preserve">2.3784646987915</t>
   </si>
   <si>
     <t xml:space="preserve">2.41461229324341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34231805801392</t>
+    <t xml:space="preserve">2.3423182964325</t>
   </si>
   <si>
     <t xml:space="preserve">2.35677671432495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35966873168945</t>
+    <t xml:space="preserve">2.35966849327087</t>
   </si>
   <si>
     <t xml:space="preserve">2.34087181091309</t>
@@ -1199,25 +1199,25 @@
     <t xml:space="preserve">2.37701869010925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39292359352112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40015268325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4059362411499</t>
+    <t xml:space="preserve">2.3929238319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40015292167664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40593647956848</t>
   </si>
   <si>
     <t xml:space="preserve">2.33653426170349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29315733909607</t>
+    <t xml:space="preserve">2.29315757751465</t>
   </si>
   <si>
     <t xml:space="preserve">2.20496010780334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2396605014801</t>
+    <t xml:space="preserve">2.23966073989868</t>
   </si>
   <si>
     <t xml:space="preserve">2.23821496963501</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">2.23387718200684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18327212333679</t>
+    <t xml:space="preserve">2.18327188491821</t>
   </si>
   <si>
     <t xml:space="preserve">2.21797251701355</t>
@@ -1238,7 +1238,7 @@
     <t xml:space="preserve">2.20062232017517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22664785385132</t>
+    <t xml:space="preserve">2.22664761543274</t>
   </si>
   <si>
     <t xml:space="preserve">2.28303670883179</t>
@@ -1253,10 +1253,10 @@
     <t xml:space="preserve">2.38858556747437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38714027404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34665560722351</t>
+    <t xml:space="preserve">2.38714003562927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34665584564209</t>
   </si>
   <si>
     <t xml:space="preserve">2.34520959854126</t>
@@ -1268,19 +1268,19 @@
     <t xml:space="preserve">2.39436912536621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40304446220398</t>
+    <t xml:space="preserve">2.4030442237854</t>
   </si>
   <si>
     <t xml:space="preserve">2.40448999404907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32785940170288</t>
+    <t xml:space="preserve">2.3278591632843</t>
   </si>
   <si>
     <t xml:space="preserve">2.34954738616943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33364295959473</t>
+    <t xml:space="preserve">2.33364319801331</t>
   </si>
   <si>
     <t xml:space="preserve">2.31195473670959</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">2.22953963279724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31484627723694</t>
+    <t xml:space="preserve">2.31484651565552</t>
   </si>
   <si>
     <t xml:space="preserve">2.30327963829041</t>
@@ -1301,13 +1301,13 @@
     <t xml:space="preserve">2.30761694908142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37268114089966</t>
+    <t xml:space="preserve">2.37268137931824</t>
   </si>
   <si>
     <t xml:space="preserve">2.42907071113586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36400604248047</t>
+    <t xml:space="preserve">2.36400580406189</t>
   </si>
   <si>
     <t xml:space="preserve">2.31629228591919</t>
@@ -1319,10 +1319,10 @@
     <t xml:space="preserve">2.27725315093994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32930493354797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30617141723633</t>
+    <t xml:space="preserve">2.32930517196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30617165565491</t>
   </si>
   <si>
     <t xml:space="preserve">2.30038809776306</t>
@@ -1334,13 +1334,13 @@
     <t xml:space="preserve">2.33075070381165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32641339302063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39726090431213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39870667457581</t>
+    <t xml:space="preserve">2.32641363143921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39726066589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39870643615723</t>
   </si>
   <si>
     <t xml:space="preserve">2.38569402694702</t>
@@ -1358,13 +1358,13 @@
     <t xml:space="preserve">2.75439214706421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77752661705017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84837460517883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84114503860474</t>
+    <t xml:space="preserve">2.77752685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84837436676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84114480018616</t>
   </si>
   <si>
     <t xml:space="preserve">2.83391571044922</t>
@@ -1379,13 +1379,13 @@
     <t xml:space="preserve">2.82957816123962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73125815391541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78620195388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75583791732788</t>
+    <t xml:space="preserve">2.73125839233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78620171546936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7558376789093</t>
   </si>
   <si>
     <t xml:space="preserve">2.82524061203003</t>
@@ -1394,13 +1394,13 @@
     <t xml:space="preserve">2.80644416809082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83680725097656</t>
+    <t xml:space="preserve">2.83680701255798</t>
   </si>
   <si>
     <t xml:space="preserve">2.74716281890869</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73848748207092</t>
+    <t xml:space="preserve">2.7384877204895</t>
   </si>
   <si>
     <t xml:space="preserve">2.6343846321106</t>
@@ -1409,10 +1409,10 @@
     <t xml:space="preserve">2.66091990470886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65060091018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71251678466797</t>
+    <t xml:space="preserve">2.65060067176819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71251702308655</t>
   </si>
   <si>
     <t xml:space="preserve">2.7036714553833</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">2.63143634796143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52824234962463</t>
+    <t xml:space="preserve">2.52824258804321</t>
   </si>
   <si>
     <t xml:space="preserve">2.48254251480103</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">2.618168592453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59015917778015</t>
+    <t xml:space="preserve">2.59015893936157</t>
   </si>
   <si>
     <t xml:space="preserve">2.54888081550598</t>
@@ -1463,13 +1463,13 @@
     <t xml:space="preserve">2.54593276977539</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57099366188049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51350045204163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51055240631104</t>
+    <t xml:space="preserve">2.57099390029907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51350069046021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51055216789246</t>
   </si>
   <si>
     <t xml:space="preserve">2.53708744049072</t>
@@ -1481,22 +1481,22 @@
     <t xml:space="preserve">2.65354871749878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65944528579712</t>
+    <t xml:space="preserve">2.65944576263428</t>
   </si>
   <si>
     <t xml:space="preserve">2.70514559745789</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6904034614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65797162055969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61964273452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63291049003601</t>
+    <t xml:space="preserve">2.69040322303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65797185897827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61964249610901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63291025161743</t>
   </si>
   <si>
     <t xml:space="preserve">2.6491265296936</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">2.64322948455811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66534233093262</t>
+    <t xml:space="preserve">2.6653425693512</t>
   </si>
   <si>
     <t xml:space="preserve">2.64470386505127</t>
@@ -1520,7 +1520,7 @@
     <t xml:space="preserve">2.71399116516113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73168158531189</t>
+    <t xml:space="preserve">2.73168182373047</t>
   </si>
   <si>
     <t xml:space="preserve">2.71693968772888</t>
@@ -1541,34 +1541,34 @@
     <t xml:space="preserve">2.68892955780029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67713594436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64617824554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64175534248352</t>
+    <t xml:space="preserve">2.67713570594788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64617800712585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6417555809021</t>
   </si>
   <si>
     <t xml:space="preserve">2.57541632652283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61374568939209</t>
+    <t xml:space="preserve">2.61374592781067</t>
   </si>
   <si>
     <t xml:space="preserve">2.60932350158691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58868479728699</t>
+    <t xml:space="preserve">2.58868455886841</t>
   </si>
   <si>
     <t xml:space="preserve">2.58131289482117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53561329841614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48843932151794</t>
+    <t xml:space="preserve">2.53561353683472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48843955993652</t>
   </si>
   <si>
     <t xml:space="preserve">2.47222352027893</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">2.67123913764954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67418766021729</t>
+    <t xml:space="preserve">2.67418742179871</t>
   </si>
   <si>
     <t xml:space="preserve">2.65502333641052</t>
@@ -1592,10 +1592,10 @@
     <t xml:space="preserve">2.68450689315796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66239428520203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62406516075134</t>
+    <t xml:space="preserve">2.66239404678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62406539916992</t>
   </si>
   <si>
     <t xml:space="preserve">2.62996172904968</t>
@@ -1604,13 +1604,13 @@
     <t xml:space="preserve">2.63733291625977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62111687660217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42210054397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41915202140808</t>
+    <t xml:space="preserve">2.62111663818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42210030555725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4191517829895</t>
   </si>
   <si>
     <t xml:space="preserve">2.36608123779297</t>
@@ -1622,16 +1622,16 @@
     <t xml:space="preserve">2.41325521469116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33659648895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24667167663574</t>
+    <t xml:space="preserve">2.33659672737122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24667191505432</t>
   </si>
   <si>
     <t xml:space="preserve">2.23045563697815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22898125648499</t>
+    <t xml:space="preserve">2.22898149490356</t>
   </si>
   <si>
     <t xml:space="preserve">2.16706490516663</t>
@@ -1643,7 +1643,7 @@
     <t xml:space="preserve">2.15674567222595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20244526863098</t>
+    <t xml:space="preserve">2.20244550704956</t>
   </si>
   <si>
     <t xml:space="preserve">2.19360017776489</t>
@@ -1652,22 +1652,22 @@
     <t xml:space="preserve">2.13905549049377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11399435997009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08745813369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04175853729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00932645797729</t>
+    <t xml:space="preserve">2.11399412155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08745837211609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0417582988739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00932621955872</t>
   </si>
   <si>
     <t xml:space="preserve">2.05207777023315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10514903068542</t>
+    <t xml:space="preserve">2.105149269104</t>
   </si>
   <si>
     <t xml:space="preserve">2.05797410011292</t>
@@ -1676,7 +1676,7 @@
     <t xml:space="preserve">2.05502605438232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09335565567017</t>
+    <t xml:space="preserve">2.09335589408875</t>
   </si>
   <si>
     <t xml:space="preserve">2.13610696792603</t>
@@ -1694,7 +1694,7 @@
     <t xml:space="preserve">2.10072636604309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09040665626526</t>
+    <t xml:space="preserve">2.09040641784668</t>
   </si>
   <si>
     <t xml:space="preserve">2.04912924766541</t>
@@ -1703,10 +1703,10 @@
     <t xml:space="preserve">2.06829380989075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05060338973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04765510559082</t>
+    <t xml:space="preserve">2.05060315132141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0476553440094</t>
   </si>
   <si>
     <t xml:space="preserve">2.02701640129089</t>
@@ -1718,22 +1718,22 @@
     <t xml:space="preserve">1.97394585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97984278202057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96215176582336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98426508903503</t>
+    <t xml:space="preserve">1.97984254360199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96215164661407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98426485061646</t>
   </si>
   <si>
     <t xml:space="preserve">2.08008742332458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06387090682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07861280441284</t>
+    <t xml:space="preserve">2.06387114524841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07861304283142</t>
   </si>
   <si>
     <t xml:space="preserve">2.04618096351624</t>
@@ -1745,40 +1745,40 @@
     <t xml:space="preserve">2.05650043487549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95625495910645</t>
+    <t xml:space="preserve">1.95625483989716</t>
   </si>
   <si>
     <t xml:space="preserve">1.98279082775116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94446110725403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9370903968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96657431125641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96804857254028</t>
+    <t xml:space="preserve">1.9444614648819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93709027767181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96657407283783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96804869174957</t>
   </si>
   <si>
     <t xml:space="preserve">1.89286494255066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98131680488586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91497790813446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87517464160919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87370049953461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94003903865814</t>
+    <t xml:space="preserve">1.98131704330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91497778892517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87517476081848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87370038032532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94003891944885</t>
   </si>
   <si>
     <t xml:space="preserve">1.92677128314972</t>
@@ -1793,37 +1793,37 @@
     <t xml:space="preserve">1.994584441185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99163615703583</t>
+    <t xml:space="preserve">1.99163639545441</t>
   </si>
   <si>
     <t xml:space="preserve">1.94888389110565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88844239711761</t>
+    <t xml:space="preserve">1.8884425163269</t>
   </si>
   <si>
     <t xml:space="preserve">1.87222623825073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91940009593964</t>
+    <t xml:space="preserve">1.9194004535675</t>
   </si>
   <si>
     <t xml:space="preserve">1.89433920383453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86485552787781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85306215286255</t>
+    <t xml:space="preserve">1.86485540866852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85306203365326</t>
   </si>
   <si>
     <t xml:space="preserve">1.83831942081451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88549411296844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85158741474152</t>
+    <t xml:space="preserve">1.88549423217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85158753395081</t>
   </si>
   <si>
     <t xml:space="preserve">1.82505166530609</t>
@@ -1835,7 +1835,7 @@
     <t xml:space="preserve">1.71596133708954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69532263278961</t>
+    <t xml:space="preserve">1.69532251358032</t>
   </si>
   <si>
     <t xml:space="preserve">1.71006453037262</t>
@@ -1847,7 +1847,7 @@
     <t xml:space="preserve">1.78377449512482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76313591003418</t>
+    <t xml:space="preserve">1.76313579082489</t>
   </si>
   <si>
     <t xml:space="preserve">1.76166164875031</t>
@@ -1856,22 +1856,22 @@
     <t xml:space="preserve">1.78672301769257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80588722229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83389675617218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87664878368378</t>
+    <t xml:space="preserve">1.80588710308075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83389663696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87664890289307</t>
   </si>
   <si>
     <t xml:space="preserve">1.86927807331085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84569001197815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83979344367981</t>
+    <t xml:space="preserve">1.84569025039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8397935628891</t>
   </si>
   <si>
     <t xml:space="preserve">1.83242249488831</t>
@@ -1880,10 +1880,10 @@
     <t xml:space="preserve">1.84274184703827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83684527873993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8972874879837</t>
+    <t xml:space="preserve">1.83684515953064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89728736877441</t>
   </si>
   <si>
     <t xml:space="preserve">1.88991641998291</t>
@@ -1895,46 +1895,46 @@
     <t xml:space="preserve">1.91055512428284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87075209617615</t>
+    <t xml:space="preserve">1.87075221538544</t>
   </si>
   <si>
     <t xml:space="preserve">1.80293893814087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80441308021545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79114544391632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75576496124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81325829029083</t>
+    <t xml:space="preserve">1.80441319942474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79114556312561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75576508045197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81325840950012</t>
   </si>
   <si>
     <t xml:space="preserve">1.81178379058838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83537089824677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79556798934937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77492940425873</t>
+    <t xml:space="preserve">1.83537101745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79556787014008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77492928504944</t>
   </si>
   <si>
     <t xml:space="preserve">1.8088356256485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79851615428925</t>
+    <t xml:space="preserve">1.79851627349854</t>
   </si>
   <si>
     <t xml:space="preserve">1.79704225063324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80736148357391</t>
+    <t xml:space="preserve">1.8073616027832</t>
   </si>
   <si>
     <t xml:space="preserve">1.78082633018494</t>
@@ -1946,37 +1946,37 @@
     <t xml:space="preserve">1.71301293373108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70711624622345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74544560909271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76460993289948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77198088169098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77787744998932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78819692134857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74839413166046</t>
+    <t xml:space="preserve">1.70711612701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74544548988342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76461005210876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77198076248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77787756919861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78819704055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74839401245117</t>
   </si>
   <si>
     <t xml:space="preserve">1.6658388376236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67910647392273</t>
+    <t xml:space="preserve">1.67910659313202</t>
   </si>
   <si>
     <t xml:space="preserve">1.61129403114319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57886135578156</t>
+    <t xml:space="preserve">1.57886123657227</t>
   </si>
   <si>
     <t xml:space="preserve">1.53610992431641</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">1.53596556186676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56466102600098</t>
+    <t xml:space="preserve">1.56466090679169</t>
   </si>
   <si>
     <t xml:space="preserve">1.54351699352264</t>
@@ -2012,7 +2012,7 @@
     <t xml:space="preserve">1.60543847084045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58429443836212</t>
+    <t xml:space="preserve">1.58429455757141</t>
   </si>
   <si>
     <t xml:space="preserve">1.56768143177032</t>
@@ -2024,19 +2024,19 @@
     <t xml:space="preserve">1.58882534503937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51028990745544</t>
+    <t xml:space="preserve">1.51029002666473</t>
   </si>
   <si>
     <t xml:space="preserve">1.51935243606567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52690374851227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47177791595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47026741504669</t>
+    <t xml:space="preserve">1.52690386772156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4717777967453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47026753425598</t>
   </si>
   <si>
     <t xml:space="preserve">1.471022605896</t>
@@ -2072,7 +2072,7 @@
     <t xml:space="preserve">1.4808394908905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53294491767883</t>
+    <t xml:space="preserve">1.53294479846954</t>
   </si>
   <si>
     <t xml:space="preserve">1.57523286342621</t>
@@ -2084,7 +2084,7 @@
     <t xml:space="preserve">1.52539372444153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50424885749817</t>
+    <t xml:space="preserve">1.50424873828888</t>
   </si>
   <si>
     <t xml:space="preserve">1.47328805923462</t>
@@ -2096,7 +2096,7 @@
     <t xml:space="preserve">1.44912350177765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4536544084549</t>
+    <t xml:space="preserve">1.45365452766418</t>
   </si>
   <si>
     <t xml:space="preserve">1.46649181842804</t>
@@ -2120,16 +2120,16 @@
     <t xml:space="preserve">1.42722451686859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41665256023407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40683555603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40079462528229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39097762107849</t>
+    <t xml:space="preserve">1.41665244102478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40683567523956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.400794506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39097774028778</t>
   </si>
   <si>
     <t xml:space="preserve">1.3864461183548</t>
@@ -2138,19 +2138,19 @@
     <t xml:space="preserve">1.28374707698822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25354063510895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25127530097961</t>
+    <t xml:space="preserve">1.25354051589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25127518177032</t>
   </si>
   <si>
     <t xml:space="preserve">1.20068073272705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23617243766785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25278532505035</t>
+    <t xml:space="preserve">1.23617231845856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25278544425964</t>
   </si>
   <si>
     <t xml:space="preserve">1.22182464599609</t>
@@ -2204,7 +2204,7 @@
     <t xml:space="preserve">1.35095453262329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35926103591919</t>
+    <t xml:space="preserve">1.35926115512848</t>
   </si>
   <si>
     <t xml:space="preserve">1.36454689502716</t>
@@ -2213,7 +2213,7 @@
     <t xml:space="preserve">1.33736193180084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30262541770935</t>
+    <t xml:space="preserve">1.30262529850006</t>
   </si>
   <si>
     <t xml:space="preserve">1.2897881269455</t>
@@ -2228,7 +2228,7 @@
     <t xml:space="preserve">1.25505089759827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27468514442444</t>
+    <t xml:space="preserve">1.27468526363373</t>
   </si>
   <si>
     <t xml:space="preserve">1.27997124195099</t>
@@ -2240,7 +2240,7 @@
     <t xml:space="preserve">1.25429570674896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26939916610718</t>
+    <t xml:space="preserve">1.26939928531647</t>
   </si>
   <si>
     <t xml:space="preserve">1.28148150444031</t>
@@ -2270,25 +2270,25 @@
     <t xml:space="preserve">1.36152637004852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36228168010712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34113764762878</t>
+    <t xml:space="preserve">1.36228179931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34113776683807</t>
   </si>
   <si>
     <t xml:space="preserve">1.36756777763367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42495906352997</t>
+    <t xml:space="preserve">1.42495894432068</t>
   </si>
   <si>
     <t xml:space="preserve">1.41740763187408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43326556682587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40532529354095</t>
+    <t xml:space="preserve">1.43326544761658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40532541275024</t>
   </si>
   <si>
     <t xml:space="preserve">1.43477594852448</t>
@@ -2297,22 +2297,22 @@
     <t xml:space="preserve">1.62960290908813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58278429508209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57825362682343</t>
+    <t xml:space="preserve">1.5827841758728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57825350761414</t>
   </si>
   <si>
     <t xml:space="preserve">1.58127391338348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54653751850128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53747582435608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52237296104431</t>
+    <t xml:space="preserve">1.54653739929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53747594356537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52237284183502</t>
   </si>
   <si>
     <t xml:space="preserve">1.55257856845856</t>
@@ -2321,10 +2321,10 @@
     <t xml:space="preserve">1.60241782665253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63111317157745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6009076833725</t>
+    <t xml:space="preserve">1.63111329078674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60090780258179</t>
   </si>
   <si>
     <t xml:space="preserve">1.62054145336151</t>
@@ -2333,19 +2333,19 @@
     <t xml:space="preserve">1.54955792427063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57221233844757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61147952079773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64168608188629</t>
+    <t xml:space="preserve">1.57221245765686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61147940158844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64168620109558</t>
   </si>
   <si>
     <t xml:space="preserve">1.61298990249634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61752080917358</t>
+    <t xml:space="preserve">1.61752068996429</t>
   </si>
   <si>
     <t xml:space="preserve">1.59184587001801</t>
@@ -2360,19 +2360,19 @@
     <t xml:space="preserve">1.57976365089417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56013000011444</t>
+    <t xml:space="preserve">1.56013011932373</t>
   </si>
   <si>
     <t xml:space="preserve">1.55861973762512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59788703918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60392832756042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58580493927002</t>
+    <t xml:space="preserve">1.59788715839386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60392820835114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58580482006073</t>
   </si>
   <si>
     <t xml:space="preserve">1.59939742088318</t>
@@ -2384,10 +2384,10 @@
     <t xml:space="preserve">1.5903354883194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5299243927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51331114768982</t>
+    <t xml:space="preserve">1.52992451190948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51331126689911</t>
   </si>
   <si>
     <t xml:space="preserve">1.50953483581543</t>
@@ -2402,10 +2402,10 @@
     <t xml:space="preserve">1.63866460323334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75948786735535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80630743503571</t>
+    <t xml:space="preserve">1.75948798656464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80630731582642</t>
   </si>
   <si>
     <t xml:space="preserve">1.78365314006805</t>
@@ -2414,37 +2414,37 @@
     <t xml:space="preserve">1.83953356742859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02983069419861</t>
+    <t xml:space="preserve">2.02983093261719</t>
   </si>
   <si>
     <t xml:space="preserve">2.06909823417664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94827461242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89088296890259</t>
+    <t xml:space="preserve">1.94827473163605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89088308811188</t>
   </si>
   <si>
     <t xml:space="preserve">1.77912247180939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77308118343353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81687951087952</t>
+    <t xml:space="preserve">1.77308130264282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81687939167023</t>
   </si>
   <si>
     <t xml:space="preserve">1.70813846588135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4800843000412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37511897087097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3245245218277</t>
+    <t xml:space="preserve">1.48008418083191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37511885166168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32452464103699</t>
   </si>
   <si>
     <t xml:space="preserve">1.2407032251358</t>
@@ -2456,7 +2456,7 @@
     <t xml:space="preserve">1.18406772613525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.959789395332336</t>
+    <t xml:space="preserve">0.959789335727692</t>
   </si>
   <si>
     <t xml:space="preserve">0.995280861854553</t>
@@ -2465,7 +2465,7 @@
     <t xml:space="preserve">0.91901171207428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.945441484451294</t>
+    <t xml:space="preserve">0.945441544055939</t>
   </si>
   <si>
     <t xml:space="preserve">0.962809801101685</t>
@@ -2483,7 +2483,7 @@
     <t xml:space="preserve">1.07155084609985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07910239696503</t>
+    <t xml:space="preserve">1.07910227775574</t>
   </si>
   <si>
     <t xml:space="preserve">1.06777513027191</t>
@@ -2504,16 +2504,16 @@
     <t xml:space="preserve">1.10628736019135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05720317363739</t>
+    <t xml:space="preserve">1.05720329284668</t>
   </si>
   <si>
     <t xml:space="preserve">1.11459386348724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13875901699066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20219087600708</t>
+    <t xml:space="preserve">1.13875913619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20219099521637</t>
   </si>
   <si>
     <t xml:space="preserve">1.16745460033417</t>
@@ -2552,10 +2552,10 @@
     <t xml:space="preserve">1.09269499778748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03756964206696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07306110858917</t>
+    <t xml:space="preserve">1.03756952285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07306122779846</t>
   </si>
   <si>
     <t xml:space="preserve">1.04965174198151</t>
@@ -2567,13 +2567,13 @@
     <t xml:space="preserve">1.04436588287354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04285562038422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01189482212067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985464155673981</t>
+    <t xml:space="preserve">1.04285550117493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01189470291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985464036464691</t>
   </si>
   <si>
     <t xml:space="preserve">0.970361292362213</t>
@@ -2585,10 +2585,10 @@
     <t xml:space="preserve">0.943176209926605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.926563084125519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921276986598969</t>
+    <t xml:space="preserve">0.926563024520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921277046203613</t>
   </si>
   <si>
     <t xml:space="preserve">0.913725674152374</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">0.997546255588531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.058713555336</t>
+    <t xml:space="preserve">1.05871343612671</t>
   </si>
   <si>
     <t xml:space="preserve">1.09722566604614</t>
@@ -2627,13 +2627,13 @@
     <t xml:space="preserve">1.18935358524323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14782083034515</t>
+    <t xml:space="preserve">1.14782094955444</t>
   </si>
   <si>
     <t xml:space="preserve">1.16820967197418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1870881319046</t>
+    <t xml:space="preserve">1.18708825111389</t>
   </si>
   <si>
     <t xml:space="preserve">1.16216850280762</t>
@@ -2654,7 +2654,7 @@
     <t xml:space="preserve">1.36303675174713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40381515026093</t>
+    <t xml:space="preserve">1.40381503105164</t>
   </si>
   <si>
     <t xml:space="preserve">1.41136658191681</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">1.39399826526642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39928424358368</t>
+    <t xml:space="preserve">1.39928436279297</t>
   </si>
   <si>
     <t xml:space="preserve">1.4015496969223</t>
@@ -2681,10 +2681,10 @@
     <t xml:space="preserve">1.44836843013763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48763585090637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47630858421326</t>
+    <t xml:space="preserve">1.48763573169708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47630870342255</t>
   </si>
   <si>
     <t xml:space="preserve">1.46498155593872</t>
@@ -2714,7 +2714,7 @@
     <t xml:space="preserve">1.48461532592773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55106842517853</t>
+    <t xml:space="preserve">1.55106854438782</t>
   </si>
   <si>
     <t xml:space="preserve">1.5208625793457</t>
@@ -2726,16 +2726,16 @@
     <t xml:space="preserve">1.37813949584961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34415817260742</t>
+    <t xml:space="preserve">1.34415805339813</t>
   </si>
   <si>
     <t xml:space="preserve">1.37209844589233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39475333690643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37964987754822</t>
+    <t xml:space="preserve">1.39475345611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37964999675751</t>
   </si>
   <si>
     <t xml:space="preserve">1.38795721530914</t>
@@ -2753,7 +2753,7 @@
     <t xml:space="preserve">1.34340298175812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30036008358002</t>
+    <t xml:space="preserve">1.30036020278931</t>
   </si>
   <si>
     <t xml:space="preserve">1.32376945018768</t>
@@ -2765,13 +2765,13 @@
     <t xml:space="preserve">1.39777410030365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36983287334442</t>
+    <t xml:space="preserve">1.36983299255371</t>
   </si>
   <si>
     <t xml:space="preserve">1.38191533088684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34038245677948</t>
+    <t xml:space="preserve">1.34038257598877</t>
   </si>
   <si>
     <t xml:space="preserve">1.35473012924194</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">1.33207595348358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33585178852081</t>
+    <t xml:space="preserve">1.33585166931152</t>
   </si>
   <si>
     <t xml:space="preserve">1.27393019199371</t>
@@ -2810,7 +2810,7 @@
     <t xml:space="preserve">1.22711062431335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24221324920654</t>
+    <t xml:space="preserve">1.24221336841583</t>
   </si>
   <si>
     <t xml:space="preserve">1.23843777179718</t>
@@ -2819,7 +2819,7 @@
     <t xml:space="preserve">1.22862088680267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44232738018036</t>
+    <t xml:space="preserve">1.44232726097107</t>
   </si>
   <si>
     <t xml:space="preserve">1.43251049518585</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">1.50273859500885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55408895015717</t>
+    <t xml:space="preserve">1.55408883094788</t>
   </si>
   <si>
     <t xml:space="preserve">1.81234860420227</t>
@@ -2843,10 +2843,10 @@
     <t xml:space="preserve">1.75797772407532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69303560256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72173094749451</t>
+    <t xml:space="preserve">1.69303548336029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7217310667038</t>
   </si>
   <si>
     <t xml:space="preserve">1.68548405170441</t>
@@ -2858,7 +2858,7 @@
     <t xml:space="preserve">1.70360767841339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73079264163971</t>
+    <t xml:space="preserve">1.73079252243042</t>
   </si>
   <si>
     <t xml:space="preserve">1.72777223587036</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">1.69907665252686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6688711643219</t>
+    <t xml:space="preserve">1.66887104511261</t>
   </si>
   <si>
     <t xml:space="preserve">1.66282987594604</t>
@@ -2879,10 +2879,10 @@
     <t xml:space="preserve">1.66131985187531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67642259597778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64470660686493</t>
+    <t xml:space="preserve">1.67642247676849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64470648765564</t>
   </si>
   <si>
     <t xml:space="preserve">1.61601030826569</t>
@@ -2900,7 +2900,7 @@
     <t xml:space="preserve">1.66434013843536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74438512325287</t>
+    <t xml:space="preserve">1.74438524246216</t>
   </si>
   <si>
     <t xml:space="preserve">1.77761209011078</t>
@@ -2909,19 +2909,19 @@
     <t xml:space="preserve">1.756467461586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72022044658661</t>
+    <t xml:space="preserve">1.7202205657959</t>
   </si>
   <si>
     <t xml:space="preserve">1.73683369159698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69454598426819</t>
+    <t xml:space="preserve">1.6945458650589</t>
   </si>
   <si>
     <t xml:space="preserve">1.65225791931152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67491221427917</t>
+    <t xml:space="preserve">1.67491233348846</t>
   </si>
   <si>
     <t xml:space="preserve">1.65376830101013</t>
@@ -2933,7 +2933,7 @@
     <t xml:space="preserve">1.57070183753967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59486663341522</t>
+    <t xml:space="preserve">1.59486651420593</t>
   </si>
   <si>
     <t xml:space="preserve">1.62205147743225</t>
@@ -2945,13 +2945,13 @@
     <t xml:space="preserve">1.88635241985321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85765719413757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88031113147736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86822903156281</t>
+    <t xml:space="preserve">1.85765731334686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88031125068665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86822915077209</t>
   </si>
   <si>
     <t xml:space="preserve">1.85463631153107</t>
@@ -2966,7 +2966,7 @@
     <t xml:space="preserve">1.80932819843292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83047223091125</t>
+    <t xml:space="preserve">1.83047211170197</t>
   </si>
   <si>
     <t xml:space="preserve">1.82141005992889</t>
@@ -2984,16 +2984,16 @@
     <t xml:space="preserve">1.80177652835846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84557473659515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83500289916992</t>
+    <t xml:space="preserve">1.84557461738586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83500301837921</t>
   </si>
   <si>
     <t xml:space="preserve">1.82745134830475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87124979496002</t>
+    <t xml:space="preserve">1.87124967575073</t>
   </si>
   <si>
     <t xml:space="preserve">1.86369800567627</t>
@@ -3011,13 +3011,13 @@
     <t xml:space="preserve">2.13706088066101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18085932731628</t>
+    <t xml:space="preserve">2.18085956573486</t>
   </si>
   <si>
     <t xml:space="preserve">2.15216398239136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12950897216797</t>
+    <t xml:space="preserve">2.12950921058655</t>
   </si>
   <si>
     <t xml:space="preserve">2.10685515403748</t>
@@ -3038,13 +3038,13 @@
     <t xml:space="preserve">2.15669512748718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18992137908936</t>
+    <t xml:space="preserve">2.18992114067078</t>
   </si>
   <si>
     <t xml:space="preserve">2.18690085411072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16877746582031</t>
+    <t xml:space="preserve">2.16877722740173</t>
   </si>
   <si>
     <t xml:space="preserve">2.17028784751892</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">2.23673987388611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24580144882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24882245063782</t>
+    <t xml:space="preserve">2.2458016872406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24882221221924</t>
   </si>
   <si>
     <t xml:space="preserve">2.36964559555054</t>
@@ -3077,16 +3077,16 @@
     <t xml:space="preserve">2.39985179901123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48140740394592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54937028884888</t>
+    <t xml:space="preserve">2.48140716552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54937052726746</t>
   </si>
   <si>
     <t xml:space="preserve">2.64300799369812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61733317375183</t>
+    <t xml:space="preserve">2.61733341217041</t>
   </si>
   <si>
     <t xml:space="preserve">2.60223031044006</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">2.8650209903717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86200022697449</t>
+    <t xml:space="preserve">2.86200046539307</t>
   </si>
   <si>
     <t xml:space="preserve">2.94204592704773</t>
@@ -3116,13 +3116,13 @@
     <t xml:space="preserve">2.94506645202637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93147397041321</t>
+    <t xml:space="preserve">2.93147373199463</t>
   </si>
   <si>
     <t xml:space="preserve">2.97980284690857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96621060371399</t>
+    <t xml:space="preserve">2.96621036529541</t>
   </si>
   <si>
     <t xml:space="preserve">2.9571487903595</t>
@@ -3131,10 +3131,10 @@
     <t xml:space="preserve">2.97829294204712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08411264419556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07337737083435</t>
+    <t xml:space="preserve">3.08411288261414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07337760925293</t>
   </si>
   <si>
     <t xml:space="preserve">3.05804061889648</t>
@@ -3143,19 +3143,19 @@
     <t xml:space="preserve">3.15312528610229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0917809009552</t>
+    <t xml:space="preserve">3.09178066253662</t>
   </si>
   <si>
     <t xml:space="preserve">3.11478519439697</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19299936294556</t>
+    <t xml:space="preserve">3.19299960136414</t>
   </si>
   <si>
     <t xml:space="preserve">3.21600413322449</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18839859962463</t>
+    <t xml:space="preserve">3.18839836120605</t>
   </si>
   <si>
     <t xml:space="preserve">3.17459583282471</t>
@@ -3173,7 +3173,7 @@
     <t xml:space="preserve">2.96602392196655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95988965034485</t>
+    <t xml:space="preserve">2.95988941192627</t>
   </si>
   <si>
     <t xml:space="preserve">2.9445526599884</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">2.80039238929749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73598051071167</t>
+    <t xml:space="preserve">2.73598027229309</t>
   </si>
   <si>
     <t xml:space="preserve">2.7942578792572</t>
@@ -3206,16 +3206,16 @@
     <t xml:space="preserve">2.83719968795776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76665258407593</t>
+    <t xml:space="preserve">2.76665282249451</t>
   </si>
   <si>
     <t xml:space="preserve">2.80499291419983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79119038581848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85713648796082</t>
+    <t xml:space="preserve">2.79119062423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85713672637939</t>
   </si>
   <si>
     <t xml:space="preserve">2.78198885917664</t>
@@ -3224,22 +3224,22 @@
     <t xml:space="preserve">2.75131678581238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72371172904968</t>
+    <t xml:space="preserve">2.72371196746826</t>
   </si>
   <si>
     <t xml:space="preserve">2.84333419799805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79579138755798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77892184257507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72524523735046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6731014251709</t>
+    <t xml:space="preserve">2.7957911491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77892160415649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72524499893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67310166358948</t>
   </si>
   <si>
     <t xml:space="preserve">2.58108496665955</t>
@@ -3254,7 +3254,7 @@
     <t xml:space="preserve">2.75745129585266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78352236747742</t>
+    <t xml:space="preserve">2.783522605896</t>
   </si>
   <si>
     <t xml:space="preserve">2.92614936828613</t>
@@ -3269,25 +3269,25 @@
     <t xml:space="preserve">2.90774583816528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85100221633911</t>
+    <t xml:space="preserve">2.85100197792053</t>
   </si>
   <si>
     <t xml:space="preserve">2.86020398139954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8586699962616</t>
+    <t xml:space="preserve">2.85867023468018</t>
   </si>
   <si>
     <t xml:space="preserve">2.83873343467712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84486794471741</t>
+    <t xml:space="preserve">2.84486770629883</t>
   </si>
   <si>
     <t xml:space="preserve">2.91848111152649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95222139358521</t>
+    <t xml:space="preserve">2.95222115516663</t>
   </si>
   <si>
     <t xml:space="preserve">2.90467858314514</t>
@@ -3299,13 +3299,13 @@
     <t xml:space="preserve">2.92768263816833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92461585998535</t>
+    <t xml:space="preserve">2.92461562156677</t>
   </si>
   <si>
     <t xml:space="preserve">2.83566617965698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8617377281189</t>
+    <t xml:space="preserve">2.86173748970032</t>
   </si>
   <si>
     <t xml:space="preserve">2.84640145301819</t>
@@ -3317,13 +3317,13 @@
     <t xml:space="preserve">2.89854431152344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99976348876953</t>
+    <t xml:space="preserve">2.99976372718811</t>
   </si>
   <si>
     <t xml:space="preserve">3.0074315071106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98289346694946</t>
+    <t xml:space="preserve">2.98289370536804</t>
   </si>
   <si>
     <t xml:space="preserve">2.98596096038818</t>
@@ -3344,13 +3344,13 @@
     <t xml:space="preserve">2.90007781982422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84180045127869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8740062713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81726288795471</t>
+    <t xml:space="preserve">2.84180068969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87400650978088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81726264953613</t>
   </si>
   <si>
     <t xml:space="preserve">2.76511931419373</t>
@@ -3404,16 +3404,16 @@
     <t xml:space="preserve">2.87554001808167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90621209144592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95528841018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9752254486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98902797698975</t>
+    <t xml:space="preserve">2.9062123298645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95528864860535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97522568702698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98902821540833</t>
   </si>
   <si>
     <t xml:space="preserve">2.95068788528442</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">2.85560321807861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80806040763855</t>
+    <t xml:space="preserve">2.80806064605713</t>
   </si>
   <si>
     <t xml:space="preserve">2.76205205917358</t>
@@ -3461,22 +3461,22 @@
     <t xml:space="preserve">2.77432084083557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69917416572571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70684170722961</t>
+    <t xml:space="preserve">2.69917392730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70684194564819</t>
   </si>
   <si>
     <t xml:space="preserve">2.66083288192749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76051831245422</t>
+    <t xml:space="preserve">2.76051807403564</t>
   </si>
   <si>
     <t xml:space="preserve">2.71144270896912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58875274658203</t>
+    <t xml:space="preserve">2.58875298500061</t>
   </si>
   <si>
     <t xml:space="preserve">2.73137974739075</t>
@@ -3488,13 +3488,13 @@
     <t xml:space="preserve">2.65009760856628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67770266532898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67463517189026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74671602249146</t>
+    <t xml:space="preserve">2.6777024269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67463541030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74671578407288</t>
   </si>
   <si>
     <t xml:space="preserve">2.72064423561096</t>
@@ -3512,10 +3512,10 @@
     <t xml:space="preserve">2.75438380241394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8249306678772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85406923294067</t>
+    <t xml:space="preserve">2.82493090629578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85406947135925</t>
   </si>
   <si>
     <t xml:space="preserve">2.89701056480408</t>
@@ -3527,22 +3527,22 @@
     <t xml:space="preserve">2.94148540496826</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03503656387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02736878395081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89087605476379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74058127403259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78505611419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86480474472046</t>
+    <t xml:space="preserve">3.03503680229187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02736854553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89087629318237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74058151245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7850558757782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86480450630188</t>
   </si>
   <si>
     <t xml:space="preserve">2.82799816131592</t>
@@ -3563,13 +3563,13 @@
     <t xml:space="preserve">3.07029485702515</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15472817420959</t>
+    <t xml:space="preserve">3.15472841262817</t>
   </si>
   <si>
     <t xml:space="preserve">3.08871674537659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19771194458008</t>
+    <t xml:space="preserve">3.19771218299866</t>
   </si>
   <si>
     <t xml:space="preserve">3.21459889411926</t>
@@ -3590,28 +3590,28 @@
     <t xml:space="preserve">2.94748306274414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80010890960693</t>
+    <t xml:space="preserve">2.80010914802551</t>
   </si>
   <si>
     <t xml:space="preserve">2.84769868850708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72028136253357</t>
+    <t xml:space="preserve">2.72028112411499</t>
   </si>
   <si>
     <t xml:space="preserve">2.55602025985718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58979392051697</t>
+    <t xml:space="preserve">2.58979368209839</t>
   </si>
   <si>
     <t xml:space="preserve">2.54066896438599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25359654426575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24592065811157</t>
+    <t xml:space="preserve">2.25359630584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24592089653015</t>
   </si>
   <si>
     <t xml:space="preserve">2.33342409133911</t>
@@ -3656,13 +3656,13 @@
     <t xml:space="preserve">2.73870325088501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79703879356384</t>
+    <t xml:space="preserve">2.79703855514526</t>
   </si>
   <si>
     <t xml:space="preserve">2.92292094230652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9290611743927</t>
+    <t xml:space="preserve">2.92906141281128</t>
   </si>
   <si>
     <t xml:space="preserve">2.85383892059326</t>
@@ -3695,7 +3695,7 @@
     <t xml:space="preserve">2.93980741500854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88607716560364</t>
+    <t xml:space="preserve">2.88607740402222</t>
   </si>
   <si>
     <t xml:space="preserve">2.96590495109558</t>
@@ -3707,7 +3707,7 @@
     <t xml:space="preserve">2.90603423118591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92752599716187</t>
+    <t xml:space="preserve">2.92752623558044</t>
   </si>
   <si>
     <t xml:space="preserve">2.91678023338318</t>
@@ -3731,10 +3731,10 @@
     <t xml:space="preserve">2.68343782424927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78168749809265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80624961853027</t>
+    <t xml:space="preserve">2.78168725967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80624938011169</t>
   </si>
   <si>
     <t xml:space="preserve">2.82467126846313</t>
@@ -3743,34 +3743,34 @@
     <t xml:space="preserve">2.81853079795837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88147211074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86151480674744</t>
+    <t xml:space="preserve">2.88147187232971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86151504516602</t>
   </si>
   <si>
     <t xml:space="preserve">2.85230422019958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81239008903503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05271005630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07706642150879</t>
+    <t xml:space="preserve">2.81239032745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05270981788635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07706665992737</t>
   </si>
   <si>
     <t xml:space="preserve">3.13065147399902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13877058029175</t>
+    <t xml:space="preserve">3.13877034187317</t>
   </si>
   <si>
     <t xml:space="preserve">3.11766123771667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07544302940369</t>
+    <t xml:space="preserve">3.07544279098511</t>
   </si>
   <si>
     <t xml:space="preserve">3.04946231842041</t>
@@ -3794,28 +3794,28 @@
     <t xml:space="preserve">2.96664953231812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76205277442932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63377404212952</t>
+    <t xml:space="preserve">2.7620530128479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6337742805481</t>
   </si>
   <si>
     <t xml:space="preserve">2.62565517425537</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74256777763367</t>
+    <t xml:space="preserve">2.74256753921509</t>
   </si>
   <si>
     <t xml:space="preserve">2.66137862205505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70197296142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76367688179016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78478574752808</t>
+    <t xml:space="preserve">2.70197319984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76367664337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78478598594666</t>
   </si>
   <si>
     <t xml:space="preserve">2.77666711807251</t>
@@ -3827,10 +3827,10 @@
     <t xml:space="preserve">2.73282480239868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69385409355164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7003493309021</t>
+    <t xml:space="preserve">2.69385433197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70034909248352</t>
   </si>
   <si>
     <t xml:space="preserve">2.75880527496338</t>
@@ -3848,13 +3848,13 @@
     <t xml:space="preserve">2.59480357170105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60129880905151</t>
+    <t xml:space="preserve">2.60129857063293</t>
   </si>
   <si>
     <t xml:space="preserve">2.67274498939514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76042938232422</t>
+    <t xml:space="preserve">2.76042914390564</t>
   </si>
   <si>
     <t xml:space="preserve">2.71821093559265</t>
@@ -3878,19 +3878,19 @@
     <t xml:space="preserve">2.69060659408569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61428904533386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57856583595276</t>
+    <t xml:space="preserve">2.61428880691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57856559753418</t>
   </si>
   <si>
     <t xml:space="preserve">2.54608988761902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58343696594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5168616771698</t>
+    <t xml:space="preserve">2.58343720436096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51686191558838</t>
   </si>
   <si>
     <t xml:space="preserve">2.55908012390137</t>
@@ -3905,7 +3905,7 @@
     <t xml:space="preserve">2.72957730293274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66949772834778</t>
+    <t xml:space="preserve">2.6694974899292</t>
   </si>
   <si>
     <t xml:space="preserve">2.78153848648071</t>
@@ -3917,19 +3917,19 @@
     <t xml:space="preserve">2.71496343612671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71171545982361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70684432983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6175365447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66624975204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60941767692566</t>
+    <t xml:space="preserve">2.71171569824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70684456825256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61753630638123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66624999046326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60941743850708</t>
   </si>
   <si>
     <t xml:space="preserve">2.56395149230957</t>
@@ -3941,13 +3941,13 @@
     <t xml:space="preserve">2.59155607223511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59967470169067</t>
+    <t xml:space="preserve">2.59967494010925</t>
   </si>
   <si>
     <t xml:space="preserve">2.56070399284363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59642744064331</t>
+    <t xml:space="preserve">2.59642720222473</t>
   </si>
   <si>
     <t xml:space="preserve">2.59805107116699</t>
@@ -3965,7 +3965,7 @@
     <t xml:space="preserve">2.81726145744324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84811329841614</t>
+    <t xml:space="preserve">2.84811353683472</t>
   </si>
   <si>
     <t xml:space="preserve">2.92767882347107</t>
@@ -3977,16 +3977,16 @@
     <t xml:space="preserve">2.88870811462402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83999443054199</t>
+    <t xml:space="preserve">2.83999466896057</t>
   </si>
   <si>
     <t xml:space="preserve">2.78965735435486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85136127471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7880334854126</t>
+    <t xml:space="preserve">2.85136103630066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78803324699402</t>
   </si>
   <si>
     <t xml:space="preserve">2.76530051231384</t>
@@ -3995,13 +3995,13 @@
     <t xml:space="preserve">2.64514064788818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75393390655518</t>
+    <t xml:space="preserve">2.75393414497375</t>
   </si>
   <si>
     <t xml:space="preserve">2.76692414283752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85460877418518</t>
+    <t xml:space="preserve">2.8546085357666</t>
   </si>
   <si>
     <t xml:space="preserve">2.7929048538208</t>
@@ -4019,7 +4019,7 @@
     <t xml:space="preserve">2.64189314842224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75555801391602</t>
+    <t xml:space="preserve">2.75555777549744</t>
   </si>
   <si>
     <t xml:space="preserve">2.83512306213379</t>
@@ -4031,7 +4031,7 @@
     <t xml:space="preserve">2.87734150886536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9163122177124</t>
+    <t xml:space="preserve">2.91631245613098</t>
   </si>
   <si>
     <t xml:space="preserve">2.95853066444397</t>
@@ -4064,10 +4064,10 @@
     <t xml:space="preserve">2.87409400939941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8497371673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89520311355591</t>
+    <t xml:space="preserve">2.84973740577698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89520335197449</t>
   </si>
   <si>
     <t xml:space="preserve">2.88708424568176</t>
@@ -4091,13 +4091,13 @@
     <t xml:space="preserve">3.11441373825073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15987944602966</t>
+    <t xml:space="preserve">3.15987968444824</t>
   </si>
   <si>
     <t xml:space="preserve">3.12740397453308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16637492179871</t>
+    <t xml:space="preserve">3.16637468338013</t>
   </si>
   <si>
     <t xml:space="preserve">3.14201784133911</t>
@@ -4106,22 +4106,22 @@
     <t xml:space="preserve">3.1209089756012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08031415939331</t>
+    <t xml:space="preserve">3.08031392097473</t>
   </si>
   <si>
     <t xml:space="preserve">3.07219505310059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08193778991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09168076515198</t>
+    <t xml:space="preserve">3.08193802833557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0916805267334</t>
   </si>
   <si>
     <t xml:space="preserve">3.09817576408386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06894755363464</t>
+    <t xml:space="preserve">3.06894779205322</t>
   </si>
   <si>
     <t xml:space="preserve">3.04134345054626</t>
@@ -4130,16 +4130,16 @@
     <t xml:space="preserve">3.11278986930847</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17449378967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.182612657547</t>
+    <t xml:space="preserve">3.17449355125427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18261241912842</t>
   </si>
   <si>
     <t xml:space="preserve">3.17611742019653</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14039421081543</t>
+    <t xml:space="preserve">3.14039444923401</t>
   </si>
   <si>
     <t xml:space="preserve">3.12415647506714</t>
@@ -4148,7 +4148,7 @@
     <t xml:space="preserve">3.17774128913879</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21508812904358</t>
+    <t xml:space="preserve">3.21508836746216</t>
   </si>
   <si>
     <t xml:space="preserve">3.26542520523071</t>
@@ -4163,7 +4163,7 @@
     <t xml:space="preserve">3.27029657363892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31251502037048</t>
+    <t xml:space="preserve">3.3125147819519</t>
   </si>
   <si>
     <t xml:space="preserve">3.3417432308197</t>
@@ -4184,7 +4184,7 @@
     <t xml:space="preserve">3.43917012214661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46190309524536</t>
+    <t xml:space="preserve">3.46190285682678</t>
   </si>
   <si>
     <t xml:space="preserve">3.48301196098328</t>
@@ -4193,7 +4193,7 @@
     <t xml:space="preserve">3.51386380195618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53822040557861</t>
+    <t xml:space="preserve">3.53822064399719</t>
   </si>
   <si>
     <t xml:space="preserve">3.52035927772522</t>
@@ -4205,7 +4205,7 @@
     <t xml:space="preserve">3.733074426651</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65675711631775</t>
+    <t xml:space="preserve">3.65675687789917</t>
   </si>
   <si>
     <t xml:space="preserve">3.66487550735474</t>
@@ -4214,7 +4214,7 @@
     <t xml:space="preserve">3.7022225856781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68436098098755</t>
+    <t xml:space="preserve">3.68436121940613</t>
   </si>
   <si>
     <t xml:space="preserve">3.65026164054871</t>
@@ -4229,7 +4229,7 @@
     <t xml:space="preserve">3.59505319595337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60804343223572</t>
+    <t xml:space="preserve">3.60804319381714</t>
   </si>
   <si>
     <t xml:space="preserve">3.64539003372192</t>
@@ -4244,40 +4244,40 @@
     <t xml:space="preserve">3.61616206169128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68598508834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69572782516479</t>
+    <t xml:space="preserve">3.68598484992981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69572758674622</t>
   </si>
   <si>
     <t xml:space="preserve">3.81101608276367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90032410621643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87921500205994</t>
+    <t xml:space="preserve">3.90032386779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87921476364136</t>
   </si>
   <si>
     <t xml:space="preserve">3.89870047569275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89382886886597</t>
+    <t xml:space="preserve">3.89382863044739</t>
   </si>
   <si>
     <t xml:space="preserve">3.97177052497864</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89220523834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91980934143066</t>
+    <t xml:space="preserve">3.89220547676086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91980957984924</t>
   </si>
   <si>
     <t xml:space="preserve">3.82400631904602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41806077957153</t>
+    <t xml:space="preserve">3.41806101799011</t>
   </si>
   <si>
     <t xml:space="preserve">3.41643738746643</t>
@@ -4289,10 +4289,10 @@
     <t xml:space="preserve">3.21021676063538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09492802619934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37259483337402</t>
+    <t xml:space="preserve">3.09492826461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3725950717926</t>
   </si>
   <si>
     <t xml:space="preserve">3.28491067886353</t>
@@ -4307,7 +4307,7 @@
     <t xml:space="preserve">3.09330439567566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09979963302612</t>
+    <t xml:space="preserve">3.09979939460754</t>
   </si>
   <si>
     <t xml:space="preserve">3.19560289382935</t>
@@ -4319,7 +4319,7 @@
     <t xml:space="preserve">3.1517608165741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27192044258118</t>
+    <t xml:space="preserve">3.27192068099976</t>
   </si>
   <si>
     <t xml:space="preserve">3.28815841674805</t>
@@ -4328,19 +4328,19 @@
     <t xml:space="preserve">3.31738638877869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36122822761536</t>
+    <t xml:space="preserve">3.36122846603394</t>
   </si>
   <si>
     <t xml:space="preserve">3.34823822975159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44891309738159</t>
+    <t xml:space="preserve">3.44891285896301</t>
   </si>
   <si>
     <t xml:space="preserve">3.4342987537384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47326922416687</t>
+    <t xml:space="preserve">3.47326946258545</t>
   </si>
   <si>
     <t xml:space="preserve">3.47002196311951</t>
@@ -4352,7 +4352,7 @@
     <t xml:space="preserve">3.34661459922791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32712888717651</t>
+    <t xml:space="preserve">3.32712912559509</t>
   </si>
   <si>
     <t xml:space="preserve">3.26704931259155</t>
@@ -4367,7 +4367,7 @@
     <t xml:space="preserve">3.50736880302429</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36934733390808</t>
+    <t xml:space="preserve">3.36934757232666</t>
   </si>
   <si>
     <t xml:space="preserve">3.38558530807495</t>
@@ -4388,19 +4388,19 @@
     <t xml:space="preserve">3.18703985214233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19400238990784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20096492767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18355870246887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13134098052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04605150222778</t>
+    <t xml:space="preserve">3.19400262832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20096468925476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18355894088745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13134074211121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0460512638092</t>
   </si>
   <si>
     <t xml:space="preserve">3.13308143615723</t>
@@ -4409,22 +4409,22 @@
     <t xml:space="preserve">3.22533321380615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19748377799988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21140837669373</t>
+    <t xml:space="preserve">3.1974835395813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2114086151123</t>
   </si>
   <si>
     <t xml:space="preserve">3.23055481910706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24273943901062</t>
+    <t xml:space="preserve">3.24273920059204</t>
   </si>
   <si>
     <t xml:space="preserve">3.23229551315308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22011160850525</t>
+    <t xml:space="preserve">3.22011137008667</t>
   </si>
   <si>
     <t xml:space="preserve">3.29321646690369</t>
@@ -4433,25 +4433,25 @@
     <t xml:space="preserve">3.25840449333191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28625440597534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30017900466919</t>
+    <t xml:space="preserve">3.28625416755676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30017924308777</t>
   </si>
   <si>
     <t xml:space="preserve">3.34891581535339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38546848297119</t>
+    <t xml:space="preserve">3.38546872138977</t>
   </si>
   <si>
     <t xml:space="preserve">3.41505861282349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37676572799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38024687767029</t>
+    <t xml:space="preserve">3.37676548957825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38024663925171</t>
   </si>
   <si>
     <t xml:space="preserve">3.32106614112854</t>
@@ -4472,28 +4472,28 @@
     <t xml:space="preserve">3.33673167228699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30888223648071</t>
+    <t xml:space="preserve">3.30888199806213</t>
   </si>
   <si>
     <t xml:space="preserve">3.34369397163391</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40809607505798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42028069496155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4342052936554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50905132293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53167915344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55430698394775</t>
+    <t xml:space="preserve">3.40809631347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42028045654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43420553207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50905108451843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5316789150238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55430674552917</t>
   </si>
   <si>
     <t xml:space="preserve">3.63785552978516</t>
@@ -4508,7 +4508,7 @@
     <t xml:space="preserve">3.70922040939331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78406596183777</t>
+    <t xml:space="preserve">3.78406620025635</t>
   </si>
   <si>
     <t xml:space="preserve">3.82409977912903</t>
@@ -4520,31 +4520,31 @@
     <t xml:space="preserve">3.75099468231201</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72140431404114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7318480014801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73881030082703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52471661567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65352082252502</t>
+    <t xml:space="preserve">3.72140455245972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73184823989868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73881053924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52471685409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6535210609436</t>
   </si>
   <si>
     <t xml:space="preserve">3.68833303451538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74229168891907</t>
+    <t xml:space="preserve">3.74229192733765</t>
   </si>
   <si>
     <t xml:space="preserve">3.73358845710754</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6848521232605</t>
+    <t xml:space="preserve">3.68485188484192</t>
   </si>
   <si>
     <t xml:space="preserve">3.64655876159668</t>
@@ -4553,37 +4553,37 @@
     <t xml:space="preserve">3.68137073516846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69007349014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71270132064819</t>
+    <t xml:space="preserve">3.69007325172424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71270108222961</t>
   </si>
   <si>
     <t xml:space="preserve">3.72314476966858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80321264266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83802461624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8171374797821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76666021347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7684006690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86065268516541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90416789054871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90590786933899</t>
+    <t xml:space="preserve">3.8032124042511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83802437782288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81713771820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76665997505188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76840043067932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86065220832825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90416741371155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90590834617615</t>
   </si>
   <si>
     <t xml:space="preserve">4.00338172912598</t>
@@ -4598,7 +4598,7 @@
     <t xml:space="preserve">4.07648706436157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17744159698486</t>
+    <t xml:space="preserve">4.17744207382202</t>
   </si>
   <si>
     <t xml:space="preserve">4.34976148605347</t>
@@ -4628,7 +4628,7 @@
     <t xml:space="preserve">4.31668996810913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22095632553101</t>
+    <t xml:space="preserve">4.22095680236816</t>
   </si>
   <si>
     <t xml:space="preserve">4.19310712814331</t>
@@ -4637,7 +4637,7 @@
     <t xml:space="preserve">4.28884029388428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3732590675354</t>
+    <t xml:space="preserve">4.37325954437256</t>
   </si>
   <si>
     <t xml:space="preserve">4.3393177986145</t>
@@ -4709,10 +4709,10 @@
     <t xml:space="preserve">5.0607967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21309900283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1956934928894</t>
+    <t xml:space="preserve">5.21309947967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19569301605225</t>
   </si>
   <si>
     <t xml:space="preserve">5.13042068481445</t>
@@ -4721,7 +4721,7 @@
     <t xml:space="preserve">5.14347505569458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08690595626831</t>
+    <t xml:space="preserve">5.08690547943115</t>
   </si>
   <si>
     <t xml:space="preserve">5.04774236679077</t>
@@ -4826,13 +4826,13 @@
     <t xml:space="preserve">5.33494138717651</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55251693725586</t>
+    <t xml:space="preserve">5.5525164604187</t>
   </si>
   <si>
     <t xml:space="preserve">5.65695238113403</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7048192024231</t>
+    <t xml:space="preserve">5.70481872558594</t>
   </si>
   <si>
     <t xml:space="preserve">5.7091703414917</t>
@@ -4850,7 +4850,7 @@
     <t xml:space="preserve">6.13561773300171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80055236816406</t>
+    <t xml:space="preserve">5.8005518913269</t>
   </si>
   <si>
     <t xml:space="preserve">5.78749752044678</t>
@@ -4859,7 +4859,7 @@
     <t xml:space="preserve">5.87017583847046</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83971548080444</t>
+    <t xml:space="preserve">5.8397159576416</t>
   </si>
   <si>
     <t xml:space="preserve">5.71352195739746</t>
@@ -4868,10 +4868,10 @@
     <t xml:space="preserve">5.72222471237183</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84406757354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93109750747681</t>
+    <t xml:space="preserve">5.84406709671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93109703063965</t>
   </si>
   <si>
     <t xml:space="preserve">5.97896337509155</t>
@@ -4880,7 +4880,7 @@
     <t xml:space="preserve">5.94415140151978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89628505706787</t>
+    <t xml:space="preserve">5.89628553390503</t>
   </si>
   <si>
     <t xml:space="preserve">5.98766660690308</t>
@@ -4898,7 +4898,7 @@
     <t xml:space="preserve">6.24005365371704</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17913293838501</t>
+    <t xml:space="preserve">6.17913246154785</t>
   </si>
   <si>
     <t xml:space="preserve">6.01812744140625</t>
@@ -4907,10 +4907,10 @@
     <t xml:space="preserve">6.16172647476196</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23570251464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23135042190552</t>
+    <t xml:space="preserve">6.23570203781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23135089874268</t>
   </si>
   <si>
     <t xml:space="preserve">6.07904815673828</t>
@@ -4919,7 +4919,7 @@
     <t xml:space="preserve">6.00507259368896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86582469940186</t>
+    <t xml:space="preserve">5.8658242225647</t>
   </si>
   <si>
     <t xml:space="preserve">5.69176435470581</t>
@@ -4931,34 +4931,34 @@
     <t xml:space="preserve">5.91369104385376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93979978561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18783569335938</t>
+    <t xml:space="preserve">5.93980026245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18783617019653</t>
   </si>
   <si>
     <t xml:space="preserve">6.065993309021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0398850440979</t>
+    <t xml:space="preserve">6.03988456726074</t>
   </si>
   <si>
     <t xml:space="preserve">6.09645414352417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22264814376831</t>
+    <t xml:space="preserve">6.22264766693115</t>
   </si>
   <si>
     <t xml:space="preserve">5.93544864654541</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06164264678955</t>
+    <t xml:space="preserve">6.06164216995239</t>
   </si>
   <si>
     <t xml:space="preserve">5.82666110992432</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85276985168457</t>
+    <t xml:space="preserve">5.85277032852173</t>
   </si>
   <si>
     <t xml:space="preserve">5.92674541473389</t>
@@ -4967,28 +4967,28 @@
     <t xml:space="preserve">6.11821174621582</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37930154800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53595638275146</t>
+    <t xml:space="preserve">6.37930202484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53595590591431</t>
   </si>
   <si>
     <t xml:space="preserve">6.53160429000854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47068357467651</t>
+    <t xml:space="preserve">6.47068309783936</t>
   </si>
   <si>
     <t xml:space="preserve">6.66650104522705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82315492630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8405613899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90148162841797</t>
+    <t xml:space="preserve">6.82315540313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84056091308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90148210525513</t>
   </si>
   <si>
     <t xml:space="preserve">6.80574893951416</t>
@@ -4997,7 +4997,7 @@
     <t xml:space="preserve">6.95369958877563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07119035720825</t>
+    <t xml:space="preserve">7.07119083404541</t>
   </si>
   <si>
     <t xml:space="preserve">6.96240282058716</t>
@@ -5009,10 +5009,10 @@
     <t xml:space="preserve">6.99286365509033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12775945663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12340927124023</t>
+    <t xml:space="preserve">7.12775993347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12340879440308</t>
   </si>
   <si>
     <t xml:space="preserve">7.20173501968384</t>
@@ -5961,6 +5961,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.8299999237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9350004196167</t>
   </si>
 </sst>
 </file>
@@ -71793,7 +71796,7 @@
     </row>
     <row r="2520">
       <c r="A2520" s="1" t="n">
-        <v>45987.6911689815</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B2520" t="n">
         <v>708368</v>
@@ -71814,6 +71817,32 @@
         <v>1982</v>
       </c>
       <c r="H2520" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" s="1" t="n">
+        <v>45988.69125</v>
+      </c>
+      <c r="B2521" t="n">
+        <v>436999</v>
+      </c>
+      <c r="C2521" t="n">
+        <v>14.9849996566772</v>
+      </c>
+      <c r="D2521" t="n">
+        <v>14.7399997711182</v>
+      </c>
+      <c r="E2521" t="n">
+        <v>14.8199996948242</v>
+      </c>
+      <c r="F2521" t="n">
+        <v>14.9350004196167</v>
+      </c>
+      <c r="G2521" t="s">
+        <v>1983</v>
+      </c>
+      <c r="H2521" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BPSO.MI.xlsx
+++ b/data/BPSO.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1984" uniqueCount="1984">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1985" uniqueCount="1985">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82907128334045</t>
+    <t xml:space="preserve">2.82907176017761</t>
   </si>
   <si>
     <t xml:space="preserve">BPSO.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80963754653931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74855804443359</t>
+    <t xml:space="preserve">2.80963706970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74855828285217</t>
   </si>
   <si>
     <t xml:space="preserve">2.7124662399292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63611721992493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60835385322571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69303202629089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69858455657959</t>
+    <t xml:space="preserve">2.63611698150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60835409164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69303226470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69858479499817</t>
   </si>
   <si>
     <t xml:space="preserve">2.61113023757935</t>
@@ -74,16 +74,16 @@
     <t xml:space="preserve">2.45565629005432</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2668662071228</t>
+    <t xml:space="preserve">2.26686644554138</t>
   </si>
   <si>
     <t xml:space="preserve">2.38069558143616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40568232536316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3654260635376</t>
+    <t xml:space="preserve">2.40568208694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36542558670044</t>
   </si>
   <si>
     <t xml:space="preserve">2.51951146125793</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">2.44455099105835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35570859909058</t>
+    <t xml:space="preserve">2.35570883750916</t>
   </si>
   <si>
     <t xml:space="preserve">2.43899869918823</t>
@@ -101,16 +101,16 @@
     <t xml:space="preserve">2.40429401397705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32100510597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22105765342712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23216247558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20995211601257</t>
+    <t xml:space="preserve">2.32100486755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22105741500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23216223716736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20995187759399</t>
   </si>
   <si>
     <t xml:space="preserve">2.04059624671936</t>
@@ -122,52 +122,52 @@
     <t xml:space="preserve">2.14331984519958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07668828964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18218803405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22522187232971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27797150611877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19329380989075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16553044319153</t>
+    <t xml:space="preserve">2.07668781280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18218851089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22522163391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27797174453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19329357147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16553020477295</t>
   </si>
   <si>
     <t xml:space="preserve">2.24604439735413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18635272979736</t>
+    <t xml:space="preserve">2.18635296821594</t>
   </si>
   <si>
     <t xml:space="preserve">2.17663598060608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21550440788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25992560386658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31822872161865</t>
+    <t xml:space="preserve">2.21550464630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.259925365448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31822848320007</t>
   </si>
   <si>
     <t xml:space="preserve">2.38763618469238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38208341598511</t>
+    <t xml:space="preserve">2.38208365440369</t>
   </si>
   <si>
     <t xml:space="preserve">2.37514281272888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24187922477722</t>
+    <t xml:space="preserve">2.2418794631958</t>
   </si>
   <si>
     <t xml:space="preserve">2.26270174980164</t>
@@ -176,67 +176,67 @@
     <t xml:space="preserve">2.25020861625671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31961703300476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43344521522522</t>
+    <t xml:space="preserve">2.31961679458618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4334454536438</t>
   </si>
   <si>
     <t xml:space="preserve">2.35848498344421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30156993865967</t>
+    <t xml:space="preserve">2.30157017707825</t>
   </si>
   <si>
     <t xml:space="preserve">2.34599161148071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35987305641174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39318895339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29324126243591</t>
+    <t xml:space="preserve">2.35987329483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3931884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29324150085449</t>
   </si>
   <si>
     <t xml:space="preserve">2.23771500587463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18774056434631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.139155626297</t>
+    <t xml:space="preserve">2.18774080276489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13915610313416</t>
   </si>
   <si>
     <t xml:space="preserve">2.14748454093933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12110996246338</t>
+    <t xml:space="preserve">2.1211097240448</t>
   </si>
   <si>
     <t xml:space="preserve">2.06974720954895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01283311843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01838541030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07113552093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11694502830505</t>
+    <t xml:space="preserve">2.01283264160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01838564872742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07113528251648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11694550514221</t>
   </si>
   <si>
     <t xml:space="preserve">2.12527418136597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22799777984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30295825004578</t>
+    <t xml:space="preserve">2.22799801826477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30295848846436</t>
   </si>
   <si>
     <t xml:space="preserve">2.23910331726074</t>
@@ -245,163 +245,163 @@
     <t xml:space="preserve">2.29046487808228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3321099281311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32655763626099</t>
+    <t xml:space="preserve">2.33211016654968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32655739784241</t>
   </si>
   <si>
     <t xml:space="preserve">2.27935934066772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32378101348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30851125717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26131391525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.234938621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15720152854919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11139249801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08224081993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09889912605286</t>
+    <t xml:space="preserve">2.32378125190735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30851101875305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26131343841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23493885993958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15720176696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11139225959778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08224058151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09889888763428</t>
   </si>
   <si>
     <t xml:space="preserve">2.08918213844299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10584020614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04892492294312</t>
+    <t xml:space="preserve">2.10583996772766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04892468452454</t>
   </si>
   <si>
     <t xml:space="preserve">2.03781986236572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06558275222778</t>
+    <t xml:space="preserve">2.06558299064636</t>
   </si>
   <si>
     <t xml:space="preserve">2.03226709365845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07252359390259</t>
+    <t xml:space="preserve">2.07252407073975</t>
   </si>
   <si>
     <t xml:space="preserve">2.05725383758545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05156683921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12691855430603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19942736625671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15393209457397</t>
+    <t xml:space="preserve">2.05156755447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12691831588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19942760467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15393233299255</t>
   </si>
   <si>
     <t xml:space="preserve">2.17525792121887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15535402297974</t>
+    <t xml:space="preserve">2.15535378456116</t>
   </si>
   <si>
     <t xml:space="preserve">2.09279704093933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07147145271301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99896240234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95773243904114</t>
+    <t xml:space="preserve">2.07147121429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99896228313446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95773231983185</t>
   </si>
   <si>
     <t xml:space="preserve">1.87669312953949</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98900997638702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93640649318695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94351518154144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84114956855774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78143703937531</t>
+    <t xml:space="preserve">1.98901009559631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93640625476837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94351506233215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84114992618561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78143692016602</t>
   </si>
   <si>
     <t xml:space="preserve">1.751580119133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72598874568939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64210605621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69613242149353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77006256580353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81129324436188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78001427650452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89375340938568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63499772548676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56533265113831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66911971569061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65632355213165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6392627954483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63641929626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57670652866364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51130640506744</t>
+    <t xml:space="preserve">1.72598886489868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64210617542267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69613265991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77006244659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81129336357117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78001439571381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89375352859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63499748706818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56533253192902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66911959648132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65632343292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63926291465759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63641941547394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57670676708221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51130652427673</t>
   </si>
   <si>
     <t xml:space="preserve">1.52552390098572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53121078014374</t>
+    <t xml:space="preserve">1.53121066093445</t>
   </si>
   <si>
     <t xml:space="preserve">1.63784086704254</t>
@@ -413,25 +413,25 @@
     <t xml:space="preserve">1.69471085071564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67054164409637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74304962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70892822742462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72172379493713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77574944496155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76721906661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72741067409515</t>
+    <t xml:space="preserve">1.67054152488708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74304986000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70892798900604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72172367572784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77574968338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.767218708992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72741091251373</t>
   </si>
   <si>
     <t xml:space="preserve">1.69755446910858</t>
@@ -440,16 +440,16 @@
     <t xml:space="preserve">1.72456741333008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71888029575348</t>
+    <t xml:space="preserve">1.71888017654419</t>
   </si>
   <si>
     <t xml:space="preserve">1.66343295574188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55395901203156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57528507709503</t>
+    <t xml:space="preserve">1.55395913124084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57528483867645</t>
   </si>
   <si>
     <t xml:space="preserve">1.52125859260559</t>
@@ -458,214 +458,214 @@
     <t xml:space="preserve">1.63357579708099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6591671705246</t>
+    <t xml:space="preserve">1.65916705131531</t>
   </si>
   <si>
     <t xml:space="preserve">1.64779317378998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68760216236115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71461486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70608484745026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70039796829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74447131156921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70750641822815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72030162811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73167562484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78285884857178</t>
+    <t xml:space="preserve">1.68760228157043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71461498737335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70608472824097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70039772987366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7444714307785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70750653743744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72030198574066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73167586326599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78285896778107</t>
   </si>
   <si>
     <t xml:space="preserve">1.77859282493591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77148425579071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76437544822693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75584530830383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76295387744904</t>
+    <t xml:space="preserve">1.77148449420929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76437556743622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75584518909454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76295411586761</t>
   </si>
   <si>
     <t xml:space="preserve">1.74162769317627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76864075660706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74873661994934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73451924324036</t>
+    <t xml:space="preserve">1.76864063739777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74873650074005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73451912403107</t>
   </si>
   <si>
     <t xml:space="preserve">1.78428041934967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85252356529236</t>
+    <t xml:space="preserve">1.85252380371094</t>
   </si>
   <si>
     <t xml:space="preserve">1.84967982769012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81271493434906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8354629278183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84825825691223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85963201522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9477801322937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9762145280838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09848403930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10843634605408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07573628425598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08568835258484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0885317325592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09706234931946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16104102134705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18236660957336</t>
+    <t xml:space="preserve">1.81271505355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83546268939972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84825801849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85963213443756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94778025150299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97621476650238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09848380088806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1084361076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07573652267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08568859100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08853197097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09706258773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16104125976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18236637115479</t>
   </si>
   <si>
     <t xml:space="preserve">2.11412334442139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00038385391235</t>
+    <t xml:space="preserve">2.00038361549377</t>
   </si>
   <si>
     <t xml:space="preserve">2.03877139091492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00891423225403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05298852920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06294059753418</t>
+    <t xml:space="preserve">2.00891447067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0529887676239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06294083595276</t>
   </si>
   <si>
     <t xml:space="preserve">2.11554479598999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12549686431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16246247291565</t>
+    <t xml:space="preserve">2.12549662590027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16246223449707</t>
   </si>
   <si>
     <t xml:space="preserve">2.15961909294128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13260555267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08142328262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03592801094055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07715797424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09990525245667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08995366096497</t>
+    <t xml:space="preserve">2.13260579109192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08142304420471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03592753410339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07715845108032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09990572929382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08995389938354</t>
   </si>
   <si>
     <t xml:space="preserve">2.01033592224121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12407517433167</t>
+    <t xml:space="preserve">2.12407493591309</t>
   </si>
   <si>
     <t xml:space="preserve">2.10417079925537</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0728931427002</t>
+    <t xml:space="preserve">2.07289266586304</t>
   </si>
   <si>
     <t xml:space="preserve">2.16814970970154</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27478003501892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37430167198181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26340627670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23354887962341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27193665504456</t>
+    <t xml:space="preserve">2.27477979660034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37430143356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26340579986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23354911804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27193641662598</t>
   </si>
   <si>
     <t xml:space="preserve">2.23212718963623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1781017780304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16957092285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23639249801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22217488288879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21791005134583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2051146030426</t>
+    <t xml:space="preserve">2.17810153961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16957116127014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23639225959778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22217512130737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21790981292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20511436462402</t>
   </si>
   <si>
     <t xml:space="preserve">2.22359704971313</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">2.26482772827148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31032299995422</t>
+    <t xml:space="preserve">2.3103232383728</t>
   </si>
   <si>
     <t xml:space="preserve">2.31743144989014</t>
@@ -692,19 +692,19 @@
     <t xml:space="preserve">2.297527551651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29610562324524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36008381843567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35297536849976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34017944335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40273594856262</t>
+    <t xml:space="preserve">2.29610586166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36008358001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3529748916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34017968177795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4027361869812</t>
   </si>
   <si>
     <t xml:space="preserve">2.41695356369019</t>
@@ -716,25 +716,25 @@
     <t xml:space="preserve">2.41126656532288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.415531873703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4240620136261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44396662712097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35439658164978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33733630180359</t>
+    <t xml:space="preserve">2.41553163528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42406225204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44396615028381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3543963432312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33733582496643</t>
   </si>
   <si>
     <t xml:space="preserve">2.33022737503052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3643491268158</t>
+    <t xml:space="preserve">2.36434888839722</t>
   </si>
   <si>
     <t xml:space="preserve">2.32738375663757</t>
@@ -743,22 +743,22 @@
     <t xml:space="preserve">2.28188824653625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30037140846252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32311844825745</t>
+    <t xml:space="preserve">2.30037117004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32311868667603</t>
   </si>
   <si>
     <t xml:space="preserve">2.33449220657349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30890154838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29894924163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25629734992981</t>
+    <t xml:space="preserve">2.30890130996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2989490032196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25629711151123</t>
   </si>
   <si>
     <t xml:space="preserve">2.12834048271179</t>
@@ -767,13 +767,13 @@
     <t xml:space="preserve">2.13402724266052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28473234176636</t>
+    <t xml:space="preserve">2.28473210334778</t>
   </si>
   <si>
     <t xml:space="preserve">2.22928404808044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27335810661316</t>
+    <t xml:space="preserve">2.27335786819458</t>
   </si>
   <si>
     <t xml:space="preserve">2.27904510498047</t>
@@ -788,31 +788,31 @@
     <t xml:space="preserve">2.37856698036194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32880520820618</t>
+    <t xml:space="preserve">2.32880568504333</t>
   </si>
   <si>
     <t xml:space="preserve">2.36719226837158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34870982170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29468441009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30321431159973</t>
+    <t xml:space="preserve">2.34871006011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29468417167664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30321455001831</t>
   </si>
   <si>
     <t xml:space="preserve">2.28757548332214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32027554512024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2833104133606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29041838645935</t>
+    <t xml:space="preserve">2.32027530670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28331017494202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29041886329651</t>
   </si>
   <si>
     <t xml:space="preserve">2.29326248168945</t>
@@ -824,61 +824,61 @@
     <t xml:space="preserve">2.35581827163696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31174445152283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33164930343628</t>
+    <t xml:space="preserve">2.31174468994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33164882659912</t>
   </si>
   <si>
     <t xml:space="preserve">2.46671414375305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43117117881775</t>
+    <t xml:space="preserve">2.43117094039917</t>
   </si>
   <si>
     <t xml:space="preserve">2.42974901199341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49799275398254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46387076377869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48661828041077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51647520065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51789689064026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56907916069031</t>
+    <t xml:space="preserve">2.49799299240112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46387052536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48661851882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5164749622345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51789736747742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56907939910889</t>
   </si>
   <si>
     <t xml:space="preserve">2.533536195755</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48803997039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50510120391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5079448223114</t>
+    <t xml:space="preserve">2.48803973197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50510144233704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50794506072998</t>
   </si>
   <si>
     <t xml:space="preserve">2.50936627388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50652313232422</t>
+    <t xml:space="preserve">2.50652289390564</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486178398132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5722119808197</t>
+    <t xml:space="preserve">2.57221245765686</t>
   </si>
   <si>
     <t xml:space="preserve">2.63293862342834</t>
@@ -887,31 +887,31 @@
     <t xml:space="preserve">2.65607333183289</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70667886734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56642889976501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52594375610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5288360118866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47389245033264</t>
+    <t xml:space="preserve">2.70667862892151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56642913818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52594327926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52883553504944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47389268875122</t>
   </si>
   <si>
     <t xml:space="preserve">2.52160620689392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5143768787384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4710009098053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48979711532593</t>
+    <t xml:space="preserve">2.51437664031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47100067138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48979735374451</t>
   </si>
   <si>
     <t xml:space="preserve">2.47533869743347</t>
@@ -920,43 +920,43 @@
     <t xml:space="preserve">2.51726841926575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45654225349426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47967576980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46088004112244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48112201690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45798802375793</t>
+    <t xml:space="preserve">2.4565417766571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47967600822449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46087956428528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48112177848816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45798826217651</t>
   </si>
   <si>
     <t xml:space="preserve">2.48256778717041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48835134506226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48690533638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50859355926514</t>
+    <t xml:space="preserve">2.48835110664368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48690509796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50859332084656</t>
   </si>
   <si>
     <t xml:space="preserve">2.53751134872437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6025755405426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55919909477234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49558091163635</t>
+    <t xml:space="preserve">2.60257530212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55919933319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49558067321777</t>
   </si>
   <si>
     <t xml:space="preserve">2.59245419502258</t>
@@ -974,31 +974,31 @@
     <t xml:space="preserve">2.6228175163269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61703443527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72692060470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73704195022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72258281707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71246218681335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71390771865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7081241607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68932819366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68643641471863</t>
+    <t xml:space="preserve">2.61703419685364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72692036628723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73704171180725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72258305549622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71246194839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71390795707703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70812439918518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68932795524597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68643665313721</t>
   </si>
   <si>
     <t xml:space="preserve">2.6878821849823</t>
@@ -1007,10 +1007,10 @@
     <t xml:space="preserve">2.7110161781311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65028882026672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67920732498169</t>
+    <t xml:space="preserve">2.6502890586853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67920708656311</t>
   </si>
   <si>
     <t xml:space="preserve">2.67197775840759</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">2.65318083763123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65173506736755</t>
+    <t xml:space="preserve">2.6517345905304</t>
   </si>
   <si>
     <t xml:space="preserve">2.66763997077942</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">2.64595150947571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59823775291443</t>
+    <t xml:space="preserve">2.59823751449585</t>
   </si>
   <si>
     <t xml:space="preserve">2.62426352500916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60402131080627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54474067687988</t>
+    <t xml:space="preserve">2.60402154922485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54474091529846</t>
   </si>
   <si>
     <t xml:space="preserve">2.57654976844788</t>
@@ -1052,10 +1052,10 @@
     <t xml:space="preserve">2.52449774742126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48545932769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50281000137329</t>
+    <t xml:space="preserve">2.48545956611633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50280976295471</t>
   </si>
   <si>
     <t xml:space="preserve">2.52016019821167</t>
@@ -1070,7 +1070,7 @@
     <t xml:space="preserve">2.53317284584045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55196976661682</t>
+    <t xml:space="preserve">2.5519700050354</t>
   </si>
   <si>
     <t xml:space="preserve">2.50714755058289</t>
@@ -1079,16 +1079,16 @@
     <t xml:space="preserve">2.55052447319031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54618644714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53606557846069</t>
+    <t xml:space="preserve">2.54618668556213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53606581687927</t>
   </si>
   <si>
     <t xml:space="preserve">2.57944130897522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64161348342896</t>
+    <t xml:space="preserve">2.64161396026611</t>
   </si>
   <si>
     <t xml:space="preserve">2.63004684448242</t>
@@ -1103,13 +1103,13 @@
     <t xml:space="preserve">2.51582264900208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49268865585327</t>
+    <t xml:space="preserve">2.49268889427185</t>
   </si>
   <si>
     <t xml:space="preserve">2.53461909294128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49124312400818</t>
+    <t xml:space="preserve">2.4912428855896</t>
   </si>
   <si>
     <t xml:space="preserve">2.47244668006897</t>
@@ -1118,19 +1118,19 @@
     <t xml:space="preserve">2.50425577163696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48401379585266</t>
+    <t xml:space="preserve">2.48401355743408</t>
   </si>
   <si>
     <t xml:space="preserve">2.49413442611694</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4984724521637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47823023796082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51293063163757</t>
+    <t xml:space="preserve">2.49847221374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47822999954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51293087005615</t>
   </si>
   <si>
     <t xml:space="preserve">2.44931268692017</t>
@@ -1139,10 +1139,10 @@
     <t xml:space="preserve">2.407381772995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45509600639343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41027355194092</t>
+    <t xml:space="preserve">2.45509624481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4102737903595</t>
   </si>
   <si>
     <t xml:space="preserve">2.29605031013489</t>
@@ -1154,16 +1154,16 @@
     <t xml:space="preserve">2.28159070014954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18471789360046</t>
+    <t xml:space="preserve">2.18471765518188</t>
   </si>
   <si>
     <t xml:space="preserve">2.19773054122925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22086429595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26279425621033</t>
+    <t xml:space="preserve">2.22086453437805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26279473304749</t>
   </si>
   <si>
     <t xml:space="preserve">2.28448271751404</t>
@@ -1172,7 +1172,7 @@
     <t xml:space="preserve">2.28592824935913</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32496738433838</t>
+    <t xml:space="preserve">2.32496762275696</t>
   </si>
   <si>
     <t xml:space="preserve">2.34810137748718</t>
@@ -1181,10 +1181,10 @@
     <t xml:space="preserve">2.3784646987915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41461229324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3423182964325</t>
+    <t xml:space="preserve">2.41461205482483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34231781959534</t>
   </si>
   <si>
     <t xml:space="preserve">2.35677671432495</t>
@@ -1193,7 +1193,7 @@
     <t xml:space="preserve">2.35966849327087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34087181091309</t>
+    <t xml:space="preserve">2.34087228775024</t>
   </si>
   <si>
     <t xml:space="preserve">2.37701869010925</t>
@@ -1202,10 +1202,10 @@
     <t xml:space="preserve">2.3929238319397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40015292167664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40593647956848</t>
+    <t xml:space="preserve">2.40015268325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4059362411499</t>
   </si>
   <si>
     <t xml:space="preserve">2.33653426170349</t>
@@ -1214,19 +1214,19 @@
     <t xml:space="preserve">2.29315757751465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20496010780334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23966073989868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23821496963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23387718200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18327188491821</t>
+    <t xml:space="preserve">2.20495986938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2396605014801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23821473121643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23387694358826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18327212333679</t>
   </si>
   <si>
     <t xml:space="preserve">2.21797251701355</t>
@@ -1235,46 +1235,46 @@
     <t xml:space="preserve">2.24544405937195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20062232017517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22664761543274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28303670883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31340050697327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31050896644592</t>
+    <t xml:space="preserve">2.20062208175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22664785385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28303694725037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31340074539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31050872802734</t>
   </si>
   <si>
     <t xml:space="preserve">2.38858556747437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38714003562927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34665584564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34520959854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36545205116272</t>
+    <t xml:space="preserve">2.38713979721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34665536880493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34520983695984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36545181274414</t>
   </si>
   <si>
     <t xml:space="preserve">2.39436912536621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4030442237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40448999404907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3278591632843</t>
+    <t xml:space="preserve">2.40304446220398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40449023246765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32785940170288</t>
   </si>
   <si>
     <t xml:space="preserve">2.34954738616943</t>
@@ -1283,25 +1283,25 @@
     <t xml:space="preserve">2.33364319801331</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31195473670959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22953963279724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31484651565552</t>
+    <t xml:space="preserve">2.31195449829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22953987121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31484627723694</t>
   </si>
   <si>
     <t xml:space="preserve">2.30327963829041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32062959671021</t>
+    <t xml:space="preserve">2.32063007354736</t>
   </si>
   <si>
     <t xml:space="preserve">2.30761694908142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37268137931824</t>
+    <t xml:space="preserve">2.37268114089966</t>
   </si>
   <si>
     <t xml:space="preserve">2.42907071113586</t>
@@ -1316,40 +1316,40 @@
     <t xml:space="preserve">2.35388493537903</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27725315093994</t>
+    <t xml:space="preserve">2.27725291252136</t>
   </si>
   <si>
     <t xml:space="preserve">2.32930517196655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30617165565491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30038809776306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37412691116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33075070381165</t>
+    <t xml:space="preserve">2.30617141723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3003876209259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37412667274475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33075094223022</t>
   </si>
   <si>
     <t xml:space="preserve">2.32641363143921</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39726066589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39870643615723</t>
+    <t xml:space="preserve">2.39726090431213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39870691299438</t>
   </si>
   <si>
     <t xml:space="preserve">2.38569402694702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60112977027893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71969151496887</t>
+    <t xml:space="preserve">2.60112953186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71969127655029</t>
   </si>
   <si>
     <t xml:space="preserve">2.70957016944885</t>
@@ -1358,25 +1358,25 @@
     <t xml:space="preserve">2.75439214706421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77752685546875</t>
+    <t xml:space="preserve">2.77752661705017</t>
   </si>
   <si>
     <t xml:space="preserve">2.84837436676025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84114480018616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83391571044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86861634254456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90042614936829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82957816123962</t>
+    <t xml:space="preserve">2.84114503860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83391547203064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8686158657074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90042591094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82957792282104</t>
   </si>
   <si>
     <t xml:space="preserve">2.73125839233398</t>
@@ -1385,16 +1385,16 @@
     <t xml:space="preserve">2.78620171546936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7558376789093</t>
+    <t xml:space="preserve">2.75583815574646</t>
   </si>
   <si>
     <t xml:space="preserve">2.82524061203003</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80644416809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83680701255798</t>
+    <t xml:space="preserve">2.80644392967224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83680748939514</t>
   </si>
   <si>
     <t xml:space="preserve">2.74716281890869</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">2.7384877204895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6343846321106</t>
+    <t xml:space="preserve">2.63438487052917</t>
   </si>
   <si>
     <t xml:space="preserve">2.66091990470886</t>
@@ -1415,13 +1415,13 @@
     <t xml:space="preserve">2.71251702308655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7036714553833</t>
+    <t xml:space="preserve">2.70367121696472</t>
   </si>
   <si>
     <t xml:space="preserve">2.63143634796143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52824258804321</t>
+    <t xml:space="preserve">2.52824211120605</t>
   </si>
   <si>
     <t xml:space="preserve">2.48254251480103</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">2.6107976436615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57689046859741</t>
+    <t xml:space="preserve">2.57689070701599</t>
   </si>
   <si>
     <t xml:space="preserve">2.51939725875854</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">2.618168592453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59015893936157</t>
+    <t xml:space="preserve">2.59015917778015</t>
   </si>
   <si>
     <t xml:space="preserve">2.54888081550598</t>
@@ -1457,7 +1457,7 @@
     <t xml:space="preserve">2.5606746673584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55625176429749</t>
+    <t xml:space="preserve">2.55625200271606</t>
   </si>
   <si>
     <t xml:space="preserve">2.54593276977539</t>
@@ -1469,28 +1469,28 @@
     <t xml:space="preserve">2.51350069046021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51055216789246</t>
+    <t xml:space="preserve">2.51055240631104</t>
   </si>
   <si>
     <t xml:space="preserve">2.53708744049072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54150986671448</t>
+    <t xml:space="preserve">2.54151010513306</t>
   </si>
   <si>
     <t xml:space="preserve">2.65354871749878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65944576263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70514559745789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69040322303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65797185897827</t>
+    <t xml:space="preserve">2.6594455242157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70514583587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6904034614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65797162055969</t>
   </si>
   <si>
     <t xml:space="preserve">2.61964249610901</t>
@@ -1499,16 +1499,16 @@
     <t xml:space="preserve">2.63291025161743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6491265296936</t>
+    <t xml:space="preserve">2.64912629127502</t>
   </si>
   <si>
     <t xml:space="preserve">2.64322948455811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6653425693512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64470386505127</t>
+    <t xml:space="preserve">2.66534280776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64470410346985</t>
   </si>
   <si>
     <t xml:space="preserve">2.63880705833435</t>
@@ -1517,61 +1517,61 @@
     <t xml:space="preserve">2.66386818885803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71399116516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73168182373047</t>
+    <t xml:space="preserve">2.71399140357971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73168158531189</t>
   </si>
   <si>
     <t xml:space="preserve">2.71693968772888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73315572738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78180360794067</t>
+    <t xml:space="preserve">2.7331554889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78180384635925</t>
   </si>
   <si>
     <t xml:space="preserve">2.70661950111389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69187808036804</t>
+    <t xml:space="preserve">2.69187784194946</t>
   </si>
   <si>
     <t xml:space="preserve">2.68892955780029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67713570594788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64617800712585</t>
+    <t xml:space="preserve">2.67713594436646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64617776870728</t>
   </si>
   <si>
     <t xml:space="preserve">2.6417555809021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57541632652283</t>
+    <t xml:space="preserve">2.57541584968567</t>
   </si>
   <si>
     <t xml:space="preserve">2.61374592781067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60932350158691</t>
+    <t xml:space="preserve">2.60932326316833</t>
   </si>
   <si>
     <t xml:space="preserve">2.58868455886841</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58131289482117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53561353683472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48843955993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47222352027893</t>
+    <t xml:space="preserve">2.58131337165833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53561305999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48843908309937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47222328186035</t>
   </si>
   <si>
     <t xml:space="preserve">2.50170707702637</t>
@@ -1583,10 +1583,10 @@
     <t xml:space="preserve">2.67123913764954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67418742179871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65502333641052</t>
+    <t xml:space="preserve">2.67418766021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65502309799194</t>
   </si>
   <si>
     <t xml:space="preserve">2.68450689315796</t>
@@ -1598,19 +1598,19 @@
     <t xml:space="preserve">2.62406539916992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62996172904968</t>
+    <t xml:space="preserve">2.62996196746826</t>
   </si>
   <si>
     <t xml:space="preserve">2.63733291625977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62111663818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42210030555725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4191517829895</t>
+    <t xml:space="preserve">2.62111687660217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42210054397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41915202140808</t>
   </si>
   <si>
     <t xml:space="preserve">2.36608123779297</t>
@@ -1619,13 +1619,13 @@
     <t xml:space="preserve">2.38966846466064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41325521469116</t>
+    <t xml:space="preserve">2.41325545310974</t>
   </si>
   <si>
     <t xml:space="preserve">2.33659672737122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24667191505432</t>
+    <t xml:space="preserve">2.24667167663574</t>
   </si>
   <si>
     <t xml:space="preserve">2.23045563697815</t>
@@ -1634,31 +1634,31 @@
     <t xml:space="preserve">2.22898149490356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16706490516663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18033242225647</t>
+    <t xml:space="preserve">2.16706466674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18033266067505</t>
   </si>
   <si>
     <t xml:space="preserve">2.15674567222595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20244550704956</t>
+    <t xml:space="preserve">2.20244526863098</t>
   </si>
   <si>
     <t xml:space="preserve">2.19360017776489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13905549049377</t>
+    <t xml:space="preserve">2.1390552520752</t>
   </si>
   <si>
     <t xml:space="preserve">2.11399412155151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08745837211609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0417582988739</t>
+    <t xml:space="preserve">2.08745813369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04175853729248</t>
   </si>
   <si>
     <t xml:space="preserve">2.00932621955872</t>
@@ -1670,34 +1670,34 @@
     <t xml:space="preserve">2.105149269104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05797410011292</t>
+    <t xml:space="preserve">2.05797433853149</t>
   </si>
   <si>
     <t xml:space="preserve">2.05502605438232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09335589408875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13610696792603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11694264411926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09925246238708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10220098495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10072636604309</t>
+    <t xml:space="preserve">2.09335541725159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13610672950745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11694240570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09925222396851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10220074653625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10072612762451</t>
   </si>
   <si>
     <t xml:space="preserve">2.09040641784668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04912924766541</t>
+    <t xml:space="preserve">2.04912900924683</t>
   </si>
   <si>
     <t xml:space="preserve">2.06829380989075</t>
@@ -1706,43 +1706,43 @@
     <t xml:space="preserve">2.05060315132141</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0476553440094</t>
+    <t xml:space="preserve">2.04765510559082</t>
   </si>
   <si>
     <t xml:space="preserve">2.02701640129089</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01964592933655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97394585609436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97984254360199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96215164661407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98426485061646</t>
+    <t xml:space="preserve">2.01964569091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97394573688507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9798424243927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96215176582336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98426508903503</t>
   </si>
   <si>
     <t xml:space="preserve">2.08008742332458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06387114524841</t>
+    <t xml:space="preserve">2.06387138366699</t>
   </si>
   <si>
     <t xml:space="preserve">2.07861304283142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04618096351624</t>
+    <t xml:space="preserve">2.04618120193481</t>
   </si>
   <si>
     <t xml:space="preserve">2.08598399162292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05650043487549</t>
+    <t xml:space="preserve">2.05650019645691</t>
   </si>
   <si>
     <t xml:space="preserve">1.95625483989716</t>
@@ -1751,37 +1751,37 @@
     <t xml:space="preserve">1.98279082775116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9444614648819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93709027767181</t>
+    <t xml:space="preserve">1.94446134567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9370903968811</t>
   </si>
   <si>
     <t xml:space="preserve">1.96657407283783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96804869174957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89286494255066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98131704330444</t>
+    <t xml:space="preserve">1.96804857254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89286482334137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98131692409515</t>
   </si>
   <si>
     <t xml:space="preserve">1.91497778892517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87517476081848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87370038032532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94003891944885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92677128314972</t>
+    <t xml:space="preserve">1.8751745223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8737006187439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94003903865814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92677104473114</t>
   </si>
   <si>
     <t xml:space="preserve">1.99311017990112</t>
@@ -1790,7 +1790,7 @@
     <t xml:space="preserve">2.0034294128418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.994584441185</t>
+    <t xml:space="preserve">1.99458456039429</t>
   </si>
   <si>
     <t xml:space="preserve">1.99163639545441</t>
@@ -1799,13 +1799,13 @@
     <t xml:space="preserve">1.94888389110565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8884425163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87222623825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9194004535675</t>
+    <t xml:space="preserve">1.88844227790833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87222635746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91940033435822</t>
   </si>
   <si>
     <t xml:space="preserve">1.89433920383453</t>
@@ -1814,37 +1814,37 @@
     <t xml:space="preserve">1.86485540866852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85306203365326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83831942081451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88549423217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85158753395081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82505166530609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78230023384094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71596133708954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69532251358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71006453037262</t>
+    <t xml:space="preserve">1.85306191444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83831918239594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88549411296844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85158729553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82505178451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78230035305023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71596121788025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69532263278961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71006464958191</t>
   </si>
   <si>
     <t xml:space="preserve">1.73217809200287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78377449512482</t>
+    <t xml:space="preserve">1.78377461433411</t>
   </si>
   <si>
     <t xml:space="preserve">1.76313579082489</t>
@@ -1853,13 +1853,13 @@
     <t xml:space="preserve">1.76166164875031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78672301769257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80588710308075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83389663696289</t>
+    <t xml:space="preserve">1.78672313690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80588698387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83389687538147</t>
   </si>
   <si>
     <t xml:space="preserve">1.87664890289307</t>
@@ -1868,7 +1868,7 @@
     <t xml:space="preserve">1.86927807331085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84569025039673</t>
+    <t xml:space="preserve">1.84569013118744</t>
   </si>
   <si>
     <t xml:space="preserve">1.8397935628891</t>
@@ -1877,22 +1877,22 @@
     <t xml:space="preserve">1.83242249488831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84274184703827</t>
+    <t xml:space="preserve">1.84274172782898</t>
   </si>
   <si>
     <t xml:space="preserve">1.83684515953064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89728736877441</t>
+    <t xml:space="preserve">1.89728760719299</t>
   </si>
   <si>
     <t xml:space="preserve">1.88991641998291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8825455904007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91055512428284</t>
+    <t xml:space="preserve">1.88254547119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91055524349213</t>
   </si>
   <si>
     <t xml:space="preserve">1.87075221538544</t>
@@ -1901,25 +1901,25 @@
     <t xml:space="preserve">1.80293893814087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80441319942474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79114556312561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75576508045197</t>
+    <t xml:space="preserve">1.80441308021545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79114544391632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75576496124268</t>
   </si>
   <si>
     <t xml:space="preserve">1.81325840950012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81178379058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83537101745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79556787014008</t>
+    <t xml:space="preserve">1.81178367137909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83537089824677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79556775093079</t>
   </si>
   <si>
     <t xml:space="preserve">1.77492928504944</t>
@@ -1928,67 +1928,67 @@
     <t xml:space="preserve">1.8088356256485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79851627349854</t>
+    <t xml:space="preserve">1.79851615428925</t>
   </si>
   <si>
     <t xml:space="preserve">1.79704225063324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8073616027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78082633018494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75429081916809</t>
+    <t xml:space="preserve">1.80736148357391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78082621097565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7542906999588</t>
   </si>
   <si>
     <t xml:space="preserve">1.71301293373108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70711612701416</t>
+    <t xml:space="preserve">1.70711624622345</t>
   </si>
   <si>
     <t xml:space="preserve">1.74544548988342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76461005210876</t>
+    <t xml:space="preserve">1.76460981369019</t>
   </si>
   <si>
     <t xml:space="preserve">1.77198076248169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77787756919861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78819704055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74839401245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6658388376236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67910659313202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61129403114319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57886123657227</t>
+    <t xml:space="preserve">1.77787733078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78819692134857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74839413166046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66583895683289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67910647392273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61129415035248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57886135578156</t>
   </si>
   <si>
     <t xml:space="preserve">1.53610992431641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55822277069092</t>
+    <t xml:space="preserve">1.55822265148163</t>
   </si>
   <si>
     <t xml:space="preserve">1.54200661182404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53445518016815</t>
+    <t xml:space="preserve">1.53445506095886</t>
   </si>
   <si>
     <t xml:space="preserve">1.53596556186676</t>
@@ -2018,19 +2018,19 @@
     <t xml:space="preserve">1.56768143177032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56919157505035</t>
+    <t xml:space="preserve">1.56919169425964</t>
   </si>
   <si>
     <t xml:space="preserve">1.58882534503937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51029002666473</t>
+    <t xml:space="preserve">1.51028990745544</t>
   </si>
   <si>
     <t xml:space="preserve">1.51935243606567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52690386772156</t>
+    <t xml:space="preserve">1.52690374851227</t>
   </si>
   <si>
     <t xml:space="preserve">1.4717777967453</t>
@@ -2042,7 +2042,7 @@
     <t xml:space="preserve">1.471022605896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45138907432556</t>
+    <t xml:space="preserve">1.45138895511627</t>
   </si>
   <si>
     <t xml:space="preserve">1.46875727176666</t>
@@ -2063,16 +2063,16 @@
     <t xml:space="preserve">1.46800208091736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.489901304245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48234987258911</t>
+    <t xml:space="preserve">1.48990118503571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48234975337982</t>
   </si>
   <si>
     <t xml:space="preserve">1.4808394908905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53294479846954</t>
+    <t xml:space="preserve">1.53294491767883</t>
   </si>
   <si>
     <t xml:space="preserve">1.57523286342621</t>
@@ -2081,13 +2081,13 @@
     <t xml:space="preserve">1.56315052509308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52539372444153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50424873828888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47328805923462</t>
+    <t xml:space="preserve">1.52539360523224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50424885749817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47328817844391</t>
   </si>
   <si>
     <t xml:space="preserve">1.4725329875946</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">1.46649181842804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44987869262695</t>
+    <t xml:space="preserve">1.44987881183624</t>
   </si>
   <si>
     <t xml:space="preserve">1.44610297679901</t>
@@ -2120,13 +2120,13 @@
     <t xml:space="preserve">1.42722451686859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41665244102478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40683567523956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.400794506073</t>
+    <t xml:space="preserve">1.41665256023407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40683555603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40079462528229</t>
   </si>
   <si>
     <t xml:space="preserve">1.39097774028778</t>
@@ -2135,22 +2135,22 @@
     <t xml:space="preserve">1.3864461183548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28374707698822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25354051589966</t>
+    <t xml:space="preserve">1.28374695777893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25354063510895</t>
   </si>
   <si>
     <t xml:space="preserve">1.25127518177032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20068073272705</t>
+    <t xml:space="preserve">1.20068061351776</t>
   </si>
   <si>
     <t xml:space="preserve">1.23617231845856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25278544425964</t>
+    <t xml:space="preserve">1.25278532505035</t>
   </si>
   <si>
     <t xml:space="preserve">1.22182464599609</t>
@@ -2168,7 +2168,7 @@
     <t xml:space="preserve">1.27619552612305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31395256519318</t>
+    <t xml:space="preserve">1.31395244598389</t>
   </si>
   <si>
     <t xml:space="preserve">1.27090954780579</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">1.28223669528961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28752279281616</t>
+    <t xml:space="preserve">1.28752267360687</t>
   </si>
   <si>
     <t xml:space="preserve">1.35775077342987</t>
@@ -2189,7 +2189,7 @@
     <t xml:space="preserve">1.37436389923096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35246479511261</t>
+    <t xml:space="preserve">1.35246467590332</t>
   </si>
   <si>
     <t xml:space="preserve">1.40985631942749</t>
@@ -2204,22 +2204,22 @@
     <t xml:space="preserve">1.35095453262329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35926115512848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36454689502716</t>
+    <t xml:space="preserve">1.35926103591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36454701423645</t>
   </si>
   <si>
     <t xml:space="preserve">1.33736193180084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30262529850006</t>
+    <t xml:space="preserve">1.30262541770935</t>
   </si>
   <si>
     <t xml:space="preserve">1.2897881269455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26109278202057</t>
+    <t xml:space="preserve">1.26109266281128</t>
   </si>
   <si>
     <t xml:space="preserve">1.26864409446716</t>
@@ -2228,13 +2228,13 @@
     <t xml:space="preserve">1.25505089759827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27468526363373</t>
+    <t xml:space="preserve">1.27468514442444</t>
   </si>
   <si>
     <t xml:space="preserve">1.27997124195099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25958168506622</t>
+    <t xml:space="preserve">1.25958156585693</t>
   </si>
   <si>
     <t xml:space="preserve">1.25429570674896</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">1.30413579940796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33660686016083</t>
+    <t xml:space="preserve">1.33660674095154</t>
   </si>
   <si>
     <t xml:space="preserve">1.36077129840851</t>
@@ -2258,7 +2258,7 @@
     <t xml:space="preserve">1.38871240615845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38267052173615</t>
+    <t xml:space="preserve">1.38267040252686</t>
   </si>
   <si>
     <t xml:space="preserve">1.3517097234726</t>
@@ -2267,31 +2267,31 @@
     <t xml:space="preserve">1.35699570178986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36152637004852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36228179931641</t>
+    <t xml:space="preserve">1.36152648925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36228168010712</t>
   </si>
   <si>
     <t xml:space="preserve">1.34113776683807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36756777763367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42495894432068</t>
+    <t xml:space="preserve">1.36756765842438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42495906352997</t>
   </si>
   <si>
     <t xml:space="preserve">1.41740763187408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43326544761658</t>
+    <t xml:space="preserve">1.43326556682587</t>
   </si>
   <si>
     <t xml:space="preserve">1.40532541275024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43477594852448</t>
+    <t xml:space="preserve">1.43477582931519</t>
   </si>
   <si>
     <t xml:space="preserve">1.62960290908813</t>
@@ -2303,13 +2303,13 @@
     <t xml:space="preserve">1.57825350761414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58127391338348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54653739929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53747594356537</t>
+    <t xml:space="preserve">1.58127403259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54653751850128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53747582435608</t>
   </si>
   <si>
     <t xml:space="preserve">1.52237284183502</t>
@@ -2318,7 +2318,7 @@
     <t xml:space="preserve">1.55257856845856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60241782665253</t>
+    <t xml:space="preserve">1.60241770744324</t>
   </si>
   <si>
     <t xml:space="preserve">1.63111329078674</t>
@@ -2333,25 +2333,25 @@
     <t xml:space="preserve">1.54955792427063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57221245765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61147940158844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64168620109558</t>
+    <t xml:space="preserve">1.57221233844757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61147952079773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64168608188629</t>
   </si>
   <si>
     <t xml:space="preserve">1.61298990249634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61752068996429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59184587001801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58731520175934</t>
+    <t xml:space="preserve">1.61752080917358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59184598922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58731508255005</t>
   </si>
   <si>
     <t xml:space="preserve">1.6190310716629</t>
@@ -2360,22 +2360,22 @@
     <t xml:space="preserve">1.57976365089417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56013011932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55861973762512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59788715839386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60392820835114</t>
+    <t xml:space="preserve">1.56013000011444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55861985683441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59788703918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60392832756042</t>
   </si>
   <si>
     <t xml:space="preserve">1.58580482006073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59939742088318</t>
+    <t xml:space="preserve">1.59939730167389</t>
   </si>
   <si>
     <t xml:space="preserve">1.59637677669525</t>
@@ -2393,7 +2393,7 @@
     <t xml:space="preserve">1.50953483581543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52388322353363</t>
+    <t xml:space="preserve">1.52388334274292</t>
   </si>
   <si>
     <t xml:space="preserve">1.54049634933472</t>
@@ -2402,67 +2402,67 @@
     <t xml:space="preserve">1.63866460323334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75948798656464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80630731582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78365314006805</t>
+    <t xml:space="preserve">1.75948786735535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80630743503571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78365302085876</t>
   </si>
   <si>
     <t xml:space="preserve">1.83953356742859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02983093261719</t>
+    <t xml:space="preserve">2.02983069419861</t>
   </si>
   <si>
     <t xml:space="preserve">2.06909823417664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94827473163605</t>
+    <t xml:space="preserve">1.94827461242676</t>
   </si>
   <si>
     <t xml:space="preserve">1.89088308811188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77912247180939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77308130264282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81687939167023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70813846588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48008418083191</t>
+    <t xml:space="preserve">1.77912259101868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77308106422424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81687951087952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70813834667206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48008441925049</t>
   </si>
   <si>
     <t xml:space="preserve">1.37511885166168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32452464103699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2407032251358</t>
+    <t xml:space="preserve">1.3245245218277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24070310592651</t>
   </si>
   <si>
     <t xml:space="preserve">1.19917047023773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18406772613525</t>
+    <t xml:space="preserve">1.18406760692596</t>
   </si>
   <si>
     <t xml:space="preserve">0.959789335727692</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995280861854553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91901171207428</t>
+    <t xml:space="preserve">0.995280921459198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919011771678925</t>
   </si>
   <si>
     <t xml:space="preserve">0.945441544055939</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">0.962809801101685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01869106292725</t>
+    <t xml:space="preserve">1.01869094371796</t>
   </si>
   <si>
     <t xml:space="preserve">1.04361057281494</t>
@@ -2525,7 +2525,7 @@
     <t xml:space="preserve">1.08740890026093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0670200586319</t>
+    <t xml:space="preserve">1.06701993942261</t>
   </si>
   <si>
     <t xml:space="preserve">1.0942051410675</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">1.07834708690643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08212292194366</t>
+    <t xml:space="preserve">1.08212280273438</t>
   </si>
   <si>
     <t xml:space="preserve">1.07457137107849</t>
@@ -2549,7 +2549,7 @@
     <t xml:space="preserve">1.08665359020233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09269499778748</t>
+    <t xml:space="preserve">1.09269487857819</t>
   </si>
   <si>
     <t xml:space="preserve">1.03756952285767</t>
@@ -2570,19 +2570,19 @@
     <t xml:space="preserve">1.04285550117493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01189470291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985464036464691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970361292362213</t>
+    <t xml:space="preserve">1.01189482212067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985464096069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970361232757568</t>
   </si>
   <si>
     <t xml:space="preserve">0.989239692687988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.943176209926605</t>
+    <t xml:space="preserve">0.94317626953125</t>
   </si>
   <si>
     <t xml:space="preserve">0.926563024520874</t>
@@ -2591,16 +2591,16 @@
     <t xml:space="preserve">0.921277046203613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.913725674152374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986219227313995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997546255588531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05871343612671</t>
+    <t xml:space="preserve">0.913725733757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986219108104706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997546374797821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.058713555336</t>
   </si>
   <si>
     <t xml:space="preserve">1.09722566604614</t>
@@ -2609,19 +2609,19 @@
     <t xml:space="preserve">1.1025116443634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13422763347626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18180227279663</t>
+    <t xml:space="preserve">1.13422751426697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18180215358734</t>
   </si>
   <si>
     <t xml:space="preserve">1.21502840518951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23919284343719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19992554187775</t>
+    <t xml:space="preserve">1.23919296264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19992566108704</t>
   </si>
   <si>
     <t xml:space="preserve">1.18935358524323</t>
@@ -2630,10 +2630,10 @@
     <t xml:space="preserve">1.14782094955444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16820967197418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18708825111389</t>
+    <t xml:space="preserve">1.16820955276489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1870881319046</t>
   </si>
   <si>
     <t xml:space="preserve">1.16216850280762</t>
@@ -2642,13 +2642,13 @@
     <t xml:space="preserve">1.19312942028046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17047512531281</t>
+    <t xml:space="preserve">1.17047524452209</t>
   </si>
   <si>
     <t xml:space="preserve">1.24598920345306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29280865192413</t>
+    <t xml:space="preserve">1.29280877113342</t>
   </si>
   <si>
     <t xml:space="preserve">1.36303675174713</t>
@@ -2663,13 +2663,13 @@
     <t xml:space="preserve">1.39399826526642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39928436279297</t>
+    <t xml:space="preserve">1.39928424358368</t>
   </si>
   <si>
     <t xml:space="preserve">1.4015496969223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4030601978302</t>
+    <t xml:space="preserve">1.40306007862091</t>
   </si>
   <si>
     <t xml:space="preserve">1.41589736938477</t>
@@ -2678,7 +2678,7 @@
     <t xml:space="preserve">1.49292182922363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44836843013763</t>
+    <t xml:space="preserve">1.44836831092834</t>
   </si>
   <si>
     <t xml:space="preserve">1.48763573169708</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">1.46498155593872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39626371860504</t>
+    <t xml:space="preserve">1.39626359939575</t>
   </si>
   <si>
     <t xml:space="preserve">1.37662935256958</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">1.43175530433655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.445347905159</t>
+    <t xml:space="preserve">1.44534778594971</t>
   </si>
   <si>
     <t xml:space="preserve">1.47479832172394</t>
@@ -2714,34 +2714,34 @@
     <t xml:space="preserve">1.48461532592773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55106854438782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5208625793457</t>
+    <t xml:space="preserve">1.55106842517853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52086269855499</t>
   </si>
   <si>
     <t xml:space="preserve">1.37889468669891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37813949584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34415805339813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37209844589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39475345611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37964999675751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38795721530914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39248812198639</t>
+    <t xml:space="preserve">1.37813937664032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34415817260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37209856510162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39475333690643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37964987754822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38795709609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3924880027771</t>
   </si>
   <si>
     <t xml:space="preserve">1.32150399684906</t>
@@ -2753,13 +2753,13 @@
     <t xml:space="preserve">1.34340298175812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30036020278931</t>
+    <t xml:space="preserve">1.30036008358002</t>
   </si>
   <si>
     <t xml:space="preserve">1.32376945018768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33434152603149</t>
+    <t xml:space="preserve">1.33434164524078</t>
   </si>
   <si>
     <t xml:space="preserve">1.39777410030365</t>
@@ -2768,13 +2768,13 @@
     <t xml:space="preserve">1.36983299255371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38191533088684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34038257598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35473012924194</t>
+    <t xml:space="preserve">1.38191521167755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34038245677948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35473024845123</t>
   </si>
   <si>
     <t xml:space="preserve">1.31772828102112</t>
@@ -2792,16 +2792,16 @@
     <t xml:space="preserve">1.26486837863922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22484517097473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24145829677582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11761438846588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10779774188995</t>
+    <t xml:space="preserve">1.22484505176544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24145841598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11761450767517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10779762268066</t>
   </si>
   <si>
     <t xml:space="preserve">1.13800394535065</t>
@@ -2813,25 +2813,25 @@
     <t xml:space="preserve">1.24221336841583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23843777179718</t>
+    <t xml:space="preserve">1.23843789100647</t>
   </si>
   <si>
     <t xml:space="preserve">1.22862088680267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44232726097107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43251049518585</t>
+    <t xml:space="preserve">1.44232738018036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43251037597656</t>
   </si>
   <si>
     <t xml:space="preserve">1.50273859500885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55408883094788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81234860420227</t>
+    <t xml:space="preserve">1.55408895015717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81234872341156</t>
   </si>
   <si>
     <t xml:space="preserve">1.78214311599731</t>
@@ -2843,10 +2843,10 @@
     <t xml:space="preserve">1.75797772407532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69303548336029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7217310667038</t>
+    <t xml:space="preserve">1.69303560256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72173094749451</t>
   </si>
   <si>
     <t xml:space="preserve">1.68548405170441</t>
@@ -2855,46 +2855,46 @@
     <t xml:space="preserve">1.70209717750549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70360767841339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73079252243042</t>
+    <t xml:space="preserve">1.7036075592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73079264163971</t>
   </si>
   <si>
     <t xml:space="preserve">1.72777223587036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69907665252686</t>
+    <t xml:space="preserve">1.69907653331757</t>
   </si>
   <si>
     <t xml:space="preserve">1.66887104511261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66282987594604</t>
+    <t xml:space="preserve">1.66282975673676</t>
   </si>
   <si>
     <t xml:space="preserve">1.67944300174713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66131985187531</t>
+    <t xml:space="preserve">1.66131973266602</t>
   </si>
   <si>
     <t xml:space="preserve">1.67642247676849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64470648765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61601030826569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6356440782547</t>
+    <t xml:space="preserve">1.64470660686493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61601042747498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63564395904541</t>
   </si>
   <si>
     <t xml:space="preserve">1.65829908847809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66585063934326</t>
+    <t xml:space="preserve">1.66585052013397</t>
   </si>
   <si>
     <t xml:space="preserve">1.66434013843536</t>
@@ -2903,10 +2903,10 @@
     <t xml:space="preserve">1.74438524246216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77761209011078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.756467461586</t>
+    <t xml:space="preserve">1.77761197090149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75646734237671</t>
   </si>
   <si>
     <t xml:space="preserve">1.7202205657959</t>
@@ -2915,7 +2915,7 @@
     <t xml:space="preserve">1.73683369159698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6945458650589</t>
+    <t xml:space="preserve">1.69454598426819</t>
   </si>
   <si>
     <t xml:space="preserve">1.65225791931152</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">1.67491233348846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65376830101013</t>
+    <t xml:space="preserve">1.65376818180084</t>
   </si>
   <si>
     <t xml:space="preserve">1.63715434074402</t>
@@ -2933,34 +2933,34 @@
     <t xml:space="preserve">1.57070183753967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59486651420593</t>
+    <t xml:space="preserve">1.59486663341522</t>
   </si>
   <si>
     <t xml:space="preserve">1.62205147743225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74740564823151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88635241985321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85765731334686</t>
+    <t xml:space="preserve">1.74740552902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8863525390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85765719413757</t>
   </si>
   <si>
     <t xml:space="preserve">1.88031125068665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86822915077209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85463631153107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88937282562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85010552406311</t>
+    <t xml:space="preserve">1.86822903156281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85463654994965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88937294483185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85010540485382</t>
   </si>
   <si>
     <t xml:space="preserve">1.80932819843292</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">1.83047211170197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82141005992889</t>
+    <t xml:space="preserve">1.8214099407196</t>
   </si>
   <si>
     <t xml:space="preserve">1.81838965415955</t>
@@ -2984,13 +2984,13 @@
     <t xml:space="preserve">1.80177652835846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84557461738586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83500301837921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82745134830475</t>
+    <t xml:space="preserve">1.84557449817657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83500289916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82745146751404</t>
   </si>
   <si>
     <t xml:space="preserve">1.87124967575073</t>
@@ -2999,7 +2999,7 @@
     <t xml:space="preserve">1.86369800567627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.927130818367</t>
+    <t xml:space="preserve">1.92713093757629</t>
   </si>
   <si>
     <t xml:space="preserve">1.97999048233032</t>
@@ -3017,13 +3017,13 @@
     <t xml:space="preserve">2.15216398239136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12950921058655</t>
+    <t xml:space="preserve">2.12950944900513</t>
   </si>
   <si>
     <t xml:space="preserve">2.10685515403748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15518498420715</t>
+    <t xml:space="preserve">2.15518474578857</t>
   </si>
   <si>
     <t xml:space="preserve">2.13555026054382</t>
@@ -3032,7 +3032,7 @@
     <t xml:space="preserve">2.13857102394104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2246572971344</t>
+    <t xml:space="preserve">2.22465753555298</t>
   </si>
   <si>
     <t xml:space="preserve">2.15669512748718</t>
@@ -3059,13 +3059,13 @@
     <t xml:space="preserve">2.2699670791626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30168318748474</t>
+    <t xml:space="preserve">2.30168294906616</t>
   </si>
   <si>
     <t xml:space="preserve">2.23673987388611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2458016872406</t>
+    <t xml:space="preserve">2.24580192565918</t>
   </si>
   <si>
     <t xml:space="preserve">2.24882221221924</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">2.48140716552734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54937052726746</t>
+    <t xml:space="preserve">2.54937028884888</t>
   </si>
   <si>
     <t xml:space="preserve">2.64300799369812</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">2.61733341217041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60223031044006</t>
+    <t xml:space="preserve">2.60223054885864</t>
   </si>
   <si>
     <t xml:space="preserve">2.70190978050232</t>
@@ -3098,25 +3098,25 @@
     <t xml:space="preserve">2.73815655708313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78648638725281</t>
+    <t xml:space="preserve">2.78648614883423</t>
   </si>
   <si>
     <t xml:space="preserve">2.88616490364075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8650209903717</t>
+    <t xml:space="preserve">2.86502075195312</t>
   </si>
   <si>
     <t xml:space="preserve">2.86200046539307</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94204592704773</t>
+    <t xml:space="preserve">2.94204616546631</t>
   </si>
   <si>
     <t xml:space="preserve">2.94506645202637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93147373199463</t>
+    <t xml:space="preserve">2.93147420883179</t>
   </si>
   <si>
     <t xml:space="preserve">2.97980284690857</t>
@@ -3125,16 +3125,16 @@
     <t xml:space="preserve">2.96621036529541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9571487903595</t>
+    <t xml:space="preserve">2.95714902877808</t>
   </si>
   <si>
     <t xml:space="preserve">2.97829294204712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08411288261414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07337760925293</t>
+    <t xml:space="preserve">3.08411264419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07337737083435</t>
   </si>
   <si>
     <t xml:space="preserve">3.05804061889648</t>
@@ -3143,19 +3143,19 @@
     <t xml:space="preserve">3.15312528610229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09178066253662</t>
+    <t xml:space="preserve">3.0917809009552</t>
   </si>
   <si>
     <t xml:space="preserve">3.11478519439697</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19299960136414</t>
+    <t xml:space="preserve">3.19299936294556</t>
   </si>
   <si>
     <t xml:space="preserve">3.21600413322449</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18839836120605</t>
+    <t xml:space="preserve">3.18839859962463</t>
   </si>
   <si>
     <t xml:space="preserve">3.17459583282471</t>
@@ -3173,7 +3173,7 @@
     <t xml:space="preserve">2.96602392196655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95988941192627</t>
+    <t xml:space="preserve">2.95988965034485</t>
   </si>
   <si>
     <t xml:space="preserve">2.9445526599884</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">2.80039238929749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73598027229309</t>
+    <t xml:space="preserve">2.73598051071167</t>
   </si>
   <si>
     <t xml:space="preserve">2.7942578792572</t>
@@ -3206,16 +3206,16 @@
     <t xml:space="preserve">2.83719968795776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76665282249451</t>
+    <t xml:space="preserve">2.76665258407593</t>
   </si>
   <si>
     <t xml:space="preserve">2.80499291419983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79119062423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85713672637939</t>
+    <t xml:space="preserve">2.79119038581848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85713648796082</t>
   </si>
   <si>
     <t xml:space="preserve">2.78198885917664</t>
@@ -3224,22 +3224,22 @@
     <t xml:space="preserve">2.75131678581238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72371196746826</t>
+    <t xml:space="preserve">2.72371172904968</t>
   </si>
   <si>
     <t xml:space="preserve">2.84333419799805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7957911491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77892160415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72524499893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67310166358948</t>
+    <t xml:space="preserve">2.79579138755798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77892184257507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72524523735046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6731014251709</t>
   </si>
   <si>
     <t xml:space="preserve">2.58108496665955</t>
@@ -3254,7 +3254,7 @@
     <t xml:space="preserve">2.75745129585266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.783522605896</t>
+    <t xml:space="preserve">2.78352236747742</t>
   </si>
   <si>
     <t xml:space="preserve">2.92614936828613</t>
@@ -3269,25 +3269,25 @@
     <t xml:space="preserve">2.90774583816528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85100197792053</t>
+    <t xml:space="preserve">2.85100221633911</t>
   </si>
   <si>
     <t xml:space="preserve">2.86020398139954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85867023468018</t>
+    <t xml:space="preserve">2.8586699962616</t>
   </si>
   <si>
     <t xml:space="preserve">2.83873343467712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84486770629883</t>
+    <t xml:space="preserve">2.84486794471741</t>
   </si>
   <si>
     <t xml:space="preserve">2.91848111152649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95222115516663</t>
+    <t xml:space="preserve">2.95222139358521</t>
   </si>
   <si>
     <t xml:space="preserve">2.90467858314514</t>
@@ -3299,13 +3299,13 @@
     <t xml:space="preserve">2.92768263816833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92461562156677</t>
+    <t xml:space="preserve">2.92461585998535</t>
   </si>
   <si>
     <t xml:space="preserve">2.83566617965698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86173748970032</t>
+    <t xml:space="preserve">2.8617377281189</t>
   </si>
   <si>
     <t xml:space="preserve">2.84640145301819</t>
@@ -3317,13 +3317,13 @@
     <t xml:space="preserve">2.89854431152344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99976372718811</t>
+    <t xml:space="preserve">2.99976348876953</t>
   </si>
   <si>
     <t xml:space="preserve">3.0074315071106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98289370536804</t>
+    <t xml:space="preserve">2.98289346694946</t>
   </si>
   <si>
     <t xml:space="preserve">2.98596096038818</t>
@@ -3344,13 +3344,13 @@
     <t xml:space="preserve">2.90007781982422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84180068969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87400650978088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81726264953613</t>
+    <t xml:space="preserve">2.84180045127869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8740062713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81726288795471</t>
   </si>
   <si>
     <t xml:space="preserve">2.76511931419373</t>
@@ -3404,16 +3404,16 @@
     <t xml:space="preserve">2.87554001808167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9062123298645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95528864860535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97522568702698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98902821540833</t>
+    <t xml:space="preserve">2.90621209144592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95528841018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9752254486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98902797698975</t>
   </si>
   <si>
     <t xml:space="preserve">2.95068788528442</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">2.85560321807861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80806064605713</t>
+    <t xml:space="preserve">2.80806040763855</t>
   </si>
   <si>
     <t xml:space="preserve">2.76205205917358</t>
@@ -3461,22 +3461,22 @@
     <t xml:space="preserve">2.77432084083557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69917392730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70684194564819</t>
+    <t xml:space="preserve">2.69917416572571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70684170722961</t>
   </si>
   <si>
     <t xml:space="preserve">2.66083288192749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76051807403564</t>
+    <t xml:space="preserve">2.76051831245422</t>
   </si>
   <si>
     <t xml:space="preserve">2.71144270896912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58875298500061</t>
+    <t xml:space="preserve">2.58875274658203</t>
   </si>
   <si>
     <t xml:space="preserve">2.73137974739075</t>
@@ -3488,13 +3488,13 @@
     <t xml:space="preserve">2.65009760856628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6777024269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67463541030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74671578407288</t>
+    <t xml:space="preserve">2.67770266532898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67463517189026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74671602249146</t>
   </si>
   <si>
     <t xml:space="preserve">2.72064423561096</t>
@@ -3512,10 +3512,10 @@
     <t xml:space="preserve">2.75438380241394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82493090629578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85406947135925</t>
+    <t xml:space="preserve">2.8249306678772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85406923294067</t>
   </si>
   <si>
     <t xml:space="preserve">2.89701056480408</t>
@@ -3527,22 +3527,22 @@
     <t xml:space="preserve">2.94148540496826</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03503680229187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02736854553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89087629318237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74058151245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7850558757782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86480450630188</t>
+    <t xml:space="preserve">3.03503656387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02736878395081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89087605476379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74058127403259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78505611419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86480474472046</t>
   </si>
   <si>
     <t xml:space="preserve">2.82799816131592</t>
@@ -3563,13 +3563,13 @@
     <t xml:space="preserve">3.07029485702515</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15472841262817</t>
+    <t xml:space="preserve">3.15472817420959</t>
   </si>
   <si>
     <t xml:space="preserve">3.08871674537659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19771218299866</t>
+    <t xml:space="preserve">3.19771194458008</t>
   </si>
   <si>
     <t xml:space="preserve">3.21459889411926</t>
@@ -3590,28 +3590,28 @@
     <t xml:space="preserve">2.94748306274414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80010914802551</t>
+    <t xml:space="preserve">2.80010890960693</t>
   </si>
   <si>
     <t xml:space="preserve">2.84769868850708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72028112411499</t>
+    <t xml:space="preserve">2.72028136253357</t>
   </si>
   <si>
     <t xml:space="preserve">2.55602025985718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58979368209839</t>
+    <t xml:space="preserve">2.58979392051697</t>
   </si>
   <si>
     <t xml:space="preserve">2.54066896438599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25359630584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24592089653015</t>
+    <t xml:space="preserve">2.25359654426575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24592065811157</t>
   </si>
   <si>
     <t xml:space="preserve">2.33342409133911</t>
@@ -3656,13 +3656,13 @@
     <t xml:space="preserve">2.73870325088501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79703855514526</t>
+    <t xml:space="preserve">2.79703879356384</t>
   </si>
   <si>
     <t xml:space="preserve">2.92292094230652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92906141281128</t>
+    <t xml:space="preserve">2.9290611743927</t>
   </si>
   <si>
     <t xml:space="preserve">2.85383892059326</t>
@@ -3695,7 +3695,7 @@
     <t xml:space="preserve">2.93980741500854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88607740402222</t>
+    <t xml:space="preserve">2.88607716560364</t>
   </si>
   <si>
     <t xml:space="preserve">2.96590495109558</t>
@@ -3707,7 +3707,7 @@
     <t xml:space="preserve">2.90603423118591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92752623558044</t>
+    <t xml:space="preserve">2.92752599716187</t>
   </si>
   <si>
     <t xml:space="preserve">2.91678023338318</t>
@@ -3731,10 +3731,10 @@
     <t xml:space="preserve">2.68343782424927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78168725967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80624938011169</t>
+    <t xml:space="preserve">2.78168749809265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80624961853027</t>
   </si>
   <si>
     <t xml:space="preserve">2.82467126846313</t>
@@ -3743,34 +3743,34 @@
     <t xml:space="preserve">2.81853079795837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88147187232971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86151504516602</t>
+    <t xml:space="preserve">2.88147211074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86151480674744</t>
   </si>
   <si>
     <t xml:space="preserve">2.85230422019958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81239032745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05270981788635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07706665992737</t>
+    <t xml:space="preserve">2.81239008903503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05271005630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07706642150879</t>
   </si>
   <si>
     <t xml:space="preserve">3.13065147399902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13877034187317</t>
+    <t xml:space="preserve">3.13877058029175</t>
   </si>
   <si>
     <t xml:space="preserve">3.11766123771667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07544279098511</t>
+    <t xml:space="preserve">3.07544302940369</t>
   </si>
   <si>
     <t xml:space="preserve">3.04946231842041</t>
@@ -3794,28 +3794,28 @@
     <t xml:space="preserve">2.96664953231812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7620530128479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6337742805481</t>
+    <t xml:space="preserve">2.76205277442932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63377404212952</t>
   </si>
   <si>
     <t xml:space="preserve">2.62565517425537</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74256753921509</t>
+    <t xml:space="preserve">2.74256777763367</t>
   </si>
   <si>
     <t xml:space="preserve">2.66137862205505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70197319984436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76367664337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78478598594666</t>
+    <t xml:space="preserve">2.70197296142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76367688179016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78478574752808</t>
   </si>
   <si>
     <t xml:space="preserve">2.77666711807251</t>
@@ -3827,10 +3827,10 @@
     <t xml:space="preserve">2.73282480239868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69385433197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70034909248352</t>
+    <t xml:space="preserve">2.69385409355164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7003493309021</t>
   </si>
   <si>
     <t xml:space="preserve">2.75880527496338</t>
@@ -3848,13 +3848,13 @@
     <t xml:space="preserve">2.59480357170105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60129857063293</t>
+    <t xml:space="preserve">2.60129880905151</t>
   </si>
   <si>
     <t xml:space="preserve">2.67274498939514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76042914390564</t>
+    <t xml:space="preserve">2.76042938232422</t>
   </si>
   <si>
     <t xml:space="preserve">2.71821093559265</t>
@@ -3878,19 +3878,19 @@
     <t xml:space="preserve">2.69060659408569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61428880691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57856559753418</t>
+    <t xml:space="preserve">2.61428904533386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57856583595276</t>
   </si>
   <si>
     <t xml:space="preserve">2.54608988761902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58343720436096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51686191558838</t>
+    <t xml:space="preserve">2.58343696594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5168616771698</t>
   </si>
   <si>
     <t xml:space="preserve">2.55908012390137</t>
@@ -3905,7 +3905,7 @@
     <t xml:space="preserve">2.72957730293274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6694974899292</t>
+    <t xml:space="preserve">2.66949772834778</t>
   </si>
   <si>
     <t xml:space="preserve">2.78153848648071</t>
@@ -3917,19 +3917,19 @@
     <t xml:space="preserve">2.71496343612671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71171569824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70684456825256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61753630638123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66624999046326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60941743850708</t>
+    <t xml:space="preserve">2.71171545982361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70684432983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6175365447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66624975204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60941767692566</t>
   </si>
   <si>
     <t xml:space="preserve">2.56395149230957</t>
@@ -3941,13 +3941,13 @@
     <t xml:space="preserve">2.59155607223511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59967494010925</t>
+    <t xml:space="preserve">2.59967470169067</t>
   </si>
   <si>
     <t xml:space="preserve">2.56070399284363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59642720222473</t>
+    <t xml:space="preserve">2.59642744064331</t>
   </si>
   <si>
     <t xml:space="preserve">2.59805107116699</t>
@@ -3965,7 +3965,7 @@
     <t xml:space="preserve">2.81726145744324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84811353683472</t>
+    <t xml:space="preserve">2.84811329841614</t>
   </si>
   <si>
     <t xml:space="preserve">2.92767882347107</t>
@@ -3977,16 +3977,16 @@
     <t xml:space="preserve">2.88870811462402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83999466896057</t>
+    <t xml:space="preserve">2.83999443054199</t>
   </si>
   <si>
     <t xml:space="preserve">2.78965735435486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85136103630066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78803324699402</t>
+    <t xml:space="preserve">2.85136127471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7880334854126</t>
   </si>
   <si>
     <t xml:space="preserve">2.76530051231384</t>
@@ -3995,13 +3995,13 @@
     <t xml:space="preserve">2.64514064788818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75393414497375</t>
+    <t xml:space="preserve">2.75393390655518</t>
   </si>
   <si>
     <t xml:space="preserve">2.76692414283752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8546085357666</t>
+    <t xml:space="preserve">2.85460877418518</t>
   </si>
   <si>
     <t xml:space="preserve">2.7929048538208</t>
@@ -4019,7 +4019,7 @@
     <t xml:space="preserve">2.64189314842224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75555777549744</t>
+    <t xml:space="preserve">2.75555801391602</t>
   </si>
   <si>
     <t xml:space="preserve">2.83512306213379</t>
@@ -4031,7 +4031,7 @@
     <t xml:space="preserve">2.87734150886536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91631245613098</t>
+    <t xml:space="preserve">2.9163122177124</t>
   </si>
   <si>
     <t xml:space="preserve">2.95853066444397</t>
@@ -4064,10 +4064,10 @@
     <t xml:space="preserve">2.87409400939941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84973740577698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89520335197449</t>
+    <t xml:space="preserve">2.8497371673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89520311355591</t>
   </si>
   <si>
     <t xml:space="preserve">2.88708424568176</t>
@@ -4091,13 +4091,13 @@
     <t xml:space="preserve">3.11441373825073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15987968444824</t>
+    <t xml:space="preserve">3.15987944602966</t>
   </si>
   <si>
     <t xml:space="preserve">3.12740397453308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16637468338013</t>
+    <t xml:space="preserve">3.16637492179871</t>
   </si>
   <si>
     <t xml:space="preserve">3.14201784133911</t>
@@ -4106,22 +4106,22 @@
     <t xml:space="preserve">3.1209089756012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08031392097473</t>
+    <t xml:space="preserve">3.08031415939331</t>
   </si>
   <si>
     <t xml:space="preserve">3.07219505310059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08193802833557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0916805267334</t>
+    <t xml:space="preserve">3.08193778991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09168076515198</t>
   </si>
   <si>
     <t xml:space="preserve">3.09817576408386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06894779205322</t>
+    <t xml:space="preserve">3.06894755363464</t>
   </si>
   <si>
     <t xml:space="preserve">3.04134345054626</t>
@@ -4130,16 +4130,16 @@
     <t xml:space="preserve">3.11278986930847</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17449355125427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18261241912842</t>
+    <t xml:space="preserve">3.17449378967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.182612657547</t>
   </si>
   <si>
     <t xml:space="preserve">3.17611742019653</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14039444923401</t>
+    <t xml:space="preserve">3.14039421081543</t>
   </si>
   <si>
     <t xml:space="preserve">3.12415647506714</t>
@@ -4148,7 +4148,7 @@
     <t xml:space="preserve">3.17774128913879</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21508836746216</t>
+    <t xml:space="preserve">3.21508812904358</t>
   </si>
   <si>
     <t xml:space="preserve">3.26542520523071</t>
@@ -4163,7 +4163,7 @@
     <t xml:space="preserve">3.27029657363892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3125147819519</t>
+    <t xml:space="preserve">3.31251502037048</t>
   </si>
   <si>
     <t xml:space="preserve">3.3417432308197</t>
@@ -4184,7 +4184,7 @@
     <t xml:space="preserve">3.43917012214661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46190285682678</t>
+    <t xml:space="preserve">3.46190309524536</t>
   </si>
   <si>
     <t xml:space="preserve">3.48301196098328</t>
@@ -4193,7 +4193,7 @@
     <t xml:space="preserve">3.51386380195618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53822064399719</t>
+    <t xml:space="preserve">3.53822040557861</t>
   </si>
   <si>
     <t xml:space="preserve">3.52035927772522</t>
@@ -4205,7 +4205,7 @@
     <t xml:space="preserve">3.733074426651</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65675687789917</t>
+    <t xml:space="preserve">3.65675711631775</t>
   </si>
   <si>
     <t xml:space="preserve">3.66487550735474</t>
@@ -4214,7 +4214,7 @@
     <t xml:space="preserve">3.7022225856781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68436121940613</t>
+    <t xml:space="preserve">3.68436098098755</t>
   </si>
   <si>
     <t xml:space="preserve">3.65026164054871</t>
@@ -4229,7 +4229,7 @@
     <t xml:space="preserve">3.59505319595337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60804319381714</t>
+    <t xml:space="preserve">3.60804343223572</t>
   </si>
   <si>
     <t xml:space="preserve">3.64539003372192</t>
@@ -4244,40 +4244,40 @@
     <t xml:space="preserve">3.61616206169128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68598484992981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69572758674622</t>
+    <t xml:space="preserve">3.68598508834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69572782516479</t>
   </si>
   <si>
     <t xml:space="preserve">3.81101608276367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90032386779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87921476364136</t>
+    <t xml:space="preserve">3.90032410621643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87921500205994</t>
   </si>
   <si>
     <t xml:space="preserve">3.89870047569275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89382863044739</t>
+    <t xml:space="preserve">3.89382886886597</t>
   </si>
   <si>
     <t xml:space="preserve">3.97177052497864</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89220547676086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91980957984924</t>
+    <t xml:space="preserve">3.89220523834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91980934143066</t>
   </si>
   <si>
     <t xml:space="preserve">3.82400631904602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41806101799011</t>
+    <t xml:space="preserve">3.41806077957153</t>
   </si>
   <si>
     <t xml:space="preserve">3.41643738746643</t>
@@ -4289,10 +4289,10 @@
     <t xml:space="preserve">3.21021676063538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09492826461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3725950717926</t>
+    <t xml:space="preserve">3.09492802619934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37259483337402</t>
   </si>
   <si>
     <t xml:space="preserve">3.28491067886353</t>
@@ -4307,7 +4307,7 @@
     <t xml:space="preserve">3.09330439567566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09979939460754</t>
+    <t xml:space="preserve">3.09979963302612</t>
   </si>
   <si>
     <t xml:space="preserve">3.19560289382935</t>
@@ -4319,7 +4319,7 @@
     <t xml:space="preserve">3.1517608165741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27192068099976</t>
+    <t xml:space="preserve">3.27192044258118</t>
   </si>
   <si>
     <t xml:space="preserve">3.28815841674805</t>
@@ -4328,19 +4328,19 @@
     <t xml:space="preserve">3.31738638877869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36122846603394</t>
+    <t xml:space="preserve">3.36122822761536</t>
   </si>
   <si>
     <t xml:space="preserve">3.34823822975159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44891285896301</t>
+    <t xml:space="preserve">3.44891309738159</t>
   </si>
   <si>
     <t xml:space="preserve">3.4342987537384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47326946258545</t>
+    <t xml:space="preserve">3.47326922416687</t>
   </si>
   <si>
     <t xml:space="preserve">3.47002196311951</t>
@@ -4352,7 +4352,7 @@
     <t xml:space="preserve">3.34661459922791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32712912559509</t>
+    <t xml:space="preserve">3.32712888717651</t>
   </si>
   <si>
     <t xml:space="preserve">3.26704931259155</t>
@@ -4367,7 +4367,7 @@
     <t xml:space="preserve">3.50736880302429</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36934757232666</t>
+    <t xml:space="preserve">3.36934733390808</t>
   </si>
   <si>
     <t xml:space="preserve">3.38558530807495</t>
@@ -4388,19 +4388,19 @@
     <t xml:space="preserve">3.18703985214233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19400262832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20096468925476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18355894088745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13134074211121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0460512638092</t>
+    <t xml:space="preserve">3.19400238990784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20096492767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18355870246887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13134098052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04605150222778</t>
   </si>
   <si>
     <t xml:space="preserve">3.13308143615723</t>
@@ -4409,22 +4409,22 @@
     <t xml:space="preserve">3.22533321380615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1974835395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2114086151123</t>
+    <t xml:space="preserve">3.19748377799988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21140837669373</t>
   </si>
   <si>
     <t xml:space="preserve">3.23055481910706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24273920059204</t>
+    <t xml:space="preserve">3.24273943901062</t>
   </si>
   <si>
     <t xml:space="preserve">3.23229551315308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22011137008667</t>
+    <t xml:space="preserve">3.22011160850525</t>
   </si>
   <si>
     <t xml:space="preserve">3.29321646690369</t>
@@ -4433,25 +4433,25 @@
     <t xml:space="preserve">3.25840449333191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28625416755676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30017924308777</t>
+    <t xml:space="preserve">3.28625440597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30017900466919</t>
   </si>
   <si>
     <t xml:space="preserve">3.34891581535339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38546872138977</t>
+    <t xml:space="preserve">3.38546848297119</t>
   </si>
   <si>
     <t xml:space="preserve">3.41505861282349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37676548957825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38024663925171</t>
+    <t xml:space="preserve">3.37676572799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38024687767029</t>
   </si>
   <si>
     <t xml:space="preserve">3.32106614112854</t>
@@ -4472,28 +4472,28 @@
     <t xml:space="preserve">3.33673167228699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30888199806213</t>
+    <t xml:space="preserve">3.30888223648071</t>
   </si>
   <si>
     <t xml:space="preserve">3.34369397163391</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40809631347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42028045654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43420553207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50905108451843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5316789150238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55430674552917</t>
+    <t xml:space="preserve">3.40809607505798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42028069496155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4342052936554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50905132293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53167915344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55430698394775</t>
   </si>
   <si>
     <t xml:space="preserve">3.63785552978516</t>
@@ -4508,7 +4508,7 @@
     <t xml:space="preserve">3.70922040939331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78406620025635</t>
+    <t xml:space="preserve">3.78406596183777</t>
   </si>
   <si>
     <t xml:space="preserve">3.82409977912903</t>
@@ -4520,31 +4520,31 @@
     <t xml:space="preserve">3.75099468231201</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72140455245972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73184823989868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73881053924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52471685409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6535210609436</t>
+    <t xml:space="preserve">3.72140431404114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7318480014801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73881030082703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52471661567688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65352082252502</t>
   </si>
   <si>
     <t xml:space="preserve">3.68833303451538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74229192733765</t>
+    <t xml:space="preserve">3.74229168891907</t>
   </si>
   <si>
     <t xml:space="preserve">3.73358845710754</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68485188484192</t>
+    <t xml:space="preserve">3.6848521232605</t>
   </si>
   <si>
     <t xml:space="preserve">3.64655876159668</t>
@@ -4553,37 +4553,37 @@
     <t xml:space="preserve">3.68137073516846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69007325172424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71270108222961</t>
+    <t xml:space="preserve">3.69007349014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71270132064819</t>
   </si>
   <si>
     <t xml:space="preserve">3.72314476966858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8032124042511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83802437782288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81713771820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76665997505188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76840043067932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86065220832825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90416741371155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90590834617615</t>
+    <t xml:space="preserve">3.80321264266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83802461624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8171374797821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76666021347046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7684006690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86065268516541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90416789054871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90590786933899</t>
   </si>
   <si>
     <t xml:space="preserve">4.00338172912598</t>
@@ -4598,7 +4598,7 @@
     <t xml:space="preserve">4.07648706436157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17744207382202</t>
+    <t xml:space="preserve">4.17744159698486</t>
   </si>
   <si>
     <t xml:space="preserve">4.34976148605347</t>
@@ -4628,7 +4628,7 @@
     <t xml:space="preserve">4.31668996810913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22095680236816</t>
+    <t xml:space="preserve">4.22095632553101</t>
   </si>
   <si>
     <t xml:space="preserve">4.19310712814331</t>
@@ -4637,7 +4637,7 @@
     <t xml:space="preserve">4.28884029388428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37325954437256</t>
+    <t xml:space="preserve">4.3732590675354</t>
   </si>
   <si>
     <t xml:space="preserve">4.3393177986145</t>
@@ -4709,10 +4709,10 @@
     <t xml:space="preserve">5.0607967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21309947967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19569301605225</t>
+    <t xml:space="preserve">5.21309900283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1956934928894</t>
   </si>
   <si>
     <t xml:space="preserve">5.13042068481445</t>
@@ -4721,7 +4721,7 @@
     <t xml:space="preserve">5.14347505569458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08690547943115</t>
+    <t xml:space="preserve">5.08690595626831</t>
   </si>
   <si>
     <t xml:space="preserve">5.04774236679077</t>
@@ -4826,13 +4826,13 @@
     <t xml:space="preserve">5.33494138717651</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5525164604187</t>
+    <t xml:space="preserve">5.55251693725586</t>
   </si>
   <si>
     <t xml:space="preserve">5.65695238113403</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70481872558594</t>
+    <t xml:space="preserve">5.7048192024231</t>
   </si>
   <si>
     <t xml:space="preserve">5.7091703414917</t>
@@ -4850,7 +4850,7 @@
     <t xml:space="preserve">6.13561773300171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8005518913269</t>
+    <t xml:space="preserve">5.80055236816406</t>
   </si>
   <si>
     <t xml:space="preserve">5.78749752044678</t>
@@ -4859,7 +4859,7 @@
     <t xml:space="preserve">5.87017583847046</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8397159576416</t>
+    <t xml:space="preserve">5.83971548080444</t>
   </si>
   <si>
     <t xml:space="preserve">5.71352195739746</t>
@@ -4868,10 +4868,10 @@
     <t xml:space="preserve">5.72222471237183</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84406709671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93109703063965</t>
+    <t xml:space="preserve">5.84406757354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93109750747681</t>
   </si>
   <si>
     <t xml:space="preserve">5.97896337509155</t>
@@ -4880,7 +4880,7 @@
     <t xml:space="preserve">5.94415140151978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89628553390503</t>
+    <t xml:space="preserve">5.89628505706787</t>
   </si>
   <si>
     <t xml:space="preserve">5.98766660690308</t>
@@ -4898,7 +4898,7 @@
     <t xml:space="preserve">6.24005365371704</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17913246154785</t>
+    <t xml:space="preserve">6.17913293838501</t>
   </si>
   <si>
     <t xml:space="preserve">6.01812744140625</t>
@@ -4907,10 +4907,10 @@
     <t xml:space="preserve">6.16172647476196</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23570203781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23135089874268</t>
+    <t xml:space="preserve">6.23570251464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23135042190552</t>
   </si>
   <si>
     <t xml:space="preserve">6.07904815673828</t>
@@ -4919,7 +4919,7 @@
     <t xml:space="preserve">6.00507259368896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8658242225647</t>
+    <t xml:space="preserve">5.86582469940186</t>
   </si>
   <si>
     <t xml:space="preserve">5.69176435470581</t>
@@ -4931,34 +4931,34 @@
     <t xml:space="preserve">5.91369104385376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93980026245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18783617019653</t>
+    <t xml:space="preserve">5.93979978561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18783569335938</t>
   </si>
   <si>
     <t xml:space="preserve">6.065993309021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03988456726074</t>
+    <t xml:space="preserve">6.0398850440979</t>
   </si>
   <si>
     <t xml:space="preserve">6.09645414352417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22264766693115</t>
+    <t xml:space="preserve">6.22264814376831</t>
   </si>
   <si>
     <t xml:space="preserve">5.93544864654541</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06164216995239</t>
+    <t xml:space="preserve">6.06164264678955</t>
   </si>
   <si>
     <t xml:space="preserve">5.82666110992432</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85277032852173</t>
+    <t xml:space="preserve">5.85276985168457</t>
   </si>
   <si>
     <t xml:space="preserve">5.92674541473389</t>
@@ -4967,28 +4967,28 @@
     <t xml:space="preserve">6.11821174621582</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37930202484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53595590591431</t>
+    <t xml:space="preserve">6.37930154800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53595638275146</t>
   </si>
   <si>
     <t xml:space="preserve">6.53160429000854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47068309783936</t>
+    <t xml:space="preserve">6.47068357467651</t>
   </si>
   <si>
     <t xml:space="preserve">6.66650104522705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82315540313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84056091308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90148210525513</t>
+    <t xml:space="preserve">6.82315492630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8405613899231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90148162841797</t>
   </si>
   <si>
     <t xml:space="preserve">6.80574893951416</t>
@@ -4997,7 +4997,7 @@
     <t xml:space="preserve">6.95369958877563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07119083404541</t>
+    <t xml:space="preserve">7.07119035720825</t>
   </si>
   <si>
     <t xml:space="preserve">6.96240282058716</t>
@@ -5009,10 +5009,10 @@
     <t xml:space="preserve">6.99286365509033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12775993347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12340879440308</t>
+    <t xml:space="preserve">7.12775945663452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12340927124023</t>
   </si>
   <si>
     <t xml:space="preserve">7.20173501968384</t>
@@ -5964,6 +5964,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.9350004196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.875</t>
   </si>
 </sst>
 </file>
@@ -71822,7 +71825,7 @@
     </row>
     <row r="2521">
       <c r="A2521" s="1" t="n">
-        <v>45988.69125</v>
+        <v>45988.3333333333</v>
       </c>
       <c r="B2521" t="n">
         <v>436999</v>
@@ -71843,6 +71846,32 @@
         <v>1983</v>
       </c>
       <c r="H2521" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2522">
+      <c r="A2522" s="1" t="n">
+        <v>45989.6915162037</v>
+      </c>
+      <c r="B2522" t="n">
+        <v>444485</v>
+      </c>
+      <c r="C2522" t="n">
+        <v>15.0200004577637</v>
+      </c>
+      <c r="D2522" t="n">
+        <v>14.789999961853</v>
+      </c>
+      <c r="E2522" t="n">
+        <v>14.8850002288818</v>
+      </c>
+      <c r="F2522" t="n">
+        <v>14.875</v>
+      </c>
+      <c r="G2522" t="s">
+        <v>1984</v>
+      </c>
+      <c r="H2522" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BPSO.MI.xlsx
+++ b/data/BPSO.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1993" uniqueCount="1993">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1994" uniqueCount="1994">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82907152175903</t>
+    <t xml:space="preserve">2.82907199859619</t>
   </si>
   <si>
     <t xml:space="preserve">BPSO.MI</t>
@@ -47,43 +47,43 @@
     <t xml:space="preserve">2.80963730812073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74855828285217</t>
+    <t xml:space="preserve">2.74855804443359</t>
   </si>
   <si>
     <t xml:space="preserve">2.71246576309204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63611721992493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60835385322571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69303178787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69858455657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61113023757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51257085800171</t>
+    <t xml:space="preserve">2.63611698150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60835409164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69303202629089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69858479499817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61113047599792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51257038116455</t>
   </si>
   <si>
     <t xml:space="preserve">2.4556565284729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26686644554138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38069534301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40568256378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36542630195618</t>
+    <t xml:space="preserve">2.2668662071228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38069558143616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40568232536316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36542582511902</t>
   </si>
   <si>
     <t xml:space="preserve">2.51951169967651</t>
@@ -92,28 +92,28 @@
     <t xml:space="preserve">2.44455099105835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35570859909058</t>
+    <t xml:space="preserve">2.35570907592773</t>
   </si>
   <si>
     <t xml:space="preserve">2.43899893760681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40429401397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32100486755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22105717658997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23216223716736</t>
+    <t xml:space="preserve">2.40429449081421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32100510597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22105765342712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23216247558594</t>
   </si>
   <si>
     <t xml:space="preserve">2.20995187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04059624671936</t>
+    <t xml:space="preserve">2.04059600830078</t>
   </si>
   <si>
     <t xml:space="preserve">2.06280660629272</t>
@@ -122,19 +122,19 @@
     <t xml:space="preserve">2.14331984519958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07668828964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18218779563904</t>
+    <t xml:space="preserve">2.07668805122375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1821882724762</t>
   </si>
   <si>
     <t xml:space="preserve">2.22522163391113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27797174453735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19329380989075</t>
+    <t xml:space="preserve">2.27797150611877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19329357147217</t>
   </si>
   <si>
     <t xml:space="preserve">2.16553044319153</t>
@@ -149,10 +149,10 @@
     <t xml:space="preserve">2.17663598060608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21550440788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.259925365448</t>
+    <t xml:space="preserve">2.21550488471985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25992560386658</t>
   </si>
   <si>
     <t xml:space="preserve">2.31822872161865</t>
@@ -170,13 +170,13 @@
     <t xml:space="preserve">2.2418794631958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26270198822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25020861625671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31961703300476</t>
+    <t xml:space="preserve">2.26270174980164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25020837783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31961679458618</t>
   </si>
   <si>
     <t xml:space="preserve">2.43344521522522</t>
@@ -185,13 +185,13 @@
     <t xml:space="preserve">2.35848498344421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30157017707825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34599161148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35987329483032</t>
+    <t xml:space="preserve">2.30156993865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34599137306213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3598735332489</t>
   </si>
   <si>
     <t xml:space="preserve">2.39318871498108</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">2.29324150085449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23771476745605</t>
+    <t xml:space="preserve">2.23771500587463</t>
   </si>
   <si>
     <t xml:space="preserve">2.18774056434631</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">2.139155626297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14748430252075</t>
+    <t xml:space="preserve">2.14748477935791</t>
   </si>
   <si>
     <t xml:space="preserve">2.1211097240448</t>
@@ -218,52 +218,52 @@
     <t xml:space="preserve">2.06974720954895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01283311843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01838564872742</t>
+    <t xml:space="preserve">2.01283288002014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.018385887146</t>
   </si>
   <si>
     <t xml:space="preserve">2.07113552093506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11694526672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12527370452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22799777984619</t>
+    <t xml:space="preserve">2.11694502830505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12527418136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22799801826477</t>
   </si>
   <si>
     <t xml:space="preserve">2.30295848846436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23910307884216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29046511650085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33211040496826</t>
+    <t xml:space="preserve">2.23910331726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29046487808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3321099281311</t>
   </si>
   <si>
     <t xml:space="preserve">2.32655763626099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2793595790863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32378149032593</t>
+    <t xml:space="preserve">2.27935934066772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32378125190735</t>
   </si>
   <si>
     <t xml:space="preserve">2.30851101875305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26131343841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23493909835815</t>
+    <t xml:space="preserve">2.26131391525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23493885993958</t>
   </si>
   <si>
     <t xml:space="preserve">2.15720152854919</t>
@@ -275,25 +275,25 @@
     <t xml:space="preserve">2.08224058151245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09889912605286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08918190002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10584020614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04892492294312</t>
+    <t xml:space="preserve">2.09889888763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08918237686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10583972930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04892516136169</t>
   </si>
   <si>
     <t xml:space="preserve">2.03781986236572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06558299064636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03226709365845</t>
+    <t xml:space="preserve">2.06558275222778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03226733207703</t>
   </si>
   <si>
     <t xml:space="preserve">2.07252359390259</t>
@@ -302,31 +302,31 @@
     <t xml:space="preserve">2.05725383758545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05156683921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12691879272461</t>
+    <t xml:space="preserve">2.05156707763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12691903114319</t>
   </si>
   <si>
     <t xml:space="preserve">2.19942736625671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15393209457397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17525792121887</t>
+    <t xml:space="preserve">2.15393233299255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17525815963745</t>
   </si>
   <si>
     <t xml:space="preserve">2.15535402297974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09279704093933</t>
+    <t xml:space="preserve">2.09279680252075</t>
   </si>
   <si>
     <t xml:space="preserve">2.07147121429443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99896228313446</t>
+    <t xml:space="preserve">1.99896240234375</t>
   </si>
   <si>
     <t xml:space="preserve">1.95773220062256</t>
@@ -335,115 +335,115 @@
     <t xml:space="preserve">1.87669289112091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98901033401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93640637397766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94351482391357</t>
+    <t xml:space="preserve">1.98901009559631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93640613555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.943514585495</t>
   </si>
   <si>
     <t xml:space="preserve">1.84114968776703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78143715858459</t>
+    <t xml:space="preserve">1.78143727779388</t>
   </si>
   <si>
     <t xml:space="preserve">1.75157999992371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7259886264801</t>
+    <t xml:space="preserve">1.72598886489868</t>
   </si>
   <si>
     <t xml:space="preserve">1.64210617542267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69613254070282</t>
+    <t xml:space="preserve">1.69613265991211</t>
   </si>
   <si>
     <t xml:space="preserve">1.77006244659424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81129312515259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78001439571381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89375376701355</t>
+    <t xml:space="preserve">1.81129336357117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78001463413239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89375388622284</t>
   </si>
   <si>
     <t xml:space="preserve">1.63499760627747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56533300876617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66911959648132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65632367134094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63926267623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63641941547394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5767068862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51130640506744</t>
+    <t xml:space="preserve">1.5653327703476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66911971569061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65632355213165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6392627954483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63641929626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57670676708221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51130664348602</t>
   </si>
   <si>
     <t xml:space="preserve">1.52552390098572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53121054172516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63784086704254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67196333408356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69471108913422</t>
+    <t xml:space="preserve">1.53121078014374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63784098625183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67196321487427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69471085071564</t>
   </si>
   <si>
     <t xml:space="preserve">1.67054152488708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7430499792099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70892810821533</t>
+    <t xml:space="preserve">1.74304986000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70892798900604</t>
   </si>
   <si>
     <t xml:space="preserve">1.72172379493713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77574956417084</t>
+    <t xml:space="preserve">1.77574968338013</t>
   </si>
   <si>
     <t xml:space="preserve">1.76721894741058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72741091251373</t>
+    <t xml:space="preserve">1.72741067409515</t>
   </si>
   <si>
     <t xml:space="preserve">1.69755434989929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7245671749115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71888017654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6634327173233</t>
+    <t xml:space="preserve">1.72456729412079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71888029575348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66343283653259</t>
   </si>
   <si>
     <t xml:space="preserve">1.55395901203156</t>
@@ -452,31 +452,31 @@
     <t xml:space="preserve">1.57528495788574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5212584733963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63357591629028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65916705131531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64779329299927</t>
+    <t xml:space="preserve">1.52125859260559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63357603549957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65916693210602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64779305458069</t>
   </si>
   <si>
     <t xml:space="preserve">1.68760228157043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71461486816406</t>
+    <t xml:space="preserve">1.71461510658264</t>
   </si>
   <si>
     <t xml:space="preserve">1.70608472824097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70039761066437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74447119235992</t>
+    <t xml:space="preserve">1.70039796829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74447166919708</t>
   </si>
   <si>
     <t xml:space="preserve">1.70750641822815</t>
@@ -485,100 +485,100 @@
     <t xml:space="preserve">1.72030210494995</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73167598247528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78285872936249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77859306335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77148425579071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76437568664551</t>
+    <t xml:space="preserve">1.73167586326599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78285896778107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7785929441452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.771484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76437556743622</t>
   </si>
   <si>
     <t xml:space="preserve">1.75584530830383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76295399665833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74162781238556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76864099502563</t>
+    <t xml:space="preserve">1.76295375823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74162793159485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76864075660706</t>
   </si>
   <si>
     <t xml:space="preserve">1.74873650074005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73451912403107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78428030014038</t>
+    <t xml:space="preserve">1.73451924324036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78428018093109</t>
   </si>
   <si>
     <t xml:space="preserve">1.85252356529236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84968030452728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81271517276764</t>
+    <t xml:space="preserve">1.84967994689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81271505355835</t>
   </si>
   <si>
     <t xml:space="preserve">1.83546268939972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84825801849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85963213443756</t>
+    <t xml:space="preserve">1.84825825691223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85963237285614</t>
   </si>
   <si>
     <t xml:space="preserve">1.9477801322937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97621440887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09848403930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10843634605408</t>
+    <t xml:space="preserve">1.97621488571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09848380088806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10843586921692</t>
   </si>
   <si>
     <t xml:space="preserve">2.07573628425598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08568859100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0885317325592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09706234931946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16104102134705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18236708641052</t>
+    <t xml:space="preserve">2.08568835258484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08853197097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09706211090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16104078292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18236684799194</t>
   </si>
   <si>
     <t xml:space="preserve">2.11412310600281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00038385391235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0387716293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00891423225403</t>
+    <t xml:space="preserve">2.00038433074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03877186775208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00891470909119</t>
   </si>
   <si>
     <t xml:space="preserve">2.05298852920532</t>
@@ -587,10 +587,10 @@
     <t xml:space="preserve">2.06294083595276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11554503440857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12549686431885</t>
+    <t xml:space="preserve">2.11554479598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12549710273743</t>
   </si>
   <si>
     <t xml:space="preserve">2.16246247291565</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">2.13260555267334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08142328262329</t>
+    <t xml:space="preserve">2.08142304420471</t>
   </si>
   <si>
     <t xml:space="preserve">2.03592801094055</t>
@@ -614,73 +614,73 @@
     <t xml:space="preserve">2.09990572929382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08995389938354</t>
+    <t xml:space="preserve">2.08995366096497</t>
   </si>
   <si>
     <t xml:space="preserve">2.01033616065979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12407493591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10417103767395</t>
+    <t xml:space="preserve">2.12407517433167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10417079925537</t>
   </si>
   <si>
     <t xml:space="preserve">2.07289290428162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16814970970154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27477979660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37430167198181</t>
+    <t xml:space="preserve">2.16814923286438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27478003501892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37430143356323</t>
   </si>
   <si>
     <t xml:space="preserve">2.26340579986572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23354935646057</t>
+    <t xml:space="preserve">2.23354911804199</t>
   </si>
   <si>
     <t xml:space="preserve">2.27193641662598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23212718963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1781017780304</t>
+    <t xml:space="preserve">2.23212742805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17810153961182</t>
   </si>
   <si>
     <t xml:space="preserve">2.16957116127014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23639225959778</t>
+    <t xml:space="preserve">2.23639273643494</t>
   </si>
   <si>
     <t xml:space="preserve">2.22217488288879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21791005134583</t>
+    <t xml:space="preserve">2.2179102897644</t>
   </si>
   <si>
     <t xml:space="preserve">2.2051146030426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22359681129456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26482748985291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31032299995422</t>
+    <t xml:space="preserve">2.22359657287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26482772827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31032276153564</t>
   </si>
   <si>
     <t xml:space="preserve">2.31743192672729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34302282333374</t>
+    <t xml:space="preserve">2.34302258491516</t>
   </si>
   <si>
     <t xml:space="preserve">2.34160089492798</t>
@@ -692,61 +692,61 @@
     <t xml:space="preserve">2.297527551651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29610562324524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36008381843567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35297536849976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34017968177795</t>
+    <t xml:space="preserve">2.29610586166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36008358001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35297513008118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34017944335938</t>
   </si>
   <si>
     <t xml:space="preserve">2.4027361869812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41695356369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45249652862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41126656532288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41553163528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42406249046326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44396615028381</t>
+    <t xml:space="preserve">2.41695332527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45249676704407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41126680374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.415531873703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42406225204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44396638870239</t>
   </si>
   <si>
     <t xml:space="preserve">2.35439658164978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33733582496643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33022737503052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36434888839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32738399505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28188824653625</t>
+    <t xml:space="preserve">2.33733558654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33022713661194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3643491268158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32738375663757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28188848495483</t>
   </si>
   <si>
     <t xml:space="preserve">2.30037093162537</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32311868667603</t>
+    <t xml:space="preserve">2.32311844825745</t>
   </si>
   <si>
     <t xml:space="preserve">2.33449244499207</t>
@@ -755,49 +755,49 @@
     <t xml:space="preserve">2.30890130996704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29894924163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25629758834839</t>
+    <t xml:space="preserve">2.2989490032196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25629711151123</t>
   </si>
   <si>
     <t xml:space="preserve">2.12834048271179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1340274810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28473234176636</t>
+    <t xml:space="preserve">2.13402724266052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28473162651062</t>
   </si>
   <si>
     <t xml:space="preserve">2.22928404808044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27335786819458</t>
+    <t xml:space="preserve">2.27335834503174</t>
   </si>
   <si>
     <t xml:space="preserve">2.27904486656189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31316661834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33875775337219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37856721878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32880568504333</t>
+    <t xml:space="preserve">2.31316637992859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33875751495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37856698036194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32880544662476</t>
   </si>
   <si>
     <t xml:space="preserve">2.367192029953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34871006011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29468417167664</t>
+    <t xml:space="preserve">2.34870982170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29468393325806</t>
   </si>
   <si>
     <t xml:space="preserve">2.30321455001831</t>
@@ -806,10 +806,10 @@
     <t xml:space="preserve">2.28757524490356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32027506828308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28330993652344</t>
+    <t xml:space="preserve">2.32027554512024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28331017494202</t>
   </si>
   <si>
     <t xml:space="preserve">2.29041862487793</t>
@@ -818,22 +818,22 @@
     <t xml:space="preserve">2.29326224327087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3060576915741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35581851005554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31174468994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3316490650177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46671390533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43117094039917</t>
+    <t xml:space="preserve">2.30605792999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35581827163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31174445152283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33164882659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46671414375305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43117070198059</t>
   </si>
   <si>
     <t xml:space="preserve">2.42974901199341</t>
@@ -842,10 +842,10 @@
     <t xml:space="preserve">2.49799299240112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46387076377869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48661828041077</t>
+    <t xml:space="preserve">2.46387052536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48661804199219</t>
   </si>
   <si>
     <t xml:space="preserve">2.5164749622345</t>
@@ -863,22 +863,22 @@
     <t xml:space="preserve">2.48803973197937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50510120391846</t>
+    <t xml:space="preserve">2.50510144233704</t>
   </si>
   <si>
     <t xml:space="preserve">2.5079448223114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50936627388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5065233707428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55486178398132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5722119808197</t>
+    <t xml:space="preserve">2.50936651229858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50652313232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55486154556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57221221923828</t>
   </si>
   <si>
     <t xml:space="preserve">2.63293862342834</t>
@@ -887,28 +887,28 @@
     <t xml:space="preserve">2.65607309341431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70667862892151</t>
+    <t xml:space="preserve">2.70667839050293</t>
   </si>
   <si>
     <t xml:space="preserve">2.56642889976501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52594375610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52883577346802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47389245033264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52160596847534</t>
+    <t xml:space="preserve">2.52594351768494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52883529663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47389268875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5216064453125</t>
   </si>
   <si>
     <t xml:space="preserve">2.51437664031982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4710009098053</t>
+    <t xml:space="preserve">2.47100067138672</t>
   </si>
   <si>
     <t xml:space="preserve">2.48979711532593</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">2.45654225349426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47967576980591</t>
+    <t xml:space="preserve">2.47967600822449</t>
   </si>
   <si>
     <t xml:space="preserve">2.46087980270386</t>
@@ -932,22 +932,22 @@
     <t xml:space="preserve">2.48112177848816</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45798826217651</t>
+    <t xml:space="preserve">2.45798778533936</t>
   </si>
   <si>
     <t xml:space="preserve">2.48256778717041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4883508682251</t>
+    <t xml:space="preserve">2.48835110664368</t>
   </si>
   <si>
     <t xml:space="preserve">2.48690533638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50859332084656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53751158714294</t>
+    <t xml:space="preserve">2.50859355926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53751134872437</t>
   </si>
   <si>
     <t xml:space="preserve">2.6025755405426</t>
@@ -956,19 +956,19 @@
     <t xml:space="preserve">2.55919933319092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49558043479919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59245419502258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6633026599884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61414265632629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63149261474609</t>
+    <t xml:space="preserve">2.49558067321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59245443344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66330242156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61414241790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63149309158325</t>
   </si>
   <si>
     <t xml:space="preserve">2.6228175163269</t>
@@ -977,10 +977,10 @@
     <t xml:space="preserve">2.61703419685364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72692060470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73704171180725</t>
+    <t xml:space="preserve">2.72692084312439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73704195022583</t>
   </si>
   <si>
     <t xml:space="preserve">2.72258305549622</t>
@@ -989,10 +989,10 @@
     <t xml:space="preserve">2.71246218681335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71390771865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70812392234802</t>
+    <t xml:space="preserve">2.71390795707703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70812439918518</t>
   </si>
   <si>
     <t xml:space="preserve">2.68932819366455</t>
@@ -1004,19 +1004,19 @@
     <t xml:space="preserve">2.6878821849823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7110161781311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65028929710388</t>
+    <t xml:space="preserve">2.71101641654968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65028882026672</t>
   </si>
   <si>
     <t xml:space="preserve">2.67920708656311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67197751998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67053174972534</t>
+    <t xml:space="preserve">2.67197775840759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67053198814392</t>
   </si>
   <si>
     <t xml:space="preserve">2.65318083763123</t>
@@ -1025,58 +1025,58 @@
     <t xml:space="preserve">2.65173482894897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66763997077942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65896487236023</t>
+    <t xml:space="preserve">2.66763973236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65896463394165</t>
   </si>
   <si>
     <t xml:space="preserve">2.64595150947571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59823775291443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62426352500916</t>
+    <t xml:space="preserve">2.59823751449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.624263048172</t>
   </si>
   <si>
     <t xml:space="preserve">2.60402131080627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54474067687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57654976844788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52449798583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48545956611633</t>
+    <t xml:space="preserve">2.54474091529846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57655000686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52449774742126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48545932769775</t>
   </si>
   <si>
     <t xml:space="preserve">2.50281000137329</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52016043663025</t>
+    <t xml:space="preserve">2.52016019821167</t>
   </si>
   <si>
     <t xml:space="preserve">2.51148509979248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.518714427948</t>
+    <t xml:space="preserve">2.51871466636658</t>
   </si>
   <si>
     <t xml:space="preserve">2.53317308425903</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5519700050354</t>
+    <t xml:space="preserve">2.55196976661682</t>
   </si>
   <si>
     <t xml:space="preserve">2.50714755058289</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55052423477173</t>
+    <t xml:space="preserve">2.55052399635315</t>
   </si>
   <si>
     <t xml:space="preserve">2.54618668556213</t>
@@ -1088,16 +1088,16 @@
     <t xml:space="preserve">2.5794415473938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64161372184753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.630047082901</t>
+    <t xml:space="preserve">2.64161396026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63004684448242</t>
   </si>
   <si>
     <t xml:space="preserve">2.58956265449524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52305197715759</t>
+    <t xml:space="preserve">2.52305221557617</t>
   </si>
   <si>
     <t xml:space="preserve">2.51582288742065</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">2.53461885452271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49124312400818</t>
+    <t xml:space="preserve">2.4912428855896</t>
   </si>
   <si>
     <t xml:space="preserve">2.47244668006897</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">2.50425577163696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48401379585266</t>
+    <t xml:space="preserve">2.4840133190155</t>
   </si>
   <si>
     <t xml:space="preserve">2.49413442611694</t>
@@ -1133,16 +1133,16 @@
     <t xml:space="preserve">2.51293110847473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44931292533875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.407381772995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45509624481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41027355194092</t>
+    <t xml:space="preserve">2.44931268692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40738201141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45509576797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41027331352234</t>
   </si>
   <si>
     <t xml:space="preserve">2.29605031013489</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">2.28159070014954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18471789360046</t>
+    <t xml:space="preserve">2.18471765518188</t>
   </si>
   <si>
     <t xml:space="preserve">2.19773054122925</t>
@@ -1163,43 +1163,43 @@
     <t xml:space="preserve">2.22086429595947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26279473304749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28448271751404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28592848777771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32496738433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34810137748718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37846446037292</t>
+    <t xml:space="preserve">2.26279449462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28448247909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28592824935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32496762275696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34810161590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37846493721008</t>
   </si>
   <si>
     <t xml:space="preserve">2.41461181640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34231781959534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35677695274353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35966873168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34087204933167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37701845169067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39292359352112</t>
+    <t xml:space="preserve">2.34231805801392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35677671432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35966825485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34087228775024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37701892852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39292335510254</t>
   </si>
   <si>
     <t xml:space="preserve">2.40015268325806</t>
@@ -1208,10 +1208,10 @@
     <t xml:space="preserve">2.4059362411499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33653473854065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29315781593323</t>
+    <t xml:space="preserve">2.33653450012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29315757751465</t>
   </si>
   <si>
     <t xml:space="preserve">2.20495986938477</t>
@@ -1220,49 +1220,49 @@
     <t xml:space="preserve">2.23966073989868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23821473121643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23387718200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18327164649963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21797251701355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24544405937195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20062232017517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2266480922699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28303694725037</t>
+    <t xml:space="preserve">2.23821496963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23387742042542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18327212333679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21797275543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24544382095337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20062208175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22664761543274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28303670883179</t>
   </si>
   <si>
     <t xml:space="preserve">2.31340050697327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3105092048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38858580589294</t>
+    <t xml:space="preserve">2.31050872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38858556747437</t>
   </si>
   <si>
     <t xml:space="preserve">2.38713979721069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34665584564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34520959854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36545157432556</t>
+    <t xml:space="preserve">2.34665560722351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34520936012268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36545181274414</t>
   </si>
   <si>
     <t xml:space="preserve">2.39436912536621</t>
@@ -1277,7 +1277,7 @@
     <t xml:space="preserve">2.32785940170288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34954738616943</t>
+    <t xml:space="preserve">2.34954690933228</t>
   </si>
   <si>
     <t xml:space="preserve">2.33364295959473</t>
@@ -1286,28 +1286,28 @@
     <t xml:space="preserve">2.31195473670959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22953963279724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31484651565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30327963829041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32062983512878</t>
+    <t xml:space="preserve">2.22953987121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31484627723694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30327939987183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32063007354736</t>
   </si>
   <si>
     <t xml:space="preserve">2.3076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37268137931824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42907071113586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36400580406189</t>
+    <t xml:space="preserve">2.37268114089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42907047271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36400604248047</t>
   </si>
   <si>
     <t xml:space="preserve">2.31629228591919</t>
@@ -1316,10 +1316,10 @@
     <t xml:space="preserve">2.35388493537903</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27725315093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32930493354797</t>
+    <t xml:space="preserve">2.27725338935852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32930517196655</t>
   </si>
   <si>
     <t xml:space="preserve">2.30617117881775</t>
@@ -1328,13 +1328,13 @@
     <t xml:space="preserve">2.30038785934448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37412691116333</t>
+    <t xml:space="preserve">2.37412714958191</t>
   </si>
   <si>
     <t xml:space="preserve">2.33075094223022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32641363143921</t>
+    <t xml:space="preserve">2.32641339302063</t>
   </si>
   <si>
     <t xml:space="preserve">2.39726066589355</t>
@@ -1349,43 +1349,43 @@
     <t xml:space="preserve">2.60112977027893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71969151496887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70957040786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75439214706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77752685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84837436676025</t>
+    <t xml:space="preserve">2.71969127655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70957016944885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75439238548279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77752661705017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84837412834167</t>
   </si>
   <si>
     <t xml:space="preserve">2.84114503860474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83391547203064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86861634254456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90042591094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82957816123962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73125815391541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78620171546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75583791732788</t>
+    <t xml:space="preserve">2.83391523361206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86861610412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90042614936829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82957792282104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73125839233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78620195388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75583815574646</t>
   </si>
   <si>
     <t xml:space="preserve">2.82524037361145</t>
@@ -1394,112 +1394,112 @@
     <t xml:space="preserve">2.80644416809082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83680748939514</t>
+    <t xml:space="preserve">2.83680725097656</t>
   </si>
   <si>
     <t xml:space="preserve">2.74716281890869</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7384877204895</t>
+    <t xml:space="preserve">2.73848724365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63438439369202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66091990470886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65060067176819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71251726150513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70367121696472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63143634796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52824234962463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48254251480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52234578132629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56509733200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6107976436615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57689046859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51939725875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59163331985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.618168592453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59015893936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54888129234314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5606746673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55625200271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54593253135681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57099366188049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51350092887878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51055216789246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53708744049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54150986671448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65354871749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65944576263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70514535903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6904034614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65797162055969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61964273452759</t>
   </si>
   <si>
     <t xml:space="preserve">2.6343846321106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66092014312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65060067176819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71251702308655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70367097854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63143610954285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52824234962463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4825427532196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52234530448914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56509709358215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61079788208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57689046859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51939749717712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59163308143616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61816835403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59015917778015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54888105392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5606746673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55625200271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54593276977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57099413871765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51350069046021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51055240631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5370876789093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54151010513306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65354895591736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65944576263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70514559745789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6904034614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65797138214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61964273452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63438439369202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63291025161743</t>
+    <t xml:space="preserve">2.63291049003601</t>
   </si>
   <si>
     <t xml:space="preserve">2.64912629127502</t>
@@ -1511,16 +1511,16 @@
     <t xml:space="preserve">2.6653425693512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64470410346985</t>
+    <t xml:space="preserve">2.64470362663269</t>
   </si>
   <si>
     <t xml:space="preserve">2.63880705833435</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66386842727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71399140357971</t>
+    <t xml:space="preserve">2.66386818885803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71399116516113</t>
   </si>
   <si>
     <t xml:space="preserve">2.73168134689331</t>
@@ -1529,22 +1529,22 @@
     <t xml:space="preserve">2.71693968772888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73315572738647</t>
+    <t xml:space="preserve">2.7331554889679</t>
   </si>
   <si>
     <t xml:space="preserve">2.78180360794067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70661950111389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69187784194946</t>
+    <t xml:space="preserve">2.70661973953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69187808036804</t>
   </si>
   <si>
     <t xml:space="preserve">2.68892931938171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67713594436646</t>
+    <t xml:space="preserve">2.67713570594788</t>
   </si>
   <si>
     <t xml:space="preserve">2.64617800712585</t>
@@ -1553,25 +1553,25 @@
     <t xml:space="preserve">2.64175534248352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57541608810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61374568939209</t>
+    <t xml:space="preserve">2.57541632652283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61374616622925</t>
   </si>
   <si>
     <t xml:space="preserve">2.60932326316833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58868455886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58131313323975</t>
+    <t xml:space="preserve">2.58868479728699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58131289482117</t>
   </si>
   <si>
     <t xml:space="preserve">2.53561329841614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48843955993652</t>
+    <t xml:space="preserve">2.4884397983551</t>
   </si>
   <si>
     <t xml:space="preserve">2.47222328186035</t>
@@ -1580,7 +1580,7 @@
     <t xml:space="preserve">2.50170707702637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56362295150757</t>
+    <t xml:space="preserve">2.56362271308899</t>
   </si>
   <si>
     <t xml:space="preserve">2.67123913764954</t>
@@ -1595,61 +1595,61 @@
     <t xml:space="preserve">2.68450689315796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66239404678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6240656375885</t>
+    <t xml:space="preserve">2.66239380836487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62406539916992</t>
   </si>
   <si>
     <t xml:space="preserve">2.62996196746826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63733315467834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62111663818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42210054397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41915225982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36608123779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38966846466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41325521469116</t>
+    <t xml:space="preserve">2.63733291625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62111687660217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42210030555725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41915202140808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36608147621155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38966822624207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41325545310974</t>
   </si>
   <si>
     <t xml:space="preserve">2.33659672737122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24667167663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23045563697815</t>
+    <t xml:space="preserve">2.24667143821716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23045539855957</t>
   </si>
   <si>
     <t xml:space="preserve">2.22898149490356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16706490516663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18033266067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15674567222595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2024450302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19360041618347</t>
+    <t xml:space="preserve">2.16706466674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18033242225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15674543380737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20244550704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19360017776489</t>
   </si>
   <si>
     <t xml:space="preserve">2.13905549049377</t>
@@ -1658,13 +1658,13 @@
     <t xml:space="preserve">2.11399412155151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08745837211609</t>
+    <t xml:space="preserve">2.08745789527893</t>
   </si>
   <si>
     <t xml:space="preserve">2.0417582988739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00932621955872</t>
+    <t xml:space="preserve">2.00932645797729</t>
   </si>
   <si>
     <t xml:space="preserve">2.05207777023315</t>
@@ -1676,13 +1676,13 @@
     <t xml:space="preserve">2.05797457695007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05502581596375</t>
+    <t xml:space="preserve">2.0550262928009</t>
   </si>
   <si>
     <t xml:space="preserve">2.09335565567017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13610696792603</t>
+    <t xml:space="preserve">2.1361072063446</t>
   </si>
   <si>
     <t xml:space="preserve">2.11694240570068</t>
@@ -1694,16 +1694,16 @@
     <t xml:space="preserve">2.10220074653625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10072636604309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09040641784668</t>
+    <t xml:space="preserve">2.10072660446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09040665626526</t>
   </si>
   <si>
     <t xml:space="preserve">2.04912924766541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06829357147217</t>
+    <t xml:space="preserve">2.06829380989075</t>
   </si>
   <si>
     <t xml:space="preserve">2.05060315132141</t>
@@ -1712,7 +1712,7 @@
     <t xml:space="preserve">2.04765510559082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02701616287231</t>
+    <t xml:space="preserve">2.02701663970947</t>
   </si>
   <si>
     <t xml:space="preserve">2.01964569091797</t>
@@ -1724,19 +1724,19 @@
     <t xml:space="preserve">1.97984254360199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96215176582336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98426520824432</t>
+    <t xml:space="preserve">1.96215164661407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98426532745361</t>
   </si>
   <si>
     <t xml:space="preserve">2.08008742332458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06387090682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07861304283142</t>
+    <t xml:space="preserve">2.06387114524841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07861280441284</t>
   </si>
   <si>
     <t xml:space="preserve">2.04618096351624</t>
@@ -1745,49 +1745,49 @@
     <t xml:space="preserve">2.08598375320435</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05650019645691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95625507831573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98279082775116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94446134567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93709027767181</t>
+    <t xml:space="preserve">2.05650043487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95625495910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98279106616974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94446122646332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93709051609039</t>
   </si>
   <si>
     <t xml:space="preserve">1.96657419204712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96804857254028</t>
+    <t xml:space="preserve">1.9680483341217</t>
   </si>
   <si>
     <t xml:space="preserve">1.89286482334137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98131656646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91497766971588</t>
+    <t xml:space="preserve">1.98131668567657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91497755050659</t>
   </si>
   <si>
     <t xml:space="preserve">1.87517464160919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8737006187439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94003891944885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92677116394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99311006069183</t>
+    <t xml:space="preserve">1.87370073795319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94003868103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92677128314972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9931104183197</t>
   </si>
   <si>
     <t xml:space="preserve">2.0034294128418</t>
@@ -1796,16 +1796,16 @@
     <t xml:space="preserve">1.99458456039429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99163627624512</t>
+    <t xml:space="preserve">1.99163615703583</t>
   </si>
   <si>
     <t xml:space="preserve">1.94888401031494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88844239711761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87222623825073</t>
+    <t xml:space="preserve">1.8884425163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8722265958786</t>
   </si>
   <si>
     <t xml:space="preserve">1.91940033435822</t>
@@ -1814,7 +1814,7 @@
     <t xml:space="preserve">1.89433908462524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86485552787781</t>
+    <t xml:space="preserve">1.86485540866852</t>
   </si>
   <si>
     <t xml:space="preserve">1.85306203365326</t>
@@ -1823,25 +1823,25 @@
     <t xml:space="preserve">1.83831918239594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88549423217773</t>
+    <t xml:space="preserve">1.88549435138702</t>
   </si>
   <si>
     <t xml:space="preserve">1.85158777236938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8250515460968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78230035305023</t>
+    <t xml:space="preserve">1.82505166530609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78230047225952</t>
   </si>
   <si>
     <t xml:space="preserve">1.71596121788025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69532263278961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71006453037262</t>
+    <t xml:space="preserve">1.6953227519989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71006464958191</t>
   </si>
   <si>
     <t xml:space="preserve">1.73217809200287</t>
@@ -1850,25 +1850,25 @@
     <t xml:space="preserve">1.78377437591553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76313591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76166176795959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78672289848328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80588722229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83389663696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87664890289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86927807331085</t>
+    <t xml:space="preserve">1.76313579082489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76166164875031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78672301769257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80588710308075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83389675617218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87664914131165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86927771568298</t>
   </si>
   <si>
     <t xml:space="preserve">1.84569013118744</t>
@@ -1877,43 +1877,43 @@
     <t xml:space="preserve">1.83979368209839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8324226140976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84274172782898</t>
+    <t xml:space="preserve">1.83242237567902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84274184703827</t>
   </si>
   <si>
     <t xml:space="preserve">1.83684504032135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8972874879837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88991665840149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88254547119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91055524349213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87075197696686</t>
+    <t xml:space="preserve">1.89728736877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88991677761078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88254582881927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91055500507355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87075209617615</t>
   </si>
   <si>
     <t xml:space="preserve">1.80293881893158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80441296100616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79114544391632</t>
+    <t xml:space="preserve">1.80441308021545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79114532470703</t>
   </si>
   <si>
     <t xml:space="preserve">1.75576496124268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81325805187225</t>
+    <t xml:space="preserve">1.81325840950012</t>
   </si>
   <si>
     <t xml:space="preserve">1.81178390979767</t>
@@ -1922,1093 +1922,1093 @@
     <t xml:space="preserve">1.83537089824677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79556798934937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77492928504944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80883550643921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79851615428925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79704236984253</t>
+    <t xml:space="preserve">1.79556787014008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77492940425873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8088356256485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79851627349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79704201221466</t>
   </si>
   <si>
     <t xml:space="preserve">1.8073616027832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78082633018494</t>
+    <t xml:space="preserve">1.78082609176636</t>
   </si>
   <si>
     <t xml:space="preserve">1.7542906999588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71301293373108</t>
+    <t xml:space="preserve">1.71301281452179</t>
   </si>
   <si>
     <t xml:space="preserve">1.70711624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74544560909271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76460993289948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77198100090027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77787756919861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78819680213928</t>
+    <t xml:space="preserve">1.745445728302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76461005210876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77198088169098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7778776884079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78819715976715</t>
   </si>
   <si>
     <t xml:space="preserve">1.74839401245117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6658388376236</t>
+    <t xml:space="preserve">1.66583871841431</t>
   </si>
   <si>
     <t xml:space="preserve">1.67910647392273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61129403114319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57886135578156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53610992431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55822265148163</t>
+    <t xml:space="preserve">1.6112939119339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57886111736298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53610980510712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55822253227234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54200649261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53445518016815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53596556186676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56466102600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54351699352264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55559897422791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5389860868454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54502737522125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60543859004974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58429443836212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56768143177032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56919169425964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58882534503937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51029002666473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51935243606567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52690386772156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4717777967453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47026753425598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.471022605896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45138907432556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46875715255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49367690086365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48386001586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50047314167023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45894050598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46800208091736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48990118503571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48234975337982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48083961009979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53294491767883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57523274421692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56315064430237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52539348602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50424873828888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47328805923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4725329875946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44912350177765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4536544084549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46649169921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44987881183624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44610285758972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43779647350311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42269361019135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4204283952713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4272243976593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41665256023407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40683567523956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40079462528229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39097774028778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38644623756409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28374695777893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25354063510895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25127518177032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20068073272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23617231845856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25278544425964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22182464599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2308863401413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27695071697235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26637864112854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27619564533234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31395268440247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27090954780579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28223657608032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28752279281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35775065422058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38342559337616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37436389923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35246479511261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40985631942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39852929115295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36681246757507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35095453262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35926103591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36454701423645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33736193180084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30262541770935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2897881269455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26109278202057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26864409446716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25505077838898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27468538284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27997124195099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25958168506622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25429558753967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26939928531647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28148150444031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30413579940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33660686016083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36077117919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38871228694916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38267028331757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3517097234726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35699558258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36152648925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36228156089783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34113764762878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36756753921509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42495894432068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41740763187408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43326568603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40532553195953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43477594852448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62960290908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58278405666351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57825350761414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58127403259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54653751850128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53747582435608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52237284183502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55257844924927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60241782665253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63111317157745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60090780258179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62054133415222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54955804347992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57221221923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61147952079773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64168584346771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61298990249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.617520570755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59184610843658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58731520175934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6190310716629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57976365089417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56013011932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55861973762512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59788703918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60392820835114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58580470085144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59939730167389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59637677669525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59033560752869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5299243927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51331126689911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50953483581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52388334274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54049634933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63866460323334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75948786735535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80630731582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78365325927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83953356742859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02983069419861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06909799575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94827461242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89088308811188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7791223526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77308118343353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81687951087952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70813846588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4800843000412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37511909008026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3245245218277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24070310592651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19917047023773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18406772613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959789395332336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995280861854553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919011652469635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945441544055939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962809801101685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01869094371796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04361069202423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990750193595886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07155084609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07910239696503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06777513027191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01944613456726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999811708927155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0413453578949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02699756622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10628747940063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05720329284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11459398269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13875913619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20219111442566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16745448112488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16594421863556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08740878105164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06701993942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09420502185822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06324422359467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09496021270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07834708690643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08212292194366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07457137107849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08665382862091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09269487857819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03756964206696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07306122779846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04965174198151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03530418872833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04436588287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04285562038422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01189470291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985464096069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970361292362213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989239871501923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94317615032196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926563143730164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921277046203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913725674152374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986219227313995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997546255588531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.058713555336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09722566604614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1025116443634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13422763347626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18180227279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21502840518951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23919296264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19992554187775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18935358524323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14782083034515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16820979118347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18708825111389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16216850280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19312930107117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17047512531281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24598920345306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29280865192413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36303675174713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40381515026093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41136646270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39399826526642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39928424358368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4015496969223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40306007862091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41589748859406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49292171001434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44836843013763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48763561248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47630870342255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46498155593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39626371860504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37662923336029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3426479101181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36907780170441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43175542354584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.445347905159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47479844093323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48461508750916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55106842517853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52086269855499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37889468669891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37813949584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34415817260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37209844589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39475321769714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37964987754822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38795721530914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39248788356781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32150399684906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31848347187042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34340310096741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30035996437073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32376933097839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33434164524078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39777386188507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.369833111763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38191533088684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34038245677948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35473012924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31772828102112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33207607269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33585166931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.273930311203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26486837863922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22484505176544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24145829677582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11761462688446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10779750347137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13800394535065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22711062431335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24221348762512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23843765258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22862100601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44232738018036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43251049518585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50273859500885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55408895015717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81234848499298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78214311599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77459144592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75797772407532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69303548336029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72173118591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68548405170441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70209729671478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70360743999481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73079264163971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72777199745178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69907653331757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6688711643219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66282999515533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67944300174713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66131961345673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67642247676849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64470648765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61601042747498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63564395904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6582989692688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66585063934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66434013843536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74438512325287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77761209011078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.756467461586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72022068500519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73683381080627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69454574584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65225791931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67491233348846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65376818180084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63715434074402</t>
   </si>
   <si>
     <t xml:space="preserve">1.54200661182404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53445518016815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53596556186676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56466102600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54351699352264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55559909343719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5389860868454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54502713680267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60543847084045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58429443836212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56768143177032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56919169425964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58882546424866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51028990745544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51935231685638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52690386772156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47177791595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47026753425598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.471022605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45138895511627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46875739097595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49367666244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48386001586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50047314167023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45894038677216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46800208091736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.489901304245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48234975337982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4808394908905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53294503688812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57523286342621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56315052509308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52539360523224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50424873828888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47328805923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47253286838531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44912362098694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45365428924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46649181842804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44987881183624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44610297679901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43779647350311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42269372940063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42042827606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42722451686859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41665256023407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40683567523956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40079438686371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39097774028778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38644623756409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28374683856964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25354063510895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25127506256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20068073272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23617243766785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25278532505035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22182464599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23088645935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27695071697235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26637876033783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27619564533234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31395256519318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2709094285965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28223657608032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28752267360687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35775065422058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38342559337616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37436389923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35246467590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40985631942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39852917194366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36681246757507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.350954413414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35926103591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36454701423645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33736205101013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30262541770935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2897881269455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26109266281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26864421367645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25505077838898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27468526363373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27997124195099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25958156585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25429570674896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26939916610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28148150444031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30413579940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33660662174225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36077129840851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38871240615845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38267040252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3517097234726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35699570178986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36152648925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36228168010712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34113764762878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36756765842438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42495894432068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41740763187408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43326568603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40532541275024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43477582931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62960290908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5827841758728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57825350761414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58127391338348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54653751850128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53747594356537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52237284183502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55257868766785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60241782665253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63111340999603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6009076833725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62054133415222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54955792427063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57221233844757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61147952079773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64168620109558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61298990249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61752080917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59184598922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58731520175934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6190310716629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57976365089417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56013000011444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55861973762512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59788691997528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60392808914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58580493927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59939742088318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59637677669525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59033560752869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52992451190948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5133113861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50953483581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52388322353363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54049623012543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63866472244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75948810577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80630743503571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78365314006805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8395334482193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02983093261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06909823417664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94827485084534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89088320732117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77912259101868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77308106422424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81687951087952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70813846588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4800843000412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37511885166168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3245245218277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24070310592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19917058944702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18406760692596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959789276123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995281040668488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919011771678925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945441603660583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962809860706329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01869106292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04361057281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990750074386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07155084609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07910239696503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0677752494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01944613456726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999811708927155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0413453578949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02699756622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10628736019135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05720329284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11459386348724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13875913619995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20219099521637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16745460033417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16594421863556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08740890026093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06701993942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09420502185822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06324434280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09496033191681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07834708690643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08212292194366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07457137107849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08665370941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09269487857819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03756952285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07306110858917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04965174198151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03530406951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04436588287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04285550117493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01189482212067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985464036464691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970361292362213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989239692687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943176209926605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926563084125519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921276986598969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913725733757019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98621928691864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997546315193176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05871343612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09722566604614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10251140594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13422751426697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18180215358734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21502840518951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23919296264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19992554187775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18935370445251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14782094955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16820967197418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1870881319046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16216850280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19312930107117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17047512531281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24598908424377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29280865192413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36303675174713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40381503105164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41136646270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39399814605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39928424358368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40154981613159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40306007862091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41589736938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49292182922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44836831092834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48763585090637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47630858421326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46498155593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39626383781433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37662923336029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3426479101181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36907804012299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43175530433655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.445347905159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47479832172394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48461532592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55106842517853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5208625793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37889456748962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37813949584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34415817260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37209844589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39475333690643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37964999675751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38795709609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3924880027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32150399684906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31848347187042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34340310096741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30036008358002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32376933097839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3343414068222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39777398109436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36983299255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38191521167755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34038257598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35473024845123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31772840023041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33207607269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33585166931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27393019199371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26486849784851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22484517097473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24145841598511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11761450767517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10779762268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13800406455994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22711062431335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24221336841583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23843777179718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22862088680267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44232726097107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43251037597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50273859500885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55408895015717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81234872341156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78214299678802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77459168434143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75797772407532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69303548336029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7217310667038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68548405170441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70209729671478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7036075592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.730792760849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72777223587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69907677173615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6688711643219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66282975673676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67944324016571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66131973266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67642259597778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64470660686493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61601042747498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63564395904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65829920768738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66585063934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66434013843536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74438524246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77761197090149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.756467461586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7202205657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73683369159698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69454574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65225791931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67491221427917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65376830101013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63715422153473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54200649261475</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.57070183753967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59486651420593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62205147743225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74740552902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88635241985321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85765695571899</t>
+    <t xml:space="preserve">1.59486663341522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62205159664154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74740564823151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88635230064392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85765719413757</t>
   </si>
   <si>
     <t xml:space="preserve">1.88031125068665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86822891235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85463654994965</t>
+    <t xml:space="preserve">1.86822903156281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85463666915894</t>
   </si>
   <si>
     <t xml:space="preserve">1.88937294483185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8501056432724</t>
+    <t xml:space="preserve">1.85010552406311</t>
   </si>
   <si>
     <t xml:space="preserve">1.80932819843292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83047223091125</t>
+    <t xml:space="preserve">1.83047199249268</t>
   </si>
   <si>
     <t xml:space="preserve">1.82141017913818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81838965415955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82594108581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80781781673431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80177652835846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84557473659515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83500277996063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82745146751404</t>
+    <t xml:space="preserve">1.81838977336884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82594120502472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80781769752502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80177640914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84557497501373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83500266075134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82745134830475</t>
   </si>
   <si>
     <t xml:space="preserve">1.87124967575073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86369800567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92713105678558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97999060153961</t>
+    <t xml:space="preserve">1.86369824409485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92713069915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97999036312103</t>
   </si>
   <si>
     <t xml:space="preserve">2.05399513244629</t>
@@ -3017,13 +3017,13 @@
     <t xml:space="preserve">2.13706064224243</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18085932731628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15216398239136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12950897216797</t>
+    <t xml:space="preserve">2.18085956573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15216422080994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12950921058655</t>
   </si>
   <si>
     <t xml:space="preserve">2.1068549156189</t>
@@ -3032,7 +3032,7 @@
     <t xml:space="preserve">2.15518474578857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1355504989624</t>
+    <t xml:space="preserve">2.13555026054382</t>
   </si>
   <si>
     <t xml:space="preserve">2.13857102394104</t>
@@ -3041,13 +3041,13 @@
     <t xml:space="preserve">2.22465777397156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15669512748718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18992137908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18690085411072</t>
+    <t xml:space="preserve">2.1566948890686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18992114067078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18690061569214</t>
   </si>
   <si>
     <t xml:space="preserve">2.16877722740173</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">2.17028784751892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23522973060608</t>
+    <t xml:space="preserve">2.23522996902466</t>
   </si>
   <si>
     <t xml:space="preserve">2.24731206893921</t>
@@ -3065,13 +3065,13 @@
     <t xml:space="preserve">2.26996684074402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30168294906616</t>
+    <t xml:space="preserve">2.30168271064758</t>
   </si>
   <si>
     <t xml:space="preserve">2.23673987388611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24580192565918</t>
+    <t xml:space="preserve">2.2458016872406</t>
   </si>
   <si>
     <t xml:space="preserve">2.24882221221924</t>
@@ -3086,13 +3086,13 @@
     <t xml:space="preserve">2.48140716552734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54937052726746</t>
+    <t xml:space="preserve">2.54937076568604</t>
   </si>
   <si>
     <t xml:space="preserve">2.64300799369812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61733317375183</t>
+    <t xml:space="preserve">2.61733293533325</t>
   </si>
   <si>
     <t xml:space="preserve">2.60223054885864</t>
@@ -3104,19 +3104,19 @@
     <t xml:space="preserve">2.73815655708313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78648638725281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88616466522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86502075195312</t>
+    <t xml:space="preserve">2.78648614883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88616490364075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8650209903717</t>
   </si>
   <si>
     <t xml:space="preserve">2.86200022697449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94204592704773</t>
+    <t xml:space="preserve">2.94204616546631</t>
   </si>
   <si>
     <t xml:space="preserve">2.94506645202637</t>
@@ -3125,10 +3125,10 @@
     <t xml:space="preserve">2.93147397041321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97980308532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96621060371399</t>
+    <t xml:space="preserve">2.97980332374573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96621036529541</t>
   </si>
   <si>
     <t xml:space="preserve">2.9571487903595</t>
@@ -3140,19 +3140,19 @@
     <t xml:space="preserve">3.08411288261414</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07337760925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05804061889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15312528610229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09178066253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11478519439697</t>
+    <t xml:space="preserve">3.07337737083435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05804085731506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15312552452087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0917809009552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11478495597839</t>
   </si>
   <si>
     <t xml:space="preserve">3.19299960136414</t>
@@ -3161,7 +3161,7 @@
     <t xml:space="preserve">3.21600413322449</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18839836120605</t>
+    <t xml:space="preserve">3.18839812278748</t>
   </si>
   <si>
     <t xml:space="preserve">3.17459583282471</t>
@@ -3170,16 +3170,16 @@
     <t xml:space="preserve">3.12858748435974</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06264162063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98749446868896</t>
+    <t xml:space="preserve">3.06264138221741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98749470710754</t>
   </si>
   <si>
     <t xml:space="preserve">2.96602392196655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95988941192627</t>
+    <t xml:space="preserve">2.95988965034485</t>
   </si>
   <si>
     <t xml:space="preserve">2.9445526599884</t>
@@ -3194,61 +3194,61 @@
     <t xml:space="preserve">2.83106517791748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80192589759827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80039238929749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73598027229309</t>
+    <t xml:space="preserve">2.80192565917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80039262771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73598051071167</t>
   </si>
   <si>
     <t xml:space="preserve">2.7942578792572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79272437095642</t>
+    <t xml:space="preserve">2.79272413253784</t>
   </si>
   <si>
     <t xml:space="preserve">2.83719968795776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76665282249451</t>
+    <t xml:space="preserve">2.76665258407593</t>
   </si>
   <si>
     <t xml:space="preserve">2.80499291419983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79119062423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85713672637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78198885917664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75131678581238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72371196746826</t>
+    <t xml:space="preserve">2.79119038581848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85713648796082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78198909759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7513165473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72371172904968</t>
   </si>
   <si>
     <t xml:space="preserve">2.84333419799805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7957911491394</t>
+    <t xml:space="preserve">2.79579138755798</t>
   </si>
   <si>
     <t xml:space="preserve">2.77892160415649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72524499893188</t>
+    <t xml:space="preserve">2.72524523735046</t>
   </si>
   <si>
     <t xml:space="preserve">2.67310166358948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58108496665955</t>
+    <t xml:space="preserve">2.58108472824097</t>
   </si>
   <si>
     <t xml:space="preserve">2.66543364524841</t>
@@ -3275,10 +3275,10 @@
     <t xml:space="preserve">2.90774583816528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85100197792053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86020398139954</t>
+    <t xml:space="preserve">2.85100221633911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86020374298096</t>
   </si>
   <si>
     <t xml:space="preserve">2.85867023468018</t>
@@ -3287,34 +3287,34 @@
     <t xml:space="preserve">2.83873343467712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84486770629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91848111152649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95222115516663</t>
+    <t xml:space="preserve">2.84486746788025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91848087310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95222163200378</t>
   </si>
   <si>
     <t xml:space="preserve">2.90467858314514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96755743026733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92768263816833</t>
+    <t xml:space="preserve">2.96755790710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92768287658691</t>
   </si>
   <si>
     <t xml:space="preserve">2.92461562156677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83566617965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86173748970032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84640145301819</t>
+    <t xml:space="preserve">2.83566641807556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8617377281189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84640121459961</t>
   </si>
   <si>
     <t xml:space="preserve">2.87860727310181</t>
@@ -3323,7 +3323,7 @@
     <t xml:space="preserve">2.89854431152344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99976372718811</t>
+    <t xml:space="preserve">2.99976348876953</t>
   </si>
   <si>
     <t xml:space="preserve">3.0074315071106</t>
@@ -3338,13 +3338,13 @@
     <t xml:space="preserve">2.95375514030457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99056148529053</t>
+    <t xml:space="preserve">2.99056172370911</t>
   </si>
   <si>
     <t xml:space="preserve">2.93688440322876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95682215690613</t>
+    <t xml:space="preserve">2.95682191848755</t>
   </si>
   <si>
     <t xml:space="preserve">2.90007781982422</t>
@@ -3371,13 +3371,13 @@
     <t xml:space="preserve">2.70224118232727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70530843734741</t>
+    <t xml:space="preserve">2.70530819892883</t>
   </si>
   <si>
     <t xml:space="preserve">2.79732513427734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80652666091919</t>
+    <t xml:space="preserve">2.80652689933777</t>
   </si>
   <si>
     <t xml:space="preserve">2.81419491767883</t>
@@ -3386,25 +3386,25 @@
     <t xml:space="preserve">2.78045535087585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82646441459656</t>
+    <t xml:space="preserve">2.82646465301514</t>
   </si>
   <si>
     <t xml:space="preserve">2.84793496131897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82339715957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93075013160706</t>
+    <t xml:space="preserve">2.823397397995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93074989318848</t>
   </si>
   <si>
     <t xml:space="preserve">2.90314507484436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88320827484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86633849143982</t>
+    <t xml:space="preserve">2.88320803642273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86633825302124</t>
   </si>
   <si>
     <t xml:space="preserve">2.87554001808167</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">2.97522568702698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98902821540833</t>
+    <t xml:space="preserve">2.98902797698975</t>
   </si>
   <si>
     <t xml:space="preserve">2.95068788528442</t>
@@ -3431,7 +3431,7 @@
     <t xml:space="preserve">3.02890205383301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03656983375549</t>
+    <t xml:space="preserve">3.03657007217407</t>
   </si>
   <si>
     <t xml:space="preserve">2.92001485824585</t>
@@ -3458,7 +3458,7 @@
     <t xml:space="preserve">2.85560321807861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80806064605713</t>
+    <t xml:space="preserve">2.80806040763855</t>
   </si>
   <si>
     <t xml:space="preserve">2.76205205917358</t>
@@ -3470,28 +3470,28 @@
     <t xml:space="preserve">2.69917392730713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70684194564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66083288192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76051807403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71144270896912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58875298500061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73137974739075</t>
+    <t xml:space="preserve">2.70684170722961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66083264350891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76051831245422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7114429473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58875274658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73137950897217</t>
   </si>
   <si>
     <t xml:space="preserve">2.62249255180359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65009760856628</t>
+    <t xml:space="preserve">2.65009737014771</t>
   </si>
   <si>
     <t xml:space="preserve">2.6777024269104</t>
@@ -3512,19 +3512,19 @@
     <t xml:space="preserve">2.69610667228699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66850066184998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75438380241394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82493090629578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85406947135925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89701056480408</t>
+    <t xml:space="preserve">2.66850113868713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75438404083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8249306678772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85406970977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89701080322266</t>
   </si>
   <si>
     <t xml:space="preserve">2.97829294204712</t>
@@ -3533,25 +3533,25 @@
     <t xml:space="preserve">2.86327123641968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94148540496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03503680229187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02736854553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89087629318237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74058151245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7850558757782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86480450630188</t>
+    <t xml:space="preserve">2.94148564338684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03503656387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02736830711365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89087605476379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74058127403259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78505611419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86480474472046</t>
   </si>
   <si>
     <t xml:space="preserve">2.82799816131592</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">2.92445588111877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90142869949341</t>
+    <t xml:space="preserve">2.90142893791199</t>
   </si>
   <si>
     <t xml:space="preserve">3.05187320709229</t>
@@ -3572,7 +3572,7 @@
     <t xml:space="preserve">3.07029485702515</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15472841262817</t>
+    <t xml:space="preserve">3.15472817420959</t>
   </si>
   <si>
     <t xml:space="preserve">3.08871674537659</t>
@@ -3581,7 +3581,7 @@
     <t xml:space="preserve">3.19771218299866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21459889411926</t>
+    <t xml:space="preserve">3.21459913253784</t>
   </si>
   <si>
     <t xml:space="preserve">3.18850111961365</t>
@@ -3590,7 +3590,7 @@
     <t xml:space="preserve">3.2529776096344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16547441482544</t>
+    <t xml:space="preserve">3.16547417640686</t>
   </si>
   <si>
     <t xml:space="preserve">3.09485745429993</t>
@@ -3602,10 +3602,10 @@
     <t xml:space="preserve">2.80010914802551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84769868850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72028112411499</t>
+    <t xml:space="preserve">2.8476984500885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72028136253357</t>
   </si>
   <si>
     <t xml:space="preserve">2.55602025985718</t>
@@ -3617,55 +3617,55 @@
     <t xml:space="preserve">2.54066896438599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25359630584717</t>
+    <t xml:space="preserve">2.25359654426575</t>
   </si>
   <si>
     <t xml:space="preserve">2.24592089653015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33342409133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5345287322998</t>
+    <t xml:space="preserve">2.33342432975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53452849388123</t>
   </si>
   <si>
     <t xml:space="preserve">2.40557622909546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42860317230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5299232006073</t>
+    <t xml:space="preserve">2.42860341072083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52992296218872</t>
   </si>
   <si>
     <t xml:space="preserve">2.56983685493469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75098443031311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7248866558075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76326537132263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78015208244324</t>
+    <t xml:space="preserve">2.75098419189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72488689422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76326560974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78015232086182</t>
   </si>
   <si>
     <t xml:space="preserve">2.82927680015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79550337791443</t>
+    <t xml:space="preserve">2.79550361633301</t>
   </si>
   <si>
     <t xml:space="preserve">2.79243326187134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73870325088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79703855514526</t>
+    <t xml:space="preserve">2.73870301246643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79703879356384</t>
   </si>
   <si>
     <t xml:space="preserve">2.92292094230652</t>
@@ -3677,13 +3677,13 @@
     <t xml:space="preserve">2.85383892059326</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89221787452698</t>
+    <t xml:space="preserve">2.8922176361084</t>
   </si>
   <si>
     <t xml:space="preserve">2.91831541061401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89835834503174</t>
+    <t xml:space="preserve">2.89835858345032</t>
   </si>
   <si>
     <t xml:space="preserve">2.80931997299194</t>
@@ -3692,34 +3692,34 @@
     <t xml:space="preserve">2.79857397079468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93366718292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94594812393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87226104736328</t>
+    <t xml:space="preserve">2.93366670608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94594788551331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8722608089447</t>
   </si>
   <si>
     <t xml:space="preserve">2.93980741500854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88607740402222</t>
+    <t xml:space="preserve">2.88607716560364</t>
   </si>
   <si>
     <t xml:space="preserve">2.96590495109558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95208859443665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90603423118591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92752623558044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91678023338318</t>
+    <t xml:space="preserve">2.95208835601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90603399276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92752599716187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91678047180176</t>
   </si>
   <si>
     <t xml:space="preserve">2.90296387672424</t>
@@ -3728,19 +3728,19 @@
     <t xml:space="preserve">2.90756940841675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7908980846405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78936290740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75712490081787</t>
+    <t xml:space="preserve">2.79089784622192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78936314582825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75712466239929</t>
   </si>
   <si>
     <t xml:space="preserve">2.68343782424927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78168725967407</t>
+    <t xml:space="preserve">2.78168749809265</t>
   </si>
   <si>
     <t xml:space="preserve">2.80624938011169</t>
@@ -3758,10 +3758,10 @@
     <t xml:space="preserve">2.86151504516602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85230422019958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81239032745361</t>
+    <t xml:space="preserve">2.85230398178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81239008903503</t>
   </si>
   <si>
     <t xml:space="preserve">3.05270981788635</t>
@@ -3776,13 +3776,13 @@
     <t xml:space="preserve">3.13877034187317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11766123771667</t>
+    <t xml:space="preserve">3.1176609992981</t>
   </si>
   <si>
     <t xml:space="preserve">3.07544279098511</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04946231842041</t>
+    <t xml:space="preserve">3.04946255683899</t>
   </si>
   <si>
     <t xml:space="preserve">3.01211524009705</t>
@@ -3803,10 +3803,10 @@
     <t xml:space="preserve">2.96664953231812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7620530128479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6337742805481</t>
+    <t xml:space="preserve">2.76205277442932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63377404212952</t>
   </si>
   <si>
     <t xml:space="preserve">2.62565517425537</t>
@@ -3818,7 +3818,7 @@
     <t xml:space="preserve">2.66137862205505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70197319984436</t>
+    <t xml:space="preserve">2.70197296142578</t>
   </si>
   <si>
     <t xml:space="preserve">2.76367664337158</t>
@@ -3827,7 +3827,7 @@
     <t xml:space="preserve">2.78478598594666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77666711807251</t>
+    <t xml:space="preserve">2.77666735649109</t>
   </si>
   <si>
     <t xml:space="preserve">2.6954779624939</t>
@@ -3860,7 +3860,7 @@
     <t xml:space="preserve">2.60129857063293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67274498939514</t>
+    <t xml:space="preserve">2.67274522781372</t>
   </si>
   <si>
     <t xml:space="preserve">2.76042914390564</t>
@@ -3872,19 +3872,19 @@
     <t xml:space="preserve">2.70359683036804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64026951789856</t>
+    <t xml:space="preserve">2.64026927947998</t>
   </si>
   <si>
     <t xml:space="preserve">2.51361417770386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52822852134705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57207059860229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69060659408569</t>
+    <t xml:space="preserve">2.52822875976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57207036018372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69060635566711</t>
   </si>
   <si>
     <t xml:space="preserve">2.61428880691528</t>
@@ -3896,7 +3896,7 @@
     <t xml:space="preserve">2.54608988761902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58343720436096</t>
+    <t xml:space="preserve">2.58343696594238</t>
   </si>
   <si>
     <t xml:space="preserve">2.51686191558838</t>
@@ -3905,7 +3905,7 @@
     <t xml:space="preserve">2.55908012390137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62727928161621</t>
+    <t xml:space="preserve">2.62727904319763</t>
   </si>
   <si>
     <t xml:space="preserve">2.65975475311279</t>
@@ -3920,10 +3920,10 @@
     <t xml:space="preserve">2.78153848648071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73607230186462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71496343612671</t>
+    <t xml:space="preserve">2.7360725402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71496367454529</t>
   </si>
   <si>
     <t xml:space="preserve">2.71171569824219</t>
@@ -3935,7 +3935,7 @@
     <t xml:space="preserve">2.61753630638123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66624999046326</t>
+    <t xml:space="preserve">2.66624975204468</t>
   </si>
   <si>
     <t xml:space="preserve">2.60941743850708</t>
@@ -3950,7 +3950,7 @@
     <t xml:space="preserve">2.59155607223511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59967494010925</t>
+    <t xml:space="preserve">2.59967470169067</t>
   </si>
   <si>
     <t xml:space="preserve">2.56070399284363</t>
@@ -3971,19 +3971,19 @@
     <t xml:space="preserve">2.82050919532776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81726145744324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84811353683472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92767882347107</t>
+    <t xml:space="preserve">2.81726169586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84811329841614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92767858505249</t>
   </si>
   <si>
     <t xml:space="preserve">2.90819334983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88870811462402</t>
+    <t xml:space="preserve">2.88870787620544</t>
   </si>
   <si>
     <t xml:space="preserve">2.83999466896057</t>
@@ -3995,7 +3995,7 @@
     <t xml:space="preserve">2.85136103630066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78803324699402</t>
+    <t xml:space="preserve">2.7880334854126</t>
   </si>
   <si>
     <t xml:space="preserve">2.76530051231384</t>
@@ -4007,7 +4007,7 @@
     <t xml:space="preserve">2.75393414497375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76692414283752</t>
+    <t xml:space="preserve">2.7669243812561</t>
   </si>
   <si>
     <t xml:space="preserve">2.8546085357666</t>
@@ -4028,19 +4028,19 @@
     <t xml:space="preserve">2.64189314842224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75555777549744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83512306213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86435151100159</t>
+    <t xml:space="preserve">2.75555801391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83512330055237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86435127258301</t>
   </si>
   <si>
     <t xml:space="preserve">2.87734150886536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91631245613098</t>
+    <t xml:space="preserve">2.9163122177124</t>
   </si>
   <si>
     <t xml:space="preserve">2.95853066444397</t>
@@ -4055,7 +4055,7 @@
     <t xml:space="preserve">2.95528316497803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94716429710388</t>
+    <t xml:space="preserve">2.9471640586853</t>
   </si>
   <si>
     <t xml:space="preserve">2.95690679550171</t>
@@ -4064,28 +4064,28 @@
     <t xml:space="preserve">3.02997708320618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04459095001221</t>
+    <t xml:space="preserve">3.04459118843079</t>
   </si>
   <si>
     <t xml:space="preserve">3.10467100143433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87409400939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84973740577698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89520335197449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88708424568176</t>
+    <t xml:space="preserve">2.87409377098083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8497371673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89520311355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88708400726318</t>
   </si>
   <si>
     <t xml:space="preserve">2.91793608665466</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04621481895447</t>
+    <t xml:space="preserve">3.04621505737305</t>
   </si>
   <si>
     <t xml:space="preserve">3.05108594894409</t>
@@ -4094,13 +4094,13 @@
     <t xml:space="preserve">3.1014232635498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10629463195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11441373825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15987968444824</t>
+    <t xml:space="preserve">3.10629487037659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11441349983215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15987944602966</t>
   </si>
   <si>
     <t xml:space="preserve">3.12740397453308</t>
@@ -4112,10 +4112,10 @@
     <t xml:space="preserve">3.14201784133911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1209089756012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08031392097473</t>
+    <t xml:space="preserve">3.12090873718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08031415939331</t>
   </si>
   <si>
     <t xml:space="preserve">3.07219505310059</t>
@@ -4124,7 +4124,7 @@
     <t xml:space="preserve">3.08193802833557</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0916805267334</t>
+    <t xml:space="preserve">3.09168076515198</t>
   </si>
   <si>
     <t xml:space="preserve">3.09817576408386</t>
@@ -4145,16 +4145,16 @@
     <t xml:space="preserve">3.18261241912842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17611742019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14039444923401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12415647506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17774128913879</t>
+    <t xml:space="preserve">3.17611718177795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14039421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12415623664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17774105072021</t>
   </si>
   <si>
     <t xml:space="preserve">3.21508836746216</t>
@@ -4166,19 +4166,19 @@
     <t xml:space="preserve">3.28003931045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2767915725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27029657363892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3125147819519</t>
+    <t xml:space="preserve">3.27679181098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2702968120575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31251502037048</t>
   </si>
   <si>
     <t xml:space="preserve">3.3417432308197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29465341567993</t>
+    <t xml:space="preserve">3.29465365409851</t>
   </si>
   <si>
     <t xml:space="preserve">3.32388138771057</t>
@@ -4193,40 +4193,40 @@
     <t xml:space="preserve">3.43917012214661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46190285682678</t>
+    <t xml:space="preserve">3.46190309524536</t>
   </si>
   <si>
     <t xml:space="preserve">3.48301196098328</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51386380195618</t>
+    <t xml:space="preserve">3.51386404037476</t>
   </si>
   <si>
     <t xml:space="preserve">3.53822064399719</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52035927772522</t>
+    <t xml:space="preserve">3.52035903930664</t>
   </si>
   <si>
     <t xml:space="preserve">3.65838050842285</t>
   </si>
   <si>
-    <t xml:space="preserve">3.733074426651</t>
+    <t xml:space="preserve">3.73307466506958</t>
   </si>
   <si>
     <t xml:space="preserve">3.65675687789917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66487550735474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7022225856781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68436121940613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65026164054871</t>
+    <t xml:space="preserve">3.66487574577332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70222282409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68436098098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65026140213013</t>
   </si>
   <si>
     <t xml:space="preserve">3.62428140640259</t>
@@ -4238,7 +4238,7 @@
     <t xml:space="preserve">3.59505319595337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60804319381714</t>
+    <t xml:space="preserve">3.60804295539856</t>
   </si>
   <si>
     <t xml:space="preserve">3.64539003372192</t>
@@ -4247,22 +4247,22 @@
     <t xml:space="preserve">3.59830093383789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64376664161682</t>
+    <t xml:space="preserve">3.64376640319824</t>
   </si>
   <si>
     <t xml:space="preserve">3.61616206169128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68598484992981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69572758674622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81101608276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90032386779785</t>
+    <t xml:space="preserve">3.68598461151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69572734832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81101536750793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90032410621643</t>
   </si>
   <si>
     <t xml:space="preserve">3.87921476364136</t>
@@ -4274,10 +4274,10 @@
     <t xml:space="preserve">3.89382863044739</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97177052497864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89220547676086</t>
+    <t xml:space="preserve">3.97177076339722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89220499992371</t>
   </si>
   <si>
     <t xml:space="preserve">3.91980957984924</t>
@@ -4292,16 +4292,16 @@
     <t xml:space="preserve">3.41643738746643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19885039329529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21021676063538</t>
+    <t xml:space="preserve">3.19885015487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21021699905396</t>
   </si>
   <si>
     <t xml:space="preserve">3.09492826461792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3725950717926</t>
+    <t xml:space="preserve">3.37259483337402</t>
   </si>
   <si>
     <t xml:space="preserve">3.28491067886353</t>
@@ -4310,25 +4310,25 @@
     <t xml:space="preserve">3.21995949745178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08843302726746</t>
+    <t xml:space="preserve">3.08843326568604</t>
   </si>
   <si>
     <t xml:space="preserve">3.09330439567566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09979939460754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19560289382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21184062957764</t>
+    <t xml:space="preserve">3.09979963302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19560265541077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21184086799622</t>
   </si>
   <si>
     <t xml:space="preserve">3.1517608165741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27192068099976</t>
+    <t xml:space="preserve">3.27192091941833</t>
   </si>
   <si>
     <t xml:space="preserve">3.28815841674805</t>
@@ -4343,13 +4343,13 @@
     <t xml:space="preserve">3.34823822975159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44891285896301</t>
+    <t xml:space="preserve">3.44891262054443</t>
   </si>
   <si>
     <t xml:space="preserve">3.4342987537384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47326946258545</t>
+    <t xml:space="preserve">3.47326922416687</t>
   </si>
   <si>
     <t xml:space="preserve">3.47002196311951</t>
@@ -4370,16 +4370,16 @@
     <t xml:space="preserve">3.38720893859863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43105101585388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50736880302429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36934757232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38558530807495</t>
+    <t xml:space="preserve">3.4310507774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50736904144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36934733390808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38558506965637</t>
   </si>
   <si>
     <t xml:space="preserve">3.38233757019043</t>
@@ -4397,19 +4397,19 @@
     <t xml:space="preserve">3.18703985214233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19400262832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20096468925476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18355894088745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13134074211121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0460512638092</t>
+    <t xml:space="preserve">3.19400238990784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20096492767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18355870246887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13134098052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04605150222778</t>
   </si>
   <si>
     <t xml:space="preserve">3.13308143615723</t>
@@ -4418,22 +4418,22 @@
     <t xml:space="preserve">3.22533321380615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1974835395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2114086151123</t>
+    <t xml:space="preserve">3.19748377799988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21140837669373</t>
   </si>
   <si>
     <t xml:space="preserve">3.23055481910706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24273920059204</t>
+    <t xml:space="preserve">3.24273943901062</t>
   </si>
   <si>
     <t xml:space="preserve">3.23229551315308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22011137008667</t>
+    <t xml:space="preserve">3.22011160850525</t>
   </si>
   <si>
     <t xml:space="preserve">3.29321646690369</t>
@@ -4442,25 +4442,25 @@
     <t xml:space="preserve">3.25840449333191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28625416755676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30017924308777</t>
+    <t xml:space="preserve">3.28625440597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30017900466919</t>
   </si>
   <si>
     <t xml:space="preserve">3.34891581535339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38546872138977</t>
+    <t xml:space="preserve">3.38546848297119</t>
   </si>
   <si>
     <t xml:space="preserve">3.41505861282349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37676548957825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38024663925171</t>
+    <t xml:space="preserve">3.37676572799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38024687767029</t>
   </si>
   <si>
     <t xml:space="preserve">3.32106614112854</t>
@@ -4481,28 +4481,28 @@
     <t xml:space="preserve">3.33673167228699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30888199806213</t>
+    <t xml:space="preserve">3.30888223648071</t>
   </si>
   <si>
     <t xml:space="preserve">3.34369397163391</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40809631347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42028045654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43420553207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50905108451843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5316789150238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55430674552917</t>
+    <t xml:space="preserve">3.40809607505798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42028069496155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4342052936554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50905132293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53167915344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55430698394775</t>
   </si>
   <si>
     <t xml:space="preserve">3.63785552978516</t>
@@ -4517,7 +4517,7 @@
     <t xml:space="preserve">3.70922040939331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78406620025635</t>
+    <t xml:space="preserve">3.78406596183777</t>
   </si>
   <si>
     <t xml:space="preserve">3.82409977912903</t>
@@ -4529,31 +4529,31 @@
     <t xml:space="preserve">3.75099468231201</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72140455245972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73184823989868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73881053924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52471685409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6535210609436</t>
+    <t xml:space="preserve">3.72140431404114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7318480014801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73881030082703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52471661567688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65352082252502</t>
   </si>
   <si>
     <t xml:space="preserve">3.68833303451538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74229192733765</t>
+    <t xml:space="preserve">3.74229168891907</t>
   </si>
   <si>
     <t xml:space="preserve">3.73358845710754</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68485188484192</t>
+    <t xml:space="preserve">3.6848521232605</t>
   </si>
   <si>
     <t xml:space="preserve">3.64655876159668</t>
@@ -4562,37 +4562,37 @@
     <t xml:space="preserve">3.68137073516846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69007325172424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71270108222961</t>
+    <t xml:space="preserve">3.69007349014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71270132064819</t>
   </si>
   <si>
     <t xml:space="preserve">3.72314476966858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8032124042511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83802437782288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81713771820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76665997505188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76840043067932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86065220832825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90416741371155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90590834617615</t>
+    <t xml:space="preserve">3.80321264266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83802461624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8171374797821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76666021347046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7684006690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86065268516541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90416789054871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90590786933899</t>
   </si>
   <si>
     <t xml:space="preserve">4.00338172912598</t>
@@ -4607,7 +4607,7 @@
     <t xml:space="preserve">4.07648706436157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17744207382202</t>
+    <t xml:space="preserve">4.17744159698486</t>
   </si>
   <si>
     <t xml:space="preserve">4.34976148605347</t>
@@ -4637,7 +4637,7 @@
     <t xml:space="preserve">4.31668996810913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22095680236816</t>
+    <t xml:space="preserve">4.22095632553101</t>
   </si>
   <si>
     <t xml:space="preserve">4.19310712814331</t>
@@ -4646,7 +4646,7 @@
     <t xml:space="preserve">4.28884029388428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37325954437256</t>
+    <t xml:space="preserve">4.3732590675354</t>
   </si>
   <si>
     <t xml:space="preserve">4.3393177986145</t>
@@ -4718,10 +4718,10 @@
     <t xml:space="preserve">5.0607967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21309947967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19569301605225</t>
+    <t xml:space="preserve">5.21309900283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1956934928894</t>
   </si>
   <si>
     <t xml:space="preserve">5.13042068481445</t>
@@ -4730,7 +4730,7 @@
     <t xml:space="preserve">5.14347505569458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08690547943115</t>
+    <t xml:space="preserve">5.08690595626831</t>
   </si>
   <si>
     <t xml:space="preserve">5.04774236679077</t>
@@ -4835,13 +4835,13 @@
     <t xml:space="preserve">5.33494138717651</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5525164604187</t>
+    <t xml:space="preserve">5.55251693725586</t>
   </si>
   <si>
     <t xml:space="preserve">5.65695238113403</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70481872558594</t>
+    <t xml:space="preserve">5.7048192024231</t>
   </si>
   <si>
     <t xml:space="preserve">5.7091703414917</t>
@@ -4859,7 +4859,7 @@
     <t xml:space="preserve">6.13561773300171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8005518913269</t>
+    <t xml:space="preserve">5.80055236816406</t>
   </si>
   <si>
     <t xml:space="preserve">5.78749752044678</t>
@@ -4868,7 +4868,7 @@
     <t xml:space="preserve">5.87017583847046</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8397159576416</t>
+    <t xml:space="preserve">5.83971548080444</t>
   </si>
   <si>
     <t xml:space="preserve">5.71352195739746</t>
@@ -4877,10 +4877,10 @@
     <t xml:space="preserve">5.72222471237183</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84406709671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93109703063965</t>
+    <t xml:space="preserve">5.84406757354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93109750747681</t>
   </si>
   <si>
     <t xml:space="preserve">5.97896337509155</t>
@@ -4889,7 +4889,7 @@
     <t xml:space="preserve">5.94415140151978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89628553390503</t>
+    <t xml:space="preserve">5.89628505706787</t>
   </si>
   <si>
     <t xml:space="preserve">5.98766660690308</t>
@@ -4907,7 +4907,7 @@
     <t xml:space="preserve">6.24005365371704</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17913246154785</t>
+    <t xml:space="preserve">6.17913293838501</t>
   </si>
   <si>
     <t xml:space="preserve">6.01812744140625</t>
@@ -4916,10 +4916,10 @@
     <t xml:space="preserve">6.16172647476196</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23570203781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23135089874268</t>
+    <t xml:space="preserve">6.23570251464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23135042190552</t>
   </si>
   <si>
     <t xml:space="preserve">6.07904815673828</t>
@@ -4928,7 +4928,7 @@
     <t xml:space="preserve">6.00507259368896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8658242225647</t>
+    <t xml:space="preserve">5.86582469940186</t>
   </si>
   <si>
     <t xml:space="preserve">5.69176435470581</t>
@@ -4940,34 +4940,34 @@
     <t xml:space="preserve">5.91369104385376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93980026245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18783617019653</t>
+    <t xml:space="preserve">5.93979978561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18783569335938</t>
   </si>
   <si>
     <t xml:space="preserve">6.065993309021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03988456726074</t>
+    <t xml:space="preserve">6.0398850440979</t>
   </si>
   <si>
     <t xml:space="preserve">6.09645414352417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22264766693115</t>
+    <t xml:space="preserve">6.22264814376831</t>
   </si>
   <si>
     <t xml:space="preserve">5.93544864654541</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06164216995239</t>
+    <t xml:space="preserve">6.06164264678955</t>
   </si>
   <si>
     <t xml:space="preserve">5.82666110992432</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85277032852173</t>
+    <t xml:space="preserve">5.85276985168457</t>
   </si>
   <si>
     <t xml:space="preserve">5.92674541473389</t>
@@ -4976,28 +4976,28 @@
     <t xml:space="preserve">6.11821174621582</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37930202484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53595590591431</t>
+    <t xml:space="preserve">6.37930154800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53595638275146</t>
   </si>
   <si>
     <t xml:space="preserve">6.53160429000854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47068309783936</t>
+    <t xml:space="preserve">6.47068357467651</t>
   </si>
   <si>
     <t xml:space="preserve">6.66650104522705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82315540313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84056091308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90148210525513</t>
+    <t xml:space="preserve">6.82315492630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8405613899231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90148162841797</t>
   </si>
   <si>
     <t xml:space="preserve">6.80574893951416</t>
@@ -5006,7 +5006,7 @@
     <t xml:space="preserve">6.95369958877563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07119083404541</t>
+    <t xml:space="preserve">7.07119035720825</t>
   </si>
   <si>
     <t xml:space="preserve">6.96240282058716</t>
@@ -5018,10 +5018,10 @@
     <t xml:space="preserve">6.99286365509033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12775993347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12340879440308</t>
+    <t xml:space="preserve">7.12775945663452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12340927124023</t>
   </si>
   <si>
     <t xml:space="preserve">7.20173501968384</t>
@@ -5991,6 +5991,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.914999961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0950002670288</t>
   </si>
 </sst>
 </file>
@@ -72005,7 +72008,7 @@
     </row>
     <row r="2527">
       <c r="A2527" s="1" t="n">
-        <v>45996.6913194444</v>
+        <v>45996.3333333333</v>
       </c>
       <c r="B2527" t="n">
         <v>745863</v>
@@ -72026,6 +72029,32 @@
         <v>1992</v>
       </c>
       <c r="H2527" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2528">
+      <c r="A2528" s="1" t="n">
+        <v>45999.6916435185</v>
+      </c>
+      <c r="B2528" t="n">
+        <v>433752</v>
+      </c>
+      <c r="C2528" t="n">
+        <v>15.0950002670288</v>
+      </c>
+      <c r="D2528" t="n">
+        <v>14.8500003814697</v>
+      </c>
+      <c r="E2528" t="n">
+        <v>15.0950002670288</v>
+      </c>
+      <c r="F2528" t="n">
+        <v>15.0950002670288</v>
+      </c>
+      <c r="G2528" t="s">
+        <v>1993</v>
+      </c>
+      <c r="H2528" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BPSO.MI.xlsx
+++ b/data/BPSO.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1993" uniqueCount="1993">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1994" uniqueCount="1994">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,40 +38,40 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82907152175903</t>
+    <t xml:space="preserve">2.82907176017761</t>
   </si>
   <si>
     <t xml:space="preserve">BPSO.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80963706970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74855828285217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71246600151062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63611698150635</t>
+    <t xml:space="preserve">2.80963730812073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74855780601501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71246576309204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63611674308777</t>
   </si>
   <si>
     <t xml:space="preserve">2.60835409164429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69303226470947</t>
+    <t xml:space="preserve">2.69303202629089</t>
   </si>
   <si>
     <t xml:space="preserve">2.69858455657959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61113023757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51257038116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4556565284729</t>
+    <t xml:space="preserve">2.61113047599792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51257061958313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45565676689148</t>
   </si>
   <si>
     <t xml:space="preserve">2.26686644554138</t>
@@ -80,13 +80,13 @@
     <t xml:space="preserve">2.38069534301758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40568208694458</t>
+    <t xml:space="preserve">2.40568232536316</t>
   </si>
   <si>
     <t xml:space="preserve">2.36542582511902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51951169967651</t>
+    <t xml:space="preserve">2.51951146125793</t>
   </si>
   <si>
     <t xml:space="preserve">2.44455122947693</t>
@@ -95,43 +95,43 @@
     <t xml:space="preserve">2.35570859909058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43899893760681</t>
+    <t xml:space="preserve">2.43899869918823</t>
   </si>
   <si>
     <t xml:space="preserve">2.40429425239563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32100462913513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22105717658997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23216247558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20995187759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04059624671936</t>
+    <t xml:space="preserve">2.32100486755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22105741500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23216223716736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20995211601257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04059600830078</t>
   </si>
   <si>
     <t xml:space="preserve">2.06280636787415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14331984519958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07668805122375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18218803405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22522187232971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27797174453735</t>
+    <t xml:space="preserve">2.14332008361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07668828964233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1821882724762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22522163391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2779712677002</t>
   </si>
   <si>
     <t xml:space="preserve">2.19329357147217</t>
@@ -140,55 +140,55 @@
     <t xml:space="preserve">2.16553068161011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24604392051697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18635296821594</t>
+    <t xml:space="preserve">2.24604415893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18635272979736</t>
   </si>
   <si>
     <t xml:space="preserve">2.1766357421875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21550488471985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25992584228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31822872161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38763642311096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38208341598511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37514305114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24187922477722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26270174980164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25020861625671</t>
+    <t xml:space="preserve">2.21550464630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.259925365448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31822848320007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38763618469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38208389282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37514281272888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2418794631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26270198822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25020837783813</t>
   </si>
   <si>
     <t xml:space="preserve">2.3196165561676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4334454536438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35848522186279</t>
+    <t xml:space="preserve">2.43344521522522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35848498344421</t>
   </si>
   <si>
     <t xml:space="preserve">2.30156993865967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34599161148071</t>
+    <t xml:space="preserve">2.34599184989929</t>
   </si>
   <si>
     <t xml:space="preserve">2.35987329483032</t>
@@ -197,76 +197,76 @@
     <t xml:space="preserve">2.39318895339966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29324150085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23771548271179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18774104118347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.139155626297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14748477935791</t>
+    <t xml:space="preserve">2.29324102401733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23771500587463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18774080276489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13915610313416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14748454093933</t>
   </si>
   <si>
     <t xml:space="preserve">2.12110948562622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06974720954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01283288002014</t>
+    <t xml:space="preserve">2.06974697113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01283311843872</t>
   </si>
   <si>
     <t xml:space="preserve">2.01838564872742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07113552093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11694502830505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12527370452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22799825668335</t>
+    <t xml:space="preserve">2.07113528251648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11694526672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12527418136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22799801826477</t>
   </si>
   <si>
     <t xml:space="preserve">2.30295825004578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23910355567932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29046511650085</t>
+    <t xml:space="preserve">2.23910307884216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29046487808228</t>
   </si>
   <si>
     <t xml:space="preserve">2.33211016654968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32655763626099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27935981750488</t>
+    <t xml:space="preserve">2.32655739784241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2793595790863</t>
   </si>
   <si>
     <t xml:space="preserve">2.32378101348877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30851078033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26131343841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23493885993958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15720152854919</t>
+    <t xml:space="preserve">2.30851101875305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26131367683411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.234938621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15720129013062</t>
   </si>
   <si>
     <t xml:space="preserve">2.11139249801636</t>
@@ -275,34 +275,34 @@
     <t xml:space="preserve">2.08224058151245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09889936447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08918213844299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10584020614624</t>
+    <t xml:space="preserve">2.09889888763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08918190002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10583972930908</t>
   </si>
   <si>
     <t xml:space="preserve">2.04892492294312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03781986236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06558322906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03226709365845</t>
+    <t xml:space="preserve">2.0378201007843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06558299064636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03226685523987</t>
   </si>
   <si>
     <t xml:space="preserve">2.07252359390259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05725359916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05156683921814</t>
+    <t xml:space="preserve">2.05725383758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05156707763672</t>
   </si>
   <si>
     <t xml:space="preserve">2.12691879272461</t>
@@ -314,19 +314,19 @@
     <t xml:space="preserve">2.15393233299255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17525815963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15535378456116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09279727935791</t>
+    <t xml:space="preserve">2.17525792121887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15535402297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09279704093933</t>
   </si>
   <si>
     <t xml:space="preserve">2.07147097587585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99896264076233</t>
+    <t xml:space="preserve">1.99896228313446</t>
   </si>
   <si>
     <t xml:space="preserve">1.95773220062256</t>
@@ -335,13 +335,13 @@
     <t xml:space="preserve">1.87669289112091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98900997638702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93640613555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94351506233215</t>
+    <t xml:space="preserve">1.98901009559631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93640637397766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94351482391357</t>
   </si>
   <si>
     <t xml:space="preserve">1.84114980697632</t>
@@ -350,10 +350,10 @@
     <t xml:space="preserve">1.78143715858459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75157999992371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72598886489868</t>
+    <t xml:space="preserve">1.751580119133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72598898410797</t>
   </si>
   <si>
     <t xml:space="preserve">1.64210629463196</t>
@@ -365,28 +365,28 @@
     <t xml:space="preserve">1.77006256580353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81129336357117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78001475334167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89375400543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63499748706818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56533288955688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66911971569061</t>
+    <t xml:space="preserve">1.81129324436188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78001427650452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89375364780426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63499760627747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56533300876617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66911959648132</t>
   </si>
   <si>
     <t xml:space="preserve">1.65632367134094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63926267623901</t>
+    <t xml:space="preserve">1.63926255702972</t>
   </si>
   <si>
     <t xml:space="preserve">1.63641941547394</t>
@@ -398,19 +398,19 @@
     <t xml:space="preserve">1.51130640506744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52552390098572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53121066093445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63784098625183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67196333408356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69471073150635</t>
+    <t xml:space="preserve">1.52552366256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53121078014374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63784086704254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67196345329285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69471085071564</t>
   </si>
   <si>
     <t xml:space="preserve">1.67054152488708</t>
@@ -422,25 +422,25 @@
     <t xml:space="preserve">1.70892810821533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72172379493713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77574932575226</t>
+    <t xml:space="preserve">1.72172355651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77574944496155</t>
   </si>
   <si>
     <t xml:space="preserve">1.76721882820129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72741031646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69755458831787</t>
+    <t xml:space="preserve">1.72741079330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69755446910858</t>
   </si>
   <si>
     <t xml:space="preserve">1.72456705570221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71888029575348</t>
+    <t xml:space="preserve">1.71888017654419</t>
   </si>
   <si>
     <t xml:space="preserve">1.66343283653259</t>
@@ -449,19 +449,19 @@
     <t xml:space="preserve">1.55395877361298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57528519630432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52125871181488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63357579708099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65916693210602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64779329299927</t>
+    <t xml:space="preserve">1.57528495788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5212584733963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63357555866241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65916705131531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64779317378998</t>
   </si>
   <si>
     <t xml:space="preserve">1.68760240077972</t>
@@ -470,7 +470,7 @@
     <t xml:space="preserve">1.71461498737335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70608460903168</t>
+    <t xml:space="preserve">1.70608472824097</t>
   </si>
   <si>
     <t xml:space="preserve">1.70039784908295</t>
@@ -479,13 +479,13 @@
     <t xml:space="preserve">1.74447119235992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70750665664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72030210494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73167586326599</t>
+    <t xml:space="preserve">1.70750653743744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72030198574066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73167598247528</t>
   </si>
   <si>
     <t xml:space="preserve">1.78285884857178</t>
@@ -494,67 +494,67 @@
     <t xml:space="preserve">1.7785929441452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77148449420929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76437568664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75584530830383</t>
+    <t xml:space="preserve">1.77148401737213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76437544822693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75584518909454</t>
   </si>
   <si>
     <t xml:space="preserve">1.76295387744904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74162769317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76864111423492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74873673915863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73451912403107</t>
+    <t xml:space="preserve">1.74162793159485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76864087581635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74873661994934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73451936244965</t>
   </si>
   <si>
     <t xml:space="preserve">1.78428041934967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85252344608307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84967982769012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81271541118622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8354629278183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84825849533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85963177680969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9477801322937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97621488571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09848427772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10843634605408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07573652267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08568859100342</t>
+    <t xml:space="preserve">1.85252356529236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84968030452728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81271505355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83546245098114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84825813770294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85963225364685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94777989387512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9762145280838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09848380088806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1084361076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07573676109314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08568835258484</t>
   </si>
   <si>
     <t xml:space="preserve">2.08853220939636</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">2.09706234931946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16104078292847</t>
+    <t xml:space="preserve">2.16104054450989</t>
   </si>
   <si>
     <t xml:space="preserve">2.18236660957336</t>
@@ -572,25 +572,25 @@
     <t xml:space="preserve">2.11412310600281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00038361549377</t>
+    <t xml:space="preserve">2.00038433074951</t>
   </si>
   <si>
     <t xml:space="preserve">2.03877115249634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00891447067261</t>
+    <t xml:space="preserve">2.00891423225403</t>
   </si>
   <si>
     <t xml:space="preserve">2.05298852920532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06294083595276</t>
+    <t xml:space="preserve">2.06294131278992</t>
   </si>
   <si>
     <t xml:space="preserve">2.11554503440857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12549710273743</t>
+    <t xml:space="preserve">2.12549686431885</t>
   </si>
   <si>
     <t xml:space="preserve">2.16246247291565</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">2.08142328262329</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03592777252197</t>
+    <t xml:space="preserve">2.03592824935913</t>
   </si>
   <si>
     <t xml:space="preserve">2.07715797424316</t>
@@ -614,10 +614,10 @@
     <t xml:space="preserve">2.09990572929382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08995389938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01033616065979</t>
+    <t xml:space="preserve">2.08995366096497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01033592224121</t>
   </si>
   <si>
     <t xml:space="preserve">2.12407517433167</t>
@@ -626,61 +626,61 @@
     <t xml:space="preserve">2.10417079925537</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07289290428162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16814947128296</t>
+    <t xml:space="preserve">2.07289266586304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16814970970154</t>
   </si>
   <si>
     <t xml:space="preserve">2.27477979660034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37430167198181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2634060382843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23354887962341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27193641662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23212718963623</t>
+    <t xml:space="preserve">2.37430143356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26340627670288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23354935646057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27193665504456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23212742805481</t>
   </si>
   <si>
     <t xml:space="preserve">2.1781017780304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16957139968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23639225959778</t>
+    <t xml:space="preserve">2.16957092285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23639273643494</t>
   </si>
   <si>
     <t xml:space="preserve">2.22217512130737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21791005134583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20511436462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22359681129456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26482748985291</t>
+    <t xml:space="preserve">2.21790981292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2051146030426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22359704971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26482796669006</t>
   </si>
   <si>
     <t xml:space="preserve">2.3103232383728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31743168830872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34302306175232</t>
+    <t xml:space="preserve">2.31743192672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34302282333374</t>
   </si>
   <si>
     <t xml:space="preserve">2.34160113334656</t>
@@ -689,10 +689,10 @@
     <t xml:space="preserve">2.30463624000549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.297527551651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29610538482666</t>
+    <t xml:space="preserve">2.29752779006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29610586166382</t>
   </si>
   <si>
     <t xml:space="preserve">2.36008381843567</t>
@@ -707,82 +707,82 @@
     <t xml:space="preserve">2.4027361869812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41695332527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45249676704407</t>
+    <t xml:space="preserve">2.41695356369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45249629020691</t>
   </si>
   <si>
     <t xml:space="preserve">2.41126656532288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.415531873703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4240620136261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44396638870239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35439658164978</t>
+    <t xml:space="preserve">2.41553163528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42406225204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44396615028381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35439682006836</t>
   </si>
   <si>
     <t xml:space="preserve">2.33733606338501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33022737503052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36434864997864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32738399505615</t>
+    <t xml:space="preserve">2.33022713661194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36434888839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32738375663757</t>
   </si>
   <si>
     <t xml:space="preserve">2.28188872337341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30037093162537</t>
+    <t xml:space="preserve">2.30037117004395</t>
   </si>
   <si>
     <t xml:space="preserve">2.32311868667603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33449268341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30890107154846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29894924163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25629758834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12834072113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13402724266052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28473162651062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22928380966187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27335786819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27904534339905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31316637992859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33875775337219</t>
+    <t xml:space="preserve">2.33449244499207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30890154838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2989490032196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25629734992981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12834024429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13402700424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28473210334778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22928404808044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27335810661316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27904462814331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31316685676575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33875751495361</t>
   </si>
   <si>
     <t xml:space="preserve">2.37856698036194</t>
@@ -791,85 +791,85 @@
     <t xml:space="preserve">2.32880568504333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36719179153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34870982170105</t>
+    <t xml:space="preserve">2.36719226837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34870958328247</t>
   </si>
   <si>
     <t xml:space="preserve">2.29468417167664</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30321431159973</t>
+    <t xml:space="preserve">2.30321455001831</t>
   </si>
   <si>
     <t xml:space="preserve">2.28757524490356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32027506828308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28330993652344</t>
+    <t xml:space="preserve">2.32027530670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28331017494202</t>
   </si>
   <si>
     <t xml:space="preserve">2.29041886329651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29326248168945</t>
+    <t xml:space="preserve">2.29326224327087</t>
   </si>
   <si>
     <t xml:space="preserve">2.3060576915741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35581851005554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31174468994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3316490650177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46671390533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43117046356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42974901199341</t>
+    <t xml:space="preserve">2.35581827163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31174445152283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33164882659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46671414375305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43117070198059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42974925041199</t>
   </si>
   <si>
     <t xml:space="preserve">2.49799299240112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46387028694153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48661828041077</t>
+    <t xml:space="preserve">2.46387076377869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48661851882935</t>
   </si>
   <si>
     <t xml:space="preserve">2.51647520065308</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51789665222168</t>
+    <t xml:space="preserve">2.51789736747742</t>
   </si>
   <si>
     <t xml:space="preserve">2.56907939910889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.533536195755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48803973197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50510120391846</t>
+    <t xml:space="preserve">2.53353571891785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48803997039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50510168075562</t>
   </si>
   <si>
     <t xml:space="preserve">2.5079448223114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50936675071716</t>
+    <t xml:space="preserve">2.50936651229858</t>
   </si>
   <si>
     <t xml:space="preserve">2.50652289390564</t>
@@ -881,55 +881,55 @@
     <t xml:space="preserve">2.5722119808197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63293862342834</t>
+    <t xml:space="preserve">2.63293838500977</t>
   </si>
   <si>
     <t xml:space="preserve">2.65607309341431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70667839050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56642913818359</t>
+    <t xml:space="preserve">2.70667886734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56642866134644</t>
   </si>
   <si>
     <t xml:space="preserve">2.52594375610352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52883553504944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47389268875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52160620689392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51437664031982</t>
+    <t xml:space="preserve">2.52883577346802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47389245033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5216064453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5143768787384</t>
   </si>
   <si>
     <t xml:space="preserve">2.4710009098053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48979711532593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47533869743347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51726865768433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45654225349426</t>
+    <t xml:space="preserve">2.48979687690735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47533845901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51726841926575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45654201507568</t>
   </si>
   <si>
     <t xml:space="preserve">2.47967600822449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46087980270386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48112177848816</t>
+    <t xml:space="preserve">2.46087956428528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48112201690674</t>
   </si>
   <si>
     <t xml:space="preserve">2.45798802375793</t>
@@ -938,31 +938,31 @@
     <t xml:space="preserve">2.48256754875183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4883508682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48690557479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50859332084656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53751134872437</t>
+    <t xml:space="preserve">2.48835134506226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48690533638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50859355926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53751158714294</t>
   </si>
   <si>
     <t xml:space="preserve">2.6025755405426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5591995716095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49558043479919</t>
+    <t xml:space="preserve">2.55919933319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49558067321777</t>
   </si>
   <si>
     <t xml:space="preserve">2.59245419502258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66330242156982</t>
+    <t xml:space="preserve">2.6633026599884</t>
   </si>
   <si>
     <t xml:space="preserve">2.61414241790771</t>
@@ -971,19 +971,19 @@
     <t xml:space="preserve">2.63149261474609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62281775474548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61703395843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72692084312439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73704195022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72258281707764</t>
+    <t xml:space="preserve">2.6228175163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61703419685364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72692060470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73704171180725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72258305549622</t>
   </si>
   <si>
     <t xml:space="preserve">2.71246218681335</t>
@@ -992,19 +992,19 @@
     <t xml:space="preserve">2.71390795707703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7081241607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68932795524597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68643617630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68788242340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7110161781311</t>
+    <t xml:space="preserve">2.70812439918518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68932819366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68643641471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6878821849823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71101593971252</t>
   </si>
   <si>
     <t xml:space="preserve">2.6502890586853</t>
@@ -1016,16 +1016,16 @@
     <t xml:space="preserve">2.67197775840759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67053198814392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65318059921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65173506736755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66763997077942</t>
+    <t xml:space="preserve">2.67053174972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65318083763123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6517345905304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.667640209198</t>
   </si>
   <si>
     <t xml:space="preserve">2.65896487236023</t>
@@ -1037,19 +1037,19 @@
     <t xml:space="preserve">2.59823775291443</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62426352500916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6040210723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54474067687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57655000686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52449774742126</t>
+    <t xml:space="preserve">2.62426328659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60402131080627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54474091529846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57654976844788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52449822425842</t>
   </si>
   <si>
     <t xml:space="preserve">2.48545956611633</t>
@@ -1058,40 +1058,40 @@
     <t xml:space="preserve">2.50280976295471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52016043663025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51148509979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.518714427948</t>
+    <t xml:space="preserve">2.52016019821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51148533821106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51871466636658</t>
   </si>
   <si>
     <t xml:space="preserve">2.53317308425903</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55197024345398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50714755058289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55052423477173</t>
+    <t xml:space="preserve">2.5519700050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50714731216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55052447319031</t>
   </si>
   <si>
     <t xml:space="preserve">2.54618668556213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53606557846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5794415473938</t>
+    <t xml:space="preserve">2.53606534004211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57944130897522</t>
   </si>
   <si>
     <t xml:space="preserve">2.64161372184753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63004684448242</t>
+    <t xml:space="preserve">2.630047082901</t>
   </si>
   <si>
     <t xml:space="preserve">2.58956265449524</t>
@@ -1100,34 +1100,34 @@
     <t xml:space="preserve">2.52305197715759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51582288742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49268889427185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53461909294128</t>
+    <t xml:space="preserve">2.51582264900208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49268913269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53461861610413</t>
   </si>
   <si>
     <t xml:space="preserve">2.4912428855896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47244644165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50425601005554</t>
+    <t xml:space="preserve">2.47244668006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50425577163696</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401379585266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49413466453552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4984724521637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47823023796082</t>
+    <t xml:space="preserve">2.49413442611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49847221374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47822999954224</t>
   </si>
   <si>
     <t xml:space="preserve">2.51293087005615</t>
@@ -1136,22 +1136,22 @@
     <t xml:space="preserve">2.44931292533875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40738153457642</t>
+    <t xml:space="preserve">2.407381772995</t>
   </si>
   <si>
     <t xml:space="preserve">2.45509624481201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4102737903595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29605031013489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24688982963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28159093856812</t>
+    <t xml:space="preserve">2.41027355194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29605007171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2468900680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28159046173096</t>
   </si>
   <si>
     <t xml:space="preserve">2.18471765518188</t>
@@ -1160,16 +1160,16 @@
     <t xml:space="preserve">2.19773030281067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22086405754089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26279473304749</t>
+    <t xml:space="preserve">2.22086429595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26279449462891</t>
   </si>
   <si>
     <t xml:space="preserve">2.28448271751404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28592848777771</t>
+    <t xml:space="preserve">2.28592824935913</t>
   </si>
   <si>
     <t xml:space="preserve">2.32496762275696</t>
@@ -1187,16 +1187,16 @@
     <t xml:space="preserve">2.34231781959534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35677647590637</t>
+    <t xml:space="preserve">2.35677695274353</t>
   </si>
   <si>
     <t xml:space="preserve">2.35966849327087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34087228775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37701869010925</t>
+    <t xml:space="preserve">2.34087181091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37701892852783</t>
   </si>
   <si>
     <t xml:space="preserve">2.39292335510254</t>
@@ -1205,16 +1205,16 @@
     <t xml:space="preserve">2.40015268325806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4059362411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33653450012207</t>
+    <t xml:space="preserve">2.40593600273132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33653473854065</t>
   </si>
   <si>
     <t xml:space="preserve">2.29315757751465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20495986938477</t>
+    <t xml:space="preserve">2.20496010780334</t>
   </si>
   <si>
     <t xml:space="preserve">2.23966073989868</t>
@@ -1223,16 +1223,16 @@
     <t xml:space="preserve">2.23821473121643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23387694358826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18327164649963</t>
+    <t xml:space="preserve">2.23387718200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18327212333679</t>
   </si>
   <si>
     <t xml:space="preserve">2.21797275543213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24544405937195</t>
+    <t xml:space="preserve">2.24544382095337</t>
   </si>
   <si>
     <t xml:space="preserve">2.20062232017517</t>
@@ -1241,7 +1241,7 @@
     <t xml:space="preserve">2.2266480922699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28303647041321</t>
+    <t xml:space="preserve">2.28303670883179</t>
   </si>
   <si>
     <t xml:space="preserve">2.31340050697327</t>
@@ -1250,13 +1250,13 @@
     <t xml:space="preserve">2.31050896644592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38858580589294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38713979721069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34665584564209</t>
+    <t xml:space="preserve">2.38858556747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38713955879211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34665560722351</t>
   </si>
   <si>
     <t xml:space="preserve">2.34520959854126</t>
@@ -1268,13 +1268,13 @@
     <t xml:space="preserve">2.39436912536621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40304470062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40448999404907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32785940170288</t>
+    <t xml:space="preserve">2.40304446220398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40449023246765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3278591632843</t>
   </si>
   <si>
     <t xml:space="preserve">2.34954738616943</t>
@@ -1283,43 +1283,43 @@
     <t xml:space="preserve">2.33364295959473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31195449829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2295401096344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31484627723694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30327939987183</t>
+    <t xml:space="preserve">2.31195497512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22953963279724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31484651565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30327963829041</t>
   </si>
   <si>
     <t xml:space="preserve">2.32063007354736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30761742591858</t>
+    <t xml:space="preserve">2.3076171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.37268137931824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42907047271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36400580406189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31629204750061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35388517379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27725338935852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32930517196655</t>
+    <t xml:space="preserve">2.42907071113586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36400604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31629252433777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35388445854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27725291252136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32930493354797</t>
   </si>
   <si>
     <t xml:space="preserve">2.30617141723633</t>
@@ -1328,10 +1328,10 @@
     <t xml:space="preserve">2.3003876209259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37412714958191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3307511806488</t>
+    <t xml:space="preserve">2.37412691116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33075094223022</t>
   </si>
   <si>
     <t xml:space="preserve">2.32641339302063</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">2.39726066589355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39870667457581</t>
+    <t xml:space="preserve">2.39870691299438</t>
   </si>
   <si>
     <t xml:space="preserve">2.38569402694702</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">2.71969151496887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70956993103027</t>
+    <t xml:space="preserve">2.70957040786743</t>
   </si>
   <si>
     <t xml:space="preserve">2.75439214706421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77752661705017</t>
+    <t xml:space="preserve">2.77752685546875</t>
   </si>
   <si>
     <t xml:space="preserve">2.84837436676025</t>
@@ -1367,10 +1367,10 @@
     <t xml:space="preserve">2.84114503860474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83391571044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86861634254456</t>
+    <t xml:space="preserve">2.83391523361206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86861610412598</t>
   </si>
   <si>
     <t xml:space="preserve">2.90042591094971</t>
@@ -1379,16 +1379,16 @@
     <t xml:space="preserve">2.82957792282104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73125839233398</t>
+    <t xml:space="preserve">2.73125815391541</t>
   </si>
   <si>
     <t xml:space="preserve">2.78620195388794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75583815574646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82524037361145</t>
+    <t xml:space="preserve">2.7558376789093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82524013519287</t>
   </si>
   <si>
     <t xml:space="preserve">2.80644392967224</t>
@@ -1400,40 +1400,40 @@
     <t xml:space="preserve">2.74716281890869</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7384877204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63438439369202</t>
+    <t xml:space="preserve">2.73848795890808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6343846321106</t>
   </si>
   <si>
     <t xml:space="preserve">2.66091990470886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65060091018677</t>
+    <t xml:space="preserve">2.65060067176819</t>
   </si>
   <si>
     <t xml:space="preserve">2.71251702308655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7036714553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63143610954285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52824258804321</t>
+    <t xml:space="preserve">2.70367097854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63143634796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52824234962463</t>
   </si>
   <si>
     <t xml:space="preserve">2.4825427532196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52234578132629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56509733200073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61079740524292</t>
+    <t xml:space="preserve">2.52234554290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56509709358215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61079788208008</t>
   </si>
   <si>
     <t xml:space="preserve">2.57689046859741</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">2.51939749717712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59163331985474</t>
+    <t xml:space="preserve">2.59163308143616</t>
   </si>
   <si>
     <t xml:space="preserve">2.61816835403442</t>
@@ -1451,49 +1451,49 @@
     <t xml:space="preserve">2.59015917778015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54888081550598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56067442893982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55625200271606</t>
+    <t xml:space="preserve">2.54888105392456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5606746673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55625176429749</t>
   </si>
   <si>
     <t xml:space="preserve">2.54593300819397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57099390029907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51350045204163</t>
+    <t xml:space="preserve">2.57099413871765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51350069046021</t>
   </si>
   <si>
     <t xml:space="preserve">2.51055240631104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53708744049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54151010513306</t>
+    <t xml:space="preserve">2.5370876789093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54151034355164</t>
   </si>
   <si>
     <t xml:space="preserve">2.65354895591736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65944576263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70514535903931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69040369987488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65797138214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61964273452759</t>
+    <t xml:space="preserve">2.6594455242157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70514559745789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6904034614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65797162055969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61964297294617</t>
   </si>
   <si>
     <t xml:space="preserve">2.63291025161743</t>
@@ -1508,13 +1508,13 @@
     <t xml:space="preserve">2.6653425693512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64470362663269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63880729675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66386866569519</t>
+    <t xml:space="preserve">2.64470410346985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63880705833435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66386842727661</t>
   </si>
   <si>
     <t xml:space="preserve">2.71399140357971</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">2.73168134689331</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71693992614746</t>
+    <t xml:space="preserve">2.7169394493103</t>
   </si>
   <si>
     <t xml:space="preserve">2.73315572738647</t>
@@ -1535,13 +1535,13 @@
     <t xml:space="preserve">2.70661950111389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69187784194946</t>
+    <t xml:space="preserve">2.69187808036804</t>
   </si>
   <si>
     <t xml:space="preserve">2.68892931938171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67713618278503</t>
+    <t xml:space="preserve">2.67713594436646</t>
   </si>
   <si>
     <t xml:space="preserve">2.64617800712585</t>
@@ -1553,58 +1553,58 @@
     <t xml:space="preserve">2.57541632652283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61374592781067</t>
+    <t xml:space="preserve">2.61374568939209</t>
   </si>
   <si>
     <t xml:space="preserve">2.60932326316833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58868479728699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58131289482117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53561353683472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48843932151794</t>
+    <t xml:space="preserve">2.58868455886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58131313323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53561329841614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48843955993652</t>
   </si>
   <si>
     <t xml:space="preserve">2.47222352027893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50170731544495</t>
+    <t xml:space="preserve">2.50170707702637</t>
   </si>
   <si>
     <t xml:space="preserve">2.56362295150757</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67123913764954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67418766021729</t>
+    <t xml:space="preserve">2.67123937606812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67418742179871</t>
   </si>
   <si>
     <t xml:space="preserve">2.65502309799194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68450689315796</t>
+    <t xml:space="preserve">2.68450665473938</t>
   </si>
   <si>
     <t xml:space="preserve">2.66239404678345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62406516075134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62996196746826</t>
+    <t xml:space="preserve">2.6240656375885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62996172904968</t>
   </si>
   <si>
     <t xml:space="preserve">2.63733291625977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62111687660217</t>
+    <t xml:space="preserve">2.62111663818359</t>
   </si>
   <si>
     <t xml:space="preserve">2.42210030555725</t>
@@ -1613,7 +1613,7 @@
     <t xml:space="preserve">2.41915225982666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36608171463013</t>
+    <t xml:space="preserve">2.36608147621155</t>
   </si>
   <si>
     <t xml:space="preserve">2.38966846466064</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">2.24667167663574</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23045539855957</t>
+    <t xml:space="preserve">2.23045563697815</t>
   </si>
   <si>
     <t xml:space="preserve">2.22898149490356</t>
@@ -1640,7 +1640,7 @@
     <t xml:space="preserve">2.18033266067505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15674543380737</t>
+    <t xml:space="preserve">2.15674567222595</t>
   </si>
   <si>
     <t xml:space="preserve">2.20244526863098</t>
@@ -1649,43 +1649,43 @@
     <t xml:space="preserve">2.19360041618347</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13905549049377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11399388313293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08745813369751</t>
+    <t xml:space="preserve">2.13905572891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11399412155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08745837211609</t>
   </si>
   <si>
     <t xml:space="preserve">2.0417582988739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00932645797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05207777023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.105149269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05797457695007</t>
+    <t xml:space="preserve">2.00932621955872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05207800865173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10514903068542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05797410011292</t>
   </si>
   <si>
     <t xml:space="preserve">2.05502581596375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09335565567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13610696792603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11694240570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09925246238708</t>
+    <t xml:space="preserve">2.09335589408875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1361072063446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11694264411926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09925222396851</t>
   </si>
   <si>
     <t xml:space="preserve">2.10220098495483</t>
@@ -1694,10 +1694,10 @@
     <t xml:space="preserve">2.10072636604309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09040641784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04912948608398</t>
+    <t xml:space="preserve">2.09040665626526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04912924766541</t>
   </si>
   <si>
     <t xml:space="preserve">2.06829380989075</t>
@@ -1709,91 +1709,91 @@
     <t xml:space="preserve">2.04765510559082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02701640129089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01964569091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97394597530365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97984254360199</t>
+    <t xml:space="preserve">2.02701663970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01964545249939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97394573688507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97984278202057</t>
   </si>
   <si>
     <t xml:space="preserve">1.96215176582336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98426496982574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08008742332458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06387090682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07861304283142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04618120193481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08598375320435</t>
+    <t xml:space="preserve">1.98426520824432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08008718490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06387114524841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07861328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04618096351624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08598399162292</t>
   </si>
   <si>
     <t xml:space="preserve">2.05650043487549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95625483989716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98279118537903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94446110725403</t>
+    <t xml:space="preserve">1.95625507831573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98279082775116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94446134567261</t>
   </si>
   <si>
     <t xml:space="preserve">1.93709051609039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9665744304657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96804821491241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89286530017853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98131656646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91497766971588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87517464160919</t>
+    <t xml:space="preserve">1.96657419204712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9680483341217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89286506175995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98131680488586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91497790813446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87517440319061</t>
   </si>
   <si>
     <t xml:space="preserve">1.87370049953461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94003915786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92677140235901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99311053752899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00342965126038</t>
+    <t xml:space="preserve">1.94003891944885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92677116394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99311006069183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0034294128418</t>
   </si>
   <si>
     <t xml:space="preserve">1.99458432197571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99163603782654</t>
+    <t xml:space="preserve">1.99163627624512</t>
   </si>
   <si>
     <t xml:space="preserve">1.94888401031494</t>
@@ -1802,40 +1802,40 @@
     <t xml:space="preserve">1.88844239711761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87222623825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91940057277679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89433884620667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86485517024994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85306191444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83831918239594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88549399375916</t>
+    <t xml:space="preserve">1.87222647666931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91940033435822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89433932304382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86485540866852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85306179523468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83831942081451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88549423217773</t>
   </si>
   <si>
     <t xml:space="preserve">1.8515876531601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82505142688751</t>
+    <t xml:space="preserve">1.8250515460968</t>
   </si>
   <si>
     <t xml:space="preserve">1.78230023384094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71596133708954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69532251358032</t>
+    <t xml:space="preserve">1.71596109867096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69532263278961</t>
   </si>
   <si>
     <t xml:space="preserve">1.71006453037262</t>
@@ -1844,34 +1844,34 @@
     <t xml:space="preserve">1.73217809200287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78377461433411</t>
+    <t xml:space="preserve">1.78377437591553</t>
   </si>
   <si>
     <t xml:space="preserve">1.76313591003418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76166188716888</t>
+    <t xml:space="preserve">1.76166152954102</t>
   </si>
   <si>
     <t xml:space="preserve">1.78672301769257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80588710308075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83389711380005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87664890289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86927819252014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84569025039673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8397935628891</t>
+    <t xml:space="preserve">1.80588722229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83389687538147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87664914131165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86927783489227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84568989276886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83979368209839</t>
   </si>
   <si>
     <t xml:space="preserve">1.83242237567902</t>
@@ -1880,37 +1880,37 @@
     <t xml:space="preserve">1.84274184703827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83684527873993</t>
+    <t xml:space="preserve">1.83684492111206</t>
   </si>
   <si>
     <t xml:space="preserve">1.8972874879837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88991665840149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88254570960999</t>
+    <t xml:space="preserve">1.88991689682007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88254547119141</t>
   </si>
   <si>
     <t xml:space="preserve">1.91055500507355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87075197696686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80293893814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80441308021545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79114508628845</t>
+    <t xml:space="preserve">1.87075221538544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80293881893158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80441284179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79114556312561</t>
   </si>
   <si>
     <t xml:space="preserve">1.75576496124268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81325829029083</t>
+    <t xml:space="preserve">1.81325817108154</t>
   </si>
   <si>
     <t xml:space="preserve">1.81178390979767</t>
@@ -1919,37 +1919,37 @@
     <t xml:space="preserve">1.83537101745605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79556798934937</t>
+    <t xml:space="preserve">1.79556810855865</t>
   </si>
   <si>
     <t xml:space="preserve">1.77492940425873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80883550643921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79851627349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79704236984253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8073616027832</t>
+    <t xml:space="preserve">1.80883538722992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79851639270782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79704225063324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80736148357391</t>
   </si>
   <si>
     <t xml:space="preserve">1.78082621097565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75429081916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7130126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70711612701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74544548988342</t>
+    <t xml:space="preserve">1.75429093837738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71301281452179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70711624622345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74544560909271</t>
   </si>
   <si>
     <t xml:space="preserve">1.76460993289948</t>
@@ -1964,7 +1964,7 @@
     <t xml:space="preserve">1.78819692134857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74839389324188</t>
+    <t xml:space="preserve">1.74839401245117</t>
   </si>
   <si>
     <t xml:space="preserve">1.66583895683289</t>
@@ -1973,7 +1973,7 @@
     <t xml:space="preserve">1.67910659313202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61129379272461</t>
+    <t xml:space="preserve">1.6112939119339</t>
   </si>
   <si>
     <t xml:space="preserve">1.57886123657227</t>
@@ -1988,7 +1988,7 @@
     <t xml:space="preserve">1.54200661182404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53445518016815</t>
+    <t xml:space="preserve">1.53445506095886</t>
   </si>
   <si>
     <t xml:space="preserve">1.53596544265747</t>
@@ -1997,10 +1997,10 @@
     <t xml:space="preserve">1.56466090679169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54351687431335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55559897422791</t>
+    <t xml:space="preserve">1.54351699352264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55559921264648</t>
   </si>
   <si>
     <t xml:space="preserve">1.5389860868454</t>
@@ -2012,7 +2012,7 @@
     <t xml:space="preserve">1.60543847084045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58429443836212</t>
+    <t xml:space="preserve">1.58429455757141</t>
   </si>
   <si>
     <t xml:space="preserve">1.56768143177032</t>
@@ -2027,28 +2027,28 @@
     <t xml:space="preserve">1.51028990745544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51935243606567</t>
+    <t xml:space="preserve">1.51935231685638</t>
   </si>
   <si>
     <t xml:space="preserve">1.52690386772156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4717777967453</t>
+    <t xml:space="preserve">1.47177791595459</t>
   </si>
   <si>
     <t xml:space="preserve">1.47026753425598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47102272510529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45138907432556</t>
+    <t xml:space="preserve">1.471022605896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45138895511627</t>
   </si>
   <si>
     <t xml:space="preserve">1.46875727176666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49367690086365</t>
+    <t xml:space="preserve">1.49367678165436</t>
   </si>
   <si>
     <t xml:space="preserve">1.48385989665985</t>
@@ -2057,25 +2057,25 @@
     <t xml:space="preserve">1.50047302246094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45894038677216</t>
+    <t xml:space="preserve">1.45894026756287</t>
   </si>
   <si>
     <t xml:space="preserve">1.46800208091736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48990118503571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48234987258911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4808394908905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53294491767883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57523274421692</t>
+    <t xml:space="preserve">1.489901304245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48234975337982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48083961009979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53294503688812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57523286342621</t>
   </si>
   <si>
     <t xml:space="preserve">1.56315040588379</t>
@@ -2084,10 +2084,10 @@
     <t xml:space="preserve">1.52539360523224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50424873828888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47328805923462</t>
+    <t xml:space="preserve">1.50424885749817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47328794002533</t>
   </si>
   <si>
     <t xml:space="preserve">1.47253286838531</t>
@@ -2111,31 +2111,31 @@
     <t xml:space="preserve">1.4377965927124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42269372940063</t>
+    <t xml:space="preserve">1.42269361019135</t>
   </si>
   <si>
     <t xml:space="preserve">1.42042827606201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4272243976593</t>
+    <t xml:space="preserve">1.42722451686859</t>
   </si>
   <si>
     <t xml:space="preserve">1.41665256023407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40683579444885</t>
+    <t xml:space="preserve">1.40683567523956</t>
   </si>
   <si>
     <t xml:space="preserve">1.400794506073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39097762107849</t>
+    <t xml:space="preserve">1.39097774028778</t>
   </si>
   <si>
     <t xml:space="preserve">1.3864461183548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28374683856964</t>
+    <t xml:space="preserve">1.28374695777893</t>
   </si>
   <si>
     <t xml:space="preserve">1.25354063510895</t>
@@ -2147,16 +2147,16 @@
     <t xml:space="preserve">1.20068073272705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23617231845856</t>
+    <t xml:space="preserve">1.23617243766785</t>
   </si>
   <si>
     <t xml:space="preserve">1.25278532505035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22182464599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23088622093201</t>
+    <t xml:space="preserve">1.2218245267868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2308863401413</t>
   </si>
   <si>
     <t xml:space="preserve">1.27695071697235</t>
@@ -2177,49 +2177,49 @@
     <t xml:space="preserve">1.28223657608032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28752255439758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35775077342987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38342559337616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37436378002167</t>
+    <t xml:space="preserve">1.28752267360687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35775065422058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38342547416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37436389923096</t>
   </si>
   <si>
     <t xml:space="preserve">1.35246479511261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4098562002182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39852917194366</t>
+    <t xml:space="preserve">1.40985631942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39852929115295</t>
   </si>
   <si>
     <t xml:space="preserve">1.36681246757507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35095453262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35926103591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36454689502716</t>
+    <t xml:space="preserve">1.350954413414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35926115512848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36454701423645</t>
   </si>
   <si>
     <t xml:space="preserve">1.33736193180084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30262553691864</t>
+    <t xml:space="preserve">1.30262541770935</t>
   </si>
   <si>
     <t xml:space="preserve">1.2897881269455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26109278202057</t>
+    <t xml:space="preserve">1.26109266281128</t>
   </si>
   <si>
     <t xml:space="preserve">1.26864409446716</t>
@@ -2228,10 +2228,10 @@
     <t xml:space="preserve">1.25505077838898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27468514442444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27997124195099</t>
+    <t xml:space="preserve">1.27468526363373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27997136116028</t>
   </si>
   <si>
     <t xml:space="preserve">1.25958168506622</t>
@@ -2255,19 +2255,19 @@
     <t xml:space="preserve">1.36077117919922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38871228694916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38267040252686</t>
+    <t xml:space="preserve">1.38871240615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38267052173615</t>
   </si>
   <si>
     <t xml:space="preserve">1.3517097234726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35699558258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3615266084671</t>
+    <t xml:space="preserve">1.35699570178986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36152637004852</t>
   </si>
   <si>
     <t xml:space="preserve">1.36228168010712</t>
@@ -2276,19 +2276,19 @@
     <t xml:space="preserve">1.34113776683807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36756765842438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42495906352997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41740763187408</t>
+    <t xml:space="preserve">1.36756753921509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42495894432068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41740751266479</t>
   </si>
   <si>
     <t xml:space="preserve">1.43326556682587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40532553195953</t>
+    <t xml:space="preserve">1.40532541275024</t>
   </si>
   <si>
     <t xml:space="preserve">1.43477582931519</t>
@@ -2297,7 +2297,7 @@
     <t xml:space="preserve">1.62960290908813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58278405666351</t>
+    <t xml:space="preserve">1.5827841758728</t>
   </si>
   <si>
     <t xml:space="preserve">1.57825338840485</t>
@@ -2306,19 +2306,19 @@
     <t xml:space="preserve">1.58127391338348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54653763771057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53747582435608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52237296104431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55257868766785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60241782665253</t>
+    <t xml:space="preserve">1.54653751850128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53747594356537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52237284183502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55257856845856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60241794586182</t>
   </si>
   <si>
     <t xml:space="preserve">1.63111317157745</t>
@@ -2327,34 +2327,34 @@
     <t xml:space="preserve">1.6009076833725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62054133415222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54955792427063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57221245765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61147952079773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.641685962677</t>
+    <t xml:space="preserve">1.62054145336151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54955804347992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57221233844757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61147940158844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64168608188629</t>
   </si>
   <si>
     <t xml:space="preserve">1.61298990249634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.617520570755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59184598922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58731508255005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6190310716629</t>
+    <t xml:space="preserve">1.61752068996429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59184610843658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58731520175934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61903095245361</t>
   </si>
   <si>
     <t xml:space="preserve">1.57976377010345</t>
@@ -2363,10 +2363,10 @@
     <t xml:space="preserve">1.56013000011444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55861985683441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59788691997528</t>
+    <t xml:space="preserve">1.55861973762512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59788703918457</t>
   </si>
   <si>
     <t xml:space="preserve">1.60392808914185</t>
@@ -2375,7 +2375,7 @@
     <t xml:space="preserve">1.58580482006073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59939730167389</t>
+    <t xml:space="preserve">1.59939742088318</t>
   </si>
   <si>
     <t xml:space="preserve">1.59637677669525</t>
@@ -2384,13 +2384,13 @@
     <t xml:space="preserve">1.59033560752869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52992463111877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51331114768982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50953495502472</t>
+    <t xml:space="preserve">1.5299243927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51331126689911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50953483581543</t>
   </si>
   <si>
     <t xml:space="preserve">1.52388322353363</t>
@@ -2402,7 +2402,7 @@
     <t xml:space="preserve">1.63866472244263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75948822498322</t>
+    <t xml:space="preserve">1.75948810577393</t>
   </si>
   <si>
     <t xml:space="preserve">1.806307554245</t>
@@ -2411,31 +2411,31 @@
     <t xml:space="preserve">1.78365314006805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83953368663788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02983045578003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06909799575806</t>
+    <t xml:space="preserve">1.83953356742859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02983069419861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06909823417664</t>
   </si>
   <si>
     <t xml:space="preserve">1.94827461242676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89088344573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7791223526001</t>
+    <t xml:space="preserve">1.89088296890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77912247180939</t>
   </si>
   <si>
     <t xml:space="preserve">1.77308118343353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81687963008881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70813846588135</t>
+    <t xml:space="preserve">1.81687951087952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70813834667206</t>
   </si>
   <si>
     <t xml:space="preserve">1.4800843000412</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">1.24070310592651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19917058944702</t>
+    <t xml:space="preserve">1.19917047023773</t>
   </si>
   <si>
     <t xml:space="preserve">1.18406772613525</t>
@@ -2459,43 +2459,43 @@
     <t xml:space="preserve">0.959789276123047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995281040668488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91901171207428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945441722869873</t>
+    <t xml:space="preserve">0.995280921459198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919011771678925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945441484451294</t>
   </si>
   <si>
     <t xml:space="preserve">0.962809860706329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01869094371796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04361069202423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990750074386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07155084609985</t>
+    <t xml:space="preserve">1.01869106292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04361057281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990749955177307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07155072689056</t>
   </si>
   <si>
     <t xml:space="preserve">1.07910239696503</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0677752494812</t>
+    <t xml:space="preserve">1.06777513027191</t>
   </si>
   <si>
     <t xml:space="preserve">1.01944613456726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999811708927155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04134523868561</t>
+    <t xml:space="preserve">0.999811828136444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0413453578949</t>
   </si>
   <si>
     <t xml:space="preserve">1.02699756622314</t>
@@ -2504,7 +2504,7 @@
     <t xml:space="preserve">1.10628736019135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0572030544281</t>
+    <t xml:space="preserve">1.05720329284668</t>
   </si>
   <si>
     <t xml:space="preserve">1.11459386348724</t>
@@ -2513,16 +2513,16 @@
     <t xml:space="preserve">1.13875913619995</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20219111442566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16745460033417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16594409942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08740878105164</t>
+    <t xml:space="preserve">1.20219099521637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16745448112488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16594421863556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08740890026093</t>
   </si>
   <si>
     <t xml:space="preserve">1.0670200586319</t>
@@ -2531,10 +2531,10 @@
     <t xml:space="preserve">1.09420502185822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06324422359467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09496009349823</t>
+    <t xml:space="preserve">1.06324434280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09496021270752</t>
   </si>
   <si>
     <t xml:space="preserve">1.07834708690643</t>
@@ -2546,13 +2546,13 @@
     <t xml:space="preserve">1.07457137107849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08665382862091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09269499778748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03756952285767</t>
+    <t xml:space="preserve">1.08665370941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09269487857819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03756964206696</t>
   </si>
   <si>
     <t xml:space="preserve">1.07306110858917</t>
@@ -2570,7 +2570,7 @@
     <t xml:space="preserve">1.04285562038422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01189494132996</t>
+    <t xml:space="preserve">1.01189482212067</t>
   </si>
   <si>
     <t xml:space="preserve">0.985464036464691</t>
@@ -2579,22 +2579,22 @@
     <t xml:space="preserve">0.970361292362213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989239811897278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943176209926605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926563084125519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921277046203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913725733757019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986219048500061</t>
+    <t xml:space="preserve">0.989239692687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94317626953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926563024520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921277105808258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913725674152374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98621928691864</t>
   </si>
   <si>
     <t xml:space="preserve">0.997546315193176</t>
@@ -2606,10 +2606,10 @@
     <t xml:space="preserve">1.09722566604614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1025116443634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13422763347626</t>
+    <t xml:space="preserve">1.10251152515411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13422775268555</t>
   </si>
   <si>
     <t xml:space="preserve">1.18180215358734</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">1.19992554187775</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18935370445251</t>
+    <t xml:space="preserve">1.18935358524323</t>
   </si>
   <si>
     <t xml:space="preserve">1.14782083034515</t>
@@ -2645,16 +2645,16 @@
     <t xml:space="preserve">1.17047512531281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24598920345306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29280877113342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36303675174713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40381503105164</t>
+    <t xml:space="preserve">1.24598908424377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29280865192413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36303687095642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40381491184235</t>
   </si>
   <si>
     <t xml:space="preserve">1.41136658191681</t>
@@ -2669,34 +2669,34 @@
     <t xml:space="preserve">1.40154981613159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40305995941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41589725017548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49292171001434</t>
+    <t xml:space="preserve">1.40306007862091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41589748859406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49292182922363</t>
   </si>
   <si>
     <t xml:space="preserve">1.44836843013763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48763573169708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47630870342255</t>
+    <t xml:space="preserve">1.48763561248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47630858421326</t>
   </si>
   <si>
     <t xml:space="preserve">1.46498155593872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39626359939575</t>
+    <t xml:space="preserve">1.39626371860504</t>
   </si>
   <si>
     <t xml:space="preserve">1.37662935256958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34264802932739</t>
+    <t xml:space="preserve">1.3426479101181</t>
   </si>
   <si>
     <t xml:space="preserve">1.3690779209137</t>
@@ -2705,49 +2705,49 @@
     <t xml:space="preserve">1.43175530433655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.445347905159</t>
+    <t xml:space="preserve">1.44534778594971</t>
   </si>
   <si>
     <t xml:space="preserve">1.47479844093323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48461520671844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55106842517853</t>
+    <t xml:space="preserve">1.48461532592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55106854438782</t>
   </si>
   <si>
     <t xml:space="preserve">1.5208625793457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37889468669891</t>
+    <t xml:space="preserve">1.37889456748962</t>
   </si>
   <si>
     <t xml:space="preserve">1.3781396150589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34415805339813</t>
+    <t xml:space="preserve">1.34415817260742</t>
   </si>
   <si>
     <t xml:space="preserve">1.37209844589233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39475345611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37964999675751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38795721530914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39248788356781</t>
+    <t xml:space="preserve">1.39475333690643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37964987754822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38795709609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3924880027771</t>
   </si>
   <si>
     <t xml:space="preserve">1.32150399684906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31848335266113</t>
+    <t xml:space="preserve">1.31848359107971</t>
   </si>
   <si>
     <t xml:space="preserve">1.34340298175812</t>
@@ -2756,7 +2756,7 @@
     <t xml:space="preserve">1.30036008358002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32376956939697</t>
+    <t xml:space="preserve">1.32376933097839</t>
   </si>
   <si>
     <t xml:space="preserve">1.3343414068222</t>
@@ -2765,10 +2765,10 @@
     <t xml:space="preserve">1.39777398109436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.369833111763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38191509246826</t>
+    <t xml:space="preserve">1.36983299255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38191521167755</t>
   </si>
   <si>
     <t xml:space="preserve">1.34038257598877</t>
@@ -2777,25 +2777,25 @@
     <t xml:space="preserve">1.35473024845123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31772828102112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33207595348358</t>
+    <t xml:space="preserve">1.31772840023041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33207607269287</t>
   </si>
   <si>
     <t xml:space="preserve">1.33585166931152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27393007278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26486849784851</t>
+    <t xml:space="preserve">1.27393019199371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26486837863922</t>
   </si>
   <si>
     <t xml:space="preserve">1.22484529018402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24145829677582</t>
+    <t xml:space="preserve">1.24145841598511</t>
   </si>
   <si>
     <t xml:space="preserve">1.11761450767517</t>
@@ -2804,7 +2804,7 @@
     <t xml:space="preserve">1.10779774188995</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13800406455994</t>
+    <t xml:space="preserve">1.13800394535065</t>
   </si>
   <si>
     <t xml:space="preserve">1.22711062431335</t>
@@ -2819,43 +2819,43 @@
     <t xml:space="preserve">1.22862100601196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44232726097107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43251061439514</t>
+    <t xml:space="preserve">1.44232738018036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43251037597656</t>
   </si>
   <si>
     <t xml:space="preserve">1.50273859500885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55408895015717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81234848499298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78214299678802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77459168434143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75797772407532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.693035364151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7217310667038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68548429012299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70209729671478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70360743999481</t>
+    <t xml:space="preserve">1.55408883094788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81234860420227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78214287757874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77459156513214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75797760486603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69303548336029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72173094749451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6854841709137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70209717750549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70360767841339</t>
   </si>
   <si>
     <t xml:space="preserve">1.73079264163971</t>
@@ -2864,70 +2864,73 @@
     <t xml:space="preserve">1.72777211666107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69907653331757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66887104511261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66282999515533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67944288253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66131949424744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67642247676849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64470648765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61601054668427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63564419746399</t>
+    <t xml:space="preserve">1.69907665252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6688711643219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66282987594604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67944300174713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66131961345673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67642259597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64470660686493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61601042747498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63564395904541</t>
   </si>
   <si>
     <t xml:space="preserve">1.65829908847809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66585052013397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66434013843536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74438524246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77761209011078</t>
+    <t xml:space="preserve">1.66585063934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66434025764465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74438536167145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77761220932007</t>
   </si>
   <si>
     <t xml:space="preserve">1.756467461586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72022068500519</t>
+    <t xml:space="preserve">1.72022044658661</t>
   </si>
   <si>
     <t xml:space="preserve">1.73683369159698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6945458650589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65225803852081</t>
+    <t xml:space="preserve">1.69454574584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65225791931152</t>
   </si>
   <si>
     <t xml:space="preserve">1.67491221427917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65376830101013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63715434074402</t>
+    <t xml:space="preserve">1.65376818180084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63715422153473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54200649261475</t>
   </si>
   <si>
     <t xml:space="preserve">1.57070183753967</t>
@@ -2936,67 +2939,67 @@
     <t xml:space="preserve">1.59486651420593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62205159664154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74740564823151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88635241985321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85765707492828</t>
+    <t xml:space="preserve">1.62205147743225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74740552902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8863525390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85765719413757</t>
   </si>
   <si>
     <t xml:space="preserve">1.88031125068665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86822915077209</t>
+    <t xml:space="preserve">1.86822891235352</t>
   </si>
   <si>
     <t xml:space="preserve">1.85463643074036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88937318325043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85010552406311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80932807922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83047211170197</t>
+    <t xml:space="preserve">1.88937294483185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8501056432724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80932819843292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83047223091125</t>
   </si>
   <si>
     <t xml:space="preserve">1.82141017913818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81838977336884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82594120502472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80781757831573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80177640914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84557461738586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83500254154205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82745146751404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87124967575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86369800567627</t>
+    <t xml:space="preserve">1.81838965415955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82594108581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80781745910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80177652835846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84557473659515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83500266075134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82745134830475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87124943733215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86369788646698</t>
   </si>
   <si>
     <t xml:space="preserve">1.927130818367</t>
@@ -3008,16 +3011,16 @@
     <t xml:space="preserve">2.05399513244629</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13706040382385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18085956573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15216422080994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12950897216797</t>
+    <t xml:space="preserve">2.13706064224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18085932731628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15216398239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12950921058655</t>
   </si>
   <si>
     <t xml:space="preserve">2.1068549156189</t>
@@ -3026,34 +3029,34 @@
     <t xml:space="preserve">2.15518474578857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1355504989624</t>
+    <t xml:space="preserve">2.13555026054382</t>
   </si>
   <si>
     <t xml:space="preserve">2.13857126235962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22465753555298</t>
+    <t xml:space="preserve">2.2246572971344</t>
   </si>
   <si>
     <t xml:space="preserve">2.15669536590576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18992114067078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18690085411072</t>
+    <t xml:space="preserve">2.18992137908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18690061569214</t>
   </si>
   <si>
     <t xml:space="preserve">2.16877722740173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17028760910034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2352294921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24731183052063</t>
+    <t xml:space="preserve">2.17028784751892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23522973060608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24731206893921</t>
   </si>
   <si>
     <t xml:space="preserve">2.26996684074402</t>
@@ -3068,19 +3071,19 @@
     <t xml:space="preserve">2.2458016872406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24882245063782</t>
+    <t xml:space="preserve">2.24882221221924</t>
   </si>
   <si>
     <t xml:space="preserve">2.36964535713196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39985203742981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48140692710876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54937028884888</t>
+    <t xml:space="preserve">2.39985179901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48140716552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54937052726746</t>
   </si>
   <si>
     <t xml:space="preserve">2.64300799369812</t>
@@ -3092,28 +3095,28 @@
     <t xml:space="preserve">2.60223031044006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70190978050232</t>
+    <t xml:space="preserve">2.7019100189209</t>
   </si>
   <si>
     <t xml:space="preserve">2.73815655708313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78648614883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88616490364075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86502122879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86200022697449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94204592704773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94506669044495</t>
+    <t xml:space="preserve">2.78648638725281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88616466522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86502075195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86200046539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94204616546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94506645202637</t>
   </si>
   <si>
     <t xml:space="preserve">2.93147397041321</t>
@@ -3122,13 +3125,13 @@
     <t xml:space="preserve">2.97980308532715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96621060371399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95714855194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97829270362854</t>
+    <t xml:space="preserve">2.96621036529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95714902877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97829294204712</t>
   </si>
   <si>
     <t xml:space="preserve">3.08411288261414</t>
@@ -3137,13 +3140,13 @@
     <t xml:space="preserve">3.07337760925293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05804085731506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15312552452087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09178066253662</t>
+    <t xml:space="preserve">3.05804061889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15312528610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09178042411804</t>
   </si>
   <si>
     <t xml:space="preserve">3.11478519439697</t>
@@ -3152,7 +3155,7 @@
     <t xml:space="preserve">3.19299960136414</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21600413322449</t>
+    <t xml:space="preserve">3.21600437164307</t>
   </si>
   <si>
     <t xml:space="preserve">3.18839836120605</t>
@@ -3161,7 +3164,7 @@
     <t xml:space="preserve">3.17459583282471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12858772277832</t>
+    <t xml:space="preserve">3.12858748435974</t>
   </si>
   <si>
     <t xml:space="preserve">3.06264162063599</t>
@@ -3191,28 +3194,28 @@
     <t xml:space="preserve">2.80192589759827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80039215087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73598051071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7942578792572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79272413253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83719944953918</t>
+    <t xml:space="preserve">2.80039238929749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73598027229309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79425811767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79272437095642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83719968795776</t>
   </si>
   <si>
     <t xml:space="preserve">2.76665282249451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80499291419983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79119062423706</t>
+    <t xml:space="preserve">2.80499315261841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79119038581848</t>
   </si>
   <si>
     <t xml:space="preserve">2.85713672637939</t>
@@ -3221,13 +3224,13 @@
     <t xml:space="preserve">2.78198885917664</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7513165473938</t>
+    <t xml:space="preserve">2.75131678581238</t>
   </si>
   <si>
     <t xml:space="preserve">2.72371172904968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84333443641663</t>
+    <t xml:space="preserve">2.84333419799805</t>
   </si>
   <si>
     <t xml:space="preserve">2.79579138755798</t>
@@ -3248,16 +3251,16 @@
     <t xml:space="preserve">2.66543364524841</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73291349411011</t>
+    <t xml:space="preserve">2.73291325569153</t>
   </si>
   <si>
     <t xml:space="preserve">2.75745129585266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78352236747742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92614936828613</t>
+    <t xml:space="preserve">2.783522605896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92614912986755</t>
   </si>
   <si>
     <t xml:space="preserve">2.88934254646301</t>
@@ -3266,7 +3269,7 @@
     <t xml:space="preserve">2.94301891326904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90774583816528</t>
+    <t xml:space="preserve">2.9077455997467</t>
   </si>
   <si>
     <t xml:space="preserve">2.85100197792053</t>
@@ -3278,19 +3281,19 @@
     <t xml:space="preserve">2.85867023468018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83873319625854</t>
+    <t xml:space="preserve">2.83873343467712</t>
   </si>
   <si>
     <t xml:space="preserve">2.84486770629883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91848134994507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95222139358521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90467858314514</t>
+    <t xml:space="preserve">2.91848111152649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95222115516663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90467882156372</t>
   </si>
   <si>
     <t xml:space="preserve">2.96755766868591</t>
@@ -3299,13 +3302,13 @@
     <t xml:space="preserve">2.92768287658691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92461538314819</t>
+    <t xml:space="preserve">2.92461562156677</t>
   </si>
   <si>
     <t xml:space="preserve">2.83566617965698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86173725128174</t>
+    <t xml:space="preserve">2.86173748970032</t>
   </si>
   <si>
     <t xml:space="preserve">2.84640145301819</t>
@@ -3314,19 +3317,19 @@
     <t xml:space="preserve">2.87860727310181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89854407310486</t>
+    <t xml:space="preserve">2.89854431152344</t>
   </si>
   <si>
     <t xml:space="preserve">2.99976348876953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00743174552917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98289394378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98596096038818</t>
+    <t xml:space="preserve">3.0074315071106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98289370536804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98596119880676</t>
   </si>
   <si>
     <t xml:space="preserve">2.95375514030457</t>
@@ -3344,10 +3347,10 @@
     <t xml:space="preserve">2.90007758140564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84180068969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8740062713623</t>
+    <t xml:space="preserve">2.84180045127869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87400650978088</t>
   </si>
   <si>
     <t xml:space="preserve">2.81726264953613</t>
@@ -3362,19 +3365,19 @@
     <t xml:space="preserve">2.76972007751465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70224118232727</t>
+    <t xml:space="preserve">2.70224142074585</t>
   </si>
   <si>
     <t xml:space="preserve">2.70530819892883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79732513427734</t>
+    <t xml:space="preserve">2.79732489585876</t>
   </si>
   <si>
     <t xml:space="preserve">2.80652666091919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81419467926025</t>
+    <t xml:space="preserve">2.81419491767883</t>
   </si>
   <si>
     <t xml:space="preserve">2.78045535087585</t>
@@ -3386,13 +3389,13 @@
     <t xml:space="preserve">2.84793496131897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82339715957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93075037002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90314507484436</t>
+    <t xml:space="preserve">2.82339692115784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93075013160706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90314531326294</t>
   </si>
   <si>
     <t xml:space="preserve">2.88320803642273</t>
@@ -3404,7 +3407,7 @@
     <t xml:space="preserve">2.87554001808167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90621256828308</t>
+    <t xml:space="preserve">2.9062123298645</t>
   </si>
   <si>
     <t xml:space="preserve">2.95528864860535</t>
@@ -3413,31 +3416,31 @@
     <t xml:space="preserve">2.97522568702698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98902797698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.950688123703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99669623374939</t>
+    <t xml:space="preserve">2.98902821540833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95068788528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99669647216797</t>
   </si>
   <si>
     <t xml:space="preserve">3.02890205383301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03657007217407</t>
+    <t xml:space="preserve">3.03656983375549</t>
   </si>
   <si>
     <t xml:space="preserve">2.92001485824585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93535089492798</t>
+    <t xml:space="preserve">2.9353506565094</t>
   </si>
   <si>
     <t xml:space="preserve">2.88014078140259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91234660148621</t>
+    <t xml:space="preserve">2.91234683990479</t>
   </si>
   <si>
     <t xml:space="preserve">2.98135995864868</t>
@@ -3446,7 +3449,7 @@
     <t xml:space="preserve">3.03350281715393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94915390014648</t>
+    <t xml:space="preserve">2.94915413856506</t>
   </si>
   <si>
     <t xml:space="preserve">2.85560321807861</t>
@@ -3461,16 +3464,16 @@
     <t xml:space="preserve">2.77432084083557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69917368888855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70684194564819</t>
+    <t xml:space="preserve">2.69917392730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70684170722961</t>
   </si>
   <si>
     <t xml:space="preserve">2.66083288192749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76051831245422</t>
+    <t xml:space="preserve">2.76051807403564</t>
   </si>
   <si>
     <t xml:space="preserve">2.71144270896912</t>
@@ -3482,13 +3485,13 @@
     <t xml:space="preserve">2.73137974739075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62249231338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65009760856628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6777024269104</t>
+    <t xml:space="preserve">2.62249255180359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65009737014771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67770266532898</t>
   </si>
   <si>
     <t xml:space="preserve">2.67463541030884</t>
@@ -3512,16 +3515,13 @@
     <t xml:space="preserve">2.75438380241394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8249306678772</t>
+    <t xml:space="preserve">2.82493090629578</t>
   </si>
   <si>
     <t xml:space="preserve">2.85406947135925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89701080322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97829294204712</t>
+    <t xml:space="preserve">2.89701056480408</t>
   </si>
   <si>
     <t xml:space="preserve">2.86327123641968</t>
@@ -3536,19 +3536,19 @@
     <t xml:space="preserve">3.02736854553223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89087605476379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74058127403259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78505611419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86480474472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82799792289734</t>
+    <t xml:space="preserve">2.89087629318237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74058151245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7850558757782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86480450630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82799816131592</t>
   </si>
   <si>
     <t xml:space="preserve">2.97062468528748</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">2.92445588111877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90142893791199</t>
+    <t xml:space="preserve">2.90142869949341</t>
   </si>
   <si>
     <t xml:space="preserve">3.05187344551086</t>
@@ -3566,13 +3566,13 @@
     <t xml:space="preserve">3.07029509544373</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15472841262817</t>
+    <t xml:space="preserve">3.15472817420959</t>
   </si>
   <si>
     <t xml:space="preserve">3.08871674537659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19771218299866</t>
+    <t xml:space="preserve">3.19771242141724</t>
   </si>
   <si>
     <t xml:space="preserve">3.21459913253784</t>
@@ -3581,10 +3581,10 @@
     <t xml:space="preserve">3.18850111961365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25297737121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16547417640686</t>
+    <t xml:space="preserve">3.2529776096344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16547441482544</t>
   </si>
   <si>
     <t xml:space="preserve">3.09485745429993</t>
@@ -3605,13 +3605,13 @@
     <t xml:space="preserve">2.55602049827576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58979368209839</t>
+    <t xml:space="preserve">2.58979392051697</t>
   </si>
   <si>
     <t xml:space="preserve">2.54066896438599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25359630584717</t>
+    <t xml:space="preserve">2.25359654426575</t>
   </si>
   <si>
     <t xml:space="preserve">2.24592089653015</t>
@@ -3626,7 +3626,7 @@
     <t xml:space="preserve">2.40557622909546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42860341072083</t>
+    <t xml:space="preserve">2.42860317230225</t>
   </si>
   <si>
     <t xml:space="preserve">2.52992296218872</t>
@@ -3641,7 +3641,7 @@
     <t xml:space="preserve">2.72488689422607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76326560974121</t>
+    <t xml:space="preserve">2.76326537132263</t>
   </si>
   <si>
     <t xml:space="preserve">2.78015208244324</t>
@@ -3686,7 +3686,7 @@
     <t xml:space="preserve">2.79857397079468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93366670608521</t>
+    <t xml:space="preserve">2.93366694450378</t>
   </si>
   <si>
     <t xml:space="preserve">2.94594812393188</t>
@@ -3695,19 +3695,19 @@
     <t xml:space="preserve">2.87226104736328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93980741500854</t>
+    <t xml:space="preserve">2.93980717658997</t>
   </si>
   <si>
     <t xml:space="preserve">2.88607740402222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96590518951416</t>
+    <t xml:space="preserve">2.96590495109558</t>
   </si>
   <si>
     <t xml:space="preserve">2.95208859443665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90603423118591</t>
+    <t xml:space="preserve">2.90603446960449</t>
   </si>
   <si>
     <t xml:space="preserve">2.92752599716187</t>
@@ -3719,7 +3719,7 @@
     <t xml:space="preserve">2.90296387672424</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90756964683533</t>
+    <t xml:space="preserve">2.90756940841675</t>
   </si>
   <si>
     <t xml:space="preserve">2.7908980846405</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">2.68343782424927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78168702125549</t>
+    <t xml:space="preserve">2.78168725967407</t>
   </si>
   <si>
     <t xml:space="preserve">2.80624938011169</t>
@@ -3743,16 +3743,16 @@
     <t xml:space="preserve">2.82467126846313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81853055953979</t>
+    <t xml:space="preserve">2.81853079795837</t>
   </si>
   <si>
     <t xml:space="preserve">2.88147187232971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86151480674744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85230422019958</t>
+    <t xml:space="preserve">2.86151504516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85230398178101</t>
   </si>
   <si>
     <t xml:space="preserve">2.81239032745361</t>
@@ -5991,6 +5991,9 @@
   </si>
   <si>
     <t xml:space="preserve">15.3050003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3100004196167</t>
   </si>
 </sst>
 </file>
@@ -39809,7 +39812,7 @@
         <v>2.03996992111206</v>
       </c>
       <c r="G1288" t="s">
-        <v>657</v>
+        <v>972</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -39835,7 +39838,7 @@
         <v>2.07793188095093</v>
       </c>
       <c r="G1289" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -39913,7 +39916,7 @@
         <v>2.10989999771118</v>
       </c>
       <c r="G1292" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -39939,7 +39942,7 @@
         <v>2.14586400985718</v>
       </c>
       <c r="G1293" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -39991,7 +39994,7 @@
         <v>2.31169891357422</v>
       </c>
       <c r="G1295" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -40017,7 +40020,7 @@
         <v>2.49551606178284</v>
       </c>
       <c r="G1296" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -40043,7 +40046,7 @@
         <v>2.45755410194397</v>
       </c>
       <c r="G1297" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -40069,7 +40072,7 @@
         <v>2.48752403259277</v>
       </c>
       <c r="G1298" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -40095,7 +40098,7 @@
         <v>2.47153997421265</v>
       </c>
       <c r="G1299" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -40121,7 +40124,7 @@
         <v>2.48752403259277</v>
       </c>
       <c r="G1300" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -40147,7 +40150,7 @@
         <v>2.45355796813965</v>
       </c>
       <c r="G1301" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -40173,7 +40176,7 @@
         <v>2.49951195716858</v>
       </c>
       <c r="G1302" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -40199,7 +40202,7 @@
         <v>2.44756388664246</v>
       </c>
       <c r="G1303" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -40225,7 +40228,7 @@
         <v>2.39361810684204</v>
       </c>
       <c r="G1304" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -40251,7 +40254,7 @@
         <v>2.42159008979797</v>
       </c>
       <c r="G1305" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -40277,7 +40280,7 @@
         <v>2.40960192680359</v>
       </c>
       <c r="G1306" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -40303,7 +40306,7 @@
         <v>2.40560603141785</v>
       </c>
       <c r="G1307" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -40329,7 +40332,7 @@
         <v>2.41559600830078</v>
       </c>
       <c r="G1308" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -40355,7 +40358,7 @@
         <v>2.39161992073059</v>
       </c>
       <c r="G1309" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -40381,7 +40384,7 @@
         <v>2.38362789154053</v>
       </c>
       <c r="G1310" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -40407,7 +40410,7 @@
         <v>2.44157004356384</v>
       </c>
       <c r="G1311" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -40433,7 +40436,7 @@
         <v>2.42758393287659</v>
       </c>
       <c r="G1312" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -40459,7 +40462,7 @@
         <v>2.44157004356384</v>
       </c>
       <c r="G1313" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -40485,7 +40488,7 @@
         <v>2.41759395599365</v>
       </c>
       <c r="G1314" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -40511,7 +40514,7 @@
         <v>2.44756388664246</v>
       </c>
       <c r="G1315" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -40537,7 +40540,7 @@
         <v>2.47553610801697</v>
       </c>
       <c r="G1316" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -40563,7 +40566,7 @@
         <v>2.47153997421265</v>
       </c>
       <c r="G1317" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -40589,7 +40592,7 @@
         <v>2.46554589271545</v>
       </c>
       <c r="G1318" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -40615,7 +40618,7 @@
         <v>2.54946303367615</v>
       </c>
       <c r="G1319" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -40641,7 +40644,7 @@
         <v>2.61939311027527</v>
       </c>
       <c r="G1320" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -40667,7 +40670,7 @@
         <v>2.71729588508606</v>
       </c>
       <c r="G1321" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -40693,7 +40696,7 @@
         <v>2.8271861076355</v>
       </c>
       <c r="G1322" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -40719,7 +40722,7 @@
         <v>2.88512897491455</v>
       </c>
       <c r="G1323" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -40745,7 +40748,7 @@
         <v>2.84716701507568</v>
       </c>
       <c r="G1324" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -40771,7 +40774,7 @@
         <v>2.84716701507568</v>
       </c>
       <c r="G1325" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -40797,7 +40800,7 @@
         <v>2.81719589233398</v>
       </c>
       <c r="G1326" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -40823,7 +40826,7 @@
         <v>2.78722596168518</v>
       </c>
       <c r="G1327" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -40849,7 +40852,7 @@
         <v>2.85116291046143</v>
       </c>
       <c r="G1328" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -40875,7 +40878,7 @@
         <v>2.82518792152405</v>
       </c>
       <c r="G1329" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -40901,7 +40904,7 @@
         <v>2.84716701507568</v>
       </c>
       <c r="G1330" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -40927,7 +40930,7 @@
         <v>2.82918405532837</v>
       </c>
       <c r="G1331" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -40953,7 +40956,7 @@
         <v>2.94307088851929</v>
       </c>
       <c r="G1332" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -40979,7 +40982,7 @@
         <v>2.85316109657288</v>
       </c>
       <c r="G1333" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -41005,7 +41008,7 @@
         <v>2.89711689949036</v>
       </c>
       <c r="G1334" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -41031,7 +41034,7 @@
         <v>2.89711689949036</v>
       </c>
       <c r="G1335" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -41057,7 +41060,7 @@
         <v>2.89312100410461</v>
       </c>
       <c r="G1336" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -41083,7 +41086,7 @@
         <v>2.84716701507568</v>
       </c>
       <c r="G1337" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -41109,7 +41112,7 @@
         <v>2.82518792152405</v>
       </c>
       <c r="G1338" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -41135,7 +41138,7 @@
         <v>2.86914491653442</v>
       </c>
       <c r="G1339" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -41161,7 +41164,7 @@
         <v>2.87114310264587</v>
       </c>
       <c r="G1340" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -41187,7 +41190,7 @@
         <v>2.95705699920654</v>
       </c>
       <c r="G1341" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -41213,7 +41216,7 @@
         <v>2.97304105758667</v>
       </c>
       <c r="G1342" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -41239,7 +41242,7 @@
         <v>3.00301194190979</v>
       </c>
       <c r="G1343" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -41265,7 +41268,7 @@
         <v>3.04497003555298</v>
       </c>
       <c r="G1344" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -41291,7 +41294,7 @@
         <v>2.95905494689941</v>
       </c>
       <c r="G1345" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -41317,7 +41320,7 @@
         <v>2.9710431098938</v>
       </c>
       <c r="G1346" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -41343,7 +41346,7 @@
         <v>2.97503900527954</v>
       </c>
       <c r="G1347" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -41369,7 +41372,7 @@
         <v>3.04497003555298</v>
       </c>
       <c r="G1348" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -41395,7 +41398,7 @@
         <v>3.13488006591797</v>
       </c>
       <c r="G1349" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -41421,7 +41424,7 @@
         <v>3.17484092712402</v>
       </c>
       <c r="G1350" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -41447,7 +41450,7 @@
         <v>3.28273296356201</v>
       </c>
       <c r="G1351" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -41473,7 +41476,7 @@
         <v>3.37264394760132</v>
       </c>
       <c r="G1352" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -41499,7 +41502,7 @@
         <v>3.49652004241943</v>
       </c>
       <c r="G1353" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -41525,7 +41528,7 @@
         <v>3.46255397796631</v>
       </c>
       <c r="G1354" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -41551,7 +41554,7 @@
         <v>3.44257402420044</v>
       </c>
       <c r="G1355" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -41577,7 +41580,7 @@
         <v>3.57444310188293</v>
       </c>
       <c r="G1356" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -41603,7 +41606,7 @@
         <v>3.62239503860474</v>
       </c>
       <c r="G1357" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -41629,7 +41632,7 @@
         <v>3.68633198738098</v>
       </c>
       <c r="G1358" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -41655,7 +41658,7 @@
         <v>3.81820011138916</v>
       </c>
       <c r="G1359" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -41681,7 +41684,7 @@
         <v>3.79022789001465</v>
       </c>
       <c r="G1360" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -41707,7 +41710,7 @@
         <v>3.78623199462891</v>
       </c>
       <c r="G1361" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -41733,7 +41736,7 @@
         <v>3.89212703704834</v>
       </c>
       <c r="G1362" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -41759,7 +41762,7 @@
         <v>3.89612293243408</v>
       </c>
       <c r="G1363" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -41785,7 +41788,7 @@
         <v>3.87814092636108</v>
       </c>
       <c r="G1364" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -41811,7 +41814,7 @@
         <v>3.94207692146301</v>
       </c>
       <c r="G1365" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -41837,7 +41840,7 @@
         <v>3.92409491539001</v>
       </c>
       <c r="G1366" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -41863,7 +41866,7 @@
         <v>3.91210699081421</v>
       </c>
       <c r="G1367" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -41889,7 +41892,7 @@
         <v>3.94007897377014</v>
       </c>
       <c r="G1368" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -41915,7 +41918,7 @@
         <v>4.01800203323364</v>
       </c>
       <c r="G1369" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -41941,7 +41944,7 @@
         <v>4.00401592254639</v>
       </c>
       <c r="G1370" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -41967,7 +41970,7 @@
         <v>3.9840350151062</v>
       </c>
       <c r="G1371" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -41993,7 +41996,7 @@
         <v>4.10791206359863</v>
       </c>
       <c r="G1372" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -42019,7 +42022,7 @@
         <v>4.027991771698</v>
       </c>
       <c r="G1373" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -42045,7 +42048,7 @@
         <v>4.05796194076538</v>
       </c>
       <c r="G1374" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -42071,7 +42074,7 @@
         <v>4.15986013412476</v>
       </c>
       <c r="G1375" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -42097,7 +42100,7 @@
         <v>4.1898307800293</v>
       </c>
       <c r="G1376" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -42123,7 +42126,7 @@
         <v>4.15386581420898</v>
       </c>
       <c r="G1377" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -42149,7 +42152,7 @@
         <v>4.13588380813599</v>
       </c>
       <c r="G1378" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -42175,7 +42178,7 @@
         <v>4.07594394683838</v>
       </c>
       <c r="G1379" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -42201,7 +42204,7 @@
         <v>3.99002909660339</v>
       </c>
       <c r="G1380" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -42227,7 +42230,7 @@
         <v>3.89212703704834</v>
       </c>
       <c r="G1381" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -42253,7 +42256,7 @@
         <v>3.86415505409241</v>
       </c>
       <c r="G1382" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -42279,7 +42282,7 @@
         <v>3.85616302490234</v>
       </c>
       <c r="G1383" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -42305,7 +42308,7 @@
         <v>3.83618211746216</v>
       </c>
       <c r="G1384" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -42331,7 +42334,7 @@
         <v>3.79622197151184</v>
       </c>
       <c r="G1385" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -42357,7 +42360,7 @@
         <v>3.78023791313171</v>
       </c>
       <c r="G1386" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -42383,7 +42386,7 @@
         <v>3.68832993507385</v>
       </c>
       <c r="G1387" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -42409,7 +42412,7 @@
         <v>3.65036702156067</v>
       </c>
       <c r="G1388" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -42435,7 +42438,7 @@
         <v>3.6483690738678</v>
       </c>
       <c r="G1389" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -42461,7 +42464,7 @@
         <v>3.56445288658142</v>
       </c>
       <c r="G1390" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -42487,7 +42490,7 @@
         <v>3.64037704467773</v>
       </c>
       <c r="G1391" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -42513,7 +42516,7 @@
         <v>3.63837909698486</v>
       </c>
       <c r="G1392" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -42539,7 +42542,7 @@
         <v>3.69632196426392</v>
       </c>
       <c r="G1393" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -42565,7 +42568,7 @@
         <v>3.60441303253174</v>
       </c>
       <c r="G1394" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -42591,7 +42594,7 @@
         <v>3.69632196426392</v>
       </c>
       <c r="G1395" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -42617,7 +42620,7 @@
         <v>3.65436291694641</v>
       </c>
       <c r="G1396" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -42643,7 +42646,7 @@
         <v>3.68832993507385</v>
       </c>
       <c r="G1397" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -42669,7 +42672,7 @@
         <v>3.63638091087341</v>
       </c>
       <c r="G1398" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -42695,7 +42698,7 @@
         <v>3.72229599952698</v>
       </c>
       <c r="G1399" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -42721,7 +42724,7 @@
         <v>3.62439298629761</v>
       </c>
       <c r="G1400" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -42747,7 +42750,7 @@
         <v>3.58443307876587</v>
       </c>
       <c r="G1401" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -42773,7 +42776,7 @@
         <v>3.54846906661987</v>
       </c>
       <c r="G1402" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -42799,7 +42802,7 @@
         <v>3.70431399345398</v>
       </c>
       <c r="G1403" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -42825,7 +42828,7 @@
         <v>3.64237499237061</v>
       </c>
       <c r="G1404" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -42851,7 +42854,7 @@
         <v>3.62039709091187</v>
       </c>
       <c r="G1405" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -42877,7 +42880,7 @@
         <v>3.63638091087341</v>
       </c>
       <c r="G1406" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -42903,7 +42906,7 @@
         <v>3.55046701431274</v>
       </c>
       <c r="G1407" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -42929,7 +42932,7 @@
         <v>3.48253393173218</v>
       </c>
       <c r="G1408" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -42955,7 +42958,7 @@
         <v>3.36265397071838</v>
       </c>
       <c r="G1409" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -42981,7 +42984,7 @@
         <v>3.47254395484924</v>
       </c>
       <c r="G1410" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -43007,7 +43010,7 @@
         <v>3.56045699119568</v>
       </c>
       <c r="G1411" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -43033,7 +43036,7 @@
         <v>3.59242510795593</v>
       </c>
       <c r="G1412" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -43059,7 +43062,7 @@
         <v>3.62639093399048</v>
       </c>
       <c r="G1413" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -43085,7 +43088,7 @@
         <v>3.81220602989197</v>
       </c>
       <c r="G1414" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -43111,7 +43114,7 @@
         <v>3.76425409317017</v>
       </c>
       <c r="G1415" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -43137,7 +43140,7 @@
         <v>3.83418393135071</v>
       </c>
       <c r="G1416" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -43163,7 +43166,7 @@
         <v>3.78822994232178</v>
       </c>
       <c r="G1417" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -43189,7 +43192,7 @@
         <v>3.71430397033691</v>
       </c>
       <c r="G1418" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -43215,7 +43218,7 @@
         <v>3.72629189491272</v>
       </c>
       <c r="G1419" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -43241,7 +43244,7 @@
         <v>3.72429394721985</v>
       </c>
       <c r="G1420" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -43267,7 +43270,7 @@
         <v>3.69831991195679</v>
       </c>
       <c r="G1421" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -43293,7 +43296,7 @@
         <v>3.70631194114685</v>
       </c>
       <c r="G1422" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -43319,7 +43322,7 @@
         <v>3.80221605300903</v>
       </c>
       <c r="G1423" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -43345,7 +43348,7 @@
         <v>3.84617304801941</v>
       </c>
       <c r="G1424" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -43371,7 +43374,7 @@
         <v>3.78423404693604</v>
       </c>
       <c r="G1425" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -43397,7 +43400,7 @@
         <v>3.86615300178528</v>
       </c>
       <c r="G1426" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -43423,7 +43426,7 @@
         <v>3.81420397758484</v>
       </c>
       <c r="G1427" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -43449,7 +43452,7 @@
         <v>3.8102080821991</v>
       </c>
       <c r="G1428" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -43475,7 +43478,7 @@
         <v>3.79622197151184</v>
       </c>
       <c r="G1429" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -43501,7 +43504,7 @@
         <v>3.69432401657104</v>
       </c>
       <c r="G1430" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -43527,7 +43530,7 @@
         <v>3.72829008102417</v>
       </c>
       <c r="G1431" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -43553,7 +43556,7 @@
         <v>3.70830988883972</v>
       </c>
       <c r="G1432" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -43579,7 +43582,7 @@
         <v>3.69432401657104</v>
       </c>
       <c r="G1433" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -43605,7 +43608,7 @@
         <v>3.75026798248291</v>
       </c>
       <c r="G1434" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -43631,7 +43634,7 @@
         <v>3.77624201774597</v>
       </c>
       <c r="G1435" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -43657,7 +43660,7 @@
         <v>3.90811109542847</v>
       </c>
       <c r="G1436" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -43683,7 +43686,7 @@
         <v>3.9181010723114</v>
       </c>
       <c r="G1437" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -43709,7 +43712,7 @@
         <v>3.88613295555115</v>
       </c>
       <c r="G1438" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -43735,7 +43738,7 @@
         <v>3.89012908935547</v>
       </c>
       <c r="G1439" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -43761,7 +43764,7 @@
         <v>3.84817099571228</v>
       </c>
       <c r="G1440" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -43787,7 +43790,7 @@
         <v>3.89212703704834</v>
       </c>
       <c r="G1441" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -43813,7 +43816,7 @@
         <v>3.89612293243408</v>
       </c>
       <c r="G1442" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -43839,7 +43842,7 @@
         <v>3.82619190216064</v>
       </c>
       <c r="G1443" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -43865,7 +43868,7 @@
         <v>3.85216689109802</v>
       </c>
       <c r="G1444" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -43891,7 +43894,7 @@
         <v>3.77823996543884</v>
       </c>
       <c r="G1445" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -43917,7 +43920,7 @@
         <v>3.70231604576111</v>
       </c>
       <c r="G1446" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -43943,7 +43946,7 @@
         <v>3.74427390098572</v>
       </c>
       <c r="G1447" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -43969,7 +43972,7 @@
         <v>3.68832993507385</v>
       </c>
       <c r="G1448" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -43995,7 +43998,7 @@
         <v>3.70830988883972</v>
       </c>
       <c r="G1449" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -44021,7 +44024,7 @@
         <v>3.67034792900085</v>
       </c>
       <c r="G1450" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -44047,7 +44050,7 @@
         <v>3.60241508483887</v>
       </c>
       <c r="G1451" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -44073,7 +44076,7 @@
         <v>3.68633198738098</v>
       </c>
       <c r="G1452" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -44099,7 +44102,7 @@
         <v>3.60840892791748</v>
       </c>
       <c r="G1453" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -44125,7 +44128,7 @@
         <v>3.52049708366394</v>
       </c>
       <c r="G1454" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -44151,7 +44154,7 @@
         <v>3.52449297904968</v>
       </c>
       <c r="G1455" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -44177,7 +44180,7 @@
         <v>3.64437294006348</v>
       </c>
       <c r="G1456" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -44203,7 +44206,7 @@
         <v>3.65636110305786</v>
       </c>
       <c r="G1457" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -44229,7 +44232,7 @@
         <v>3.6663510799408</v>
       </c>
       <c r="G1458" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -44255,7 +44258,7 @@
         <v>3.69632196426392</v>
       </c>
       <c r="G1459" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -44281,7 +44284,7 @@
         <v>3.63638091087341</v>
       </c>
       <c r="G1460" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -44307,7 +44310,7 @@
         <v>3.62239503860474</v>
       </c>
       <c r="G1461" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -44333,7 +44336,7 @@
         <v>3.68233609199524</v>
       </c>
       <c r="G1462" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -44359,7 +44362,7 @@
         <v>3.71030807495117</v>
       </c>
       <c r="G1463" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -44385,7 +44388,7 @@
         <v>3.67833995819092</v>
       </c>
       <c r="G1464" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -44411,7 +44414,7 @@
         <v>3.81820011138916</v>
       </c>
       <c r="G1465" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -44437,7 +44440,7 @@
         <v>3.78223609924316</v>
       </c>
       <c r="G1466" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -44463,7 +44466,7 @@
         <v>3.7562620639801</v>
       </c>
       <c r="G1467" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -44489,7 +44492,7 @@
         <v>3.73428392410278</v>
       </c>
       <c r="G1468" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -44515,7 +44518,7 @@
         <v>3.74627208709717</v>
       </c>
       <c r="G1469" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -44541,7 +44544,7 @@
         <v>3.78623199462891</v>
       </c>
       <c r="G1470" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -44567,7 +44570,7 @@
         <v>3.73428392410278</v>
       </c>
       <c r="G1471" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -44593,7 +44596,7 @@
         <v>3.77624201774597</v>
       </c>
       <c r="G1472" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -44619,7 +44622,7 @@
         <v>3.85016894340515</v>
       </c>
       <c r="G1473" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -44645,7 +44648,7 @@
         <v>3.87614297866821</v>
       </c>
       <c r="G1474" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -44671,7 +44674,7 @@
         <v>3.88613295555115</v>
       </c>
       <c r="G1475" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -44697,7 +44700,7 @@
         <v>3.89412498474121</v>
       </c>
       <c r="G1476" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -44723,7 +44726,7 @@
         <v>3.84417510032654</v>
       </c>
       <c r="G1477" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -44749,7 +44752,7 @@
         <v>3.90411496162415</v>
       </c>
       <c r="G1478" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -44775,7 +44778,7 @@
         <v>3.94607305526733</v>
       </c>
       <c r="G1479" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -44801,7 +44804,7 @@
         <v>3.95606303215027</v>
       </c>
       <c r="G1480" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -44827,7 +44830,7 @@
         <v>3.8042140007019</v>
       </c>
       <c r="G1481" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -44853,7 +44856,7 @@
         <v>3.82419395446777</v>
       </c>
       <c r="G1482" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -44879,7 +44882,7 @@
         <v>3.75226593017578</v>
       </c>
       <c r="G1483" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -44905,7 +44908,7 @@
         <v>3.79422402381897</v>
       </c>
       <c r="G1484" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -44931,7 +44934,7 @@
         <v>3.85016894340515</v>
       </c>
       <c r="G1485" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -44957,7 +44960,7 @@
         <v>3.85616302490234</v>
       </c>
       <c r="G1486" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -44983,7 +44986,7 @@
         <v>3.88413500785828</v>
       </c>
       <c r="G1487" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -45009,7 +45012,7 @@
         <v>3.95206689834595</v>
       </c>
       <c r="G1488" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -45035,7 +45038,7 @@
         <v>3.99002909660339</v>
       </c>
       <c r="G1489" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -45061,7 +45064,7 @@
         <v>3.84217691421509</v>
       </c>
       <c r="G1490" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -45087,7 +45090,7 @@
         <v>3.8102080821991</v>
       </c>
       <c r="G1491" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -45113,7 +45116,7 @@
         <v>3.7562620639801</v>
       </c>
       <c r="G1492" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -45139,7 +45142,7 @@
         <v>3.72029805183411</v>
       </c>
       <c r="G1493" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -45165,7 +45168,7 @@
         <v>3.68633198738098</v>
       </c>
       <c r="G1494" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -45191,7 +45194,7 @@
         <v>3.65835905075073</v>
       </c>
       <c r="G1495" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -45217,7 +45220,7 @@
         <v>3.59841895103455</v>
       </c>
       <c r="G1496" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -45243,7 +45246,7 @@
         <v>3.61440300941467</v>
       </c>
       <c r="G1497" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -45269,7 +45272,7 @@
         <v>3.51650094985962</v>
       </c>
       <c r="G1498" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -45295,7 +45298,7 @@
         <v>3.52649092674255</v>
       </c>
       <c r="G1499" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -45321,7 +45324,7 @@
         <v>3.46655011177063</v>
       </c>
       <c r="G1500" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -45347,7 +45350,7 @@
         <v>3.59642100334167</v>
       </c>
       <c r="G1501" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -45373,7 +45376,7 @@
         <v>3.53248500823975</v>
       </c>
       <c r="G1502" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -45399,7 +45402,7 @@
         <v>3.37264394760132</v>
       </c>
       <c r="G1503" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -45425,7 +45428,7 @@
         <v>3.55845904350281</v>
       </c>
       <c r="G1504" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -45451,7 +45454,7 @@
         <v>3.41659998893738</v>
       </c>
       <c r="G1505" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -45477,7 +45480,7 @@
         <v>3.45256400108337</v>
       </c>
       <c r="G1506" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -45503,7 +45506,7 @@
         <v>3.48852801322937</v>
       </c>
       <c r="G1507" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -45529,7 +45532,7 @@
         <v>3.48453211784363</v>
       </c>
       <c r="G1508" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -45555,7 +45558,7 @@
         <v>3.57843899726868</v>
       </c>
       <c r="G1509" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -45581,7 +45584,7 @@
         <v>3.59242510795593</v>
       </c>
       <c r="G1510" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -45607,7 +45610,7 @@
         <v>3.54447293281555</v>
       </c>
       <c r="G1511" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -45633,7 +45636,7 @@
         <v>3.54247498512268</v>
       </c>
       <c r="G1512" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -45659,7 +45662,7 @@
         <v>3.51250505447388</v>
       </c>
       <c r="G1513" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -45685,7 +45688,7 @@
         <v>3.47654008865356</v>
       </c>
       <c r="G1514" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -45711,7 +45714,7 @@
         <v>3.56445288658142</v>
       </c>
       <c r="G1515" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -45737,7 +45740,7 @@
         <v>3.70431399345398</v>
       </c>
       <c r="G1516" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -45763,7 +45766,7 @@
         <v>3.65436291694641</v>
       </c>
       <c r="G1517" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -45789,7 +45792,7 @@
         <v>3.59841895103455</v>
       </c>
       <c r="G1518" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -45815,7 +45818,7 @@
         <v>3.58842897415161</v>
       </c>
       <c r="G1519" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -45841,7 +45844,7 @@
         <v>3.62039709091187</v>
       </c>
       <c r="G1520" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -45867,7 +45870,7 @@
         <v>3.68033790588379</v>
       </c>
       <c r="G1521" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -45893,7 +45896,7 @@
         <v>3.70631194114685</v>
       </c>
       <c r="G1522" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -45919,7 +45922,7 @@
         <v>3.70431399345398</v>
       </c>
       <c r="G1523" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -45945,7 +45948,7 @@
         <v>3.71830010414124</v>
       </c>
       <c r="G1524" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -45971,7 +45974,7 @@
         <v>3.7742440700531</v>
       </c>
       <c r="G1525" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -45997,7 +46000,7 @@
         <v>3.69432401657104</v>
       </c>
       <c r="G1526" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -46023,7 +46026,7 @@
         <v>3.78423404693604</v>
       </c>
       <c r="G1527" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -46049,7 +46052,7 @@
         <v>3.84217691421509</v>
       </c>
       <c r="G1528" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -46075,7 +46078,7 @@
         <v>3.88013911247253</v>
       </c>
       <c r="G1529" t="s">
-        <v>1169</v>
+        <v>1039</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -46101,7 +46104,7 @@
         <v>3.83618211746216</v>
       </c>
       <c r="G1530" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -46127,7 +46130,7 @@
         <v>3.78623199462891</v>
       </c>
       <c r="G1531" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -46205,7 +46208,7 @@
         <v>3.94607305526733</v>
       </c>
       <c r="G1534" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -46257,7 +46260,7 @@
         <v>3.95206689834595</v>
       </c>
       <c r="G1536" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -46309,7 +46312,7 @@
         <v>3.82419395446777</v>
       </c>
       <c r="G1538" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -46335,7 +46338,7 @@
         <v>3.76425409317017</v>
       </c>
       <c r="G1539" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -46465,7 +46468,7 @@
         <v>3.69831991195679</v>
       </c>
       <c r="G1544" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -46543,7 +46546,7 @@
         <v>3.70830988883972</v>
       </c>
       <c r="G1547" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -46569,7 +46572,7 @@
         <v>3.82619190216064</v>
       </c>
       <c r="G1548" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -46621,7 +46624,7 @@
         <v>3.89212703704834</v>
       </c>
       <c r="G1550" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -72057,7 +72060,7 @@
     </row>
     <row r="2529">
       <c r="A2529" s="1" t="n">
-        <v>46000.6923263889</v>
+        <v>46000.3333333333</v>
       </c>
       <c r="B2529" t="n">
         <v>665892</v>
@@ -72078,6 +72081,32 @@
         <v>1992</v>
       </c>
       <c r="H2529" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2530">
+      <c r="A2530" s="1" t="n">
+        <v>46001.6929513889</v>
+      </c>
+      <c r="B2530" t="n">
+        <v>534166</v>
+      </c>
+      <c r="C2530" t="n">
+        <v>15.3900003433228</v>
+      </c>
+      <c r="D2530" t="n">
+        <v>15.0299997329712</v>
+      </c>
+      <c r="E2530" t="n">
+        <v>15.2200002670288</v>
+      </c>
+      <c r="F2530" t="n">
+        <v>15.3100004196167</v>
+      </c>
+      <c r="G2530" t="s">
+        <v>1993</v>
+      </c>
+      <c r="H2530" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BPSO.MI.xlsx
+++ b/data/BPSO.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1997" uniqueCount="1997">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1998" uniqueCount="1998">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,52 +47,52 @@
     <t xml:space="preserve">2.80963706970215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74855780601501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7124662399292</t>
+    <t xml:space="preserve">2.74855804443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71246600151062</t>
   </si>
   <si>
     <t xml:space="preserve">2.63611721992493</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60835433006287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69303178787231</t>
+    <t xml:space="preserve">2.60835409164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69303202629089</t>
   </si>
   <si>
     <t xml:space="preserve">2.69858431816101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61113023757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51257061958313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4556565284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2668662071228</t>
+    <t xml:space="preserve">2.61113047599792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51257085800171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45565629005432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26686644554138</t>
   </si>
   <si>
     <t xml:space="preserve">2.38069534301758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40568256378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36542582511902</t>
+    <t xml:space="preserve">2.40568232536316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3654260635376</t>
   </si>
   <si>
     <t xml:space="preserve">2.51951146125793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44455122947693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35570859909058</t>
+    <t xml:space="preserve">2.44455099105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35570907592773</t>
   </si>
   <si>
     <t xml:space="preserve">2.43899869918823</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">2.22105741500854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23216247558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20995211601257</t>
+    <t xml:space="preserve">2.23216223716736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20995259284973</t>
   </si>
   <si>
     <t xml:space="preserve">2.04059600830078</t>
@@ -119,70 +119,70 @@
     <t xml:space="preserve">2.06280660629272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14331984519958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07668805122375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18218851089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22522115707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27797150611877</t>
+    <t xml:space="preserve">2.14332008361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07668828964233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18218803405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22522163391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27797174453735</t>
   </si>
   <si>
     <t xml:space="preserve">2.19329357147217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16553068161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24604392051697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18635272979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17663598060608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21550440788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.259925365448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31822848320007</t>
+    <t xml:space="preserve">2.16553044319153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24604368209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18635296821594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1766357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21550464630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25992560386658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31822872161865</t>
   </si>
   <si>
     <t xml:space="preserve">2.3876359462738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38208341598511</t>
+    <t xml:space="preserve">2.38208365440369</t>
   </si>
   <si>
     <t xml:space="preserve">2.37514305114746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24187970161438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26270198822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25020813941956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3196165561676</t>
+    <t xml:space="preserve">2.2418794631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26270174980164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25020861625671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31961679458618</t>
   </si>
   <si>
     <t xml:space="preserve">2.43344521522522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35848522186279</t>
+    <t xml:space="preserve">2.35848498344421</t>
   </si>
   <si>
     <t xml:space="preserve">2.30157017707825</t>
@@ -194,13 +194,13 @@
     <t xml:space="preserve">2.35987329483032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39318895339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29324102401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23771524429321</t>
+    <t xml:space="preserve">2.39318871498108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29324150085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23771476745605</t>
   </si>
   <si>
     <t xml:space="preserve">2.18774080276489</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">2.13915586471558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14748454093933</t>
+    <t xml:space="preserve">2.14748477935791</t>
   </si>
   <si>
     <t xml:space="preserve">2.1211097240448</t>
@@ -224,34 +224,34 @@
     <t xml:space="preserve">2.01838564872742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07113552093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11694502830505</t>
+    <t xml:space="preserve">2.07113575935364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11694526672363</t>
   </si>
   <si>
     <t xml:space="preserve">2.12527394294739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22799801826477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30295825004578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23910355567932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29046487808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3321099281311</t>
+    <t xml:space="preserve">2.22799777984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30295848846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23910331726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29046511650085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33211016654968</t>
   </si>
   <si>
     <t xml:space="preserve">2.32655739784241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2793595790863</t>
+    <t xml:space="preserve">2.27935981750488</t>
   </si>
   <si>
     <t xml:space="preserve">2.32378125190735</t>
@@ -260,25 +260,25 @@
     <t xml:space="preserve">2.30851101875305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26131367683411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23493909835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15720129013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11139273643494</t>
+    <t xml:space="preserve">2.26131343841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.234938621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15720152854919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11139225959778</t>
   </si>
   <si>
     <t xml:space="preserve">2.08224034309387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09889936447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08918166160583</t>
+    <t xml:space="preserve">2.09889912605286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08918213844299</t>
   </si>
   <si>
     <t xml:space="preserve">2.10583972930908</t>
@@ -296,22 +296,22 @@
     <t xml:space="preserve">2.03226685523987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07252359390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05725383758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05156683921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12691855430603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19942736625671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15393233299255</t>
+    <t xml:space="preserve">2.07252335548401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05725407600403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05156707763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12691879272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19942784309387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15393209457397</t>
   </si>
   <si>
     <t xml:space="preserve">2.17525815963745</t>
@@ -320,91 +320,91 @@
     <t xml:space="preserve">2.15535402297974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09279704093933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07147121429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99896204471588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95773243904114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8766930103302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9890102148056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93640625476837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94351482391357</t>
+    <t xml:space="preserve">2.09279727935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07147097587585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99896240234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95773220062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87669312953949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98901009559631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93640613555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94351506233215</t>
   </si>
   <si>
     <t xml:space="preserve">1.84114968776703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78143680095673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.751580119133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72598910331726</t>
+    <t xml:space="preserve">1.78143692016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75157999992371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72598898410797</t>
   </si>
   <si>
     <t xml:space="preserve">1.64210617542267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69613265991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77006244659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81129312515259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78001439571381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89375340938568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63499748706818</t>
+    <t xml:space="preserve">1.69613230228424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77006256580353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81129336357117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7800145149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89375400543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63499760627747</t>
   </si>
   <si>
     <t xml:space="preserve">1.5653327703476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6691198348999</t>
+    <t xml:space="preserve">1.66911959648132</t>
   </si>
   <si>
     <t xml:space="preserve">1.65632355213165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63926255702972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63641929626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57670664787292</t>
+    <t xml:space="preserve">1.63926291465759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63641941547394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57670676708221</t>
   </si>
   <si>
     <t xml:space="preserve">1.51130652427673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52552390098572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53121078014374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63784086704254</t>
+    <t xml:space="preserve">1.52552378177643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53121066093445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63784098625183</t>
   </si>
   <si>
     <t xml:space="preserve">1.67196333408356</t>
@@ -416,43 +416,43 @@
     <t xml:space="preserve">1.67054152488708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74304974079132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70892822742462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72172379493713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77574956417084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76721894741058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72741031646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69755434989929</t>
+    <t xml:space="preserve">1.74304950237274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70892810821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72172367572784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77574932575226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76721906661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72741055488586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69755470752716</t>
   </si>
   <si>
     <t xml:space="preserve">1.7245671749115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71888041496277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66343259811401</t>
+    <t xml:space="preserve">1.71888017654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6634327173233</t>
   </si>
   <si>
     <t xml:space="preserve">1.55395889282227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57528495788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52125871181488</t>
+    <t xml:space="preserve">1.57528519630432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5212584733963</t>
   </si>
   <si>
     <t xml:space="preserve">1.63357603549957</t>
@@ -461,28 +461,28 @@
     <t xml:space="preserve">1.6591671705246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64779329299927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68760228157043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71461498737335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70608472824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70039784908295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74447131156921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70750629901886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72030186653137</t>
+    <t xml:space="preserve">1.64779317378998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68760240077972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71461522579193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70608460903168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70039761066437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74447154998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70750617980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72030222415924</t>
   </si>
   <si>
     <t xml:space="preserve">1.7316757440567</t>
@@ -491,19 +491,19 @@
     <t xml:space="preserve">1.78285872936249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7785929441452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.771484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76437568664551</t>
+    <t xml:space="preserve">1.77859270572662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77148425579071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76437544822693</t>
   </si>
   <si>
     <t xml:space="preserve">1.75584530830383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76295375823975</t>
+    <t xml:space="preserve">1.76295399665833</t>
   </si>
   <si>
     <t xml:space="preserve">1.74162781238556</t>
@@ -512,10 +512,10 @@
     <t xml:space="preserve">1.76864087581635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74873673915863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73451924324036</t>
+    <t xml:space="preserve">1.74873650074005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73451900482178</t>
   </si>
   <si>
     <t xml:space="preserve">1.78428053855896</t>
@@ -524,31 +524,31 @@
     <t xml:space="preserve">1.85252344608307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84967994689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81271493434906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8354629278183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84825849533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85963225364685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9477801322937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97621488571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09848427772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10843634605408</t>
+    <t xml:space="preserve">1.84967970848083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81271529197693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83546268939972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84825813770294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85963213443756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94778037071228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97621440887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09848403930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1084361076355</t>
   </si>
   <si>
     <t xml:space="preserve">2.07573628425598</t>
@@ -560,19 +560,19 @@
     <t xml:space="preserve">2.0885317325592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09706211090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16104054450989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18236660957336</t>
+    <t xml:space="preserve">2.09706258773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16104078292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18236708641052</t>
   </si>
   <si>
     <t xml:space="preserve">2.11412334442139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00038409233093</t>
+    <t xml:space="preserve">2.00038385391235</t>
   </si>
   <si>
     <t xml:space="preserve">2.03877139091492</t>
@@ -581,31 +581,31 @@
     <t xml:space="preserve">2.00891447067261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05298852920532</t>
+    <t xml:space="preserve">2.0529887676239</t>
   </si>
   <si>
     <t xml:space="preserve">2.06294083595276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11554503440857</t>
+    <t xml:space="preserve">2.11554479598999</t>
   </si>
   <si>
     <t xml:space="preserve">2.12549686431885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16246271133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15961885452271</t>
+    <t xml:space="preserve">2.16246223449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15961909294128</t>
   </si>
   <si>
     <t xml:space="preserve">2.13260531425476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08142328262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03592801094055</t>
+    <t xml:space="preserve">2.08142304420471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03592777252197</t>
   </si>
   <si>
     <t xml:space="preserve">2.07715797424316</t>
@@ -614,31 +614,31 @@
     <t xml:space="preserve">2.09990572929382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08995389938354</t>
+    <t xml:space="preserve">2.08995366096497</t>
   </si>
   <si>
     <t xml:space="preserve">2.01033592224121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12407517433167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10417103767395</t>
+    <t xml:space="preserve">2.12407565116882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10417127609253</t>
   </si>
   <si>
     <t xml:space="preserve">2.07289290428162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16814923286438</t>
+    <t xml:space="preserve">2.16814970970154</t>
   </si>
   <si>
     <t xml:space="preserve">2.27478003501892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37430143356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26340579986572</t>
+    <t xml:space="preserve">2.37430167198181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26340651512146</t>
   </si>
   <si>
     <t xml:space="preserve">2.23354911804199</t>
@@ -650,10 +650,10 @@
     <t xml:space="preserve">2.23212718963623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17810153961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16957139968872</t>
+    <t xml:space="preserve">2.1781017780304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16957116127014</t>
   </si>
   <si>
     <t xml:space="preserve">2.23639249801636</t>
@@ -662,10 +662,10 @@
     <t xml:space="preserve">2.22217512130737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21791052818298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20511484146118</t>
+    <t xml:space="preserve">2.21791005134583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2051146030426</t>
   </si>
   <si>
     <t xml:space="preserve">2.22359681129456</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">2.26482772827148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3103232383728</t>
+    <t xml:space="preserve">2.31032276153564</t>
   </si>
   <si>
     <t xml:space="preserve">2.31743168830872</t>
@@ -686,25 +686,25 @@
     <t xml:space="preserve">2.34160113334656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30463600158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29752731323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29610586166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36008334159851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35297513008118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34017968177795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4027361869812</t>
+    <t xml:space="preserve">2.30463624000549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.297527551651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29610562324524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36008381843567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35297465324402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34017944335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40273642539978</t>
   </si>
   <si>
     <t xml:space="preserve">2.41695356369019</t>
@@ -713,52 +713,52 @@
     <t xml:space="preserve">2.45249652862549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41126680374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.415531873703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42406177520752</t>
+    <t xml:space="preserve">2.41126656532288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41553163528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42406225204468</t>
   </si>
   <si>
     <t xml:space="preserve">2.44396638870239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35439705848694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33733582496643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3302276134491</t>
+    <t xml:space="preserve">2.35439682006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33733606338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33022737503052</t>
   </si>
   <si>
     <t xml:space="preserve">2.36434888839722</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32738375663757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28188848495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30037117004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3231189250946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33449244499207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30890107154846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29894924163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25629758834839</t>
+    <t xml:space="preserve">2.32738399505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28188824653625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30037069320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32311868667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33449268341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30890130996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2989490032196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25629734992981</t>
   </si>
   <si>
     <t xml:space="preserve">2.12834048271179</t>
@@ -767,25 +767,25 @@
     <t xml:space="preserve">2.1340274810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28473210334778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22928404808044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.273357629776</t>
+    <t xml:space="preserve">2.28473162651062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22928380966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27335786819458</t>
   </si>
   <si>
     <t xml:space="preserve">2.27904486656189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31316661834717</t>
+    <t xml:space="preserve">2.31316637992859</t>
   </si>
   <si>
     <t xml:space="preserve">2.33875775337219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37856650352478</t>
+    <t xml:space="preserve">2.37856721878052</t>
   </si>
   <si>
     <t xml:space="preserve">2.32880544662476</t>
@@ -797,13 +797,13 @@
     <t xml:space="preserve">2.34871006011963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29468441009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30321431159973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28757524490356</t>
+    <t xml:space="preserve">2.29468393325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30321455001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28757548332214</t>
   </si>
   <si>
     <t xml:space="preserve">2.32027554512024</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">2.28331017494202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29041910171509</t>
+    <t xml:space="preserve">2.29041886329651</t>
   </si>
   <si>
     <t xml:space="preserve">2.29326248168945</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">2.31174445152283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33164882659912</t>
+    <t xml:space="preserve">2.33164930343628</t>
   </si>
   <si>
     <t xml:space="preserve">2.46671390533447</t>
@@ -836,31 +836,31 @@
     <t xml:space="preserve">2.43117070198059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42974925041199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49799299240112</t>
+    <t xml:space="preserve">2.42974948883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49799275398254</t>
   </si>
   <si>
     <t xml:space="preserve">2.46387052536011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48661828041077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51647520065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51789689064026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56907939910889</t>
+    <t xml:space="preserve">2.48661851882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51647543907166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51789712905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56907916069031</t>
   </si>
   <si>
     <t xml:space="preserve">2.53353595733643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48803973197937</t>
+    <t xml:space="preserve">2.48803997039795</t>
   </si>
   <si>
     <t xml:space="preserve">2.50510144233704</t>
@@ -869,31 +869,31 @@
     <t xml:space="preserve">2.5079448223114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50936651229858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5065233707428</t>
+    <t xml:space="preserve">2.50936627388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50652313232422</t>
   </si>
   <si>
     <t xml:space="preserve">2.55486178398132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5722119808197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63293838500977</t>
+    <t xml:space="preserve">2.57221221923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63293886184692</t>
   </si>
   <si>
     <t xml:space="preserve">2.65607309341431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70667886734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56642889976501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52594375610352</t>
+    <t xml:space="preserve">2.70667839050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56642866134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52594351768494</t>
   </si>
   <si>
     <t xml:space="preserve">2.52883577346802</t>
@@ -902,13 +902,13 @@
     <t xml:space="preserve">2.47389245033264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52160596847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51437664031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47100067138672</t>
+    <t xml:space="preserve">2.52160620689392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5143768787384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47100114822388</t>
   </si>
   <si>
     <t xml:space="preserve">2.48979711532593</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">2.47533822059631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51726865768433</t>
+    <t xml:space="preserve">2.51726889610291</t>
   </si>
   <si>
     <t xml:space="preserve">2.45654225349426</t>
@@ -932,31 +932,31 @@
     <t xml:space="preserve">2.48112177848816</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45798802375793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48256778717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48835110664368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48690533638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50859355926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53751134872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60257506370544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55919933319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49558067321777</t>
+    <t xml:space="preserve">2.45798826217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48256802558899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48835134506226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48690509796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50859332084656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53751158714294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6025755405426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55919981002808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49558043479919</t>
   </si>
   <si>
     <t xml:space="preserve">2.59245419502258</t>
@@ -965,46 +965,46 @@
     <t xml:space="preserve">2.66330242156982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61414217948914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63149285316467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6228175163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61703395843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72692084312439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73704171180725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72258305549622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71246194839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71390771865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70812463760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68932819366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68643641471863</t>
+    <t xml:space="preserve">2.61414265632629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63149261474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62281775474548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61703419685364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72692060470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73704147338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72258281707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71246218681335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71390795707703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70812439918518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68932843208313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68643617630005</t>
   </si>
   <si>
     <t xml:space="preserve">2.68788242340088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71101641654968</t>
+    <t xml:space="preserve">2.7110161781311</t>
   </si>
   <si>
     <t xml:space="preserve">2.65028882026672</t>
@@ -1016,37 +1016,37 @@
     <t xml:space="preserve">2.67197775840759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67053174972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65318059921265</t>
+    <t xml:space="preserve">2.67053198814392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65318083763123</t>
   </si>
   <si>
     <t xml:space="preserve">2.65173482894897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.667640209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65896511077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64595150947571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59823799133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62426352500916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60402131080627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54474067687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57655000686646</t>
+    <t xml:space="preserve">2.66763997077942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65896487236023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64595127105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59823775291443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62426328659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6040210723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54474091529846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57654976844788</t>
   </si>
   <si>
     <t xml:space="preserve">2.52449798583984</t>
@@ -1055,46 +1055,46 @@
     <t xml:space="preserve">2.48545956611633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50280976295471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52016019821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5114848613739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.518714427948</t>
+    <t xml:space="preserve">2.50281000137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52016043663025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51148509979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51871466636658</t>
   </si>
   <si>
     <t xml:space="preserve">2.53317308425903</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55196976661682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50714755058289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55052423477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54618692398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53606534004211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57944178581238</t>
+    <t xml:space="preserve">2.5519700050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50714731216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55052399635315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54618644714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53606581687927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5794415473938</t>
   </si>
   <si>
     <t xml:space="preserve">2.64161396026611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63004684448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58956289291382</t>
+    <t xml:space="preserve">2.630047082901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58956265449524</t>
   </si>
   <si>
     <t xml:space="preserve">2.52305197715759</t>
@@ -1115,40 +1115,40 @@
     <t xml:space="preserve">2.47244668006897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50425601005554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48401379585266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49413466453552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49847221374512</t>
+    <t xml:space="preserve">2.50425553321838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48401355743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49413442611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4984724521637</t>
   </si>
   <si>
     <t xml:space="preserve">2.47823023796082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51293110847473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44931268692017</t>
+    <t xml:space="preserve">2.51293134689331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44931292533875</t>
   </si>
   <si>
     <t xml:space="preserve">2.407381772995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45509648323059</t>
+    <t xml:space="preserve">2.45509624481201</t>
   </si>
   <si>
     <t xml:space="preserve">2.41027355194092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29605007171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2468900680542</t>
+    <t xml:space="preserve">2.29605031013489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24688982963562</t>
   </si>
   <si>
     <t xml:space="preserve">2.28159093856812</t>
@@ -1157,40 +1157,40 @@
     <t xml:space="preserve">2.18471765518188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19773054122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22086453437805</t>
+    <t xml:space="preserve">2.19773030281067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22086429595947</t>
   </si>
   <si>
     <t xml:space="preserve">2.26279449462891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28448247909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28592848777771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32496738433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34810161590576</t>
+    <t xml:space="preserve">2.28448271751404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28592872619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32496762275696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34810137748718</t>
   </si>
   <si>
     <t xml:space="preserve">2.3784646987915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41461229324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34231781959534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35677623748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35966825485229</t>
+    <t xml:space="preserve">2.41461205482483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34231805801392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35677647590637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35966873168945</t>
   </si>
   <si>
     <t xml:space="preserve">2.34087204933167</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">2.37701869010925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39292335510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40015268325806</t>
+    <t xml:space="preserve">2.39292311668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40015292167664</t>
   </si>
   <si>
     <t xml:space="preserve">2.4059362411499</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">2.23387694358826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18327212333679</t>
+    <t xml:space="preserve">2.18327164649963</t>
   </si>
   <si>
     <t xml:space="preserve">2.21797251701355</t>
@@ -1235,22 +1235,22 @@
     <t xml:space="preserve">2.24544405937195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20062232017517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22664761543274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28303694725037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31340074539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31050896644592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38858556747437</t>
+    <t xml:space="preserve">2.20062208175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22664785385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28303670883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31340050697327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31050872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38858580589294</t>
   </si>
   <si>
     <t xml:space="preserve">2.38713979721069</t>
@@ -1259,10 +1259,10 @@
     <t xml:space="preserve">2.34665560722351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34520959854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36545157432556</t>
+    <t xml:space="preserve">2.34520983695984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36545205116272</t>
   </si>
   <si>
     <t xml:space="preserve">2.39436936378479</t>
@@ -1271,37 +1271,37 @@
     <t xml:space="preserve">2.40304446220398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40448999404907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32785964012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34954738616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33364295959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31195473670959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22953963279724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31484603881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30327916145325</t>
+    <t xml:space="preserve">2.40449023246765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32785940170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34954690933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33364272117615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31195449829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22953987121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31484651565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30327963829041</t>
   </si>
   <si>
     <t xml:space="preserve">2.32062983512878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30761742591858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37268114089966</t>
+    <t xml:space="preserve">2.3076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37268137931824</t>
   </si>
   <si>
     <t xml:space="preserve">2.42907047271729</t>
@@ -1316,52 +1316,52 @@
     <t xml:space="preserve">2.35388493537903</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27725291252136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32930517196655</t>
+    <t xml:space="preserve">2.27725315093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32930493354797</t>
   </si>
   <si>
     <t xml:space="preserve">2.30617141723633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30038785934448</t>
+    <t xml:space="preserve">2.3003876209259</t>
   </si>
   <si>
     <t xml:space="preserve">2.37412714958191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3307511806488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32641339302063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39726090431213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39870667457581</t>
+    <t xml:space="preserve">2.33075094223022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32641363143921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39726066589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39870691299438</t>
   </si>
   <si>
     <t xml:space="preserve">2.38569402694702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60112953186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71969127655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70957040786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75439238548279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77752685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8483738899231</t>
+    <t xml:space="preserve">2.60112977027893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71969151496887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70957016944885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75439214706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77752661705017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84837460517883</t>
   </si>
   <si>
     <t xml:space="preserve">2.84114503860474</t>
@@ -1370,16 +1370,16 @@
     <t xml:space="preserve">2.83391571044922</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86861610412598</t>
+    <t xml:space="preserve">2.86861634254456</t>
   </si>
   <si>
     <t xml:space="preserve">2.90042591094971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82957792282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73125863075256</t>
+    <t xml:space="preserve">2.82957816123962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73125839233398</t>
   </si>
   <si>
     <t xml:space="preserve">2.78620195388794</t>
@@ -1391,55 +1391,55 @@
     <t xml:space="preserve">2.82524037361145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80644369125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83680725097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74716281890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7384877204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63438439369202</t>
+    <t xml:space="preserve">2.80644416809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83680748939514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74716305732727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73848724365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6343846321106</t>
   </si>
   <si>
     <t xml:space="preserve">2.66091990470886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65060043334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71251702308655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70367097854614</t>
+    <t xml:space="preserve">2.65060067176819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71251726150513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70367121696472</t>
   </si>
   <si>
     <t xml:space="preserve">2.63143610954285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52824211120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4825427532196</t>
+    <t xml:space="preserve">2.52824234962463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48254251480103</t>
   </si>
   <si>
     <t xml:space="preserve">2.52234578132629</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56509733200073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61079740524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57689070701599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51939725875854</t>
+    <t xml:space="preserve">2.56509709358215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61079788208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57689046859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51939749717712</t>
   </si>
   <si>
     <t xml:space="preserve">2.59163331985474</t>
@@ -1448,40 +1448,40 @@
     <t xml:space="preserve">2.618168592453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59015917778015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5488805770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56067419052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55625200271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54593253135681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57099390029907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51350069046021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51055216789246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53708720207214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54150986671448</t>
+    <t xml:space="preserve">2.59015893936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54888105392456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5606746673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55625176429749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54593300819397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57099413871765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51350045204163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51055240631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5370876789093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54151010513306</t>
   </si>
   <si>
     <t xml:space="preserve">2.65354871749878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6594455242157</t>
+    <t xml:space="preserve">2.65944600105286</t>
   </si>
   <si>
     <t xml:space="preserve">2.70514559745789</t>
@@ -1490,10 +1490,10 @@
     <t xml:space="preserve">2.6904034614563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65797162055969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61964249610901</t>
+    <t xml:space="preserve">2.65797138214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61964273452759</t>
   </si>
   <si>
     <t xml:space="preserve">2.63291025161743</t>
@@ -1502,43 +1502,43 @@
     <t xml:space="preserve">2.64912629127502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64322948455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66534233093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64470362663269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63880681991577</t>
+    <t xml:space="preserve">2.64322972297668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6653425693512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64470386505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63880729675293</t>
   </si>
   <si>
     <t xml:space="preserve">2.66386842727661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71399116516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73168158531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71693968772888</t>
+    <t xml:space="preserve">2.71399140357971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73168134689331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7169394493103</t>
   </si>
   <si>
     <t xml:space="preserve">2.73315572738647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78180360794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70661973953247</t>
+    <t xml:space="preserve">2.78180408477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70661950111389</t>
   </si>
   <si>
     <t xml:space="preserve">2.69187784194946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68892931938171</t>
+    <t xml:space="preserve">2.68892955780029</t>
   </si>
   <si>
     <t xml:space="preserve">2.67713570594788</t>
@@ -1547,16 +1547,16 @@
     <t xml:space="preserve">2.64617800712585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64175510406494</t>
+    <t xml:space="preserve">2.6417555809021</t>
   </si>
   <si>
     <t xml:space="preserve">2.57541632652283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61374568939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60932350158691</t>
+    <t xml:space="preserve">2.61374592781067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60932326316833</t>
   </si>
   <si>
     <t xml:space="preserve">2.58868479728699</t>
@@ -1565,25 +1565,25 @@
     <t xml:space="preserve">2.58131289482117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53561329841614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48843932151794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47222352027893</t>
+    <t xml:space="preserve">2.53561305999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48843955993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47222375869751</t>
   </si>
   <si>
     <t xml:space="preserve">2.50170731544495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56362271308899</t>
+    <t xml:space="preserve">2.56362295150757</t>
   </si>
   <si>
     <t xml:space="preserve">2.67123913764954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67418742179871</t>
+    <t xml:space="preserve">2.67418766021729</t>
   </si>
   <si>
     <t xml:space="preserve">2.65502309799194</t>
@@ -1592,16 +1592,16 @@
     <t xml:space="preserve">2.68450689315796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66239380836487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62406516075134</t>
+    <t xml:space="preserve">2.66239404678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62406539916992</t>
   </si>
   <si>
     <t xml:space="preserve">2.62996172904968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63733291625977</t>
+    <t xml:space="preserve">2.63733315467834</t>
   </si>
   <si>
     <t xml:space="preserve">2.62111687660217</t>
@@ -1616,10 +1616,10 @@
     <t xml:space="preserve">2.36608123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38966822624207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41325545310974</t>
+    <t xml:space="preserve">2.38966798782349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41325497627258</t>
   </si>
   <si>
     <t xml:space="preserve">2.33659696578979</t>
@@ -1631,40 +1631,40 @@
     <t xml:space="preserve">2.23045563697815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22898149490356</t>
+    <t xml:space="preserve">2.22898125648499</t>
   </si>
   <si>
     <t xml:space="preserve">2.16706514358521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18033242225647</t>
+    <t xml:space="preserve">2.18033266067505</t>
   </si>
   <si>
     <t xml:space="preserve">2.15674567222595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2024450302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19360017776489</t>
+    <t xml:space="preserve">2.20244526863098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19360041618347</t>
   </si>
   <si>
     <t xml:space="preserve">2.13905549049377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11399435997009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08745837211609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04175853729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00932645797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05207777023315</t>
+    <t xml:space="preserve">2.11399412155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08745813369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0417582988739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00932598114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05207800865173</t>
   </si>
   <si>
     <t xml:space="preserve">2.105149269104</t>
@@ -1673,10 +1673,10 @@
     <t xml:space="preserve">2.05797433853149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0550262928009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09335565567017</t>
+    <t xml:space="preserve">2.05502605438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09335589408875</t>
   </si>
   <si>
     <t xml:space="preserve">2.13610696792603</t>
@@ -1685,10 +1685,10 @@
     <t xml:space="preserve">2.11694264411926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09925246238708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10220074653625</t>
+    <t xml:space="preserve">2.09925222396851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10220050811768</t>
   </si>
   <si>
     <t xml:space="preserve">2.10072636604309</t>
@@ -1697,19 +1697,19 @@
     <t xml:space="preserve">2.09040641784668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04912924766541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06829357147217</t>
+    <t xml:space="preserve">2.04912900924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06829380989075</t>
   </si>
   <si>
     <t xml:space="preserve">2.05060338973999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04765510559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02701663970947</t>
+    <t xml:space="preserve">2.0476553440094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02701640129089</t>
   </si>
   <si>
     <t xml:space="preserve">2.01964545249939</t>
@@ -1718,7 +1718,7 @@
     <t xml:space="preserve">1.97394573688507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97984278202057</t>
+    <t xml:space="preserve">1.97984254360199</t>
   </si>
   <si>
     <t xml:space="preserve">1.96215176582336</t>
@@ -1727,25 +1727,25 @@
     <t xml:space="preserve">1.98426496982574</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08008718490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06387138366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07861280441284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04618120193481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0859842300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05650043487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95625495910645</t>
+    <t xml:space="preserve">2.08008742332458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06387066841125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07861328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04618096351624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08598399162292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05649995803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95625483989716</t>
   </si>
   <si>
     <t xml:space="preserve">1.98279106616974</t>
@@ -1757,19 +1757,19 @@
     <t xml:space="preserve">1.93709051609039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96657419204712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96804857254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89286506175995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98131692409515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9149774312973</t>
+    <t xml:space="preserve">1.9665744304657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9680483341217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89286482334137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98131656646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91497790813446</t>
   </si>
   <si>
     <t xml:space="preserve">1.87517464160919</t>
@@ -1778,61 +1778,61 @@
     <t xml:space="preserve">1.87370049953461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94003903865814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92677104473114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99311029911041</t>
+    <t xml:space="preserve">1.94003891944885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92677116394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99311053752899</t>
   </si>
   <si>
     <t xml:space="preserve">2.00342965126038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99458420276642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99163615703583</t>
+    <t xml:space="preserve">1.99458432197571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99163627624512</t>
   </si>
   <si>
     <t xml:space="preserve">1.94888377189636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88844227790833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87222635746002</t>
+    <t xml:space="preserve">1.88844215869904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87222623825073</t>
   </si>
   <si>
     <t xml:space="preserve">1.91940033435822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89433920383453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86485517024994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85306179523468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83831918239594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88549411296844</t>
+    <t xml:space="preserve">1.89433908462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86485540866852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85306215286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8383195400238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88549399375916</t>
   </si>
   <si>
     <t xml:space="preserve">1.8515876531601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82505166530609</t>
+    <t xml:space="preserve">1.8250515460968</t>
   </si>
   <si>
     <t xml:space="preserve">1.78230035305023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71596121788025</t>
+    <t xml:space="preserve">1.71596133708954</t>
   </si>
   <si>
     <t xml:space="preserve">1.69532263278961</t>
@@ -1841,61 +1841,61 @@
     <t xml:space="preserve">1.71006441116333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73217797279358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78377437591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76313579082489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76166188716888</t>
+    <t xml:space="preserve">1.73217809200287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78377449512482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76313602924347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76166164875031</t>
   </si>
   <si>
     <t xml:space="preserve">1.78672289848328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80588710308075</t>
+    <t xml:space="preserve">1.80588722229004</t>
   </si>
   <si>
     <t xml:space="preserve">1.83389675617218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87664878368378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86927819252014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84569013118744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83979344367981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83242225646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84274172782898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83684492111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8972874879837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88991665840149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8825455904007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91055524349213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87075209617615</t>
+    <t xml:space="preserve">1.87664914131165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86927807331085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84569001197815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83979380130768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83242249488831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84274184703827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83684527873993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89728724956512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88991641998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88254547119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91055500507355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87075197696686</t>
   </si>
   <si>
     <t xml:space="preserve">1.80293881893158</t>
@@ -1904,22 +1904,22 @@
     <t xml:space="preserve">1.80441319942474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79114520549774</t>
+    <t xml:space="preserve">1.79114532470703</t>
   </si>
   <si>
     <t xml:space="preserve">1.75576496124268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81325840950012</t>
+    <t xml:space="preserve">1.81325852870941</t>
   </si>
   <si>
     <t xml:space="preserve">1.81178390979767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83537101745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79556798934937</t>
+    <t xml:space="preserve">1.83537077903748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79556775093079</t>
   </si>
   <si>
     <t xml:space="preserve">1.77492928504944</t>
@@ -1928,40 +1928,40 @@
     <t xml:space="preserve">1.8088356256485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79851627349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79704201221466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8073616027832</t>
+    <t xml:space="preserve">1.79851603507996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79704213142395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80736148357391</t>
   </si>
   <si>
     <t xml:space="preserve">1.78082609176636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7542906999588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7130126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70711612701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.745445728302</t>
+    <t xml:space="preserve">1.75429081916809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71301293373108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70711600780487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74544548988342</t>
   </si>
   <si>
     <t xml:space="preserve">1.76461005210876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77198088169098</t>
+    <t xml:space="preserve">1.77198076248169</t>
   </si>
   <si>
     <t xml:space="preserve">1.7778776884079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78819704055786</t>
+    <t xml:space="preserve">1.78819715976715</t>
   </si>
   <si>
     <t xml:space="preserve">1.74839389324188</t>
@@ -1973,16 +1973,16 @@
     <t xml:space="preserve">1.67910647392273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61129415035248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57886123657227</t>
+    <t xml:space="preserve">1.61129403114319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57886111736298</t>
   </si>
   <si>
     <t xml:space="preserve">1.53610992431641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55822253227234</t>
+    <t xml:space="preserve">1.55822277069092</t>
   </si>
   <si>
     <t xml:space="preserve">1.54200673103333</t>
@@ -1994,46 +1994,46 @@
     <t xml:space="preserve">1.53596544265747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56466102600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54351711273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55559909343719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53898620605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54502737522125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60543859004974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58429431915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56768155097961</t>
+    <t xml:space="preserve">1.56466090679169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54351687431335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55559897422791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5389860868454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54502713680267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60543847084045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58429443836212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56768131256104</t>
   </si>
   <si>
     <t xml:space="preserve">1.56919169425964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58882522583008</t>
+    <t xml:space="preserve">1.58882546424866</t>
   </si>
   <si>
     <t xml:space="preserve">1.51028990745544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51935231685638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52690374851227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47177791595459</t>
+    <t xml:space="preserve">1.51935243606567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52690386772156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4717777967453</t>
   </si>
   <si>
     <t xml:space="preserve">1.47026753425598</t>
@@ -2042,49 +2042,49 @@
     <t xml:space="preserve">1.471022605896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45138907432556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46875727176666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49367666244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48386001586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50047314167023</t>
+    <t xml:space="preserve">1.45138895511627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46875715255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49367690086365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48385989665985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50047302246094</t>
   </si>
   <si>
     <t xml:space="preserve">1.45894038677216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46800196170807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48990106582642</t>
+    <t xml:space="preserve">1.46800208091736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48990118503571</t>
   </si>
   <si>
     <t xml:space="preserve">1.48234975337982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48083961009979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53294503688812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57523286342621</t>
+    <t xml:space="preserve">1.4808394908905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53294491767883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57523274421692</t>
   </si>
   <si>
     <t xml:space="preserve">1.56315052509308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52539348602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50424873828888</t>
+    <t xml:space="preserve">1.52539360523224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50424885749817</t>
   </si>
   <si>
     <t xml:space="preserve">1.47328805923462</t>
@@ -2093,16 +2093,16 @@
     <t xml:space="preserve">1.47253286838531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44912350177765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4536544084549</t>
+    <t xml:space="preserve">1.44912362098694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45365452766418</t>
   </si>
   <si>
     <t xml:space="preserve">1.46649181842804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44987881183624</t>
+    <t xml:space="preserve">1.44987869262695</t>
   </si>
   <si>
     <t xml:space="preserve">1.44610285758972</t>
@@ -2114,7 +2114,7 @@
     <t xml:space="preserve">1.42269372940063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42042827606201</t>
+    <t xml:space="preserve">1.42042815685272</t>
   </si>
   <si>
     <t xml:space="preserve">1.42722451686859</t>
@@ -2123,55 +2123,55 @@
     <t xml:space="preserve">1.41665256023407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40683555603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.400794506073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39097762107849</t>
+    <t xml:space="preserve">1.40683567523956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40079438686371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39097774028778</t>
   </si>
   <si>
     <t xml:space="preserve">1.3864461183548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28374707698822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25354063510895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25127518177032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20068061351776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23617243766785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25278532505035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22182464599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23088645935059</t>
+    <t xml:space="preserve">1.28374683856964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25354051589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25127506256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20068073272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23617231845856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25278544425964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22182476520538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23088622093201</t>
   </si>
   <si>
     <t xml:space="preserve">1.27695071697235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26637876033783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27619564533234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31395268440247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27090954780579</t>
+    <t xml:space="preserve">1.26637887954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27619552612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31395256519318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2709094285965</t>
   </si>
   <si>
     <t xml:space="preserve">1.28223669528961</t>
@@ -2183,22 +2183,22 @@
     <t xml:space="preserve">1.35775077342987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38342547416687</t>
+    <t xml:space="preserve">1.38342559337616</t>
   </si>
   <si>
     <t xml:space="preserve">1.37436378002167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35246479511261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4098562002182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39852917194366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36681234836578</t>
+    <t xml:space="preserve">1.35246467590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40985631942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39852929115295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36681246757507</t>
   </si>
   <si>
     <t xml:space="preserve">1.350954413414</t>
@@ -2219,10 +2219,10 @@
     <t xml:space="preserve">1.2897881269455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26109266281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26864409446716</t>
+    <t xml:space="preserve">1.26109278202057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26864421367645</t>
   </si>
   <si>
     <t xml:space="preserve">1.25505077838898</t>
@@ -2234,46 +2234,46 @@
     <t xml:space="preserve">1.27997136116028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25958168506622</t>
+    <t xml:space="preserve">1.25958180427551</t>
   </si>
   <si>
     <t xml:space="preserve">1.25429570674896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26939940452576</t>
+    <t xml:space="preserve">1.26939928531647</t>
   </si>
   <si>
     <t xml:space="preserve">1.2814816236496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30413568019867</t>
+    <t xml:space="preserve">1.30413591861725</t>
   </si>
   <si>
     <t xml:space="preserve">1.33660686016083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36077129840851</t>
+    <t xml:space="preserve">1.36077117919922</t>
   </si>
   <si>
     <t xml:space="preserve">1.38871240615845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38267040252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35170960426331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35699558258057</t>
+    <t xml:space="preserve">1.38267052173615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3517097234726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35699570178986</t>
   </si>
   <si>
     <t xml:space="preserve">1.36152637004852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36228156089783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34113788604736</t>
+    <t xml:space="preserve">1.36228168010712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34113764762878</t>
   </si>
   <si>
     <t xml:space="preserve">1.36756753921509</t>
@@ -2294,22 +2294,22 @@
     <t xml:space="preserve">1.43477582931519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62960290908813</t>
+    <t xml:space="preserve">1.62960302829742</t>
   </si>
   <si>
     <t xml:space="preserve">1.5827841758728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57825350761414</t>
+    <t xml:space="preserve">1.57825338840485</t>
   </si>
   <si>
     <t xml:space="preserve">1.58127391338348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54653751850128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53747594356537</t>
+    <t xml:space="preserve">1.54653763771057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53747582435608</t>
   </si>
   <si>
     <t xml:space="preserve">1.52237284183502</t>
@@ -2318,7 +2318,7 @@
     <t xml:space="preserve">1.55257856845856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60241794586182</t>
+    <t xml:space="preserve">1.60241782665253</t>
   </si>
   <si>
     <t xml:space="preserve">1.63111317157745</t>
@@ -2327,31 +2327,31 @@
     <t xml:space="preserve">1.60090756416321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62054145336151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54955792427063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57221233844757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61147952079773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.641685962677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61298990249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61752068996429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59184598922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58731496334076</t>
+    <t xml:space="preserve">1.62054121494293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54955804347992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57221245765686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61147964000702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64168608188629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61299002170563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.617520570755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59184610843658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58731508255005</t>
   </si>
   <si>
     <t xml:space="preserve">1.6190310716629</t>
@@ -2360,10 +2360,10 @@
     <t xml:space="preserve">1.57976377010345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56013011932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55861973762512</t>
+    <t xml:space="preserve">1.56013000011444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55861985683441</t>
   </si>
   <si>
     <t xml:space="preserve">1.59788691997528</t>
@@ -2372,16 +2372,16 @@
     <t xml:space="preserve">1.60392808914185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58580470085144</t>
+    <t xml:space="preserve">1.58580482006073</t>
   </si>
   <si>
     <t xml:space="preserve">1.59939742088318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59637665748596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5903354883194</t>
+    <t xml:space="preserve">1.59637677669525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59033560752869</t>
   </si>
   <si>
     <t xml:space="preserve">1.52992451190948</t>
@@ -2390,61 +2390,61 @@
     <t xml:space="preserve">1.51331126689911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50953495502472</t>
+    <t xml:space="preserve">1.50953483581543</t>
   </si>
   <si>
     <t xml:space="preserve">1.52388322353363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54049634933472</t>
+    <t xml:space="preserve">1.54049623012543</t>
   </si>
   <si>
     <t xml:space="preserve">1.63866460323334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75948810577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80630743503571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78365325927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83953368663788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02983069419861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06909775733948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94827497005463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89088308811188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7791223526001</t>
+    <t xml:space="preserve">1.75948798656464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.806307554245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78365337848663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8395334482193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02983045578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06909799575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94827485084534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89088296890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77912223339081</t>
   </si>
   <si>
     <t xml:space="preserve">1.77308118343353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81687951087952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70813834667206</t>
+    <t xml:space="preserve">1.81687939167023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70813846588135</t>
   </si>
   <si>
     <t xml:space="preserve">1.48008441925049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37511909008026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32452464103699</t>
+    <t xml:space="preserve">1.37511897087097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3245245218277</t>
   </si>
   <si>
     <t xml:space="preserve">1.2407032251358</t>
@@ -2456,28 +2456,28 @@
     <t xml:space="preserve">1.18406772613525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.959789216518402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995280981063843</t>
+    <t xml:space="preserve">0.959789276123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995281040668488</t>
   </si>
   <si>
     <t xml:space="preserve">0.91901171207428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.945441544055939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96280974149704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01869118213654</t>
+    <t xml:space="preserve">0.945441484451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962809860706329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01869094371796</t>
   </si>
   <si>
     <t xml:space="preserve">1.04361057281494</t>
   </si>
   <si>
-    <t xml:space="preserve">0.990750193595886</t>
+    <t xml:space="preserve">0.990750074386597</t>
   </si>
   <si>
     <t xml:space="preserve">1.07155084609985</t>
@@ -2486,28 +2486,28 @@
     <t xml:space="preserve">1.07910239696503</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0677752494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01944613456726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999811828136444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0413453578949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02699744701385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10628747940063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05720329284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11459398269653</t>
+    <t xml:space="preserve">1.06777513027191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01944625377655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999811708927155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04134523868561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02699756622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10628736019135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0572030544281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11459386348724</t>
   </si>
   <si>
     <t xml:space="preserve">1.13875913619995</t>
@@ -2516,13 +2516,13 @@
     <t xml:space="preserve">1.20219111442566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16745448112488</t>
+    <t xml:space="preserve">1.16745460033417</t>
   </si>
   <si>
     <t xml:space="preserve">1.16594409942627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08740878105164</t>
+    <t xml:space="preserve">1.08740890026093</t>
   </si>
   <si>
     <t xml:space="preserve">1.06701993942261</t>
@@ -2534,22 +2534,22 @@
     <t xml:space="preserve">1.06324434280396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09496033191681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07834708690643</t>
+    <t xml:space="preserve">1.09496021270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07834720611572</t>
   </si>
   <si>
     <t xml:space="preserve">1.08212280273438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07457149028778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08665359020233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0926947593689</t>
+    <t xml:space="preserve">1.07457137107849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08665370941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09269487857819</t>
   </si>
   <si>
     <t xml:space="preserve">1.03756952285767</t>
@@ -2567,37 +2567,37 @@
     <t xml:space="preserve">1.04436576366425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04285562038422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01189470291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985464155673981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970361232757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989239871501923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943176209926605</t>
+    <t xml:space="preserve">1.04285550117493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01189482212067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985464036464691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.970361173152924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989239692687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94317626953125</t>
   </si>
   <si>
     <t xml:space="preserve">0.926563084125519</t>
   </si>
   <si>
-    <t xml:space="preserve">0.921277046203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913725674152374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986219227313995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997546255588531</t>
+    <t xml:space="preserve">0.921276986598969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913725733757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986219048500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997546315193176</t>
   </si>
   <si>
     <t xml:space="preserve">1.058713555336</t>
@@ -2606,10 +2606,10 @@
     <t xml:space="preserve">1.09722566604614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1025116443634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13422763347626</t>
+    <t xml:space="preserve">1.10251152515411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13422751426697</t>
   </si>
   <si>
     <t xml:space="preserve">1.18180215358734</t>
@@ -2621,34 +2621,34 @@
     <t xml:space="preserve">1.23919296264648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19992554187775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18935346603394</t>
+    <t xml:space="preserve">1.19992542266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18935358524323</t>
   </si>
   <si>
     <t xml:space="preserve">1.14782094955444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16820967197418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18708825111389</t>
+    <t xml:space="preserve">1.16820979118347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1870881319046</t>
   </si>
   <si>
     <t xml:space="preserve">1.16216850280762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19312942028046</t>
+    <t xml:space="preserve">1.19312918186188</t>
   </si>
   <si>
     <t xml:space="preserve">1.17047512531281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24598908424377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29280865192413</t>
+    <t xml:space="preserve">1.24598920345306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29280877113342</t>
   </si>
   <si>
     <t xml:space="preserve">1.36303675174713</t>
@@ -2660,25 +2660,25 @@
     <t xml:space="preserve">1.41136646270752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39399826526642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39928436279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40154957771301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40305995941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41589736938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49292171001434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44836854934692</t>
+    <t xml:space="preserve">1.39399814605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39928424358368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40154981613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40306007862091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41589748859406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49292182922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44836843013763</t>
   </si>
   <si>
     <t xml:space="preserve">1.48763573169708</t>
@@ -2699,19 +2699,19 @@
     <t xml:space="preserve">1.34264802932739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3690779209137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43175542354584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.445347905159</t>
+    <t xml:space="preserve">1.36907804012299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43175530433655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44534778594971</t>
   </si>
   <si>
     <t xml:space="preserve">1.47479844093323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48461520671844</t>
+    <t xml:space="preserve">1.48461508750916</t>
   </si>
   <si>
     <t xml:space="preserve">1.55106842517853</t>
@@ -2720,76 +2720,76 @@
     <t xml:space="preserve">1.5208625793457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37889468669891</t>
+    <t xml:space="preserve">1.37889456748962</t>
   </si>
   <si>
     <t xml:space="preserve">1.3781396150589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34415829181671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37209844589233</t>
+    <t xml:space="preserve">1.34415817260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37209832668304</t>
   </si>
   <si>
     <t xml:space="preserve">1.39475345611572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37964999675751</t>
+    <t xml:space="preserve">1.37964987754822</t>
   </si>
   <si>
     <t xml:space="preserve">1.38795721530914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3924880027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32150411605835</t>
+    <t xml:space="preserve">1.39248788356781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32150387763977</t>
   </si>
   <si>
     <t xml:space="preserve">1.31848347187042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34340310096741</t>
+    <t xml:space="preserve">1.3434032201767</t>
   </si>
   <si>
     <t xml:space="preserve">1.30036008358002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32376933097839</t>
+    <t xml:space="preserve">1.32376945018768</t>
   </si>
   <si>
     <t xml:space="preserve">1.3343414068222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39777410030365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36983299255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38191521167755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34038257598877</t>
+    <t xml:space="preserve">1.39777398109436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36983323097229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38191533088684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34038245677948</t>
   </si>
   <si>
     <t xml:space="preserve">1.35473012924194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31772828102112</t>
+    <t xml:space="preserve">1.31772840023041</t>
   </si>
   <si>
     <t xml:space="preserve">1.33207607269287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33585178852081</t>
+    <t xml:space="preserve">1.33585166931152</t>
   </si>
   <si>
     <t xml:space="preserve">1.27393007278442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26486849784851</t>
+    <t xml:space="preserve">1.26486837863922</t>
   </si>
   <si>
     <t xml:space="preserve">1.22484529018402</t>
@@ -2804,46 +2804,46 @@
     <t xml:space="preserve">1.10779762268066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13800406455994</t>
+    <t xml:space="preserve">1.13800394535065</t>
   </si>
   <si>
     <t xml:space="preserve">1.22711062431335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24221348762512</t>
+    <t xml:space="preserve">1.24221336841583</t>
   </si>
   <si>
     <t xml:space="preserve">1.23843765258789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22862088680267</t>
+    <t xml:space="preserve">1.22862100601196</t>
   </si>
   <si>
     <t xml:space="preserve">1.44232726097107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43251049518585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50273847579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55408895015717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81234860420227</t>
+    <t xml:space="preserve">1.43251037597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50273859500885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55408883094788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81234848499298</t>
   </si>
   <si>
     <t xml:space="preserve">1.78214299678802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77459156513214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75797760486603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69303572177887</t>
+    <t xml:space="preserve">1.77459168434143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75797784328461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69303548336029</t>
   </si>
   <si>
     <t xml:space="preserve">1.7217310667038</t>
@@ -2852,16 +2852,16 @@
     <t xml:space="preserve">1.68548405170441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70209717750549</t>
+    <t xml:space="preserve">1.70209741592407</t>
   </si>
   <si>
     <t xml:space="preserve">1.70360743999481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73079264163971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72777223587036</t>
+    <t xml:space="preserve">1.73079252243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72777211666107</t>
   </si>
   <si>
     <t xml:space="preserve">1.69907653331757</t>
@@ -2870,10 +2870,10 @@
     <t xml:space="preserve">1.66887104511261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66282987594604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67944288253784</t>
+    <t xml:space="preserve">1.66282999515533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67944300174713</t>
   </si>
   <si>
     <t xml:space="preserve">1.66131961345673</t>
@@ -2894,7 +2894,7 @@
     <t xml:space="preserve">1.65829908847809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66585063934326</t>
+    <t xml:space="preserve">1.66585052013397</t>
   </si>
   <si>
     <t xml:space="preserve">1.66434001922607</t>
@@ -2906,19 +2906,19 @@
     <t xml:space="preserve">1.77761209011078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75646758079529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72022044658661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73683369159698</t>
+    <t xml:space="preserve">1.756467461586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7202205657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73683381080627</t>
   </si>
   <si>
     <t xml:space="preserve">1.69454598426819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6522581577301</t>
+    <t xml:space="preserve">1.65225803852081</t>
   </si>
   <si>
     <t xml:space="preserve">1.67491221427917</t>
@@ -2927,13 +2927,13 @@
     <t xml:space="preserve">1.65376818180084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63715434074402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54200661182404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57070207595825</t>
+    <t xml:space="preserve">1.63715422153473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54200649261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57070195674896</t>
   </si>
   <si>
     <t xml:space="preserve">1.59486639499664</t>
@@ -2942,79 +2942,79 @@
     <t xml:space="preserve">1.62205159664154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7474057674408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88635241985321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85765719413757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88031125068665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86822915077209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85463654994965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88937306404114</t>
+    <t xml:space="preserve">1.74740564823151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8863525390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85765731334686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88031101226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86822891235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85463643074036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88937294483185</t>
   </si>
   <si>
     <t xml:space="preserve">1.85010552406311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80932807922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83047199249268</t>
+    <t xml:space="preserve">1.80932831764221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83047211170197</t>
   </si>
   <si>
     <t xml:space="preserve">1.82141017913818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81838965415955</t>
+    <t xml:space="preserve">1.81838953495026</t>
   </si>
   <si>
     <t xml:space="preserve">1.82594120502472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80781769752502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80177652835846</t>
+    <t xml:space="preserve">1.80781781673431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80177640914917</t>
   </si>
   <si>
     <t xml:space="preserve">1.84557485580444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83500266075134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82745134830475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87124955654144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86369824409485</t>
+    <t xml:space="preserve">1.83500277996063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82745146751404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87124967575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86369800567627</t>
   </si>
   <si>
     <t xml:space="preserve">1.927130818367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9799907207489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05399489402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13706088066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18085956573486</t>
+    <t xml:space="preserve">1.97999083995819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05399513244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13706064224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18085932731628</t>
   </si>
   <si>
     <t xml:space="preserve">2.15216398239136</t>
@@ -3023,13 +3023,13 @@
     <t xml:space="preserve">2.12950921058655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10685515403748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15518450737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1355504989624</t>
+    <t xml:space="preserve">2.10685467720032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15518474578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13555026054382</t>
   </si>
   <si>
     <t xml:space="preserve">2.13857102394104</t>
@@ -3038,40 +3038,40 @@
     <t xml:space="preserve">2.22465777397156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15669512748718</t>
+    <t xml:space="preserve">2.15669536590576</t>
   </si>
   <si>
     <t xml:space="preserve">2.18992114067078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18690061569214</t>
+    <t xml:space="preserve">2.18690085411072</t>
   </si>
   <si>
     <t xml:space="preserve">2.16877722740173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17028737068176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2352294921875</t>
+    <t xml:space="preserve">2.17028784751892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23522973060608</t>
   </si>
   <si>
     <t xml:space="preserve">2.24731206893921</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2699670791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30168294906616</t>
+    <t xml:space="preserve">2.26996684074402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30168271064758</t>
   </si>
   <si>
     <t xml:space="preserve">2.23673987388611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2458016872406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24882221221924</t>
+    <t xml:space="preserve">2.24580192565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24882245063782</t>
   </si>
   <si>
     <t xml:space="preserve">2.36964559555054</t>
@@ -3086,447 +3086,447 @@
     <t xml:space="preserve">2.54937052726746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6430082321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61733317375183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60223031044006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70190978050232</t>
+    <t xml:space="preserve">2.64300775527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61733293533325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60223054885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7019100189209</t>
   </si>
   <si>
     <t xml:space="preserve">2.73815655708313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78648638725281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88616490364075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8650209903717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86200070381165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94204616546631</t>
+    <t xml:space="preserve">2.78648614883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88616466522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86502075195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86200022697449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94204592704773</t>
   </si>
   <si>
     <t xml:space="preserve">2.94506669044495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93147397041321</t>
+    <t xml:space="preserve">2.93147373199463</t>
   </si>
   <si>
     <t xml:space="preserve">2.97980308532715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96621036529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9571487903595</t>
+    <t xml:space="preserve">2.96621060371399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95714855194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97829294204712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08411288261414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07337760925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05804061889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15312528610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09178066253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11478519439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19299960136414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21600413322449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18839836120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17459583282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12858748435974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06264162063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98749446868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96602392196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95988941192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9445526599884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91388034820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.901611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83106517791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80192613601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80039238929749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73598027229309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7942578792572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79272413253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83719944953918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76665306091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80499315261841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79119062423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85713672637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78198862075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75131678581238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72371196746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84333443641663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79579138755798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77892184257507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72524523735046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67310166358948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58108496665955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66543364524841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73291325569153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75745105743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78352236747742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92614936828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88934254646301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94301891326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90774583816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85100197792053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86020374298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8586699962616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83873319625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84486770629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91848134994507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95222139358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90467858314514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96755766868591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92768311500549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92461562156677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83566617965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86173748970032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84640145301819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87860727310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89854431152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99976348876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0074315071106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98289370536804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98596096038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95375490188599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99056148529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93688440322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95682215690613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90007781982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84180068969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87400650978088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81726264953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76511931419373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8295316696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76972007751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70224118232727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70530819892883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79732513427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80652666091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81419467926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78045535087585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82646417617798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84793496131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82339715957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93075013160706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90314507484436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88320803642273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86633825302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87554025650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9062123298645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95528864860535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9752254486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98902797698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95068788528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99669623374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02890205383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03657007217407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92001485824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9353506565094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88014054298401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91234660148621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98135995864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03350257873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94915390014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85560297966003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80806040763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.762051820755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77432084083557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69917392730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70684170722961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66083288192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76051807403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71144270896912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58875298500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73137974739075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62249231338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65009760856628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67770266532898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67463541030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74671578407288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72064447402954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71911072731018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69610667228699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66850090026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75438380241394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82493090629578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85406947135925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89701080322266</t>
   </si>
   <si>
     <t xml:space="preserve">2.97829270362854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08411288261414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07337737083435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05804061889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15312528610229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09178066253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11478495597839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19299936294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21600413322449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18839836120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17459583282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12858748435974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06264138221741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98749470710754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96602416038513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95988941192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9445526599884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91388010978699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.901611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83106517791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80192589759827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80039238929749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73598051071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7942578792572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79272437095642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83719944953918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76665258407593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80499315261841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79119038581848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85713648796082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78198909759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7513165473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7237114906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84333419799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79579138755798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77892160415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72524523735046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6731014251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58108496665955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66543340682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73291325569153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75745105743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.783522605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92614912986755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88934254646301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94301891326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90774607658386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85100221633911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86020374298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85867023468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83873343467712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84486770629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91848111152649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95222139358521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90467858314514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96755766868591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92768287658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92461538314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83566617965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8617377281189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84640121459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87860727310181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89854431152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99976348876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00743126869202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98289346694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98596119880676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95375514030457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99056172370911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93688416481018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95682215690613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9000780582428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84180045127869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87400650978088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81726264953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76511931419373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8295316696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76972007751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70224118232727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70530843734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79732513427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80652689933777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81419491767883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78045535087585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82646441459656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84793496131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82339715957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93075013160706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90314531326294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88320827484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86633825302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87554025650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90621256828308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95528864860535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97522568702698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98902821540833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95068788528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99669623374939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02890205383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03657007217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92001485824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93535089492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88014078140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91234660148621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98136019706726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03350281715393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94915413856506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85560321807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80806040763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76205205917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77432084083557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69917392730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70684194564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66083264350891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76051831245422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71144270896912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58875298500061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73137950897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62249255180359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65009737014771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6777024269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67463541030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74671578407288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72064423561096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71911072731018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69610667228699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66850090026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75438380241394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8249306678772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85406947135925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89701080322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9782931804657</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.86327123641968</t>
   </si>
   <si>
@@ -3536,22 +3536,22 @@
     <t xml:space="preserve">3.03503656387329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02736830711365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89087629318237</t>
+    <t xml:space="preserve">3.02736854553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89087605476379</t>
   </si>
   <si>
     <t xml:space="preserve">2.74058127403259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78505611419678</t>
+    <t xml:space="preserve">2.7850558757782</t>
   </si>
   <si>
     <t xml:space="preserve">2.86480474472046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82799816131592</t>
+    <t xml:space="preserve">2.82799792289734</t>
   </si>
   <si>
     <t xml:space="preserve">2.97062468528748</t>
@@ -3560,10 +3560,10 @@
     <t xml:space="preserve">2.92445588111877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90142869949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05187320709229</t>
+    <t xml:space="preserve">2.90142893791199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05187344551086</t>
   </si>
   <si>
     <t xml:space="preserve">3.07029509544373</t>
@@ -3572,19 +3572,19 @@
     <t xml:space="preserve">3.15472817420959</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08871698379517</t>
+    <t xml:space="preserve">3.08871674537659</t>
   </si>
   <si>
     <t xml:space="preserve">3.19771218299866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21459889411926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18850111961365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25297737121582</t>
+    <t xml:space="preserve">3.21459913253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18850135803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2529776096344</t>
   </si>
   <si>
     <t xml:space="preserve">3.16547417640686</t>
@@ -3593,25 +3593,25 @@
     <t xml:space="preserve">3.09485745429993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94748306274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80010914802551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8476984500885</t>
+    <t xml:space="preserve">2.94748330116272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80010890960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84769868850708</t>
   </si>
   <si>
     <t xml:space="preserve">2.72028136253357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55602025985718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58979392051697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54066920280457</t>
+    <t xml:space="preserve">2.55602049827576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58979368209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54066896438599</t>
   </si>
   <si>
     <t xml:space="preserve">2.25359654426575</t>
@@ -3629,13 +3629,13 @@
     <t xml:space="preserve">2.40557622909546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42860341072083</t>
+    <t xml:space="preserve">2.42860317230225</t>
   </si>
   <si>
     <t xml:space="preserve">2.52992296218872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56983685493469</t>
+    <t xml:space="preserve">2.56983709335327</t>
   </si>
   <si>
     <t xml:space="preserve">2.75098443031311</t>
@@ -3650,13 +3650,13 @@
     <t xml:space="preserve">2.78015208244324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82927680015564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79550361633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79243302345276</t>
+    <t xml:space="preserve">2.82927703857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79550337791443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79243326187134</t>
   </si>
   <si>
     <t xml:space="preserve">2.73870325088501</t>
@@ -3665,7 +3665,7 @@
     <t xml:space="preserve">2.79703879356384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92292094230652</t>
+    <t xml:space="preserve">2.92292070388794</t>
   </si>
   <si>
     <t xml:space="preserve">2.92906141281128</t>
@@ -3680,19 +3680,19 @@
     <t xml:space="preserve">2.91831541061401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89835858345032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80931973457336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7985737323761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93366694450378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94594788551331</t>
+    <t xml:space="preserve">2.89835834503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80931997299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79857397079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93366670608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94594812393188</t>
   </si>
   <si>
     <t xml:space="preserve">2.87226104736328</t>
@@ -3701,25 +3701,25 @@
     <t xml:space="preserve">2.93980741500854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88607740402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96590495109558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95208835601807</t>
+    <t xml:space="preserve">2.88607716560364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96590518951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95208859443665</t>
   </si>
   <si>
     <t xml:space="preserve">2.90603423118591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92752623558044</t>
+    <t xml:space="preserve">2.92752599716187</t>
   </si>
   <si>
     <t xml:space="preserve">2.91678023338318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90296411514282</t>
+    <t xml:space="preserve">2.90296387672424</t>
   </si>
   <si>
     <t xml:space="preserve">2.90756940841675</t>
@@ -3728,19 +3728,19 @@
     <t xml:space="preserve">2.7908980846405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78936290740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75712490081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68343806266785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78168749809265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80624961853027</t>
+    <t xml:space="preserve">2.78936314582825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75712513923645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68343782424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78168702125549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80624938011169</t>
   </si>
   <si>
     <t xml:space="preserve">2.82467126846313</t>
@@ -3749,7 +3749,7 @@
     <t xml:space="preserve">2.81853055953979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88147187232971</t>
+    <t xml:space="preserve">2.88147163391113</t>
   </si>
   <si>
     <t xml:space="preserve">2.86151480674744</t>
@@ -3758,13 +3758,13 @@
     <t xml:space="preserve">2.85230398178101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81239008903503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05271005630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07706642150879</t>
+    <t xml:space="preserve">2.81239032745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05270981788635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07706665992737</t>
   </si>
   <si>
     <t xml:space="preserve">3.13065147399902</t>
@@ -3773,13 +3773,13 @@
     <t xml:space="preserve">3.13877034187317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1176609992981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07544302940369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04946255683899</t>
+    <t xml:space="preserve">3.11766123771667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07544279098511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04946231842041</t>
   </si>
   <si>
     <t xml:space="preserve">3.01211524009705</t>
@@ -3797,13 +3797,13 @@
     <t xml:space="preserve">3.0088677406311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96664929389954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76205277442932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63377404212952</t>
+    <t xml:space="preserve">2.96664953231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7620530128479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6337742805481</t>
   </si>
   <si>
     <t xml:space="preserve">2.62565517425537</t>
@@ -3812,16 +3812,16 @@
     <t xml:space="preserve">2.74256753921509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66137838363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70197296142578</t>
+    <t xml:space="preserve">2.66137862205505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70197319984436</t>
   </si>
   <si>
     <t xml:space="preserve">2.76367664337158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78478574752808</t>
+    <t xml:space="preserve">2.78478598594666</t>
   </si>
   <si>
     <t xml:space="preserve">2.77666711807251</t>
@@ -3830,13 +3830,13 @@
     <t xml:space="preserve">2.6954779624939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73282504081726</t>
+    <t xml:space="preserve">2.73282480239868</t>
   </si>
   <si>
     <t xml:space="preserve">2.69385433197021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7003493309021</t>
+    <t xml:space="preserve">2.70034909248352</t>
   </si>
   <si>
     <t xml:space="preserve">2.75880527496338</t>
@@ -3857,28 +3857,28 @@
     <t xml:space="preserve">2.60129857063293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67274522781372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76042938232422</t>
+    <t xml:space="preserve">2.67274498939514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76042914390564</t>
   </si>
   <si>
     <t xml:space="preserve">2.71821093559265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70359659194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64026927947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51361441612244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52822875976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57207036018372</t>
+    <t xml:space="preserve">2.70359683036804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64026951789856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51361417770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52822852134705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57207059860229</t>
   </si>
   <si>
     <t xml:space="preserve">2.69060659408569</t>
@@ -3887,16 +3887,16 @@
     <t xml:space="preserve">2.61428880691528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57856583595276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5460901260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58343696594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5168616771698</t>
+    <t xml:space="preserve">2.57856559753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54608988761902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58343720436096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51686191558838</t>
   </si>
   <si>
     <t xml:space="preserve">2.55908012390137</t>
@@ -3911,34 +3911,34 @@
     <t xml:space="preserve">2.72957730293274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66949772834778</t>
+    <t xml:space="preserve">2.6694974899292</t>
   </si>
   <si>
     <t xml:space="preserve">2.78153848648071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7360725402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71496367454529</t>
+    <t xml:space="preserve">2.73607230186462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71496343612671</t>
   </si>
   <si>
     <t xml:space="preserve">2.71171569824219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70684432983398</t>
+    <t xml:space="preserve">2.70684456825256</t>
   </si>
   <si>
     <t xml:space="preserve">2.61753630638123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66624975204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60941767692566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56395173072815</t>
+    <t xml:space="preserve">2.66624999046326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60941743850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56395149230957</t>
   </si>
   <si>
     <t xml:space="preserve">2.56232762336731</t>
@@ -3947,7 +3947,7 @@
     <t xml:space="preserve">2.59155607223511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59967470169067</t>
+    <t xml:space="preserve">2.59967494010925</t>
   </si>
   <si>
     <t xml:space="preserve">2.56070399284363</t>
@@ -3956,7 +3956,7 @@
     <t xml:space="preserve">2.59642720222473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59805083274841</t>
+    <t xml:space="preserve">2.59805107116699</t>
   </si>
   <si>
     <t xml:space="preserve">2.58830833435059</t>
@@ -3968,13 +3968,13 @@
     <t xml:space="preserve">2.82050919532776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81726169586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84811329841614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92767858505249</t>
+    <t xml:space="preserve">2.81726145744324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84811353683472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92767882347107</t>
   </si>
   <si>
     <t xml:space="preserve">2.90819334983826</t>
@@ -3983,7 +3983,7 @@
     <t xml:space="preserve">2.88870811462402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83999443054199</t>
+    <t xml:space="preserve">2.83999466896057</t>
   </si>
   <si>
     <t xml:space="preserve">2.78965735435486</t>
@@ -3992,7 +3992,7 @@
     <t xml:space="preserve">2.85136103630066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7880334854126</t>
+    <t xml:space="preserve">2.78803324699402</t>
   </si>
   <si>
     <t xml:space="preserve">2.76530051231384</t>
@@ -4010,7 +4010,7 @@
     <t xml:space="preserve">2.8546085357666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79290509223938</t>
+    <t xml:space="preserve">2.7929048538208</t>
   </si>
   <si>
     <t xml:space="preserve">2.68086385726929</t>
@@ -4025,19 +4025,19 @@
     <t xml:space="preserve">2.64189314842224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75555801391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83512330055237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86435127258301</t>
+    <t xml:space="preserve">2.75555777549744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83512306213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86435151100159</t>
   </si>
   <si>
     <t xml:space="preserve">2.87734150886536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9163122177124</t>
+    <t xml:space="preserve">2.91631245613098</t>
   </si>
   <si>
     <t xml:space="preserve">2.95853066444397</t>
@@ -4064,16 +4064,16 @@
     <t xml:space="preserve">3.04459095001221</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10467076301575</t>
+    <t xml:space="preserve">3.10467100143433</t>
   </si>
   <si>
     <t xml:space="preserve">2.87409400939941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8497371673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89520311355591</t>
+    <t xml:space="preserve">2.84973740577698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89520335197449</t>
   </si>
   <si>
     <t xml:space="preserve">2.88708424568176</t>
@@ -4082,7 +4082,7 @@
     <t xml:space="preserve">2.91793608665466</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04621505737305</t>
+    <t xml:space="preserve">3.04621481895447</t>
   </si>
   <si>
     <t xml:space="preserve">3.05108594894409</t>
@@ -4091,19 +4091,19 @@
     <t xml:space="preserve">3.1014232635498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10629487037659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11441349983215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15987944602966</t>
+    <t xml:space="preserve">3.10629463195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11441373825073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15987968444824</t>
   </si>
   <si>
     <t xml:space="preserve">3.12740397453308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16637492179871</t>
+    <t xml:space="preserve">3.16637468338013</t>
   </si>
   <si>
     <t xml:space="preserve">3.14201784133911</t>
@@ -4112,7 +4112,7 @@
     <t xml:space="preserve">3.1209089756012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08031415939331</t>
+    <t xml:space="preserve">3.08031392097473</t>
   </si>
   <si>
     <t xml:space="preserve">3.07219505310059</t>
@@ -4121,7 +4121,7 @@
     <t xml:space="preserve">3.08193802833557</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09168076515198</t>
+    <t xml:space="preserve">3.0916805267334</t>
   </si>
   <si>
     <t xml:space="preserve">3.09817576408386</t>
@@ -4145,13 +4145,13 @@
     <t xml:space="preserve">3.17611742019653</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14039397239685</t>
+    <t xml:space="preserve">3.14039444923401</t>
   </si>
   <si>
     <t xml:space="preserve">3.12415647506714</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17774105072021</t>
+    <t xml:space="preserve">3.17774128913879</t>
   </si>
   <si>
     <t xml:space="preserve">3.21508836746216</t>
@@ -4169,7 +4169,7 @@
     <t xml:space="preserve">3.27029657363892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31251502037048</t>
+    <t xml:space="preserve">3.3125147819519</t>
   </si>
   <si>
     <t xml:space="preserve">3.3417432308197</t>
@@ -4190,19 +4190,19 @@
     <t xml:space="preserve">3.43917012214661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46190309524536</t>
+    <t xml:space="preserve">3.46190285682678</t>
   </si>
   <si>
     <t xml:space="preserve">3.48301196098328</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51386404037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53822040557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52035880088806</t>
+    <t xml:space="preserve">3.51386380195618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53822064399719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52035927772522</t>
   </si>
   <si>
     <t xml:space="preserve">3.65838050842285</t>
@@ -4220,10 +4220,10 @@
     <t xml:space="preserve">3.7022225856781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68436098098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65026140213013</t>
+    <t xml:space="preserve">3.68436121940613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65026164054871</t>
   </si>
   <si>
     <t xml:space="preserve">3.62428140640259</t>
@@ -4235,7 +4235,7 @@
     <t xml:space="preserve">3.59505319595337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60804295539856</t>
+    <t xml:space="preserve">3.60804319381714</t>
   </si>
   <si>
     <t xml:space="preserve">3.64539003372192</t>
@@ -4244,46 +4244,46 @@
     <t xml:space="preserve">3.59830093383789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64376616477966</t>
+    <t xml:space="preserve">3.64376664161682</t>
   </si>
   <si>
     <t xml:space="preserve">3.61616206169128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68598461151123</t>
+    <t xml:space="preserve">3.68598484992981</t>
   </si>
   <si>
     <t xml:space="preserve">3.69572758674622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81101560592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90032410621643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87921500205994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89869999885559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89382886886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9717710018158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89220499992371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91980934143066</t>
+    <t xml:space="preserve">3.81101608276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90032386779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87921476364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89870047569275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89382863044739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97177052497864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89220547676086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91980957984924</t>
   </si>
   <si>
     <t xml:space="preserve">3.82400631904602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41806077957153</t>
+    <t xml:space="preserve">3.41806101799011</t>
   </si>
   <si>
     <t xml:space="preserve">3.41643738746643</t>
@@ -4298,7 +4298,7 @@
     <t xml:space="preserve">3.09492826461792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37259483337402</t>
+    <t xml:space="preserve">3.3725950717926</t>
   </si>
   <si>
     <t xml:space="preserve">3.28491067886353</t>
@@ -4307,19 +4307,19 @@
     <t xml:space="preserve">3.21995949745178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08843326568604</t>
+    <t xml:space="preserve">3.08843302726746</t>
   </si>
   <si>
     <t xml:space="preserve">3.09330439567566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09979963302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19560265541077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21184086799622</t>
+    <t xml:space="preserve">3.09979939460754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19560289382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21184062957764</t>
   </si>
   <si>
     <t xml:space="preserve">3.1517608165741</t>
@@ -4346,7 +4346,7 @@
     <t xml:space="preserve">3.4342987537384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47326922416687</t>
+    <t xml:space="preserve">3.47326946258545</t>
   </si>
   <si>
     <t xml:space="preserve">3.47002196311951</t>
@@ -4358,22 +4358,22 @@
     <t xml:space="preserve">3.34661459922791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32712888717651</t>
+    <t xml:space="preserve">3.32712912559509</t>
   </si>
   <si>
     <t xml:space="preserve">3.26704931259155</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38720870018005</t>
+    <t xml:space="preserve">3.38720893859863</t>
   </si>
   <si>
     <t xml:space="preserve">3.43105101585388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50736904144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36934733390808</t>
+    <t xml:space="preserve">3.50736880302429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36934757232666</t>
   </si>
   <si>
     <t xml:space="preserve">3.38558530807495</t>
@@ -4382,7 +4382,7 @@
     <t xml:space="preserve">3.38233757019043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38396167755127</t>
+    <t xml:space="preserve">3.38396143913269</t>
   </si>
   <si>
     <t xml:space="preserve">3.33499121665955</t>
@@ -4394,19 +4394,19 @@
     <t xml:space="preserve">3.18703985214233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19400238990784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20096492767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18355870246887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13134098052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04605150222778</t>
+    <t xml:space="preserve">3.19400262832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20096468925476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18355894088745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13134074211121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0460512638092</t>
   </si>
   <si>
     <t xml:space="preserve">3.13308143615723</t>
@@ -4415,22 +4415,22 @@
     <t xml:space="preserve">3.22533321380615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19748377799988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21140837669373</t>
+    <t xml:space="preserve">3.1974835395813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2114086151123</t>
   </si>
   <si>
     <t xml:space="preserve">3.23055481910706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24273943901062</t>
+    <t xml:space="preserve">3.24273920059204</t>
   </si>
   <si>
     <t xml:space="preserve">3.23229551315308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22011160850525</t>
+    <t xml:space="preserve">3.22011137008667</t>
   </si>
   <si>
     <t xml:space="preserve">3.29321646690369</t>
@@ -4439,25 +4439,25 @@
     <t xml:space="preserve">3.25840449333191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28625440597534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30017900466919</t>
+    <t xml:space="preserve">3.28625416755676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30017924308777</t>
   </si>
   <si>
     <t xml:space="preserve">3.34891581535339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38546848297119</t>
+    <t xml:space="preserve">3.38546872138977</t>
   </si>
   <si>
     <t xml:space="preserve">3.41505861282349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37676572799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38024687767029</t>
+    <t xml:space="preserve">3.37676548957825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38024663925171</t>
   </si>
   <si>
     <t xml:space="preserve">3.32106614112854</t>
@@ -4478,28 +4478,28 @@
     <t xml:space="preserve">3.33673167228699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30888223648071</t>
+    <t xml:space="preserve">3.30888199806213</t>
   </si>
   <si>
     <t xml:space="preserve">3.34369397163391</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40809607505798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42028069496155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4342052936554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50905132293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53167915344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55430698394775</t>
+    <t xml:space="preserve">3.40809631347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42028045654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43420553207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50905108451843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5316789150238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55430674552917</t>
   </si>
   <si>
     <t xml:space="preserve">3.63785552978516</t>
@@ -4514,7 +4514,7 @@
     <t xml:space="preserve">3.70922040939331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78406596183777</t>
+    <t xml:space="preserve">3.78406620025635</t>
   </si>
   <si>
     <t xml:space="preserve">3.82409977912903</t>
@@ -4526,31 +4526,31 @@
     <t xml:space="preserve">3.75099468231201</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72140431404114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7318480014801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73881030082703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52471661567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65352082252502</t>
+    <t xml:space="preserve">3.72140455245972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73184823989868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73881053924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52471685409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6535210609436</t>
   </si>
   <si>
     <t xml:space="preserve">3.68833303451538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74229168891907</t>
+    <t xml:space="preserve">3.74229192733765</t>
   </si>
   <si>
     <t xml:space="preserve">3.73358845710754</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6848521232605</t>
+    <t xml:space="preserve">3.68485188484192</t>
   </si>
   <si>
     <t xml:space="preserve">3.64655876159668</t>
@@ -4559,37 +4559,37 @@
     <t xml:space="preserve">3.68137073516846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69007349014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71270132064819</t>
+    <t xml:space="preserve">3.69007325172424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71270108222961</t>
   </si>
   <si>
     <t xml:space="preserve">3.72314476966858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80321264266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83802461624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8171374797821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76666021347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7684006690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86065268516541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90416789054871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90590786933899</t>
+    <t xml:space="preserve">3.8032124042511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83802437782288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81713771820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76665997505188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76840043067932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86065220832825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90416741371155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90590834617615</t>
   </si>
   <si>
     <t xml:space="preserve">4.00338172912598</t>
@@ -4604,7 +4604,7 @@
     <t xml:space="preserve">4.07648706436157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17744159698486</t>
+    <t xml:space="preserve">4.17744207382202</t>
   </si>
   <si>
     <t xml:space="preserve">4.34976148605347</t>
@@ -4634,7 +4634,7 @@
     <t xml:space="preserve">4.31668996810913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22095632553101</t>
+    <t xml:space="preserve">4.22095680236816</t>
   </si>
   <si>
     <t xml:space="preserve">4.19310712814331</t>
@@ -4643,7 +4643,7 @@
     <t xml:space="preserve">4.28884029388428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3732590675354</t>
+    <t xml:space="preserve">4.37325954437256</t>
   </si>
   <si>
     <t xml:space="preserve">4.3393177986145</t>
@@ -4715,10 +4715,10 @@
     <t xml:space="preserve">5.0607967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21309900283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1956934928894</t>
+    <t xml:space="preserve">5.21309947967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19569301605225</t>
   </si>
   <si>
     <t xml:space="preserve">5.13042068481445</t>
@@ -4727,7 +4727,7 @@
     <t xml:space="preserve">5.14347505569458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08690595626831</t>
+    <t xml:space="preserve">5.08690547943115</t>
   </si>
   <si>
     <t xml:space="preserve">5.04774236679077</t>
@@ -4832,13 +4832,13 @@
     <t xml:space="preserve">5.33494138717651</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55251693725586</t>
+    <t xml:space="preserve">5.5525164604187</t>
   </si>
   <si>
     <t xml:space="preserve">5.65695238113403</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7048192024231</t>
+    <t xml:space="preserve">5.70481872558594</t>
   </si>
   <si>
     <t xml:space="preserve">5.7091703414917</t>
@@ -4856,7 +4856,7 @@
     <t xml:space="preserve">6.13561773300171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80055236816406</t>
+    <t xml:space="preserve">5.8005518913269</t>
   </si>
   <si>
     <t xml:space="preserve">5.78749752044678</t>
@@ -4865,7 +4865,7 @@
     <t xml:space="preserve">5.87017583847046</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83971548080444</t>
+    <t xml:space="preserve">5.8397159576416</t>
   </si>
   <si>
     <t xml:space="preserve">5.71352195739746</t>
@@ -4874,10 +4874,10 @@
     <t xml:space="preserve">5.72222471237183</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84406757354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93109750747681</t>
+    <t xml:space="preserve">5.84406709671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93109703063965</t>
   </si>
   <si>
     <t xml:space="preserve">5.97896337509155</t>
@@ -4886,7 +4886,7 @@
     <t xml:space="preserve">5.94415140151978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89628505706787</t>
+    <t xml:space="preserve">5.89628553390503</t>
   </si>
   <si>
     <t xml:space="preserve">5.98766660690308</t>
@@ -4904,7 +4904,7 @@
     <t xml:space="preserve">6.24005365371704</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17913293838501</t>
+    <t xml:space="preserve">6.17913246154785</t>
   </si>
   <si>
     <t xml:space="preserve">6.01812744140625</t>
@@ -4913,10 +4913,10 @@
     <t xml:space="preserve">6.16172647476196</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23570251464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23135042190552</t>
+    <t xml:space="preserve">6.23570203781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23135089874268</t>
   </si>
   <si>
     <t xml:space="preserve">6.07904815673828</t>
@@ -4925,7 +4925,7 @@
     <t xml:space="preserve">6.00507259368896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86582469940186</t>
+    <t xml:space="preserve">5.8658242225647</t>
   </si>
   <si>
     <t xml:space="preserve">5.69176435470581</t>
@@ -4937,34 +4937,34 @@
     <t xml:space="preserve">5.91369104385376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93979978561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18783569335938</t>
+    <t xml:space="preserve">5.93980026245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18783617019653</t>
   </si>
   <si>
     <t xml:space="preserve">6.065993309021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0398850440979</t>
+    <t xml:space="preserve">6.03988456726074</t>
   </si>
   <si>
     <t xml:space="preserve">6.09645414352417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22264814376831</t>
+    <t xml:space="preserve">6.22264766693115</t>
   </si>
   <si>
     <t xml:space="preserve">5.93544864654541</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06164264678955</t>
+    <t xml:space="preserve">6.06164216995239</t>
   </si>
   <si>
     <t xml:space="preserve">5.82666110992432</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85276985168457</t>
+    <t xml:space="preserve">5.85277032852173</t>
   </si>
   <si>
     <t xml:space="preserve">5.92674541473389</t>
@@ -4973,28 +4973,28 @@
     <t xml:space="preserve">6.11821174621582</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37930154800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53595638275146</t>
+    <t xml:space="preserve">6.37930202484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53595590591431</t>
   </si>
   <si>
     <t xml:space="preserve">6.53160429000854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47068357467651</t>
+    <t xml:space="preserve">6.47068309783936</t>
   </si>
   <si>
     <t xml:space="preserve">6.66650104522705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82315492630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8405613899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90148162841797</t>
+    <t xml:space="preserve">6.82315540313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84056091308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90148210525513</t>
   </si>
   <si>
     <t xml:space="preserve">6.80574893951416</t>
@@ -5003,7 +5003,7 @@
     <t xml:space="preserve">6.95369958877563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07119035720825</t>
+    <t xml:space="preserve">7.07119083404541</t>
   </si>
   <si>
     <t xml:space="preserve">6.96240282058716</t>
@@ -5015,10 +5015,10 @@
     <t xml:space="preserve">6.99286365509033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12775945663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12340927124023</t>
+    <t xml:space="preserve">7.12775993347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12340879440308</t>
   </si>
   <si>
     <t xml:space="preserve">7.20173501968384</t>
@@ -6003,6 +6003,9 @@
   </si>
   <si>
     <t xml:space="preserve">15.4250001907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.835000038147</t>
   </si>
 </sst>
 </file>
@@ -72147,7 +72150,7 @@
     </row>
     <row r="2532">
       <c r="A2532" s="1" t="n">
-        <v>46003.6932523148</v>
+        <v>46003.3333333333</v>
       </c>
       <c r="B2532" t="n">
         <v>765504</v>
@@ -72156,7 +72159,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="D2532" t="n">
-        <v>15.4499998092651</v>
+        <v>15.4250001907349</v>
       </c>
       <c r="E2532" t="n">
         <v>15.6499996185303</v>
@@ -72168,6 +72171,32 @@
         <v>1996</v>
       </c>
       <c r="H2532" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2533">
+      <c r="A2533" s="1" t="n">
+        <v>46006.6912615741</v>
+      </c>
+      <c r="B2533" t="n">
+        <v>890105</v>
+      </c>
+      <c r="C2533" t="n">
+        <v>15.8500003814697</v>
+      </c>
+      <c r="D2533" t="n">
+        <v>15.585000038147</v>
+      </c>
+      <c r="E2533" t="n">
+        <v>15.6549997329712</v>
+      </c>
+      <c r="F2533" t="n">
+        <v>15.835000038147</v>
+      </c>
+      <c r="G2533" t="s">
+        <v>1997</v>
+      </c>
+      <c r="H2533" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BPSO.MI.xlsx
+++ b/data/BPSO.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2002" uniqueCount="2002">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2003" uniqueCount="2003">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,31 +44,31 @@
     <t xml:space="preserve">BPSO.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80963730812073</t>
+    <t xml:space="preserve">2.80963754653931</t>
   </si>
   <si>
     <t xml:space="preserve">2.74855804443359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71246576309204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63611674308777</t>
+    <t xml:space="preserve">2.71246600151062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63611721992493</t>
   </si>
   <si>
     <t xml:space="preserve">2.60835409164429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69303202629089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69858431816101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61113047599792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51257038116455</t>
+    <t xml:space="preserve">2.69303178787231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69858479499817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61113023757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51257061958313</t>
   </si>
   <si>
     <t xml:space="preserve">2.45565629005432</t>
@@ -77,28 +77,28 @@
     <t xml:space="preserve">2.2668662071228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38069534301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40568232536316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36542582511902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51951169967651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44455122947693</t>
+    <t xml:space="preserve">2.38069558143616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40568208694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36542558670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51951122283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44455099105835</t>
   </si>
   <si>
     <t xml:space="preserve">2.35570883750916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43899846076965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40429425239563</t>
+    <t xml:space="preserve">2.43899893760681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40429449081421</t>
   </si>
   <si>
     <t xml:space="preserve">2.32100486755371</t>
@@ -107,13 +107,13 @@
     <t xml:space="preserve">2.22105741500854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23216223716736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20995187759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04059624671936</t>
+    <t xml:space="preserve">2.23216247558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20995211601257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04059600830078</t>
   </si>
   <si>
     <t xml:space="preserve">2.06280636787415</t>
@@ -122,34 +122,34 @@
     <t xml:space="preserve">2.14331984519958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07668781280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18218851089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22522139549255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27797150611877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19329333305359</t>
+    <t xml:space="preserve">2.07668805122375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1821882724762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22522163391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2779712677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19329380989075</t>
   </si>
   <si>
     <t xml:space="preserve">2.16553044319153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24604415893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18635296821594</t>
+    <t xml:space="preserve">2.24604392051697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18635249137878</t>
   </si>
   <si>
     <t xml:space="preserve">2.1766357421875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21550464630127</t>
+    <t xml:space="preserve">2.21550488471985</t>
   </si>
   <si>
     <t xml:space="preserve">2.25992560386658</t>
@@ -158,37 +158,37 @@
     <t xml:space="preserve">2.31822848320007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38763642311096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38208365440369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37514305114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2418794631958</t>
+    <t xml:space="preserve">2.38763618469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38208341598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3751425743103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24187970161438</t>
   </si>
   <si>
     <t xml:space="preserve">2.26270174980164</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25020861625671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31961679458618</t>
+    <t xml:space="preserve">2.25020837783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3196165561676</t>
   </si>
   <si>
     <t xml:space="preserve">2.43344521522522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35848522186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30156970024109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34599184989929</t>
+    <t xml:space="preserve">2.35848498344421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30156993865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34599161148071</t>
   </si>
   <si>
     <t xml:space="preserve">2.35987329483032</t>
@@ -197,58 +197,58 @@
     <t xml:space="preserve">2.39318895339966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29324078559875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23771524429321</t>
+    <t xml:space="preserve">2.29324126243591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23771500587463</t>
   </si>
   <si>
     <t xml:space="preserve">2.18774080276489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.139155626297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14748454093933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12110924720764</t>
+    <t xml:space="preserve">2.13915586471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14748477935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12110996246338</t>
   </si>
   <si>
     <t xml:space="preserve">2.06974744796753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01283288002014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01838564872742</t>
+    <t xml:space="preserve">2.01283311843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01838541030884</t>
   </si>
   <si>
     <t xml:space="preserve">2.07113552093506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11694502830505</t>
+    <t xml:space="preserve">2.11694526672363</t>
   </si>
   <si>
     <t xml:space="preserve">2.12527394294739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22799825668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30295825004578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23910307884216</t>
+    <t xml:space="preserve">2.22799777984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3029580116272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23910331726074</t>
   </si>
   <si>
     <t xml:space="preserve">2.29046487808228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33211016654968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32655787467957</t>
+    <t xml:space="preserve">2.3321099281311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32655763626099</t>
   </si>
   <si>
     <t xml:space="preserve">2.2793595790863</t>
@@ -257,13 +257,13 @@
     <t xml:space="preserve">2.32378101348877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30851101875305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26131367683411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.234938621521</t>
+    <t xml:space="preserve">2.30851078033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26131343841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23493885993958</t>
   </si>
   <si>
     <t xml:space="preserve">2.15720152854919</t>
@@ -272,13 +272,13 @@
     <t xml:space="preserve">2.11139225959778</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08224058151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09889912605286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08918190002441</t>
+    <t xml:space="preserve">2.08224081993103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09889936447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08918213844299</t>
   </si>
   <si>
     <t xml:space="preserve">2.10583996772766</t>
@@ -287,19 +287,19 @@
     <t xml:space="preserve">2.04892516136169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03781962394714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06558275222778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03226709365845</t>
+    <t xml:space="preserve">2.03781938552856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0655825138092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03226685523987</t>
   </si>
   <si>
     <t xml:space="preserve">2.07252359390259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05725359916687</t>
+    <t xml:space="preserve">2.05725407600403</t>
   </si>
   <si>
     <t xml:space="preserve">2.05156707763672</t>
@@ -308,46 +308,46 @@
     <t xml:space="preserve">2.12691879272461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19942736625671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15393209457397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17525792121887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15535378456116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09279704093933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07147097587585</t>
+    <t xml:space="preserve">2.19942760467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15393233299255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17525839805603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15535402297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09279727935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07147121429443</t>
   </si>
   <si>
     <t xml:space="preserve">1.99896240234375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95773208141327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87669265270233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98901033401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93640649318695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94351494312286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84114968776703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78143692016602</t>
+    <t xml:space="preserve">1.95773243904114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87669312953949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98901009559631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93640613555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94351506233215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84114944934845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78143727779388</t>
   </si>
   <si>
     <t xml:space="preserve">1.75157999992371</t>
@@ -356,202 +356,202 @@
     <t xml:space="preserve">1.72598874568939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64210617542267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69613230228424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77006268501282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81129324436188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78001463413239</t>
+    <t xml:space="preserve">1.64210605621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6961327791214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77006244659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81129348278046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78001427650452</t>
   </si>
   <si>
     <t xml:space="preserve">1.89375364780426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63499736785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56533288955688</t>
+    <t xml:space="preserve">1.63499772548676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5653327703476</t>
   </si>
   <si>
     <t xml:space="preserve">1.66911971569061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65632355213165</t>
+    <t xml:space="preserve">1.65632343292236</t>
   </si>
   <si>
     <t xml:space="preserve">1.63926267623901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63641917705536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57670640945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51130652427673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52552354335785</t>
+    <t xml:space="preserve">1.63641941547394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57670676708221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51130640506744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52552366256714</t>
   </si>
   <si>
     <t xml:space="preserve">1.53121066093445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63784074783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67196333408356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69471073150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67054164409637</t>
+    <t xml:space="preserve">1.63784110546112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67196321487427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69471085071564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67054152488708</t>
   </si>
   <si>
     <t xml:space="preserve">1.74304974079132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70892822742462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72172379493713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77574956417084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76721906661987</t>
+    <t xml:space="preserve">1.70892798900604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72172391414642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77574944496155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76721894741058</t>
   </si>
   <si>
     <t xml:space="preserve">1.72741067409515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69755446910858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72456729412079</t>
+    <t xml:space="preserve">1.69755423069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72456741333008</t>
   </si>
   <si>
     <t xml:space="preserve">1.71888029575348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66343295574188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55395889282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57528483867645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52125859260559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63357579708099</t>
+    <t xml:space="preserve">1.66343283653259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55395877361298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57528507709503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5212584733963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63357603549957</t>
   </si>
   <si>
     <t xml:space="preserve">1.65916693210602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64779305458069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68760240077972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71461510658264</t>
+    <t xml:space="preserve">1.64779317378998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68760204315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71461534500122</t>
   </si>
   <si>
     <t xml:space="preserve">1.70608460903168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70039784908295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74447154998779</t>
+    <t xml:space="preserve">1.70039772987366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74447131156921</t>
   </si>
   <si>
     <t xml:space="preserve">1.70750629901886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72030198574066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73167610168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78285896778107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7785929441452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77148449420929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76437556743622</t>
+    <t xml:space="preserve">1.72030210494995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73167586326599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7828586101532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77859258651733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77148425579071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76437532901764</t>
   </si>
   <si>
     <t xml:space="preserve">1.75584530830383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76295387744904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74162793159485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76864087581635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74873661994934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73451948165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78428030014038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85252344608307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8496800661087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81271541118622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83546268939972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84825825691223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85963213443756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94778025150299</t>
+    <t xml:space="preserve">1.76295399665833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74162781238556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76864075660706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74873650074005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73451936244965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78428041934967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85252368450165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84967994689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81271517276764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83546257019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84825813770294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85963189601898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9477801322937</t>
   </si>
   <si>
     <t xml:space="preserve">1.97621464729309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09848380088806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10843634605408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07573628425598</t>
+    <t xml:space="preserve">2.09848427772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1084361076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07573652267456</t>
   </si>
   <si>
     <t xml:space="preserve">2.08568835258484</t>
@@ -560,7 +560,7 @@
     <t xml:space="preserve">2.08853197097778</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09706234931946</t>
+    <t xml:space="preserve">2.09706211090088</t>
   </si>
   <si>
     <t xml:space="preserve">2.16104078292847</t>
@@ -569,10 +569,10 @@
     <t xml:space="preserve">2.18236660957336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11412286758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00038385391235</t>
+    <t xml:space="preserve">2.11412310600281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00038409233093</t>
   </si>
   <si>
     <t xml:space="preserve">2.03877139091492</t>
@@ -581,13 +581,13 @@
     <t xml:space="preserve">2.00891447067261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05298852920532</t>
+    <t xml:space="preserve">2.0529887676239</t>
   </si>
   <si>
     <t xml:space="preserve">2.06294083595276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11554503440857</t>
+    <t xml:space="preserve">2.11554455757141</t>
   </si>
   <si>
     <t xml:space="preserve">2.12549686431885</t>
@@ -596,67 +596,67 @@
     <t xml:space="preserve">2.16246247291565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15961885452271</t>
+    <t xml:space="preserve">2.15961933135986</t>
   </si>
   <si>
     <t xml:space="preserve">2.13260555267334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08142328262329</t>
+    <t xml:space="preserve">2.08142304420471</t>
   </si>
   <si>
     <t xml:space="preserve">2.03592801094055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07715821266174</t>
+    <t xml:space="preserve">2.07715797424316</t>
   </si>
   <si>
     <t xml:space="preserve">2.09990572929382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08995389938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01033616065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12407517433167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10417079925537</t>
+    <t xml:space="preserve">2.08995342254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01033592224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12407493591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10417103767395</t>
   </si>
   <si>
     <t xml:space="preserve">2.07289290428162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16814947128296</t>
+    <t xml:space="preserve">2.16814970970154</t>
   </si>
   <si>
     <t xml:space="preserve">2.27478003501892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37430191040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2634060382843</t>
+    <t xml:space="preserve">2.37430167198181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26340579986572</t>
   </si>
   <si>
     <t xml:space="preserve">2.23354911804199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27193665504456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23212718963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17810153961182</t>
+    <t xml:space="preserve">2.2719361782074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23212742805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1781017780304</t>
   </si>
   <si>
     <t xml:space="preserve">2.16957139968872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23639273643494</t>
+    <t xml:space="preserve">2.23639249801636</t>
   </si>
   <si>
     <t xml:space="preserve">2.22217512130737</t>
@@ -665,31 +665,31 @@
     <t xml:space="preserve">2.21791005134583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20511436462402</t>
+    <t xml:space="preserve">2.2051146030426</t>
   </si>
   <si>
     <t xml:space="preserve">2.22359704971313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26482725143433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31032276153564</t>
+    <t xml:space="preserve">2.26482772827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31032299995422</t>
   </si>
   <si>
     <t xml:space="preserve">2.31743168830872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34302306175232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34160137176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30463600158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29752731323242</t>
+    <t xml:space="preserve">2.34302258491516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34160113334656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30463576316833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29752707481384</t>
   </si>
   <si>
     <t xml:space="preserve">2.29610586166382</t>
@@ -698,10 +698,10 @@
     <t xml:space="preserve">2.36008358001709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35297513008118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34017968177795</t>
+    <t xml:space="preserve">2.3529748916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3401792049408</t>
   </si>
   <si>
     <t xml:space="preserve">2.4027361869812</t>
@@ -710,70 +710,70 @@
     <t xml:space="preserve">2.41695356369019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45249676704407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4112663269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.415531873703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4240620136261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44396638870239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35439705848694</t>
+    <t xml:space="preserve">2.45249652862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41126680374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41553211212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42406225204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44396662712097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35439658164978</t>
   </si>
   <si>
     <t xml:space="preserve">2.33733582496643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33022713661194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3643491268158</t>
+    <t xml:space="preserve">2.33022737503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36434888839722</t>
   </si>
   <si>
     <t xml:space="preserve">2.32738399505615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28188872337341</t>
+    <t xml:space="preserve">2.28188824653625</t>
   </si>
   <si>
     <t xml:space="preserve">2.30037093162537</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32311844825745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33449220657349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30890154838562</t>
+    <t xml:space="preserve">2.32311868667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33449244499207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30890130996704</t>
   </si>
   <si>
     <t xml:space="preserve">2.2989490032196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25629734992981</t>
+    <t xml:space="preserve">2.25629711151123</t>
   </si>
   <si>
     <t xml:space="preserve">2.12834048271179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1340274810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2847318649292</t>
+    <t xml:space="preserve">2.13402724266052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28473162651062</t>
   </si>
   <si>
     <t xml:space="preserve">2.22928380966187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27335786819458</t>
+    <t xml:space="preserve">2.27335810661316</t>
   </si>
   <si>
     <t xml:space="preserve">2.27904486656189</t>
@@ -782,16 +782,16 @@
     <t xml:space="preserve">2.31316661834717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33875775337219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37856650352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32880592346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36719226837158</t>
+    <t xml:space="preserve">2.33875799179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37856698036194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32880568504333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36719250679016</t>
   </si>
   <si>
     <t xml:space="preserve">2.34870958328247</t>
@@ -803,22 +803,22 @@
     <t xml:space="preserve">2.30321431159973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28757500648499</t>
+    <t xml:space="preserve">2.28757548332214</t>
   </si>
   <si>
     <t xml:space="preserve">2.32027506828308</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2833104133606</t>
+    <t xml:space="preserve">2.28331017494202</t>
   </si>
   <si>
     <t xml:space="preserve">2.29041862487793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29326248168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30605816841125</t>
+    <t xml:space="preserve">2.29326224327087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30605792999268</t>
   </si>
   <si>
     <t xml:space="preserve">2.35581827163696</t>
@@ -830,16 +830,16 @@
     <t xml:space="preserve">2.3316490650177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46671414375305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43117117881775</t>
+    <t xml:space="preserve">2.46671390533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43117094039917</t>
   </si>
   <si>
     <t xml:space="preserve">2.42974925041199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49799275398254</t>
+    <t xml:space="preserve">2.49799299240112</t>
   </si>
   <si>
     <t xml:space="preserve">2.46387052536011</t>
@@ -851,13 +851,13 @@
     <t xml:space="preserve">2.5164749622345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51789712905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56907916069031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.533536195755</t>
+    <t xml:space="preserve">2.51789689064026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56907963752747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53353595733643</t>
   </si>
   <si>
     <t xml:space="preserve">2.48803973197937</t>
@@ -869,25 +869,25 @@
     <t xml:space="preserve">2.5079448223114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50936675071716</t>
+    <t xml:space="preserve">2.50936627388</t>
   </si>
   <si>
     <t xml:space="preserve">2.50652313232422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55486178398132</t>
+    <t xml:space="preserve">2.5548620223999</t>
   </si>
   <si>
     <t xml:space="preserve">2.57221221923828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63293838500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65607309341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70667839050293</t>
+    <t xml:space="preserve">2.63293862342834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65607333183289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70667862892151</t>
   </si>
   <si>
     <t xml:space="preserve">2.56642889976501</t>
@@ -905,46 +905,46 @@
     <t xml:space="preserve">2.5216064453125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5143768787384</t>
+    <t xml:space="preserve">2.51437664031982</t>
   </si>
   <si>
     <t xml:space="preserve">2.4710009098053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48979711532593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47533869743347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51726841926575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45654225349426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47967600822449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46088004112244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48112201690674</t>
+    <t xml:space="preserve">2.48979687690735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47533822059631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51726865768433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45654249191284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47967576980591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46087956428528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48112177848816</t>
   </si>
   <si>
     <t xml:space="preserve">2.45798802375793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48256754875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48835110664368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48690557479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50859355926514</t>
+    <t xml:space="preserve">2.48256778717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48835134506226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48690533638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50859332084656</t>
   </si>
   <si>
     <t xml:space="preserve">2.53751134872437</t>
@@ -956,19 +956,19 @@
     <t xml:space="preserve">2.55919933319092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49558091163635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59245419502258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66330242156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61414265632629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63149261474609</t>
+    <t xml:space="preserve">2.49558067321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59245443344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66330218315125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61414241790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63149285316467</t>
   </si>
   <si>
     <t xml:space="preserve">2.6228175163269</t>
@@ -977,16 +977,16 @@
     <t xml:space="preserve">2.61703419685364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72692060470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73704195022583</t>
+    <t xml:space="preserve">2.72692084312439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73704171180725</t>
   </si>
   <si>
     <t xml:space="preserve">2.72258281707764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71246218681335</t>
+    <t xml:space="preserve">2.71246194839478</t>
   </si>
   <si>
     <t xml:space="preserve">2.71390795707703</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">2.70812439918518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68932795524597</t>
+    <t xml:space="preserve">2.68932843208313</t>
   </si>
   <si>
     <t xml:space="preserve">2.68643641471863</t>
@@ -1007,16 +1007,16 @@
     <t xml:space="preserve">2.71101641654968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6502890586853</t>
+    <t xml:space="preserve">2.65028882026672</t>
   </si>
   <si>
     <t xml:space="preserve">2.67920732498169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67197751998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67053174972534</t>
+    <t xml:space="preserve">2.67197775840759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67053198814392</t>
   </si>
   <si>
     <t xml:space="preserve">2.65318059921265</t>
@@ -1028,10 +1028,10 @@
     <t xml:space="preserve">2.66763997077942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65896511077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64595174789429</t>
+    <t xml:space="preserve">2.65896487236023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64595150947571</t>
   </si>
   <si>
     <t xml:space="preserve">2.59823775291443</t>
@@ -1040,37 +1040,37 @@
     <t xml:space="preserve">2.62426328659058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6040210723877</t>
+    <t xml:space="preserve">2.60402131080627</t>
   </si>
   <si>
     <t xml:space="preserve">2.54474067687988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57654976844788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52449774742126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48545932769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50281000137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52016043663025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51148509979248</t>
+    <t xml:space="preserve">2.57655000686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52449798583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48545956611633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50280976295471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52016019821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51148533821106</t>
   </si>
   <si>
     <t xml:space="preserve">2.518714427948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53317284584045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55197024345398</t>
+    <t xml:space="preserve">2.53317332267761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5519700050354</t>
   </si>
   <si>
     <t xml:space="preserve">2.50714755058289</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">2.55052423477173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54618668556213</t>
+    <t xml:space="preserve">2.54618644714355</t>
   </si>
   <si>
     <t xml:space="preserve">2.53606557846069</t>
@@ -1088,49 +1088,49 @@
     <t xml:space="preserve">2.5794415473938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64161372184753</t>
+    <t xml:space="preserve">2.64161396026611</t>
   </si>
   <si>
     <t xml:space="preserve">2.63004684448242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58956289291382</t>
+    <t xml:space="preserve">2.58956241607666</t>
   </si>
   <si>
     <t xml:space="preserve">2.52305197715759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51582264900208</t>
+    <t xml:space="preserve">2.51582288742065</t>
   </si>
   <si>
     <t xml:space="preserve">2.49268865585327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53461909294128</t>
+    <t xml:space="preserve">2.53461885452271</t>
   </si>
   <si>
     <t xml:space="preserve">2.49124312400818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47244668006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50425553321838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48401355743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49413466453552</t>
+    <t xml:space="preserve">2.47244691848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50425577163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4840133190155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49413442611694</t>
   </si>
   <si>
     <t xml:space="preserve">2.49847221374512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47822999954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51293063163757</t>
+    <t xml:space="preserve">2.47823023796082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51293087005615</t>
   </si>
   <si>
     <t xml:space="preserve">2.44931292533875</t>
@@ -1145,55 +1145,55 @@
     <t xml:space="preserve">2.41027355194092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29605054855347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24689030647278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28159093856812</t>
+    <t xml:space="preserve">2.29605031013489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2468900680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28159070014954</t>
   </si>
   <si>
     <t xml:space="preserve">2.18471765518188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19773030281067</t>
+    <t xml:space="preserve">2.19773054122925</t>
   </si>
   <si>
     <t xml:space="preserve">2.22086429595947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26279449462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28448247909546</t>
+    <t xml:space="preserve">2.26279473304749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28448271751404</t>
   </si>
   <si>
     <t xml:space="preserve">2.28592848777771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3249671459198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34810137748718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3784646987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41461229324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34231805801392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35677671432495</t>
+    <t xml:space="preserve">2.32496738433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34810161590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37846493721008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41461181640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34231781959534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35677647590637</t>
   </si>
   <si>
     <t xml:space="preserve">2.35966825485229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34087228775024</t>
+    <t xml:space="preserve">2.34087204933167</t>
   </si>
   <si>
     <t xml:space="preserve">2.37701869010925</t>
@@ -1202,100 +1202,100 @@
     <t xml:space="preserve">2.39292335510254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40015292167664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40593647956848</t>
+    <t xml:space="preserve">2.40015244483948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4059362411499</t>
   </si>
   <si>
     <t xml:space="preserve">2.33653426170349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29315757751465</t>
+    <t xml:space="preserve">2.29315781593323</t>
   </si>
   <si>
     <t xml:space="preserve">2.20495986938477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23966073989868</t>
+    <t xml:space="preserve">2.2396605014801</t>
   </si>
   <si>
     <t xml:space="preserve">2.23821473121643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23387694358826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18327140808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21797251701355</t>
+    <t xml:space="preserve">2.23387718200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18327212333679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21797275543213</t>
   </si>
   <si>
     <t xml:space="preserve">2.24544405937195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20062208175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2266480922699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28303670883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31340050697327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31050896644592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38858532905579</t>
+    <t xml:space="preserve">2.20062184333801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22664785385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28303694725037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31340098381042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31050872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38858580589294</t>
   </si>
   <si>
     <t xml:space="preserve">2.38713979721069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34665608406067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34520983695984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36545205116272</t>
+    <t xml:space="preserve">2.34665560722351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34520959854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3654522895813</t>
   </si>
   <si>
     <t xml:space="preserve">2.39436912536621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4030442237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40449047088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3278591632843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34954738616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33364272117615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31195449829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22953987121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31484651565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30327939987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32063007354736</t>
+    <t xml:space="preserve">2.40304446220398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40449023246765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32785964012146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34954690933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33364295959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31195473670959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22953963279724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31484627723694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30327987670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32062983512878</t>
   </si>
   <si>
     <t xml:space="preserve">2.3076171875</t>
@@ -1304,10 +1304,10 @@
     <t xml:space="preserve">2.37268114089966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42907071113586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36400580406189</t>
+    <t xml:space="preserve">2.42907047271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36400604248047</t>
   </si>
   <si>
     <t xml:space="preserve">2.31629228591919</t>
@@ -1316,19 +1316,19 @@
     <t xml:space="preserve">2.35388493537903</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27725338935852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32930517196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30617141723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3003876209259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37412691116333</t>
+    <t xml:space="preserve">2.27725291252136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32930493354797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30617165565491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30038785934448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37412714958191</t>
   </si>
   <si>
     <t xml:space="preserve">2.33075094223022</t>
@@ -1337,22 +1337,22 @@
     <t xml:space="preserve">2.32641363143921</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39726090431213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39870691299438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38569378852844</t>
+    <t xml:space="preserve">2.39726066589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39870667457581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38569402694702</t>
   </si>
   <si>
     <t xml:space="preserve">2.60112977027893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71969175338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70957016944885</t>
+    <t xml:space="preserve">2.71969151496887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70957040786743</t>
   </si>
   <si>
     <t xml:space="preserve">2.75439214706421</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">2.77752661705017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8483738899231</t>
+    <t xml:space="preserve">2.84837436676025</t>
   </si>
   <si>
     <t xml:space="preserve">2.84114480018616</t>
@@ -1376,31 +1376,31 @@
     <t xml:space="preserve">2.90042591094971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82957792282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73125863075256</t>
+    <t xml:space="preserve">2.8295783996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73125839233398</t>
   </si>
   <si>
     <t xml:space="preserve">2.78620195388794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75583815574646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82524013519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80644416809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83680725097656</t>
+    <t xml:space="preserve">2.75583791732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82524037361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80644392967224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83680748939514</t>
   </si>
   <si>
     <t xml:space="preserve">2.74716281890869</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73848748207092</t>
+    <t xml:space="preserve">2.7384877204895</t>
   </si>
   <si>
     <t xml:space="preserve">2.63438439369202</t>
@@ -1412,22 +1412,22 @@
     <t xml:space="preserve">2.65060067176819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71251726150513</t>
+    <t xml:space="preserve">2.71251702308655</t>
   </si>
   <si>
     <t xml:space="preserve">2.70367121696472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63143610954285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52824258804321</t>
+    <t xml:space="preserve">2.63143634796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52824234962463</t>
   </si>
   <si>
     <t xml:space="preserve">2.4825427532196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52234554290771</t>
+    <t xml:space="preserve">2.52234578132629</t>
   </si>
   <si>
     <t xml:space="preserve">2.56509733200073</t>
@@ -1442,13 +1442,13 @@
     <t xml:space="preserve">2.51939725875854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59163331985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61816835403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59015893936157</t>
+    <t xml:space="preserve">2.59163308143616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.618168592453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59015917778015</t>
   </si>
   <si>
     <t xml:space="preserve">2.54888105392456</t>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">2.55625200271606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54593276977539</t>
+    <t xml:space="preserve">2.54593253135681</t>
   </si>
   <si>
     <t xml:space="preserve">2.57099390029907</t>
@@ -1469,7 +1469,7 @@
     <t xml:space="preserve">2.51350069046021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51055240631104</t>
+    <t xml:space="preserve">2.51055216789246</t>
   </si>
   <si>
     <t xml:space="preserve">2.53708744049072</t>
@@ -1478,10 +1478,10 @@
     <t xml:space="preserve">2.54151010513306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65354895591736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65944576263428</t>
+    <t xml:space="preserve">2.65354871749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6594455242157</t>
   </si>
   <si>
     <t xml:space="preserve">2.70514535903931</t>
@@ -1490,61 +1490,61 @@
     <t xml:space="preserve">2.69040369987488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65797138214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61964249610901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63291025161743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6491265296936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64322924613953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66534233093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64470386505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63880753517151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66386842727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71399092674255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73168134689331</t>
+    <t xml:space="preserve">2.65797162055969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61964273452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63291049003601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64912629127502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64322948455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6653425693512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64470362663269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63880705833435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66386818885803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71399140357971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73168158531189</t>
   </si>
   <si>
     <t xml:space="preserve">2.7169394493103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73315596580505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78180384635925</t>
+    <t xml:space="preserve">2.73315572738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78180408477783</t>
   </si>
   <si>
     <t xml:space="preserve">2.70661950111389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69187760353088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68892931938171</t>
+    <t xml:space="preserve">2.69187808036804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68892908096313</t>
   </si>
   <si>
     <t xml:space="preserve">2.67713570594788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64617824554443</t>
+    <t xml:space="preserve">2.64617800712585</t>
   </si>
   <si>
     <t xml:space="preserve">2.6417555809021</t>
@@ -1553,7 +1553,7 @@
     <t xml:space="preserve">2.57541656494141</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61374568939209</t>
+    <t xml:space="preserve">2.61374592781067</t>
   </si>
   <si>
     <t xml:space="preserve">2.60932350158691</t>
@@ -1562,10 +1562,10 @@
     <t xml:space="preserve">2.58868479728699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58131313323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53561353683472</t>
+    <t xml:space="preserve">2.58131289482117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53561329841614</t>
   </si>
   <si>
     <t xml:space="preserve">2.48843932151794</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">2.47222352027893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50170707702637</t>
+    <t xml:space="preserve">2.50170683860779</t>
   </si>
   <si>
     <t xml:space="preserve">2.56362271308899</t>
@@ -1586,16 +1586,16 @@
     <t xml:space="preserve">2.67418742179871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65502285957336</t>
+    <t xml:space="preserve">2.65502309799194</t>
   </si>
   <si>
     <t xml:space="preserve">2.68450689315796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66239404678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62406516075134</t>
+    <t xml:space="preserve">2.66239380836487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62406539916992</t>
   </si>
   <si>
     <t xml:space="preserve">2.62996196746826</t>
@@ -1607,46 +1607,46 @@
     <t xml:space="preserve">2.62111663818359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42210030555725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4191517829895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36608147621155</t>
+    <t xml:space="preserve">2.42210054397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41915225982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36608123779297</t>
   </si>
   <si>
     <t xml:space="preserve">2.38966822624207</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41325521469116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33659672737122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24667191505432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23045516014099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22898149490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16706490516663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18033242225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15674543380737</t>
+    <t xml:space="preserve">2.41325545310974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33659696578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24667167663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23045539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22898125648499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16706466674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18033266067505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15674567222595</t>
   </si>
   <si>
     <t xml:space="preserve">2.20244526863098</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19360017776489</t>
+    <t xml:space="preserve">2.19359993934631</t>
   </si>
   <si>
     <t xml:space="preserve">2.13905549049377</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">2.08745789527893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04175853729248</t>
+    <t xml:space="preserve">2.0417582988739</t>
   </si>
   <si>
     <t xml:space="preserve">2.00932645797729</t>
@@ -1670,16 +1670,16 @@
     <t xml:space="preserve">2.105149269104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05797433853149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05502605438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09335589408875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13610696792603</t>
+    <t xml:space="preserve">2.05797410011292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0550262928009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09335565567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1361072063446</t>
   </si>
   <si>
     <t xml:space="preserve">2.11694240570068</t>
@@ -1691,10 +1691,10 @@
     <t xml:space="preserve">2.10220074653625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10072636604309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09040641784668</t>
+    <t xml:space="preserve">2.10072684288025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09040665626526</t>
   </si>
   <si>
     <t xml:space="preserve">2.04912924766541</t>
@@ -1709,13 +1709,13 @@
     <t xml:space="preserve">2.04765510559082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02701663970947</t>
+    <t xml:space="preserve">2.02701640129089</t>
   </si>
   <si>
     <t xml:space="preserve">2.01964569091797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97394609451294</t>
+    <t xml:space="preserve">1.97394573688507</t>
   </si>
   <si>
     <t xml:space="preserve">1.97984278202057</t>
@@ -1724,13 +1724,13 @@
     <t xml:space="preserve">1.96215164661407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98426520824432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08008694648743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06387114524841</t>
+    <t xml:space="preserve">1.98426532745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08008718490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06387138366699</t>
   </si>
   <si>
     <t xml:space="preserve">2.07861304283142</t>
@@ -1745,40 +1745,40 @@
     <t xml:space="preserve">2.05650019645691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95625472068787</t>
+    <t xml:space="preserve">1.95625495910645</t>
   </si>
   <si>
     <t xml:space="preserve">1.98279082775116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94446134567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93709051609039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96657419204712</t>
+    <t xml:space="preserve">1.9444614648819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93709027767181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96657395362854</t>
   </si>
   <si>
     <t xml:space="preserve">1.96804857254028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89286494255066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98131704330444</t>
+    <t xml:space="preserve">1.89286506175995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98131668567657</t>
   </si>
   <si>
     <t xml:space="preserve">1.91497778892517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87517476081848</t>
+    <t xml:space="preserve">1.87517464160919</t>
   </si>
   <si>
     <t xml:space="preserve">1.87370073795319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94003903865814</t>
+    <t xml:space="preserve">1.94003891944885</t>
   </si>
   <si>
     <t xml:space="preserve">1.92677128314972</t>
@@ -1790,67 +1790,67 @@
     <t xml:space="preserve">2.0034294128418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.994584441185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99163639545441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94888389110565</t>
+    <t xml:space="preserve">1.99458432197571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99163615703583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94888401031494</t>
   </si>
   <si>
     <t xml:space="preserve">1.8884425163269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87222611904144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91940021514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89433896541595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86485540866852</t>
+    <t xml:space="preserve">1.87222635746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91940057277679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89433908462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86485552787781</t>
   </si>
   <si>
     <t xml:space="preserve">1.85306203365326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83831918239594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88549411296844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8515876531601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82505142688751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78230035305023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71596121788025</t>
+    <t xml:space="preserve">1.83831930160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88549423217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85158777236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82505166530609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78230023384094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71596109867096</t>
   </si>
   <si>
     <t xml:space="preserve">1.69532263278961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71006441116333</t>
+    <t xml:space="preserve">1.71006453037262</t>
   </si>
   <si>
     <t xml:space="preserve">1.73217809200287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78377449512482</t>
+    <t xml:space="preserve">1.78377437591553</t>
   </si>
   <si>
     <t xml:space="preserve">1.76313602924347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76166176795959</t>
+    <t xml:space="preserve">1.76166164875031</t>
   </si>
   <si>
     <t xml:space="preserve">1.78672301769257</t>
@@ -1859,19 +1859,19 @@
     <t xml:space="preserve">1.80588722229004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83389687538147</t>
+    <t xml:space="preserve">1.83389675617218</t>
   </si>
   <si>
     <t xml:space="preserve">1.87664890289307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86927807331085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84569013118744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8397935628891</t>
+    <t xml:space="preserve">1.86927795410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84569025039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83979368209839</t>
   </si>
   <si>
     <t xml:space="preserve">1.83242249488831</t>
@@ -1880,46 +1880,46 @@
     <t xml:space="preserve">1.84274184703827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83684527873993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89728736877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88991641998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88254547119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91055524349213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87075197696686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80293893814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80441284179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79114544391632</t>
+    <t xml:space="preserve">1.83684504032135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89728760719299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8899165391922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88254582881927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91055500507355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87075209617615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80293881893158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80441308021545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79114532470703</t>
   </si>
   <si>
     <t xml:space="preserve">1.75576496124268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81325829029083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81178402900696</t>
+    <t xml:space="preserve">1.81325852870941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81178390979767</t>
   </si>
   <si>
     <t xml:space="preserve">1.83537101745605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79556787014008</t>
+    <t xml:space="preserve">1.79556798934937</t>
   </si>
   <si>
     <t xml:space="preserve">1.77492940425873</t>
@@ -1931,10 +1931,10 @@
     <t xml:space="preserve">1.79851627349854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79704225063324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80736136436462</t>
+    <t xml:space="preserve">1.79704213142395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80736148357391</t>
   </si>
   <si>
     <t xml:space="preserve">1.78082621097565</t>
@@ -1943,58 +1943,58 @@
     <t xml:space="preserve">1.75429081916809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7130126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70711600780487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.745445728302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76460981369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77198100090027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7778776884079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78819704055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74839413166046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6658388376236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67910647392273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61129403114319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57886099815369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53610992431641</t>
+    <t xml:space="preserve">1.71301293373108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70711624622345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74544560909271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76461005210876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77198112010956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77787780761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78819715976715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74839389324188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66583895683289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67910659313202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61129415035248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57886123657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5361100435257</t>
   </si>
   <si>
     <t xml:space="preserve">1.55822265148163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54200661182404</t>
+    <t xml:space="preserve">1.54200649261475</t>
   </si>
   <si>
     <t xml:space="preserve">1.53445518016815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53596556186676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56466090679169</t>
+    <t xml:space="preserve">1.53596544265747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56466102600098</t>
   </si>
   <si>
     <t xml:space="preserve">1.54351687431335</t>
@@ -2012,7 +2012,7 @@
     <t xml:space="preserve">1.60543847084045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58429443836212</t>
+    <t xml:space="preserve">1.58429455757141</t>
   </si>
   <si>
     <t xml:space="preserve">1.56768143177032</t>
@@ -2021,10 +2021,10 @@
     <t xml:space="preserve">1.56919157505035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58882546424866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51029002666473</t>
+    <t xml:space="preserve">1.58882534503937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51028990745544</t>
   </si>
   <si>
     <t xml:space="preserve">1.51935243606567</t>
@@ -2033,10 +2033,10 @@
     <t xml:space="preserve">1.52690386772156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4717777967453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47026741504669</t>
+    <t xml:space="preserve">1.47177791595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47026753425598</t>
   </si>
   <si>
     <t xml:space="preserve">1.471022605896</t>
@@ -2045,10 +2045,10 @@
     <t xml:space="preserve">1.45138907432556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46875727176666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49367678165436</t>
+    <t xml:space="preserve">1.46875715255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49367690086365</t>
   </si>
   <si>
     <t xml:space="preserve">1.48386001586914</t>
@@ -2063,10 +2063,10 @@
     <t xml:space="preserve">1.46800208091736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48990118503571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48234987258911</t>
+    <t xml:space="preserve">1.489901304245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48234975337982</t>
   </si>
   <si>
     <t xml:space="preserve">1.48083961009979</t>
@@ -2075,19 +2075,19 @@
     <t xml:space="preserve">1.53294491767883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57523274421692</t>
+    <t xml:space="preserve">1.57523286342621</t>
   </si>
   <si>
     <t xml:space="preserve">1.56315052509308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52539360523224</t>
+    <t xml:space="preserve">1.52539348602295</t>
   </si>
   <si>
     <t xml:space="preserve">1.50424885749817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47328794002533</t>
+    <t xml:space="preserve">1.47328805923462</t>
   </si>
   <si>
     <t xml:space="preserve">1.4725329875946</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">1.46649181842804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44987869262695</t>
+    <t xml:space="preserve">1.44987881183624</t>
   </si>
   <si>
     <t xml:space="preserve">1.44610297679901</t>
@@ -2114,31 +2114,31 @@
     <t xml:space="preserve">1.42269361019135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42042827606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42722451686859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41665244102478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40683567523956</t>
+    <t xml:space="preserve">1.4204283952713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4272243976593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41665256023407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40683579444885</t>
   </si>
   <si>
     <t xml:space="preserve">1.400794506073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39097774028778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3864461183548</t>
+    <t xml:space="preserve">1.39097762107849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38644623756409</t>
   </si>
   <si>
     <t xml:space="preserve">1.28374695777893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25354051589966</t>
+    <t xml:space="preserve">1.25354063510895</t>
   </si>
   <si>
     <t xml:space="preserve">1.25127518177032</t>
@@ -2147,19 +2147,19 @@
     <t xml:space="preserve">1.20068073272705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23617243766785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25278532505035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22182464599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2308863401413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27695071697235</t>
+    <t xml:space="preserve">1.23617231845856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25278544425964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2218245267868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23088645935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27695083618164</t>
   </si>
   <si>
     <t xml:space="preserve">1.26637876033783</t>
@@ -2168,7 +2168,7 @@
     <t xml:space="preserve">1.27619564533234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31395268440247</t>
+    <t xml:space="preserve">1.31395256519318</t>
   </si>
   <si>
     <t xml:space="preserve">1.27090954780579</t>
@@ -2180,22 +2180,22 @@
     <t xml:space="preserve">1.28752267360687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35775077342987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38342571258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37436389923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35246479511261</t>
+    <t xml:space="preserve">1.35775065422058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38342559337616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37436378002167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35246467590332</t>
   </si>
   <si>
     <t xml:space="preserve">1.40985631942749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39852917194366</t>
+    <t xml:space="preserve">1.39852929115295</t>
   </si>
   <si>
     <t xml:space="preserve">1.36681246757507</t>
@@ -2210,10 +2210,10 @@
     <t xml:space="preserve">1.36454701423645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33736181259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30262529850006</t>
+    <t xml:space="preserve">1.33736193180084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30262541770935</t>
   </si>
   <si>
     <t xml:space="preserve">1.2897881269455</t>
@@ -2222,10 +2222,10 @@
     <t xml:space="preserve">1.26109278202057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26864409446716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25505089759827</t>
+    <t xml:space="preserve">1.26864421367645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25505077838898</t>
   </si>
   <si>
     <t xml:space="preserve">1.27468526363373</t>
@@ -2246,13 +2246,13 @@
     <t xml:space="preserve">1.28148150444031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30413579940796</t>
+    <t xml:space="preserve">1.30413591861725</t>
   </si>
   <si>
     <t xml:space="preserve">1.33660686016083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3607714176178</t>
+    <t xml:space="preserve">1.36077117919922</t>
   </si>
   <si>
     <t xml:space="preserve">1.38871240615845</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">1.36152648925781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36228168010712</t>
+    <t xml:space="preserve">1.36228179931641</t>
   </si>
   <si>
     <t xml:space="preserve">1.34113776683807</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">1.43326556682587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40532541275024</t>
+    <t xml:space="preserve">1.40532529354095</t>
   </si>
   <si>
     <t xml:space="preserve">1.43477594852448</t>
@@ -2297,46 +2297,46 @@
     <t xml:space="preserve">1.62960290908813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5827841758728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57825350761414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58127379417419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54653739929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53747582435608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52237284183502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55257868766785</t>
+    <t xml:space="preserve">1.58278429508209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57825338840485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58127403259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54653751850128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53747606277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52237272262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55257856845856</t>
   </si>
   <si>
     <t xml:space="preserve">1.60241782665253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63111329078674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6009076833725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62054133415222</t>
+    <t xml:space="preserve">1.63111317157745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60090780258179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62054145336151</t>
   </si>
   <si>
     <t xml:space="preserve">1.54955792427063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57221245765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61147940158844</t>
+    <t xml:space="preserve">1.57221233844757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61147952079773</t>
   </si>
   <si>
     <t xml:space="preserve">1.64168608188629</t>
@@ -2345,13 +2345,13 @@
     <t xml:space="preserve">1.61298990249634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61752045154572</t>
+    <t xml:space="preserve">1.61752080917358</t>
   </si>
   <si>
     <t xml:space="preserve">1.59184598922729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58731520175934</t>
+    <t xml:space="preserve">1.58731508255005</t>
   </si>
   <si>
     <t xml:space="preserve">1.6190310716629</t>
@@ -2363,10 +2363,10 @@
     <t xml:space="preserve">1.56013011932373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55861973762512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59788715839386</t>
+    <t xml:space="preserve">1.55861961841583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59788703918457</t>
   </si>
   <si>
     <t xml:space="preserve">1.60392820835114</t>
@@ -2384,16 +2384,16 @@
     <t xml:space="preserve">1.59033560752869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52992451190948</t>
+    <t xml:space="preserve">1.5299243927002</t>
   </si>
   <si>
     <t xml:space="preserve">1.51331126689911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50953471660614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52388322353363</t>
+    <t xml:space="preserve">1.50953483581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52388334274292</t>
   </si>
   <si>
     <t xml:space="preserve">1.54049634933472</t>
@@ -2402,7 +2402,7 @@
     <t xml:space="preserve">1.63866460323334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75948798656464</t>
+    <t xml:space="preserve">1.75948810577393</t>
   </si>
   <si>
     <t xml:space="preserve">1.806307554245</t>
@@ -2411,22 +2411,22 @@
     <t xml:space="preserve">1.78365314006805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83953356742859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02983093261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06909799575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94827473163605</t>
+    <t xml:space="preserve">1.83953368663788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02983069419861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06909823417664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94827485084534</t>
   </si>
   <si>
     <t xml:space="preserve">1.89088308811188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7791223526001</t>
+    <t xml:space="preserve">1.77912259101868</t>
   </si>
   <si>
     <t xml:space="preserve">1.77308118343353</t>
@@ -2435,28 +2435,28 @@
     <t xml:space="preserve">1.81687939167023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70813846588135</t>
+    <t xml:space="preserve">1.70813834667206</t>
   </si>
   <si>
     <t xml:space="preserve">1.4800843000412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37511885166168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32452464103699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2407032251358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19917047023773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18406760692596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959789335727692</t>
+    <t xml:space="preserve">1.37511897087097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3245245218277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24070310592651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19917035102844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18406772613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959789276123047</t>
   </si>
   <si>
     <t xml:space="preserve">0.995280861854553</t>
@@ -2471,28 +2471,28 @@
     <t xml:space="preserve">0.962809801101685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01869094371796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04361057281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990750014781952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07155096530914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07910227775574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0677752494812</t>
+    <t xml:space="preserve">1.01869106292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04361069202423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990750074386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07155084609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07910239696503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06777513027191</t>
   </si>
   <si>
     <t xml:space="preserve">1.01944613456726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999811768531799</t>
+    <t xml:space="preserve">0.999811828136444</t>
   </si>
   <si>
     <t xml:space="preserve">1.0413453578949</t>
@@ -2501,13 +2501,13 @@
     <t xml:space="preserve">1.02699756622314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10628736019135</t>
+    <t xml:space="preserve">1.10628747940063</t>
   </si>
   <si>
     <t xml:space="preserve">1.05720317363739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11459386348724</t>
+    <t xml:space="preserve">1.11459398269653</t>
   </si>
   <si>
     <t xml:space="preserve">1.13875913619995</t>
@@ -2516,7 +2516,7 @@
     <t xml:space="preserve">1.20219099521637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16745460033417</t>
+    <t xml:space="preserve">1.16745448112488</t>
   </si>
   <si>
     <t xml:space="preserve">1.16594421863556</t>
@@ -2525,25 +2525,25 @@
     <t xml:space="preserve">1.08740890026093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0670200586319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0942051410675</t>
+    <t xml:space="preserve">1.06701993942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09420502185822</t>
   </si>
   <si>
     <t xml:space="preserve">1.06324434280396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09496021270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07834708690643</t>
+    <t xml:space="preserve">1.09496033191681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07834720611572</t>
   </si>
   <si>
     <t xml:space="preserve">1.08212280273438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07457149028778</t>
+    <t xml:space="preserve">1.07457137107849</t>
   </si>
   <si>
     <t xml:space="preserve">1.08665370941162</t>
@@ -2552,40 +2552,40 @@
     <t xml:space="preserve">1.09269499778748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03756952285767</t>
+    <t xml:space="preserve">1.03756964206696</t>
   </si>
   <si>
     <t xml:space="preserve">1.07306122779846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04965174198151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03530430793762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04436588287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04285550117493</t>
+    <t xml:space="preserve">1.0496518611908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03530418872833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04436576366425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04285562038422</t>
   </si>
   <si>
     <t xml:space="preserve">1.01189470291138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.985464036464691</t>
+    <t xml:space="preserve">0.985464096069336</t>
   </si>
   <si>
     <t xml:space="preserve">0.970361292362213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989239811897278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.943176090717316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926563143730164</t>
+    <t xml:space="preserve">0.989239752292633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94317626953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.926563024520874</t>
   </si>
   <si>
     <t xml:space="preserve">0.921277046203613</t>
@@ -2603,13 +2603,13 @@
     <t xml:space="preserve">1.058713555336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09722566604614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1025116443634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13422775268555</t>
+    <t xml:space="preserve">1.09722554683685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10251152515411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13422763347626</t>
   </si>
   <si>
     <t xml:space="preserve">1.18180227279663</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">1.18708825111389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16216862201691</t>
+    <t xml:space="preserve">1.16216850280762</t>
   </si>
   <si>
     <t xml:space="preserve">1.19312930107117</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">1.39399838447571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39928424358368</t>
+    <t xml:space="preserve">1.39928436279297</t>
   </si>
   <si>
     <t xml:space="preserve">1.4015496969223</t>
@@ -2672,7 +2672,7 @@
     <t xml:space="preserve">1.40306007862091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41589736938477</t>
+    <t xml:space="preserve">1.41589748859406</t>
   </si>
   <si>
     <t xml:space="preserve">1.49292182922363</t>
@@ -2684,13 +2684,13 @@
     <t xml:space="preserve">1.48763573169708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47630870342255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46498143672943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39626359939575</t>
+    <t xml:space="preserve">1.47630858421326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46498155593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39626371860504</t>
   </si>
   <si>
     <t xml:space="preserve">1.37662935256958</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">1.43175530433655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.445347905159</t>
+    <t xml:space="preserve">1.44534778594971</t>
   </si>
   <si>
     <t xml:space="preserve">1.47479832172394</t>
@@ -2714,10 +2714,10 @@
     <t xml:space="preserve">1.48461520671844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55106854438782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52086269855499</t>
+    <t xml:space="preserve">1.55106842517853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5208625793457</t>
   </si>
   <si>
     <t xml:space="preserve">1.37889468669891</t>
@@ -2726,37 +2726,37 @@
     <t xml:space="preserve">1.3781396150589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34415805339813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37209856510162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39475345611572</t>
+    <t xml:space="preserve">1.34415817260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37209844589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39475321769714</t>
   </si>
   <si>
     <t xml:space="preserve">1.37964987754822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38795733451843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39248812198639</t>
+    <t xml:space="preserve">1.38795721530914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3924880027771</t>
   </si>
   <si>
     <t xml:space="preserve">1.32150399684906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31848347187042</t>
+    <t xml:space="preserve">1.31848359107971</t>
   </si>
   <si>
     <t xml:space="preserve">1.34340298175812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30036020278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32376945018768</t>
+    <t xml:space="preserve">1.30035996437073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32376933097839</t>
   </si>
   <si>
     <t xml:space="preserve">1.33434152603149</t>
@@ -2765,25 +2765,25 @@
     <t xml:space="preserve">1.39777398109436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36983299255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38191533088684</t>
+    <t xml:space="preserve">1.369833111763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38191521167755</t>
   </si>
   <si>
     <t xml:space="preserve">1.34038257598877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35473012924194</t>
+    <t xml:space="preserve">1.35473024845123</t>
   </si>
   <si>
     <t xml:space="preserve">1.31772828102112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33207583427429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33585178852081</t>
+    <t xml:space="preserve">1.33207595348358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33585166931152</t>
   </si>
   <si>
     <t xml:space="preserve">1.27393019199371</t>
@@ -2792,19 +2792,19 @@
     <t xml:space="preserve">1.26486837863922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22484529018402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24145817756653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11761438846588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10779774188995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13800406455994</t>
+    <t xml:space="preserve">1.22484517097473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24145829677582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11761450767517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10779762268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13800394535065</t>
   </si>
   <si>
     <t xml:space="preserve">1.22711062431335</t>
@@ -2813,16 +2813,16 @@
     <t xml:space="preserve">1.24221348762512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23843765258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22862076759338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44232726097107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43251049518585</t>
+    <t xml:space="preserve">1.23843777179718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22862088680267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44232738018036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43251037597656</t>
   </si>
   <si>
     <t xml:space="preserve">1.50273859500885</t>
@@ -2840,16 +2840,16 @@
     <t xml:space="preserve">1.77459168434143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75797772407532</t>
+    <t xml:space="preserve">1.75797760486603</t>
   </si>
   <si>
     <t xml:space="preserve">1.69303548336029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72173118591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68548429012299</t>
+    <t xml:space="preserve">1.72173082828522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6854841709137</t>
   </si>
   <si>
     <t xml:space="preserve">1.70209717750549</t>
@@ -2864,10 +2864,10 @@
     <t xml:space="preserve">1.72777211666107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69907653331757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66887104511261</t>
+    <t xml:space="preserve">1.69907665252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66887128353119</t>
   </si>
   <si>
     <t xml:space="preserve">1.66282987594604</t>
@@ -2879,22 +2879,22 @@
     <t xml:space="preserve">1.66131961345673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67642247676849</t>
+    <t xml:space="preserve">1.67642259597778</t>
   </si>
   <si>
     <t xml:space="preserve">1.64470648765564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61601042747498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63564419746399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6582989692688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66585052013397</t>
+    <t xml:space="preserve">1.61601030826569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63564395904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65829908847809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66585063934326</t>
   </si>
   <si>
     <t xml:space="preserve">1.66434013843536</t>
@@ -2903,10 +2903,10 @@
     <t xml:space="preserve">1.74438524246216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77761220932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75646758079529</t>
+    <t xml:space="preserve">1.77761209011078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75646734237671</t>
   </si>
   <si>
     <t xml:space="preserve">1.7202205657959</t>
@@ -2915,94 +2915,94 @@
     <t xml:space="preserve">1.73683369159698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69454598426819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65225803852081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67491221427917</t>
+    <t xml:space="preserve">1.69454574584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65225791931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67491209506989</t>
   </si>
   <si>
     <t xml:space="preserve">1.65376830101013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63715445995331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57070183753967</t>
+    <t xml:space="preserve">1.63715434074402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57070195674896</t>
   </si>
   <si>
     <t xml:space="preserve">1.59486651420593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62205159664154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7474057674408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88635218143463</t>
+    <t xml:space="preserve">1.62205147743225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74740552902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8863525390625</t>
   </si>
   <si>
     <t xml:space="preserve">1.85765707492828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88031125068665</t>
+    <t xml:space="preserve">1.88031136989594</t>
   </si>
   <si>
     <t xml:space="preserve">1.86822903156281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85463654994965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88937306404114</t>
+    <t xml:space="preserve">1.85463643074036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88937294483185</t>
   </si>
   <si>
     <t xml:space="preserve">1.85010552406311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80932819843292</t>
+    <t xml:space="preserve">1.80932807922363</t>
   </si>
   <si>
     <t xml:space="preserve">1.83047211170197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82141017913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81838977336884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82594120502472</t>
+    <t xml:space="preserve">1.82141005992889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81838965415955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82594096660614</t>
   </si>
   <si>
     <t xml:space="preserve">1.80781745910645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80177640914917</t>
+    <t xml:space="preserve">1.80177652835846</t>
   </si>
   <si>
     <t xml:space="preserve">1.84557461738586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83500277996063</t>
+    <t xml:space="preserve">1.83500266075134</t>
   </si>
   <si>
     <t xml:space="preserve">1.82745134830475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87124967575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86369800567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.927130818367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9799907207489</t>
+    <t xml:space="preserve">1.87124943733215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86369788646698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92713069915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97999060153961</t>
   </si>
   <si>
     <t xml:space="preserve">2.05399513244629</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">2.18085956573486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15216398239136</t>
+    <t xml:space="preserve">2.15216422080994</t>
   </si>
   <si>
     <t xml:space="preserve">2.12950921058655</t>
@@ -3026,16 +3026,16 @@
     <t xml:space="preserve">2.15518498420715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1355504989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13857078552246</t>
+    <t xml:space="preserve">2.13555026054382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13857102394104</t>
   </si>
   <si>
     <t xml:space="preserve">2.22465753555298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15669536590576</t>
+    <t xml:space="preserve">2.15669512748718</t>
   </si>
   <si>
     <t xml:space="preserve">2.18992114067078</t>
@@ -3050,16 +3050,16 @@
     <t xml:space="preserve">2.17028784751892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2352294921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24731183052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2699670791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30168318748474</t>
+    <t xml:space="preserve">2.23522973060608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24731206893921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26996684074402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30168294906616</t>
   </si>
   <si>
     <t xml:space="preserve">2.23673987388611</t>
@@ -3086,10 +3086,10 @@
     <t xml:space="preserve">2.64300799369812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61733341217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60223031044006</t>
+    <t xml:space="preserve">2.61733317375183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60223054885864</t>
   </si>
   <si>
     <t xml:space="preserve">2.70190978050232</t>
@@ -3101,429 +3101,429 @@
     <t xml:space="preserve">2.78648638725281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88616490364075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8650209903717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86200046539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94204592704773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94506669044495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93147397041321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97980308532715</t>
+    <t xml:space="preserve">2.88616514205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86502075195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86200022697449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94204616546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94506645202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93147420883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97980284690857</t>
   </si>
   <si>
     <t xml:space="preserve">2.96621036529541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95714902877808</t>
+    <t xml:space="preserve">2.9571487903595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97829294204712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08411264419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07337760925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05804085731506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15312528610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09178066253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11478519439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19299960136414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21600413322449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18839836120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17459583282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12858748435974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06264138221741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98749470710754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96602392196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95988941192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9445526599884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91388034820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.901611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83106541633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80192589759827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80039238929749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73598051071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79425811767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79272413253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83719968795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76665258407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80499291419983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79119038581848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85713672637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78198885917664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75131678581238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72371172904968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84333395957947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79579138755798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77892160415649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72524523735046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6731014251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58108472824097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66543340682983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73291325569153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75745129585266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.783522605896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92614936828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88934254646301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94301891326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90774583816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85100197792053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86020398139954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85867023468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83873343467712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84486770629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91848111152649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95222115516663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90467882156372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96755766868591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92768263816833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92461562156677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83566617965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86173748970032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84640121459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87860703468323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89854407310486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99976348876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00743126869202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98289346694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98596096038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95375514030457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99056148529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93688440322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95682215690613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90007781982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84180068969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87400650978088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81726264953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76511931419373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8295316696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76972007751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70224118232727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70530819892883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79732489585876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80652689933777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81419491767883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78045535087585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82646441459656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84793519973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82339715957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93075013160706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90314507484436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88320803642273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86633825302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87554025650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9062123298645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95528864860535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97522568702698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98902797698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95068788528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99669623374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02890205383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03656983375549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92001485824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9353506565094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88014078140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91234660148621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98135995864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03350281715393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94915413856506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85560321807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80806040763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76205205917358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77432084083557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69917392730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70684170722961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66083264350891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76051831245422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71144270896912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58875274658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73137974739075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62249255180359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65009737014771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67770266532898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67463564872742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74671578407288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72064423561096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71911072731018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69610667228699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66850090026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75438404083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8249306678772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85406947135925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89701056480408</t>
   </si>
   <si>
     <t xml:space="preserve">2.97829270362854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08411288261414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07337760925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05804061889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15312552452087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09178066253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11478519439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19299960136414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21600437164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18839836120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17459583282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12858748435974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06264162063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98749446868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96602392196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95988941192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9445526599884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91388034820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.901611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83106541633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80192589759827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80039215087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73598051071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7942578792572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79272437095642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83719968795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76665282249451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80499315261841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79119038581848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85713672637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78198885917664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75131678581238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7237114906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84333443641663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79579138755798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77892160415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72524499893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67310166358948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58108496665955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66543364524841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73291349411011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75745129585266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.783522605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92614912986755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88934254646301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94301891326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90774583816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85100197792053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86020374298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85867023468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83873319625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84486770629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91848111152649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95222139358521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90467882156372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96755766868591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92768287658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92461538314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8356659412384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86173748970032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84640145301819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87860727310181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89854431152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99976348876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00743174552917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98289370536804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98596096038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95375514030457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99056172370911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93688440322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95682215690613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90007758140564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84180045127869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8740062713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81726264953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76511907577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8295316696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76972007751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70224118232727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70530819892883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79732489585876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80652689933777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81419467926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78045535087585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82646441459656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84793472290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82339692115784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93075013160706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90314531326294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88320803642273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86633825302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87554001808167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9062123298645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95528864860535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9752254486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98902821540833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95068788528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99669623374939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02890205383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03656983375549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92001485824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93535089492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88014078140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91234660148621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98135995864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03350281715393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94915413856506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85560321807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80806040763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.762051820755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77432084083557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69917368888855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70684194564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66083288192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76051831245422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71144247055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58875298500061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73137974739075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62249255180359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65009760856628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6777024269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67463541030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74671578407288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72064447402954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71911072731018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69610691070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66850090026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75438380241394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82493090629578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85406947135925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89701080322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97829294204712</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.86327123641968</t>
   </si>
   <si>
@@ -3536,10 +3536,10 @@
     <t xml:space="preserve">3.02736854553223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89087629318237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74058127403259</t>
+    <t xml:space="preserve">2.89087605476379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74058151245117</t>
   </si>
   <si>
     <t xml:space="preserve">2.7850558757782</t>
@@ -3551,7 +3551,7 @@
     <t xml:space="preserve">2.82799816131592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97062468528748</t>
+    <t xml:space="preserve">2.9706244468689</t>
   </si>
   <si>
     <t xml:space="preserve">2.92445588111877</t>
@@ -3569,13 +3569,13 @@
     <t xml:space="preserve">3.15472817420959</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08871698379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19771242141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21459913253784</t>
+    <t xml:space="preserve">3.08871674537659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19771218299866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21459889411926</t>
   </si>
   <si>
     <t xml:space="preserve">3.18850111961365</t>
@@ -3587,7 +3587,7 @@
     <t xml:space="preserve">3.16547441482544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09485745429993</t>
+    <t xml:space="preserve">3.09485721588135</t>
   </si>
   <si>
     <t xml:space="preserve">2.94748306274414</t>
@@ -3599,16 +3599,16 @@
     <t xml:space="preserve">2.84769868850708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72028112411499</t>
+    <t xml:space="preserve">2.72028136253357</t>
   </si>
   <si>
     <t xml:space="preserve">2.55602049827576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58979368209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54066896438599</t>
+    <t xml:space="preserve">2.58979392051697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54066920280457</t>
   </si>
   <si>
     <t xml:space="preserve">2.25359654426575</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">2.24592089653015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33342409133911</t>
+    <t xml:space="preserve">2.33342432975769</t>
   </si>
   <si>
     <t xml:space="preserve">2.53452849388123</t>
@@ -3632,16 +3632,16 @@
     <t xml:space="preserve">2.52992296218872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56983685493469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75098419189453</t>
+    <t xml:space="preserve">2.56983661651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75098443031311</t>
   </si>
   <si>
     <t xml:space="preserve">2.72488689422607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76326537132263</t>
+    <t xml:space="preserve">2.76326560974121</t>
   </si>
   <si>
     <t xml:space="preserve">2.78015208244324</t>
@@ -3650,13 +3650,13 @@
     <t xml:space="preserve">2.82927703857422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79550337791443</t>
+    <t xml:space="preserve">2.79550361633301</t>
   </si>
   <si>
     <t xml:space="preserve">2.79243350028992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73870325088501</t>
+    <t xml:space="preserve">2.73870301246643</t>
   </si>
   <si>
     <t xml:space="preserve">2.79703879356384</t>
@@ -3671,34 +3671,34 @@
     <t xml:space="preserve">2.85383915901184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89221787452698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91831541061401</t>
+    <t xml:space="preserve">2.8922176361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91831517219543</t>
   </si>
   <si>
     <t xml:space="preserve">2.89835834503174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80931997299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79857397079468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93366670608521</t>
+    <t xml:space="preserve">2.80932021141052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7985737323761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93366694450378</t>
   </si>
   <si>
     <t xml:space="preserve">2.94594812393188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87226128578186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93980741500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88607740402222</t>
+    <t xml:space="preserve">2.8722608089447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93980717658997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88607716560364</t>
   </si>
   <si>
     <t xml:space="preserve">2.96590495109558</t>
@@ -3707,10 +3707,10 @@
     <t xml:space="preserve">2.95208859443665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90603446960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92752599716187</t>
+    <t xml:space="preserve">2.90603423118591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92752623558044</t>
   </si>
   <si>
     <t xml:space="preserve">2.91678023338318</t>
@@ -3725,16 +3725,16 @@
     <t xml:space="preserve">2.7908980846405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78936314582825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75712490081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68343782424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78168702125549</t>
+    <t xml:space="preserve">2.78936290740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75712466239929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68343758583069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78168749809265</t>
   </si>
   <si>
     <t xml:space="preserve">2.80624938011169</t>
@@ -3773,7 +3773,7 @@
     <t xml:space="preserve">3.1176609992981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07544302940369</t>
+    <t xml:space="preserve">3.07544279098511</t>
   </si>
   <si>
     <t xml:space="preserve">3.04946231842041</t>
@@ -3782,10 +3782,10 @@
     <t xml:space="preserve">3.01211524009705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99587750434875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03809595108032</t>
+    <t xml:space="preserve">2.99587774276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0380961894989</t>
   </si>
   <si>
     <t xml:space="preserve">3.03322458267212</t>
@@ -3794,13 +3794,13 @@
     <t xml:space="preserve">3.0088677406311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96664929389954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7620530128479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6337742805481</t>
+    <t xml:space="preserve">2.96664953231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76205277442932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63377404212952</t>
   </si>
   <si>
     <t xml:space="preserve">2.62565517425537</t>
@@ -3821,16 +3821,16 @@
     <t xml:space="preserve">2.78478598594666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77666711807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6954779624939</t>
+    <t xml:space="preserve">2.77666735649109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69547772407532</t>
   </si>
   <si>
     <t xml:space="preserve">2.73282480239868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69385433197021</t>
+    <t xml:space="preserve">2.69385409355164</t>
   </si>
   <si>
     <t xml:space="preserve">2.70034909248352</t>
@@ -3860,7 +3860,7 @@
     <t xml:space="preserve">2.76042938232422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71821069717407</t>
+    <t xml:space="preserve">2.71821093559265</t>
   </si>
   <si>
     <t xml:space="preserve">2.70359683036804</t>
@@ -3878,19 +3878,19 @@
     <t xml:space="preserve">2.57207036018372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69060659408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61428880691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57856583595276</t>
+    <t xml:space="preserve">2.69060635566711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61428904533386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57856559753418</t>
   </si>
   <si>
     <t xml:space="preserve">2.54608988761902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58343696594238</t>
+    <t xml:space="preserve">2.58343720436096</t>
   </si>
   <si>
     <t xml:space="preserve">2.51686191558838</t>
@@ -3902,16 +3902,16 @@
     <t xml:space="preserve">2.62727904319763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65975451469421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72957730293274</t>
+    <t xml:space="preserve">2.65975475311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72957754135132</t>
   </si>
   <si>
     <t xml:space="preserve">2.6694974899292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78153848648071</t>
+    <t xml:space="preserve">2.78153872489929</t>
   </si>
   <si>
     <t xml:space="preserve">2.73607230186462</t>
@@ -3932,7 +3932,7 @@
     <t xml:space="preserve">2.66624999046326</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60941743850708</t>
+    <t xml:space="preserve">2.60941767692566</t>
   </si>
   <si>
     <t xml:space="preserve">2.56395149230957</t>
@@ -3944,7 +3944,7 @@
     <t xml:space="preserve">2.59155583381653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59967494010925</t>
+    <t xml:space="preserve">2.59967470169067</t>
   </si>
   <si>
     <t xml:space="preserve">2.56070399284363</t>
@@ -3953,16 +3953,16 @@
     <t xml:space="preserve">2.59642720222473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59805083274841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58830833435059</t>
+    <t xml:space="preserve">2.59805107116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58830857276917</t>
   </si>
   <si>
     <t xml:space="preserve">2.7263298034668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82050919532776</t>
+    <t xml:space="preserve">2.82050895690918</t>
   </si>
   <si>
     <t xml:space="preserve">2.81726145744324</t>
@@ -3998,13 +3998,13 @@
     <t xml:space="preserve">2.64514064788818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75393414497375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76692414283752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8546085357666</t>
+    <t xml:space="preserve">2.75393390655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7669243812561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85460877418518</t>
   </si>
   <si>
     <t xml:space="preserve">2.7929048538208</t>
@@ -4031,16 +4031,16 @@
     <t xml:space="preserve">2.86435127258301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87734150886536</t>
+    <t xml:space="preserve">2.87734127044678</t>
   </si>
   <si>
     <t xml:space="preserve">2.9163122177124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95853066444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92443132400513</t>
+    <t xml:space="preserve">2.95853090286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92443108558655</t>
   </si>
   <si>
     <t xml:space="preserve">2.93904519081116</t>
@@ -4058,7 +4058,7 @@
     <t xml:space="preserve">3.02997708320618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04459118843079</t>
+    <t xml:space="preserve">3.04459095001221</t>
   </si>
   <si>
     <t xml:space="preserve">3.10467100143433</t>
@@ -4073,7 +4073,7 @@
     <t xml:space="preserve">2.89520311355591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88708424568176</t>
+    <t xml:space="preserve">2.88708400726318</t>
   </si>
   <si>
     <t xml:space="preserve">2.91793608665466</t>
@@ -4088,7 +4088,7 @@
     <t xml:space="preserve">3.1014232635498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10629487037659</t>
+    <t xml:space="preserve">3.10629463195801</t>
   </si>
   <si>
     <t xml:space="preserve">3.11441349983215</t>
@@ -4097,13 +4097,13 @@
     <t xml:space="preserve">3.15987944602966</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12740397453308</t>
+    <t xml:space="preserve">3.1274037361145</t>
   </si>
   <si>
     <t xml:space="preserve">3.16637468338013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14201784133911</t>
+    <t xml:space="preserve">3.14201807975769</t>
   </si>
   <si>
     <t xml:space="preserve">3.1209089756012</t>
@@ -4127,7 +4127,7 @@
     <t xml:space="preserve">3.06894779205322</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04134321212769</t>
+    <t xml:space="preserve">3.04134345054626</t>
   </si>
   <si>
     <t xml:space="preserve">3.11278986930847</t>
@@ -4145,7 +4145,7 @@
     <t xml:space="preserve">3.14039421081543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12415647506714</t>
+    <t xml:space="preserve">3.12415623664856</t>
   </si>
   <si>
     <t xml:space="preserve">3.17774128913879</t>
@@ -4163,7 +4163,7 @@
     <t xml:space="preserve">3.27679181098938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27029633522034</t>
+    <t xml:space="preserve">3.27029657363892</t>
   </si>
   <si>
     <t xml:space="preserve">3.3125147819519</t>
@@ -4205,13 +4205,13 @@
     <t xml:space="preserve">3.65838074684143</t>
   </si>
   <si>
-    <t xml:space="preserve">3.733074426651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65675687789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66487574577332</t>
+    <t xml:space="preserve">3.73307466506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65675711631775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66487598419189</t>
   </si>
   <si>
     <t xml:space="preserve">3.7022225856781</t>
@@ -4229,10 +4229,10 @@
     <t xml:space="preserve">3.66325187683105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59505295753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60804295539856</t>
+    <t xml:space="preserve">3.59505319595337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60804319381714</t>
   </si>
   <si>
     <t xml:space="preserve">3.6453902721405</t>
@@ -4241,7 +4241,7 @@
     <t xml:space="preserve">3.59830069541931</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64376664161682</t>
+    <t xml:space="preserve">3.6437668800354</t>
   </si>
   <si>
     <t xml:space="preserve">3.61616230010986</t>
@@ -4253,10 +4253,10 @@
     <t xml:space="preserve">3.69572734832764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81101608276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90032386779785</t>
+    <t xml:space="preserve">3.81101584434509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90032410621643</t>
   </si>
   <si>
     <t xml:space="preserve">3.87921476364136</t>
@@ -4268,10 +4268,10 @@
     <t xml:space="preserve">3.89382863044739</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97177052497864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89220499992371</t>
+    <t xml:space="preserve">3.97177076339722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89220547676086</t>
   </si>
   <si>
     <t xml:space="preserve">3.91980957984924</t>
@@ -4286,10 +4286,10 @@
     <t xml:space="preserve">3.41643714904785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19885063171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21021676063538</t>
+    <t xml:space="preserve">3.19885039329529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21021699905396</t>
   </si>
   <si>
     <t xml:space="preserve">3.0949285030365</t>
@@ -4301,31 +4301,31 @@
     <t xml:space="preserve">3.28491067886353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21995949745178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08843302726746</t>
+    <t xml:space="preserve">3.21995973587036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08843326568604</t>
   </si>
   <si>
     <t xml:space="preserve">3.09330439567566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09979963302612</t>
+    <t xml:space="preserve">3.0997998714447</t>
   </si>
   <si>
     <t xml:space="preserve">3.19560265541077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21184039115906</t>
+    <t xml:space="preserve">3.21184062957764</t>
   </si>
   <si>
     <t xml:space="preserve">3.1517608165741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27192068099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28815841674805</t>
+    <t xml:space="preserve">3.27192091941833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28815865516663</t>
   </si>
   <si>
     <t xml:space="preserve">3.31738615036011</t>
@@ -4343,13 +4343,13 @@
     <t xml:space="preserve">3.4342987537384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47326946258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47002196311951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44241738319397</t>
+    <t xml:space="preserve">3.47326922416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47002220153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44241714477539</t>
   </si>
   <si>
     <t xml:space="preserve">3.34661459922791</t>
@@ -4364,22 +4364,22 @@
     <t xml:space="preserve">3.38720893859863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43105101585388</t>
+    <t xml:space="preserve">3.4310507774353</t>
   </si>
   <si>
     <t xml:space="preserve">3.50736880302429</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36934757232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38558530807495</t>
+    <t xml:space="preserve">3.36934733390808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38558506965637</t>
   </si>
   <si>
     <t xml:space="preserve">3.38233757019043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38396167755127</t>
+    <t xml:space="preserve">3.38396143913269</t>
   </si>
   <si>
     <t xml:space="preserve">3.33499121665955</t>
@@ -6018,6 +6018,9 @@
   </si>
   <si>
     <t xml:space="preserve">16.4400005340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3449993133545</t>
   </si>
 </sst>
 </file>
@@ -72368,6 +72371,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2540">
+      <c r="A2540" s="1" t="n">
+        <v>46020.6910069444</v>
+      </c>
+      <c r="B2540" t="n">
+        <v>590267</v>
+      </c>
+      <c r="C2540" t="n">
+        <v>16.5400009155273</v>
+      </c>
+      <c r="D2540" t="n">
+        <v>16.3449993133545</v>
+      </c>
+      <c r="E2540" t="n">
+        <v>16.4500007629395</v>
+      </c>
+      <c r="F2540" t="n">
+        <v>16.3449993133545</v>
+      </c>
+      <c r="G2540" t="s">
+        <v>2002</v>
+      </c>
+      <c r="H2540" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BPSO.MI.xlsx
+++ b/data/BPSO.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2003" uniqueCount="2003">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2004" uniqueCount="2004">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,25 +44,25 @@
     <t xml:space="preserve">BPSO.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80963754653931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74855804443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71246600151062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63611721992493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60835409164429</t>
+    <t xml:space="preserve">2.80963730812073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74855828285217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71246576309204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63611698150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60835385322571</t>
   </si>
   <si>
     <t xml:space="preserve">2.69303178787231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69858479499817</t>
+    <t xml:space="preserve">2.69858455657959</t>
   </si>
   <si>
     <t xml:space="preserve">2.61113023757935</t>
@@ -71,10 +71,10 @@
     <t xml:space="preserve">2.51257061958313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45565629005432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2668662071228</t>
+    <t xml:space="preserve">2.4556565284729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26686644554138</t>
   </si>
   <si>
     <t xml:space="preserve">2.38069558143616</t>
@@ -83,40 +83,40 @@
     <t xml:space="preserve">2.40568208694458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36542558670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51951122283936</t>
+    <t xml:space="preserve">2.36542630195618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51951146125793</t>
   </si>
   <si>
     <t xml:space="preserve">2.44455099105835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35570883750916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43899893760681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40429449081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32100486755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22105741500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23216247558594</t>
+    <t xml:space="preserve">2.35570907592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43899869918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40429401397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32100510597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22105693817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23216223716736</t>
   </si>
   <si>
     <t xml:space="preserve">2.20995211601257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04059600830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06280636787415</t>
+    <t xml:space="preserve">2.04059624671936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06280660629272</t>
   </si>
   <si>
     <t xml:space="preserve">2.14331984519958</t>
@@ -128,13 +128,13 @@
     <t xml:space="preserve">2.1821882724762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22522163391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2779712677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19329380989075</t>
+    <t xml:space="preserve">2.22522139549255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27797174453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19329333305359</t>
   </si>
   <si>
     <t xml:space="preserve">2.16553044319153</t>
@@ -143,28 +143,28 @@
     <t xml:space="preserve">2.24604392051697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18635249137878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1766357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21550488471985</t>
+    <t xml:space="preserve">2.18635296821594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17663598060608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21550440788269</t>
   </si>
   <si>
     <t xml:space="preserve">2.25992560386658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31822848320007</t>
+    <t xml:space="preserve">2.31822872161865</t>
   </si>
   <si>
     <t xml:space="preserve">2.38763618469238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38208341598511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3751425743103</t>
+    <t xml:space="preserve">2.38208389282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37514305114746</t>
   </si>
   <si>
     <t xml:space="preserve">2.24187970161438</t>
@@ -173,34 +173,34 @@
     <t xml:space="preserve">2.26270174980164</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25020837783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3196165561676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43344521522522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35848498344421</t>
+    <t xml:space="preserve">2.25020861625671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31961679458618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43344497680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35848522186279</t>
   </si>
   <si>
     <t xml:space="preserve">2.30156993865967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34599161148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35987329483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39318895339966</t>
+    <t xml:space="preserve">2.34599184989929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3598735332489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39318871498108</t>
   </si>
   <si>
     <t xml:space="preserve">2.29324126243591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23771500587463</t>
+    <t xml:space="preserve">2.23771476745605</t>
   </si>
   <si>
     <t xml:space="preserve">2.18774080276489</t>
@@ -209,25 +209,25 @@
     <t xml:space="preserve">2.13915586471558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14748477935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12110996246338</t>
+    <t xml:space="preserve">2.14748454093933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1211097240448</t>
   </si>
   <si>
     <t xml:space="preserve">2.06974744796753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01283311843872</t>
+    <t xml:space="preserve">2.01283264160156</t>
   </si>
   <si>
     <t xml:space="preserve">2.01838541030884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07113552093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11694526672363</t>
+    <t xml:space="preserve">2.07113575935364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11694550514221</t>
   </si>
   <si>
     <t xml:space="preserve">2.12527394294739</t>
@@ -236,28 +236,28 @@
     <t xml:space="preserve">2.22799777984619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3029580116272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23910331726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29046487808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3321099281311</t>
+    <t xml:space="preserve">2.30295872688293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23910307884216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29046511650085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33211016654968</t>
   </si>
   <si>
     <t xml:space="preserve">2.32655763626099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2793595790863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32378101348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30851078033447</t>
+    <t xml:space="preserve">2.27935981750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32378125190735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30851101875305</t>
   </si>
   <si>
     <t xml:space="preserve">2.26131343841553</t>
@@ -266,31 +266,31 @@
     <t xml:space="preserve">2.23493885993958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15720152854919</t>
+    <t xml:space="preserve">2.15720176696777</t>
   </si>
   <si>
     <t xml:space="preserve">2.11139225959778</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08224081993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09889936447144</t>
+    <t xml:space="preserve">2.08224058151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09889912605286</t>
   </si>
   <si>
     <t xml:space="preserve">2.08918213844299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10583996772766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04892516136169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03781938552856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0655825138092</t>
+    <t xml:space="preserve">2.10583972930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04892492294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03781986236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06558275222778</t>
   </si>
   <si>
     <t xml:space="preserve">2.03226685523987</t>
@@ -299,13 +299,13 @@
     <t xml:space="preserve">2.07252359390259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05725407600403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05156707763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12691879272461</t>
+    <t xml:space="preserve">2.05725359916687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05156683921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12691855430603</t>
   </si>
   <si>
     <t xml:space="preserve">2.19942760467529</t>
@@ -323,10 +323,10 @@
     <t xml:space="preserve">2.09279727935791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07147121429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99896240234375</t>
+    <t xml:space="preserve">2.07147097587585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99896264076233</t>
   </si>
   <si>
     <t xml:space="preserve">1.95773243904114</t>
@@ -335,46 +335,46 @@
     <t xml:space="preserve">1.87669312953949</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98901009559631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93640613555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94351506233215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84114944934845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78143727779388</t>
+    <t xml:space="preserve">1.98901033401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93640637397766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94351482391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84114992618561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78143715858459</t>
   </si>
   <si>
     <t xml:space="preserve">1.75157999992371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72598874568939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64210605621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6961327791214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77006244659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81129348278046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78001427650452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89375364780426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63499772548676</t>
+    <t xml:space="preserve">1.72598898410797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64210629463196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69613265991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77006232738495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81129312515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7800145149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89375376701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63499748706818</t>
   </si>
   <si>
     <t xml:space="preserve">1.5653327703476</t>
@@ -389,22 +389,22 @@
     <t xml:space="preserve">1.63926267623901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63641941547394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57670676708221</t>
+    <t xml:space="preserve">1.63641917705536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57670664787292</t>
   </si>
   <si>
     <t xml:space="preserve">1.51130640506744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52552366256714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53121066093445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63784110546112</t>
+    <t xml:space="preserve">1.52552378177643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53121054172516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63784098625183</t>
   </si>
   <si>
     <t xml:space="preserve">1.67196321487427</t>
@@ -416,88 +416,88 @@
     <t xml:space="preserve">1.67054152488708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74304974079132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70892798900604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72172391414642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77574944496155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76721894741058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72741067409515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69755423069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72456741333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71888029575348</t>
+    <t xml:space="preserve">1.74304986000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70892786979675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72172343730927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77574968338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76721906661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72741055488586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69755434989929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7245671749115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71888017654419</t>
   </si>
   <si>
     <t xml:space="preserve">1.66343283653259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55395877361298</t>
+    <t xml:space="preserve">1.55395889282227</t>
   </si>
   <si>
     <t xml:space="preserve">1.57528507709503</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5212584733963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63357603549957</t>
+    <t xml:space="preserve">1.52125871181488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6335756778717</t>
   </si>
   <si>
     <t xml:space="preserve">1.65916693210602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64779317378998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68760204315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71461534500122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70608460903168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70039772987366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74447131156921</t>
+    <t xml:space="preserve">1.64779305458069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68760228157043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71461498737335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70608448982239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70039796829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7444714307785</t>
   </si>
   <si>
     <t xml:space="preserve">1.70750629901886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72030210494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73167586326599</t>
+    <t xml:space="preserve">1.72030222415924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73167562484741</t>
   </si>
   <si>
     <t xml:space="preserve">1.7828586101532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77859258651733</t>
+    <t xml:space="preserve">1.77859282493591</t>
   </si>
   <si>
     <t xml:space="preserve">1.77148425579071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76437532901764</t>
+    <t xml:space="preserve">1.76437568664551</t>
   </si>
   <si>
     <t xml:space="preserve">1.75584530830383</t>
@@ -509,94 +509,94 @@
     <t xml:space="preserve">1.74162781238556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76864075660706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74873650074005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73451936244965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78428041934967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85252368450165</t>
+    <t xml:space="preserve">1.76864099502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74873673915863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73451900482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78428065776825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85252344608307</t>
   </si>
   <si>
     <t xml:space="preserve">1.84967994689941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81271517276764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83546257019043</t>
+    <t xml:space="preserve">1.81271493434906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83546245098114</t>
   </si>
   <si>
     <t xml:space="preserve">1.84825813770294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85963189601898</t>
+    <t xml:space="preserve">1.85963213443756</t>
   </si>
   <si>
     <t xml:space="preserve">1.9477801322937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97621464729309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09848427772522</t>
+    <t xml:space="preserve">1.97621440887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09848403930664</t>
   </si>
   <si>
     <t xml:space="preserve">2.1084361076355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07573652267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08568835258484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08853197097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09706211090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16104078292847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18236660957336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11412310600281</t>
+    <t xml:space="preserve">2.07573628425598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08568859100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08853220939636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09706234931946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16104102134705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18236684799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11412334442139</t>
   </si>
   <si>
     <t xml:space="preserve">2.00038409233093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03877139091492</t>
+    <t xml:space="preserve">2.03877115249634</t>
   </si>
   <si>
     <t xml:space="preserve">2.00891447067261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0529887676239</t>
+    <t xml:space="preserve">2.05298852920532</t>
   </si>
   <si>
     <t xml:space="preserve">2.06294083595276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11554455757141</t>
+    <t xml:space="preserve">2.11554479598999</t>
   </si>
   <si>
     <t xml:space="preserve">2.12549686431885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16246247291565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15961933135986</t>
+    <t xml:space="preserve">2.16246223449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15961909294128</t>
   </si>
   <si>
     <t xml:space="preserve">2.13260555267334</t>
@@ -605,22 +605,22 @@
     <t xml:space="preserve">2.08142304420471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03592801094055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07715797424316</t>
+    <t xml:space="preserve">2.03592753410339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07715821266174</t>
   </si>
   <si>
     <t xml:space="preserve">2.09990572929382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08995342254639</t>
+    <t xml:space="preserve">2.08995389938354</t>
   </si>
   <si>
     <t xml:space="preserve">2.01033592224121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12407493591309</t>
+    <t xml:space="preserve">2.12407517433167</t>
   </si>
   <si>
     <t xml:space="preserve">2.10417103767395</t>
@@ -629,16 +629,16 @@
     <t xml:space="preserve">2.07289290428162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16814970970154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27478003501892</t>
+    <t xml:space="preserve">2.16814994812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27477955818176</t>
   </si>
   <si>
     <t xml:space="preserve">2.37430167198181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26340579986572</t>
+    <t xml:space="preserve">2.2634060382843</t>
   </si>
   <si>
     <t xml:space="preserve">2.23354911804199</t>
@@ -650,10 +650,10 @@
     <t xml:space="preserve">2.23212742805481</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1781017780304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16957139968872</t>
+    <t xml:space="preserve">2.17810201644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16957116127014</t>
   </si>
   <si>
     <t xml:space="preserve">2.23639249801636</t>
@@ -665,31 +665,31 @@
     <t xml:space="preserve">2.21791005134583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2051146030426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22359704971313</t>
+    <t xml:space="preserve">2.20511436462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22359681129456</t>
   </si>
   <si>
     <t xml:space="preserve">2.26482772827148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31032299995422</t>
+    <t xml:space="preserve">2.31032276153564</t>
   </si>
   <si>
     <t xml:space="preserve">2.31743168830872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34302258491516</t>
+    <t xml:space="preserve">2.34302282333374</t>
   </si>
   <si>
     <t xml:space="preserve">2.34160113334656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30463576316833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29752707481384</t>
+    <t xml:space="preserve">2.30463624000549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.297527551651</t>
   </si>
   <si>
     <t xml:space="preserve">2.29610586166382</t>
@@ -704,31 +704,31 @@
     <t xml:space="preserve">2.3401792049408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4027361869812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41695356369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45249652862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41126680374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41553211212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42406225204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44396662712097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35439658164978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33733582496643</t>
+    <t xml:space="preserve">2.40273642539978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41695380210876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45249676704407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4112663269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.415531873703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42406249046326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44396615028381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35439682006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33733606338501</t>
   </si>
   <si>
     <t xml:space="preserve">2.33022737503052</t>
@@ -749,16 +749,16 @@
     <t xml:space="preserve">2.32311868667603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33449244499207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30890130996704</t>
+    <t xml:space="preserve">2.33449268341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30890107154846</t>
   </si>
   <si>
     <t xml:space="preserve">2.2989490032196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25629711151123</t>
+    <t xml:space="preserve">2.25629734992981</t>
   </si>
   <si>
     <t xml:space="preserve">2.12834048271179</t>
@@ -770,34 +770,34 @@
     <t xml:space="preserve">2.28473162651062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22928380966187</t>
+    <t xml:space="preserve">2.22928404808044</t>
   </si>
   <si>
     <t xml:space="preserve">2.27335810661316</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27904486656189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31316661834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33875799179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37856698036194</t>
+    <t xml:space="preserve">2.27904462814331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31316637992859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33875775337219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37856721878052</t>
   </si>
   <si>
     <t xml:space="preserve">2.32880568504333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36719250679016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34870958328247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29468417167664</t>
+    <t xml:space="preserve">2.36719226837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34870982170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29468369483948</t>
   </si>
   <si>
     <t xml:space="preserve">2.30321431159973</t>
@@ -806,13 +806,13 @@
     <t xml:space="preserve">2.28757548332214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32027506828308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28331017494202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29041862487793</t>
+    <t xml:space="preserve">2.32027530670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28330993652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29041886329651</t>
   </si>
   <si>
     <t xml:space="preserve">2.29326224327087</t>
@@ -830,19 +830,19 @@
     <t xml:space="preserve">2.3316490650177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46671390533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43117094039917</t>
+    <t xml:space="preserve">2.46671414375305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43117046356201</t>
   </si>
   <si>
     <t xml:space="preserve">2.42974925041199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49799299240112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46387052536011</t>
+    <t xml:space="preserve">2.49799275398254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46387028694153</t>
   </si>
   <si>
     <t xml:space="preserve">2.48661828041077</t>
@@ -851,19 +851,19 @@
     <t xml:space="preserve">2.5164749622345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51789689064026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56907963752747</t>
+    <t xml:space="preserve">2.51789712905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56907939910889</t>
   </si>
   <si>
     <t xml:space="preserve">2.53353595733643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48803973197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50510144233704</t>
+    <t xml:space="preserve">2.48803997039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50510120391846</t>
   </si>
   <si>
     <t xml:space="preserve">2.5079448223114</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">2.50652313232422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5548620223999</t>
+    <t xml:space="preserve">2.55486178398132</t>
   </si>
   <si>
     <t xml:space="preserve">2.57221221923828</t>
@@ -890,37 +890,37 @@
     <t xml:space="preserve">2.70667862892151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56642889976501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52594399452209</t>
+    <t xml:space="preserve">2.56642866134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52594375610352</t>
   </si>
   <si>
     <t xml:space="preserve">2.52883553504944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47389245033264</t>
+    <t xml:space="preserve">2.47389268875122</t>
   </si>
   <si>
     <t xml:space="preserve">2.5216064453125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51437664031982</t>
+    <t xml:space="preserve">2.5143768787384</t>
   </si>
   <si>
     <t xml:space="preserve">2.4710009098053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48979687690735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47533822059631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51726865768433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45654249191284</t>
+    <t xml:space="preserve">2.48979711532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47533869743347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51726841926575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45654225349426</t>
   </si>
   <si>
     <t xml:space="preserve">2.47967576980591</t>
@@ -932,22 +932,22 @@
     <t xml:space="preserve">2.48112177848816</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45798802375793</t>
+    <t xml:space="preserve">2.45798826217651</t>
   </si>
   <si>
     <t xml:space="preserve">2.48256778717041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48835134506226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48690533638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50859332084656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53751134872437</t>
+    <t xml:space="preserve">2.48835110664368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48690509796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50859355926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53751158714294</t>
   </si>
   <si>
     <t xml:space="preserve">2.6025755405426</t>
@@ -959,13 +959,13 @@
     <t xml:space="preserve">2.49558067321777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59245443344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66330218315125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61414241790771</t>
+    <t xml:space="preserve">2.59245419502258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6633026599884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61414265632629</t>
   </si>
   <si>
     <t xml:space="preserve">2.63149285316467</t>
@@ -983,58 +983,58 @@
     <t xml:space="preserve">2.73704171180725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72258281707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71246194839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71390795707703</t>
+    <t xml:space="preserve">2.72258305549622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71246218681335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71390771865845</t>
   </si>
   <si>
     <t xml:space="preserve">2.70812439918518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68932843208313</t>
+    <t xml:space="preserve">2.68932795524597</t>
   </si>
   <si>
     <t xml:space="preserve">2.68643641471863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6878821849823</t>
+    <t xml:space="preserve">2.68788242340088</t>
   </si>
   <si>
     <t xml:space="preserve">2.71101641654968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65028882026672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67920732498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67197775840759</t>
+    <t xml:space="preserve">2.6502890586853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67920708656311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67197751998901</t>
   </si>
   <si>
     <t xml:space="preserve">2.67053198814392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65318059921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65173506736755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66763997077942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65896487236023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64595150947571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59823775291443</t>
+    <t xml:space="preserve">2.65318083763123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65173482894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.667640209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65896463394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64595127105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59823799133301</t>
   </si>
   <si>
     <t xml:space="preserve">2.62426328659058</t>
@@ -1046,16 +1046,16 @@
     <t xml:space="preserve">2.54474067687988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57655000686646</t>
+    <t xml:space="preserve">2.57654976844788</t>
   </si>
   <si>
     <t xml:space="preserve">2.52449798583984</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48545956611633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50280976295471</t>
+    <t xml:space="preserve">2.48545932769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50281000137329</t>
   </si>
   <si>
     <t xml:space="preserve">2.52016019821167</t>
@@ -1067,19 +1067,19 @@
     <t xml:space="preserve">2.518714427948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53317332267761</t>
+    <t xml:space="preserve">2.53317308425903</t>
   </si>
   <si>
     <t xml:space="preserve">2.5519700050354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50714755058289</t>
+    <t xml:space="preserve">2.50714731216431</t>
   </si>
   <si>
     <t xml:space="preserve">2.55052423477173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54618644714355</t>
+    <t xml:space="preserve">2.54618668556213</t>
   </si>
   <si>
     <t xml:space="preserve">2.53606557846069</t>
@@ -1088,43 +1088,43 @@
     <t xml:space="preserve">2.5794415473938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64161396026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63004684448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58956241607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52305197715759</t>
+    <t xml:space="preserve">2.64161372184753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.630047082901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58956265449524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52305173873901</t>
   </si>
   <si>
     <t xml:space="preserve">2.51582288742065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49268865585327</t>
+    <t xml:space="preserve">2.49268889427185</t>
   </si>
   <si>
     <t xml:space="preserve">2.53461885452271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49124312400818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47244691848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50425577163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4840133190155</t>
+    <t xml:space="preserve">2.4912428855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47244668006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50425553321838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48401379585266</t>
   </si>
   <si>
     <t xml:space="preserve">2.49413442611694</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49847221374512</t>
+    <t xml:space="preserve">2.4984724521637</t>
   </si>
   <si>
     <t xml:space="preserve">2.47823023796082</t>
@@ -1133,28 +1133,28 @@
     <t xml:space="preserve">2.51293087005615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44931292533875</t>
+    <t xml:space="preserve">2.44931316375732</t>
   </si>
   <si>
     <t xml:space="preserve">2.40738201141357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45509600639343</t>
+    <t xml:space="preserve">2.45509624481201</t>
   </si>
   <si>
     <t xml:space="preserve">2.41027355194092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29605031013489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2468900680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28159070014954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18471765518188</t>
+    <t xml:space="preserve">2.29605007171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24688982963562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28159093856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18471789360046</t>
   </si>
   <si>
     <t xml:space="preserve">2.19773054122925</t>
@@ -1166,22 +1166,22 @@
     <t xml:space="preserve">2.26279473304749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28448271751404</t>
+    <t xml:space="preserve">2.28448247909546</t>
   </si>
   <si>
     <t xml:space="preserve">2.28592848777771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32496738433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34810161590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37846493721008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41461181640625</t>
+    <t xml:space="preserve">2.32496762275696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34810137748718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3784646987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41461205482483</t>
   </si>
   <si>
     <t xml:space="preserve">2.34231781959534</t>
@@ -1190,10 +1190,10 @@
     <t xml:space="preserve">2.35677647590637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35966825485229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34087204933167</t>
+    <t xml:space="preserve">2.35966849327087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34087228775024</t>
   </si>
   <si>
     <t xml:space="preserve">2.37701869010925</t>
@@ -1202,16 +1202,16 @@
     <t xml:space="preserve">2.39292335510254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40015244483948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4059362411499</t>
+    <t xml:space="preserve">2.40015268325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40593600273132</t>
   </si>
   <si>
     <t xml:space="preserve">2.33653426170349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29315781593323</t>
+    <t xml:space="preserve">2.29315757751465</t>
   </si>
   <si>
     <t xml:space="preserve">2.20495986938477</t>
@@ -1223,46 +1223,46 @@
     <t xml:space="preserve">2.23821473121643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23387718200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18327212333679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21797275543213</t>
+    <t xml:space="preserve">2.23387670516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18327164649963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21797251701355</t>
   </si>
   <si>
     <t xml:space="preserve">2.24544405937195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20062184333801</t>
+    <t xml:space="preserve">2.20062232017517</t>
   </si>
   <si>
     <t xml:space="preserve">2.22664785385132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28303694725037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31340098381042</t>
+    <t xml:space="preserve">2.28303670883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31340050697327</t>
   </si>
   <si>
     <t xml:space="preserve">2.31050872802734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38858580589294</t>
+    <t xml:space="preserve">2.38858556747437</t>
   </si>
   <si>
     <t xml:space="preserve">2.38713979721069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34665560722351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34520959854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3654522895813</t>
+    <t xml:space="preserve">2.34665584564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.345210313797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36545205116272</t>
   </si>
   <si>
     <t xml:space="preserve">2.39436912536621</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">2.40449023246765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32785964012146</t>
+    <t xml:space="preserve">2.32785940170288</t>
   </si>
   <si>
     <t xml:space="preserve">2.34954690933228</t>
@@ -1286,49 +1286,49 @@
     <t xml:space="preserve">2.31195473670959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22953963279724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31484627723694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30327987670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32062983512878</t>
+    <t xml:space="preserve">2.22953987121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31484651565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30327963829041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32063007354736</t>
   </si>
   <si>
     <t xml:space="preserve">2.3076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37268114089966</t>
+    <t xml:space="preserve">2.37268090248108</t>
   </si>
   <si>
     <t xml:space="preserve">2.42907047271729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36400604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31629228591919</t>
+    <t xml:space="preserve">2.36400580406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31629204750061</t>
   </si>
   <si>
     <t xml:space="preserve">2.35388493537903</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27725291252136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32930493354797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30617165565491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30038785934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37412714958191</t>
+    <t xml:space="preserve">2.27725315093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32930517196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30617141723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3003876209259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37412691116333</t>
   </si>
   <si>
     <t xml:space="preserve">2.33075094223022</t>
@@ -1340,43 +1340,43 @@
     <t xml:space="preserve">2.39726066589355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39870667457581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38569402694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60112977027893</t>
+    <t xml:space="preserve">2.39870691299438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3856942653656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60112953186035</t>
   </si>
   <si>
     <t xml:space="preserve">2.71969151496887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70957040786743</t>
+    <t xml:space="preserve">2.70957016944885</t>
   </si>
   <si>
     <t xml:space="preserve">2.75439214706421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77752661705017</t>
+    <t xml:space="preserve">2.77752685546875</t>
   </si>
   <si>
     <t xml:space="preserve">2.84837436676025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84114480018616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83391571044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86861634254456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90042591094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8295783996582</t>
+    <t xml:space="preserve">2.84114503860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83391547203064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86861610412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90042614936829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82957816123962</t>
   </si>
   <si>
     <t xml:space="preserve">2.73125839233398</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">2.78620195388794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75583791732788</t>
+    <t xml:space="preserve">2.7558376789093</t>
   </si>
   <si>
     <t xml:space="preserve">2.82524037361145</t>
@@ -1397,19 +1397,19 @@
     <t xml:space="preserve">2.83680748939514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74716281890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7384877204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63438439369202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66091990470886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65060067176819</t>
+    <t xml:space="preserve">2.74716305732727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73848748207092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6343846321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66091966629028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65060091018677</t>
   </si>
   <si>
     <t xml:space="preserve">2.71251702308655</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">2.70367121696472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63143634796143</t>
+    <t xml:space="preserve">2.63143610954285</t>
   </si>
   <si>
     <t xml:space="preserve">2.52824234962463</t>
@@ -1427,10 +1427,10 @@
     <t xml:space="preserve">2.4825427532196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52234578132629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56509733200073</t>
+    <t xml:space="preserve">2.52234554290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56509709358215</t>
   </si>
   <si>
     <t xml:space="preserve">2.6107976436615</t>
@@ -1439,55 +1439,55 @@
     <t xml:space="preserve">2.57689046859741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51939725875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59163308143616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.618168592453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59015917778015</t>
+    <t xml:space="preserve">2.51939749717712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59163331985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61816883087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59015893936157</t>
   </si>
   <si>
     <t xml:space="preserve">2.54888105392456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56067442893982</t>
+    <t xml:space="preserve">2.5606746673584</t>
   </si>
   <si>
     <t xml:space="preserve">2.55625200271606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54593253135681</t>
+    <t xml:space="preserve">2.54593276977539</t>
   </si>
   <si>
     <t xml:space="preserve">2.57099390029907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51350069046021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51055216789246</t>
+    <t xml:space="preserve">2.51350045204163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51055264472961</t>
   </si>
   <si>
     <t xml:space="preserve">2.53708744049072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54151010513306</t>
+    <t xml:space="preserve">2.54151034355164</t>
   </si>
   <si>
     <t xml:space="preserve">2.65354871749878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6594455242157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70514535903931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69040369987488</t>
+    <t xml:space="preserve">2.65944576263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70514559745789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6904034614563</t>
   </si>
   <si>
     <t xml:space="preserve">2.65797162055969</t>
@@ -1496,7 +1496,7 @@
     <t xml:space="preserve">2.61964273452759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63291049003601</t>
+    <t xml:space="preserve">2.63291025161743</t>
   </si>
   <si>
     <t xml:space="preserve">2.64912629127502</t>
@@ -1508,19 +1508,19 @@
     <t xml:space="preserve">2.6653425693512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64470362663269</t>
+    <t xml:space="preserve">2.64470386505127</t>
   </si>
   <si>
     <t xml:space="preserve">2.63880705833435</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66386818885803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71399140357971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73168158531189</t>
+    <t xml:space="preserve">2.66386842727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71399116516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73168134689331</t>
   </si>
   <si>
     <t xml:space="preserve">2.7169394493103</t>
@@ -1535,10 +1535,10 @@
     <t xml:space="preserve">2.70661950111389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69187808036804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68892908096313</t>
+    <t xml:space="preserve">2.69187784194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68892931938171</t>
   </si>
   <si>
     <t xml:space="preserve">2.67713570594788</t>
@@ -1550,40 +1550,40 @@
     <t xml:space="preserve">2.6417555809021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57541656494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61374592781067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60932350158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58868479728699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58131289482117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53561329841614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48843932151794</t>
+    <t xml:space="preserve">2.57541608810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61374568939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60932326316833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58868455886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58131313323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53561305999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48843955993652</t>
   </si>
   <si>
     <t xml:space="preserve">2.47222352027893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50170683860779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56362271308899</t>
+    <t xml:space="preserve">2.50170707702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56362295150757</t>
   </si>
   <si>
     <t xml:space="preserve">2.67123913764954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67418742179871</t>
+    <t xml:space="preserve">2.67418766021729</t>
   </si>
   <si>
     <t xml:space="preserve">2.65502309799194</t>
@@ -1592,34 +1592,34 @@
     <t xml:space="preserve">2.68450689315796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66239380836487</t>
+    <t xml:space="preserve">2.66239404678345</t>
   </si>
   <si>
     <t xml:space="preserve">2.62406539916992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62996196746826</t>
+    <t xml:space="preserve">2.62996172904968</t>
   </si>
   <si>
     <t xml:space="preserve">2.63733291625977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62111663818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42210054397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41915225982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36608123779297</t>
+    <t xml:space="preserve">2.62111687660217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42210030555725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41915202140808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36608147621155</t>
   </si>
   <si>
     <t xml:space="preserve">2.38966822624207</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41325545310974</t>
+    <t xml:space="preserve">2.41325521469116</t>
   </si>
   <si>
     <t xml:space="preserve">2.33659696578979</t>
@@ -1628,49 +1628,49 @@
     <t xml:space="preserve">2.24667167663574</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23045539855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22898125648499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16706466674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18033266067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15674567222595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20244526863098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19359993934631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13905549049377</t>
+    <t xml:space="preserve">2.23045563697815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22898149490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16706490516663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18033242225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15674543380737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20244550704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19360017776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13905572891235</t>
   </si>
   <si>
     <t xml:space="preserve">2.11399412155151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08745789527893</t>
+    <t xml:space="preserve">2.08745813369751</t>
   </si>
   <si>
     <t xml:space="preserve">2.0417582988739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00932645797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05207777023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.105149269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05797410011292</t>
+    <t xml:space="preserve">2.00932598114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05207800865173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10514903068542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05797433853149</t>
   </si>
   <si>
     <t xml:space="preserve">2.0550262928009</t>
@@ -1679,10 +1679,10 @@
     <t xml:space="preserve">2.09335565567017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1361072063446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11694240570068</t>
+    <t xml:space="preserve">2.13610672950745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11694264411926</t>
   </si>
   <si>
     <t xml:space="preserve">2.09925222396851</t>
@@ -1691,13 +1691,13 @@
     <t xml:space="preserve">2.10220074653625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10072684288025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09040665626526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04912924766541</t>
+    <t xml:space="preserve">2.10072660446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0904061794281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04912900924683</t>
   </si>
   <si>
     <t xml:space="preserve">2.06829380989075</t>
@@ -1706,85 +1706,85 @@
     <t xml:space="preserve">2.05060338973999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04765510559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02701640129089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01964569091797</t>
+    <t xml:space="preserve">2.0476553440094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02701663970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01964545249939</t>
   </si>
   <si>
     <t xml:space="preserve">1.97394573688507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97984278202057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96215164661407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98426532745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08008718490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06387138366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07861304283142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04618096351624</t>
+    <t xml:space="preserve">1.97984254360199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96215152740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98426496982574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08008694648743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06387090682983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07861328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04618072509766</t>
   </si>
   <si>
     <t xml:space="preserve">2.08598399162292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05650019645691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95625495910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98279082775116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9444614648819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93709027767181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96657395362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96804857254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89286506175995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98131668567657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91497778892517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87517464160919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87370073795319</t>
+    <t xml:space="preserve">2.05649995803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95625483989716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98279106616974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94446134567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93709051609039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9665744304657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9680483341217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89286482334137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98131680488586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91497790813446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87517488002777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87370049953461</t>
   </si>
   <si>
     <t xml:space="preserve">1.94003891944885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92677128314972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9931104183197</t>
+    <t xml:space="preserve">1.92677116394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99311053752899</t>
   </si>
   <si>
     <t xml:space="preserve">2.0034294128418</t>
@@ -1793,70 +1793,70 @@
     <t xml:space="preserve">1.99458432197571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99163615703583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94888401031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8884425163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87222635746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91940057277679</t>
+    <t xml:space="preserve">1.99163627624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94888377189636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88844239711761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87222623825073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91940033435822</t>
   </si>
   <si>
     <t xml:space="preserve">1.89433908462524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86485552787781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85306203365326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83831930160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88549423217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85158777236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82505166530609</t>
+    <t xml:space="preserve">1.86485540866852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85306191444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83831906318665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88549375534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85158741474152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8250515460968</t>
   </si>
   <si>
     <t xml:space="preserve">1.78230023384094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71596109867096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69532263278961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71006453037262</t>
+    <t xml:space="preserve">1.71596121788025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6953227519989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71006441116333</t>
   </si>
   <si>
     <t xml:space="preserve">1.73217809200287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78377437591553</t>
+    <t xml:space="preserve">1.78377449512482</t>
   </si>
   <si>
     <t xml:space="preserve">1.76313602924347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76166164875031</t>
+    <t xml:space="preserve">1.76166152954102</t>
   </si>
   <si>
     <t xml:space="preserve">1.78672301769257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80588722229004</t>
+    <t xml:space="preserve">1.80588710308075</t>
   </si>
   <si>
     <t xml:space="preserve">1.83389675617218</t>
@@ -1865,13 +1865,13 @@
     <t xml:space="preserve">1.87664890289307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86927795410156</t>
+    <t xml:space="preserve">1.86927807331085</t>
   </si>
   <si>
     <t xml:space="preserve">1.84569025039673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83979368209839</t>
+    <t xml:space="preserve">1.8397935628891</t>
   </si>
   <si>
     <t xml:space="preserve">1.83242249488831</t>
@@ -1880,40 +1880,40 @@
     <t xml:space="preserve">1.84274184703827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83684504032135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89728760719299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8899165391922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88254582881927</t>
+    <t xml:space="preserve">1.83684527873993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8972874879837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88991641998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88254547119141</t>
   </si>
   <si>
     <t xml:space="preserve">1.91055500507355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87075209617615</t>
+    <t xml:space="preserve">1.87075221538544</t>
   </si>
   <si>
     <t xml:space="preserve">1.80293881893158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80441308021545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79114532470703</t>
+    <t xml:space="preserve">1.80441319942474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79114520549774</t>
   </si>
   <si>
     <t xml:space="preserve">1.75576496124268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81325852870941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81178390979767</t>
+    <t xml:space="preserve">1.81325840950012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81178379058838</t>
   </si>
   <si>
     <t xml:space="preserve">1.83537101745605</t>
@@ -1922,25 +1922,25 @@
     <t xml:space="preserve">1.79556798934937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77492940425873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80883574485779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79851627349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79704213142395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80736148357391</t>
+    <t xml:space="preserve">1.77492928504944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8088356256485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79851615428925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79704236984253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80736172199249</t>
   </si>
   <si>
     <t xml:space="preserve">1.78082621097565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75429081916809</t>
+    <t xml:space="preserve">1.7542906999588</t>
   </si>
   <si>
     <t xml:space="preserve">1.71301293373108</t>
@@ -1949,43 +1949,43 @@
     <t xml:space="preserve">1.70711624622345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74544560909271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76461005210876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77198112010956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77787780761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78819715976715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74839389324188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66583895683289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67910659313202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61129415035248</t>
+    <t xml:space="preserve">1.745445728302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76460993289948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77198076248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77787744998932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78819692134857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74839401245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6658388376236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67910647392273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6112939119339</t>
   </si>
   <si>
     <t xml:space="preserve">1.57886123657227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5361100435257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55822265148163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54200649261475</t>
+    <t xml:space="preserve">1.53610992431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55822277069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54200673103333</t>
   </si>
   <si>
     <t xml:space="preserve">1.53445518016815</t>
@@ -1994,31 +1994,31 @@
     <t xml:space="preserve">1.53596544265747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56466102600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54351687431335</t>
+    <t xml:space="preserve">1.5646607875824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54351699352264</t>
   </si>
   <si>
     <t xml:space="preserve">1.55559909343719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5389860868454</t>
+    <t xml:space="preserve">1.53898596763611</t>
   </si>
   <si>
     <t xml:space="preserve">1.54502725601196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60543847084045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58429455757141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56768143177032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56919157505035</t>
+    <t xml:space="preserve">1.60543859004974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58429443836212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56768155097961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56919169425964</t>
   </si>
   <si>
     <t xml:space="preserve">1.58882534503937</t>
@@ -2030,7 +2030,7 @@
     <t xml:space="preserve">1.51935243606567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52690386772156</t>
+    <t xml:space="preserve">1.52690374851227</t>
   </si>
   <si>
     <t xml:space="preserve">1.47177791595459</t>
@@ -2042,19 +2042,19 @@
     <t xml:space="preserve">1.471022605896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45138907432556</t>
+    <t xml:space="preserve">1.45138883590698</t>
   </si>
   <si>
     <t xml:space="preserve">1.46875715255737</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49367690086365</t>
+    <t xml:space="preserve">1.49367678165436</t>
   </si>
   <si>
     <t xml:space="preserve">1.48386001586914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50047314167023</t>
+    <t xml:space="preserve">1.50047302246094</t>
   </si>
   <si>
     <t xml:space="preserve">1.45894038677216</t>
@@ -2063,25 +2063,25 @@
     <t xml:space="preserve">1.46800208091736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.489901304245</t>
+    <t xml:space="preserve">1.48990118503571</t>
   </si>
   <si>
     <t xml:space="preserve">1.48234975337982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48083961009979</t>
+    <t xml:space="preserve">1.4808394908905</t>
   </si>
   <si>
     <t xml:space="preserve">1.53294491767883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57523286342621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56315052509308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52539348602295</t>
+    <t xml:space="preserve">1.57523274421692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56315040588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52539360523224</t>
   </si>
   <si>
     <t xml:space="preserve">1.50424885749817</t>
@@ -2090,31 +2090,31 @@
     <t xml:space="preserve">1.47328805923462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4725329875946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44912350177765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45365452766418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46649181842804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44987881183624</t>
+    <t xml:space="preserve">1.47253286838531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44912362098694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4536544084549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46649193763733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44987869262695</t>
   </si>
   <si>
     <t xml:space="preserve">1.44610297679901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43779647350311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42269361019135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4204283952713</t>
+    <t xml:space="preserve">1.43779635429382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42269372940063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42042815685272</t>
   </si>
   <si>
     <t xml:space="preserve">1.4272243976593</t>
@@ -2126,13 +2126,13 @@
     <t xml:space="preserve">1.40683579444885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.400794506073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39097762107849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38644623756409</t>
+    <t xml:space="preserve">1.40079438686371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39097774028778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3864461183548</t>
   </si>
   <si>
     <t xml:space="preserve">1.28374695777893</t>
@@ -2147,25 +2147,25 @@
     <t xml:space="preserve">1.20068073272705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23617231845856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25278544425964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2218245267868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23088645935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27695083618164</t>
+    <t xml:space="preserve">1.23617243766785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25278532505035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22182476520538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2308863401413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27695071697235</t>
   </si>
   <si>
     <t xml:space="preserve">1.26637876033783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27619564533234</t>
+    <t xml:space="preserve">1.27619552612305</t>
   </si>
   <si>
     <t xml:space="preserve">1.31395256519318</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">1.27090954780579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28223669528961</t>
+    <t xml:space="preserve">1.28223657608032</t>
   </si>
   <si>
     <t xml:space="preserve">1.28752267360687</t>
@@ -2186,7 +2186,7 @@
     <t xml:space="preserve">1.38342559337616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37436378002167</t>
+    <t xml:space="preserve">1.37436389923096</t>
   </si>
   <si>
     <t xml:space="preserve">1.35246467590332</t>
@@ -2210,16 +2210,16 @@
     <t xml:space="preserve">1.36454701423645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33736193180084</t>
+    <t xml:space="preserve">1.33736205101013</t>
   </si>
   <si>
     <t xml:space="preserve">1.30262541770935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2897881269455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26109278202057</t>
+    <t xml:space="preserve">1.28978824615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26109266281128</t>
   </si>
   <si>
     <t xml:space="preserve">1.26864421367645</t>
@@ -2231,7 +2231,7 @@
     <t xml:space="preserve">1.27468526363373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27997124195099</t>
+    <t xml:space="preserve">1.27997136116028</t>
   </si>
   <si>
     <t xml:space="preserve">1.25958168506622</t>
@@ -2246,22 +2246,22 @@
     <t xml:space="preserve">1.28148150444031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30413591861725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33660686016083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36077117919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38871240615845</t>
+    <t xml:space="preserve">1.30413579940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33660674095154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36077129840851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38871228694916</t>
   </si>
   <si>
     <t xml:space="preserve">1.38267040252686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3517097234726</t>
+    <t xml:space="preserve">1.35170984268188</t>
   </si>
   <si>
     <t xml:space="preserve">1.35699570178986</t>
@@ -2270,13 +2270,13 @@
     <t xml:space="preserve">1.36152648925781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36228179931641</t>
+    <t xml:space="preserve">1.36228156089783</t>
   </si>
   <si>
     <t xml:space="preserve">1.34113776683807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36756765842438</t>
+    <t xml:space="preserve">1.36756753921509</t>
   </si>
   <si>
     <t xml:space="preserve">1.42495906352997</t>
@@ -2285,34 +2285,34 @@
     <t xml:space="preserve">1.41740763187408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43326556682587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40532529354095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43477594852448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62960290908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58278429508209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57825338840485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58127403259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54653751850128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53747606277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52237272262573</t>
+    <t xml:space="preserve">1.43326568603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40532541275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43477582931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62960314750671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5827841758728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57825350761414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58127391338348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54653763771057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53747582435608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52237284183502</t>
   </si>
   <si>
     <t xml:space="preserve">1.55257856845856</t>
@@ -2321,13 +2321,13 @@
     <t xml:space="preserve">1.60241782665253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63111317157745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60090780258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62054145336151</t>
+    <t xml:space="preserve">1.63111329078674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60090756416321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62054133415222</t>
   </si>
   <si>
     <t xml:space="preserve">1.54955792427063</t>
@@ -2336,40 +2336,40 @@
     <t xml:space="preserve">1.57221233844757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61147952079773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64168608188629</t>
+    <t xml:space="preserve">1.61147964000702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.641685962677</t>
   </si>
   <si>
     <t xml:space="preserve">1.61298990249634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61752080917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59184598922729</t>
+    <t xml:space="preserve">1.61752068996429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59184610843658</t>
   </si>
   <si>
     <t xml:space="preserve">1.58731508255005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6190310716629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57976365089417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56013011932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55861961841583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59788703918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60392820835114</t>
+    <t xml:space="preserve">1.61903119087219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57976377010345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56013000011444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55861973762512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59788691997528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60392808914185</t>
   </si>
   <si>
     <t xml:space="preserve">1.58580482006073</t>
@@ -2384,25 +2384,25 @@
     <t xml:space="preserve">1.59033560752869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5299243927002</t>
+    <t xml:space="preserve">1.52992451190948</t>
   </si>
   <si>
     <t xml:space="preserve">1.51331126689911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50953483581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52388334274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54049634933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63866460323334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75948810577393</t>
+    <t xml:space="preserve">1.50953495502472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52388322353363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54049623012543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63866448402405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75948786735535</t>
   </si>
   <si>
     <t xml:space="preserve">1.806307554245</t>
@@ -2417,25 +2417,25 @@
     <t xml:space="preserve">2.02983069419861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06909823417664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94827485084534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89088308811188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77912259101868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77308118343353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81687939167023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70813834667206</t>
+    <t xml:space="preserve">2.06909799575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94827461242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89088320732117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7791223526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77308106422424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81687951087952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70813846588135</t>
   </si>
   <si>
     <t xml:space="preserve">1.4800843000412</t>
@@ -2450,25 +2450,25 @@
     <t xml:space="preserve">1.24070310592651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19917035102844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18406772613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.959789276123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995280861854553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91901171207428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945441544055939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962809801101685</t>
+    <t xml:space="preserve">1.19917047023773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18406760692596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959789395332336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995280921459198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919011771678925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945441603660583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.962809860706329</t>
   </si>
   <si>
     <t xml:space="preserve">1.01869106292725</t>
@@ -2486,13 +2486,13 @@
     <t xml:space="preserve">1.07910239696503</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06777513027191</t>
+    <t xml:space="preserve">1.0677752494812</t>
   </si>
   <si>
     <t xml:space="preserve">1.01944613456726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999811828136444</t>
+    <t xml:space="preserve">0.999811708927155</t>
   </si>
   <si>
     <t xml:space="preserve">1.0413453578949</t>
@@ -2501,22 +2501,22 @@
     <t xml:space="preserve">1.02699756622314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10628747940063</t>
+    <t xml:space="preserve">1.10628736019135</t>
   </si>
   <si>
     <t xml:space="preserve">1.05720317363739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11459398269653</t>
+    <t xml:space="preserve">1.11459386348724</t>
   </si>
   <si>
     <t xml:space="preserve">1.13875913619995</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20219099521637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16745448112488</t>
+    <t xml:space="preserve">1.20219111442566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16745460033417</t>
   </si>
   <si>
     <t xml:space="preserve">1.16594421863556</t>
@@ -2528,19 +2528,19 @@
     <t xml:space="preserve">1.06701993942261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09420502185822</t>
+    <t xml:space="preserve">1.0942051410675</t>
   </si>
   <si>
     <t xml:space="preserve">1.06324434280396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09496033191681</t>
+    <t xml:space="preserve">1.09496021270752</t>
   </si>
   <si>
     <t xml:space="preserve">1.07834720611572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08212280273438</t>
+    <t xml:space="preserve">1.08212292194366</t>
   </si>
   <si>
     <t xml:space="preserve">1.07457137107849</t>
@@ -2549,73 +2549,73 @@
     <t xml:space="preserve">1.08665370941162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09269499778748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03756964206696</t>
+    <t xml:space="preserve">1.09269487857819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03756940364838</t>
   </si>
   <si>
     <t xml:space="preserve">1.07306122779846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0496518611908</t>
+    <t xml:space="preserve">1.04965174198151</t>
   </si>
   <si>
     <t xml:space="preserve">1.03530418872833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04436576366425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04285562038422</t>
+    <t xml:space="preserve">1.04436588287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04285550117493</t>
   </si>
   <si>
     <t xml:space="preserve">1.01189470291138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.985464096069336</t>
+    <t xml:space="preserve">0.985464155673981</t>
   </si>
   <si>
     <t xml:space="preserve">0.970361292362213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.989239752292633</t>
+    <t xml:space="preserve">0.989239692687988</t>
   </si>
   <si>
     <t xml:space="preserve">0.94317626953125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.926563024520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.921277046203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913725674152374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.986219227313995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997546374797821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.058713555336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09722554683685</t>
+    <t xml:space="preserve">0.926563084125519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.921276986598969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913725733757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986219167709351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997546434402466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05871343612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09722566604614</t>
   </si>
   <si>
     <t xml:space="preserve">1.10251152515411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13422763347626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18180227279663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21502840518951</t>
+    <t xml:space="preserve">1.13422751426697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18180215358734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21502828598022</t>
   </si>
   <si>
     <t xml:space="preserve">1.23919296264648</t>
@@ -2627,16 +2627,16 @@
     <t xml:space="preserve">1.18935358524323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14782083034515</t>
+    <t xml:space="preserve">1.14782094955444</t>
   </si>
   <si>
     <t xml:space="preserve">1.16820967197418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18708825111389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16216850280762</t>
+    <t xml:space="preserve">1.18708801269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16216862201691</t>
   </si>
   <si>
     <t xml:space="preserve">1.19312930107117</t>
@@ -2645,7 +2645,7 @@
     <t xml:space="preserve">1.17047512531281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24598920345306</t>
+    <t xml:space="preserve">1.24598908424377</t>
   </si>
   <si>
     <t xml:space="preserve">1.29280865192413</t>
@@ -2654,16 +2654,16 @@
     <t xml:space="preserve">1.36303675174713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40381503105164</t>
+    <t xml:space="preserve">1.40381515026093</t>
   </si>
   <si>
     <t xml:space="preserve">1.41136646270752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39399838447571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39928436279297</t>
+    <t xml:space="preserve">1.39399814605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39928424358368</t>
   </si>
   <si>
     <t xml:space="preserve">1.4015496969223</t>
@@ -2678,7 +2678,7 @@
     <t xml:space="preserve">1.49292182922363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44836843013763</t>
+    <t xml:space="preserve">1.44836831092834</t>
   </si>
   <si>
     <t xml:space="preserve">1.48763573169708</t>
@@ -2687,7 +2687,7 @@
     <t xml:space="preserve">1.47630858421326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46498155593872</t>
+    <t xml:space="preserve">1.46498167514801</t>
   </si>
   <si>
     <t xml:space="preserve">1.39626371860504</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">1.43175530433655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44534778594971</t>
+    <t xml:space="preserve">1.445347905159</t>
   </si>
   <si>
     <t xml:space="preserve">1.47479832172394</t>
@@ -2720,7 +2720,7 @@
     <t xml:space="preserve">1.5208625793457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37889468669891</t>
+    <t xml:space="preserve">1.37889456748962</t>
   </si>
   <si>
     <t xml:space="preserve">1.3781396150589</t>
@@ -2732,7 +2732,7 @@
     <t xml:space="preserve">1.37209844589233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39475321769714</t>
+    <t xml:space="preserve">1.39475333690643</t>
   </si>
   <si>
     <t xml:space="preserve">1.37964987754822</t>
@@ -2741,22 +2741,22 @@
     <t xml:space="preserve">1.38795721530914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3924880027771</t>
+    <t xml:space="preserve">1.39248812198639</t>
   </si>
   <si>
     <t xml:space="preserve">1.32150399684906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31848359107971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34340298175812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30035996437073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32376933097839</t>
+    <t xml:space="preserve">1.31848347187042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34340310096741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30036008358002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32376945018768</t>
   </si>
   <si>
     <t xml:space="preserve">1.33434152603149</t>
@@ -2777,16 +2777,16 @@
     <t xml:space="preserve">1.35473024845123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31772828102112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33207595348358</t>
+    <t xml:space="preserve">1.31772840023041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33207607269287</t>
   </si>
   <si>
     <t xml:space="preserve">1.33585166931152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27393019199371</t>
+    <t xml:space="preserve">1.27393007278442</t>
   </si>
   <si>
     <t xml:space="preserve">1.26486837863922</t>
@@ -2810,7 +2810,7 @@
     <t xml:space="preserve">1.22711062431335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24221348762512</t>
+    <t xml:space="preserve">1.24221336841583</t>
   </si>
   <si>
     <t xml:space="preserve">1.23843777179718</t>
@@ -2831,43 +2831,43 @@
     <t xml:space="preserve">1.55408895015717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81234860420227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78214299678802</t>
+    <t xml:space="preserve">1.81234872341156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78214275836945</t>
   </si>
   <si>
     <t xml:space="preserve">1.77459168434143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75797760486603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69303548336029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72173082828522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6854841709137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70209717750549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7036075592041</t>
+    <t xml:space="preserve">1.75797772407532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.693035364151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7217310667038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68548405170441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70209729671478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70360743999481</t>
   </si>
   <si>
     <t xml:space="preserve">1.73079264163971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72777211666107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69907665252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66887128353119</t>
+    <t xml:space="preserve">1.72777199745178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69907653331757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6688711643219</t>
   </si>
   <si>
     <t xml:space="preserve">1.66282987594604</t>
@@ -2879,31 +2879,31 @@
     <t xml:space="preserve">1.66131961345673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67642259597778</t>
+    <t xml:space="preserve">1.67642247676849</t>
   </si>
   <si>
     <t xml:space="preserve">1.64470648765564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61601030826569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63564395904541</t>
+    <t xml:space="preserve">1.61601054668427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6356440782547</t>
   </si>
   <si>
     <t xml:space="preserve">1.65829908847809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66585063934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66434013843536</t>
+    <t xml:space="preserve">1.66585052013397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66434001922607</t>
   </si>
   <si>
     <t xml:space="preserve">1.74438524246216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77761209011078</t>
+    <t xml:space="preserve">1.77761220932007</t>
   </si>
   <si>
     <t xml:space="preserve">1.75646734237671</t>
@@ -2912,22 +2912,25 @@
     <t xml:space="preserve">1.7202205657959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73683369159698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69454574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65225791931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67491209506989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65376830101013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63715434074402</t>
+    <t xml:space="preserve">1.73683381080627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69454598426819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65225803852081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67491221427917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65376818180084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63715422153473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54200661182404</t>
   </si>
   <si>
     <t xml:space="preserve">1.57070195674896</t>
@@ -2936,73 +2939,73 @@
     <t xml:space="preserve">1.59486651420593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62205147743225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74740552902222</t>
+    <t xml:space="preserve">1.62205159664154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7474057674408</t>
   </si>
   <si>
     <t xml:space="preserve">1.8863525390625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85765707492828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88031136989594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86822903156281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85463643074036</t>
+    <t xml:space="preserve">1.85765719413757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88031125068665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86822915077209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85463654994965</t>
   </si>
   <si>
     <t xml:space="preserve">1.88937294483185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85010552406311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80932807922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83047211170197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82141005992889</t>
+    <t xml:space="preserve">1.85010540485382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80932819843292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83047223091125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8214099407196</t>
   </si>
   <si>
     <t xml:space="preserve">1.81838965415955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82594096660614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80781745910645</t>
+    <t xml:space="preserve">1.82594108581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80781757831573</t>
   </si>
   <si>
     <t xml:space="preserve">1.80177652835846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84557461738586</t>
+    <t xml:space="preserve">1.84557473659515</t>
   </si>
   <si>
     <t xml:space="preserve">1.83500266075134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82745134830475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87124943733215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86369788646698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92713069915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97999060153961</t>
+    <t xml:space="preserve">1.82745146751404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87124967575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86369800567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92713105678558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97999083995819</t>
   </si>
   <si>
     <t xml:space="preserve">2.05399513244629</t>
@@ -3020,13 +3023,13 @@
     <t xml:space="preserve">2.12950921058655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1068549156189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15518498420715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13555026054382</t>
+    <t xml:space="preserve">2.10685467720032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15518450737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1355504989624</t>
   </si>
   <si>
     <t xml:space="preserve">2.13857102394104</t>
@@ -3041,7 +3044,7 @@
     <t xml:space="preserve">2.18992114067078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18690061569214</t>
+    <t xml:space="preserve">2.18690085411072</t>
   </si>
   <si>
     <t xml:space="preserve">2.16877722740173</t>
@@ -3053,28 +3056,28 @@
     <t xml:space="preserve">2.23522973060608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24731206893921</t>
+    <t xml:space="preserve">2.24731183052063</t>
   </si>
   <si>
     <t xml:space="preserve">2.26996684074402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30168294906616</t>
+    <t xml:space="preserve">2.30168271064758</t>
   </si>
   <si>
     <t xml:space="preserve">2.23673987388611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2458016872406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24882221221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36964535713196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39985179901123</t>
+    <t xml:space="preserve">2.24580192565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24882245063782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36964583396912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39985203742981</t>
   </si>
   <si>
     <t xml:space="preserve">2.48140716552734</t>
@@ -3101,7 +3104,7 @@
     <t xml:space="preserve">2.78648638725281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88616514205933</t>
+    <t xml:space="preserve">2.88616466522217</t>
   </si>
   <si>
     <t xml:space="preserve">2.86502075195312</t>
@@ -3116,28 +3119,28 @@
     <t xml:space="preserve">2.94506645202637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93147420883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97980284690857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96621036529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9571487903595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97829294204712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08411264419556</t>
+    <t xml:space="preserve">2.93147397041321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97980308532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96621060371399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95714902877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97829270362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08411288261414</t>
   </si>
   <si>
     <t xml:space="preserve">3.07337760925293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05804085731506</t>
+    <t xml:space="preserve">3.05804061889648</t>
   </si>
   <si>
     <t xml:space="preserve">3.15312528610229</t>
@@ -3155,7 +3158,7 @@
     <t xml:space="preserve">3.21600413322449</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18839836120605</t>
+    <t xml:space="preserve">3.18839812278748</t>
   </si>
   <si>
     <t xml:space="preserve">3.17459583282471</t>
@@ -3164,10 +3167,10 @@
     <t xml:space="preserve">3.12858748435974</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06264138221741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98749470710754</t>
+    <t xml:space="preserve">3.06264162063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98749446868896</t>
   </si>
   <si>
     <t xml:space="preserve">2.96602392196655</t>
@@ -3185,7 +3188,7 @@
     <t xml:space="preserve">2.901611328125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83106541633606</t>
+    <t xml:space="preserve">2.83106517791748</t>
   </si>
   <si>
     <t xml:space="preserve">2.80192589759827</t>
@@ -3194,28 +3197,28 @@
     <t xml:space="preserve">2.80039238929749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73598051071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79425811767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79272413253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83719968795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76665258407593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80499291419983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79119038581848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85713672637939</t>
+    <t xml:space="preserve">2.73598027229309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7942578792572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79272437095642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83719944953918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76665306091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80499315261841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79119062423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85713696479797</t>
   </si>
   <si>
     <t xml:space="preserve">2.78198885917664</t>
@@ -3224,28 +3227,28 @@
     <t xml:space="preserve">2.75131678581238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72371172904968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84333395957947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79579138755798</t>
+    <t xml:space="preserve">2.72371196746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84333419799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7957911491394</t>
   </si>
   <si>
     <t xml:space="preserve">2.77892160415649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72524523735046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6731014251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58108472824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66543340682983</t>
+    <t xml:space="preserve">2.72524499893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67310166358948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58108496665955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66543364524841</t>
   </si>
   <si>
     <t xml:space="preserve">2.73291325569153</t>
@@ -3269,34 +3272,34 @@
     <t xml:space="preserve">2.90774583816528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85100197792053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86020398139954</t>
+    <t xml:space="preserve">2.85100221633911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86020374298096</t>
   </si>
   <si>
     <t xml:space="preserve">2.85867023468018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83873343467712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84486770629883</t>
+    <t xml:space="preserve">2.83873319625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84486746788025</t>
   </si>
   <si>
     <t xml:space="preserve">2.91848111152649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95222115516663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90467882156372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96755766868591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92768263816833</t>
+    <t xml:space="preserve">2.95222139358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90467858314514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96755743026733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92768287658691</t>
   </si>
   <si>
     <t xml:space="preserve">2.92461562156677</t>
@@ -3308,37 +3311,37 @@
     <t xml:space="preserve">2.86173748970032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84640121459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87860703468323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89854407310486</t>
+    <t xml:space="preserve">2.84640145301819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87860727310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89854431152344</t>
   </si>
   <si>
     <t xml:space="preserve">2.99976348876953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00743126869202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98289346694946</t>
+    <t xml:space="preserve">3.0074315071106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98289370536804</t>
   </si>
   <si>
     <t xml:space="preserve">2.98596096038818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95375514030457</t>
+    <t xml:space="preserve">2.95375490188599</t>
   </si>
   <si>
     <t xml:space="preserve">2.99056148529053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93688440322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95682215690613</t>
+    <t xml:space="preserve">2.93688416481018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95682239532471</t>
   </si>
   <si>
     <t xml:space="preserve">2.90007781982422</t>
@@ -3365,25 +3368,25 @@
     <t xml:space="preserve">2.70224118232727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70530819892883</t>
+    <t xml:space="preserve">2.70530843734741</t>
   </si>
   <si>
     <t xml:space="preserve">2.79732489585876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80652689933777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81419491767883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78045535087585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82646441459656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84793519973755</t>
+    <t xml:space="preserve">2.80652666091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81419467926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78045558929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82646417617798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84793496131897</t>
   </si>
   <si>
     <t xml:space="preserve">2.82339715957642</t>
@@ -3392,7 +3395,7 @@
     <t xml:space="preserve">2.93075013160706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90314507484436</t>
+    <t xml:space="preserve">2.90314531326294</t>
   </si>
   <si>
     <t xml:space="preserve">2.88320803642273</t>
@@ -3401,7 +3404,7 @@
     <t xml:space="preserve">2.86633825302124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87554025650024</t>
+    <t xml:space="preserve">2.87554001808167</t>
   </si>
   <si>
     <t xml:space="preserve">2.9062123298645</t>
@@ -3419,7 +3422,7 @@
     <t xml:space="preserve">2.95068788528442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99669623374939</t>
+    <t xml:space="preserve">2.99669599533081</t>
   </si>
   <si>
     <t xml:space="preserve">3.02890205383301</t>
@@ -3428,10 +3431,10 @@
     <t xml:space="preserve">3.03656983375549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92001485824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9353506565094</t>
+    <t xml:space="preserve">2.92001461982727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93535089492798</t>
   </si>
   <si>
     <t xml:space="preserve">2.88014078140259</t>
@@ -3440,7 +3443,7 @@
     <t xml:space="preserve">2.91234660148621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98135995864868</t>
+    <t xml:space="preserve">2.98136019706726</t>
   </si>
   <si>
     <t xml:space="preserve">3.03350281715393</t>
@@ -3449,13 +3452,13 @@
     <t xml:space="preserve">2.94915413856506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85560321807861</t>
+    <t xml:space="preserve">2.85560297966003</t>
   </si>
   <si>
     <t xml:space="preserve">2.80806040763855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76205205917358</t>
+    <t xml:space="preserve">2.762051820755</t>
   </si>
   <si>
     <t xml:space="preserve">2.77432084083557</t>
@@ -3464,19 +3467,19 @@
     <t xml:space="preserve">2.69917392730713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70684170722961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66083264350891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76051831245422</t>
+    <t xml:space="preserve">2.70684194564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66083288192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76051807403564</t>
   </si>
   <si>
     <t xml:space="preserve">2.71144270896912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58875274658203</t>
+    <t xml:space="preserve">2.58875298500061</t>
   </si>
   <si>
     <t xml:space="preserve">2.73137974739075</t>
@@ -3485,19 +3488,19 @@
     <t xml:space="preserve">2.62249255180359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65009737014771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67770266532898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67463564872742</t>
+    <t xml:space="preserve">2.65009760856628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6777024269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67463541030884</t>
   </si>
   <si>
     <t xml:space="preserve">2.74671578407288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72064423561096</t>
+    <t xml:space="preserve">2.72064447402954</t>
   </si>
   <si>
     <t xml:space="preserve">2.71911072731018</t>
@@ -3506,13 +3509,13 @@
     <t xml:space="preserve">2.69610667228699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66850090026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75438404083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8249306678772</t>
+    <t xml:space="preserve">2.66850066184998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75438380241394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82493090629578</t>
   </si>
   <si>
     <t xml:space="preserve">2.85406947135925</t>
@@ -3521,16 +3524,13 @@
     <t xml:space="preserve">2.89701056480408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97829270362854</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.86327123641968</t>
   </si>
   <si>
     <t xml:space="preserve">2.94148540496826</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03503656387329</t>
+    <t xml:space="preserve">3.03503680229187</t>
   </si>
   <si>
     <t xml:space="preserve">3.02736854553223</t>
@@ -3545,13 +3545,13 @@
     <t xml:space="preserve">2.7850558757782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86480450630188</t>
+    <t xml:space="preserve">2.86480474472046</t>
   </si>
   <si>
     <t xml:space="preserve">2.82799816131592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9706244468689</t>
+    <t xml:space="preserve">2.97062468528748</t>
   </si>
   <si>
     <t xml:space="preserve">2.92445588111877</t>
@@ -3560,10 +3560,10 @@
     <t xml:space="preserve">2.90142869949341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05187344551086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07029509544373</t>
+    <t xml:space="preserve">3.05187320709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07029485702515</t>
   </si>
   <si>
     <t xml:space="preserve">3.15472817420959</t>
@@ -3572,43 +3572,43 @@
     <t xml:space="preserve">3.08871674537659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19771218299866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21459889411926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18850111961365</t>
+    <t xml:space="preserve">3.19771242141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21459913253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18850135803223</t>
   </si>
   <si>
     <t xml:space="preserve">3.2529776096344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16547441482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09485721588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94748306274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80010890960693</t>
+    <t xml:space="preserve">3.16547417640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09485745429993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94748330116272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80010914802551</t>
   </si>
   <si>
     <t xml:space="preserve">2.84769868850708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72028136253357</t>
+    <t xml:space="preserve">2.72028112411499</t>
   </si>
   <si>
     <t xml:space="preserve">2.55602049827576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58979392051697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54066920280457</t>
+    <t xml:space="preserve">2.58979368209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54066896438599</t>
   </si>
   <si>
     <t xml:space="preserve">2.25359654426575</t>
@@ -3617,10 +3617,10 @@
     <t xml:space="preserve">2.24592089653015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33342432975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53452849388123</t>
+    <t xml:space="preserve">2.33342409133911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5345287322998</t>
   </si>
   <si>
     <t xml:space="preserve">2.40557622909546</t>
@@ -3632,7 +3632,7 @@
     <t xml:space="preserve">2.52992296218872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56983661651611</t>
+    <t xml:space="preserve">2.56983685493469</t>
   </si>
   <si>
     <t xml:space="preserve">2.75098443031311</t>
@@ -3641,7 +3641,7 @@
     <t xml:space="preserve">2.72488689422607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76326560974121</t>
+    <t xml:space="preserve">2.76326537132263</t>
   </si>
   <si>
     <t xml:space="preserve">2.78015208244324</t>
@@ -3650,16 +3650,16 @@
     <t xml:space="preserve">2.82927703857422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79550361633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79243350028992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73870301246643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79703879356384</t>
+    <t xml:space="preserve">2.79550337791443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79243326187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73870325088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79703855514526</t>
   </si>
   <si>
     <t xml:space="preserve">2.92292094230652</t>
@@ -3668,49 +3668,49 @@
     <t xml:space="preserve">2.92906141281128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85383915901184</t>
+    <t xml:space="preserve">2.85383892059326</t>
   </si>
   <si>
     <t xml:space="preserve">2.8922176361084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91831517219543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89835834503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80932021141052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7985737323761</t>
+    <t xml:space="preserve">2.91831541061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89835810661316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80931997299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79857397079468</t>
   </si>
   <si>
     <t xml:space="preserve">2.93366694450378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94594812393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8722608089447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93980717658997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88607716560364</t>
+    <t xml:space="preserve">2.94594788551331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87226104736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93980741500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88607740402222</t>
   </si>
   <si>
     <t xml:space="preserve">2.96590495109558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95208859443665</t>
+    <t xml:space="preserve">2.95208883285522</t>
   </si>
   <si>
     <t xml:space="preserve">2.90603423118591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92752623558044</t>
+    <t xml:space="preserve">2.92752599716187</t>
   </si>
   <si>
     <t xml:space="preserve">2.91678023338318</t>
@@ -3719,22 +3719,22 @@
     <t xml:space="preserve">2.90296387672424</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90756940841675</t>
+    <t xml:space="preserve">2.90756916999817</t>
   </si>
   <si>
     <t xml:space="preserve">2.7908980846405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78936290740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75712466239929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68343758583069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78168749809265</t>
+    <t xml:space="preserve">2.78936314582825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75712490081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68343782424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78168725967407</t>
   </si>
   <si>
     <t xml:space="preserve">2.80624938011169</t>
@@ -3746,10 +3746,10 @@
     <t xml:space="preserve">2.81853079795837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88147187232971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86151504516602</t>
+    <t xml:space="preserve">2.88147163391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86151480674744</t>
   </si>
   <si>
     <t xml:space="preserve">2.85230398178101</t>
@@ -3758,7 +3758,7 @@
     <t xml:space="preserve">2.81239032745361</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05271005630493</t>
+    <t xml:space="preserve">3.05270981788635</t>
   </si>
   <si>
     <t xml:space="preserve">3.07706665992737</t>
@@ -3770,7 +3770,7 @@
     <t xml:space="preserve">3.13877034187317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1176609992981</t>
+    <t xml:space="preserve">3.11766123771667</t>
   </si>
   <si>
     <t xml:space="preserve">3.07544279098511</t>
@@ -3782,10 +3782,10 @@
     <t xml:space="preserve">3.01211524009705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99587774276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0380961894989</t>
+    <t xml:space="preserve">2.99587750434875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03809595108032</t>
   </si>
   <si>
     <t xml:space="preserve">3.03322458267212</t>
@@ -3797,10 +3797,10 @@
     <t xml:space="preserve">2.96664953231812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76205277442932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63377404212952</t>
+    <t xml:space="preserve">2.7620530128479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6337742805481</t>
   </si>
   <si>
     <t xml:space="preserve">2.62565517425537</t>
@@ -3809,10 +3809,10 @@
     <t xml:space="preserve">2.74256753921509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66137886047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70197296142578</t>
+    <t xml:space="preserve">2.66137862205505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70197319984436</t>
   </si>
   <si>
     <t xml:space="preserve">2.76367664337158</t>
@@ -3821,16 +3821,16 @@
     <t xml:space="preserve">2.78478598594666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77666735649109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69547772407532</t>
+    <t xml:space="preserve">2.77666711807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6954779624939</t>
   </si>
   <si>
     <t xml:space="preserve">2.73282480239868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69385409355164</t>
+    <t xml:space="preserve">2.69385433197021</t>
   </si>
   <si>
     <t xml:space="preserve">2.70034909248352</t>
@@ -3857,7 +3857,7 @@
     <t xml:space="preserve">2.67274498939514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76042938232422</t>
+    <t xml:space="preserve">2.76042914390564</t>
   </si>
   <si>
     <t xml:space="preserve">2.71821093559265</t>
@@ -3866,7 +3866,7 @@
     <t xml:space="preserve">2.70359683036804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64026927947998</t>
+    <t xml:space="preserve">2.64026951789856</t>
   </si>
   <si>
     <t xml:space="preserve">2.51361417770386</t>
@@ -3875,13 +3875,13 @@
     <t xml:space="preserve">2.52822852134705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57207036018372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69060635566711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61428904533386</t>
+    <t xml:space="preserve">2.57207059860229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69060659408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61428880691528</t>
   </si>
   <si>
     <t xml:space="preserve">2.57856559753418</t>
@@ -3899,19 +3899,19 @@
     <t xml:space="preserve">2.55908012390137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62727904319763</t>
+    <t xml:space="preserve">2.62727928161621</t>
   </si>
   <si>
     <t xml:space="preserve">2.65975475311279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72957754135132</t>
+    <t xml:space="preserve">2.72957730293274</t>
   </si>
   <si>
     <t xml:space="preserve">2.6694974899292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78153872489929</t>
+    <t xml:space="preserve">2.78153848648071</t>
   </si>
   <si>
     <t xml:space="preserve">2.73607230186462</t>
@@ -3932,19 +3932,19 @@
     <t xml:space="preserve">2.66624999046326</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60941767692566</t>
+    <t xml:space="preserve">2.60941743850708</t>
   </si>
   <si>
     <t xml:space="preserve">2.56395149230957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56232786178589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59155583381653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59967470169067</t>
+    <t xml:space="preserve">2.56232762336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59155607223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59967494010925</t>
   </si>
   <si>
     <t xml:space="preserve">2.56070399284363</t>
@@ -3956,19 +3956,19 @@
     <t xml:space="preserve">2.59805107116699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58830857276917</t>
+    <t xml:space="preserve">2.58830833435059</t>
   </si>
   <si>
     <t xml:space="preserve">2.7263298034668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82050895690918</t>
+    <t xml:space="preserve">2.82050919532776</t>
   </si>
   <si>
     <t xml:space="preserve">2.81726145744324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84811329841614</t>
+    <t xml:space="preserve">2.84811353683472</t>
   </si>
   <si>
     <t xml:space="preserve">2.92767882347107</t>
@@ -3977,10 +3977,10 @@
     <t xml:space="preserve">2.90819334983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88870787620544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83999443054199</t>
+    <t xml:space="preserve">2.88870811462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83999466896057</t>
   </si>
   <si>
     <t xml:space="preserve">2.78965735435486</t>
@@ -3989,7 +3989,7 @@
     <t xml:space="preserve">2.85136103630066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7880334854126</t>
+    <t xml:space="preserve">2.78803324699402</t>
   </si>
   <si>
     <t xml:space="preserve">2.76530051231384</t>
@@ -3998,13 +3998,13 @@
     <t xml:space="preserve">2.64514064788818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75393390655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7669243812561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85460877418518</t>
+    <t xml:space="preserve">2.75393414497375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76692414283752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8546085357666</t>
   </si>
   <si>
     <t xml:space="preserve">2.7929048538208</t>
@@ -4022,25 +4022,25 @@
     <t xml:space="preserve">2.64189314842224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75555801391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83512330055237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86435127258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87734127044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9163122177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95853090286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92443108558655</t>
+    <t xml:space="preserve">2.75555777549744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83512306213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86435151100159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87734150886536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91631245613098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95853066444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92443132400513</t>
   </si>
   <si>
     <t xml:space="preserve">2.93904519081116</t>
@@ -4049,7 +4049,7 @@
     <t xml:space="preserve">2.95528316497803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9471640586853</t>
+    <t xml:space="preserve">2.94716429710388</t>
   </si>
   <si>
     <t xml:space="preserve">2.95690679550171</t>
@@ -4064,16 +4064,16 @@
     <t xml:space="preserve">3.10467100143433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87409377098083</t>
+    <t xml:space="preserve">2.87409400939941</t>
   </si>
   <si>
     <t xml:space="preserve">2.84973740577698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89520311355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88708400726318</t>
+    <t xml:space="preserve">2.89520335197449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88708424568176</t>
   </si>
   <si>
     <t xml:space="preserve">2.91793608665466</t>
@@ -4091,25 +4091,25 @@
     <t xml:space="preserve">3.10629463195801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11441349983215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15987944602966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1274037361145</t>
+    <t xml:space="preserve">3.11441373825073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15987968444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12740397453308</t>
   </si>
   <si>
     <t xml:space="preserve">3.16637468338013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14201807975769</t>
+    <t xml:space="preserve">3.14201784133911</t>
   </si>
   <si>
     <t xml:space="preserve">3.1209089756012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08031415939331</t>
+    <t xml:space="preserve">3.08031392097473</t>
   </si>
   <si>
     <t xml:space="preserve">3.07219505310059</t>
@@ -4118,7 +4118,7 @@
     <t xml:space="preserve">3.08193802833557</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09168076515198</t>
+    <t xml:space="preserve">3.0916805267334</t>
   </si>
   <si>
     <t xml:space="preserve">3.09817576408386</t>
@@ -4136,16 +4136,16 @@
     <t xml:space="preserve">3.17449355125427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.182612657547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17611718177795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14039421081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12415623664856</t>
+    <t xml:space="preserve">3.18261241912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17611742019653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14039444923401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12415647506714</t>
   </si>
   <si>
     <t xml:space="preserve">3.17774128913879</t>
@@ -4160,7 +4160,7 @@
     <t xml:space="preserve">3.28003931045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27679181098938</t>
+    <t xml:space="preserve">3.2767915725708</t>
   </si>
   <si>
     <t xml:space="preserve">3.27029657363892</t>
@@ -4193,40 +4193,40 @@
     <t xml:space="preserve">3.48301196098328</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51386404037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53822040557861</t>
+    <t xml:space="preserve">3.51386380195618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53822064399719</t>
   </si>
   <si>
     <t xml:space="preserve">3.52035927772522</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65838074684143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73307466506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65675711631775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66487598419189</t>
+    <t xml:space="preserve">3.65838050842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.733074426651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65675687789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66487550735474</t>
   </si>
   <si>
     <t xml:space="preserve">3.7022225856781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68436098098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65026140213013</t>
+    <t xml:space="preserve">3.68436121940613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65026164054871</t>
   </si>
   <si>
     <t xml:space="preserve">3.62428140640259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66325187683105</t>
+    <t xml:space="preserve">3.66325211524963</t>
   </si>
   <si>
     <t xml:space="preserve">3.59505319595337</t>
@@ -4235,28 +4235,28 @@
     <t xml:space="preserve">3.60804319381714</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6453902721405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59830069541931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6437668800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61616230010986</t>
+    <t xml:space="preserve">3.64539003372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59830093383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64376664161682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61616206169128</t>
   </si>
   <si>
     <t xml:space="preserve">3.68598484992981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69572734832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81101584434509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90032410621643</t>
+    <t xml:space="preserve">3.69572758674622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81101608276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90032386779785</t>
   </si>
   <si>
     <t xml:space="preserve">3.87921476364136</t>
@@ -4268,7 +4268,7 @@
     <t xml:space="preserve">3.89382863044739</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97177076339722</t>
+    <t xml:space="preserve">3.97177052497864</t>
   </si>
   <si>
     <t xml:space="preserve">3.89220547676086</t>
@@ -4283,37 +4283,37 @@
     <t xml:space="preserve">3.41806101799011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41643714904785</t>
+    <t xml:space="preserve">3.41643738746643</t>
   </si>
   <si>
     <t xml:space="preserve">3.19885039329529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21021699905396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0949285030365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37259483337402</t>
+    <t xml:space="preserve">3.21021676063538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09492826461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3725950717926</t>
   </si>
   <si>
     <t xml:space="preserve">3.28491067886353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21995973587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08843326568604</t>
+    <t xml:space="preserve">3.21995949745178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08843302726746</t>
   </si>
   <si>
     <t xml:space="preserve">3.09330439567566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0997998714447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19560265541077</t>
+    <t xml:space="preserve">3.09979939460754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19560289382935</t>
   </si>
   <si>
     <t xml:space="preserve">3.21184062957764</t>
@@ -4322,13 +4322,13 @@
     <t xml:space="preserve">3.1517608165741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27192091941833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28815865516663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31738615036011</t>
+    <t xml:space="preserve">3.27192068099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28815841674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31738638877869</t>
   </si>
   <si>
     <t xml:space="preserve">3.36122846603394</t>
@@ -4343,13 +4343,13 @@
     <t xml:space="preserve">3.4342987537384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47326922416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47002220153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44241714477539</t>
+    <t xml:space="preserve">3.47326946258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47002196311951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44241738319397</t>
   </si>
   <si>
     <t xml:space="preserve">3.34661459922791</t>
@@ -4364,16 +4364,16 @@
     <t xml:space="preserve">3.38720893859863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4310507774353</t>
+    <t xml:space="preserve">3.43105101585388</t>
   </si>
   <si>
     <t xml:space="preserve">3.50736880302429</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36934733390808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38558506965637</t>
+    <t xml:space="preserve">3.36934757232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38558530807495</t>
   </si>
   <si>
     <t xml:space="preserve">3.38233757019043</t>
@@ -6021,6 +6021,9 @@
   </si>
   <si>
     <t xml:space="preserve">16.3449993133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6499996185303</t>
   </si>
 </sst>
 </file>
@@ -39839,7 +39842,7 @@
         <v>2.03996992111206</v>
       </c>
       <c r="G1288" t="s">
-        <v>657</v>
+        <v>972</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -39865,7 +39868,7 @@
         <v>2.07793188095093</v>
       </c>
       <c r="G1289" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -39943,7 +39946,7 @@
         <v>2.10989999771118</v>
       </c>
       <c r="G1292" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -39969,7 +39972,7 @@
         <v>2.14586400985718</v>
       </c>
       <c r="G1293" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -40021,7 +40024,7 @@
         <v>2.31169891357422</v>
       </c>
       <c r="G1295" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -40047,7 +40050,7 @@
         <v>2.49551606178284</v>
       </c>
       <c r="G1296" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -40073,7 +40076,7 @@
         <v>2.45755410194397</v>
       </c>
       <c r="G1297" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -40099,7 +40102,7 @@
         <v>2.48752403259277</v>
       </c>
       <c r="G1298" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -40125,7 +40128,7 @@
         <v>2.47153997421265</v>
       </c>
       <c r="G1299" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -40151,7 +40154,7 @@
         <v>2.48752403259277</v>
       </c>
       <c r="G1300" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -40177,7 +40180,7 @@
         <v>2.45355796813965</v>
       </c>
       <c r="G1301" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -40203,7 +40206,7 @@
         <v>2.49951195716858</v>
       </c>
       <c r="G1302" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -40229,7 +40232,7 @@
         <v>2.44756388664246</v>
       </c>
       <c r="G1303" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -40255,7 +40258,7 @@
         <v>2.39361810684204</v>
       </c>
       <c r="G1304" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -40281,7 +40284,7 @@
         <v>2.42159008979797</v>
       </c>
       <c r="G1305" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -40307,7 +40310,7 @@
         <v>2.40960192680359</v>
       </c>
       <c r="G1306" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -40333,7 +40336,7 @@
         <v>2.40560603141785</v>
       </c>
       <c r="G1307" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -40359,7 +40362,7 @@
         <v>2.41559600830078</v>
       </c>
       <c r="G1308" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -40385,7 +40388,7 @@
         <v>2.39161992073059</v>
       </c>
       <c r="G1309" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -40411,7 +40414,7 @@
         <v>2.38362789154053</v>
       </c>
       <c r="G1310" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -40437,7 +40440,7 @@
         <v>2.44157004356384</v>
       </c>
       <c r="G1311" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -40463,7 +40466,7 @@
         <v>2.42758393287659</v>
       </c>
       <c r="G1312" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -40489,7 +40492,7 @@
         <v>2.44157004356384</v>
       </c>
       <c r="G1313" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -40515,7 +40518,7 @@
         <v>2.41759395599365</v>
       </c>
       <c r="G1314" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -40541,7 +40544,7 @@
         <v>2.44756388664246</v>
       </c>
       <c r="G1315" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -40567,7 +40570,7 @@
         <v>2.47553610801697</v>
       </c>
       <c r="G1316" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -40593,7 +40596,7 @@
         <v>2.47153997421265</v>
       </c>
       <c r="G1317" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -40619,7 +40622,7 @@
         <v>2.46554589271545</v>
       </c>
       <c r="G1318" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -40645,7 +40648,7 @@
         <v>2.54946303367615</v>
       </c>
       <c r="G1319" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -40671,7 +40674,7 @@
         <v>2.61939311027527</v>
       </c>
       <c r="G1320" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -40697,7 +40700,7 @@
         <v>2.71729588508606</v>
       </c>
       <c r="G1321" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -40723,7 +40726,7 @@
         <v>2.8271861076355</v>
       </c>
       <c r="G1322" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -40749,7 +40752,7 @@
         <v>2.88512897491455</v>
       </c>
       <c r="G1323" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -40775,7 +40778,7 @@
         <v>2.84716701507568</v>
       </c>
       <c r="G1324" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -40801,7 +40804,7 @@
         <v>2.84716701507568</v>
       </c>
       <c r="G1325" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -40827,7 +40830,7 @@
         <v>2.81719589233398</v>
       </c>
       <c r="G1326" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -40853,7 +40856,7 @@
         <v>2.78722596168518</v>
       </c>
       <c r="G1327" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -40879,7 +40882,7 @@
         <v>2.85116291046143</v>
       </c>
       <c r="G1328" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -40905,7 +40908,7 @@
         <v>2.82518792152405</v>
       </c>
       <c r="G1329" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -40931,7 +40934,7 @@
         <v>2.84716701507568</v>
       </c>
       <c r="G1330" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -40957,7 +40960,7 @@
         <v>2.82918405532837</v>
       </c>
       <c r="G1331" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -40983,7 +40986,7 @@
         <v>2.94307088851929</v>
       </c>
       <c r="G1332" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -41009,7 +41012,7 @@
         <v>2.85316109657288</v>
       </c>
       <c r="G1333" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -41035,7 +41038,7 @@
         <v>2.89711689949036</v>
       </c>
       <c r="G1334" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -41061,7 +41064,7 @@
         <v>2.89711689949036</v>
       </c>
       <c r="G1335" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -41087,7 +41090,7 @@
         <v>2.89312100410461</v>
       </c>
       <c r="G1336" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -41113,7 +41116,7 @@
         <v>2.84716701507568</v>
       </c>
       <c r="G1337" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -41139,7 +41142,7 @@
         <v>2.82518792152405</v>
       </c>
       <c r="G1338" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -41165,7 +41168,7 @@
         <v>2.86914491653442</v>
       </c>
       <c r="G1339" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -41191,7 +41194,7 @@
         <v>2.87114310264587</v>
       </c>
       <c r="G1340" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -41217,7 +41220,7 @@
         <v>2.95705699920654</v>
       </c>
       <c r="G1341" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -41243,7 +41246,7 @@
         <v>2.97304105758667</v>
       </c>
       <c r="G1342" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -41269,7 +41272,7 @@
         <v>3.00301194190979</v>
       </c>
       <c r="G1343" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -41295,7 +41298,7 @@
         <v>3.04497003555298</v>
       </c>
       <c r="G1344" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -41321,7 +41324,7 @@
         <v>2.95905494689941</v>
       </c>
       <c r="G1345" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -41347,7 +41350,7 @@
         <v>2.9710431098938</v>
       </c>
       <c r="G1346" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -41373,7 +41376,7 @@
         <v>2.97503900527954</v>
       </c>
       <c r="G1347" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -41399,7 +41402,7 @@
         <v>3.04497003555298</v>
       </c>
       <c r="G1348" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -41425,7 +41428,7 @@
         <v>3.13488006591797</v>
       </c>
       <c r="G1349" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -41451,7 +41454,7 @@
         <v>3.17484092712402</v>
       </c>
       <c r="G1350" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -41477,7 +41480,7 @@
         <v>3.28273296356201</v>
       </c>
       <c r="G1351" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -41503,7 +41506,7 @@
         <v>3.37264394760132</v>
       </c>
       <c r="G1352" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -41529,7 +41532,7 @@
         <v>3.49652004241943</v>
       </c>
       <c r="G1353" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -41555,7 +41558,7 @@
         <v>3.46255397796631</v>
       </c>
       <c r="G1354" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -41581,7 +41584,7 @@
         <v>3.44257402420044</v>
       </c>
       <c r="G1355" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -41607,7 +41610,7 @@
         <v>3.57444310188293</v>
       </c>
       <c r="G1356" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -41633,7 +41636,7 @@
         <v>3.62239503860474</v>
       </c>
       <c r="G1357" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -41659,7 +41662,7 @@
         <v>3.68633198738098</v>
       </c>
       <c r="G1358" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -41685,7 +41688,7 @@
         <v>3.81820011138916</v>
       </c>
       <c r="G1359" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -41711,7 +41714,7 @@
         <v>3.79022789001465</v>
       </c>
       <c r="G1360" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -41737,7 +41740,7 @@
         <v>3.78623199462891</v>
       </c>
       <c r="G1361" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -41763,7 +41766,7 @@
         <v>3.89212703704834</v>
       </c>
       <c r="G1362" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -41789,7 +41792,7 @@
         <v>3.89612293243408</v>
       </c>
       <c r="G1363" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -41815,7 +41818,7 @@
         <v>3.87814092636108</v>
       </c>
       <c r="G1364" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -41841,7 +41844,7 @@
         <v>3.94207692146301</v>
       </c>
       <c r="G1365" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -41867,7 +41870,7 @@
         <v>3.92409491539001</v>
       </c>
       <c r="G1366" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -41893,7 +41896,7 @@
         <v>3.91210699081421</v>
       </c>
       <c r="G1367" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -41919,7 +41922,7 @@
         <v>3.94007897377014</v>
       </c>
       <c r="G1368" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -41945,7 +41948,7 @@
         <v>4.01800203323364</v>
       </c>
       <c r="G1369" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -41971,7 +41974,7 @@
         <v>4.00401592254639</v>
       </c>
       <c r="G1370" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -41997,7 +42000,7 @@
         <v>3.9840350151062</v>
       </c>
       <c r="G1371" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -42023,7 +42026,7 @@
         <v>4.10791206359863</v>
       </c>
       <c r="G1372" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -42049,7 +42052,7 @@
         <v>4.027991771698</v>
       </c>
       <c r="G1373" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -42075,7 +42078,7 @@
         <v>4.05796194076538</v>
       </c>
       <c r="G1374" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -42101,7 +42104,7 @@
         <v>4.15986013412476</v>
       </c>
       <c r="G1375" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -42127,7 +42130,7 @@
         <v>4.1898307800293</v>
       </c>
       <c r="G1376" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -42153,7 +42156,7 @@
         <v>4.15386581420898</v>
       </c>
       <c r="G1377" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -42179,7 +42182,7 @@
         <v>4.13588380813599</v>
       </c>
       <c r="G1378" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -42205,7 +42208,7 @@
         <v>4.07594394683838</v>
       </c>
       <c r="G1379" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -42231,7 +42234,7 @@
         <v>3.99002909660339</v>
       </c>
       <c r="G1380" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -42257,7 +42260,7 @@
         <v>3.89212703704834</v>
       </c>
       <c r="G1381" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -42283,7 +42286,7 @@
         <v>3.86415505409241</v>
       </c>
       <c r="G1382" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -42309,7 +42312,7 @@
         <v>3.85616302490234</v>
       </c>
       <c r="G1383" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -42335,7 +42338,7 @@
         <v>3.83618211746216</v>
       </c>
       <c r="G1384" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -42361,7 +42364,7 @@
         <v>3.79622197151184</v>
       </c>
       <c r="G1385" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -42387,7 +42390,7 @@
         <v>3.78023791313171</v>
       </c>
       <c r="G1386" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -42413,7 +42416,7 @@
         <v>3.68832993507385</v>
       </c>
       <c r="G1387" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -42439,7 +42442,7 @@
         <v>3.65036702156067</v>
       </c>
       <c r="G1388" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -42465,7 +42468,7 @@
         <v>3.6483690738678</v>
       </c>
       <c r="G1389" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -42491,7 +42494,7 @@
         <v>3.56445288658142</v>
       </c>
       <c r="G1390" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -42517,7 +42520,7 @@
         <v>3.64037704467773</v>
       </c>
       <c r="G1391" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -42543,7 +42546,7 @@
         <v>3.63837909698486</v>
       </c>
       <c r="G1392" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -42569,7 +42572,7 @@
         <v>3.69632196426392</v>
       </c>
       <c r="G1393" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -42595,7 +42598,7 @@
         <v>3.60441303253174</v>
       </c>
       <c r="G1394" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -42621,7 +42624,7 @@
         <v>3.69632196426392</v>
       </c>
       <c r="G1395" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -42647,7 +42650,7 @@
         <v>3.65436291694641</v>
       </c>
       <c r="G1396" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -42673,7 +42676,7 @@
         <v>3.68832993507385</v>
       </c>
       <c r="G1397" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -42699,7 +42702,7 @@
         <v>3.63638091087341</v>
       </c>
       <c r="G1398" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -42725,7 +42728,7 @@
         <v>3.72229599952698</v>
       </c>
       <c r="G1399" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -42751,7 +42754,7 @@
         <v>3.62439298629761</v>
       </c>
       <c r="G1400" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -42777,7 +42780,7 @@
         <v>3.58443307876587</v>
       </c>
       <c r="G1401" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -42803,7 +42806,7 @@
         <v>3.54846906661987</v>
       </c>
       <c r="G1402" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -42829,7 +42832,7 @@
         <v>3.70431399345398</v>
       </c>
       <c r="G1403" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -42855,7 +42858,7 @@
         <v>3.64237499237061</v>
       </c>
       <c r="G1404" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -42881,7 +42884,7 @@
         <v>3.62039709091187</v>
       </c>
       <c r="G1405" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -42907,7 +42910,7 @@
         <v>3.63638091087341</v>
       </c>
       <c r="G1406" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -42933,7 +42936,7 @@
         <v>3.55046701431274</v>
       </c>
       <c r="G1407" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -42959,7 +42962,7 @@
         <v>3.48253393173218</v>
       </c>
       <c r="G1408" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -42985,7 +42988,7 @@
         <v>3.36265397071838</v>
       </c>
       <c r="G1409" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -43011,7 +43014,7 @@
         <v>3.47254395484924</v>
       </c>
       <c r="G1410" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -43037,7 +43040,7 @@
         <v>3.56045699119568</v>
       </c>
       <c r="G1411" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -43063,7 +43066,7 @@
         <v>3.59242510795593</v>
       </c>
       <c r="G1412" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -43089,7 +43092,7 @@
         <v>3.62639093399048</v>
       </c>
       <c r="G1413" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -43115,7 +43118,7 @@
         <v>3.81220602989197</v>
       </c>
       <c r="G1414" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -43141,7 +43144,7 @@
         <v>3.76425409317017</v>
       </c>
       <c r="G1415" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -43167,7 +43170,7 @@
         <v>3.83418393135071</v>
       </c>
       <c r="G1416" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -43193,7 +43196,7 @@
         <v>3.78822994232178</v>
       </c>
       <c r="G1417" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -43219,7 +43222,7 @@
         <v>3.71430397033691</v>
       </c>
       <c r="G1418" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -43245,7 +43248,7 @@
         <v>3.72629189491272</v>
       </c>
       <c r="G1419" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -43271,7 +43274,7 @@
         <v>3.72429394721985</v>
       </c>
       <c r="G1420" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -43297,7 +43300,7 @@
         <v>3.69831991195679</v>
       </c>
       <c r="G1421" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -43323,7 +43326,7 @@
         <v>3.70631194114685</v>
       </c>
       <c r="G1422" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -43349,7 +43352,7 @@
         <v>3.80221605300903</v>
       </c>
       <c r="G1423" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -43375,7 +43378,7 @@
         <v>3.84617304801941</v>
       </c>
       <c r="G1424" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -43401,7 +43404,7 @@
         <v>3.78423404693604</v>
       </c>
       <c r="G1425" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -43427,7 +43430,7 @@
         <v>3.86615300178528</v>
       </c>
       <c r="G1426" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -43453,7 +43456,7 @@
         <v>3.81420397758484</v>
       </c>
       <c r="G1427" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -43479,7 +43482,7 @@
         <v>3.8102080821991</v>
       </c>
       <c r="G1428" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -43505,7 +43508,7 @@
         <v>3.79622197151184</v>
       </c>
       <c r="G1429" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -43531,7 +43534,7 @@
         <v>3.69432401657104</v>
       </c>
       <c r="G1430" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -43557,7 +43560,7 @@
         <v>3.72829008102417</v>
       </c>
       <c r="G1431" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -43583,7 +43586,7 @@
         <v>3.70830988883972</v>
       </c>
       <c r="G1432" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -43609,7 +43612,7 @@
         <v>3.69432401657104</v>
       </c>
       <c r="G1433" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -43635,7 +43638,7 @@
         <v>3.75026798248291</v>
       </c>
       <c r="G1434" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -43661,7 +43664,7 @@
         <v>3.77624201774597</v>
       </c>
       <c r="G1435" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -43687,7 +43690,7 @@
         <v>3.90811109542847</v>
       </c>
       <c r="G1436" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -43713,7 +43716,7 @@
         <v>3.9181010723114</v>
       </c>
       <c r="G1437" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -43739,7 +43742,7 @@
         <v>3.88613295555115</v>
       </c>
       <c r="G1438" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -43765,7 +43768,7 @@
         <v>3.89012908935547</v>
       </c>
       <c r="G1439" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -43791,7 +43794,7 @@
         <v>3.84817099571228</v>
       </c>
       <c r="G1440" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -43817,7 +43820,7 @@
         <v>3.89212703704834</v>
       </c>
       <c r="G1441" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -43843,7 +43846,7 @@
         <v>3.89612293243408</v>
       </c>
       <c r="G1442" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -43869,7 +43872,7 @@
         <v>3.82619190216064</v>
       </c>
       <c r="G1443" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -43895,7 +43898,7 @@
         <v>3.85216689109802</v>
       </c>
       <c r="G1444" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -43921,7 +43924,7 @@
         <v>3.77823996543884</v>
       </c>
       <c r="G1445" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -43947,7 +43950,7 @@
         <v>3.70231604576111</v>
       </c>
       <c r="G1446" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -43973,7 +43976,7 @@
         <v>3.74427390098572</v>
       </c>
       <c r="G1447" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -43999,7 +44002,7 @@
         <v>3.68832993507385</v>
       </c>
       <c r="G1448" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -44025,7 +44028,7 @@
         <v>3.70830988883972</v>
       </c>
       <c r="G1449" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -44051,7 +44054,7 @@
         <v>3.67034792900085</v>
       </c>
       <c r="G1450" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -44077,7 +44080,7 @@
         <v>3.60241508483887</v>
       </c>
       <c r="G1451" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -44103,7 +44106,7 @@
         <v>3.68633198738098</v>
       </c>
       <c r="G1452" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -44129,7 +44132,7 @@
         <v>3.60840892791748</v>
       </c>
       <c r="G1453" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -44155,7 +44158,7 @@
         <v>3.52049708366394</v>
       </c>
       <c r="G1454" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -44181,7 +44184,7 @@
         <v>3.52449297904968</v>
       </c>
       <c r="G1455" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -44207,7 +44210,7 @@
         <v>3.64437294006348</v>
       </c>
       <c r="G1456" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -44233,7 +44236,7 @@
         <v>3.65636110305786</v>
       </c>
       <c r="G1457" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -44259,7 +44262,7 @@
         <v>3.6663510799408</v>
       </c>
       <c r="G1458" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -44285,7 +44288,7 @@
         <v>3.69632196426392</v>
       </c>
       <c r="G1459" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -44311,7 +44314,7 @@
         <v>3.63638091087341</v>
       </c>
       <c r="G1460" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -44337,7 +44340,7 @@
         <v>3.62239503860474</v>
       </c>
       <c r="G1461" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -44363,7 +44366,7 @@
         <v>3.68233609199524</v>
       </c>
       <c r="G1462" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -44389,7 +44392,7 @@
         <v>3.71030807495117</v>
       </c>
       <c r="G1463" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -44415,7 +44418,7 @@
         <v>3.67833995819092</v>
       </c>
       <c r="G1464" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -44441,7 +44444,7 @@
         <v>3.81820011138916</v>
       </c>
       <c r="G1465" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -44467,7 +44470,7 @@
         <v>3.78223609924316</v>
       </c>
       <c r="G1466" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -44493,7 +44496,7 @@
         <v>3.7562620639801</v>
       </c>
       <c r="G1467" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -44519,7 +44522,7 @@
         <v>3.73428392410278</v>
       </c>
       <c r="G1468" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -44545,7 +44548,7 @@
         <v>3.74627208709717</v>
       </c>
       <c r="G1469" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -44571,7 +44574,7 @@
         <v>3.78623199462891</v>
       </c>
       <c r="G1470" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -44597,7 +44600,7 @@
         <v>3.73428392410278</v>
       </c>
       <c r="G1471" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -44623,7 +44626,7 @@
         <v>3.77624201774597</v>
       </c>
       <c r="G1472" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -44649,7 +44652,7 @@
         <v>3.85016894340515</v>
       </c>
       <c r="G1473" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -44675,7 +44678,7 @@
         <v>3.87614297866821</v>
       </c>
       <c r="G1474" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -44701,7 +44704,7 @@
         <v>3.88613295555115</v>
       </c>
       <c r="G1475" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -44727,7 +44730,7 @@
         <v>3.89412498474121</v>
       </c>
       <c r="G1476" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -44753,7 +44756,7 @@
         <v>3.84417510032654</v>
       </c>
       <c r="G1477" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -44779,7 +44782,7 @@
         <v>3.90411496162415</v>
       </c>
       <c r="G1478" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -44805,7 +44808,7 @@
         <v>3.94607305526733</v>
       </c>
       <c r="G1479" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -44831,7 +44834,7 @@
         <v>3.95606303215027</v>
       </c>
       <c r="G1480" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -44857,7 +44860,7 @@
         <v>3.8042140007019</v>
       </c>
       <c r="G1481" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -44883,7 +44886,7 @@
         <v>3.82419395446777</v>
       </c>
       <c r="G1482" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -44909,7 +44912,7 @@
         <v>3.75226593017578</v>
       </c>
       <c r="G1483" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -44935,7 +44938,7 @@
         <v>3.79422402381897</v>
       </c>
       <c r="G1484" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -44961,7 +44964,7 @@
         <v>3.85016894340515</v>
       </c>
       <c r="G1485" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -44987,7 +44990,7 @@
         <v>3.85616302490234</v>
       </c>
       <c r="G1486" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -45013,7 +45016,7 @@
         <v>3.88413500785828</v>
       </c>
       <c r="G1487" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -45039,7 +45042,7 @@
         <v>3.95206689834595</v>
       </c>
       <c r="G1488" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -45065,7 +45068,7 @@
         <v>3.99002909660339</v>
       </c>
       <c r="G1489" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -45091,7 +45094,7 @@
         <v>3.84217691421509</v>
       </c>
       <c r="G1490" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -45117,7 +45120,7 @@
         <v>3.8102080821991</v>
       </c>
       <c r="G1491" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -45143,7 +45146,7 @@
         <v>3.7562620639801</v>
       </c>
       <c r="G1492" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -45169,7 +45172,7 @@
         <v>3.72029805183411</v>
       </c>
       <c r="G1493" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -45195,7 +45198,7 @@
         <v>3.68633198738098</v>
       </c>
       <c r="G1494" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -45221,7 +45224,7 @@
         <v>3.65835905075073</v>
       </c>
       <c r="G1495" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -45247,7 +45250,7 @@
         <v>3.59841895103455</v>
       </c>
       <c r="G1496" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -45273,7 +45276,7 @@
         <v>3.61440300941467</v>
       </c>
       <c r="G1497" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -45299,7 +45302,7 @@
         <v>3.51650094985962</v>
       </c>
       <c r="G1498" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -45325,7 +45328,7 @@
         <v>3.52649092674255</v>
       </c>
       <c r="G1499" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -45351,7 +45354,7 @@
         <v>3.46655011177063</v>
       </c>
       <c r="G1500" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -45377,7 +45380,7 @@
         <v>3.59642100334167</v>
       </c>
       <c r="G1501" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -45403,7 +45406,7 @@
         <v>3.53248500823975</v>
       </c>
       <c r="G1502" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -45429,7 +45432,7 @@
         <v>3.37264394760132</v>
       </c>
       <c r="G1503" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -45455,7 +45458,7 @@
         <v>3.55845904350281</v>
       </c>
       <c r="G1504" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -45481,7 +45484,7 @@
         <v>3.41659998893738</v>
       </c>
       <c r="G1505" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -45507,7 +45510,7 @@
         <v>3.45256400108337</v>
       </c>
       <c r="G1506" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -45533,7 +45536,7 @@
         <v>3.48852801322937</v>
       </c>
       <c r="G1507" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -45559,7 +45562,7 @@
         <v>3.48453211784363</v>
       </c>